--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE239659-947C-4324-B3E8-9849E706F529}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12870E80-828B-4F9D-821D-6D331CA29027}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="502">
   <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
@@ -1542,12 +1542,18 @@
   <si>
     <t>LANTERNA SCANIA SUPER LE</t>
   </si>
+  <si>
+    <t>SUPORTE PARALAMA TRASEIRO SCANIA LD</t>
+  </si>
+  <si>
+    <t>SUPORTE PARALAMA TRASEIRO SCANIA LE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1584,6 +1590,14 @@
       <sz val="12"/>
       <color rgb="FF242424"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1723,7 +1737,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1784,6 +1798,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1799,6 +1814,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5374,10 +5393,10 @@
     </row>
     <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="5">
-        <v>1010059549</v>
+        <v>1010026842</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>468</v>
@@ -5385,10 +5404,10 @@
     </row>
     <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="5">
-        <v>1010020552</v>
+        <v>1010026841</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>291</v>
+        <v>501</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>468</v>
@@ -5396,10 +5415,10 @@
     </row>
     <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="5">
-        <v>1040078895</v>
+        <v>1010059549</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>468</v>
@@ -5407,10 +5426,10 @@
     </row>
     <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="5">
-        <v>1040024309</v>
+        <v>1010020552</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>468</v>
@@ -5418,10 +5437,10 @@
     </row>
     <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="5">
-        <v>1040024323</v>
+        <v>1040078895</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>468</v>
@@ -5429,10 +5448,10 @@
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="5">
-        <v>1040024322</v>
+        <v>1040024309</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>468</v>
@@ -5440,10 +5459,10 @@
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="5">
-        <v>1040024314</v>
+        <v>1040024323</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>468</v>
@@ -5451,10 +5470,10 @@
     </row>
     <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="5">
-        <v>1010059685</v>
+        <v>1040024322</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>468</v>
@@ -5462,10 +5481,10 @@
     </row>
     <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="5">
-        <v>1010059687</v>
+        <v>1040024314</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>468</v>
@@ -5473,76 +5492,76 @@
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="5">
+        <v>1010059685</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A311" s="5">
+        <v>1010059687</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A312" s="5">
         <v>1010077469</v>
       </c>
-      <c r="B310" s="5" t="s">
+      <c r="B312" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="C310" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A311" s="10">
+      <c r="C312" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A313" s="10">
         <v>1010077470</v>
       </c>
-      <c r="B311" s="5" t="s">
+      <c r="B313" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="C311" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A312" s="5" t="s">
+      <c r="C313" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A314" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B312" s="9" t="s">
+      <c r="B314" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="C312" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A313" s="11">
+      <c r="C314" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A315" s="11">
         <v>1010084108</v>
       </c>
-      <c r="B313" s="5" t="s">
+      <c r="B315" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="C313" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A314" s="11">
+      <c r="C315" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A316" s="11">
         <v>1010042884</v>
       </c>
-      <c r="B314" s="5" t="s">
+      <c r="B316" s="5" t="s">
         <v>496</v>
-      </c>
-      <c r="C314" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A315" s="5">
-        <v>1040043537</v>
-      </c>
-      <c r="B315" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C315" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A316" s="5">
-        <v>1010046401</v>
-      </c>
-      <c r="B316" s="5" t="s">
-        <v>305</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>468</v>
@@ -5550,10 +5569,10 @@
     </row>
     <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" s="5">
-        <v>1010062007</v>
+        <v>1040043537</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>468</v>
@@ -5561,10 +5580,10 @@
     </row>
     <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="5">
-        <v>1010051284</v>
+        <v>1010046401</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>468</v>
@@ -5572,10 +5591,10 @@
     </row>
     <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="5">
-        <v>1010027788</v>
+        <v>1010062007</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>468</v>
@@ -5583,10 +5602,10 @@
     </row>
     <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="5">
-        <v>1010027786</v>
+        <v>1010051284</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>468</v>
@@ -5594,21 +5613,21 @@
     </row>
     <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="5">
-        <v>1010026889</v>
+        <v>1010027788</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A322" s="6">
-        <v>1010042358</v>
+      <c r="A322" s="5">
+        <v>1010027786</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>468</v>
@@ -5616,21 +5635,21 @@
     </row>
     <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="5">
-        <v>1040023848</v>
+        <v>1010026889</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A324" s="5">
-        <v>1010042341</v>
+      <c r="A324" s="6">
+        <v>1010042358</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>468</v>
@@ -5638,10 +5657,10 @@
     </row>
     <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="5">
-        <v>1040023858</v>
+        <v>1040023848</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>468</v>
@@ -5649,10 +5668,10 @@
     </row>
     <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="5">
-        <v>1040023843</v>
+        <v>1010042341</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>468</v>
@@ -5660,10 +5679,10 @@
     </row>
     <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="5">
-        <v>1040077411</v>
+        <v>1040023858</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>468</v>
@@ -5671,10 +5690,10 @@
     </row>
     <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="5">
-        <v>1040077410</v>
+        <v>1040023843</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>468</v>
@@ -5682,10 +5701,10 @@
     </row>
     <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="5">
-        <v>1010062008</v>
+        <v>1040077411</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>468</v>
@@ -5693,10 +5712,10 @@
     </row>
     <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="5">
-        <v>1040040960</v>
+        <v>1040077410</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>468</v>
@@ -5704,10 +5723,10 @@
     </row>
     <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="5">
-        <v>409578</v>
+        <v>1010062008</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>468</v>
@@ -5715,10 +5734,10 @@
     </row>
     <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="5">
-        <v>1040077360</v>
+        <v>1040040960</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>468</v>
@@ -5726,10 +5745,10 @@
     </row>
     <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="5">
-        <v>1010064470</v>
+        <v>409578</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>468</v>
@@ -5737,10 +5756,10 @@
     </row>
     <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="5">
-        <v>1010021991</v>
+        <v>1040077360</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>468</v>
@@ -5748,10 +5767,10 @@
     </row>
     <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="5">
-        <v>1010021960</v>
+        <v>1010064470</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>468</v>
@@ -5759,10 +5778,10 @@
     </row>
     <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="5">
-        <v>1010031545</v>
+        <v>1010021991</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>468</v>
@@ -5770,10 +5789,10 @@
     </row>
     <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="5">
-        <v>1010031690</v>
+        <v>1010021960</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>490</v>
+        <v>324</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>468</v>
@@ -5781,10 +5800,10 @@
     </row>
     <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="5">
-        <v>1010022590</v>
+        <v>1010031545</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>468</v>
@@ -5792,10 +5811,10 @@
     </row>
     <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="5">
-        <v>1040098643</v>
+        <v>1010031690</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>327</v>
+        <v>490</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>468</v>
@@ -5803,10 +5822,10 @@
     </row>
     <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="5">
-        <v>1010086020</v>
+        <v>1010022590</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>468</v>
@@ -5814,10 +5833,10 @@
     </row>
     <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="5">
-        <v>1010046550</v>
+        <v>1040098643</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>468</v>
@@ -5825,10 +5844,10 @@
     </row>
     <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="5">
-        <v>1010046402</v>
+        <v>1010086020</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>468</v>
@@ -5836,10 +5855,10 @@
     </row>
     <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="5">
-        <v>1010060291</v>
+        <v>1010046550</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>468</v>
@@ -5847,10 +5866,10 @@
     </row>
     <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="5">
-        <v>1010050920</v>
+        <v>1010046402</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>468</v>
@@ -5858,10 +5877,10 @@
     </row>
     <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="5">
-        <v>1040077412</v>
+        <v>1010060291</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>468</v>
@@ -5869,10 +5888,10 @@
     </row>
     <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="5">
-        <v>1010042609</v>
+        <v>1010050920</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>468</v>
@@ -5880,10 +5899,10 @@
     </row>
     <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="5">
-        <v>417701</v>
+        <v>1040077412</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>468</v>
@@ -5891,10 +5910,10 @@
     </row>
     <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="5">
-        <v>399384</v>
+        <v>1010042609</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>468</v>
@@ -5902,10 +5921,10 @@
     </row>
     <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="5">
-        <v>1010024086</v>
+        <v>417701</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>497</v>
+        <v>335</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>468</v>
@@ -5913,10 +5932,10 @@
     </row>
     <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="5">
-        <v>1040077345</v>
+        <v>399384</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>468</v>
@@ -5924,10 +5943,10 @@
     </row>
     <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="5">
-        <v>1010084315</v>
+        <v>1010024086</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>338</v>
+        <v>497</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>468</v>
@@ -5935,10 +5954,10 @@
     </row>
     <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="5">
-        <v>399253</v>
+        <v>1040077345</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>468</v>
@@ -5946,21 +5965,21 @@
     </row>
     <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="5">
-        <v>1010084317</v>
+        <v>1010084315</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A354" s="18">
-        <v>1010085369</v>
+      <c r="A354" s="5">
+        <v>399253</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>468</v>
@@ -5968,21 +5987,21 @@
     </row>
     <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="5">
-        <v>1010085370</v>
+        <v>1010084317</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A356" s="5">
-        <v>1010085204</v>
+      <c r="A356" s="18">
+        <v>1010085369</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>468</v>
@@ -5990,10 +6009,10 @@
     </row>
     <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="5">
-        <v>1010003966</v>
+        <v>1010085370</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>468</v>
@@ -6001,10 +6020,10 @@
     </row>
     <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="5">
-        <v>1010003967</v>
+        <v>1010085204</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>468</v>
@@ -6012,10 +6031,10 @@
     </row>
     <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="5">
-        <v>65219</v>
+        <v>1010003966</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>468</v>
@@ -6023,10 +6042,10 @@
     </row>
     <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="5">
-        <v>10168</v>
+        <v>1010003967</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>468</v>
@@ -6034,10 +6053,10 @@
     </row>
     <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="5">
-        <v>1010083792</v>
+        <v>65219</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>468</v>
@@ -6045,10 +6064,10 @@
     </row>
     <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="5">
-        <v>1040077414</v>
+        <v>10168</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>468</v>
@@ -6056,10 +6075,10 @@
     </row>
     <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="5">
-        <v>1010018482</v>
+        <v>1010083792</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>468</v>
@@ -6067,10 +6086,10 @@
     </row>
     <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="5">
-        <v>1010084320</v>
+        <v>1040077414</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>468</v>
@@ -6078,10 +6097,10 @@
     </row>
     <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="5">
-        <v>1010084532</v>
+        <v>1010018482</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>468</v>
@@ -6089,10 +6108,10 @@
     </row>
     <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="5">
-        <v>1010027285</v>
+        <v>1010084320</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>468</v>
@@ -6100,10 +6119,10 @@
     </row>
     <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="5">
-        <v>1040077413</v>
+        <v>1010084532</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>468</v>
@@ -6111,10 +6130,10 @@
     </row>
     <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="5">
-        <v>1010085376</v>
+        <v>1010027285</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>468</v>
@@ -6122,10 +6141,10 @@
     </row>
     <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="5">
-        <v>1010022819</v>
+        <v>1040077413</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>468</v>
@@ -6133,10 +6152,10 @@
     </row>
     <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="5">
-        <v>1010052853</v>
+        <v>1010085376</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>468</v>
@@ -6144,43 +6163,43 @@
     </row>
     <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="5">
-        <v>1010084377</v>
+        <v>1010022819</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A372" s="2">
-        <v>1010062826</v>
+      <c r="A372" s="5">
+        <v>1010052853</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>471</v>
+        <v>357</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="5">
-        <v>1010002592</v>
+        <v>1010084377</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>472</v>
+        <v>358</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A374" s="6">
-        <v>1010001155</v>
+      <c r="A374" s="2">
+        <v>1010062826</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>479</v>
@@ -6188,32 +6207,32 @@
     </row>
     <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="5">
-        <v>1010001062</v>
+        <v>1010002592</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A376" s="5">
-        <v>1010084328</v>
+      <c r="A376" s="6">
+        <v>1010001155</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A377" s="6">
-        <v>1010044502</v>
+      <c r="A377" s="5">
+        <v>1010001062</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>479</v>
@@ -6221,21 +6240,21 @@
     </row>
     <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="5">
-        <v>1010053692</v>
+        <v>1010084328</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A379" s="5">
-        <v>1010083992</v>
+      <c r="A379" s="6">
+        <v>1010044502</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>479</v>
@@ -6243,32 +6262,32 @@
     </row>
     <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="5">
-        <v>1010008578</v>
+        <v>1010053692</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>359</v>
+        <v>477</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="5">
-        <v>1010031694</v>
+        <v>1010083992</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>360</v>
+        <v>478</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="5">
-        <v>1010051997</v>
+        <v>1010008578</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>469</v>
@@ -6276,10 +6295,10 @@
     </row>
     <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" s="5">
-        <v>1010022601</v>
+        <v>1010031694</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C383" s="4" t="s">
         <v>469</v>
@@ -6287,10 +6306,10 @@
     </row>
     <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="5">
-        <v>1010054278</v>
+        <v>1010051997</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>469</v>
@@ -6298,10 +6317,10 @@
     </row>
     <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="5">
-        <v>1010083462</v>
+        <v>1010022601</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>469</v>
@@ -6309,10 +6328,10 @@
     </row>
     <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="5">
-        <v>1010027772</v>
+        <v>1010054278</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C386" s="4" t="s">
         <v>469</v>
@@ -6320,76 +6339,76 @@
     </row>
     <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="5">
-        <v>1010084144</v>
+        <v>1010083462</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C387" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A388" s="10">
-        <v>214055</v>
-      </c>
-      <c r="B388" s="9" t="s">
-        <v>367</v>
+      <c r="A388" s="5">
+        <v>1010027772</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>365</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A389" s="14">
-        <v>1010021956</v>
-      </c>
-      <c r="B389" s="9" t="s">
-        <v>368</v>
+      <c r="A389" s="5">
+        <v>1010084144</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>366</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A390" s="14">
-        <v>1010026464</v>
+      <c r="A390" s="10">
+        <v>214055</v>
       </c>
       <c r="B390" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A391" s="11">
-        <v>1010021957</v>
-      </c>
-      <c r="B391" s="5" t="s">
-        <v>370</v>
+      <c r="A391" s="14">
+        <v>1010021956</v>
+      </c>
+      <c r="B391" s="9" t="s">
+        <v>368</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A392" s="5">
-        <v>1010026462</v>
-      </c>
-      <c r="B392" s="5" t="s">
-        <v>371</v>
+      <c r="A392" s="14">
+        <v>1010026464</v>
+      </c>
+      <c r="B392" s="9" t="s">
+        <v>369</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A393" s="5">
-        <v>1010026551</v>
+      <c r="A393" s="11">
+        <v>1010021957</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>469</v>
@@ -6397,10 +6416,10 @@
     </row>
     <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="5">
-        <v>1010042554</v>
+        <v>1010026462</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C394" s="4" t="s">
         <v>469</v>
@@ -6408,10 +6427,10 @@
     </row>
     <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="5">
-        <v>1010039904</v>
+        <v>1010026551</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C395" s="4" t="s">
         <v>469</v>
@@ -6419,10 +6438,10 @@
     </row>
     <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="5">
-        <v>1010060205</v>
+        <v>1010042554</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>469</v>
@@ -6430,10 +6449,10 @@
     </row>
     <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="5">
-        <v>1010060206</v>
+        <v>1010039904</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>469</v>
@@ -6441,10 +6460,10 @@
     </row>
     <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="5">
-        <v>1010077431</v>
+        <v>1010060205</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>469</v>
@@ -6452,10 +6471,10 @@
     </row>
     <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="5">
-        <v>1010077503</v>
+        <v>1010060206</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>469</v>
@@ -6463,10 +6482,10 @@
     </row>
     <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="5">
-        <v>1010084187</v>
+        <v>1010077431</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>469</v>
@@ -6474,10 +6493,10 @@
     </row>
     <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="5">
-        <v>1010080958</v>
+        <v>1010077503</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>469</v>
@@ -6485,10 +6504,10 @@
     </row>
     <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="5">
-        <v>1010026032</v>
+        <v>1010084187</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>469</v>
@@ -6496,10 +6515,10 @@
     </row>
     <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="5">
-        <v>1010085384</v>
+        <v>1010080958</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>469</v>
@@ -6507,10 +6526,10 @@
     </row>
     <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="5">
-        <v>1010006347</v>
+        <v>1010026032</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>469</v>
@@ -6518,10 +6537,10 @@
     </row>
     <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="5">
-        <v>1010085179</v>
+        <v>1010085384</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>469</v>
@@ -6529,10 +6548,10 @@
     </row>
     <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="5">
-        <v>1010024158</v>
-      </c>
-      <c r="B406" s="10" t="s">
-        <v>385</v>
+        <v>1010006347</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>383</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>469</v>
@@ -6540,10 +6559,10 @@
     </row>
     <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="5">
-        <v>1010024131</v>
-      </c>
-      <c r="B407" s="10" t="s">
-        <v>386</v>
+        <v>1010085179</v>
+      </c>
+      <c r="B407" s="5" t="s">
+        <v>384</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>469</v>
@@ -6551,10 +6570,10 @@
     </row>
     <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="5">
-        <v>1010007160</v>
-      </c>
-      <c r="B408" s="5" t="s">
-        <v>387</v>
+        <v>1010024158</v>
+      </c>
+      <c r="B408" s="10" t="s">
+        <v>385</v>
       </c>
       <c r="C408" s="4" t="s">
         <v>469</v>
@@ -6562,10 +6581,10 @@
     </row>
     <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="5">
-        <v>1010023642</v>
-      </c>
-      <c r="B409" s="5" t="s">
-        <v>388</v>
+        <v>1010024131</v>
+      </c>
+      <c r="B409" s="10" t="s">
+        <v>386</v>
       </c>
       <c r="C409" s="4" t="s">
         <v>469</v>
@@ -6573,10 +6592,10 @@
     </row>
     <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="5">
-        <v>1010007193</v>
-      </c>
-      <c r="B410" s="6" t="s">
-        <v>389</v>
+        <v>1010007160</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>387</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>469</v>
@@ -6584,10 +6603,10 @@
     </row>
     <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="5">
-        <v>1010042637</v>
+        <v>1010023642</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C411" s="4" t="s">
         <v>469</v>
@@ -6595,10 +6614,10 @@
     </row>
     <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="5">
-        <v>1040075323</v>
-      </c>
-      <c r="B412" s="5" t="s">
-        <v>391</v>
+        <v>1010007193</v>
+      </c>
+      <c r="B412" s="6" t="s">
+        <v>389</v>
       </c>
       <c r="C412" s="4" t="s">
         <v>469</v>
@@ -6606,32 +6625,32 @@
     </row>
     <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="5">
-        <v>1040075324</v>
-      </c>
-      <c r="B413" s="10" t="s">
-        <v>392</v>
+        <v>1010042637</v>
+      </c>
+      <c r="B413" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A414" s="19">
-        <v>1040074827</v>
-      </c>
-      <c r="B414" s="10" t="s">
-        <v>498</v>
+      <c r="A414" s="5">
+        <v>1040075323</v>
+      </c>
+      <c r="B414" s="5" t="s">
+        <v>391</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A415" s="19">
-        <v>1040099488</v>
+      <c r="A415" s="5">
+        <v>1040075324</v>
       </c>
       <c r="B415" s="10" t="s">
-        <v>499</v>
+        <v>392</v>
       </c>
       <c r="C415" s="4" t="s">
         <v>469</v>
@@ -6639,10 +6658,10 @@
     </row>
     <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="19">
-        <v>1040083312</v>
+        <v>1040074827</v>
       </c>
       <c r="B416" s="10" t="s">
-        <v>393</v>
+        <v>498</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>469</v>
@@ -6650,10 +6669,10 @@
     </row>
     <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="19">
-        <v>1040077661</v>
+        <v>1040099488</v>
       </c>
       <c r="B417" s="10" t="s">
-        <v>394</v>
+        <v>499</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>469</v>
@@ -6661,54 +6680,54 @@
     </row>
     <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="19">
-        <v>1010085180</v>
-      </c>
-      <c r="B418" s="20" t="s">
-        <v>395</v>
+        <v>1040083312</v>
+      </c>
+      <c r="B418" s="10" t="s">
+        <v>393</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A419" s="11">
-        <v>1040017489</v>
-      </c>
-      <c r="B419" s="11" t="s">
-        <v>396</v>
+      <c r="A419" s="19">
+        <v>1040077661</v>
+      </c>
+      <c r="B419" s="10" t="s">
+        <v>394</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A420" s="11">
-        <v>1010085181</v>
-      </c>
-      <c r="B420" s="5" t="s">
-        <v>397</v>
+      <c r="A420" s="19">
+        <v>1010085180</v>
+      </c>
+      <c r="B420" s="20" t="s">
+        <v>395</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A421" s="5">
-        <v>400175</v>
-      </c>
-      <c r="B421" s="5" t="s">
-        <v>398</v>
+      <c r="A421" s="11">
+        <v>1040017489</v>
+      </c>
+      <c r="B421" s="11" t="s">
+        <v>396</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A422" s="5">
-        <v>1040017505</v>
+      <c r="A422" s="11">
+        <v>1010085181</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>469</v>
@@ -6716,10 +6735,10 @@
     </row>
     <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="5">
-        <v>1040017503</v>
+        <v>400175</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>469</v>
@@ -6727,10 +6746,10 @@
     </row>
     <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="5">
-        <v>1010046445</v>
+        <v>1040017505</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>469</v>
@@ -6738,10 +6757,10 @@
     </row>
     <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="5">
-        <v>1010021033</v>
+        <v>1040017503</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>469</v>
@@ -6749,10 +6768,10 @@
     </row>
     <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="5">
-        <v>1010057142</v>
+        <v>1010046445</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>469</v>
@@ -6760,10 +6779,10 @@
     </row>
     <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="5">
-        <v>1010016356</v>
+        <v>1010021033</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>469</v>
@@ -6771,10 +6790,10 @@
     </row>
     <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="5">
-        <v>1010084363</v>
+        <v>1010057142</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>469</v>
@@ -6782,10 +6801,10 @@
     </row>
     <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="5">
-        <v>1010052021</v>
+        <v>1010016356</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>469</v>
@@ -6793,10 +6812,10 @@
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="5">
-        <v>1040091721</v>
+        <v>1010084363</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>469</v>
@@ -6804,10 +6823,10 @@
     </row>
     <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="5">
-        <v>1010062022</v>
+        <v>1010052021</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>469</v>
@@ -6815,10 +6834,10 @@
     </row>
     <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="5">
-        <v>18336</v>
+        <v>1040091721</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C432" s="4" t="s">
         <v>469</v>
@@ -6826,10 +6845,10 @@
     </row>
     <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="5">
-        <v>229205</v>
+        <v>1010062022</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>469</v>
@@ -6837,10 +6856,10 @@
     </row>
     <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="5">
-        <v>60671</v>
+        <v>18336</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>469</v>
@@ -6848,10 +6867,10 @@
     </row>
     <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="5">
-        <v>1010059726</v>
+        <v>229205</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>469</v>
@@ -6859,10 +6878,10 @@
     </row>
     <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="5">
-        <v>1010008144</v>
+        <v>60671</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>469</v>
@@ -6870,10 +6889,10 @@
     </row>
     <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="5">
-        <v>1010007244</v>
+        <v>1010059726</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C437" s="4" t="s">
         <v>469</v>
@@ -6881,10 +6900,10 @@
     </row>
     <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="5">
-        <v>1010006827</v>
+        <v>1010008144</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>469</v>
@@ -6892,10 +6911,10 @@
     </row>
     <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="5">
-        <v>1040075426</v>
+        <v>1010007244</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>469</v>
@@ -6903,10 +6922,10 @@
     </row>
     <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="5">
-        <v>1040075427</v>
+        <v>1010006827</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>469</v>
@@ -6914,10 +6933,10 @@
     </row>
     <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="5">
-        <v>1010084313</v>
+        <v>1040075426</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>469</v>
@@ -6925,10 +6944,10 @@
     </row>
     <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="5">
-        <v>403459</v>
+        <v>1040075427</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>469</v>
@@ -6936,10 +6955,10 @@
     </row>
     <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="5">
-        <v>1010044828</v>
+        <v>1010084313</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>469</v>
@@ -6947,10 +6966,10 @@
     </row>
     <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="5">
-        <v>1010026973</v>
+        <v>403459</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C444" s="4" t="s">
         <v>469</v>
@@ -6958,43 +6977,43 @@
     </row>
     <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="5">
-        <v>1040017204</v>
+        <v>1010044828</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A446" s="6">
-        <v>1010022119</v>
-      </c>
-      <c r="B446" s="6" t="s">
-        <v>428</v>
+      <c r="A446" s="5">
+        <v>1010026973</v>
+      </c>
+      <c r="B446" s="5" t="s">
+        <v>421</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="5">
-        <v>1010058709</v>
+        <v>1040017204</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="5">
-        <v>1010025711</v>
-      </c>
-      <c r="B448" s="5" t="s">
-        <v>430</v>
+      <c r="A448" s="6">
+        <v>1010022119</v>
+      </c>
+      <c r="B448" s="6" t="s">
+        <v>428</v>
       </c>
       <c r="C448" s="4" t="s">
         <v>480</v>
@@ -7002,10 +7021,10 @@
     </row>
     <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="5">
-        <v>1010059684</v>
+        <v>1010058709</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>480</v>
@@ -7013,10 +7032,10 @@
     </row>
     <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="5">
-        <v>427341</v>
+        <v>1010025711</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>480</v>
@@ -7024,21 +7043,21 @@
     </row>
     <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="5">
-        <v>1010085279</v>
+        <v>1010059684</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="10">
-        <v>1010022588</v>
+      <c r="A452" s="5">
+        <v>427341</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>480</v>
@@ -7046,54 +7065,54 @@
     </row>
     <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="5">
-        <v>1010026864</v>
-      </c>
-      <c r="B453" s="9" t="s">
-        <v>435</v>
+        <v>1010085279</v>
+      </c>
+      <c r="B453" s="5" t="s">
+        <v>433</v>
       </c>
       <c r="C453" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="11">
-        <v>1010030946</v>
-      </c>
-      <c r="B454" s="9" t="s">
-        <v>436</v>
+      <c r="A454" s="10">
+        <v>1010022588</v>
+      </c>
+      <c r="B454" s="5" t="s">
+        <v>434</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A455" s="11">
-        <v>1010022589</v>
-      </c>
-      <c r="B455" s="5" t="s">
-        <v>437</v>
+      <c r="A455" s="5">
+        <v>1010026864</v>
+      </c>
+      <c r="B455" s="9" t="s">
+        <v>435</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="5">
-        <v>1040090143</v>
-      </c>
-      <c r="B456" s="5" t="s">
-        <v>438</v>
+      <c r="A456" s="11">
+        <v>1010030946</v>
+      </c>
+      <c r="B456" s="9" t="s">
+        <v>436</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A457" s="5">
-        <v>1040090138</v>
+      <c r="A457" s="11">
+        <v>1010022589</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>480</v>
@@ -7101,10 +7120,10 @@
     </row>
     <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" s="5">
-        <v>1030001314</v>
+        <v>1040090143</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>480</v>
@@ -7112,10 +7131,10 @@
     </row>
     <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="5">
-        <v>1010052319</v>
+        <v>1040090138</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>480</v>
@@ -7123,10 +7142,10 @@
     </row>
     <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" s="5">
-        <v>1010052320</v>
+        <v>1030001314</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C460" s="4" t="s">
         <v>480</v>
@@ -7134,10 +7153,10 @@
     </row>
     <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" s="5">
-        <v>1030000370</v>
+        <v>1010052319</v>
       </c>
       <c r="B461" s="5" t="s">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="C461" s="4" t="s">
         <v>480</v>
@@ -7145,10 +7164,10 @@
     </row>
     <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="5">
-        <v>1030000366</v>
+        <v>1010052320</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="C462" s="4" t="s">
         <v>480</v>
@@ -7156,10 +7175,10 @@
     </row>
     <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="5">
-        <v>1030000368</v>
+        <v>1030000370</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C463" s="4" t="s">
         <v>480</v>
@@ -7167,10 +7186,10 @@
     </row>
     <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="5">
-        <v>1030000369</v>
+        <v>1030000366</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C464" s="4" t="s">
         <v>480</v>
@@ -7178,10 +7197,10 @@
     </row>
     <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="5">
-        <v>1030000489</v>
+        <v>1030000368</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C465" s="4" t="s">
         <v>480</v>
@@ -7189,10 +7208,10 @@
     </row>
     <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="5">
-        <v>1030000490</v>
+        <v>1030000369</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C466" s="4" t="s">
         <v>480</v>
@@ -7200,10 +7219,10 @@
     </row>
     <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" s="5">
-        <v>1030000821</v>
+        <v>1030000489</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C467" s="4" t="s">
         <v>480</v>
@@ -7211,87 +7230,87 @@
     </row>
     <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="5">
-        <v>1030000511</v>
-      </c>
-      <c r="B468" s="10" t="s">
-        <v>489</v>
+        <v>1030000490</v>
+      </c>
+      <c r="B468" s="5" t="s">
+        <v>487</v>
       </c>
       <c r="C468" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A469" s="7">
-        <v>1010084279</v>
-      </c>
-      <c r="B469" s="10" t="s">
-        <v>443</v>
+      <c r="A469" s="5">
+        <v>1030000821</v>
+      </c>
+      <c r="B469" s="5" t="s">
+        <v>488</v>
       </c>
       <c r="C469" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="7">
-        <v>1010004281</v>
-      </c>
-      <c r="B470" s="5" t="s">
-        <v>444</v>
+      <c r="A470" s="5">
+        <v>1030000511</v>
+      </c>
+      <c r="B470" s="10" t="s">
+        <v>489</v>
       </c>
       <c r="C470" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A471" s="5">
-        <v>1010022118</v>
-      </c>
-      <c r="B471" s="11" t="s">
-        <v>445</v>
+      <c r="A471" s="7">
+        <v>1010084279</v>
+      </c>
+      <c r="B471" s="10" t="s">
+        <v>443</v>
       </c>
       <c r="C471" s="4" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A472" s="5">
+      <c r="A472" s="7">
+        <v>1010004281</v>
+      </c>
+      <c r="B472" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C472" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A473" s="5">
+        <v>1010022118</v>
+      </c>
+      <c r="B473" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="C473" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A474" s="5">
         <v>1010028657</v>
       </c>
-      <c r="B472" s="5" t="s">
+      <c r="B474" s="5" t="s">
         <v>446</v>
-      </c>
-      <c r="C472" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A473" s="14">
-        <v>1010028655</v>
-      </c>
-      <c r="B473" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C473" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A474" s="14">
-        <v>145165</v>
-      </c>
-      <c r="B474" s="5" t="s">
-        <v>448</v>
       </c>
       <c r="C474" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A475" s="5">
-        <v>51666</v>
+      <c r="A475" s="14">
+        <v>1010028655</v>
       </c>
       <c r="B475" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C475" s="4" t="s">
         <v>470</v>
@@ -7299,10 +7318,10 @@
     </row>
     <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="14">
-        <v>1010080930</v>
+        <v>145165</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C476" s="4" t="s">
         <v>470</v>
@@ -7310,21 +7329,21 @@
     </row>
     <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="5">
-        <v>161055</v>
+        <v>51666</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C477" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="5">
-        <v>1010050517</v>
+      <c r="A478" s="14">
+        <v>1010080930</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C478" s="4" t="s">
         <v>470</v>
@@ -7332,10 +7351,10 @@
     </row>
     <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" s="5">
-        <v>1010084190</v>
+        <v>161055</v>
       </c>
       <c r="B479" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C479" s="4" t="s">
         <v>470</v>
@@ -7343,10 +7362,10 @@
     </row>
     <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" s="5">
-        <v>1010084195</v>
+        <v>1010050517</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C480" s="4" t="s">
         <v>470</v>
@@ -7354,76 +7373,76 @@
     </row>
     <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="5">
-        <v>1010001400</v>
+        <v>1010084190</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C481" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="13">
-        <v>1010008416</v>
+      <c r="A482" s="5">
+        <v>1010084195</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="21">
-        <v>1010018372</v>
+      <c r="A483" s="5">
+        <v>1010001400</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="21">
-        <v>1010018361</v>
-      </c>
-      <c r="B484" s="10" t="s">
-        <v>458</v>
+      <c r="A484" s="13">
+        <v>1010008416</v>
+      </c>
+      <c r="B484" s="5" t="s">
+        <v>456</v>
       </c>
       <c r="C484" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A485" s="7">
-        <v>1010055398</v>
-      </c>
-      <c r="B485" s="14" t="s">
-        <v>459</v>
+      <c r="A485" s="21">
+        <v>1010018372</v>
+      </c>
+      <c r="B485" s="5" t="s">
+        <v>457</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="5">
-        <v>422131</v>
-      </c>
-      <c r="B486" s="5" t="s">
-        <v>460</v>
+      <c r="A486" s="21">
+        <v>1010018361</v>
+      </c>
+      <c r="B486" s="10" t="s">
+        <v>458</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A487" s="5">
-        <v>1010084370</v>
-      </c>
-      <c r="B487" s="5" t="s">
-        <v>461</v>
+      <c r="A487" s="7">
+        <v>1010055398</v>
+      </c>
+      <c r="B487" s="14" t="s">
+        <v>459</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>470</v>
@@ -7431,10 +7450,10 @@
     </row>
     <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="5">
-        <v>422759</v>
+        <v>422131</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>470</v>
@@ -7442,10 +7461,10 @@
     </row>
     <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="5">
-        <v>120955</v>
+        <v>1010084370</v>
       </c>
       <c r="B489" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C489" s="4" t="s">
         <v>470</v>
@@ -7453,10 +7472,10 @@
     </row>
     <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="5">
-        <v>1010000896</v>
+        <v>422759</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C490" s="4" t="s">
         <v>470</v>
@@ -7464,10 +7483,10 @@
     </row>
     <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="5">
-        <v>1010084308</v>
+        <v>120955</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C491" s="4" t="s">
         <v>470</v>
@@ -7475,22 +7494,36 @@
     </row>
     <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="5">
+        <v>1010000896</v>
+      </c>
+      <c r="B492" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C492" s="22" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A493" s="5">
+        <v>1010084308</v>
+      </c>
+      <c r="B493" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C493" s="22" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A494" s="5">
         <v>1010084035</v>
       </c>
-      <c r="B492" s="5" t="s">
+      <c r="B494" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="C492" s="4" t="s">
+      <c r="C494" s="22" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A493" s="2"/>
-      <c r="B493" s="2"/>
-    </row>
-    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A494" s="2"/>
-      <c r="B494" s="2"/>
     </row>
     <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="2"/>
@@ -10302,6 +10335,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12870E80-828B-4F9D-821D-6D331CA29027}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B378B33-90F2-401C-8FFE-665AF38B6221}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4575" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="501">
   <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
@@ -932,9 +932,6 @@
   </si>
   <si>
     <t>SUPORTE LANTERNA BASCULANTE FACCHINI LE</t>
-  </si>
-  <si>
-    <t>1010084519 </t>
   </si>
   <si>
     <t>SUPORTE LANTERNA DIANT DOLLY FACCHINI LD</t>
@@ -1737,7 +1734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1753,12 +1750,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1771,34 +1762,58 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2093,5436 +2108,5436 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+      <c r="A2" s="14">
         <v>1040019909</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="14">
         <v>1040023837</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+      <c r="A4" s="14">
         <v>1040023836</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="A5" s="14">
         <v>1010000216</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="14">
         <v>423651</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
+      <c r="A7" s="14">
         <v>1040077347</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
+      <c r="A8" s="14">
         <v>1040077348</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="A9" s="14">
         <v>417715</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
+      <c r="A10" s="14">
         <v>1010062075</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
+      <c r="A11" s="14">
         <v>1040083308</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
+      <c r="A12" s="14">
         <v>1040077346</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
+      <c r="A13" s="14">
         <v>1010049326</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
+      <c r="A14" s="14">
         <v>1040017265</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
+      <c r="A15" s="14">
         <v>1010060188</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
+      <c r="A16" s="14">
         <v>1040019851</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
+      <c r="A17" s="14">
         <v>1010077433</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
+      <c r="A18" s="14">
         <v>1010042610</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
+      <c r="A19" s="14">
         <v>1040077352</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
+      <c r="A20" s="14">
         <v>1040083258</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
+      <c r="A21" s="14">
         <v>68686</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
+      <c r="A22" s="14">
         <v>1010084124</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="11">
+      <c r="A23" s="14">
         <v>102286</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
+      <c r="A24" s="15">
         <v>1040097671</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="11">
+      <c r="A25" s="14">
         <v>1010003651</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
+      <c r="A26" s="14">
         <v>1010062027</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
+      <c r="A27" s="14">
         <v>1010021550</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
+      <c r="A28" s="14">
         <v>1040077350</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
+      <c r="A29" s="14">
         <v>1040077349</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
+      <c r="A30" s="14">
         <v>154897</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
+      <c r="A31" s="14">
         <v>13781</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
+      <c r="A32" s="14">
         <v>1010058682</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
+      <c r="A33" s="14">
         <v>1010059706</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
+      <c r="A34" s="14">
         <v>1010077386</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="11">
+      <c r="A35" s="14">
         <v>1010058325</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="11">
+      <c r="A36" s="14">
         <v>1010061986</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="11">
+      <c r="A37" s="14">
         <v>1040077354</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
+      <c r="A38" s="14">
         <v>1010050496</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="11">
+      <c r="A39" s="14">
         <v>1010050536</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="11">
+      <c r="A40" s="14">
         <v>1010061810</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="11">
+      <c r="A41" s="14">
         <v>1040092580</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
+      <c r="A42" s="14">
         <v>1010041375</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="11">
+      <c r="A43" s="14">
         <v>1040098335</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
+      <c r="A44" s="14">
         <v>1010023362</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
+      <c r="A45" s="14">
         <v>1010052336</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
+      <c r="A46" s="14">
         <v>1040077355</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
+      <c r="A47" s="14">
         <v>230110</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
+      <c r="A48" s="14">
         <v>1040077357</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
+      <c r="A49" s="14">
         <v>1040077356</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="5">
+      <c r="A50" s="15">
         <v>1040075251</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
+      <c r="A51" s="14">
         <v>1040090022</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="11">
+      <c r="A52" s="14">
         <v>1010023336</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="11">
+      <c r="A53" s="14">
         <v>1010021328</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="11">
+      <c r="A54" s="14">
         <v>1010059706</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="11">
+      <c r="A55" s="14">
         <v>1010062152</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="11">
+      <c r="A56" s="14">
         <v>1040077358</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="11">
+      <c r="A57" s="14">
         <v>1010045227</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="11">
+      <c r="A58" s="14">
         <v>1010085124</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="11">
+      <c r="A59" s="14">
         <v>1010046495</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="11">
+      <c r="A60" s="14">
         <v>1010032356</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="11">
+      <c r="A61" s="14">
         <v>1010050244</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="11">
+      <c r="A62" s="14">
         <v>1010050243</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="11">
+      <c r="A63" s="14">
         <v>428995</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="11">
+      <c r="A64" s="14">
         <v>428998</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="11">
+      <c r="A65" s="14">
         <v>1010031607</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="11">
+      <c r="A66" s="14">
         <v>1010031630</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="11">
+      <c r="A67" s="14">
         <v>1010045647</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
+      <c r="A68" s="14">
         <v>1010031567</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="11">
+      <c r="A69" s="14">
         <v>1040077361</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="11">
+      <c r="A70" s="14">
         <v>1010050445</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="11">
+      <c r="A71" s="14">
         <v>1010050461</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="11">
+      <c r="A72" s="14">
         <v>1010053885</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="5">
+      <c r="A73" s="15">
         <v>1040097102</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="5">
+      <c r="A74" s="15">
         <v>1010020838</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="7">
+      <c r="A75" s="16">
         <v>341430</v>
       </c>
-      <c r="B75" s="12" t="s">
-        <v>426</v>
+      <c r="B75" s="10" t="s">
+        <v>425</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="5">
+      <c r="A76" s="15">
         <v>1010042643</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="9" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="5">
+      <c r="A77" s="15">
         <v>425554</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>74</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="5">
+      <c r="A78" s="15">
         <v>1010084162</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="5">
+      <c r="A79" s="15">
         <v>1010084157</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="5">
+      <c r="A80" s="15">
         <v>1010084158</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="5">
+      <c r="A81" s="15">
         <v>1010084159</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>78</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="5">
+      <c r="A82" s="15">
         <v>1010084160</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="5">
+      <c r="A83" s="15">
         <v>1010084161</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
+      <c r="A84" s="15">
         <v>224382</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
+      <c r="A85" s="15">
         <v>94314</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="13">
+      <c r="A86" s="17">
         <v>1010003982</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="5">
+      <c r="A87" s="15">
         <v>1010000182</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>84</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="5">
+      <c r="A88" s="15">
         <v>1010021079</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="5">
+      <c r="A89" s="15">
         <v>1010002463</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="5">
+      <c r="A90" s="15">
         <v>1010062982</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>87</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="5">
+      <c r="A91" s="15">
         <v>1010063209</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="5">
+      <c r="A92" s="15">
         <v>1040076302</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>89</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="5">
+      <c r="A93" s="15">
         <v>1040098396</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="5">
+      <c r="A94" s="15">
         <v>1040041006</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="5">
+      <c r="A95" s="15">
         <v>1040077362</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="5">
+      <c r="A96" s="15">
         <v>1040077363</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>92</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="5">
+      <c r="A97" s="15">
         <v>1040077364</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>93</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="5">
+      <c r="A98" s="15">
         <v>1040048463</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>94</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="5">
+      <c r="A99" s="15">
         <v>1040096343</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="5">
+      <c r="A100" s="15">
         <v>409640</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="5">
+      <c r="A101" s="15">
         <v>1010032753</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="5">
+      <c r="A102" s="15">
         <v>1040098597</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>98</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="5">
+      <c r="A103" s="15">
         <v>1040084464</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="5">
+      <c r="A104" s="15">
         <v>1040017773</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>100</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="5">
+      <c r="A105" s="15">
         <v>1010007405</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>101</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="13">
+      <c r="A106" s="17">
         <v>1040077365</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>102</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="5">
+      <c r="A107" s="15">
         <v>1010027794</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>103</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="5">
+      <c r="A108" s="15">
         <v>1040077366</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>104</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="5">
+      <c r="A109" s="15">
         <v>1040077367</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="5">
+      <c r="A110" s="15">
         <v>1010021561</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="5">
+      <c r="A111" s="15">
         <v>1010021562</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="5">
+      <c r="A112" s="15">
         <v>1010027792</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>108</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="5">
+      <c r="A113" s="15">
         <v>1010084930</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>109</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="5">
+      <c r="A114" s="15">
         <v>341430</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="5">
+      <c r="A115" s="15">
         <v>1010029366</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="14">
+      <c r="A116" s="18">
         <v>1010031723</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="14">
+      <c r="A117" s="18">
         <v>1010049216</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="5">
+      <c r="A118" s="15">
         <v>405558</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>114</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="5">
+      <c r="A119" s="15">
         <v>1010023038</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>115</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="5">
+      <c r="A120" s="15">
         <v>1010084109</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="5">
+      <c r="A121" s="15">
         <v>1010021582</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="5">
+      <c r="A122" s="15">
         <v>1010021544</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="5">
+      <c r="A123" s="15">
         <v>1010021564</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>119</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="5">
+      <c r="A124" s="15">
         <v>1010023019</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="5">
+      <c r="A125" s="15">
         <v>1010048541</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>121</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="5">
+      <c r="A126" s="15">
         <v>1010059334</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="5">
+      <c r="A127" s="15">
         <v>1010000277</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>123</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="10">
+      <c r="A128" s="19">
         <v>1010085344</v>
       </c>
-      <c r="B128" s="10" t="s">
+      <c r="B128" s="8" t="s">
         <v>124</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="10">
+      <c r="A129" s="19">
         <v>1010085383</v>
       </c>
-      <c r="B129" s="10" t="s">
+      <c r="B129" s="8" t="s">
         <v>125</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="5">
+      <c r="A130" s="15">
         <v>1010001389</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>126</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="5">
+      <c r="A131" s="15">
         <v>1010017703</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>127</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="5">
+      <c r="A132" s="15">
         <v>1010052036</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="5">
+      <c r="A133" s="15">
         <v>1040097133</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>129</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="5">
+      <c r="A134" s="15">
         <v>1040019325</v>
       </c>
-      <c r="B134" s="11" t="s">
+      <c r="B134" s="9" t="s">
         <v>130</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="5">
+      <c r="A135" s="15">
         <v>64262</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="9" t="s">
         <v>131</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="11">
+      <c r="A136" s="14">
         <v>1010047089</v>
       </c>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="9" t="s">
         <v>132</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="11">
+      <c r="A137" s="14">
         <v>1040050168</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="9" t="s">
         <v>133</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="11">
+      <c r="A138" s="14">
         <v>1040077370</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="9" t="s">
         <v>134</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="11">
+      <c r="A139" s="14">
         <v>1040099247</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="9" t="s">
         <v>135</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="5">
+      <c r="A140" s="15">
         <v>1040077371</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>136</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="5">
+      <c r="A141" s="15">
         <v>1040077399</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>137</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="5">
+      <c r="A142" s="15">
         <v>1040077374</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>138</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="5">
+      <c r="A143" s="15">
         <v>1040077399</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>139</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="5">
+      <c r="A144" s="15">
         <v>357623</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>140</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="5">
+      <c r="A145" s="15">
         <v>1010020504</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>141</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="5">
+      <c r="A146" s="15">
         <v>409250</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>142</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="5">
+      <c r="A147" s="15">
         <v>1010020541</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>143</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="5">
+      <c r="A148" s="15">
         <v>1010020879</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>144</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="5">
+      <c r="A149" s="15">
         <v>1040077380</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A150" s="5">
+      <c r="A150" s="15">
         <v>1010021520</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>146</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="5">
+      <c r="A151" s="15">
         <v>1040098861</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>147</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="5">
+      <c r="A152" s="15">
         <v>1010077261</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>148</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="5">
+      <c r="A153" s="15">
         <v>1010027664</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>149</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="5">
+      <c r="A154" s="15">
         <v>1010083731</v>
       </c>
       <c r="B154" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A155" s="15">
+        <v>1010083885</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="C154" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="5">
-        <v>1010083885</v>
-      </c>
-      <c r="B155" s="5" t="s">
+      <c r="C155" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A156" s="15">
+        <v>1010014834</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" s="5">
-        <v>1010014834</v>
-      </c>
-      <c r="B156" s="5" t="s">
+      <c r="C156" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A157" s="15">
+        <v>1010083908</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="5">
-        <v>1010083908</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>495</v>
-      </c>
       <c r="C157" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="5">
+      <c r="A158" s="15">
         <v>1040077377</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>150</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="5">
+      <c r="A159" s="15">
         <v>1010061942</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>151</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="5">
+      <c r="A160" s="15">
         <v>1040097070</v>
       </c>
       <c r="B160" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="15">
+        <v>1040097068</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="C160" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="5">
-        <v>1040097068</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>425</v>
-      </c>
       <c r="C161" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="5">
+      <c r="A162" s="15">
         <v>22004</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>152</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" s="5">
+      <c r="A163" s="15">
         <v>1010058554</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>153</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="5">
+      <c r="A164" s="15">
         <v>1010027308</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>154</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="10">
+      <c r="A165" s="19">
         <v>1040077383</v>
       </c>
-      <c r="B165" s="10" t="s">
+      <c r="B165" s="8" t="s">
         <v>155</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="10">
+      <c r="A166" s="19">
         <v>1010025482</v>
       </c>
-      <c r="B166" s="10" t="s">
+      <c r="B166" s="8" t="s">
         <v>156</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="10">
+      <c r="A167" s="19">
         <v>1010025509</v>
       </c>
-      <c r="B167" s="10" t="s">
+      <c r="B167" s="8" t="s">
         <v>157</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="5">
+      <c r="A168" s="15">
         <v>1010027789</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>158</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="5">
+      <c r="A169" s="15">
         <v>1010027790</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>159</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="5">
+      <c r="A170" s="15">
         <v>1010018301</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>160</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A171" s="5">
+      <c r="A171" s="15">
         <v>1010031616</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>161</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A172" s="5">
+      <c r="A172" s="15">
         <v>1010053728</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>162</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A173" s="5">
+      <c r="A173" s="15">
         <v>1010020758</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>163</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A174" s="5">
+      <c r="A174" s="15">
         <v>1010020781</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>164</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="11">
+      <c r="A175" s="14">
         <v>1010058426</v>
       </c>
-      <c r="B175" s="11" t="s">
+      <c r="B175" s="9" t="s">
         <v>165</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="11">
+      <c r="A176" s="14">
         <v>1010059332</v>
       </c>
-      <c r="B176" s="11" t="s">
+      <c r="B176" s="9" t="s">
         <v>166</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="11">
+      <c r="A177" s="14">
         <v>1040077389</v>
       </c>
-      <c r="B177" s="11" t="s">
+      <c r="B177" s="9" t="s">
         <v>167</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A178" s="5">
+      <c r="A178" s="15">
         <v>1010021364</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>168</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" s="15">
+      <c r="A179" s="20">
         <v>1010021541</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>169</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A180" s="11">
+      <c r="A180" s="14">
         <v>1010021955</v>
       </c>
-      <c r="B180" s="11" t="s">
+      <c r="B180" s="9" t="s">
         <v>170</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A181" s="5">
+      <c r="A181" s="15">
         <v>1040077388</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>171</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" s="5">
+      <c r="A182" s="15">
         <v>1010058100</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>172</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" s="5">
+      <c r="A183" s="15">
         <v>1010020524</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>173</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="5">
+      <c r="A184" s="15">
         <v>1010021958</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>174</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A185" s="5">
+      <c r="A185" s="15">
         <v>1010019756</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>175</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A186" s="5">
+      <c r="A186" s="15">
         <v>1010019752</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>176</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A187" s="5">
+      <c r="A187" s="15">
         <v>409639</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>177</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A188" s="5">
+      <c r="A188" s="15">
         <v>1010047089</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>178</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A189" s="5">
+      <c r="A189" s="15">
         <v>1040084107</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>179</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="5">
+      <c r="A190" s="15">
         <v>1010085203</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>180</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A191" s="5">
+      <c r="A191" s="15">
         <v>424298</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>181</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A192" s="5">
+      <c r="A192" s="15">
         <v>421847</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>182</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A193" s="5">
+      <c r="A193" s="15">
         <v>431573</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>183</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A194" s="5">
+      <c r="A194" s="15">
         <v>1010021581</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>184</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A195" s="16">
+      <c r="A195" s="21">
         <v>412413</v>
       </c>
-      <c r="B195" s="9" t="s">
+      <c r="B195" s="7" t="s">
         <v>185</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A196" s="17">
+      <c r="A196" s="22">
         <v>1010022606</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>186</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A197" s="8">
+      <c r="A197" s="23">
         <v>1010003527</v>
       </c>
-      <c r="B197" s="9" t="s">
+      <c r="B197" s="7" t="s">
         <v>187</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A198" s="8">
+      <c r="A198" s="23">
         <v>1010055707</v>
       </c>
-      <c r="B198" s="9" t="s">
-        <v>481</v>
+      <c r="B198" s="7" t="s">
+        <v>480</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A199" s="14">
+      <c r="A199" s="18">
         <v>422027</v>
       </c>
-      <c r="B199" s="9" t="s">
+      <c r="B199" s="7" t="s">
         <v>188</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A200" s="11">
+      <c r="A200" s="14">
         <v>1010011313</v>
       </c>
       <c r="B200" s="5" t="s">
         <v>189</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A201" s="5">
+      <c r="A201" s="15">
         <v>27051</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>190</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A202" s="5">
+      <c r="A202" s="15">
         <v>1010011304</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>191</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A203" s="5">
+      <c r="A203" s="15">
         <v>35659</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>192</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A204" s="5">
+      <c r="A204" s="15">
         <v>1040077390</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>193</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="5">
+      <c r="A205" s="15">
         <v>1010021542</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>194</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A206" s="5">
+      <c r="A206" s="15">
         <v>1010021733</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>195</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A207" s="5">
+      <c r="A207" s="15">
         <v>1010011379</v>
       </c>
       <c r="B207" s="5" t="s">
         <v>196</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A208" s="5">
+      <c r="A208" s="15">
         <v>1010003279</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>197</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A209" s="5">
+      <c r="A209" s="15">
         <v>1010011380</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>198</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A210" s="5">
+      <c r="A210" s="15">
         <v>351197</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>199</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A211" s="5">
+      <c r="A211" s="15">
         <v>1010011286</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>200</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A212" s="5">
+      <c r="A212" s="15">
         <v>2479</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>201</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A213" s="5">
+      <c r="A213" s="15">
         <v>1010011382</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>202</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A214" s="7">
+      <c r="A214" s="16">
         <v>1010055703</v>
       </c>
-      <c r="B214" s="10" t="s">
+      <c r="B214" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A215" s="7">
+      <c r="A215" s="16">
         <v>4165</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>204</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A216" s="5">
+      <c r="A216" s="15">
         <v>301626</v>
       </c>
-      <c r="B216" s="11" t="s">
+      <c r="B216" s="9" t="s">
         <v>205</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A217" s="5">
+      <c r="A217" s="15">
         <v>429495</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>206</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A218" s="5">
+      <c r="A218" s="15">
         <v>162998</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>207</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A219" s="5">
+      <c r="A219" s="15">
         <v>432657</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>208</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A220" s="5">
+      <c r="A220" s="15">
         <v>1010021929</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>209</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A221" s="5">
+      <c r="A221" s="15">
         <v>428065</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>210</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A222" s="5">
+      <c r="A222" s="15">
         <v>1010003404</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>211</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A223" s="5">
+      <c r="A223" s="15">
         <v>1010003322</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="B223" s="7" t="s">
         <v>212</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A224" s="5">
+      <c r="A224" s="15">
         <v>17738</v>
       </c>
-      <c r="B224" s="9" t="s">
+      <c r="B224" s="7" t="s">
         <v>213</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A225" s="5">
+      <c r="A225" s="15">
         <v>1010085360</v>
       </c>
-      <c r="B225" s="9" t="s">
+      <c r="B225" s="7" t="s">
         <v>214</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A226" s="5">
+      <c r="A226" s="15">
         <v>1040077391</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>215</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A227" s="5">
+      <c r="A227" s="15">
         <v>1010058624</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>216</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A228" s="5">
+      <c r="A228" s="15">
         <v>1010024661</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>217</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A229" s="5">
+      <c r="A229" s="15">
         <v>1040019315</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>218</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A230" s="5">
+      <c r="A230" s="15">
         <v>1010021089</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>219</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A231" s="5">
+      <c r="A231" s="15">
         <v>1040017264</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>220</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A232" s="5">
+      <c r="A232" s="15">
         <v>1010051765</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>221</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A233" s="5">
+      <c r="A233" s="15">
         <v>1010035272</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>222</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A234" s="5">
+      <c r="A234" s="15">
         <v>1040077392</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>223</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A235" s="5">
+      <c r="A235" s="15">
         <v>1040077393</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>224</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A236" s="5">
+      <c r="A236" s="15">
         <v>1040077395</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>225</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A237" s="5">
+      <c r="A237" s="15">
         <v>1040077401</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>226</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A238" s="5">
+      <c r="A238" s="15">
         <v>27572</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>227</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A239" s="5">
+      <c r="A239" s="15">
         <v>18745</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>228</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A240" s="5">
+      <c r="A240" s="15">
         <v>1040077396</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>229</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A241" s="5">
+      <c r="A241" s="15">
         <v>1010036546</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>230</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A242" s="5">
+      <c r="A242" s="15">
         <v>1010014049</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>231</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A243" s="5">
+      <c r="A243" s="15">
         <v>1010025148</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>232</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A244" s="5">
+      <c r="A244" s="15">
         <v>1040077394</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>233</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A245" s="5">
+      <c r="A245" s="15">
         <v>1040077400</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>234</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A246" s="5">
+      <c r="A246" s="15">
         <v>1040079329</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>235</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A247" s="5">
+      <c r="A247" s="15">
         <v>1040040957</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>236</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A248" s="5">
+      <c r="A248" s="15">
         <v>1040077398</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>237</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A249" s="5">
+      <c r="A249" s="15">
         <v>1010031545</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>238</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A250" s="5">
+      <c r="A250" s="15">
         <v>1010053128</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>239</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A251" s="5">
+      <c r="A251" s="15">
         <v>1010010599</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>240</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A252" s="5">
+      <c r="A252" s="15">
         <v>1010056064</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>241</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A253" s="5">
+      <c r="A253" s="15">
         <v>5389</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>242</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A254" s="5">
+      <c r="A254" s="15">
         <v>1010055969</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>243</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A255" s="5">
+      <c r="A255" s="15">
         <v>1010055970</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>244</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A256" s="5">
+      <c r="A256" s="15">
         <v>181395</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>245</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A257" s="13">
+      <c r="A257" s="17">
         <v>1010055962</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>246</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A258" s="5">
+      <c r="A258" s="15">
         <v>1010003578</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>247</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A259" s="5">
+      <c r="A259" s="15">
         <v>332891</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>248</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A260" s="5">
+      <c r="A260" s="15">
         <v>17727</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>249</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A261" s="5">
+      <c r="A261" s="15">
         <v>17918</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>250</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A262" s="5">
+      <c r="A262" s="15">
         <v>1010020554</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>251</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A263" s="5">
+      <c r="A263" s="15">
         <v>1040085949</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>252</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A264" s="5">
+      <c r="A264" s="15">
         <v>1010062938</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>253</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A265" s="5">
+      <c r="A265" s="15">
         <v>1010062086</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>254</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A266" s="5">
+      <c r="A266" s="15">
         <v>1010062087</v>
       </c>
       <c r="B266" s="5" t="s">
         <v>255</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A267" s="5">
+      <c r="A267" s="15">
         <v>1040077373</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>256</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A268" s="6">
+      <c r="A268" s="24">
         <v>1040077372</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>257</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A269" s="6">
+      <c r="A269" s="24">
         <v>1040097154</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>258</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A270" s="6">
+      <c r="A270" s="24">
         <v>1010042579</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>259</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A271" s="5">
+      <c r="A271" s="15">
         <v>1010029427</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>260</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A272" s="5">
+      <c r="A272" s="15">
         <v>133108</v>
       </c>
       <c r="B272" s="5" t="s">
         <v>261</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A273" s="5">
+      <c r="A273" s="15">
         <v>269427</v>
       </c>
       <c r="B273" s="5" t="s">
         <v>262</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A274" s="5">
+      <c r="A274" s="15">
         <v>298227</v>
       </c>
       <c r="B274" s="5" t="s">
         <v>263</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A275" s="5">
+      <c r="A275" s="15">
         <v>1010062285</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>264</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A276" s="5">
+      <c r="A276" s="15">
         <v>1010058052</v>
       </c>
       <c r="B276" s="5" t="s">
         <v>265</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A277" s="5">
+      <c r="A277" s="15">
         <v>1010050033</v>
       </c>
       <c r="B277" s="5" t="s">
         <v>266</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A278" s="15">
+      <c r="A278" s="20">
         <v>1040098869</v>
       </c>
       <c r="B278" s="5" t="s">
         <v>267</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A279" s="15">
+      <c r="A279" s="20">
         <v>1010056523</v>
       </c>
       <c r="B279" s="5" t="s">
         <v>268</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A280" s="15">
+      <c r="A280" s="20">
         <v>1010062045</v>
       </c>
       <c r="B280" s="5" t="s">
         <v>269</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A281" s="5">
+      <c r="A281" s="15">
         <v>1040097575</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>270</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A282" s="5">
+      <c r="A282" s="15">
         <v>1040098437</v>
       </c>
       <c r="B282" s="5" t="s">
         <v>271</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A283" s="5">
+      <c r="A283" s="15">
         <v>1010040346</v>
       </c>
       <c r="B283" s="5" t="s">
         <v>272</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A284" s="5">
+      <c r="A284" s="15">
         <v>1010021543</v>
       </c>
       <c r="B284" s="5" t="s">
         <v>273</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A285" s="5">
+      <c r="A285" s="15">
         <v>1040077397</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>274</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A286" s="5">
+      <c r="A286" s="15">
         <v>1040094213</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>275</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A287" s="5">
+      <c r="A287" s="15">
         <v>1010085326</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>276</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A288" s="5">
+      <c r="A288" s="15">
         <v>1010042564</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>277</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A289" s="5">
+      <c r="A289" s="15">
         <v>1010042688</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>278</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A290" s="5">
+      <c r="A290" s="15">
         <v>1010040133</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>279</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A291" s="5">
+      <c r="A291" s="15">
         <v>1010039879</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>280</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A292" s="5">
+      <c r="A292" s="15">
         <v>62608</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>281</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A293" s="5">
+      <c r="A293" s="15">
         <v>1040098603</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>282</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A294" s="5">
+      <c r="A294" s="15">
         <v>1040017266</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>283</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A295" s="5">
+      <c r="A295" s="15">
         <v>1010063326</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>284</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A296" s="5">
+      <c r="A296" s="15">
         <v>1010050574</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>285</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A297" s="15">
+      <c r="A297" s="20">
         <v>1010086126</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>286</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A298" s="5">
+      <c r="A298" s="15">
         <v>1040019838</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>287</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A299" s="5">
+      <c r="A299" s="15">
         <v>1010042882</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>288</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A300" s="5">
+      <c r="A300" s="15">
         <v>1010042873</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>289</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A301" s="5">
+      <c r="A301" s="15">
         <v>1010026842</v>
       </c>
       <c r="B301" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A302" s="15">
+        <v>1010026841</v>
+      </c>
+      <c r="B302" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="C301" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A302" s="5">
-        <v>1010026841</v>
-      </c>
-      <c r="B302" s="5" t="s">
-        <v>501</v>
-      </c>
       <c r="C302" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A303" s="5">
+      <c r="A303" s="15">
         <v>1010059549</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>290</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A304" s="5">
+      <c r="A304" s="15">
         <v>1010020552</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>291</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A305" s="5">
+      <c r="A305" s="15">
         <v>1040078895</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>292</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A306" s="5">
+      <c r="A306" s="15">
         <v>1040024309</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>293</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A307" s="5">
+      <c r="A307" s="15">
         <v>1040024323</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>294</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A308" s="5">
+      <c r="A308" s="15">
         <v>1040024322</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>295</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A309" s="5">
+      <c r="A309" s="15">
         <v>1040024314</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>296</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A310" s="5">
+      <c r="A310" s="15">
         <v>1010059685</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>297</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A311" s="5">
+      <c r="A311" s="15">
         <v>1010059687</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>298</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A312" s="5">
+      <c r="A312" s="15">
         <v>1010077469</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>299</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A313" s="10">
+      <c r="A313" s="19">
         <v>1010077470</v>
       </c>
       <c r="B313" s="5" t="s">
         <v>300</v>
       </c>
       <c r="C313" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A314" s="15">
+        <v>1010084519</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A315" s="14">
+        <v>1010084108</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A316" s="14">
+        <v>1010042884</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A317" s="15">
+        <v>1040043537</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A318" s="15">
+        <v>1010046401</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A319" s="15">
+        <v>1010062007</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A320" s="15">
+        <v>1010051284</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A321" s="15">
+        <v>1010027788</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A322" s="15">
+        <v>1010027786</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A323" s="15">
+        <v>1010026889</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A324" s="24">
+        <v>1010042358</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A325" s="15">
+        <v>1040023848</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A326" s="15">
+        <v>1010042341</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A327" s="15">
+        <v>1040023858</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A328" s="15">
+        <v>1040023843</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A329" s="15">
+        <v>1040077411</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A330" s="15">
+        <v>1040077410</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A331" s="15">
+        <v>1010062008</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A332" s="15">
+        <v>1040040960</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A333" s="15">
+        <v>409578</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A334" s="15">
+        <v>1040077360</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A335" s="15">
+        <v>1010064470</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A336" s="15">
+        <v>1010021991</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A337" s="15">
+        <v>1010021960</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A338" s="15">
+        <v>1010031545</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A339" s="15">
+        <v>1010031690</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A340" s="15">
+        <v>1010022590</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A341" s="15">
+        <v>1040098643</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A342" s="15">
+        <v>1010086020</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A343" s="15">
+        <v>1010046550</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A344" s="15">
+        <v>1010046402</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A345" s="15">
+        <v>1010060291</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A346" s="15">
+        <v>1010050920</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A347" s="15">
+        <v>1040077412</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A348" s="15">
+        <v>1010042609</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A349" s="15">
+        <v>417701</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A350" s="15">
+        <v>399384</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A351" s="15">
+        <v>1010024086</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A352" s="15">
+        <v>1040077345</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A353" s="15">
+        <v>1010084315</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A354" s="15">
+        <v>399253</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A355" s="15">
+        <v>1010084317</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A356" s="25">
+        <v>1010085369</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A357" s="15">
+        <v>1010085370</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A358" s="15">
+        <v>1010085204</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A359" s="15">
+        <v>1010003966</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A360" s="15">
+        <v>1010003967</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A361" s="15">
+        <v>65219</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A362" s="15">
+        <v>10168</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A363" s="15">
+        <v>1010083792</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A364" s="15">
+        <v>1040077414</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A365" s="15">
+        <v>1010018482</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A366" s="15">
+        <v>1010084320</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A367" s="15">
+        <v>1010084532</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A368" s="15">
+        <v>1010027285</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A369" s="15">
+        <v>1040077413</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A370" s="15">
+        <v>1010085376</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A371" s="15">
+        <v>1010022819</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A372" s="15">
+        <v>1010052853</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A373" s="15">
+        <v>1010084377</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A374" s="26">
+        <v>1010062826</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A375" s="15">
+        <v>1010002592</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A376" s="24">
+        <v>1010001155</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A377" s="15">
+        <v>1010001062</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A378" s="15">
+        <v>1010084328</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A379" s="24">
+        <v>1010044502</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A380" s="15">
+        <v>1010053692</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A381" s="15">
+        <v>1010083992</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A382" s="15">
+        <v>1010008578</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C382" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A314" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B314" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="C314" s="4" t="s">
+    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A383" s="15">
+        <v>1010031694</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C383" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A315" s="11">
-        <v>1010084108</v>
-      </c>
-      <c r="B315" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="C315" s="4" t="s">
+    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A384" s="15">
+        <v>1010051997</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C384" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A316" s="11">
-        <v>1010042884</v>
-      </c>
-      <c r="B316" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C316" s="4" t="s">
+    <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A385" s="15">
+        <v>1010022601</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C385" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A317" s="5">
-        <v>1040043537</v>
-      </c>
-      <c r="B317" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C317" s="4" t="s">
+    <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A386" s="15">
+        <v>1010054278</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C386" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A318" s="5">
-        <v>1010046401</v>
-      </c>
-      <c r="B318" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C318" s="4" t="s">
+    <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A387" s="15">
+        <v>1010083462</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C387" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A319" s="5">
-        <v>1010062007</v>
-      </c>
-      <c r="B319" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C319" s="4" t="s">
+    <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A388" s="15">
+        <v>1010027772</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C388" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A320" s="5">
-        <v>1010051284</v>
-      </c>
-      <c r="B320" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C320" s="4" t="s">
+    <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A389" s="15">
+        <v>1010084144</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C389" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A321" s="5">
-        <v>1010027788</v>
-      </c>
-      <c r="B321" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C321" s="4" t="s">
+    <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A390" s="19">
+        <v>214055</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C390" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A322" s="5">
-        <v>1010027786</v>
-      </c>
-      <c r="B322" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C322" s="4" t="s">
+    <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A391" s="18">
+        <v>1010021956</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C391" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A323" s="5">
-        <v>1010026889</v>
-      </c>
-      <c r="B323" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="C323" s="4" t="s">
+    <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A392" s="18">
+        <v>1010026464</v>
+      </c>
+      <c r="B392" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C392" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A324" s="6">
-        <v>1010042358</v>
-      </c>
-      <c r="B324" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C324" s="4" t="s">
+    <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A393" s="14">
+        <v>1010021957</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C393" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A325" s="5">
-        <v>1040023848</v>
-      </c>
-      <c r="B325" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="C325" s="4" t="s">
+    <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A394" s="15">
+        <v>1010026462</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C394" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A326" s="5">
-        <v>1010042341</v>
-      </c>
-      <c r="B326" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="C326" s="4" t="s">
+    <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A395" s="15">
+        <v>1010026551</v>
+      </c>
+      <c r="B395" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C395" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A327" s="5">
-        <v>1040023858</v>
-      </c>
-      <c r="B327" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C327" s="4" t="s">
+    <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A396" s="15">
+        <v>1010042554</v>
+      </c>
+      <c r="B396" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C396" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A328" s="5">
-        <v>1040023843</v>
-      </c>
-      <c r="B328" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="C328" s="4" t="s">
+    <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A397" s="15">
+        <v>1010039904</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C397" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A329" s="5">
-        <v>1040077411</v>
-      </c>
-      <c r="B329" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="C329" s="4" t="s">
+    <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A398" s="15">
+        <v>1010060205</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C398" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A330" s="5">
-        <v>1040077410</v>
-      </c>
-      <c r="B330" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="C330" s="4" t="s">
+    <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A399" s="15">
+        <v>1010060206</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C399" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A331" s="5">
-        <v>1010062008</v>
-      </c>
-      <c r="B331" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="C331" s="4" t="s">
+    <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A400" s="15">
+        <v>1010077431</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C400" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A332" s="5">
-        <v>1040040960</v>
-      </c>
-      <c r="B332" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C332" s="4" t="s">
+    <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A401" s="15">
+        <v>1010077503</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C401" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A333" s="5">
-        <v>409578</v>
-      </c>
-      <c r="B333" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="C333" s="4" t="s">
+    <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A402" s="15">
+        <v>1010084187</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C402" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A334" s="5">
-        <v>1040077360</v>
-      </c>
-      <c r="B334" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C334" s="4" t="s">
+    <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A403" s="15">
+        <v>1010080958</v>
+      </c>
+      <c r="B403" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C403" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A335" s="5">
-        <v>1010064470</v>
-      </c>
-      <c r="B335" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C335" s="4" t="s">
+    <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A404" s="15">
+        <v>1010026032</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C404" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A336" s="5">
-        <v>1010021991</v>
-      </c>
-      <c r="B336" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C336" s="4" t="s">
+    <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A405" s="15">
+        <v>1010085384</v>
+      </c>
+      <c r="B405" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C405" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A337" s="5">
-        <v>1010021960</v>
-      </c>
-      <c r="B337" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="C337" s="4" t="s">
+    <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A406" s="15">
+        <v>1010006347</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C406" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A338" s="5">
-        <v>1010031545</v>
-      </c>
-      <c r="B338" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="C338" s="4" t="s">
+    <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A407" s="15">
+        <v>1010085179</v>
+      </c>
+      <c r="B407" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C407" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A339" s="5">
-        <v>1010031690</v>
-      </c>
-      <c r="B339" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C339" s="4" t="s">
+    <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A408" s="15">
+        <v>1010024158</v>
+      </c>
+      <c r="B408" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C408" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A340" s="5">
-        <v>1010022590</v>
-      </c>
-      <c r="B340" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="C340" s="4" t="s">
+    <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A409" s="15">
+        <v>1010024131</v>
+      </c>
+      <c r="B409" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C409" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A341" s="5">
-        <v>1040098643</v>
-      </c>
-      <c r="B341" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="C341" s="4" t="s">
+    <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A410" s="15">
+        <v>1010007160</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C410" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A342" s="5">
-        <v>1010086020</v>
-      </c>
-      <c r="B342" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C342" s="4" t="s">
+    <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A411" s="15">
+        <v>1010023642</v>
+      </c>
+      <c r="B411" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C411" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A343" s="5">
-        <v>1010046550</v>
-      </c>
-      <c r="B343" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="C343" s="4" t="s">
+    <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A412" s="15">
+        <v>1010007193</v>
+      </c>
+      <c r="B412" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C412" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A344" s="5">
-        <v>1010046402</v>
-      </c>
-      <c r="B344" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="C344" s="4" t="s">
+    <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A413" s="15">
+        <v>1010042637</v>
+      </c>
+      <c r="B413" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C413" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A345" s="5">
-        <v>1010060291</v>
-      </c>
-      <c r="B345" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="C345" s="4" t="s">
+    <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A414" s="15">
+        <v>1040075323</v>
+      </c>
+      <c r="B414" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C414" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A346" s="5">
-        <v>1010050920</v>
-      </c>
-      <c r="B346" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="C346" s="4" t="s">
+    <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A415" s="15">
+        <v>1040075324</v>
+      </c>
+      <c r="B415" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="C415" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A347" s="5">
-        <v>1040077412</v>
-      </c>
-      <c r="B347" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="C347" s="4" t="s">
+    <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A416" s="27">
+        <v>1040074827</v>
+      </c>
+      <c r="B416" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C416" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A348" s="5">
-        <v>1010042609</v>
-      </c>
-      <c r="B348" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="C348" s="4" t="s">
+    <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A417" s="27">
+        <v>1040099488</v>
+      </c>
+      <c r="B417" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C417" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A349" s="5">
-        <v>417701</v>
-      </c>
-      <c r="B349" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="C349" s="4" t="s">
+    <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A418" s="27">
+        <v>1040083312</v>
+      </c>
+      <c r="B418" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C418" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A350" s="5">
-        <v>399384</v>
-      </c>
-      <c r="B350" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C350" s="4" t="s">
+    <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A419" s="27">
+        <v>1040077661</v>
+      </c>
+      <c r="B419" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C419" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A351" s="5">
-        <v>1010024086</v>
-      </c>
-      <c r="B351" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="C351" s="4" t="s">
+    <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A420" s="27">
+        <v>1010085180</v>
+      </c>
+      <c r="B420" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="C420" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A352" s="5">
-        <v>1040077345</v>
-      </c>
-      <c r="B352" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C352" s="4" t="s">
+    <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A421" s="14">
+        <v>1040017489</v>
+      </c>
+      <c r="B421" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="C421" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A353" s="5">
-        <v>1010084315</v>
-      </c>
-      <c r="B353" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="C353" s="4" t="s">
+    <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A422" s="14">
+        <v>1010085181</v>
+      </c>
+      <c r="B422" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C422" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A354" s="5">
-        <v>399253</v>
-      </c>
-      <c r="B354" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C354" s="4" t="s">
+    <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A423" s="15">
+        <v>400175</v>
+      </c>
+      <c r="B423" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C423" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A355" s="5">
-        <v>1010084317</v>
-      </c>
-      <c r="B355" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C355" s="4" t="s">
+    <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A424" s="15">
+        <v>1040017505</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C424" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A356" s="18">
-        <v>1010085369</v>
-      </c>
-      <c r="B356" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C356" s="4" t="s">
+    <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A425" s="15">
+        <v>1040017503</v>
+      </c>
+      <c r="B425" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C425" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A357" s="5">
-        <v>1010085370</v>
-      </c>
-      <c r="B357" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="C357" s="4" t="s">
+    <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A426" s="15">
+        <v>1010046445</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C426" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A358" s="5">
-        <v>1010085204</v>
-      </c>
-      <c r="B358" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C358" s="4" t="s">
+    <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A427" s="15">
+        <v>1010021033</v>
+      </c>
+      <c r="B427" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C427" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A359" s="5">
-        <v>1010003966</v>
-      </c>
-      <c r="B359" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="C359" s="4" t="s">
+    <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A428" s="15">
+        <v>1010057142</v>
+      </c>
+      <c r="B428" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C428" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A360" s="5">
-        <v>1010003967</v>
-      </c>
-      <c r="B360" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C360" s="4" t="s">
+    <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A429" s="15">
+        <v>1010016356</v>
+      </c>
+      <c r="B429" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C429" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A361" s="5">
-        <v>65219</v>
-      </c>
-      <c r="B361" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C361" s="4" t="s">
+    <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A430" s="15">
+        <v>1010084363</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C430" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A362" s="5">
-        <v>10168</v>
-      </c>
-      <c r="B362" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C362" s="4" t="s">
+    <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A431" s="15">
+        <v>1010052021</v>
+      </c>
+      <c r="B431" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C431" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A363" s="5">
-        <v>1010083792</v>
-      </c>
-      <c r="B363" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="C363" s="4" t="s">
+    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A432" s="15">
+        <v>1040091721</v>
+      </c>
+      <c r="B432" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C432" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A364" s="5">
-        <v>1040077414</v>
-      </c>
-      <c r="B364" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="C364" s="4" t="s">
+    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A433" s="15">
+        <v>1010062022</v>
+      </c>
+      <c r="B433" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C433" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A365" s="5">
-        <v>1010018482</v>
-      </c>
-      <c r="B365" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="C365" s="4" t="s">
+    <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A434" s="15">
+        <v>18336</v>
+      </c>
+      <c r="B434" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="C434" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A366" s="5">
-        <v>1010084320</v>
-      </c>
-      <c r="B366" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C366" s="4" t="s">
+    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A435" s="15">
+        <v>229205</v>
+      </c>
+      <c r="B435" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="C435" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A367" s="5">
-        <v>1010084532</v>
-      </c>
-      <c r="B367" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C367" s="4" t="s">
+    <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A436" s="15">
+        <v>60671</v>
+      </c>
+      <c r="B436" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C436" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A368" s="5">
-        <v>1010027285</v>
-      </c>
-      <c r="B368" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="C368" s="4" t="s">
+    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A437" s="15">
+        <v>1010059726</v>
+      </c>
+      <c r="B437" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C437" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A369" s="5">
-        <v>1040077413</v>
-      </c>
-      <c r="B369" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="C369" s="4" t="s">
+    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A438" s="15">
+        <v>1010008144</v>
+      </c>
+      <c r="B438" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="C438" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A370" s="5">
-        <v>1010085376</v>
-      </c>
-      <c r="B370" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="C370" s="4" t="s">
+    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A439" s="15">
+        <v>1010007244</v>
+      </c>
+      <c r="B439" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C439" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A371" s="5">
-        <v>1010022819</v>
-      </c>
-      <c r="B371" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="C371" s="4" t="s">
+    <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A440" s="15">
+        <v>1010006827</v>
+      </c>
+      <c r="B440" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C440" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A372" s="5">
-        <v>1010052853</v>
-      </c>
-      <c r="B372" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="C372" s="4" t="s">
+    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A441" s="15">
+        <v>1040075426</v>
+      </c>
+      <c r="B441" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C441" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A373" s="5">
-        <v>1010084377</v>
-      </c>
-      <c r="B373" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C373" s="4" t="s">
+    <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A442" s="15">
+        <v>1040075427</v>
+      </c>
+      <c r="B442" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C442" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A374" s="2">
-        <v>1010062826</v>
-      </c>
-      <c r="B374" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="C374" s="4" t="s">
+    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A443" s="15">
+        <v>1010084313</v>
+      </c>
+      <c r="B443" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C443" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A444" s="15">
+        <v>403459</v>
+      </c>
+      <c r="B444" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C444" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A445" s="15">
+        <v>1010044828</v>
+      </c>
+      <c r="B445" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C445" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A446" s="15">
+        <v>1010026973</v>
+      </c>
+      <c r="B446" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C446" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A447" s="15">
+        <v>1040017204</v>
+      </c>
+      <c r="B447" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C447" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A448" s="24">
+        <v>1010022119</v>
+      </c>
+      <c r="B448" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C448" s="4" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A375" s="5">
-        <v>1010002592</v>
-      </c>
-      <c r="B375" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="C375" s="4" t="s">
+    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A449" s="15">
+        <v>1010058709</v>
+      </c>
+      <c r="B449" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C449" s="4" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A376" s="6">
-        <v>1010001155</v>
-      </c>
-      <c r="B376" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C376" s="4" t="s">
+    <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A450" s="15">
+        <v>1010025711</v>
+      </c>
+      <c r="B450" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C450" s="4" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A377" s="5">
-        <v>1010001062</v>
-      </c>
-      <c r="B377" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C377" s="4" t="s">
+    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A451" s="15">
+        <v>1010059684</v>
+      </c>
+      <c r="B451" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C451" s="4" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A378" s="5">
-        <v>1010084328</v>
-      </c>
-      <c r="B378" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C378" s="4" t="s">
+    <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A452" s="15">
+        <v>427341</v>
+      </c>
+      <c r="B452" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C452" s="4" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A379" s="6">
-        <v>1010044502</v>
-      </c>
-      <c r="B379" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="C379" s="4" t="s">
+    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A453" s="15">
+        <v>1010085279</v>
+      </c>
+      <c r="B453" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C453" s="4" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A380" s="5">
-        <v>1010053692</v>
-      </c>
-      <c r="B380" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="C380" s="4" t="s">
+    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A454" s="19">
+        <v>1010022588</v>
+      </c>
+      <c r="B454" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C454" s="4" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A381" s="5">
-        <v>1010083992</v>
-      </c>
-      <c r="B381" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="C381" s="4" t="s">
+    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A455" s="15">
+        <v>1010026864</v>
+      </c>
+      <c r="B455" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C455" s="4" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A382" s="5">
-        <v>1010008578</v>
-      </c>
-      <c r="B382" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="C382" s="4" t="s">
+    <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A456" s="14">
+        <v>1010030946</v>
+      </c>
+      <c r="B456" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C456" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A457" s="14">
+        <v>1010022589</v>
+      </c>
+      <c r="B457" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C457" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A458" s="15">
+        <v>1040090143</v>
+      </c>
+      <c r="B458" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C458" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A459" s="15">
+        <v>1040090138</v>
+      </c>
+      <c r="B459" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="C459" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A460" s="15">
+        <v>1030001314</v>
+      </c>
+      <c r="B460" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A461" s="15">
+        <v>1010052319</v>
+      </c>
+      <c r="B461" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C461" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A462" s="15">
+        <v>1010052320</v>
+      </c>
+      <c r="B462" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C462" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A463" s="15">
+        <v>1030000370</v>
+      </c>
+      <c r="B463" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="C463" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A464" s="15">
+        <v>1030000366</v>
+      </c>
+      <c r="B464" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C464" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A465" s="15">
+        <v>1030000368</v>
+      </c>
+      <c r="B465" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C465" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A466" s="15">
+        <v>1030000369</v>
+      </c>
+      <c r="B466" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A467" s="15">
+        <v>1030000489</v>
+      </c>
+      <c r="B467" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C467" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A468" s="15">
+        <v>1030000490</v>
+      </c>
+      <c r="B468" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C468" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A469" s="15">
+        <v>1030000821</v>
+      </c>
+      <c r="B469" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C469" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A470" s="15">
+        <v>1030000511</v>
+      </c>
+      <c r="B470" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="C470" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A471" s="16">
+        <v>1010084279</v>
+      </c>
+      <c r="B471" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="C471" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A472" s="16">
+        <v>1010004281</v>
+      </c>
+      <c r="B472" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C472" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A473" s="15">
+        <v>1010022118</v>
+      </c>
+      <c r="B473" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="C473" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A474" s="15">
+        <v>1010028657</v>
+      </c>
+      <c r="B474" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="C474" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A383" s="5">
-        <v>1010031694</v>
-      </c>
-      <c r="B383" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="C383" s="4" t="s">
+    <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A475" s="18">
+        <v>1010028655</v>
+      </c>
+      <c r="B475" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C475" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A384" s="5">
-        <v>1010051997</v>
-      </c>
-      <c r="B384" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="C384" s="4" t="s">
+    <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A476" s="18">
+        <v>145165</v>
+      </c>
+      <c r="B476" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C476" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A385" s="5">
-        <v>1010022601</v>
-      </c>
-      <c r="B385" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="C385" s="4" t="s">
+    <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A477" s="15">
+        <v>51666</v>
+      </c>
+      <c r="B477" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C477" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A386" s="5">
-        <v>1010054278</v>
-      </c>
-      <c r="B386" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C386" s="4" t="s">
+    <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A478" s="18">
+        <v>1010080930</v>
+      </c>
+      <c r="B478" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C478" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A387" s="5">
-        <v>1010083462</v>
-      </c>
-      <c r="B387" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C387" s="4" t="s">
+    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A479" s="15">
+        <v>161055</v>
+      </c>
+      <c r="B479" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C479" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A388" s="5">
-        <v>1010027772</v>
-      </c>
-      <c r="B388" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="C388" s="4" t="s">
+    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A480" s="15">
+        <v>1010050517</v>
+      </c>
+      <c r="B480" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C480" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A389" s="5">
-        <v>1010084144</v>
-      </c>
-      <c r="B389" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="C389" s="4" t="s">
+    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A481" s="15">
+        <v>1010084190</v>
+      </c>
+      <c r="B481" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C481" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A390" s="10">
-        <v>214055</v>
-      </c>
-      <c r="B390" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="C390" s="4" t="s">
+    <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A482" s="15">
+        <v>1010084195</v>
+      </c>
+      <c r="B482" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C482" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A391" s="14">
-        <v>1010021956</v>
-      </c>
-      <c r="B391" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C391" s="4" t="s">
+    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A483" s="15">
+        <v>1010001400</v>
+      </c>
+      <c r="B483" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C483" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A392" s="14">
-        <v>1010026464</v>
-      </c>
-      <c r="B392" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="C392" s="4" t="s">
+    <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A484" s="17">
+        <v>1010008416</v>
+      </c>
+      <c r="B484" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C484" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A393" s="11">
-        <v>1010021957</v>
-      </c>
-      <c r="B393" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="C393" s="4" t="s">
+    <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A485" s="28">
+        <v>1010018372</v>
+      </c>
+      <c r="B485" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C485" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A394" s="5">
-        <v>1010026462</v>
-      </c>
-      <c r="B394" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="C394" s="4" t="s">
+    <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A486" s="28">
+        <v>1010018361</v>
+      </c>
+      <c r="B486" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="C486" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A395" s="5">
-        <v>1010026551</v>
-      </c>
-      <c r="B395" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="C395" s="4" t="s">
+    <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A487" s="16">
+        <v>1010055398</v>
+      </c>
+      <c r="B487" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="C487" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A396" s="5">
-        <v>1010042554</v>
-      </c>
-      <c r="B396" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="C396" s="4" t="s">
+    <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A488" s="15">
+        <v>422131</v>
+      </c>
+      <c r="B488" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C488" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A397" s="5">
-        <v>1010039904</v>
-      </c>
-      <c r="B397" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="C397" s="4" t="s">
+    <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A489" s="15">
+        <v>1010084370</v>
+      </c>
+      <c r="B489" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C489" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A398" s="5">
-        <v>1010060205</v>
-      </c>
-      <c r="B398" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="C398" s="4" t="s">
+    <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A490" s="15">
+        <v>422759</v>
+      </c>
+      <c r="B490" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C490" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A399" s="5">
-        <v>1010060206</v>
-      </c>
-      <c r="B399" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="C399" s="4" t="s">
+    <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A491" s="15">
+        <v>120955</v>
+      </c>
+      <c r="B491" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C491" s="4" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A400" s="5">
-        <v>1010077431</v>
-      </c>
-      <c r="B400" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="C400" s="4" t="s">
+    <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A492" s="15">
+        <v>1010000896</v>
+      </c>
+      <c r="B492" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C492" s="13" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A401" s="5">
-        <v>1010077503</v>
-      </c>
-      <c r="B401" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="C401" s="4" t="s">
+    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A493" s="15">
+        <v>1010084308</v>
+      </c>
+      <c r="B493" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C493" s="13" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A402" s="5">
-        <v>1010084187</v>
-      </c>
-      <c r="B402" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C402" s="4" t="s">
+    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A494" s="15">
+        <v>1010084035</v>
+      </c>
+      <c r="B494" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C494" s="13" t="s">
         <v>469</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A403" s="5">
-        <v>1010080958</v>
-      </c>
-      <c r="B403" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="C403" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A404" s="5">
-        <v>1010026032</v>
-      </c>
-      <c r="B404" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="C404" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A405" s="5">
-        <v>1010085384</v>
-      </c>
-      <c r="B405" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C405" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A406" s="5">
-        <v>1010006347</v>
-      </c>
-      <c r="B406" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C406" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A407" s="5">
-        <v>1010085179</v>
-      </c>
-      <c r="B407" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="C407" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A408" s="5">
-        <v>1010024158</v>
-      </c>
-      <c r="B408" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="C408" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A409" s="5">
-        <v>1010024131</v>
-      </c>
-      <c r="B409" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="C409" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A410" s="5">
-        <v>1010007160</v>
-      </c>
-      <c r="B410" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="C410" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A411" s="5">
-        <v>1010023642</v>
-      </c>
-      <c r="B411" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C411" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A412" s="5">
-        <v>1010007193</v>
-      </c>
-      <c r="B412" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="C412" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A413" s="5">
-        <v>1010042637</v>
-      </c>
-      <c r="B413" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="C413" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A414" s="5">
-        <v>1040075323</v>
-      </c>
-      <c r="B414" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C414" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A415" s="5">
-        <v>1040075324</v>
-      </c>
-      <c r="B415" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="C415" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A416" s="19">
-        <v>1040074827</v>
-      </c>
-      <c r="B416" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="C416" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A417" s="19">
-        <v>1040099488</v>
-      </c>
-      <c r="B417" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="C417" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A418" s="19">
-        <v>1040083312</v>
-      </c>
-      <c r="B418" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="C418" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A419" s="19">
-        <v>1040077661</v>
-      </c>
-      <c r="B419" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="C419" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A420" s="19">
-        <v>1010085180</v>
-      </c>
-      <c r="B420" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="C420" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A421" s="11">
-        <v>1040017489</v>
-      </c>
-      <c r="B421" s="11" t="s">
-        <v>396</v>
-      </c>
-      <c r="C421" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A422" s="11">
-        <v>1010085181</v>
-      </c>
-      <c r="B422" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="C422" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A423" s="5">
-        <v>400175</v>
-      </c>
-      <c r="B423" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="C423" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A424" s="5">
-        <v>1040017505</v>
-      </c>
-      <c r="B424" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="C424" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A425" s="5">
-        <v>1040017503</v>
-      </c>
-      <c r="B425" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="C425" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A426" s="5">
-        <v>1010046445</v>
-      </c>
-      <c r="B426" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="C426" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A427" s="5">
-        <v>1010021033</v>
-      </c>
-      <c r="B427" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="C427" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A428" s="5">
-        <v>1010057142</v>
-      </c>
-      <c r="B428" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C428" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A429" s="5">
-        <v>1010016356</v>
-      </c>
-      <c r="B429" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="C429" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A430" s="5">
-        <v>1010084363</v>
-      </c>
-      <c r="B430" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="C430" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A431" s="5">
-        <v>1010052021</v>
-      </c>
-      <c r="B431" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="C431" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A432" s="5">
-        <v>1040091721</v>
-      </c>
-      <c r="B432" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A433" s="5">
-        <v>1010062022</v>
-      </c>
-      <c r="B433" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="C433" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A434" s="5">
-        <v>18336</v>
-      </c>
-      <c r="B434" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A435" s="5">
-        <v>229205</v>
-      </c>
-      <c r="B435" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C435" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A436" s="5">
-        <v>60671</v>
-      </c>
-      <c r="B436" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="C436" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="5">
-        <v>1010059726</v>
-      </c>
-      <c r="B437" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C437" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="5">
-        <v>1010008144</v>
-      </c>
-      <c r="B438" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="C438" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A439" s="5">
-        <v>1010007244</v>
-      </c>
-      <c r="B439" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="C439" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A440" s="5">
-        <v>1010006827</v>
-      </c>
-      <c r="B440" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C440" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A441" s="5">
-        <v>1040075426</v>
-      </c>
-      <c r="B441" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="C441" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A442" s="5">
-        <v>1040075427</v>
-      </c>
-      <c r="B442" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="C442" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A443" s="5">
-        <v>1010084313</v>
-      </c>
-      <c r="B443" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="C443" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A444" s="5">
-        <v>403459</v>
-      </c>
-      <c r="B444" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="C444" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A445" s="5">
-        <v>1010044828</v>
-      </c>
-      <c r="B445" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="C445" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A446" s="5">
-        <v>1010026973</v>
-      </c>
-      <c r="B446" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="C446" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A447" s="5">
-        <v>1040017204</v>
-      </c>
-      <c r="B447" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="C447" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="6">
-        <v>1010022119</v>
-      </c>
-      <c r="B448" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="C448" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A449" s="5">
-        <v>1010058709</v>
-      </c>
-      <c r="B449" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="C449" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A450" s="5">
-        <v>1010025711</v>
-      </c>
-      <c r="B450" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="C450" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A451" s="5">
-        <v>1010059684</v>
-      </c>
-      <c r="B451" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="C451" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="5">
-        <v>427341</v>
-      </c>
-      <c r="B452" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="C452" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A453" s="5">
-        <v>1010085279</v>
-      </c>
-      <c r="B453" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="C453" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="10">
-        <v>1010022588</v>
-      </c>
-      <c r="B454" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="C454" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A455" s="5">
-        <v>1010026864</v>
-      </c>
-      <c r="B455" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="C455" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="11">
-        <v>1010030946</v>
-      </c>
-      <c r="B456" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="C456" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A457" s="11">
-        <v>1010022589</v>
-      </c>
-      <c r="B457" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C457" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="5">
-        <v>1040090143</v>
-      </c>
-      <c r="B458" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="C458" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A459" s="5">
-        <v>1040090138</v>
-      </c>
-      <c r="B459" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="C459" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="5">
-        <v>1030001314</v>
-      </c>
-      <c r="B460" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="C460" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="5">
-        <v>1010052319</v>
-      </c>
-      <c r="B461" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="C461" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A462" s="5">
-        <v>1010052320</v>
-      </c>
-      <c r="B462" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="C462" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A463" s="5">
-        <v>1030000370</v>
-      </c>
-      <c r="B463" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="C463" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A464" s="5">
-        <v>1030000366</v>
-      </c>
-      <c r="B464" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C464" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A465" s="5">
-        <v>1030000368</v>
-      </c>
-      <c r="B465" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="C465" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A466" s="5">
-        <v>1030000369</v>
-      </c>
-      <c r="B466" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C466" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="5">
-        <v>1030000489</v>
-      </c>
-      <c r="B467" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C467" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="5">
-        <v>1030000490</v>
-      </c>
-      <c r="B468" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C468" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A469" s="5">
-        <v>1030000821</v>
-      </c>
-      <c r="B469" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C469" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="5">
-        <v>1030000511</v>
-      </c>
-      <c r="B470" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="C470" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A471" s="7">
-        <v>1010084279</v>
-      </c>
-      <c r="B471" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="C471" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A472" s="7">
-        <v>1010004281</v>
-      </c>
-      <c r="B472" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C472" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A473" s="5">
-        <v>1010022118</v>
-      </c>
-      <c r="B473" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="C473" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A474" s="5">
-        <v>1010028657</v>
-      </c>
-      <c r="B474" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C474" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A475" s="14">
-        <v>1010028655</v>
-      </c>
-      <c r="B475" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C475" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A476" s="14">
-        <v>145165</v>
-      </c>
-      <c r="B476" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C476" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A477" s="5">
-        <v>51666</v>
-      </c>
-      <c r="B477" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C477" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="14">
-        <v>1010080930</v>
-      </c>
-      <c r="B478" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C478" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="5">
-        <v>161055</v>
-      </c>
-      <c r="B479" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C479" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="5">
-        <v>1010050517</v>
-      </c>
-      <c r="B480" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C480" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="5">
-        <v>1010084190</v>
-      </c>
-      <c r="B481" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="C481" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="5">
-        <v>1010084195</v>
-      </c>
-      <c r="B482" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C482" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="5">
-        <v>1010001400</v>
-      </c>
-      <c r="B483" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C483" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="13">
-        <v>1010008416</v>
-      </c>
-      <c r="B484" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A485" s="21">
-        <v>1010018372</v>
-      </c>
-      <c r="B485" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="C485" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="21">
-        <v>1010018361</v>
-      </c>
-      <c r="B486" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="C486" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A487" s="7">
-        <v>1010055398</v>
-      </c>
-      <c r="B487" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="C487" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A488" s="5">
-        <v>422131</v>
-      </c>
-      <c r="B488" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="C488" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A489" s="5">
-        <v>1010084370</v>
-      </c>
-      <c r="B489" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="C489" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A490" s="5">
-        <v>422759</v>
-      </c>
-      <c r="B490" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C490" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A491" s="5">
-        <v>120955</v>
-      </c>
-      <c r="B491" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C491" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A492" s="5">
-        <v>1010000896</v>
-      </c>
-      <c r="B492" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C492" s="22" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A493" s="5">
-        <v>1010084308</v>
-      </c>
-      <c r="B493" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C493" s="22" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A494" s="5">
-        <v>1010084035</v>
-      </c>
-      <c r="B494" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C494" s="22" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -10349,33 +10364,33 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B1" s="4"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B378B33-90F2-401C-8FFE-665AF38B6221}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5349278A-4B39-443E-9976-97319790B4FC}"/>
   <bookViews>
-    <workbookView xWindow="4575" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="505">
   <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
@@ -1544,6 +1544,18 @@
   </si>
   <si>
     <t>SUPORTE PARALAMA TRASEIRO SCANIA LE</t>
+  </si>
+  <si>
+    <t>BROCA 6MM</t>
+  </si>
+  <si>
+    <t>BROCA 8MM</t>
+  </si>
+  <si>
+    <t>BROCA 10MM</t>
+  </si>
+  <si>
+    <t>BROCA 12MM</t>
   </si>
 </sst>
 </file>
@@ -2098,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1196"/>
+  <dimension ref="A1:C1200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2498,71 +2510,71 @@
       <c r="B36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="13" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="14">
-        <v>1040077354</v>
+      <c r="A37" s="9">
+        <v>1010004299</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
-        <v>1010050496</v>
+      <c r="A38" s="9">
+        <v>1010004301</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="14">
-        <v>1010050536</v>
+      <c r="A39" s="9">
+        <v>1010004289</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="14">
-        <v>1010061810</v>
+      <c r="A40" s="9">
+        <v>1010004292</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="14">
-        <v>1040092580</v>
+        <v>1040077354</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
-        <v>1010041375</v>
+        <v>1010050496</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>467</v>
@@ -2570,10 +2582,10 @@
     </row>
     <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="14">
-        <v>1040098335</v>
+        <v>1010050536</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>467</v>
@@ -2581,10 +2593,10 @@
     </row>
     <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="14">
-        <v>1010023362</v>
+        <v>1010061810</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>467</v>
@@ -2592,10 +2604,10 @@
     </row>
     <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="14">
-        <v>1010052336</v>
+        <v>1040092580</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>467</v>
@@ -2603,10 +2615,10 @@
     </row>
     <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
-        <v>1040077355</v>
+        <v>1010041375</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>467</v>
@@ -2614,10 +2626,10 @@
     </row>
     <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="14">
-        <v>230110</v>
+        <v>1040098335</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>467</v>
@@ -2625,10 +2637,10 @@
     </row>
     <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="14">
-        <v>1040077357</v>
+        <v>1010023362</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>467</v>
@@ -2636,21 +2648,21 @@
     </row>
     <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="14">
-        <v>1040077356</v>
+        <v>1010052336</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
-        <v>1040075251</v>
+      <c r="A50" s="14">
+        <v>1040077355</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>467</v>
@@ -2658,10 +2670,10 @@
     </row>
     <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="14">
-        <v>1040090022</v>
+        <v>230110</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>467</v>
@@ -2669,10 +2681,10 @@
     </row>
     <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
-        <v>1010023336</v>
+        <v>1040077357</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>467</v>
@@ -2680,21 +2692,21 @@
     </row>
     <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
-        <v>1010021328</v>
+        <v>1040077356</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="14">
-        <v>1010059706</v>
+      <c r="A54" s="15">
+        <v>1040075251</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>467</v>
@@ -2702,10 +2714,10 @@
     </row>
     <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
-        <v>1010062152</v>
+        <v>1040090022</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>467</v>
@@ -2713,10 +2725,10 @@
     </row>
     <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
-        <v>1040077358</v>
+        <v>1010023336</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>467</v>
@@ -2724,10 +2736,10 @@
     </row>
     <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
-        <v>1010045227</v>
+        <v>1010021328</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>467</v>
@@ -2735,10 +2747,10 @@
     </row>
     <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
-        <v>1010085124</v>
+        <v>1010059706</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>467</v>
@@ -2746,10 +2758,10 @@
     </row>
     <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
-        <v>1010046495</v>
+        <v>1010062152</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>467</v>
@@ -2757,10 +2769,10 @@
     </row>
     <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
-        <v>1010032356</v>
+        <v>1040077358</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>467</v>
@@ -2768,10 +2780,10 @@
     </row>
     <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
-        <v>1010050244</v>
+        <v>1010045227</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>467</v>
@@ -2779,10 +2791,10 @@
     </row>
     <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
-        <v>1010050243</v>
+        <v>1010085124</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>467</v>
@@ -2790,10 +2802,10 @@
     </row>
     <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
-        <v>428995</v>
+        <v>1010046495</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>467</v>
@@ -2801,10 +2813,10 @@
     </row>
     <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
-        <v>428998</v>
+        <v>1010032356</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>467</v>
@@ -2812,10 +2824,10 @@
     </row>
     <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
-        <v>1010031607</v>
+        <v>1010050244</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>467</v>
@@ -2823,10 +2835,10 @@
     </row>
     <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="14">
-        <v>1010031630</v>
+        <v>1010050243</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>467</v>
@@ -2834,10 +2846,10 @@
     </row>
     <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="14">
-        <v>1010045647</v>
+        <v>428995</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>467</v>
@@ -2845,10 +2857,10 @@
     </row>
     <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
-        <v>1010031567</v>
+        <v>428998</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>467</v>
@@ -2856,10 +2868,10 @@
     </row>
     <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="14">
-        <v>1040077361</v>
+        <v>1010031607</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>467</v>
@@ -2867,10 +2879,10 @@
     </row>
     <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
-        <v>1010050445</v>
+        <v>1010031630</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>467</v>
@@ -2878,10 +2890,10 @@
     </row>
     <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="14">
-        <v>1010050461</v>
+        <v>1010045647</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>467</v>
@@ -2889,54 +2901,54 @@
     </row>
     <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="14">
+        <v>1010031567</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="14">
+        <v>1040077361</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="14">
+        <v>1010050445</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="14">
+        <v>1010050461</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="14">
         <v>1010053885</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B76" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="15">
-        <v>1040097102</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="15">
-        <v>1010020838</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="16">
-        <v>341430</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="15">
-        <v>1010042643</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>467</v>
@@ -2944,10 +2956,10 @@
     </row>
     <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="15">
-        <v>425554</v>
+        <v>1040097102</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>467</v>
@@ -2955,21 +2967,21 @@
     </row>
     <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="15">
-        <v>1010084162</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>75</v>
+        <v>1010020838</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="15">
-        <v>1010084157</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>76</v>
+      <c r="A79" s="16">
+        <v>341430</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>425</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>467</v>
@@ -2977,10 +2989,10 @@
     </row>
     <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="15">
-        <v>1010084158</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>77</v>
+        <v>1010042643</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>467</v>
@@ -2988,10 +3000,10 @@
     </row>
     <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="15">
-        <v>1010084159</v>
+        <v>425554</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>467</v>
@@ -2999,10 +3011,10 @@
     </row>
     <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
-        <v>1010084160</v>
+        <v>1010084162</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>467</v>
@@ -3010,10 +3022,10 @@
     </row>
     <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="15">
-        <v>1010084161</v>
+        <v>1010084157</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>467</v>
@@ -3021,10 +3033,10 @@
     </row>
     <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
-        <v>224382</v>
+        <v>1010084158</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>467</v>
@@ -3032,21 +3044,21 @@
     </row>
     <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
-        <v>94314</v>
+        <v>1010084159</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="17">
-        <v>1010003982</v>
+      <c r="A86" s="15">
+        <v>1010084160</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>467</v>
@@ -3054,10 +3066,10 @@
     </row>
     <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
-        <v>1010000182</v>
+        <v>1010084161</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>467</v>
@@ -3065,10 +3077,10 @@
     </row>
     <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
-        <v>1010021079</v>
+        <v>224382</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>467</v>
@@ -3076,21 +3088,21 @@
     </row>
     <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
-        <v>1010002463</v>
+        <v>94314</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="15">
-        <v>1010062982</v>
+      <c r="A90" s="17">
+        <v>1010003982</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>467</v>
@@ -3098,10 +3110,10 @@
     </row>
     <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="15">
-        <v>1010063209</v>
+        <v>1010000182</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>467</v>
@@ -3109,10 +3121,10 @@
     </row>
     <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="15">
-        <v>1040076302</v>
+        <v>1010021079</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>467</v>
@@ -3120,10 +3132,10 @@
     </row>
     <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="15">
-        <v>1040098396</v>
+        <v>1010002463</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>467</v>
@@ -3131,10 +3143,10 @@
     </row>
     <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="15">
-        <v>1040041006</v>
+        <v>1010062982</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>490</v>
+        <v>87</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>467</v>
@@ -3142,10 +3154,10 @@
     </row>
     <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="15">
-        <v>1040077362</v>
+        <v>1010063209</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>467</v>
@@ -3153,10 +3165,10 @@
     </row>
     <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="15">
-        <v>1040077363</v>
+        <v>1040076302</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>467</v>
@@ -3164,10 +3176,10 @@
     </row>
     <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="15">
-        <v>1040077364</v>
+        <v>1040098396</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>467</v>
@@ -3175,10 +3187,10 @@
     </row>
     <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="15">
-        <v>1040048463</v>
+        <v>1040041006</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>94</v>
+        <v>490</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>467</v>
@@ -3186,10 +3198,10 @@
     </row>
     <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="15">
-        <v>1040096343</v>
+        <v>1040077362</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>467</v>
@@ -3197,10 +3209,10 @@
     </row>
     <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="15">
-        <v>409640</v>
+        <v>1040077363</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>467</v>
@@ -3208,10 +3220,10 @@
     </row>
     <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="15">
-        <v>1010032753</v>
+        <v>1040077364</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>467</v>
@@ -3219,10 +3231,10 @@
     </row>
     <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="15">
-        <v>1040098597</v>
+        <v>1040048463</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>467</v>
@@ -3230,10 +3242,10 @@
     </row>
     <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="15">
-        <v>1040084464</v>
+        <v>1040096343</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>467</v>
@@ -3241,10 +3253,10 @@
     </row>
     <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="15">
-        <v>1040017773</v>
+        <v>409640</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>467</v>
@@ -3252,21 +3264,21 @@
     </row>
     <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="15">
-        <v>1010007405</v>
+        <v>1010032753</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="17">
-        <v>1040077365</v>
+      <c r="A106" s="15">
+        <v>1040098597</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>467</v>
@@ -3274,10 +3286,10 @@
     </row>
     <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="15">
-        <v>1010027794</v>
+        <v>1040084464</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>467</v>
@@ -3285,10 +3297,10 @@
     </row>
     <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="15">
-        <v>1040077366</v>
+        <v>1040017773</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>467</v>
@@ -3296,21 +3308,21 @@
     </row>
     <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="15">
-        <v>1040077367</v>
+        <v>1010007405</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="15">
-        <v>1010021561</v>
+      <c r="A110" s="17">
+        <v>1040077365</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>467</v>
@@ -3318,10 +3330,10 @@
     </row>
     <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="15">
-        <v>1010021562</v>
+        <v>1010027794</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>467</v>
@@ -3329,10 +3341,10 @@
     </row>
     <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="15">
-        <v>1010027792</v>
+        <v>1040077366</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>467</v>
@@ -3340,10 +3352,10 @@
     </row>
     <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="15">
-        <v>1010084930</v>
+        <v>1040077367</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>467</v>
@@ -3351,10 +3363,10 @@
     </row>
     <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="15">
-        <v>341430</v>
+        <v>1010021561</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>467</v>
@@ -3362,32 +3374,32 @@
     </row>
     <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="15">
-        <v>1010029366</v>
+        <v>1010021562</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="18">
-        <v>1010031723</v>
+      <c r="A116" s="15">
+        <v>1010027792</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="18">
-        <v>1010049216</v>
+      <c r="A117" s="15">
+        <v>1010084930</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>467</v>
@@ -3395,10 +3407,10 @@
     </row>
     <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="15">
-        <v>405558</v>
+        <v>341430</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>467</v>
@@ -3406,32 +3418,32 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="15">
-        <v>1010023038</v>
+        <v>1010029366</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="15">
-        <v>1010084109</v>
+      <c r="A120" s="18">
+        <v>1010031723</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="15">
-        <v>1010021582</v>
+      <c r="A121" s="18">
+        <v>1010049216</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>467</v>
@@ -3439,10 +3451,10 @@
     </row>
     <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="15">
-        <v>1010021544</v>
+        <v>405558</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>467</v>
@@ -3450,10 +3462,10 @@
     </row>
     <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="15">
-        <v>1010021564</v>
+        <v>1010023038</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>467</v>
@@ -3461,10 +3473,10 @@
     </row>
     <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="15">
-        <v>1010023019</v>
+        <v>1010084109</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>467</v>
@@ -3472,10 +3484,10 @@
     </row>
     <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="15">
-        <v>1010048541</v>
+        <v>1010021582</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>467</v>
@@ -3483,10 +3495,10 @@
     </row>
     <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="15">
-        <v>1010059334</v>
+        <v>1010021544</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>467</v>
@@ -3494,32 +3506,32 @@
     </row>
     <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="15">
-        <v>1010000277</v>
+        <v>1010021564</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="19">
-        <v>1010085344</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>124</v>
+      <c r="A128" s="15">
+        <v>1010023019</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="19">
-        <v>1010085383</v>
-      </c>
-      <c r="B129" s="8" t="s">
-        <v>125</v>
+      <c r="A129" s="15">
+        <v>1010048541</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>467</v>
@@ -3527,10 +3539,10 @@
     </row>
     <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="15">
-        <v>1010001389</v>
+        <v>1010059334</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>467</v>
@@ -3538,32 +3550,32 @@
     </row>
     <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="15">
-        <v>1010017703</v>
+        <v>1010000277</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="15">
-        <v>1010052036</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>128</v>
+      <c r="A132" s="19">
+        <v>1010085344</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>124</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="15">
-        <v>1040097133</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>129</v>
+      <c r="A133" s="19">
+        <v>1010085383</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>467</v>
@@ -3571,10 +3583,10 @@
     </row>
     <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="15">
-        <v>1040019325</v>
-      </c>
-      <c r="B134" s="9" t="s">
-        <v>130</v>
+        <v>1010001389</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>467</v>
@@ -3582,98 +3594,98 @@
     </row>
     <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="15">
+        <v>1010017703</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A136" s="15">
+        <v>1010052036</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A137" s="15">
+        <v>1040097133</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A138" s="15">
+        <v>1040019325</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A139" s="15">
         <v>64262</v>
       </c>
-      <c r="B135" s="9" t="s">
+      <c r="B139" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C135" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="14">
+      <c r="C139" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A140" s="14">
         <v>1010047089</v>
       </c>
-      <c r="B136" s="9" t="s">
+      <c r="B140" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="C136" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="14">
+      <c r="C140" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A141" s="14">
         <v>1040050168</v>
       </c>
-      <c r="B137" s="9" t="s">
+      <c r="B141" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C137" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="14">
+      <c r="C141" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A142" s="14">
         <v>1040077370</v>
       </c>
-      <c r="B138" s="9" t="s">
+      <c r="B142" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C138" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="14">
+      <c r="C142" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A143" s="14">
         <v>1040099247</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B143" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="15">
-        <v>1040077371</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="15">
-        <v>1040077399</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="15">
-        <v>1040077374</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="15">
-        <v>1040077399</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>467</v>
@@ -3681,10 +3693,10 @@
     </row>
     <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="15">
-        <v>357623</v>
+        <v>1040077371</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>467</v>
@@ -3692,10 +3704,10 @@
     </row>
     <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="15">
-        <v>1010020504</v>
+        <v>1040077399</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>467</v>
@@ -3703,10 +3715,10 @@
     </row>
     <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="15">
-        <v>409250</v>
+        <v>1040077374</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>467</v>
@@ -3714,10 +3726,10 @@
     </row>
     <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="15">
-        <v>1010020541</v>
+        <v>1040077399</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>467</v>
@@ -3725,10 +3737,10 @@
     </row>
     <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="15">
-        <v>1010020879</v>
+        <v>357623</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>467</v>
@@ -3736,10 +3748,10 @@
     </row>
     <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="15">
-        <v>1040077380</v>
+        <v>1010020504</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>467</v>
@@ -3747,10 +3759,10 @@
     </row>
     <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="15">
-        <v>1010021520</v>
+        <v>409250</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>467</v>
@@ -3758,10 +3770,10 @@
     </row>
     <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="15">
-        <v>1040098861</v>
+        <v>1010020541</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>467</v>
@@ -3769,10 +3781,10 @@
     </row>
     <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="15">
-        <v>1010077261</v>
+        <v>1010020879</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>467</v>
@@ -3780,10 +3792,10 @@
     </row>
     <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="15">
-        <v>1010027664</v>
+        <v>1040077380</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>467</v>
@@ -3791,10 +3803,10 @@
     </row>
     <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="15">
-        <v>1010083731</v>
+        <v>1010021520</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>491</v>
+        <v>146</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>467</v>
@@ -3802,10 +3814,10 @@
     </row>
     <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="15">
-        <v>1010083885</v>
+        <v>1040098861</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>492</v>
+        <v>147</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>467</v>
@@ -3813,10 +3825,10 @@
     </row>
     <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="15">
-        <v>1010014834</v>
+        <v>1010077261</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>493</v>
+        <v>148</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>467</v>
@@ -3824,10 +3836,10 @@
     </row>
     <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="15">
-        <v>1010083908</v>
+        <v>1010027664</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>494</v>
+        <v>149</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>467</v>
@@ -3835,10 +3847,10 @@
     </row>
     <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="15">
-        <v>1040077377</v>
+        <v>1010083731</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>150</v>
+        <v>491</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>467</v>
@@ -3846,10 +3858,10 @@
     </row>
     <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="15">
-        <v>1010061942</v>
+        <v>1010083885</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>151</v>
+        <v>492</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>467</v>
@@ -3857,10 +3869,10 @@
     </row>
     <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="15">
-        <v>1040097070</v>
+        <v>1010014834</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>423</v>
+        <v>493</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>467</v>
@@ -3868,10 +3880,10 @@
     </row>
     <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="15">
-        <v>1040097068</v>
+        <v>1010083908</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>424</v>
+        <v>494</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>467</v>
@@ -3879,10 +3891,10 @@
     </row>
     <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="15">
-        <v>22004</v>
+        <v>1040077377</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>467</v>
@@ -3890,10 +3902,10 @@
     </row>
     <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="15">
-        <v>1010058554</v>
+        <v>1010061942</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>467</v>
@@ -3901,43 +3913,43 @@
     </row>
     <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="15">
-        <v>1010027308</v>
+        <v>1040097070</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>154</v>
+        <v>423</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="19">
-        <v>1040077383</v>
-      </c>
-      <c r="B165" s="8" t="s">
-        <v>155</v>
+      <c r="A165" s="15">
+        <v>1040097068</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>424</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="19">
-        <v>1010025482</v>
-      </c>
-      <c r="B166" s="8" t="s">
-        <v>156</v>
+      <c r="A166" s="15">
+        <v>22004</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="19">
-        <v>1010025509</v>
-      </c>
-      <c r="B167" s="8" t="s">
-        <v>157</v>
+      <c r="A167" s="15">
+        <v>1010058554</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>467</v>
@@ -3945,43 +3957,43 @@
     </row>
     <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="15">
-        <v>1010027789</v>
+        <v>1010027308</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="15">
-        <v>1010027790</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>159</v>
+      <c r="A169" s="19">
+        <v>1040077383</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="15">
-        <v>1010018301</v>
-      </c>
-      <c r="B170" s="5" t="s">
-        <v>160</v>
+      <c r="A170" s="19">
+        <v>1010025482</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>156</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A171" s="15">
-        <v>1010031616</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>161</v>
+      <c r="A171" s="19">
+        <v>1010025509</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>467</v>
@@ -3989,10 +4001,10 @@
     </row>
     <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="15">
-        <v>1010053728</v>
+        <v>1010027789</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>467</v>
@@ -4000,10 +4012,10 @@
     </row>
     <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="15">
-        <v>1010020758</v>
+        <v>1010027790</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>467</v>
@@ -4011,43 +4023,43 @@
     </row>
     <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="15">
-        <v>1010020781</v>
+        <v>1010018301</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="14">
-        <v>1010058426</v>
-      </c>
-      <c r="B175" s="9" t="s">
-        <v>165</v>
+      <c r="A175" s="15">
+        <v>1010031616</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="14">
-        <v>1010059332</v>
-      </c>
-      <c r="B176" s="9" t="s">
-        <v>166</v>
+      <c r="A176" s="15">
+        <v>1010053728</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="14">
-        <v>1040077389</v>
-      </c>
-      <c r="B177" s="9" t="s">
-        <v>167</v>
+      <c r="A177" s="15">
+        <v>1010020758</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>467</v>
@@ -4055,21 +4067,21 @@
     </row>
     <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="15">
-        <v>1010021364</v>
+        <v>1010020781</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" s="20">
-        <v>1010021541</v>
-      </c>
-      <c r="B179" s="5" t="s">
-        <v>169</v>
+      <c r="A179" s="14">
+        <v>1010058426</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>467</v>
@@ -4077,21 +4089,21 @@
     </row>
     <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="14">
-        <v>1010021955</v>
+        <v>1010059332</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A181" s="15">
-        <v>1040077388</v>
-      </c>
-      <c r="B181" s="5" t="s">
-        <v>171</v>
+      <c r="A181" s="14">
+        <v>1040077389</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>467</v>
@@ -4099,32 +4111,32 @@
     </row>
     <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="15">
-        <v>1010058100</v>
+        <v>1010021364</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" s="15">
-        <v>1010020524</v>
+      <c r="A183" s="20">
+        <v>1010021541</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="15">
-        <v>1010021958</v>
-      </c>
-      <c r="B184" s="5" t="s">
-        <v>174</v>
+      <c r="A184" s="14">
+        <v>1010021955</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>467</v>
@@ -4132,10 +4144,10 @@
     </row>
     <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="15">
-        <v>1010019756</v>
+        <v>1040077388</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>467</v>
@@ -4143,10 +4155,10 @@
     </row>
     <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="15">
-        <v>1010019752</v>
+        <v>1010058100</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>467</v>
@@ -4154,10 +4166,10 @@
     </row>
     <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="15">
-        <v>409639</v>
+        <v>1010020524</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>467</v>
@@ -4165,10 +4177,10 @@
     </row>
     <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="15">
-        <v>1010047089</v>
+        <v>1010021958</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>467</v>
@@ -4176,10 +4188,10 @@
     </row>
     <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="15">
-        <v>1040084107</v>
+        <v>1010019756</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>467</v>
@@ -4187,10 +4199,10 @@
     </row>
     <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="15">
-        <v>1010085203</v>
+        <v>1010019752</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>467</v>
@@ -4198,10 +4210,10 @@
     </row>
     <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="15">
-        <v>424298</v>
+        <v>409639</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>467</v>
@@ -4209,10 +4221,10 @@
     </row>
     <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="15">
-        <v>421847</v>
+        <v>1010047089</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>467</v>
@@ -4220,10 +4232,10 @@
     </row>
     <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="15">
-        <v>431573</v>
+        <v>1040084107</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>467</v>
@@ -4231,120 +4243,120 @@
     </row>
     <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="15">
+        <v>1010085203</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A195" s="15">
+        <v>424298</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A196" s="15">
+        <v>421847</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A197" s="15">
+        <v>431573</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A198" s="15">
         <v>1010021581</v>
       </c>
-      <c r="B194" s="5" t="s">
+      <c r="B198" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C194" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A195" s="21">
+      <c r="C198" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A199" s="21">
         <v>412413</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B199" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C195" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A196" s="22">
+      <c r="C199" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A200" s="22">
         <v>1010022606</v>
       </c>
-      <c r="B196" s="5" t="s">
+      <c r="B200" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C196" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A197" s="23">
+      <c r="C200" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A201" s="23">
         <v>1010003527</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B201" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C197" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A198" s="23">
+      <c r="C201" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A202" s="23">
         <v>1010055707</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B202" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="C198" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A199" s="18">
+      <c r="C202" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A203" s="18">
         <v>422027</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B203" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C199" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A200" s="14">
+      <c r="C203" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A204" s="14">
         <v>1010011313</v>
       </c>
-      <c r="B200" s="5" t="s">
+      <c r="B204" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A201" s="15">
-        <v>27051</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A202" s="15">
-        <v>1010011304</v>
-      </c>
-      <c r="B202" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A203" s="15">
-        <v>35659</v>
-      </c>
-      <c r="B203" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A204" s="15">
-        <v>1040077390</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>467</v>
@@ -4352,10 +4364,10 @@
     </row>
     <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="15">
-        <v>1010021542</v>
+        <v>27051</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>467</v>
@@ -4363,10 +4375,10 @@
     </row>
     <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="15">
-        <v>1010021733</v>
+        <v>1010011304</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>467</v>
@@ -4374,10 +4386,10 @@
     </row>
     <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="15">
-        <v>1010011379</v>
+        <v>35659</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>467</v>
@@ -4385,10 +4397,10 @@
     </row>
     <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="15">
-        <v>1010003279</v>
+        <v>1040077390</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>467</v>
@@ -4396,10 +4408,10 @@
     </row>
     <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="15">
-        <v>1010011380</v>
+        <v>1010021542</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>467</v>
@@ -4407,10 +4419,10 @@
     </row>
     <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="15">
-        <v>351197</v>
+        <v>1010021733</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>467</v>
@@ -4418,10 +4430,10 @@
     </row>
     <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="15">
-        <v>1010011286</v>
+        <v>1010011379</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>467</v>
@@ -4429,10 +4441,10 @@
     </row>
     <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="15">
-        <v>2479</v>
+        <v>1010003279</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>467</v>
@@ -4440,32 +4452,32 @@
     </row>
     <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="15">
-        <v>1010011382</v>
+        <v>1010011380</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A214" s="16">
-        <v>1010055703</v>
-      </c>
-      <c r="B214" s="8" t="s">
-        <v>203</v>
+      <c r="A214" s="15">
+        <v>351197</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A215" s="16">
-        <v>4165</v>
+      <c r="A215" s="15">
+        <v>1010011286</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>467</v>
@@ -4473,10 +4485,10 @@
     </row>
     <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="15">
-        <v>301626</v>
-      </c>
-      <c r="B216" s="9" t="s">
-        <v>205</v>
+        <v>2479</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>467</v>
@@ -4484,32 +4496,32 @@
     </row>
     <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="15">
-        <v>429495</v>
+        <v>1010011382</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A218" s="15">
-        <v>162998</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>207</v>
+      <c r="A218" s="16">
+        <v>1010055703</v>
+      </c>
+      <c r="B218" s="8" t="s">
+        <v>203</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A219" s="15">
-        <v>432657</v>
+      <c r="A219" s="16">
+        <v>4165</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>467</v>
@@ -4517,10 +4529,10 @@
     </row>
     <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="15">
-        <v>1010021929</v>
-      </c>
-      <c r="B220" s="5" t="s">
-        <v>209</v>
+        <v>301626</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>205</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>467</v>
@@ -4528,10 +4540,10 @@
     </row>
     <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="15">
-        <v>428065</v>
+        <v>429495</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C221" s="4" t="s">
         <v>467</v>
@@ -4539,10 +4551,10 @@
     </row>
     <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="15">
-        <v>1010003404</v>
+        <v>162998</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>467</v>
@@ -4550,10 +4562,10 @@
     </row>
     <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="15">
-        <v>1010003322</v>
-      </c>
-      <c r="B223" s="7" t="s">
-        <v>212</v>
+        <v>432657</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>208</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>467</v>
@@ -4561,10 +4573,10 @@
     </row>
     <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="15">
-        <v>17738</v>
-      </c>
-      <c r="B224" s="7" t="s">
-        <v>213</v>
+        <v>1010021929</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>467</v>
@@ -4572,10 +4584,10 @@
     </row>
     <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="15">
-        <v>1010085360</v>
-      </c>
-      <c r="B225" s="7" t="s">
-        <v>214</v>
+        <v>428065</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="C225" s="4" t="s">
         <v>467</v>
@@ -4583,10 +4595,10 @@
     </row>
     <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="15">
-        <v>1040077391</v>
+        <v>1010003404</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>467</v>
@@ -4594,10 +4606,10 @@
     </row>
     <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="15">
-        <v>1010058624</v>
-      </c>
-      <c r="B227" s="5" t="s">
-        <v>216</v>
+        <v>1010003322</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>467</v>
@@ -4605,10 +4617,10 @@
     </row>
     <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="15">
-        <v>1010024661</v>
-      </c>
-      <c r="B228" s="5" t="s">
-        <v>217</v>
+        <v>17738</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>213</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>467</v>
@@ -4616,10 +4628,10 @@
     </row>
     <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="15">
-        <v>1040019315</v>
-      </c>
-      <c r="B229" s="5" t="s">
-        <v>218</v>
+        <v>1010085360</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>467</v>
@@ -4627,10 +4639,10 @@
     </row>
     <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="15">
-        <v>1010021089</v>
+        <v>1040077391</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>467</v>
@@ -4638,10 +4650,10 @@
     </row>
     <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="15">
-        <v>1040017264</v>
+        <v>1010058624</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>467</v>
@@ -4649,10 +4661,10 @@
     </row>
     <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="15">
-        <v>1010051765</v>
+        <v>1010024661</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>467</v>
@@ -4660,10 +4672,10 @@
     </row>
     <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="15">
-        <v>1010035272</v>
+        <v>1040019315</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>467</v>
@@ -4671,10 +4683,10 @@
     </row>
     <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="15">
-        <v>1040077392</v>
+        <v>1010021089</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>467</v>
@@ -4682,10 +4694,10 @@
     </row>
     <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="15">
-        <v>1040077393</v>
+        <v>1040017264</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>467</v>
@@ -4693,10 +4705,10 @@
     </row>
     <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="15">
-        <v>1040077395</v>
+        <v>1010051765</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>467</v>
@@ -4704,10 +4716,10 @@
     </row>
     <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="15">
-        <v>1040077401</v>
+        <v>1010035272</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>467</v>
@@ -4715,10 +4727,10 @@
     </row>
     <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="15">
-        <v>27572</v>
+        <v>1040077392</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>467</v>
@@ -4726,10 +4738,10 @@
     </row>
     <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="15">
-        <v>18745</v>
+        <v>1040077393</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>467</v>
@@ -4737,10 +4749,10 @@
     </row>
     <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="15">
-        <v>1040077396</v>
+        <v>1040077395</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>467</v>
@@ -4748,10 +4760,10 @@
     </row>
     <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="15">
-        <v>1010036546</v>
+        <v>1040077401</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>467</v>
@@ -4759,10 +4771,10 @@
     </row>
     <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="15">
-        <v>1010014049</v>
+        <v>27572</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>467</v>
@@ -4770,10 +4782,10 @@
     </row>
     <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="15">
-        <v>1010025148</v>
+        <v>18745</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>467</v>
@@ -4781,10 +4793,10 @@
     </row>
     <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="15">
-        <v>1040077394</v>
+        <v>1040077396</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>467</v>
@@ -4792,10 +4804,10 @@
     </row>
     <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="15">
-        <v>1040077400</v>
+        <v>1010036546</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>467</v>
@@ -4803,10 +4815,10 @@
     </row>
     <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="15">
-        <v>1040079329</v>
+        <v>1010014049</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>467</v>
@@ -4814,10 +4826,10 @@
     </row>
     <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="15">
-        <v>1040040957</v>
+        <v>1010025148</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>467</v>
@@ -4825,10 +4837,10 @@
     </row>
     <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="15">
-        <v>1040077398</v>
+        <v>1040077394</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>467</v>
@@ -4836,10 +4848,10 @@
     </row>
     <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="15">
-        <v>1010031545</v>
+        <v>1040077400</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>467</v>
@@ -4847,10 +4859,10 @@
     </row>
     <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="15">
-        <v>1010053128</v>
+        <v>1040079329</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>467</v>
@@ -4858,10 +4870,10 @@
     </row>
     <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="15">
-        <v>1010010599</v>
+        <v>1040040957</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>467</v>
@@ -4869,10 +4881,10 @@
     </row>
     <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="15">
-        <v>1010056064</v>
+        <v>1040077398</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>467</v>
@@ -4880,10 +4892,10 @@
     </row>
     <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="15">
-        <v>5389</v>
+        <v>1010031545</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>467</v>
@@ -4891,10 +4903,10 @@
     </row>
     <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="15">
-        <v>1010055969</v>
+        <v>1010053128</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>467</v>
@@ -4902,10 +4914,10 @@
     </row>
     <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="15">
-        <v>1010055970</v>
+        <v>1010010599</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>467</v>
@@ -4913,21 +4925,21 @@
     </row>
     <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="15">
-        <v>181395</v>
+        <v>1010056064</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A257" s="17">
-        <v>1010055962</v>
+      <c r="A257" s="15">
+        <v>5389</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>467</v>
@@ -4935,10 +4947,10 @@
     </row>
     <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="15">
-        <v>1010003578</v>
+        <v>1010055969</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>467</v>
@@ -4946,10 +4958,10 @@
     </row>
     <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="15">
-        <v>332891</v>
+        <v>1010055970</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>467</v>
@@ -4957,21 +4969,21 @@
     </row>
     <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="15">
-        <v>17727</v>
+        <v>181395</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A261" s="15">
-        <v>17918</v>
+      <c r="A261" s="17">
+        <v>1010055962</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>467</v>
@@ -4979,10 +4991,10 @@
     </row>
     <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="15">
-        <v>1010020554</v>
+        <v>1010003578</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>467</v>
@@ -4990,10 +5002,10 @@
     </row>
     <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="15">
-        <v>1040085949</v>
+        <v>332891</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>467</v>
@@ -5001,10 +5013,10 @@
     </row>
     <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="15">
-        <v>1010062938</v>
+        <v>17727</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>467</v>
@@ -5012,10 +5024,10 @@
     </row>
     <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="15">
-        <v>1010062086</v>
+        <v>17918</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>467</v>
@@ -5023,10 +5035,10 @@
     </row>
     <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="15">
-        <v>1010062087</v>
+        <v>1010020554</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>467</v>
@@ -5034,43 +5046,43 @@
     </row>
     <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="15">
-        <v>1040077373</v>
+        <v>1040085949</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A268" s="24">
-        <v>1040077372</v>
-      </c>
-      <c r="B268" s="6" t="s">
-        <v>257</v>
+      <c r="A268" s="15">
+        <v>1010062938</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A269" s="24">
-        <v>1040097154</v>
-      </c>
-      <c r="B269" s="6" t="s">
-        <v>258</v>
+      <c r="A269" s="15">
+        <v>1010062086</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A270" s="24">
-        <v>1010042579</v>
-      </c>
-      <c r="B270" s="6" t="s">
-        <v>259</v>
+      <c r="A270" s="15">
+        <v>1010062087</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>467</v>
@@ -5078,43 +5090,43 @@
     </row>
     <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="15">
-        <v>1010029427</v>
+        <v>1040077373</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A272" s="15">
-        <v>133108</v>
-      </c>
-      <c r="B272" s="5" t="s">
-        <v>261</v>
+      <c r="A272" s="24">
+        <v>1040077372</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>257</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A273" s="15">
-        <v>269427</v>
-      </c>
-      <c r="B273" s="5" t="s">
-        <v>262</v>
+      <c r="A273" s="24">
+        <v>1040097154</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>258</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A274" s="15">
-        <v>298227</v>
-      </c>
-      <c r="B274" s="5" t="s">
-        <v>263</v>
+      <c r="A274" s="24">
+        <v>1010042579</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>467</v>
@@ -5122,10 +5134,10 @@
     </row>
     <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="15">
-        <v>1010062285</v>
+        <v>1010029427</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>467</v>
@@ -5133,10 +5145,10 @@
     </row>
     <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="15">
-        <v>1010058052</v>
+        <v>133108</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>467</v>
@@ -5144,43 +5156,43 @@
     </row>
     <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="15">
-        <v>1010050033</v>
+        <v>269427</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A278" s="20">
-        <v>1040098869</v>
+      <c r="A278" s="15">
+        <v>298227</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A279" s="20">
-        <v>1010056523</v>
+      <c r="A279" s="15">
+        <v>1010062285</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A280" s="20">
-        <v>1010062045</v>
+      <c r="A280" s="15">
+        <v>1010058052</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>467</v>
@@ -5188,43 +5200,43 @@
     </row>
     <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="15">
-        <v>1040097575</v>
+        <v>1010050033</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C281" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A282" s="15">
-        <v>1040098437</v>
+      <c r="A282" s="20">
+        <v>1040098869</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A283" s="15">
-        <v>1010040346</v>
+      <c r="A283" s="20">
+        <v>1010056523</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A284" s="15">
-        <v>1010021543</v>
+      <c r="A284" s="20">
+        <v>1010062045</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>467</v>
@@ -5232,10 +5244,10 @@
     </row>
     <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="15">
-        <v>1040077397</v>
+        <v>1040097575</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>467</v>
@@ -5243,10 +5255,10 @@
     </row>
     <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="15">
-        <v>1040094213</v>
+        <v>1040098437</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>467</v>
@@ -5254,10 +5266,10 @@
     </row>
     <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="15">
-        <v>1010085326</v>
+        <v>1010040346</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>467</v>
@@ -5265,10 +5277,10 @@
     </row>
     <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="15">
-        <v>1010042564</v>
+        <v>1010021543</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>467</v>
@@ -5276,10 +5288,10 @@
     </row>
     <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="15">
-        <v>1010042688</v>
+        <v>1040077397</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>467</v>
@@ -5287,10 +5299,10 @@
     </row>
     <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="15">
-        <v>1010040133</v>
+        <v>1040094213</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>467</v>
@@ -5298,10 +5310,10 @@
     </row>
     <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="15">
-        <v>1010039879</v>
+        <v>1010085326</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>467</v>
@@ -5309,10 +5321,10 @@
     </row>
     <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="15">
-        <v>62608</v>
+        <v>1010042564</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>467</v>
@@ -5320,10 +5332,10 @@
     </row>
     <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="15">
-        <v>1040098603</v>
+        <v>1010042688</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>467</v>
@@ -5331,10 +5343,10 @@
     </row>
     <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="15">
-        <v>1040017266</v>
+        <v>1010040133</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>467</v>
@@ -5342,10 +5354,10 @@
     </row>
     <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="15">
-        <v>1010063326</v>
+        <v>1010039879</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>467</v>
@@ -5353,21 +5365,21 @@
     </row>
     <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="15">
-        <v>1010050574</v>
+        <v>62608</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A297" s="20">
-        <v>1010086126</v>
+      <c r="A297" s="15">
+        <v>1040098603</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>467</v>
@@ -5375,10 +5387,10 @@
     </row>
     <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="15">
-        <v>1040019838</v>
+        <v>1040017266</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>467</v>
@@ -5386,10 +5398,10 @@
     </row>
     <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="15">
-        <v>1010042882</v>
+        <v>1010063326</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>467</v>
@@ -5397,21 +5409,21 @@
     </row>
     <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="15">
-        <v>1010042873</v>
+        <v>1010050574</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A301" s="15">
-        <v>1010026842</v>
+      <c r="A301" s="20">
+        <v>1010086126</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>499</v>
+        <v>286</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>467</v>
@@ -5419,10 +5431,10 @@
     </row>
     <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="15">
-        <v>1010026841</v>
+        <v>1040019838</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>500</v>
+        <v>287</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>467</v>
@@ -5430,10 +5442,10 @@
     </row>
     <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="15">
-        <v>1010059549</v>
+        <v>1010042882</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>467</v>
@@ -5441,10 +5453,10 @@
     </row>
     <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="15">
-        <v>1010020552</v>
+        <v>1010042873</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>467</v>
@@ -5452,10 +5464,10 @@
     </row>
     <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="15">
-        <v>1040078895</v>
+        <v>1010026842</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>292</v>
+        <v>499</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>467</v>
@@ -5463,10 +5475,10 @@
     </row>
     <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="15">
-        <v>1040024309</v>
+        <v>1010026841</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>293</v>
+        <v>500</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>467</v>
@@ -5474,10 +5486,10 @@
     </row>
     <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="15">
-        <v>1040024323</v>
+        <v>1010059549</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>467</v>
@@ -5485,10 +5497,10 @@
     </row>
     <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="15">
-        <v>1040024322</v>
+        <v>1010020552</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>467</v>
@@ -5496,10 +5508,10 @@
     </row>
     <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="15">
-        <v>1040024314</v>
+        <v>1040078895</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>467</v>
@@ -5507,10 +5519,10 @@
     </row>
     <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="15">
-        <v>1010059685</v>
+        <v>1040024309</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>467</v>
@@ -5518,10 +5530,10 @@
     </row>
     <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="15">
-        <v>1010059687</v>
+        <v>1040024323</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>467</v>
@@ -5529,21 +5541,21 @@
     </row>
     <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="15">
-        <v>1010077469</v>
+        <v>1040024322</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A313" s="19">
-        <v>1010077470</v>
+      <c r="A313" s="15">
+        <v>1040024314</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>467</v>
@@ -5551,43 +5563,43 @@
     </row>
     <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="15">
-        <v>1010084519</v>
-      </c>
-      <c r="B314" s="7" t="s">
-        <v>301</v>
+        <v>1010059685</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>297</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A315" s="14">
-        <v>1010084108</v>
+      <c r="A315" s="15">
+        <v>1010059687</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A316" s="14">
-        <v>1010042884</v>
+      <c r="A316" s="15">
+        <v>1010077469</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>495</v>
+        <v>299</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A317" s="15">
-        <v>1040043537</v>
+      <c r="A317" s="19">
+        <v>1010077470</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>467</v>
@@ -5595,32 +5607,32 @@
     </row>
     <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="15">
-        <v>1010046401</v>
-      </c>
-      <c r="B318" s="5" t="s">
-        <v>304</v>
+        <v>1010084519</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>301</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A319" s="15">
-        <v>1010062007</v>
+      <c r="A319" s="14">
+        <v>1010084108</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A320" s="15">
-        <v>1010051284</v>
+      <c r="A320" s="14">
+        <v>1010042884</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>306</v>
+        <v>495</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>467</v>
@@ -5628,10 +5640,10 @@
     </row>
     <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="15">
-        <v>1010027788</v>
+        <v>1040043537</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>467</v>
@@ -5639,10 +5651,10 @@
     </row>
     <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="15">
-        <v>1010027786</v>
+        <v>1010046401</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>467</v>
@@ -5650,21 +5662,21 @@
     </row>
     <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="15">
-        <v>1010026889</v>
+        <v>1010062007</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A324" s="24">
-        <v>1010042358</v>
+      <c r="A324" s="15">
+        <v>1010051284</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>467</v>
@@ -5672,10 +5684,10 @@
     </row>
     <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="15">
-        <v>1040023848</v>
+        <v>1010027788</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>467</v>
@@ -5683,10 +5695,10 @@
     </row>
     <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="15">
-        <v>1010042341</v>
+        <v>1010027786</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>467</v>
@@ -5694,21 +5706,21 @@
     </row>
     <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="15">
-        <v>1040023858</v>
+        <v>1010026889</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A328" s="15">
-        <v>1040023843</v>
+      <c r="A328" s="24">
+        <v>1010042358</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>467</v>
@@ -5716,10 +5728,10 @@
     </row>
     <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="15">
-        <v>1040077411</v>
+        <v>1040023848</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>467</v>
@@ -5727,10 +5739,10 @@
     </row>
     <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="15">
-        <v>1040077410</v>
+        <v>1010042341</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>467</v>
@@ -5738,10 +5750,10 @@
     </row>
     <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="15">
-        <v>1010062008</v>
+        <v>1040023858</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>467</v>
@@ -5749,10 +5761,10 @@
     </row>
     <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="15">
-        <v>1040040960</v>
+        <v>1040023843</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>467</v>
@@ -5760,10 +5772,10 @@
     </row>
     <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="15">
-        <v>409578</v>
+        <v>1040077411</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>467</v>
@@ -5771,10 +5783,10 @@
     </row>
     <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="15">
-        <v>1040077360</v>
+        <v>1040077410</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>467</v>
@@ -5782,10 +5794,10 @@
     </row>
     <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="15">
-        <v>1010064470</v>
+        <v>1010062008</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>467</v>
@@ -5793,10 +5805,10 @@
     </row>
     <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="15">
-        <v>1010021991</v>
+        <v>1040040960</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>467</v>
@@ -5804,10 +5816,10 @@
     </row>
     <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="15">
-        <v>1010021960</v>
+        <v>409578</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>467</v>
@@ -5815,10 +5827,10 @@
     </row>
     <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="15">
-        <v>1010031545</v>
+        <v>1040077360</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>467</v>
@@ -5826,10 +5838,10 @@
     </row>
     <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="15">
-        <v>1010031690</v>
+        <v>1010064470</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>489</v>
+        <v>321</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>467</v>
@@ -5837,10 +5849,10 @@
     </row>
     <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="15">
-        <v>1010022590</v>
+        <v>1010021991</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>467</v>
@@ -5848,10 +5860,10 @@
     </row>
     <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="15">
-        <v>1040098643</v>
+        <v>1010021960</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>467</v>
@@ -5859,10 +5871,10 @@
     </row>
     <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="15">
-        <v>1010086020</v>
+        <v>1010031545</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>467</v>
@@ -5870,10 +5882,10 @@
     </row>
     <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="15">
-        <v>1010046550</v>
+        <v>1010031690</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>328</v>
+        <v>489</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>467</v>
@@ -5881,10 +5893,10 @@
     </row>
     <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="15">
-        <v>1010046402</v>
+        <v>1010022590</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>467</v>
@@ -5892,10 +5904,10 @@
     </row>
     <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="15">
-        <v>1010060291</v>
+        <v>1040098643</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>467</v>
@@ -5903,10 +5915,10 @@
     </row>
     <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="15">
-        <v>1010050920</v>
+        <v>1010086020</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>467</v>
@@ -5914,10 +5926,10 @@
     </row>
     <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="15">
-        <v>1040077412</v>
+        <v>1010046550</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>467</v>
@@ -5925,10 +5937,10 @@
     </row>
     <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="15">
-        <v>1010042609</v>
+        <v>1010046402</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>467</v>
@@ -5936,10 +5948,10 @@
     </row>
     <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="15">
-        <v>417701</v>
+        <v>1010060291</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>467</v>
@@ -5947,10 +5959,10 @@
     </row>
     <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="15">
-        <v>399384</v>
+        <v>1010050920</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>467</v>
@@ -5958,10 +5970,10 @@
     </row>
     <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="15">
-        <v>1010024086</v>
+        <v>1040077412</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>496</v>
+        <v>332</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>467</v>
@@ -5969,10 +5981,10 @@
     </row>
     <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="15">
-        <v>1040077345</v>
+        <v>1010042609</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>467</v>
@@ -5980,10 +5992,10 @@
     </row>
     <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="15">
-        <v>1010084315</v>
+        <v>417701</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>467</v>
@@ -5991,10 +6003,10 @@
     </row>
     <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="15">
-        <v>399253</v>
+        <v>399384</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>467</v>
@@ -6002,21 +6014,21 @@
     </row>
     <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="15">
-        <v>1010084317</v>
+        <v>1010024086</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>339</v>
+        <v>496</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A356" s="25">
-        <v>1010085369</v>
+      <c r="A356" s="15">
+        <v>1040077345</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>467</v>
@@ -6024,10 +6036,10 @@
     </row>
     <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="15">
-        <v>1010085370</v>
+        <v>1010084315</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>467</v>
@@ -6035,10 +6047,10 @@
     </row>
     <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="15">
-        <v>1010085204</v>
+        <v>399253</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>467</v>
@@ -6046,21 +6058,21 @@
     </row>
     <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="15">
-        <v>1010003966</v>
+        <v>1010084317</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A360" s="15">
-        <v>1010003967</v>
+      <c r="A360" s="25">
+        <v>1010085369</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>467</v>
@@ -6068,10 +6080,10 @@
     </row>
     <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="15">
-        <v>65219</v>
+        <v>1010085370</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>467</v>
@@ -6079,10 +6091,10 @@
     </row>
     <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="15">
-        <v>10168</v>
+        <v>1010085204</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>467</v>
@@ -6090,10 +6102,10 @@
     </row>
     <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="15">
-        <v>1010083792</v>
+        <v>1010003966</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>467</v>
@@ -6101,10 +6113,10 @@
     </row>
     <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="15">
-        <v>1040077414</v>
+        <v>1010003967</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>467</v>
@@ -6112,10 +6124,10 @@
     </row>
     <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="15">
-        <v>1010018482</v>
+        <v>65219</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>467</v>
@@ -6123,10 +6135,10 @@
     </row>
     <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="15">
-        <v>1010084320</v>
+        <v>10168</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>467</v>
@@ -6134,10 +6146,10 @@
     </row>
     <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="15">
-        <v>1010084532</v>
+        <v>1010083792</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>467</v>
@@ -6145,10 +6157,10 @@
     </row>
     <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="15">
-        <v>1010027285</v>
+        <v>1040077414</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>467</v>
@@ -6156,10 +6168,10 @@
     </row>
     <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="15">
-        <v>1040077413</v>
+        <v>1010018482</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>467</v>
@@ -6167,10 +6179,10 @@
     </row>
     <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="15">
-        <v>1010085376</v>
+        <v>1010084320</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>467</v>
@@ -6178,10 +6190,10 @@
     </row>
     <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="15">
-        <v>1010022819</v>
+        <v>1010084532</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>467</v>
@@ -6189,10 +6201,10 @@
     </row>
     <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="15">
-        <v>1010052853</v>
+        <v>1010027285</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>467</v>
@@ -6200,87 +6212,87 @@
     </row>
     <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="15">
-        <v>1010084377</v>
+        <v>1040077413</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C373" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A374" s="26">
-        <v>1010062826</v>
+      <c r="A374" s="15">
+        <v>1010085376</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>470</v>
+        <v>354</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="15">
-        <v>1010002592</v>
+        <v>1010022819</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>471</v>
+        <v>355</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A376" s="24">
-        <v>1010001155</v>
+      <c r="A376" s="15">
+        <v>1010052853</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>472</v>
+        <v>356</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="15">
-        <v>1010001062</v>
+        <v>1010084377</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>473</v>
+        <v>357</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A378" s="15">
-        <v>1010084328</v>
+      <c r="A378" s="26">
+        <v>1010062826</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A379" s="24">
-        <v>1010044502</v>
+      <c r="A379" s="15">
+        <v>1010002592</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A380" s="15">
-        <v>1010053692</v>
+      <c r="A380" s="24">
+        <v>1010001155</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>478</v>
@@ -6288,10 +6300,10 @@
     </row>
     <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="15">
-        <v>1010083992</v>
+        <v>1010001062</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>478</v>
@@ -6299,54 +6311,54 @@
     </row>
     <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="15">
-        <v>1010008578</v>
+        <v>1010084328</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A383" s="15">
-        <v>1010031694</v>
+      <c r="A383" s="24">
+        <v>1010044502</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>359</v>
+        <v>475</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="15">
-        <v>1010051997</v>
+        <v>1010053692</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>360</v>
+        <v>476</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="15">
-        <v>1010022601</v>
+        <v>1010083992</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>361</v>
+        <v>477</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="15">
-        <v>1010054278</v>
+        <v>1010008578</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C386" s="4" t="s">
         <v>468</v>
@@ -6354,10 +6366,10 @@
     </row>
     <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="15">
-        <v>1010083462</v>
+        <v>1010031694</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C387" s="4" t="s">
         <v>468</v>
@@ -6365,10 +6377,10 @@
     </row>
     <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="15">
-        <v>1010027772</v>
+        <v>1010051997</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>468</v>
@@ -6376,98 +6388,98 @@
     </row>
     <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="15">
-        <v>1010084144</v>
+        <v>1010022601</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A390" s="19">
-        <v>214055</v>
-      </c>
-      <c r="B390" s="7" t="s">
-        <v>366</v>
+      <c r="A390" s="15">
+        <v>1010054278</v>
+      </c>
+      <c r="B390" s="5" t="s">
+        <v>362</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A391" s="18">
-        <v>1010021956</v>
-      </c>
-      <c r="B391" s="7" t="s">
-        <v>367</v>
+      <c r="A391" s="15">
+        <v>1010083462</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>363</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A392" s="18">
-        <v>1010026464</v>
-      </c>
-      <c r="B392" s="7" t="s">
-        <v>368</v>
+      <c r="A392" s="15">
+        <v>1010027772</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>364</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A393" s="14">
-        <v>1010021957</v>
+      <c r="A393" s="15">
+        <v>1010084144</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A394" s="15">
-        <v>1010026462</v>
-      </c>
-      <c r="B394" s="5" t="s">
-        <v>370</v>
+      <c r="A394" s="19">
+        <v>214055</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>366</v>
       </c>
       <c r="C394" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A395" s="15">
-        <v>1010026551</v>
-      </c>
-      <c r="B395" s="5" t="s">
-        <v>371</v>
+      <c r="A395" s="18">
+        <v>1010021956</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>367</v>
       </c>
       <c r="C395" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A396" s="15">
-        <v>1010042554</v>
-      </c>
-      <c r="B396" s="5" t="s">
-        <v>372</v>
+      <c r="A396" s="18">
+        <v>1010026464</v>
+      </c>
+      <c r="B396" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A397" s="15">
-        <v>1010039904</v>
+      <c r="A397" s="14">
+        <v>1010021957</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>468</v>
@@ -6475,10 +6487,10 @@
     </row>
     <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="15">
-        <v>1010060205</v>
+        <v>1010026462</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>468</v>
@@ -6486,10 +6498,10 @@
     </row>
     <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="15">
-        <v>1010060206</v>
+        <v>1010026551</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>468</v>
@@ -6497,10 +6509,10 @@
     </row>
     <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="15">
-        <v>1010077431</v>
+        <v>1010042554</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>468</v>
@@ -6508,10 +6520,10 @@
     </row>
     <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="15">
-        <v>1010077503</v>
+        <v>1010039904</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>468</v>
@@ -6519,10 +6531,10 @@
     </row>
     <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="15">
-        <v>1010084187</v>
+        <v>1010060205</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>468</v>
@@ -6530,10 +6542,10 @@
     </row>
     <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="15">
-        <v>1010080958</v>
+        <v>1010060206</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>468</v>
@@ -6541,10 +6553,10 @@
     </row>
     <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="15">
-        <v>1010026032</v>
+        <v>1010077431</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>468</v>
@@ -6552,10 +6564,10 @@
     </row>
     <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="15">
-        <v>1010085384</v>
+        <v>1010077503</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>468</v>
@@ -6563,10 +6575,10 @@
     </row>
     <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="15">
-        <v>1010006347</v>
+        <v>1010084187</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>468</v>
@@ -6574,10 +6586,10 @@
     </row>
     <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="15">
-        <v>1010085179</v>
+        <v>1010080958</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>468</v>
@@ -6585,10 +6597,10 @@
     </row>
     <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="15">
-        <v>1010024158</v>
-      </c>
-      <c r="B408" s="8" t="s">
-        <v>384</v>
+        <v>1010026032</v>
+      </c>
+      <c r="B408" s="5" t="s">
+        <v>380</v>
       </c>
       <c r="C408" s="4" t="s">
         <v>468</v>
@@ -6596,10 +6608,10 @@
     </row>
     <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="15">
-        <v>1010024131</v>
-      </c>
-      <c r="B409" s="8" t="s">
-        <v>385</v>
+        <v>1010085384</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="C409" s="4" t="s">
         <v>468</v>
@@ -6607,10 +6619,10 @@
     </row>
     <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="15">
-        <v>1010007160</v>
+        <v>1010006347</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>468</v>
@@ -6618,10 +6630,10 @@
     </row>
     <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="15">
-        <v>1010023642</v>
+        <v>1010085179</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C411" s="4" t="s">
         <v>468</v>
@@ -6629,10 +6641,10 @@
     </row>
     <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="15">
-        <v>1010007193</v>
-      </c>
-      <c r="B412" s="6" t="s">
-        <v>388</v>
+        <v>1010024158</v>
+      </c>
+      <c r="B412" s="8" t="s">
+        <v>384</v>
       </c>
       <c r="C412" s="4" t="s">
         <v>468</v>
@@ -6640,10 +6652,10 @@
     </row>
     <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="15">
-        <v>1010042637</v>
-      </c>
-      <c r="B413" s="5" t="s">
-        <v>389</v>
+        <v>1010024131</v>
+      </c>
+      <c r="B413" s="8" t="s">
+        <v>385</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>468</v>
@@ -6651,10 +6663,10 @@
     </row>
     <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="15">
-        <v>1040075323</v>
+        <v>1010007160</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>468</v>
@@ -6662,54 +6674,54 @@
     </row>
     <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="15">
-        <v>1040075324</v>
-      </c>
-      <c r="B415" s="8" t="s">
-        <v>391</v>
+        <v>1010023642</v>
+      </c>
+      <c r="B415" s="5" t="s">
+        <v>387</v>
       </c>
       <c r="C415" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A416" s="27">
-        <v>1040074827</v>
-      </c>
-      <c r="B416" s="8" t="s">
-        <v>497</v>
+      <c r="A416" s="15">
+        <v>1010007193</v>
+      </c>
+      <c r="B416" s="6" t="s">
+        <v>388</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A417" s="27">
-        <v>1040099488</v>
-      </c>
-      <c r="B417" s="8" t="s">
-        <v>498</v>
+      <c r="A417" s="15">
+        <v>1010042637</v>
+      </c>
+      <c r="B417" s="5" t="s">
+        <v>389</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A418" s="27">
-        <v>1040083312</v>
-      </c>
-      <c r="B418" s="8" t="s">
-        <v>392</v>
+      <c r="A418" s="15">
+        <v>1040075323</v>
+      </c>
+      <c r="B418" s="5" t="s">
+        <v>390</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A419" s="27">
-        <v>1040077661</v>
+      <c r="A419" s="15">
+        <v>1040075324</v>
       </c>
       <c r="B419" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>468</v>
@@ -6717,76 +6729,76 @@
     </row>
     <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="27">
-        <v>1010085180</v>
-      </c>
-      <c r="B420" s="12" t="s">
-        <v>394</v>
+        <v>1040074827</v>
+      </c>
+      <c r="B420" s="8" t="s">
+        <v>497</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A421" s="14">
-        <v>1040017489</v>
-      </c>
-      <c r="B421" s="9" t="s">
-        <v>395</v>
+      <c r="A421" s="27">
+        <v>1040099488</v>
+      </c>
+      <c r="B421" s="8" t="s">
+        <v>498</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A422" s="14">
-        <v>1010085181</v>
-      </c>
-      <c r="B422" s="5" t="s">
-        <v>396</v>
+      <c r="A422" s="27">
+        <v>1040083312</v>
+      </c>
+      <c r="B422" s="8" t="s">
+        <v>392</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A423" s="15">
-        <v>400175</v>
-      </c>
-      <c r="B423" s="5" t="s">
-        <v>397</v>
+      <c r="A423" s="27">
+        <v>1040077661</v>
+      </c>
+      <c r="B423" s="8" t="s">
+        <v>393</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A424" s="15">
-        <v>1040017505</v>
-      </c>
-      <c r="B424" s="5" t="s">
-        <v>398</v>
+      <c r="A424" s="27">
+        <v>1010085180</v>
+      </c>
+      <c r="B424" s="12" t="s">
+        <v>394</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A425" s="15">
-        <v>1040017503</v>
-      </c>
-      <c r="B425" s="5" t="s">
-        <v>399</v>
+      <c r="A425" s="14">
+        <v>1040017489</v>
+      </c>
+      <c r="B425" s="9" t="s">
+        <v>395</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A426" s="15">
-        <v>1010046445</v>
+      <c r="A426" s="14">
+        <v>1010085181</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>468</v>
@@ -6794,10 +6806,10 @@
     </row>
     <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="15">
-        <v>1010021033</v>
+        <v>400175</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>468</v>
@@ -6805,10 +6817,10 @@
     </row>
     <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="15">
-        <v>1010057142</v>
+        <v>1040017505</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>468</v>
@@ -6816,10 +6828,10 @@
     </row>
     <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="15">
-        <v>1010016356</v>
+        <v>1040017503</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>468</v>
@@ -6827,10 +6839,10 @@
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="15">
-        <v>1010084363</v>
+        <v>1010046445</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>468</v>
@@ -6838,10 +6850,10 @@
     </row>
     <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="15">
-        <v>1010052021</v>
+        <v>1010021033</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>468</v>
@@ -6849,10 +6861,10 @@
     </row>
     <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="15">
-        <v>1040091721</v>
+        <v>1010057142</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C432" s="4" t="s">
         <v>468</v>
@@ -6860,10 +6872,10 @@
     </row>
     <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="15">
-        <v>1010062022</v>
+        <v>1010016356</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>468</v>
@@ -6871,10 +6883,10 @@
     </row>
     <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="15">
-        <v>18336</v>
+        <v>1010084363</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>468</v>
@@ -6882,10 +6894,10 @@
     </row>
     <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="15">
-        <v>229205</v>
+        <v>1010052021</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>468</v>
@@ -6893,10 +6905,10 @@
     </row>
     <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="15">
-        <v>60671</v>
+        <v>1040091721</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>468</v>
@@ -6904,10 +6916,10 @@
     </row>
     <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="15">
-        <v>1010059726</v>
+        <v>1010062022</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C437" s="4" t="s">
         <v>468</v>
@@ -6915,10 +6927,10 @@
     </row>
     <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="15">
-        <v>1010008144</v>
+        <v>18336</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>468</v>
@@ -6926,10 +6938,10 @@
     </row>
     <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="15">
-        <v>1010007244</v>
+        <v>229205</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>468</v>
@@ -6937,10 +6949,10 @@
     </row>
     <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="15">
-        <v>1010006827</v>
+        <v>60671</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>468</v>
@@ -6948,10 +6960,10 @@
     </row>
     <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="15">
-        <v>1040075426</v>
+        <v>1010059726</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>468</v>
@@ -6959,10 +6971,10 @@
     </row>
     <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="15">
-        <v>1040075427</v>
+        <v>1010008144</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>468</v>
@@ -6970,10 +6982,10 @@
     </row>
     <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="15">
-        <v>1010084313</v>
+        <v>1010007244</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>468</v>
@@ -6981,10 +6993,10 @@
     </row>
     <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="15">
-        <v>403459</v>
+        <v>1010006827</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C444" s="4" t="s">
         <v>468</v>
@@ -6992,10 +7004,10 @@
     </row>
     <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="15">
-        <v>1010044828</v>
+        <v>1040075426</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>468</v>
@@ -7003,10 +7015,10 @@
     </row>
     <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="15">
-        <v>1010026973</v>
+        <v>1040075427</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>468</v>
@@ -7014,65 +7026,65 @@
     </row>
     <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="15">
-        <v>1040017204</v>
+        <v>1010084313</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C447" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="24">
-        <v>1010022119</v>
-      </c>
-      <c r="B448" s="6" t="s">
-        <v>427</v>
+      <c r="A448" s="15">
+        <v>403459</v>
+      </c>
+      <c r="B448" s="5" t="s">
+        <v>418</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="15">
-        <v>1010058709</v>
+        <v>1010044828</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="15">
-        <v>1010025711</v>
+        <v>1010026973</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="15">
-        <v>1010059684</v>
+        <v>1040017204</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="15">
-        <v>427341</v>
-      </c>
-      <c r="B452" s="5" t="s">
-        <v>431</v>
+      <c r="A452" s="24">
+        <v>1010022119</v>
+      </c>
+      <c r="B452" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>479</v>
@@ -7080,21 +7092,21 @@
     </row>
     <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="15">
-        <v>1010085279</v>
+        <v>1010058709</v>
       </c>
       <c r="B453" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C453" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="19">
-        <v>1010022588</v>
+      <c r="A454" s="15">
+        <v>1010025711</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>479</v>
@@ -7102,43 +7114,43 @@
     </row>
     <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="15">
-        <v>1010026864</v>
-      </c>
-      <c r="B455" s="7" t="s">
-        <v>434</v>
+        <v>1010059684</v>
+      </c>
+      <c r="B455" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="14">
-        <v>1010030946</v>
-      </c>
-      <c r="B456" s="7" t="s">
-        <v>435</v>
+      <c r="A456" s="15">
+        <v>427341</v>
+      </c>
+      <c r="B456" s="5" t="s">
+        <v>431</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A457" s="14">
-        <v>1010022589</v>
+      <c r="A457" s="15">
+        <v>1010085279</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="15">
-        <v>1040090143</v>
+      <c r="A458" s="19">
+        <v>1010022588</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>479</v>
@@ -7146,32 +7158,32 @@
     </row>
     <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="15">
-        <v>1040090138</v>
-      </c>
-      <c r="B459" s="5" t="s">
-        <v>438</v>
+        <v>1010026864</v>
+      </c>
+      <c r="B459" s="7" t="s">
+        <v>434</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="15">
-        <v>1030001314</v>
-      </c>
-      <c r="B460" s="5" t="s">
-        <v>439</v>
+      <c r="A460" s="14">
+        <v>1010030946</v>
+      </c>
+      <c r="B460" s="7" t="s">
+        <v>435</v>
       </c>
       <c r="C460" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="15">
-        <v>1010052319</v>
+      <c r="A461" s="14">
+        <v>1010022589</v>
       </c>
       <c r="B461" s="5" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C461" s="4" t="s">
         <v>479</v>
@@ -7179,10 +7191,10 @@
     </row>
     <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="15">
-        <v>1010052320</v>
+        <v>1040090143</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C462" s="4" t="s">
         <v>479</v>
@@ -7190,10 +7202,10 @@
     </row>
     <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="15">
-        <v>1030000370</v>
+        <v>1040090138</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>481</v>
+        <v>438</v>
       </c>
       <c r="C463" s="4" t="s">
         <v>479</v>
@@ -7201,10 +7213,10 @@
     </row>
     <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="15">
-        <v>1030000366</v>
+        <v>1030001314</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>482</v>
+        <v>439</v>
       </c>
       <c r="C464" s="4" t="s">
         <v>479</v>
@@ -7212,10 +7224,10 @@
     </row>
     <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="15">
-        <v>1030000368</v>
+        <v>1010052319</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>483</v>
+        <v>440</v>
       </c>
       <c r="C465" s="4" t="s">
         <v>479</v>
@@ -7223,10 +7235,10 @@
     </row>
     <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="15">
-        <v>1030000369</v>
+        <v>1010052320</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>484</v>
+        <v>441</v>
       </c>
       <c r="C466" s="4" t="s">
         <v>479</v>
@@ -7234,10 +7246,10 @@
     </row>
     <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" s="15">
-        <v>1030000489</v>
+        <v>1030000370</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C467" s="4" t="s">
         <v>479</v>
@@ -7245,10 +7257,10 @@
     </row>
     <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="15">
-        <v>1030000490</v>
+        <v>1030000366</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C468" s="4" t="s">
         <v>479</v>
@@ -7256,10 +7268,10 @@
     </row>
     <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="15">
-        <v>1030000821</v>
+        <v>1030000368</v>
       </c>
       <c r="B469" s="5" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C469" s="4" t="s">
         <v>479</v>
@@ -7267,32 +7279,32 @@
     </row>
     <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="15">
-        <v>1030000511</v>
-      </c>
-      <c r="B470" s="8" t="s">
-        <v>488</v>
+        <v>1030000369</v>
+      </c>
+      <c r="B470" s="5" t="s">
+        <v>484</v>
       </c>
       <c r="C470" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A471" s="16">
-        <v>1010084279</v>
-      </c>
-      <c r="B471" s="8" t="s">
-        <v>442</v>
+      <c r="A471" s="15">
+        <v>1030000489</v>
+      </c>
+      <c r="B471" s="5" t="s">
+        <v>485</v>
       </c>
       <c r="C471" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A472" s="16">
-        <v>1010004281</v>
+      <c r="A472" s="15">
+        <v>1030000490</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>443</v>
+        <v>486</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>479</v>
@@ -7300,10 +7312,10 @@
     </row>
     <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="15">
-        <v>1010022118</v>
-      </c>
-      <c r="B473" s="9" t="s">
-        <v>444</v>
+        <v>1030000821</v>
+      </c>
+      <c r="B473" s="5" t="s">
+        <v>487</v>
       </c>
       <c r="C473" s="4" t="s">
         <v>479</v>
@@ -7311,76 +7323,76 @@
     </row>
     <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="15">
-        <v>1010028657</v>
-      </c>
-      <c r="B474" s="5" t="s">
-        <v>445</v>
+        <v>1030000511</v>
+      </c>
+      <c r="B474" s="8" t="s">
+        <v>488</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A475" s="18">
-        <v>1010028655</v>
-      </c>
-      <c r="B475" s="5" t="s">
-        <v>446</v>
+      <c r="A475" s="16">
+        <v>1010084279</v>
+      </c>
+      <c r="B475" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A476" s="18">
-        <v>145165</v>
+      <c r="A476" s="16">
+        <v>1010004281</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="15">
-        <v>51666</v>
-      </c>
-      <c r="B477" s="5" t="s">
-        <v>448</v>
+        <v>1010022118</v>
+      </c>
+      <c r="B477" s="9" t="s">
+        <v>444</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="18">
-        <v>1010080930</v>
+      <c r="A478" s="15">
+        <v>1010028657</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C478" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="15">
-        <v>161055</v>
+      <c r="A479" s="18">
+        <v>1010028655</v>
       </c>
       <c r="B479" s="5" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C479" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="15">
-        <v>1010050517</v>
+      <c r="A480" s="18">
+        <v>145165</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C480" s="4" t="s">
         <v>469</v>
@@ -7388,21 +7400,21 @@
     </row>
     <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="15">
-        <v>1010084190</v>
+        <v>51666</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C481" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="15">
-        <v>1010084195</v>
+      <c r="A482" s="18">
+        <v>1010080930</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>469</v>
@@ -7410,98 +7422,98 @@
     </row>
     <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" s="15">
-        <v>1010001400</v>
+        <v>161055</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="17">
-        <v>1010008416</v>
+      <c r="A484" s="15">
+        <v>1010050517</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C484" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A485" s="28">
-        <v>1010018372</v>
+      <c r="A485" s="15">
+        <v>1010084190</v>
       </c>
       <c r="B485" s="5" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="28">
-        <v>1010018361</v>
-      </c>
-      <c r="B486" s="8" t="s">
-        <v>457</v>
+      <c r="A486" s="15">
+        <v>1010084195</v>
+      </c>
+      <c r="B486" s="5" t="s">
+        <v>453</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A487" s="16">
-        <v>1010055398</v>
-      </c>
-      <c r="B487" s="11" t="s">
-        <v>458</v>
+      <c r="A487" s="15">
+        <v>1010001400</v>
+      </c>
+      <c r="B487" s="5" t="s">
+        <v>454</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A488" s="15">
-        <v>422131</v>
+      <c r="A488" s="17">
+        <v>1010008416</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A489" s="15">
-        <v>1010084370</v>
+      <c r="A489" s="28">
+        <v>1010018372</v>
       </c>
       <c r="B489" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C489" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A490" s="15">
-        <v>422759</v>
-      </c>
-      <c r="B490" s="5" t="s">
-        <v>461</v>
+      <c r="A490" s="28">
+        <v>1010018361</v>
+      </c>
+      <c r="B490" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="C490" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A491" s="15">
-        <v>120955</v>
-      </c>
-      <c r="B491" s="5" t="s">
-        <v>462</v>
+      <c r="A491" s="16">
+        <v>1010055398</v>
+      </c>
+      <c r="B491" s="11" t="s">
+        <v>458</v>
       </c>
       <c r="C491" s="4" t="s">
         <v>469</v>
@@ -7509,106 +7521,134 @@
     </row>
     <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="15">
-        <v>1010000896</v>
+        <v>422131</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C492" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="C492" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" s="15">
-        <v>1010084308</v>
+        <v>1010084370</v>
       </c>
       <c r="B493" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C493" s="13" t="s">
+        <v>460</v>
+      </c>
+      <c r="C493" s="4" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="15">
+        <v>422759</v>
+      </c>
+      <c r="B494" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C494" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A495" s="15">
+        <v>120955</v>
+      </c>
+      <c r="B495" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C495" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A496" s="15">
+        <v>1010000896</v>
+      </c>
+      <c r="B496" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C496" s="13" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A497" s="15">
+        <v>1010084308</v>
+      </c>
+      <c r="B497" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C497" s="13" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A498" s="15">
         <v>1010084035</v>
       </c>
-      <c r="B494" s="5" t="s">
+      <c r="B498" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="C494" s="13" t="s">
+      <c r="C498" s="13" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A495" s="2"/>
-      <c r="B495" s="2"/>
-    </row>
-    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A496" s="2"/>
-      <c r="B496" s="2"/>
-    </row>
-    <row r="497" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A497" s="2"/>
-      <c r="B497" s="2"/>
-    </row>
-    <row r="498" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A498" s="2"/>
-      <c r="B498" s="2"/>
-    </row>
-    <row r="499" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
     </row>
-    <row r="500" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
     </row>
-    <row r="501" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
     </row>
-    <row r="502" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
     </row>
-    <row r="503" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
     </row>
-    <row r="504" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
     </row>
-    <row r="505" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
     </row>
-    <row r="506" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
     </row>
-    <row r="507" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
     </row>
-    <row r="508" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
     </row>
-    <row r="509" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
     </row>
-    <row r="510" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
     </row>
-    <row r="511" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
     </row>
-    <row r="512" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
     </row>
@@ -9298,19 +9338,19 @@
     </row>
     <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="2"/>
-      <c r="B934" s="1"/>
+      <c r="B934" s="2"/>
     </row>
     <row r="935" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A935" s="2"/>
-      <c r="B935" s="1"/>
+      <c r="B935" s="2"/>
     </row>
     <row r="936" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A936" s="2"/>
-      <c r="B936" s="1"/>
+      <c r="B936" s="2"/>
     </row>
     <row r="937" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A937" s="2"/>
-      <c r="B937" s="1"/>
+      <c r="B937" s="2"/>
     </row>
     <row r="938" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A938" s="2"/>
@@ -9569,19 +9609,19 @@
       <c r="B1001" s="1"/>
     </row>
     <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1002" s="1"/>
+      <c r="A1002" s="2"/>
       <c r="B1002" s="1"/>
     </row>
     <row r="1003" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1003" s="1"/>
+      <c r="A1003" s="2"/>
       <c r="B1003" s="1"/>
     </row>
     <row r="1004" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1004" s="1"/>
+      <c r="A1004" s="2"/>
       <c r="B1004" s="1"/>
     </row>
     <row r="1005" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1005" s="1"/>
+      <c r="A1005" s="2"/>
       <c r="B1005" s="1"/>
     </row>
     <row r="1006" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -10347,6 +10387,22 @@
     <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1196" s="1"/>
       <c r="B1196" s="1"/>
+    </row>
+    <row r="1197" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1197" s="1"/>
+      <c r="B1197" s="1"/>
+    </row>
+    <row r="1198" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1198" s="1"/>
+      <c r="B1198" s="1"/>
+    </row>
+    <row r="1199" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1199" s="1"/>
+      <c r="B1199" s="1"/>
+    </row>
+    <row r="1200" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1200" s="1"/>
+      <c r="B1200" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5349278A-4B39-443E-9976-97319790B4FC}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1F792B3-8E27-4F0E-B05E-AA3A495EA65D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -5254,8 +5254,8 @@
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A286" s="15">
-        <v>1040098437</v>
+      <c r="A286" s="5">
+        <v>1040100107</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>271</v>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA015759-9080-45E4-8700-C4991D7E1200}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65A379C1-DE73-44DA-BB93-F99BAFA2EA41}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1576,7 +1576,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1760,7 +1760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1838,6 +1838,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2121,14 +2124,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C1201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2139,7 +2142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>1040019909</v>
       </c>
@@ -2150,7 +2153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>1040023837</v>
       </c>
@@ -2161,7 +2164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>1040023836</v>
       </c>
@@ -2172,7 +2175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>1010000216</v>
       </c>
@@ -2183,7 +2186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>423651</v>
       </c>
@@ -2194,7 +2197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>1040077347</v>
       </c>
@@ -2205,7 +2208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>1040077348</v>
       </c>
@@ -2216,7 +2219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>417715</v>
       </c>
@@ -2227,7 +2230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>1010062075</v>
       </c>
@@ -2238,7 +2241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>1040083308</v>
       </c>
@@ -2249,7 +2252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>1040077346</v>
       </c>
@@ -2260,7 +2263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>1010049326</v>
       </c>
@@ -2271,7 +2274,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>1040017265</v>
       </c>
@@ -2282,7 +2285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>1010060188</v>
       </c>
@@ -2293,7 +2296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>1040019851</v>
       </c>
@@ -2304,7 +2307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>1010077433</v>
       </c>
@@ -2315,7 +2318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>1010042610</v>
       </c>
@@ -2326,7 +2329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>1040077352</v>
       </c>
@@ -2337,7 +2340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>1040083258</v>
       </c>
@@ -2348,7 +2351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>68686</v>
       </c>
@@ -2359,7 +2362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>1010084124</v>
       </c>
@@ -2370,7 +2373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>102286</v>
       </c>
@@ -2381,7 +2384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>1040097671</v>
       </c>
@@ -2392,7 +2395,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>1010003651</v>
       </c>
@@ -2403,7 +2406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>1010062027</v>
       </c>
@@ -2414,7 +2417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>1010021550</v>
       </c>
@@ -2425,7 +2428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>1040077350</v>
       </c>
@@ -2436,7 +2439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>1040077349</v>
       </c>
@@ -2447,7 +2450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>154897</v>
       </c>
@@ -2458,7 +2461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>13781</v>
       </c>
@@ -2469,7 +2472,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>1010058682</v>
       </c>
@@ -2480,7 +2483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>1010059706</v>
       </c>
@@ -2491,7 +2494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>1010077386</v>
       </c>
@@ -2502,7 +2505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>1010058325</v>
       </c>
@@ -2513,7 +2516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>1010061986</v>
       </c>
@@ -2524,7 +2527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>1010004299</v>
       </c>
@@ -2535,7 +2538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>1010004301</v>
       </c>
@@ -2546,7 +2549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>1010004289</v>
       </c>
@@ -2557,7 +2560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>1010004292</v>
       </c>
@@ -2568,7 +2571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="14">
         <v>1040077354</v>
       </c>
@@ -2579,7 +2582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>1010050496</v>
       </c>
@@ -2590,7 +2593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="14">
         <v>1010050536</v>
       </c>
@@ -2601,7 +2604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="14">
         <v>1010061810</v>
       </c>
@@ -2612,7 +2615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="14">
         <v>1040092580</v>
       </c>
@@ -2623,7 +2626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
         <v>1010041375</v>
       </c>
@@ -2634,7 +2637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="14">
         <v>1040098335</v>
       </c>
@@ -2645,7 +2648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="14">
         <v>1010023362</v>
       </c>
@@ -2656,7 +2659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="14">
         <v>1010052336</v>
       </c>
@@ -2667,7 +2670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="14">
         <v>1040077355</v>
       </c>
@@ -2678,7 +2681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="14">
         <v>230110</v>
       </c>
@@ -2689,7 +2692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
         <v>1040077357</v>
       </c>
@@ -2700,7 +2703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
         <v>1040077356</v>
       </c>
@@ -2711,7 +2714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="15">
         <v>1040075251</v>
       </c>
@@ -2722,7 +2725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
         <v>1040090022</v>
       </c>
@@ -2733,7 +2736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
         <v>1010023336</v>
       </c>
@@ -2744,7 +2747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
         <v>1010021328</v>
       </c>
@@ -2755,7 +2758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
         <v>1010059706</v>
       </c>
@@ -2766,7 +2769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>1010062152</v>
       </c>
@@ -2777,7 +2780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
         <v>1040077358</v>
       </c>
@@ -2788,7 +2791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
         <v>1010045227</v>
       </c>
@@ -2799,7 +2802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
         <v>1010085124</v>
       </c>
@@ -2810,7 +2813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
         <v>1010046495</v>
       </c>
@@ -2821,7 +2824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
         <v>1010032356</v>
       </c>
@@ -2832,7 +2835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
         <v>1010050244</v>
       </c>
@@ -2843,7 +2846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="14">
         <v>1010050243</v>
       </c>
@@ -2854,7 +2857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="14">
         <v>428995</v>
       </c>
@@ -2865,7 +2868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
         <v>428998</v>
       </c>
@@ -2876,7 +2879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="14">
         <v>1010031607</v>
       </c>
@@ -2887,7 +2890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
         <v>1010031630</v>
       </c>
@@ -2898,7 +2901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="14">
         <v>1010045647</v>
       </c>
@@ -2909,7 +2912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="14">
         <v>1010031567</v>
       </c>
@@ -2920,7 +2923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="14">
         <v>1040077361</v>
       </c>
@@ -2931,7 +2934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="14">
         <v>1010050445</v>
       </c>
@@ -2942,7 +2945,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75">
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="14">
         <v>1010050461</v>
       </c>
@@ -2953,7 +2956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75">
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="14">
         <v>1010053885</v>
       </c>
@@ -2964,7 +2967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75">
+    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="15">
         <v>1040097102</v>
       </c>
@@ -2975,7 +2978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75">
+    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="15">
         <v>1010020838</v>
       </c>
@@ -2986,7 +2989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.75">
+    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="16">
         <v>341430</v>
       </c>
@@ -2997,7 +3000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75">
+    <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="15">
         <v>1010042643</v>
       </c>
@@ -3008,7 +3011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.75">
+    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="15">
         <v>425554</v>
       </c>
@@ -3019,7 +3022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75">
+    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
         <v>1010084162</v>
       </c>
@@ -3030,7 +3033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75">
+    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="15">
         <v>1010084157</v>
       </c>
@@ -3041,7 +3044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75">
+    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>1010084158</v>
       </c>
@@ -3052,7 +3055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75">
+    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>1010084159</v>
       </c>
@@ -3063,7 +3066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75">
+    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>1010084160</v>
       </c>
@@ -3074,7 +3077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75">
+    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>1010084161</v>
       </c>
@@ -3085,7 +3088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75">
+    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>224382</v>
       </c>
@@ -3096,7 +3099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75">
+    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>94314</v>
       </c>
@@ -3107,7 +3110,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.75">
+    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="17">
         <v>1010003982</v>
       </c>
@@ -3118,7 +3121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.75">
+    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="15">
         <v>1010000182</v>
       </c>
@@ -3129,7 +3132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75">
+    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="15">
         <v>1010021079</v>
       </c>
@@ -3140,7 +3143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.75">
+    <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="15">
         <v>1010002463</v>
       </c>
@@ -3151,7 +3154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75">
+    <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="15">
         <v>1010062982</v>
       </c>
@@ -3162,7 +3165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.75">
+    <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="15">
         <v>1010063209</v>
       </c>
@@ -3173,7 +3176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.75">
+    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="15">
         <v>1040076302</v>
       </c>
@@ -3184,7 +3187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.75">
+    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="15">
         <v>1040098396</v>
       </c>
@@ -3195,7 +3198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.75">
+    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="15">
         <v>1040041006</v>
       </c>
@@ -3206,7 +3209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.75">
+    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="15">
         <v>1040077362</v>
       </c>
@@ -3217,7 +3220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.75">
+    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="15">
         <v>1040077363</v>
       </c>
@@ -3228,7 +3231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.75">
+    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="15">
         <v>1040074483</v>
       </c>
@@ -3239,7 +3242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75">
+    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="15">
         <v>1040077364</v>
       </c>
@@ -3250,7 +3253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.75">
+    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="15">
         <v>1040048463</v>
       </c>
@@ -3261,7 +3264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75">
+    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="15">
         <v>1040096343</v>
       </c>
@@ -3272,7 +3275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.75">
+    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="15">
         <v>409640</v>
       </c>
@@ -3283,7 +3286,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.75">
+    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="15">
         <v>1010032753</v>
       </c>
@@ -3294,7 +3297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.75">
+    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="15">
         <v>1040098597</v>
       </c>
@@ -3305,7 +3308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.75">
+    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="15">
         <v>1040084464</v>
       </c>
@@ -3316,7 +3319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.75">
+    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="15">
         <v>1040017773</v>
       </c>
@@ -3327,7 +3330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.75">
+    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="15">
         <v>1010007405</v>
       </c>
@@ -3338,7 +3341,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.75">
+    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="17">
         <v>1040077365</v>
       </c>
@@ -3349,7 +3352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.75">
+    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="15">
         <v>1010027794</v>
       </c>
@@ -3360,7 +3363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.75">
+    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="15">
         <v>1040077366</v>
       </c>
@@ -3371,7 +3374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.75">
+    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="15">
         <v>1040077367</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.75">
+    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="15">
         <v>1010021561</v>
       </c>
@@ -3393,7 +3396,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.75">
+    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="15">
         <v>1010021562</v>
       </c>
@@ -3404,7 +3407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.75">
+    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="15">
         <v>1010027792</v>
       </c>
@@ -3415,7 +3418,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.75">
+    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="15">
         <v>1010084930</v>
       </c>
@@ -3426,7 +3429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.75">
+    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="15">
         <v>341430</v>
       </c>
@@ -3437,7 +3440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75">
+    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="15">
         <v>1010029366</v>
       </c>
@@ -3448,7 +3451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.75">
+    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="18">
         <v>1010031723</v>
       </c>
@@ -3459,7 +3462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.75">
+    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="18">
         <v>1010049216</v>
       </c>
@@ -3470,7 +3473,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75">
+    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="15">
         <v>405558</v>
       </c>
@@ -3481,7 +3484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75">
+    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="15">
         <v>1010023038</v>
       </c>
@@ -3492,7 +3495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.75">
+    <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="15">
         <v>1010084109</v>
       </c>
@@ -3503,7 +3506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.75">
+    <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="15">
         <v>1010021582</v>
       </c>
@@ -3514,7 +3517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.75">
+    <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="15">
         <v>1010021544</v>
       </c>
@@ -3525,7 +3528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.75">
+    <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="15">
         <v>1010021564</v>
       </c>
@@ -3536,7 +3539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.75">
+    <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="15">
         <v>1010023019</v>
       </c>
@@ -3547,7 +3550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.75">
+    <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="15">
         <v>1010048541</v>
       </c>
@@ -3558,7 +3561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.75">
+    <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="15">
         <v>1010059334</v>
       </c>
@@ -3569,7 +3572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.75">
+    <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="15">
         <v>1010000277</v>
       </c>
@@ -3580,7 +3583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.75">
+    <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="19">
         <v>1010085344</v>
       </c>
@@ -3591,7 +3594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.75">
+    <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="19">
         <v>1010085383</v>
       </c>
@@ -3602,7 +3605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.75">
+    <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="15">
         <v>1010001389</v>
       </c>
@@ -3613,7 +3616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.75">
+    <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="15">
         <v>1010017703</v>
       </c>
@@ -3624,7 +3627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.75">
+    <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="15">
         <v>1010052036</v>
       </c>
@@ -3635,7 +3638,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.75">
+    <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="15">
         <v>1040097133</v>
       </c>
@@ -3646,7 +3649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.75">
+    <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="15">
         <v>1040019325</v>
       </c>
@@ -3657,7 +3660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.75">
+    <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="15">
         <v>64262</v>
       </c>
@@ -3668,7 +3671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.75">
+    <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="14">
         <v>1010047089</v>
       </c>
@@ -3679,7 +3682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.75">
+    <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="14">
         <v>1040050168</v>
       </c>
@@ -3690,7 +3693,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.75">
+    <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="14">
         <v>1040077370</v>
       </c>
@@ -3701,7 +3704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.75">
+    <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="14">
         <v>1040099247</v>
       </c>
@@ -3712,7 +3715,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.75">
+    <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="15">
         <v>1040077371</v>
       </c>
@@ -3723,7 +3726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.75">
+    <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="15">
         <v>1040077399</v>
       </c>
@@ -3734,7 +3737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.75">
+    <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="15">
         <v>1040077374</v>
       </c>
@@ -3745,7 +3748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.75">
+    <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="15">
         <v>1040077399</v>
       </c>
@@ -3756,7 +3759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.75">
+    <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="15">
         <v>357623</v>
       </c>
@@ -3767,7 +3770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.75">
+    <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="15">
         <v>1010020504</v>
       </c>
@@ -3778,7 +3781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.75">
+    <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="15">
         <v>409250</v>
       </c>
@@ -3789,7 +3792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.75">
+    <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="15">
         <v>1010020541</v>
       </c>
@@ -3800,7 +3803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15.75">
+    <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="15">
         <v>1010020879</v>
       </c>
@@ -3811,7 +3814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.75">
+    <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="15">
         <v>1040077380</v>
       </c>
@@ -3822,7 +3825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.75">
+    <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="15">
         <v>1010021520</v>
       </c>
@@ -3833,7 +3836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.75">
+    <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="15">
         <v>1040098861</v>
       </c>
@@ -3844,7 +3847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.75">
+    <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="15">
         <v>1010077261</v>
       </c>
@@ -3855,7 +3858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.75">
+    <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="15">
         <v>1010027664</v>
       </c>
@@ -3866,7 +3869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.75">
+    <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="15">
         <v>1010083731</v>
       </c>
@@ -3877,7 +3880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.75">
+    <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="15">
         <v>1010083885</v>
       </c>
@@ -3888,7 +3891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.75">
+    <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="15">
         <v>1010014834</v>
       </c>
@@ -3899,7 +3902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.75">
+    <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="15">
         <v>1010083908</v>
       </c>
@@ -3910,7 +3913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.75">
+    <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="15">
         <v>1040077377</v>
       </c>
@@ -3921,7 +3924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.75">
+    <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="15">
         <v>1010061942</v>
       </c>
@@ -3932,7 +3935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.75">
+    <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="15">
         <v>1040097070</v>
       </c>
@@ -3943,7 +3946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.75">
+    <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="15">
         <v>1040097068</v>
       </c>
@@ -3954,7 +3957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.75">
+    <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="15">
         <v>22004</v>
       </c>
@@ -3965,7 +3968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15.75">
+    <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="15">
         <v>1010058554</v>
       </c>
@@ -3976,7 +3979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.75">
+    <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="15">
         <v>1010027308</v>
       </c>
@@ -3987,7 +3990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.75">
+    <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="19">
         <v>1040077383</v>
       </c>
@@ -3998,7 +4001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.75">
+    <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="19">
         <v>1010025482</v>
       </c>
@@ -4009,7 +4012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.75">
+    <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="19">
         <v>1010025509</v>
       </c>
@@ -4020,7 +4023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.75">
+    <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="15">
         <v>1010027789</v>
       </c>
@@ -4031,7 +4034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15.75">
+    <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="15">
         <v>1010027790</v>
       </c>
@@ -4042,7 +4045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.75">
+    <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="15">
         <v>1010018301</v>
       </c>
@@ -4053,7 +4056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.75">
+    <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="15">
         <v>1010031616</v>
       </c>
@@ -4064,7 +4067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.75">
+    <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="15">
         <v>1010053728</v>
       </c>
@@ -4075,7 +4078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.75">
+    <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="15">
         <v>1010020758</v>
       </c>
@@ -4086,7 +4089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.75">
+    <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="15">
         <v>1010020781</v>
       </c>
@@ -4097,7 +4100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.75">
+    <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="14">
         <v>1010058426</v>
       </c>
@@ -4108,7 +4111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.75">
+    <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="14">
         <v>1010059332</v>
       </c>
@@ -4119,7 +4122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.75">
+    <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="14">
         <v>1040077389</v>
       </c>
@@ -4130,7 +4133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75">
+    <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="15">
         <v>1010021364</v>
       </c>
@@ -4141,7 +4144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75">
+    <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="20">
         <v>1010021541</v>
       </c>
@@ -4152,7 +4155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75">
+    <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="14">
         <v>1010021955</v>
       </c>
@@ -4163,7 +4166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75">
+    <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="15">
         <v>1040077388</v>
       </c>
@@ -4174,7 +4177,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75">
+    <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="15">
         <v>1010058100</v>
       </c>
@@ -4185,7 +4188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75">
+    <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="15">
         <v>1010020524</v>
       </c>
@@ -4196,7 +4199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75">
+    <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="15">
         <v>1010021958</v>
       </c>
@@ -4207,7 +4210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.75">
+    <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="15">
         <v>1010019756</v>
       </c>
@@ -4218,7 +4221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75">
+    <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="15">
         <v>1010019752</v>
       </c>
@@ -4229,7 +4232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.75">
+    <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="15">
         <v>409639</v>
       </c>
@@ -4240,7 +4243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75">
+    <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="15">
         <v>1010047089</v>
       </c>
@@ -4251,7 +4254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75">
+    <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="15">
         <v>1040084107</v>
       </c>
@@ -4262,7 +4265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75">
+    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="15">
         <v>1010085203</v>
       </c>
@@ -4273,7 +4276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75">
+    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="15">
         <v>424298</v>
       </c>
@@ -4284,7 +4287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75">
+    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="15">
         <v>421847</v>
       </c>
@@ -4295,7 +4298,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75">
+    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="15">
         <v>431573</v>
       </c>
@@ -4306,7 +4309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75">
+    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="15">
         <v>1010021581</v>
       </c>
@@ -4317,7 +4320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75">
+    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="21">
         <v>412413</v>
       </c>
@@ -4328,7 +4331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75">
+    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="22">
         <v>1010022606</v>
       </c>
@@ -4339,7 +4342,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75">
+    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="23">
         <v>1010003527</v>
       </c>
@@ -4350,7 +4353,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75">
+    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="23">
         <v>1010055707</v>
       </c>
@@ -4361,7 +4364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75">
+    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="18">
         <v>422027</v>
       </c>
@@ -4372,7 +4375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75">
+    <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="14">
         <v>1010011313</v>
       </c>
@@ -4383,7 +4386,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75">
+    <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="15">
         <v>27051</v>
       </c>
@@ -4394,7 +4397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75">
+    <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="15">
         <v>1010011304</v>
       </c>
@@ -4405,7 +4408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75">
+    <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="15">
         <v>35659</v>
       </c>
@@ -4416,7 +4419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.75">
+    <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="15">
         <v>1040077390</v>
       </c>
@@ -4427,7 +4430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75">
+    <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="15">
         <v>1010021542</v>
       </c>
@@ -4438,7 +4441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75">
+    <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="15">
         <v>1010021733</v>
       </c>
@@ -4449,7 +4452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.75">
+    <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="15">
         <v>1010011379</v>
       </c>
@@ -4460,7 +4463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75">
+    <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="15">
         <v>1010003279</v>
       </c>
@@ -4471,7 +4474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75">
+    <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="15">
         <v>1010011380</v>
       </c>
@@ -4482,7 +4485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75">
+    <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="15">
         <v>351197</v>
       </c>
@@ -4493,7 +4496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75">
+    <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="15">
         <v>1010011286</v>
       </c>
@@ -4504,7 +4507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.75">
+    <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="15">
         <v>2479</v>
       </c>
@@ -4515,7 +4518,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75">
+    <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="15">
         <v>1010011382</v>
       </c>
@@ -4526,7 +4529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75">
+    <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="16">
         <v>1010055703</v>
       </c>
@@ -4537,7 +4540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75">
+    <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="16">
         <v>4165</v>
       </c>
@@ -4548,7 +4551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75">
+    <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="15">
         <v>301626</v>
       </c>
@@ -4559,7 +4562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.75">
+    <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="15">
         <v>429495</v>
       </c>
@@ -4570,7 +4573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.75">
+    <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="15">
         <v>162998</v>
       </c>
@@ -4581,7 +4584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75">
+    <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="15">
         <v>432657</v>
       </c>
@@ -4592,7 +4595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.75">
+    <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="15">
         <v>1010021929</v>
       </c>
@@ -4603,7 +4606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.75">
+    <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="15">
         <v>428065</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.75">
+    <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="15">
         <v>1010003404</v>
       </c>
@@ -4625,7 +4628,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.75">
+    <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="15">
         <v>1010003322</v>
       </c>
@@ -4636,7 +4639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.75">
+    <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="15">
         <v>17738</v>
       </c>
@@ -4647,7 +4650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15.75">
+    <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="15">
         <v>1010085360</v>
       </c>
@@ -4658,7 +4661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.75">
+    <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="15">
         <v>1040077391</v>
       </c>
@@ -4669,7 +4672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.75">
+    <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="15">
         <v>1010058624</v>
       </c>
@@ -4680,7 +4683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15.75">
+    <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="15">
         <v>1010024661</v>
       </c>
@@ -4691,7 +4694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.75">
+    <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="15">
         <v>1040019315</v>
       </c>
@@ -4702,7 +4705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.75">
+    <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="15">
         <v>1010021089</v>
       </c>
@@ -4713,7 +4716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.75">
+    <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="15">
         <v>1040017264</v>
       </c>
@@ -4724,7 +4727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.75">
+    <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="15">
         <v>1010051765</v>
       </c>
@@ -4735,7 +4738,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15.75">
+    <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="15">
         <v>1010035272</v>
       </c>
@@ -4746,7 +4749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15.75">
+    <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="15">
         <v>1040077392</v>
       </c>
@@ -4757,7 +4760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15.75">
+    <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="15">
         <v>1040077393</v>
       </c>
@@ -4768,7 +4771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.75">
+    <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="15">
         <v>1040077395</v>
       </c>
@@ -4779,7 +4782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.75">
+    <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="15">
         <v>1040077401</v>
       </c>
@@ -4790,7 +4793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15.75">
+    <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="15">
         <v>27572</v>
       </c>
@@ -4801,7 +4804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15.75">
+    <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="15">
         <v>18745</v>
       </c>
@@ -4812,7 +4815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15.75">
+    <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="15">
         <v>1040077396</v>
       </c>
@@ -4823,7 +4826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15.75">
+    <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="15">
         <v>1010036546</v>
       </c>
@@ -4834,7 +4837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15.75">
+    <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="15">
         <v>1010014049</v>
       </c>
@@ -4845,7 +4848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15.75">
+    <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="15">
         <v>1010025148</v>
       </c>
@@ -4856,7 +4859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15.75">
+    <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="15">
         <v>1040077394</v>
       </c>
@@ -4867,7 +4870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="15.75">
+    <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="15">
         <v>1040077400</v>
       </c>
@@ -4878,7 +4881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="15.75">
+    <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="15">
         <v>1040079329</v>
       </c>
@@ -4889,7 +4892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="15.75">
+    <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="15">
         <v>1040040957</v>
       </c>
@@ -4900,7 +4903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="15.75">
+    <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="15">
         <v>1040077398</v>
       </c>
@@ -4911,7 +4914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="15.75">
+    <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="15">
         <v>1010031545</v>
       </c>
@@ -4922,7 +4925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="15.75">
+    <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="15">
         <v>1010053128</v>
       </c>
@@ -4933,7 +4936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="15.75">
+    <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="15">
         <v>1010010599</v>
       </c>
@@ -4944,7 +4947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="15.75">
+    <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="15">
         <v>1010056064</v>
       </c>
@@ -4955,7 +4958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="15.75">
+    <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="15">
         <v>5389</v>
       </c>
@@ -4966,7 +4969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="15.75">
+    <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="15">
         <v>1010055969</v>
       </c>
@@ -4977,7 +4980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="15.75">
+    <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="15">
         <v>1010055970</v>
       </c>
@@ -4988,7 +4991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="15.75">
+    <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="15">
         <v>181395</v>
       </c>
@@ -4999,7 +5002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="15.75">
+    <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="17">
         <v>1010055962</v>
       </c>
@@ -5010,7 +5013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15.75">
+    <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="15">
         <v>1010003578</v>
       </c>
@@ -5021,7 +5024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="15.75">
+    <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="15">
         <v>332891</v>
       </c>
@@ -5032,7 +5035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="15.75">
+    <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="15">
         <v>17727</v>
       </c>
@@ -5043,7 +5046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15.75">
+    <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="15">
         <v>17918</v>
       </c>
@@ -5054,7 +5057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="15.75">
+    <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="15">
         <v>1010020554</v>
       </c>
@@ -5065,7 +5068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="15.75">
+    <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="15">
         <v>1040085949</v>
       </c>
@@ -5076,7 +5079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="15.75">
+    <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="15">
         <v>1010062938</v>
       </c>
@@ -5087,7 +5090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="15.75">
+    <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="15">
         <v>1010062086</v>
       </c>
@@ -5098,7 +5101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="15.75">
+    <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="15">
         <v>1010062087</v>
       </c>
@@ -5109,7 +5112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="15.75">
+    <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="15">
         <v>1040077373</v>
       </c>
@@ -5120,7 +5123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="15.75">
+    <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="24">
         <v>1040077372</v>
       </c>
@@ -5131,7 +5134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="15.75">
+    <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="24">
         <v>1040097154</v>
       </c>
@@ -5142,7 +5145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="15.75">
+    <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="24">
         <v>1010042579</v>
       </c>
@@ -5153,7 +5156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="15.75">
+    <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="15">
         <v>1010029427</v>
       </c>
@@ -5164,7 +5167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="15.75">
+    <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="15">
         <v>133108</v>
       </c>
@@ -5175,7 +5178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="15.75">
+    <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="15">
         <v>269427</v>
       </c>
@@ -5186,7 +5189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="15.75">
+    <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="15">
         <v>298227</v>
       </c>
@@ -5197,7 +5200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="15.75">
+    <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" s="15">
         <v>1010062285</v>
       </c>
@@ -5208,7 +5211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="15.75">
+    <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="15">
         <v>1010058052</v>
       </c>
@@ -5219,7 +5222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="15.75">
+    <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="15">
         <v>1010050033</v>
       </c>
@@ -5230,7 +5233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="15.75">
+    <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" s="20">
         <v>1040098869</v>
       </c>
@@ -5241,7 +5244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="15.75">
+    <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="20">
         <v>1010056523</v>
       </c>
@@ -5252,7 +5255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="15.75">
+    <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="20">
         <v>1010062045</v>
       </c>
@@ -5263,7 +5266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="15.75">
+    <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="15">
         <v>1040097575</v>
       </c>
@@ -5274,7 +5277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="15.75">
+    <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="5">
         <v>1040100107</v>
       </c>
@@ -5285,7 +5288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="15.75">
+    <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="15">
         <v>1010040346</v>
       </c>
@@ -5296,7 +5299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="15.75">
+    <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="15">
         <v>1010021543</v>
       </c>
@@ -5307,7 +5310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="15.75">
+    <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="15">
         <v>1040077397</v>
       </c>
@@ -5318,7 +5321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="15.75">
+    <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="15">
         <v>1040094213</v>
       </c>
@@ -5329,7 +5332,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="15.75">
+    <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="15">
         <v>1010085326</v>
       </c>
@@ -5340,7 +5343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="15.75">
+    <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="15">
         <v>1010042564</v>
       </c>
@@ -5351,7 +5354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="15.75">
+    <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="15">
         <v>1010042688</v>
       </c>
@@ -5362,7 +5365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="15.75">
+    <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="15">
         <v>1010040133</v>
       </c>
@@ -5373,7 +5376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="15.75">
+    <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="15">
         <v>1010039879</v>
       </c>
@@ -5384,7 +5387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="15.75">
+    <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" s="15">
         <v>62608</v>
       </c>
@@ -5395,7 +5398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="15.75">
+    <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="15">
         <v>1040098603</v>
       </c>
@@ -5406,7 +5409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="15.75">
+    <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="15">
         <v>1040017266</v>
       </c>
@@ -5417,7 +5420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="15.75">
+    <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="15">
         <v>1010063326</v>
       </c>
@@ -5428,7 +5431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="15.75">
+    <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="15">
         <v>1010050574</v>
       </c>
@@ -5439,7 +5442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="15.75">
+    <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="20">
         <v>1010086126</v>
       </c>
@@ -5450,7 +5453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="15.75">
+    <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="15">
         <v>1040019838</v>
       </c>
@@ -5461,7 +5464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="15.75">
+    <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="15">
         <v>1010042882</v>
       </c>
@@ -5472,7 +5475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="15.75">
+    <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="15">
         <v>1010042873</v>
       </c>
@@ -5483,7 +5486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="15.75">
+    <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="15">
         <v>1010026842</v>
       </c>
@@ -5494,7 +5497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="15.75">
+    <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="15">
         <v>1010026841</v>
       </c>
@@ -5505,7 +5508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="15.75">
+    <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="15">
         <v>1010059549</v>
       </c>
@@ -5516,7 +5519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="15.75">
+    <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="15">
         <v>1010020552</v>
       </c>
@@ -5527,7 +5530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="15.75">
+    <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="15">
         <v>1040078895</v>
       </c>
@@ -5538,7 +5541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="15.75">
+    <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="15">
         <v>1040024309</v>
       </c>
@@ -5549,7 +5552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="15.75">
+    <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="15">
         <v>1040024323</v>
       </c>
@@ -5560,7 +5563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="15.75">
+    <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="15">
         <v>1040024322</v>
       </c>
@@ -5571,7 +5574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="15.75">
+    <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="15">
         <v>1040024314</v>
       </c>
@@ -5582,7 +5585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.75">
+    <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" s="15">
         <v>1010059685</v>
       </c>
@@ -5593,7 +5596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="15.75">
+    <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" s="15">
         <v>1010059687</v>
       </c>
@@ -5604,7 +5607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="15.75">
+    <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" s="15">
         <v>1010077469</v>
       </c>
@@ -5615,7 +5618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.75">
+    <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="19">
         <v>1010077470</v>
       </c>
@@ -5626,7 +5629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="15.75">
+    <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="15">
         <v>1010084519</v>
       </c>
@@ -5637,7 +5640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="15.75">
+    <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="14">
         <v>1010084108</v>
       </c>
@@ -5648,7 +5651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="15.75">
+    <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="14">
         <v>1010042884</v>
       </c>
@@ -5659,7 +5662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="15.75">
+    <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="15">
         <v>1040043537</v>
       </c>
@@ -5670,7 +5673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="15.75">
+    <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="15">
         <v>1010046401</v>
       </c>
@@ -5681,7 +5684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="15.75">
+    <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="15">
         <v>1010062007</v>
       </c>
@@ -5692,7 +5695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="15.75">
+    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="15">
         <v>1010051284</v>
       </c>
@@ -5703,7 +5706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15.75">
+    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="15">
         <v>1010027788</v>
       </c>
@@ -5714,7 +5717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15.75">
+    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="15">
         <v>1010027786</v>
       </c>
@@ -5725,7 +5728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="15.75">
+    <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="15">
         <v>1010026889</v>
       </c>
@@ -5736,7 +5739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="15.75">
+    <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="24">
         <v>1010042358</v>
       </c>
@@ -5747,7 +5750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="15.75">
+    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="15">
         <v>1040023848</v>
       </c>
@@ -5758,7 +5761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="15.75">
+    <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="15">
         <v>1010042341</v>
       </c>
@@ -5769,7 +5772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="15.75">
+    <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="15">
         <v>1040023858</v>
       </c>
@@ -5780,7 +5783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="15.75">
+    <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="15">
         <v>1040023843</v>
       </c>
@@ -5791,7 +5794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="15.75">
+    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="15">
         <v>1040077411</v>
       </c>
@@ -5802,7 +5805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="15.75">
+    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="15">
         <v>1040077410</v>
       </c>
@@ -5813,7 +5816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.75">
+    <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="15">
         <v>1010062008</v>
       </c>
@@ -5824,7 +5827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="15.75">
+    <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="15">
         <v>1040040960</v>
       </c>
@@ -5835,9 +5838,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="15.75">
-      <c r="A338" s="15">
-        <v>409578</v>
+    <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A338" s="29">
+        <v>1010084767</v>
       </c>
       <c r="B338" s="5" t="s">
         <v>340</v>
@@ -5846,7 +5849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="15.75">
+    <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="15">
         <v>1040077360</v>
       </c>
@@ -5857,7 +5860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="15.75">
+    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="15">
         <v>1010064470</v>
       </c>
@@ -5868,7 +5871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="15.75">
+    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="15">
         <v>1010021991</v>
       </c>
@@ -5879,7 +5882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="15.75">
+    <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="15">
         <v>1010021960</v>
       </c>
@@ -5890,7 +5893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="15.75">
+    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="15">
         <v>1010031545</v>
       </c>
@@ -5901,7 +5904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="15.75">
+    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="15">
         <v>1010031690</v>
       </c>
@@ -5912,7 +5915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="15.75">
+    <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="15">
         <v>1010022590</v>
       </c>
@@ -5923,7 +5926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="15.75">
+    <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="15">
         <v>1040098643</v>
       </c>
@@ -5934,7 +5937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="15.75">
+    <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="15">
         <v>1010086020</v>
       </c>
@@ -5945,7 +5948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="15.75">
+    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="15">
         <v>1010046550</v>
       </c>
@@ -5956,7 +5959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="15.75">
+    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="15">
         <v>1010046402</v>
       </c>
@@ -5967,7 +5970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="15.75">
+    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="15">
         <v>1010060291</v>
       </c>
@@ -5978,7 +5981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="15.75">
+    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="15">
         <v>1010050920</v>
       </c>
@@ -5989,7 +5992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="15.75">
+    <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="15">
         <v>1040077412</v>
       </c>
@@ -6000,7 +6003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.75">
+    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="15">
         <v>1010042609</v>
       </c>
@@ -6011,7 +6014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.75">
+    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="15">
         <v>417701</v>
       </c>
@@ -6022,7 +6025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="15.75">
+    <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="15">
         <v>399384</v>
       </c>
@@ -6033,7 +6036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="15.75">
+    <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="15">
         <v>1010024086</v>
       </c>
@@ -6044,7 +6047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75">
+    <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="15">
         <v>1040077345</v>
       </c>
@@ -6055,7 +6058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="15.75">
+    <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="15">
         <v>1010084315</v>
       </c>
@@ -6066,7 +6069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="15.75">
+    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="15">
         <v>399253</v>
       </c>
@@ -6077,7 +6080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="15.75">
+    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="15">
         <v>1010084317</v>
       </c>
@@ -6088,7 +6091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="15.75">
+    <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="25">
         <v>1010085369</v>
       </c>
@@ -6099,7 +6102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="15.75">
+    <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="15">
         <v>1010085370</v>
       </c>
@@ -6110,7 +6113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="15.75">
+    <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="15">
         <v>1010085204</v>
       </c>
@@ -6121,7 +6124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="15.75">
+    <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="15">
         <v>1010003966</v>
       </c>
@@ -6132,7 +6135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="15.75">
+    <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="15">
         <v>1010003967</v>
       </c>
@@ -6143,7 +6146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="15.75">
+    <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="15">
         <v>65219</v>
       </c>
@@ -6154,7 +6157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="15.75">
+    <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="15">
         <v>10168</v>
       </c>
@@ -6165,7 +6168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="15.75">
+    <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="15">
         <v>1010083792</v>
       </c>
@@ -6176,7 +6179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="15.75">
+    <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="15">
         <v>1040077414</v>
       </c>
@@ -6187,7 +6190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="15.75">
+    <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="15">
         <v>1010018482</v>
       </c>
@@ -6198,7 +6201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="15.75">
+    <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="15">
         <v>1010084320</v>
       </c>
@@ -6209,7 +6212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="15.75">
+    <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="15">
         <v>1010084532</v>
       </c>
@@ -6220,7 +6223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="15.75">
+    <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="15">
         <v>1010027285</v>
       </c>
@@ -6231,7 +6234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="15.75">
+    <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="15">
         <v>1040077413</v>
       </c>
@@ -6242,7 +6245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="15.75">
+    <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="15">
         <v>1010085376</v>
       </c>
@@ -6253,7 +6256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="15.75">
+    <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" s="15">
         <v>1010022819</v>
       </c>
@@ -6264,7 +6267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="15.75">
+    <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="15">
         <v>1010052853</v>
       </c>
@@ -6275,7 +6278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="15.75">
+    <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="15">
         <v>1010084377</v>
       </c>
@@ -6286,7 +6289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="15.75">
+    <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="26">
         <v>1010062826</v>
       </c>
@@ -6297,7 +6300,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="15.75">
+    <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="15">
         <v>1010002592</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="15.75">
+    <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="24">
         <v>1010001155</v>
       </c>
@@ -6319,7 +6322,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="15.75">
+    <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="15">
         <v>1010001062</v>
       </c>
@@ -6330,7 +6333,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="15.75">
+    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" s="15">
         <v>1010084328</v>
       </c>
@@ -6341,7 +6344,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="15.75">
+    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="24">
         <v>1010044502</v>
       </c>
@@ -6352,7 +6355,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="15.75">
+    <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="15">
         <v>1010053692</v>
       </c>
@@ -6363,7 +6366,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="15.75">
+    <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="15">
         <v>1010083992</v>
       </c>
@@ -6374,7 +6377,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="15.75">
+    <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="15">
         <v>1010008578</v>
       </c>
@@ -6385,7 +6388,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="15.75">
+    <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="15">
         <v>1010031694</v>
       </c>
@@ -6396,7 +6399,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="15.75">
+    <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="15">
         <v>1010051997</v>
       </c>
@@ -6407,7 +6410,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="15.75">
+    <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="15">
         <v>1010022601</v>
       </c>
@@ -6418,7 +6421,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="15.75">
+    <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="15">
         <v>1010054278</v>
       </c>
@@ -6429,7 +6432,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="15.75">
+    <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="15">
         <v>1010083462</v>
       </c>
@@ -6440,7 +6443,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="15.75">
+    <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="15">
         <v>1010027772</v>
       </c>
@@ -6451,7 +6454,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="15.75">
+    <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="15">
         <v>1010084144</v>
       </c>
@@ -6462,7 +6465,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="15.75">
+    <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="19">
         <v>214055</v>
       </c>
@@ -6473,7 +6476,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="15.75">
+    <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="18">
         <v>1010021956</v>
       </c>
@@ -6484,7 +6487,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="15.75">
+    <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="18">
         <v>1010026464</v>
       </c>
@@ -6495,7 +6498,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="15.75">
+    <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="14">
         <v>1010021957</v>
       </c>
@@ -6506,7 +6509,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="15.75">
+    <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="15">
         <v>1010026462</v>
       </c>
@@ -6517,7 +6520,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="15.75">
+    <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="15">
         <v>1010026551</v>
       </c>
@@ -6528,7 +6531,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="15.75">
+    <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="15">
         <v>1010042554</v>
       </c>
@@ -6539,7 +6542,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="15.75">
+    <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="15">
         <v>1010039904</v>
       </c>
@@ -6550,7 +6553,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="15.75">
+    <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="15">
         <v>1010060205</v>
       </c>
@@ -6561,7 +6564,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="404" spans="1:3" ht="15.75">
+    <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="15">
         <v>1010060206</v>
       </c>
@@ -6572,7 +6575,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="15.75">
+    <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="15">
         <v>1010077431</v>
       </c>
@@ -6583,7 +6586,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="15.75">
+    <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="15">
         <v>1010077503</v>
       </c>
@@ -6594,7 +6597,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="15.75">
+    <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="15">
         <v>1010084187</v>
       </c>
@@ -6605,7 +6608,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="15.75">
+    <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="15">
         <v>1010080958</v>
       </c>
@@ -6616,7 +6619,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="15.75">
+    <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="15">
         <v>1010026032</v>
       </c>
@@ -6627,7 +6630,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="15.75">
+    <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="15">
         <v>1010085384</v>
       </c>
@@ -6638,7 +6641,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="15.75">
+    <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="15">
         <v>1010006347</v>
       </c>
@@ -6649,7 +6652,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="15.75">
+    <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="15">
         <v>1010085179</v>
       </c>
@@ -6660,7 +6663,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="15.75">
+    <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="15">
         <v>1010024158</v>
       </c>
@@ -6671,7 +6674,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="15.75">
+    <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="15">
         <v>1010024131</v>
       </c>
@@ -6682,7 +6685,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="15.75">
+    <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="15">
         <v>1010007160</v>
       </c>
@@ -6693,7 +6696,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="15.75">
+    <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="15">
         <v>1010023642</v>
       </c>
@@ -6704,7 +6707,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="15.75">
+    <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="15">
         <v>1010007193</v>
       </c>
@@ -6715,7 +6718,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="15.75">
+    <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="15">
         <v>1010042637</v>
       </c>
@@ -6726,7 +6729,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="15.75">
+    <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="15">
         <v>1040075323</v>
       </c>
@@ -6737,7 +6740,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="15.75">
+    <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="15">
         <v>1040075324</v>
       </c>
@@ -6748,7 +6751,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="15.75">
+    <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="27">
         <v>1040074827</v>
       </c>
@@ -6759,7 +6762,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="422" spans="1:3" ht="15.75">
+    <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="27">
         <v>1040099488</v>
       </c>
@@ -6770,7 +6773,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="423" spans="1:3" ht="15.75">
+    <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="27">
         <v>1040083312</v>
       </c>
@@ -6781,7 +6784,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="424" spans="1:3" ht="15.75">
+    <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="27">
         <v>1040077661</v>
       </c>
@@ -6792,7 +6795,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="425" spans="1:3" ht="15.75">
+    <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="27">
         <v>1010085180</v>
       </c>
@@ -6803,7 +6806,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="426" spans="1:3" ht="15.75">
+    <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="14">
         <v>1040017489</v>
       </c>
@@ -6814,7 +6817,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="427" spans="1:3" ht="15.75">
+    <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="14">
         <v>1010085181</v>
       </c>
@@ -6825,7 +6828,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="428" spans="1:3" ht="15.75">
+    <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="15">
         <v>400175</v>
       </c>
@@ -6836,7 +6839,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="429" spans="1:3" ht="15.75">
+    <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="15">
         <v>1040017505</v>
       </c>
@@ -6847,7 +6850,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="430" spans="1:3" ht="15.75">
+    <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="15">
         <v>1040017503</v>
       </c>
@@ -6858,7 +6861,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="431" spans="1:3" ht="15.75">
+    <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="15">
         <v>1010046445</v>
       </c>
@@ -6869,7 +6872,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="432" spans="1:3" ht="15.75">
+    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="15">
         <v>1010021033</v>
       </c>
@@ -6880,7 +6883,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="433" spans="1:3" ht="15.75">
+    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="15">
         <v>1010057142</v>
       </c>
@@ -6891,7 +6894,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="434" spans="1:3" ht="15.75">
+    <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="15">
         <v>1010016356</v>
       </c>
@@ -6902,7 +6905,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="435" spans="1:3" ht="15.75">
+    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="15">
         <v>1010084363</v>
       </c>
@@ -6913,7 +6916,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="436" spans="1:3" ht="15.75">
+    <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="15">
         <v>1010052021</v>
       </c>
@@ -6924,7 +6927,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="437" spans="1:3" ht="15.75">
+    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="15">
         <v>1040091721</v>
       </c>
@@ -6935,7 +6938,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="438" spans="1:3" ht="15.75">
+    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="15">
         <v>1010062022</v>
       </c>
@@ -6946,7 +6949,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="15.75">
+    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="15">
         <v>18336</v>
       </c>
@@ -6957,7 +6960,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="440" spans="1:3" ht="15.75">
+    <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="15">
         <v>229205</v>
       </c>
@@ -6968,7 +6971,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="441" spans="1:3" ht="15.75">
+    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="15">
         <v>60671</v>
       </c>
@@ -6979,7 +6982,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="442" spans="1:3" ht="15.75">
+    <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="15">
         <v>1010059726</v>
       </c>
@@ -6990,7 +6993,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="443" spans="1:3" ht="15.75">
+    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="15">
         <v>1010008144</v>
       </c>
@@ -7001,7 +7004,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="444" spans="1:3" ht="15.75">
+    <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="15">
         <v>1010007244</v>
       </c>
@@ -7012,7 +7015,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="445" spans="1:3" ht="15.75">
+    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="15">
         <v>1010006827</v>
       </c>
@@ -7023,7 +7026,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="446" spans="1:3" ht="15.75">
+    <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="15">
         <v>1040075426</v>
       </c>
@@ -7034,7 +7037,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="447" spans="1:3" ht="15.75">
+    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="15">
         <v>1040075427</v>
       </c>
@@ -7045,7 +7048,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="448" spans="1:3" ht="15.75">
+    <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="15">
         <v>1010084313</v>
       </c>
@@ -7056,7 +7059,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="449" spans="1:3" ht="15.75">
+    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="15">
         <v>403459</v>
       </c>
@@ -7067,7 +7070,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="450" spans="1:3" ht="15.75">
+    <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="15">
         <v>1010044828</v>
       </c>
@@ -7078,7 +7081,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="451" spans="1:3" ht="15.75">
+    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="15">
         <v>1010026973</v>
       </c>
@@ -7089,7 +7092,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="15.75">
+    <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="15">
         <v>1040017204</v>
       </c>
@@ -7100,7 +7103,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="453" spans="1:3" ht="15.75">
+    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="24">
         <v>1010022119</v>
       </c>
@@ -7111,7 +7114,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="454" spans="1:3" ht="15.75">
+    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" s="15">
         <v>1010058709</v>
       </c>
@@ -7122,7 +7125,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="455" spans="1:3" ht="15.75">
+    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="15">
         <v>1010025711</v>
       </c>
@@ -7133,7 +7136,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="456" spans="1:3" ht="15.75">
+    <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" s="15">
         <v>1010059684</v>
       </c>
@@ -7144,7 +7147,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="457" spans="1:3" ht="15.75">
+    <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="15">
         <v>427341</v>
       </c>
@@ -7155,7 +7158,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="458" spans="1:3" ht="15.75">
+    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" s="15">
         <v>1010085279</v>
       </c>
@@ -7166,7 +7169,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="459" spans="1:3" ht="15.75">
+    <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="19">
         <v>1010022588</v>
       </c>
@@ -7177,7 +7180,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="460" spans="1:3" ht="15.75">
+    <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" s="15">
         <v>1010026864</v>
       </c>
@@ -7188,7 +7191,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="461" spans="1:3" ht="15.75">
+    <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" s="14">
         <v>1010030946</v>
       </c>
@@ -7199,7 +7202,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="462" spans="1:3" ht="15.75">
+    <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="14">
         <v>1010022589</v>
       </c>
@@ -7210,7 +7213,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="463" spans="1:3" ht="15.75">
+    <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="15">
         <v>1040090143</v>
       </c>
@@ -7221,7 +7224,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="464" spans="1:3" ht="15.75">
+    <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="15">
         <v>1040090138</v>
       </c>
@@ -7232,7 +7235,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="465" spans="1:3" ht="15.75">
+    <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="15">
         <v>1030001314</v>
       </c>
@@ -7243,7 +7246,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="466" spans="1:3" ht="15.75">
+    <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="15">
         <v>1010052319</v>
       </c>
@@ -7254,7 +7257,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="467" spans="1:3" ht="15.75">
+    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" s="15">
         <v>1010052320</v>
       </c>
@@ -7265,7 +7268,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="468" spans="1:3" ht="15.75">
+    <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="15">
         <v>1030000370</v>
       </c>
@@ -7276,7 +7279,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="469" spans="1:3" ht="15.75">
+    <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="15">
         <v>1030000366</v>
       </c>
@@ -7287,7 +7290,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="470" spans="1:3" ht="15.75">
+    <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="15">
         <v>1030000368</v>
       </c>
@@ -7298,7 +7301,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="471" spans="1:3" ht="15.75">
+    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="15">
         <v>1030000369</v>
       </c>
@@ -7309,7 +7312,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="472" spans="1:3" ht="15.75">
+    <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="15">
         <v>1030000489</v>
       </c>
@@ -7320,7 +7323,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="15.75">
+    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="15">
         <v>1030000490</v>
       </c>
@@ -7331,7 +7334,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="474" spans="1:3" ht="15.75">
+    <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="15">
         <v>1030000821</v>
       </c>
@@ -7342,7 +7345,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="475" spans="1:3" ht="15.75">
+    <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="15">
         <v>1030000511</v>
       </c>
@@ -7353,7 +7356,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="476" spans="1:3" ht="15.75">
+    <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="16">
         <v>1010084279</v>
       </c>
@@ -7364,7 +7367,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="477" spans="1:3" ht="15.75">
+    <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="16">
         <v>1010004281</v>
       </c>
@@ -7375,7 +7378,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="478" spans="1:3" ht="15.75">
+    <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" s="15">
         <v>1010022118</v>
       </c>
@@ -7386,7 +7389,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="479" spans="1:3" ht="15.75">
+    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" s="15">
         <v>1010028657</v>
       </c>
@@ -7397,7 +7400,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="480" spans="1:3" ht="15.75">
+    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" s="18">
         <v>1010028655</v>
       </c>
@@ -7408,7 +7411,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="481" spans="1:3" ht="15.75">
+    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="18">
         <v>145165</v>
       </c>
@@ -7419,7 +7422,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="482" spans="1:3" ht="15.75">
+    <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="15">
         <v>51666</v>
       </c>
@@ -7430,7 +7433,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="483" spans="1:3" ht="15.75">
+    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" s="18">
         <v>1010080930</v>
       </c>
@@ -7441,7 +7444,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="484" spans="1:3" ht="15.75">
+    <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" s="15">
         <v>161055</v>
       </c>
@@ -7452,7 +7455,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="485" spans="1:3" ht="15.75">
+    <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="15">
         <v>1010050517</v>
       </c>
@@ -7463,7 +7466,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="486" spans="1:3" ht="15.75">
+    <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="15">
         <v>1010084190</v>
       </c>
@@ -7474,7 +7477,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="487" spans="1:3" ht="15.75">
+    <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="15">
         <v>1010084195</v>
       </c>
@@ -7485,7 +7488,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="488" spans="1:3" ht="15.75">
+    <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="15">
         <v>1010001400</v>
       </c>
@@ -7496,7 +7499,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="489" spans="1:3" ht="15.75">
+    <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="17">
         <v>1010008416</v>
       </c>
@@ -7507,7 +7510,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="490" spans="1:3" ht="15.75">
+    <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="28">
         <v>1010018372</v>
       </c>
@@ -7518,7 +7521,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="491" spans="1:3" ht="15.75">
+    <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="28">
         <v>1010018361</v>
       </c>
@@ -7529,7 +7532,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="492" spans="1:3" ht="15.75">
+    <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="16">
         <v>1010055398</v>
       </c>
@@ -7540,7 +7543,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="493" spans="1:3" ht="15.75">
+    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" s="15">
         <v>422131</v>
       </c>
@@ -7551,7 +7554,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="494" spans="1:3" ht="15.75">
+    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="15">
         <v>1010084370</v>
       </c>
@@ -7562,7 +7565,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="495" spans="1:3" ht="15.75">
+    <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="15">
         <v>422759</v>
       </c>
@@ -7573,7 +7576,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="496" spans="1:3" ht="15.75">
+    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" s="15">
         <v>120955</v>
       </c>
@@ -7584,7 +7587,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="497" spans="1:3" ht="15.75">
+    <row r="497" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" s="15">
         <v>1010000896</v>
       </c>
@@ -7595,7 +7598,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="498" spans="1:3" ht="15.75">
+    <row r="498" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" s="15">
         <v>1010084308</v>
       </c>
@@ -7606,7 +7609,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="499" spans="1:3" ht="15.75">
+    <row r="499" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="15">
         <v>1010084035</v>
       </c>
@@ -7617,2811 +7620,2811 @@
         <v>485</v>
       </c>
     </row>
-    <row r="500" spans="1:3" ht="15.75">
+    <row r="500" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
     </row>
-    <row r="501" spans="1:3" ht="15.75">
+    <row r="501" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
     </row>
-    <row r="502" spans="1:3" ht="15.75">
+    <row r="502" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
     </row>
-    <row r="503" spans="1:3" ht="15.75">
+    <row r="503" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
     </row>
-    <row r="504" spans="1:3" ht="15.75">
+    <row r="504" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
     </row>
-    <row r="505" spans="1:3" ht="15.75">
+    <row r="505" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
     </row>
-    <row r="506" spans="1:3" ht="15.75">
+    <row r="506" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
     </row>
-    <row r="507" spans="1:3" ht="15.75">
+    <row r="507" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
     </row>
-    <row r="508" spans="1:3" ht="15.75">
+    <row r="508" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
     </row>
-    <row r="509" spans="1:3" ht="15.75">
+    <row r="509" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
     </row>
-    <row r="510" spans="1:3" ht="15.75">
+    <row r="510" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
     </row>
-    <row r="511" spans="1:3" ht="15.75">
+    <row r="511" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
     </row>
-    <row r="512" spans="1:3" ht="15.75">
+    <row r="512" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
     </row>
-    <row r="513" spans="1:2" ht="15.75">
+    <row r="513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
     </row>
-    <row r="514" spans="1:2" ht="15.75">
+    <row r="514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
     </row>
-    <row r="515" spans="1:2" ht="15.75">
+    <row r="515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
     </row>
-    <row r="516" spans="1:2" ht="15.75">
+    <row r="516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
     </row>
-    <row r="517" spans="1:2" ht="15.75">
+    <row r="517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
     </row>
-    <row r="518" spans="1:2" ht="15.75">
+    <row r="518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
     </row>
-    <row r="519" spans="1:2" ht="15.75">
+    <row r="519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
     </row>
-    <row r="520" spans="1:2" ht="15.75">
+    <row r="520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
     </row>
-    <row r="521" spans="1:2" ht="15.75">
+    <row r="521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
     </row>
-    <row r="522" spans="1:2" ht="15.75">
+    <row r="522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="1:2" ht="15.75">
+    <row r="523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
     </row>
-    <row r="524" spans="1:2" ht="15.75">
+    <row r="524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
     </row>
-    <row r="525" spans="1:2" ht="15.75">
+    <row r="525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
     </row>
-    <row r="526" spans="1:2" ht="15.75">
+    <row r="526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
     </row>
-    <row r="527" spans="1:2" ht="15.75">
+    <row r="527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
     </row>
-    <row r="528" spans="1:2" ht="15.75">
+    <row r="528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
     </row>
-    <row r="529" spans="1:2" ht="15.75">
+    <row r="529" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
     </row>
-    <row r="530" spans="1:2" ht="15.75">
+    <row r="530" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
     </row>
-    <row r="531" spans="1:2" ht="15.75">
+    <row r="531" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
     </row>
-    <row r="532" spans="1:2" ht="15.75">
+    <row r="532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
     </row>
-    <row r="533" spans="1:2" ht="15.75">
+    <row r="533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
     </row>
-    <row r="534" spans="1:2" ht="15.75">
+    <row r="534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
     </row>
-    <row r="535" spans="1:2" ht="15.75">
+    <row r="535" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
     </row>
-    <row r="536" spans="1:2" ht="15.75">
+    <row r="536" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
     </row>
-    <row r="537" spans="1:2" ht="15.75">
+    <row r="537" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
     </row>
-    <row r="538" spans="1:2" ht="15.75">
+    <row r="538" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
     </row>
-    <row r="539" spans="1:2" ht="15.75">
+    <row r="539" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
     </row>
-    <row r="540" spans="1:2" ht="15.75">
+    <row r="540" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
     </row>
-    <row r="541" spans="1:2" ht="15.75">
+    <row r="541" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
     </row>
-    <row r="542" spans="1:2" ht="15.75">
+    <row r="542" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
     </row>
-    <row r="543" spans="1:2" ht="15.75">
+    <row r="543" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
     </row>
-    <row r="544" spans="1:2" ht="15.75">
+    <row r="544" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
     </row>
-    <row r="545" spans="1:2" ht="15.75">
+    <row r="545" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
     </row>
-    <row r="546" spans="1:2" ht="15.75">
+    <row r="546" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
     </row>
-    <row r="547" spans="1:2" ht="15.75">
+    <row r="547" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
     </row>
-    <row r="548" spans="1:2" ht="15.75">
+    <row r="548" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
     </row>
-    <row r="549" spans="1:2" ht="15.75">
+    <row r="549" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
     </row>
-    <row r="550" spans="1:2" ht="15.75">
+    <row r="550" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
     </row>
-    <row r="551" spans="1:2" ht="15.75">
+    <row r="551" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
     </row>
-    <row r="552" spans="1:2" ht="15.75">
+    <row r="552" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
     </row>
-    <row r="553" spans="1:2" ht="15.75">
+    <row r="553" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
     </row>
-    <row r="554" spans="1:2" ht="15.75">
+    <row r="554" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
     </row>
-    <row r="555" spans="1:2" ht="15.75">
+    <row r="555" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
     </row>
-    <row r="556" spans="1:2" ht="15.75">
+    <row r="556" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
     </row>
-    <row r="557" spans="1:2" ht="15.75">
+    <row r="557" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
     </row>
-    <row r="558" spans="1:2" ht="15.75">
+    <row r="558" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
     </row>
-    <row r="559" spans="1:2" ht="15.75">
+    <row r="559" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
     </row>
-    <row r="560" spans="1:2" ht="15.75">
+    <row r="560" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
     </row>
-    <row r="561" spans="1:2" ht="15.75">
+    <row r="561" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
     </row>
-    <row r="562" spans="1:2" ht="15.75">
+    <row r="562" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
     </row>
-    <row r="563" spans="1:2" ht="15.75">
+    <row r="563" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
     </row>
-    <row r="564" spans="1:2" ht="15.75">
+    <row r="564" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
     </row>
-    <row r="565" spans="1:2" ht="15.75">
+    <row r="565" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
     </row>
-    <row r="566" spans="1:2" ht="15.75">
+    <row r="566" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
     </row>
-    <row r="567" spans="1:2" ht="15.75">
+    <row r="567" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
     </row>
-    <row r="568" spans="1:2" ht="15.75">
+    <row r="568" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
     </row>
-    <row r="569" spans="1:2" ht="15.75">
+    <row r="569" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
     </row>
-    <row r="570" spans="1:2" ht="15.75">
+    <row r="570" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
     </row>
-    <row r="571" spans="1:2" ht="15.75">
+    <row r="571" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
     </row>
-    <row r="572" spans="1:2" ht="15.75">
+    <row r="572" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
     </row>
-    <row r="573" spans="1:2" ht="15.75">
+    <row r="573" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
     </row>
-    <row r="574" spans="1:2" ht="15.75">
+    <row r="574" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
     </row>
-    <row r="575" spans="1:2" ht="15.75">
+    <row r="575" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
     </row>
-    <row r="576" spans="1:2" ht="15.75">
+    <row r="576" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
     </row>
-    <row r="577" spans="1:2" ht="15.75">
+    <row r="577" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
     </row>
-    <row r="578" spans="1:2" ht="15.75">
+    <row r="578" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
     </row>
-    <row r="579" spans="1:2" ht="15.75">
+    <row r="579" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
     </row>
-    <row r="580" spans="1:2" ht="15.75">
+    <row r="580" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
     </row>
-    <row r="581" spans="1:2" ht="15.75">
+    <row r="581" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
     </row>
-    <row r="582" spans="1:2" ht="15.75">
+    <row r="582" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
     </row>
-    <row r="583" spans="1:2" ht="15.75">
+    <row r="583" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
     </row>
-    <row r="584" spans="1:2" ht="15.75">
+    <row r="584" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
     </row>
-    <row r="585" spans="1:2" ht="15.75">
+    <row r="585" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
     </row>
-    <row r="586" spans="1:2" ht="15.75">
+    <row r="586" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
     </row>
-    <row r="587" spans="1:2" ht="15.75">
+    <row r="587" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
     </row>
-    <row r="588" spans="1:2" ht="15.75">
+    <row r="588" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
     </row>
-    <row r="589" spans="1:2" ht="15.75">
+    <row r="589" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
     </row>
-    <row r="590" spans="1:2" ht="15.75">
+    <row r="590" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
     </row>
-    <row r="591" spans="1:2" ht="15.75">
+    <row r="591" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
     </row>
-    <row r="592" spans="1:2" ht="15.75">
+    <row r="592" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
     </row>
-    <row r="593" spans="1:2" ht="15.75">
+    <row r="593" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
     </row>
-    <row r="594" spans="1:2" ht="15.75">
+    <row r="594" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
     </row>
-    <row r="595" spans="1:2" ht="15.75">
+    <row r="595" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
     </row>
-    <row r="596" spans="1:2" ht="15.75">
+    <row r="596" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
     </row>
-    <row r="597" spans="1:2" ht="15.75">
+    <row r="597" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
     </row>
-    <row r="598" spans="1:2" ht="15.75">
+    <row r="598" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
     </row>
-    <row r="599" spans="1:2" ht="15.75">
+    <row r="599" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
     </row>
-    <row r="600" spans="1:2" ht="15.75">
+    <row r="600" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
     </row>
-    <row r="601" spans="1:2" ht="15.75">
+    <row r="601" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
     </row>
-    <row r="602" spans="1:2" ht="15.75">
+    <row r="602" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
     </row>
-    <row r="603" spans="1:2" ht="15.75">
+    <row r="603" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
     </row>
-    <row r="604" spans="1:2" ht="15.75">
+    <row r="604" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
     </row>
-    <row r="605" spans="1:2" ht="15.75">
+    <row r="605" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
     </row>
-    <row r="606" spans="1:2" ht="15.75">
+    <row r="606" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
     </row>
-    <row r="607" spans="1:2" ht="15.75">
+    <row r="607" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
     </row>
-    <row r="608" spans="1:2" ht="15.75">
+    <row r="608" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
     </row>
-    <row r="609" spans="1:2" ht="15.75">
+    <row r="609" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
     </row>
-    <row r="610" spans="1:2" ht="15.75">
+    <row r="610" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
     </row>
-    <row r="611" spans="1:2" ht="15.75">
+    <row r="611" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
     </row>
-    <row r="612" spans="1:2" ht="15.75">
+    <row r="612" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
     </row>
-    <row r="613" spans="1:2" ht="15.75">
+    <row r="613" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
     </row>
-    <row r="614" spans="1:2" ht="15.75">
+    <row r="614" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
     </row>
-    <row r="615" spans="1:2" ht="15.75">
+    <row r="615" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
     </row>
-    <row r="616" spans="1:2" ht="15.75">
+    <row r="616" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
     </row>
-    <row r="617" spans="1:2" ht="15.75">
+    <row r="617" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
     </row>
-    <row r="618" spans="1:2" ht="15.75">
+    <row r="618" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
     </row>
-    <row r="619" spans="1:2" ht="15.75">
+    <row r="619" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
     </row>
-    <row r="620" spans="1:2" ht="15.75">
+    <row r="620" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
     </row>
-    <row r="621" spans="1:2" ht="15.75">
+    <row r="621" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
     </row>
-    <row r="622" spans="1:2" ht="15.75">
+    <row r="622" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
     </row>
-    <row r="623" spans="1:2" ht="15.75">
+    <row r="623" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
     </row>
-    <row r="624" spans="1:2" ht="15.75">
+    <row r="624" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
     </row>
-    <row r="625" spans="1:2" ht="15.75">
+    <row r="625" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
     </row>
-    <row r="626" spans="1:2" ht="15.75">
+    <row r="626" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
     </row>
-    <row r="627" spans="1:2" ht="15.75">
+    <row r="627" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="1:2" ht="15.75">
+    <row r="628" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
     </row>
-    <row r="629" spans="1:2" ht="15.75">
+    <row r="629" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
     </row>
-    <row r="630" spans="1:2" ht="15.75">
+    <row r="630" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
     </row>
-    <row r="631" spans="1:2" ht="15.75">
+    <row r="631" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
     </row>
-    <row r="632" spans="1:2" ht="15.75">
+    <row r="632" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
     </row>
-    <row r="633" spans="1:2" ht="15.75">
+    <row r="633" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
     </row>
-    <row r="634" spans="1:2" ht="15.75">
+    <row r="634" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
     </row>
-    <row r="635" spans="1:2" ht="15.75">
+    <row r="635" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
     </row>
-    <row r="636" spans="1:2" ht="15.75">
+    <row r="636" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
     </row>
-    <row r="637" spans="1:2" ht="15.75">
+    <row r="637" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
     </row>
-    <row r="638" spans="1:2" ht="15.75">
+    <row r="638" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
     </row>
-    <row r="639" spans="1:2" ht="15.75">
+    <row r="639" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
     </row>
-    <row r="640" spans="1:2" ht="15.75">
+    <row r="640" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
     </row>
-    <row r="641" spans="1:2" ht="15.75">
+    <row r="641" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
     </row>
-    <row r="642" spans="1:2" ht="15.75">
+    <row r="642" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
     </row>
-    <row r="643" spans="1:2" ht="15.75">
+    <row r="643" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
     </row>
-    <row r="644" spans="1:2" ht="15.75">
+    <row r="644" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
     </row>
-    <row r="645" spans="1:2" ht="15.75">
+    <row r="645" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
     </row>
-    <row r="646" spans="1:2" ht="15.75">
+    <row r="646" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
     </row>
-    <row r="647" spans="1:2" ht="15.75">
+    <row r="647" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
     </row>
-    <row r="648" spans="1:2" ht="15.75">
+    <row r="648" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
     </row>
-    <row r="649" spans="1:2" ht="15.75">
+    <row r="649" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
     </row>
-    <row r="650" spans="1:2" ht="15.75">
+    <row r="650" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
     </row>
-    <row r="651" spans="1:2" ht="15.75">
+    <row r="651" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
     </row>
-    <row r="652" spans="1:2" ht="15.75">
+    <row r="652" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
     </row>
-    <row r="653" spans="1:2" ht="15.75">
+    <row r="653" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
     </row>
-    <row r="654" spans="1:2" ht="15.75">
+    <row r="654" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
     </row>
-    <row r="655" spans="1:2" ht="15.75">
+    <row r="655" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
     </row>
-    <row r="656" spans="1:2" ht="15.75">
+    <row r="656" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
     </row>
-    <row r="657" spans="1:2" ht="15.75">
+    <row r="657" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
     </row>
-    <row r="658" spans="1:2" ht="15.75">
+    <row r="658" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
     </row>
-    <row r="659" spans="1:2" ht="15.75">
+    <row r="659" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
     </row>
-    <row r="660" spans="1:2" ht="15.75">
+    <row r="660" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
     </row>
-    <row r="661" spans="1:2" ht="15.75">
+    <row r="661" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
     </row>
-    <row r="662" spans="1:2" ht="15.75">
+    <row r="662" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
     </row>
-    <row r="663" spans="1:2" ht="15.75">
+    <row r="663" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
     </row>
-    <row r="664" spans="1:2" ht="15.75">
+    <row r="664" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
     </row>
-    <row r="665" spans="1:2" ht="15.75">
+    <row r="665" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
     </row>
-    <row r="666" spans="1:2" ht="15.75">
+    <row r="666" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
     </row>
-    <row r="667" spans="1:2" ht="15.75">
+    <row r="667" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
     </row>
-    <row r="668" spans="1:2" ht="15.75">
+    <row r="668" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
     </row>
-    <row r="669" spans="1:2" ht="15.75">
+    <row r="669" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
     </row>
-    <row r="670" spans="1:2" ht="15.75">
+    <row r="670" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
     </row>
-    <row r="671" spans="1:2" ht="15.75">
+    <row r="671" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
     </row>
-    <row r="672" spans="1:2" ht="15.75">
+    <row r="672" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
     </row>
-    <row r="673" spans="1:2" ht="15.75">
+    <row r="673" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
     </row>
-    <row r="674" spans="1:2" ht="15.75">
+    <row r="674" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
     </row>
-    <row r="675" spans="1:2" ht="15.75">
+    <row r="675" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
     </row>
-    <row r="676" spans="1:2" ht="15.75">
+    <row r="676" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
     </row>
-    <row r="677" spans="1:2" ht="15.75">
+    <row r="677" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
     </row>
-    <row r="678" spans="1:2" ht="15.75">
+    <row r="678" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
     </row>
-    <row r="679" spans="1:2" ht="15.75">
+    <row r="679" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
     </row>
-    <row r="680" spans="1:2" ht="15.75">
+    <row r="680" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
     </row>
-    <row r="681" spans="1:2" ht="15.75">
+    <row r="681" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
     </row>
-    <row r="682" spans="1:2" ht="15.75">
+    <row r="682" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
     </row>
-    <row r="683" spans="1:2" ht="15.75">
+    <row r="683" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
     </row>
-    <row r="684" spans="1:2" ht="15.75">
+    <row r="684" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
     </row>
-    <row r="685" spans="1:2" ht="15.75">
+    <row r="685" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
     </row>
-    <row r="686" spans="1:2" ht="15.75">
+    <row r="686" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
     </row>
-    <row r="687" spans="1:2" ht="15.75">
+    <row r="687" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
     </row>
-    <row r="688" spans="1:2" ht="15.75">
+    <row r="688" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
     </row>
-    <row r="689" spans="1:2" ht="15.75">
+    <row r="689" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
     </row>
-    <row r="690" spans="1:2" ht="15.75">
+    <row r="690" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
     </row>
-    <row r="691" spans="1:2" ht="15.75">
+    <row r="691" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
     </row>
-    <row r="692" spans="1:2" ht="15.75">
+    <row r="692" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
     </row>
-    <row r="693" spans="1:2" ht="15.75">
+    <row r="693" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
     </row>
-    <row r="694" spans="1:2" ht="15.75">
+    <row r="694" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
     </row>
-    <row r="695" spans="1:2" ht="15.75">
+    <row r="695" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
     </row>
-    <row r="696" spans="1:2" ht="15.75">
+    <row r="696" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
     </row>
-    <row r="697" spans="1:2" ht="15.75">
+    <row r="697" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
     </row>
-    <row r="698" spans="1:2" ht="15.75">
+    <row r="698" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
     </row>
-    <row r="699" spans="1:2" ht="15.75">
+    <row r="699" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
     </row>
-    <row r="700" spans="1:2" ht="15.75">
+    <row r="700" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
     </row>
-    <row r="701" spans="1:2" ht="15.75">
+    <row r="701" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
     </row>
-    <row r="702" spans="1:2" ht="15.75">
+    <row r="702" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
     </row>
-    <row r="703" spans="1:2" ht="15.75">
+    <row r="703" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
     </row>
-    <row r="704" spans="1:2" ht="15.75">
+    <row r="704" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
     </row>
-    <row r="705" spans="1:2" ht="15.75">
+    <row r="705" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
     </row>
-    <row r="706" spans="1:2" ht="15.75">
+    <row r="706" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
     </row>
-    <row r="707" spans="1:2" ht="15.75">
+    <row r="707" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
     </row>
-    <row r="708" spans="1:2" ht="15.75">
+    <row r="708" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
     </row>
-    <row r="709" spans="1:2" ht="15.75">
+    <row r="709" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
     </row>
-    <row r="710" spans="1:2" ht="15.75">
+    <row r="710" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
     </row>
-    <row r="711" spans="1:2" ht="15.75">
+    <row r="711" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
     </row>
-    <row r="712" spans="1:2" ht="15.75">
+    <row r="712" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
     </row>
-    <row r="713" spans="1:2" ht="15.75">
+    <row r="713" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
     </row>
-    <row r="714" spans="1:2" ht="15.75">
+    <row r="714" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
     </row>
-    <row r="715" spans="1:2" ht="15.75">
+    <row r="715" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
     </row>
-    <row r="716" spans="1:2" ht="15.75">
+    <row r="716" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
     </row>
-    <row r="717" spans="1:2" ht="15.75">
+    <row r="717" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
     </row>
-    <row r="718" spans="1:2" ht="15.75">
+    <row r="718" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
     </row>
-    <row r="719" spans="1:2" ht="15.75">
+    <row r="719" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
     </row>
-    <row r="720" spans="1:2" ht="15.75">
+    <row r="720" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
     </row>
-    <row r="721" spans="1:2" ht="15.75">
+    <row r="721" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
     </row>
-    <row r="722" spans="1:2" ht="15.75">
+    <row r="722" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
     </row>
-    <row r="723" spans="1:2" ht="15.75">
+    <row r="723" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
     </row>
-    <row r="724" spans="1:2" ht="15.75">
+    <row r="724" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
     </row>
-    <row r="725" spans="1:2" ht="15.75">
+    <row r="725" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
     </row>
-    <row r="726" spans="1:2" ht="15.75">
+    <row r="726" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
     </row>
-    <row r="727" spans="1:2" ht="15.75">
+    <row r="727" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
     </row>
-    <row r="728" spans="1:2" ht="15.75">
+    <row r="728" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
     </row>
-    <row r="729" spans="1:2" ht="15.75">
+    <row r="729" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
     </row>
-    <row r="730" spans="1:2" ht="15.75">
+    <row r="730" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
     </row>
-    <row r="731" spans="1:2" ht="15.75">
+    <row r="731" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
     </row>
-    <row r="732" spans="1:2" ht="15.75">
+    <row r="732" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
     </row>
-    <row r="733" spans="1:2" ht="15.75">
+    <row r="733" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
     </row>
-    <row r="734" spans="1:2" ht="15.75">
+    <row r="734" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
     </row>
-    <row r="735" spans="1:2" ht="15.75">
+    <row r="735" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
     </row>
-    <row r="736" spans="1:2" ht="15.75">
+    <row r="736" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
     </row>
-    <row r="737" spans="1:2" ht="15.75">
+    <row r="737" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
     </row>
-    <row r="738" spans="1:2" ht="15.75">
+    <row r="738" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
     </row>
-    <row r="739" spans="1:2" ht="15.75">
+    <row r="739" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
     </row>
-    <row r="740" spans="1:2" ht="15.75">
+    <row r="740" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
     </row>
-    <row r="741" spans="1:2" ht="15.75">
+    <row r="741" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
     </row>
-    <row r="742" spans="1:2" ht="15.75">
+    <row r="742" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
     </row>
-    <row r="743" spans="1:2" ht="15.75">
+    <row r="743" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
     </row>
-    <row r="744" spans="1:2" ht="15.75">
+    <row r="744" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
     </row>
-    <row r="745" spans="1:2" ht="15.75">
+    <row r="745" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
     </row>
-    <row r="746" spans="1:2" ht="15.75">
+    <row r="746" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
     </row>
-    <row r="747" spans="1:2" ht="15.75">
+    <row r="747" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
     </row>
-    <row r="748" spans="1:2" ht="15.75">
+    <row r="748" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
     </row>
-    <row r="749" spans="1:2" ht="15.75">
+    <row r="749" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
     </row>
-    <row r="750" spans="1:2" ht="15.75">
+    <row r="750" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
     </row>
-    <row r="751" spans="1:2" ht="15.75">
+    <row r="751" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
     </row>
-    <row r="752" spans="1:2" ht="15.75">
+    <row r="752" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
     </row>
-    <row r="753" spans="1:2" ht="15.75">
+    <row r="753" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
     </row>
-    <row r="754" spans="1:2" ht="15.75">
+    <row r="754" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
     </row>
-    <row r="755" spans="1:2" ht="15.75">
+    <row r="755" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
     </row>
-    <row r="756" spans="1:2" ht="15.75">
+    <row r="756" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
     </row>
-    <row r="757" spans="1:2" ht="15.75">
+    <row r="757" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
     </row>
-    <row r="758" spans="1:2" ht="15.75">
+    <row r="758" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
     </row>
-    <row r="759" spans="1:2" ht="15.75">
+    <row r="759" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
     </row>
-    <row r="760" spans="1:2" ht="15.75">
+    <row r="760" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
     </row>
-    <row r="761" spans="1:2" ht="15.75">
+    <row r="761" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
     </row>
-    <row r="762" spans="1:2" ht="15.75">
+    <row r="762" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
     </row>
-    <row r="763" spans="1:2" ht="15.75">
+    <row r="763" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
     </row>
-    <row r="764" spans="1:2" ht="15.75">
+    <row r="764" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
     </row>
-    <row r="765" spans="1:2" ht="15.75">
+    <row r="765" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
     </row>
-    <row r="766" spans="1:2" ht="15.75">
+    <row r="766" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
     </row>
-    <row r="767" spans="1:2" ht="15.75">
+    <row r="767" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
     </row>
-    <row r="768" spans="1:2" ht="15.75">
+    <row r="768" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
     </row>
-    <row r="769" spans="1:2" ht="15.75">
+    <row r="769" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
     </row>
-    <row r="770" spans="1:2" ht="15.75">
+    <row r="770" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
     </row>
-    <row r="771" spans="1:2" ht="15.75">
+    <row r="771" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
     </row>
-    <row r="772" spans="1:2" ht="15.75">
+    <row r="772" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
     </row>
-    <row r="773" spans="1:2" ht="15.75">
+    <row r="773" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
     </row>
-    <row r="774" spans="1:2" ht="15.75">
+    <row r="774" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
     </row>
-    <row r="775" spans="1:2" ht="15.75">
+    <row r="775" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
     </row>
-    <row r="776" spans="1:2" ht="15.75">
+    <row r="776" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
     </row>
-    <row r="777" spans="1:2" ht="15.75">
+    <row r="777" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
     </row>
-    <row r="778" spans="1:2" ht="15.75">
+    <row r="778" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
     </row>
-    <row r="779" spans="1:2" ht="15.75">
+    <row r="779" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
     </row>
-    <row r="780" spans="1:2" ht="15.75">
+    <row r="780" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
     </row>
-    <row r="781" spans="1:2" ht="15.75">
+    <row r="781" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
     </row>
-    <row r="782" spans="1:2" ht="15.75">
+    <row r="782" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
     </row>
-    <row r="783" spans="1:2" ht="15.75">
+    <row r="783" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
     </row>
-    <row r="784" spans="1:2" ht="15.75">
+    <row r="784" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
     </row>
-    <row r="785" spans="1:2" ht="15.75">
+    <row r="785" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
     </row>
-    <row r="786" spans="1:2" ht="15.75">
+    <row r="786" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
     </row>
-    <row r="787" spans="1:2" ht="15.75">
+    <row r="787" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
     </row>
-    <row r="788" spans="1:2" ht="15.75">
+    <row r="788" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
     </row>
-    <row r="789" spans="1:2" ht="15.75">
+    <row r="789" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
     </row>
-    <row r="790" spans="1:2" ht="15.75">
+    <row r="790" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
     </row>
-    <row r="791" spans="1:2" ht="15.75">
+    <row r="791" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
     </row>
-    <row r="792" spans="1:2" ht="15.75">
+    <row r="792" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
     </row>
-    <row r="793" spans="1:2" ht="15.75">
+    <row r="793" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
     </row>
-    <row r="794" spans="1:2" ht="15.75">
+    <row r="794" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
     </row>
-    <row r="795" spans="1:2" ht="15.75">
+    <row r="795" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
     </row>
-    <row r="796" spans="1:2" ht="15.75">
+    <row r="796" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
     </row>
-    <row r="797" spans="1:2" ht="15.75">
+    <row r="797" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
     </row>
-    <row r="798" spans="1:2" ht="15.75">
+    <row r="798" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
     </row>
-    <row r="799" spans="1:2" ht="15.75">
+    <row r="799" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
     </row>
-    <row r="800" spans="1:2" ht="15.75">
+    <row r="800" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
     </row>
-    <row r="801" spans="1:2" ht="15.75">
+    <row r="801" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
     </row>
-    <row r="802" spans="1:2" ht="15.75">
+    <row r="802" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
     </row>
-    <row r="803" spans="1:2" ht="15.75">
+    <row r="803" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
     </row>
-    <row r="804" spans="1:2" ht="15.75">
+    <row r="804" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
     </row>
-    <row r="805" spans="1:2" ht="15.75">
+    <row r="805" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
     </row>
-    <row r="806" spans="1:2" ht="15.75">
+    <row r="806" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
     </row>
-    <row r="807" spans="1:2" ht="15.75">
+    <row r="807" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
     </row>
-    <row r="808" spans="1:2" ht="15.75">
+    <row r="808" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
     </row>
-    <row r="809" spans="1:2" ht="15.75">
+    <row r="809" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
     </row>
-    <row r="810" spans="1:2" ht="15.75">
+    <row r="810" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
     </row>
-    <row r="811" spans="1:2" ht="15.75">
+    <row r="811" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
     </row>
-    <row r="812" spans="1:2" ht="15.75">
+    <row r="812" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
     </row>
-    <row r="813" spans="1:2" ht="15.75">
+    <row r="813" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
     </row>
-    <row r="814" spans="1:2" ht="15.75">
+    <row r="814" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
     </row>
-    <row r="815" spans="1:2" ht="15.75">
+    <row r="815" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
     </row>
-    <row r="816" spans="1:2" ht="15.75">
+    <row r="816" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
     </row>
-    <row r="817" spans="1:2" ht="15.75">
+    <row r="817" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
     </row>
-    <row r="818" spans="1:2" ht="15.75">
+    <row r="818" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
     </row>
-    <row r="819" spans="1:2" ht="15.75">
+    <row r="819" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
     </row>
-    <row r="820" spans="1:2" ht="15.75">
+    <row r="820" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
     </row>
-    <row r="821" spans="1:2" ht="15.75">
+    <row r="821" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
     </row>
-    <row r="822" spans="1:2" ht="15.75">
+    <row r="822" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
     </row>
-    <row r="823" spans="1:2" ht="15.75">
+    <row r="823" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
     </row>
-    <row r="824" spans="1:2" ht="15.75">
+    <row r="824" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
     </row>
-    <row r="825" spans="1:2" ht="15.75">
+    <row r="825" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
     </row>
-    <row r="826" spans="1:2" ht="15.75">
+    <row r="826" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
     </row>
-    <row r="827" spans="1:2" ht="15.75">
+    <row r="827" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
     </row>
-    <row r="828" spans="1:2" ht="15.75">
+    <row r="828" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
     </row>
-    <row r="829" spans="1:2" ht="15.75">
+    <row r="829" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
     </row>
-    <row r="830" spans="1:2" ht="15.75">
+    <row r="830" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
     </row>
-    <row r="831" spans="1:2" ht="15.75">
+    <row r="831" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
     </row>
-    <row r="832" spans="1:2" ht="15.75">
+    <row r="832" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
     </row>
-    <row r="833" spans="1:2" ht="15.75">
+    <row r="833" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
     </row>
-    <row r="834" spans="1:2" ht="15.75">
+    <row r="834" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
     </row>
-    <row r="835" spans="1:2" ht="15.75">
+    <row r="835" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
     </row>
-    <row r="836" spans="1:2" ht="15.75">
+    <row r="836" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
     </row>
-    <row r="837" spans="1:2" ht="15.75">
+    <row r="837" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
     </row>
-    <row r="838" spans="1:2" ht="15.75">
+    <row r="838" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
     </row>
-    <row r="839" spans="1:2" ht="15.75">
+    <row r="839" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
     </row>
-    <row r="840" spans="1:2" ht="15.75">
+    <row r="840" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
     </row>
-    <row r="841" spans="1:2" ht="15.75">
+    <row r="841" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
     </row>
-    <row r="842" spans="1:2" ht="15.75">
+    <row r="842" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
     </row>
-    <row r="843" spans="1:2" ht="15.75">
+    <row r="843" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
     </row>
-    <row r="844" spans="1:2" ht="15.75">
+    <row r="844" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
     </row>
-    <row r="845" spans="1:2" ht="15.75">
+    <row r="845" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
     </row>
-    <row r="846" spans="1:2" ht="15.75">
+    <row r="846" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
     </row>
-    <row r="847" spans="1:2" ht="15.75">
+    <row r="847" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
     </row>
-    <row r="848" spans="1:2" ht="15.75">
+    <row r="848" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
     </row>
-    <row r="849" spans="1:2" ht="15.75">
+    <row r="849" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
     </row>
-    <row r="850" spans="1:2" ht="15.75">
+    <row r="850" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
     </row>
-    <row r="851" spans="1:2" ht="15.75">
+    <row r="851" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
     </row>
-    <row r="852" spans="1:2" ht="15.75">
+    <row r="852" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
     </row>
-    <row r="853" spans="1:2" ht="15.75">
+    <row r="853" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
     </row>
-    <row r="854" spans="1:2" ht="15.75">
+    <row r="854" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
     </row>
-    <row r="855" spans="1:2" ht="15.75">
+    <row r="855" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
     </row>
-    <row r="856" spans="1:2" ht="15.75">
+    <row r="856" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
     </row>
-    <row r="857" spans="1:2" ht="15.75">
+    <row r="857" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
     </row>
-    <row r="858" spans="1:2" ht="15.75">
+    <row r="858" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
     </row>
-    <row r="859" spans="1:2" ht="15.75">
+    <row r="859" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
     </row>
-    <row r="860" spans="1:2" ht="15.75">
+    <row r="860" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
     </row>
-    <row r="861" spans="1:2" ht="15.75">
+    <row r="861" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
     </row>
-    <row r="862" spans="1:2" ht="15.75">
+    <row r="862" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
     </row>
-    <row r="863" spans="1:2" ht="15.75">
+    <row r="863" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
     </row>
-    <row r="864" spans="1:2" ht="15.75">
+    <row r="864" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
     </row>
-    <row r="865" spans="1:2" ht="15.75">
+    <row r="865" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
     </row>
-    <row r="866" spans="1:2" ht="15.75">
+    <row r="866" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
     </row>
-    <row r="867" spans="1:2" ht="15.75">
+    <row r="867" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
     </row>
-    <row r="868" spans="1:2" ht="15.75">
+    <row r="868" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
     </row>
-    <row r="869" spans="1:2" ht="15.75">
+    <row r="869" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
     </row>
-    <row r="870" spans="1:2" ht="15.75">
+    <row r="870" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
     </row>
-    <row r="871" spans="1:2" ht="15.75">
+    <row r="871" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
     </row>
-    <row r="872" spans="1:2" ht="15.75">
+    <row r="872" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
     </row>
-    <row r="873" spans="1:2" ht="15.75">
+    <row r="873" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
     </row>
-    <row r="874" spans="1:2" ht="15.75">
+    <row r="874" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
     </row>
-    <row r="875" spans="1:2" ht="15.75">
+    <row r="875" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
     </row>
-    <row r="876" spans="1:2" ht="15.75">
+    <row r="876" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
     </row>
-    <row r="877" spans="1:2" ht="15.75">
+    <row r="877" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
     </row>
-    <row r="878" spans="1:2" ht="15.75">
+    <row r="878" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
     </row>
-    <row r="879" spans="1:2" ht="15.75">
+    <row r="879" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
     </row>
-    <row r="880" spans="1:2" ht="15.75">
+    <row r="880" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
     </row>
-    <row r="881" spans="1:2" ht="15.75">
+    <row r="881" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
     </row>
-    <row r="882" spans="1:2" ht="15.75">
+    <row r="882" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
     </row>
-    <row r="883" spans="1:2" ht="15.75">
+    <row r="883" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
     </row>
-    <row r="884" spans="1:2" ht="15.75">
+    <row r="884" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
     </row>
-    <row r="885" spans="1:2" ht="15.75">
+    <row r="885" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
     </row>
-    <row r="886" spans="1:2" ht="15.75">
+    <row r="886" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
     </row>
-    <row r="887" spans="1:2" ht="15.75">
+    <row r="887" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
     </row>
-    <row r="888" spans="1:2" ht="15.75">
+    <row r="888" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
     </row>
-    <row r="889" spans="1:2" ht="15.75">
+    <row r="889" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
     </row>
-    <row r="890" spans="1:2" ht="15.75">
+    <row r="890" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
     </row>
-    <row r="891" spans="1:2" ht="15.75">
+    <row r="891" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
     </row>
-    <row r="892" spans="1:2" ht="15.75">
+    <row r="892" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
     </row>
-    <row r="893" spans="1:2" ht="15.75">
+    <row r="893" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
     </row>
-    <row r="894" spans="1:2" ht="15.75">
+    <row r="894" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
     </row>
-    <row r="895" spans="1:2" ht="15.75">
+    <row r="895" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
     </row>
-    <row r="896" spans="1:2" ht="15.75">
+    <row r="896" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
     </row>
-    <row r="897" spans="1:2" ht="15.75">
+    <row r="897" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
     </row>
-    <row r="898" spans="1:2" ht="15.75">
+    <row r="898" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
     </row>
-    <row r="899" spans="1:2" ht="15.75">
+    <row r="899" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
     </row>
-    <row r="900" spans="1:2" ht="15.75">
+    <row r="900" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
     </row>
-    <row r="901" spans="1:2" ht="15.75">
+    <row r="901" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
     </row>
-    <row r="902" spans="1:2" ht="15.75">
+    <row r="902" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
     </row>
-    <row r="903" spans="1:2" ht="15.75">
+    <row r="903" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
     </row>
-    <row r="904" spans="1:2" ht="15.75">
+    <row r="904" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
     </row>
-    <row r="905" spans="1:2" ht="15.75">
+    <row r="905" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
     </row>
-    <row r="906" spans="1:2" ht="15.75">
+    <row r="906" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
     </row>
-    <row r="907" spans="1:2" ht="15.75">
+    <row r="907" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
     </row>
-    <row r="908" spans="1:2" ht="15.75">
+    <row r="908" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
     </row>
-    <row r="909" spans="1:2" ht="15.75">
+    <row r="909" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
     </row>
-    <row r="910" spans="1:2" ht="15.75">
+    <row r="910" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
     </row>
-    <row r="911" spans="1:2" ht="15.75">
+    <row r="911" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
     </row>
-    <row r="912" spans="1:2" ht="15.75">
+    <row r="912" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
     </row>
-    <row r="913" spans="1:2" ht="15.75">
+    <row r="913" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
     </row>
-    <row r="914" spans="1:2" ht="15.75">
+    <row r="914" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
     </row>
-    <row r="915" spans="1:2" ht="15.75">
+    <row r="915" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
     </row>
-    <row r="916" spans="1:2" ht="15.75">
+    <row r="916" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
     </row>
-    <row r="917" spans="1:2" ht="15.75">
+    <row r="917" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
     </row>
-    <row r="918" spans="1:2" ht="15.75">
+    <row r="918" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
     </row>
-    <row r="919" spans="1:2" ht="15.75">
+    <row r="919" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
     </row>
-    <row r="920" spans="1:2" ht="15.75">
+    <row r="920" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
     </row>
-    <row r="921" spans="1:2" ht="15.75">
+    <row r="921" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
     </row>
-    <row r="922" spans="1:2" ht="15.75">
+    <row r="922" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
     </row>
-    <row r="923" spans="1:2" ht="15.75">
+    <row r="923" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
     </row>
-    <row r="924" spans="1:2" ht="15.75">
+    <row r="924" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
     </row>
-    <row r="925" spans="1:2" ht="15.75">
+    <row r="925" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
     </row>
-    <row r="926" spans="1:2" ht="15.75">
+    <row r="926" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
     </row>
-    <row r="927" spans="1:2" ht="15.75">
+    <row r="927" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
     </row>
-    <row r="928" spans="1:2" ht="15.75">
+    <row r="928" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
     </row>
-    <row r="929" spans="1:2" ht="15.75">
+    <row r="929" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
     </row>
-    <row r="930" spans="1:2" ht="15.75">
+    <row r="930" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
     </row>
-    <row r="931" spans="1:2" ht="15.75">
+    <row r="931" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
     </row>
-    <row r="932" spans="1:2" ht="15.75">
+    <row r="932" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
     </row>
-    <row r="933" spans="1:2" ht="15.75">
+    <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
     </row>
-    <row r="934" spans="1:2" ht="15.75">
+    <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
     </row>
-    <row r="935" spans="1:2" ht="15.75">
+    <row r="935" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
     </row>
-    <row r="936" spans="1:2" ht="15.75">
+    <row r="936" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
     </row>
-    <row r="937" spans="1:2" ht="15.75">
+    <row r="937" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
     </row>
-    <row r="938" spans="1:2" ht="15.75">
+    <row r="938" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
     </row>
-    <row r="939" spans="1:2" ht="15.75">
+    <row r="939" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A939" s="2"/>
       <c r="B939" s="1"/>
     </row>
-    <row r="940" spans="1:2" ht="15.75">
+    <row r="940" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A940" s="2"/>
       <c r="B940" s="1"/>
     </row>
-    <row r="941" spans="1:2" ht="15.75">
+    <row r="941" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A941" s="2"/>
       <c r="B941" s="1"/>
     </row>
-    <row r="942" spans="1:2" ht="15.75">
+    <row r="942" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A942" s="2"/>
       <c r="B942" s="1"/>
     </row>
-    <row r="943" spans="1:2" ht="15.75">
+    <row r="943" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A943" s="2"/>
       <c r="B943" s="1"/>
     </row>
-    <row r="944" spans="1:2" ht="15.75">
+    <row r="944" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A944" s="2"/>
       <c r="B944" s="1"/>
     </row>
-    <row r="945" spans="1:2" ht="15.75">
+    <row r="945" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A945" s="2"/>
       <c r="B945" s="1"/>
     </row>
-    <row r="946" spans="1:2" ht="15.75">
+    <row r="946" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A946" s="2"/>
       <c r="B946" s="1"/>
     </row>
-    <row r="947" spans="1:2" ht="15.75">
+    <row r="947" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A947" s="2"/>
       <c r="B947" s="1"/>
     </row>
-    <row r="948" spans="1:2" ht="15.75">
+    <row r="948" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A948" s="2"/>
       <c r="B948" s="1"/>
     </row>
-    <row r="949" spans="1:2" ht="15.75">
+    <row r="949" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A949" s="2"/>
       <c r="B949" s="1"/>
     </row>
-    <row r="950" spans="1:2" ht="15.75">
+    <row r="950" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A950" s="2"/>
       <c r="B950" s="1"/>
     </row>
-    <row r="951" spans="1:2" ht="15.75">
+    <row r="951" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A951" s="2"/>
       <c r="B951" s="1"/>
     </row>
-    <row r="952" spans="1:2" ht="15.75">
+    <row r="952" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A952" s="2"/>
       <c r="B952" s="1"/>
     </row>
-    <row r="953" spans="1:2" ht="15.75">
+    <row r="953" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A953" s="2"/>
       <c r="B953" s="1"/>
     </row>
-    <row r="954" spans="1:2" ht="15.75">
+    <row r="954" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A954" s="2"/>
       <c r="B954" s="1"/>
     </row>
-    <row r="955" spans="1:2" ht="15.75">
+    <row r="955" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A955" s="2"/>
       <c r="B955" s="1"/>
     </row>
-    <row r="956" spans="1:2" ht="15.75">
+    <row r="956" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A956" s="2"/>
       <c r="B956" s="1"/>
     </row>
-    <row r="957" spans="1:2" ht="15.75">
+    <row r="957" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A957" s="2"/>
       <c r="B957" s="1"/>
     </row>
-    <row r="958" spans="1:2" ht="15.75">
+    <row r="958" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A958" s="2"/>
       <c r="B958" s="1"/>
     </row>
-    <row r="959" spans="1:2" ht="15.75">
+    <row r="959" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A959" s="2"/>
       <c r="B959" s="1"/>
     </row>
-    <row r="960" spans="1:2" ht="15.75">
+    <row r="960" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A960" s="2"/>
       <c r="B960" s="1"/>
     </row>
-    <row r="961" spans="1:2" ht="15.75">
+    <row r="961" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A961" s="2"/>
       <c r="B961" s="1"/>
     </row>
-    <row r="962" spans="1:2" ht="15.75">
+    <row r="962" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A962" s="2"/>
       <c r="B962" s="1"/>
     </row>
-    <row r="963" spans="1:2" ht="15.75">
+    <row r="963" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A963" s="2"/>
       <c r="B963" s="1"/>
     </row>
-    <row r="964" spans="1:2" ht="15.75">
+    <row r="964" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A964" s="2"/>
       <c r="B964" s="1"/>
     </row>
-    <row r="965" spans="1:2" ht="15.75">
+    <row r="965" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A965" s="2"/>
       <c r="B965" s="1"/>
     </row>
-    <row r="966" spans="1:2" ht="15.75">
+    <row r="966" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A966" s="2"/>
       <c r="B966" s="1"/>
     </row>
-    <row r="967" spans="1:2" ht="15.75">
+    <row r="967" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A967" s="2"/>
       <c r="B967" s="1"/>
     </row>
-    <row r="968" spans="1:2" ht="15.75">
+    <row r="968" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A968" s="2"/>
       <c r="B968" s="1"/>
     </row>
-    <row r="969" spans="1:2" ht="15.75">
+    <row r="969" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A969" s="2"/>
       <c r="B969" s="1"/>
     </row>
-    <row r="970" spans="1:2" ht="15.75">
+    <row r="970" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A970" s="2"/>
       <c r="B970" s="1"/>
     </row>
-    <row r="971" spans="1:2" ht="15.75">
+    <row r="971" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A971" s="2"/>
       <c r="B971" s="1"/>
     </row>
-    <row r="972" spans="1:2" ht="15.75">
+    <row r="972" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A972" s="2"/>
       <c r="B972" s="1"/>
     </row>
-    <row r="973" spans="1:2" ht="15.75">
+    <row r="973" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A973" s="2"/>
       <c r="B973" s="1"/>
     </row>
-    <row r="974" spans="1:2" ht="15.75">
+    <row r="974" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A974" s="2"/>
       <c r="B974" s="1"/>
     </row>
-    <row r="975" spans="1:2" ht="15.75">
+    <row r="975" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A975" s="2"/>
       <c r="B975" s="1"/>
     </row>
-    <row r="976" spans="1:2" ht="15.75">
+    <row r="976" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A976" s="2"/>
       <c r="B976" s="1"/>
     </row>
-    <row r="977" spans="1:2" ht="15.75">
+    <row r="977" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A977" s="2"/>
       <c r="B977" s="1"/>
     </row>
-    <row r="978" spans="1:2" ht="15.75">
+    <row r="978" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A978" s="2"/>
       <c r="B978" s="1"/>
     </row>
-    <row r="979" spans="1:2" ht="15.75">
+    <row r="979" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A979" s="2"/>
       <c r="B979" s="1"/>
     </row>
-    <row r="980" spans="1:2" ht="15.75">
+    <row r="980" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A980" s="2"/>
       <c r="B980" s="1"/>
     </row>
-    <row r="981" spans="1:2" ht="15.75">
+    <row r="981" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A981" s="2"/>
       <c r="B981" s="1"/>
     </row>
-    <row r="982" spans="1:2" ht="15.75">
+    <row r="982" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A982" s="2"/>
       <c r="B982" s="1"/>
     </row>
-    <row r="983" spans="1:2" ht="15.75">
+    <row r="983" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A983" s="2"/>
       <c r="B983" s="1"/>
     </row>
-    <row r="984" spans="1:2" ht="15.75">
+    <row r="984" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A984" s="2"/>
       <c r="B984" s="1"/>
     </row>
-    <row r="985" spans="1:2" ht="15.75">
+    <row r="985" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A985" s="2"/>
       <c r="B985" s="1"/>
     </row>
-    <row r="986" spans="1:2" ht="15.75">
+    <row r="986" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A986" s="2"/>
       <c r="B986" s="1"/>
     </row>
-    <row r="987" spans="1:2" ht="15.75">
+    <row r="987" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A987" s="2"/>
       <c r="B987" s="1"/>
     </row>
-    <row r="988" spans="1:2" ht="15.75">
+    <row r="988" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A988" s="2"/>
       <c r="B988" s="1"/>
     </row>
-    <row r="989" spans="1:2" ht="15.75">
+    <row r="989" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A989" s="2"/>
       <c r="B989" s="1"/>
     </row>
-    <row r="990" spans="1:2" ht="15.75">
+    <row r="990" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A990" s="2"/>
       <c r="B990" s="1"/>
     </row>
-    <row r="991" spans="1:2" ht="15.75">
+    <row r="991" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A991" s="2"/>
       <c r="B991" s="1"/>
     </row>
-    <row r="992" spans="1:2" ht="15.75">
+    <row r="992" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A992" s="2"/>
       <c r="B992" s="1"/>
     </row>
-    <row r="993" spans="1:2" ht="15.75">
+    <row r="993" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A993" s="2"/>
       <c r="B993" s="1"/>
     </row>
-    <row r="994" spans="1:2" ht="15.75">
+    <row r="994" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A994" s="2"/>
       <c r="B994" s="1"/>
     </row>
-    <row r="995" spans="1:2" ht="15.75">
+    <row r="995" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A995" s="2"/>
       <c r="B995" s="1"/>
     </row>
-    <row r="996" spans="1:2" ht="15.75">
+    <row r="996" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A996" s="2"/>
       <c r="B996" s="1"/>
     </row>
-    <row r="997" spans="1:2" ht="15.75">
+    <row r="997" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A997" s="2"/>
       <c r="B997" s="1"/>
     </row>
-    <row r="998" spans="1:2" ht="15.75">
+    <row r="998" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A998" s="2"/>
       <c r="B998" s="1"/>
     </row>
-    <row r="999" spans="1:2" ht="15.75">
+    <row r="999" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A999" s="2"/>
       <c r="B999" s="1"/>
     </row>
-    <row r="1000" spans="1:2" ht="15.75">
+    <row r="1000" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1000" s="2"/>
       <c r="B1000" s="1"/>
     </row>
-    <row r="1001" spans="1:2" ht="15.75">
+    <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1001" s="2"/>
       <c r="B1001" s="1"/>
     </row>
-    <row r="1002" spans="1:2" ht="15.75">
+    <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1002" s="2"/>
       <c r="B1002" s="1"/>
     </row>
-    <row r="1003" spans="1:2" ht="15.75">
+    <row r="1003" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1003" s="2"/>
       <c r="B1003" s="1"/>
     </row>
-    <row r="1004" spans="1:2" ht="15.75">
+    <row r="1004" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1004" s="2"/>
       <c r="B1004" s="1"/>
     </row>
-    <row r="1005" spans="1:2" ht="15.75">
+    <row r="1005" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1005" s="2"/>
       <c r="B1005" s="1"/>
     </row>
-    <row r="1006" spans="1:2" ht="15.75">
+    <row r="1006" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1006" s="2"/>
       <c r="B1006" s="1"/>
     </row>
-    <row r="1007" spans="1:2" ht="15.75">
+    <row r="1007" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1007" s="1"/>
       <c r="B1007" s="1"/>
     </row>
-    <row r="1008" spans="1:2" ht="15.75">
+    <row r="1008" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1008" s="1"/>
       <c r="B1008" s="1"/>
     </row>
-    <row r="1009" spans="1:2" ht="15.75">
+    <row r="1009" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1009" s="1"/>
       <c r="B1009" s="1"/>
     </row>
-    <row r="1010" spans="1:2" ht="15.75">
+    <row r="1010" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1010" s="1"/>
       <c r="B1010" s="1"/>
     </row>
-    <row r="1011" spans="1:2" ht="15.75">
+    <row r="1011" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1011" s="1"/>
       <c r="B1011" s="1"/>
     </row>
-    <row r="1012" spans="1:2" ht="15.75">
+    <row r="1012" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1012" s="1"/>
       <c r="B1012" s="1"/>
     </row>
-    <row r="1013" spans="1:2" ht="15.75">
+    <row r="1013" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1013" s="1"/>
       <c r="B1013" s="1"/>
     </row>
-    <row r="1014" spans="1:2" ht="15.75">
+    <row r="1014" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1014" s="1"/>
       <c r="B1014" s="1"/>
     </row>
-    <row r="1015" spans="1:2" ht="15.75">
+    <row r="1015" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1015" s="1"/>
       <c r="B1015" s="1"/>
     </row>
-    <row r="1016" spans="1:2" ht="15.75">
+    <row r="1016" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1016" s="1"/>
       <c r="B1016" s="1"/>
     </row>
-    <row r="1017" spans="1:2" ht="15.75">
+    <row r="1017" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1017" s="1"/>
       <c r="B1017" s="1"/>
     </row>
-    <row r="1018" spans="1:2" ht="15.75">
+    <row r="1018" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1018" s="1"/>
       <c r="B1018" s="1"/>
     </row>
-    <row r="1019" spans="1:2" ht="15.75">
+    <row r="1019" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1019" s="1"/>
       <c r="B1019" s="1"/>
     </row>
-    <row r="1020" spans="1:2" ht="15.75">
+    <row r="1020" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1020" s="1"/>
       <c r="B1020" s="1"/>
     </row>
-    <row r="1021" spans="1:2" ht="15.75">
+    <row r="1021" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1021" s="1"/>
       <c r="B1021" s="1"/>
     </row>
-    <row r="1022" spans="1:2" ht="15.75">
+    <row r="1022" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1022" s="1"/>
       <c r="B1022" s="1"/>
     </row>
-    <row r="1023" spans="1:2" ht="15.75">
+    <row r="1023" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1023" s="1"/>
       <c r="B1023" s="1"/>
     </row>
-    <row r="1024" spans="1:2" ht="15.75">
+    <row r="1024" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1024" s="1"/>
       <c r="B1024" s="1"/>
     </row>
-    <row r="1025" spans="1:2" ht="15.75">
+    <row r="1025" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1025" s="1"/>
       <c r="B1025" s="1"/>
     </row>
-    <row r="1026" spans="1:2" ht="15.75">
+    <row r="1026" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1026" s="1"/>
       <c r="B1026" s="1"/>
     </row>
-    <row r="1027" spans="1:2" ht="15.75">
+    <row r="1027" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1027" s="1"/>
       <c r="B1027" s="1"/>
     </row>
-    <row r="1028" spans="1:2" ht="15.75">
+    <row r="1028" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1028" s="1"/>
       <c r="B1028" s="1"/>
     </row>
-    <row r="1029" spans="1:2" ht="15.75">
+    <row r="1029" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1029" s="1"/>
       <c r="B1029" s="1"/>
     </row>
-    <row r="1030" spans="1:2" ht="15.75">
+    <row r="1030" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1030" s="1"/>
       <c r="B1030" s="1"/>
     </row>
-    <row r="1031" spans="1:2" ht="15.75">
+    <row r="1031" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1031" s="1"/>
       <c r="B1031" s="1"/>
     </row>
-    <row r="1032" spans="1:2" ht="15.75">
+    <row r="1032" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1032" s="1"/>
       <c r="B1032" s="1"/>
     </row>
-    <row r="1033" spans="1:2" ht="15.75">
+    <row r="1033" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1033" s="1"/>
       <c r="B1033" s="1"/>
     </row>
-    <row r="1034" spans="1:2" ht="15.75">
+    <row r="1034" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1034" s="1"/>
       <c r="B1034" s="1"/>
     </row>
-    <row r="1035" spans="1:2" ht="15.75">
+    <row r="1035" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1035" s="1"/>
       <c r="B1035" s="1"/>
     </row>
-    <row r="1036" spans="1:2" ht="15.75">
+    <row r="1036" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1036" s="1"/>
       <c r="B1036" s="1"/>
     </row>
-    <row r="1037" spans="1:2" ht="15.75">
+    <row r="1037" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1037" s="1"/>
       <c r="B1037" s="1"/>
     </row>
-    <row r="1038" spans="1:2" ht="15.75">
+    <row r="1038" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1038" s="1"/>
       <c r="B1038" s="1"/>
     </row>
-    <row r="1039" spans="1:2" ht="15.75">
+    <row r="1039" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1039" s="1"/>
       <c r="B1039" s="1"/>
     </row>
-    <row r="1040" spans="1:2" ht="15.75">
+    <row r="1040" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1040" s="1"/>
       <c r="B1040" s="1"/>
     </row>
-    <row r="1041" spans="1:2" ht="15.75">
+    <row r="1041" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1041" s="1"/>
       <c r="B1041" s="1"/>
     </row>
-    <row r="1042" spans="1:2" ht="15.75">
+    <row r="1042" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1042" s="1"/>
       <c r="B1042" s="1"/>
     </row>
-    <row r="1043" spans="1:2" ht="15.75">
+    <row r="1043" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1043" s="1"/>
       <c r="B1043" s="1"/>
     </row>
-    <row r="1044" spans="1:2" ht="15.75">
+    <row r="1044" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1044" s="1"/>
       <c r="B1044" s="1"/>
     </row>
-    <row r="1045" spans="1:2" ht="15.75">
+    <row r="1045" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1045" s="1"/>
       <c r="B1045" s="1"/>
     </row>
-    <row r="1046" spans="1:2" ht="15.75">
+    <row r="1046" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1046" s="1"/>
       <c r="B1046" s="1"/>
     </row>
-    <row r="1047" spans="1:2" ht="15.75">
+    <row r="1047" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1047" s="1"/>
       <c r="B1047" s="1"/>
     </row>
-    <row r="1048" spans="1:2" ht="15.75">
+    <row r="1048" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1048" s="1"/>
       <c r="B1048" s="1"/>
     </row>
-    <row r="1049" spans="1:2" ht="15.75">
+    <row r="1049" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1049" s="1"/>
       <c r="B1049" s="1"/>
     </row>
-    <row r="1050" spans="1:2" ht="15.75">
+    <row r="1050" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1050" s="1"/>
       <c r="B1050" s="1"/>
     </row>
-    <row r="1051" spans="1:2" ht="15.75">
+    <row r="1051" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1051" s="1"/>
       <c r="B1051" s="1"/>
     </row>
-    <row r="1052" spans="1:2" ht="15.75">
+    <row r="1052" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1052" s="1"/>
       <c r="B1052" s="1"/>
     </row>
-    <row r="1053" spans="1:2" ht="15.75">
+    <row r="1053" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1053" s="1"/>
       <c r="B1053" s="1"/>
     </row>
-    <row r="1054" spans="1:2" ht="15.75">
+    <row r="1054" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1054" s="1"/>
       <c r="B1054" s="1"/>
     </row>
-    <row r="1055" spans="1:2" ht="15.75">
+    <row r="1055" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1055" s="1"/>
       <c r="B1055" s="1"/>
     </row>
-    <row r="1056" spans="1:2" ht="15.75">
+    <row r="1056" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1056" s="1"/>
       <c r="B1056" s="1"/>
     </row>
-    <row r="1057" spans="1:2" ht="15.75">
+    <row r="1057" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1057" s="1"/>
       <c r="B1057" s="1"/>
     </row>
-    <row r="1058" spans="1:2" ht="15.75">
+    <row r="1058" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1058" s="1"/>
       <c r="B1058" s="1"/>
     </row>
-    <row r="1059" spans="1:2" ht="15.75">
+    <row r="1059" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1059" s="1"/>
       <c r="B1059" s="1"/>
     </row>
-    <row r="1060" spans="1:2" ht="15.75">
+    <row r="1060" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1060" s="1"/>
       <c r="B1060" s="1"/>
     </row>
-    <row r="1061" spans="1:2" ht="15.75">
+    <row r="1061" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1061" s="1"/>
       <c r="B1061" s="1"/>
     </row>
-    <row r="1062" spans="1:2" ht="15.75">
+    <row r="1062" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1062" s="1"/>
       <c r="B1062" s="1"/>
     </row>
-    <row r="1063" spans="1:2" ht="15.75">
+    <row r="1063" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1063" s="1"/>
       <c r="B1063" s="1"/>
     </row>
-    <row r="1064" spans="1:2" ht="15.75">
+    <row r="1064" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1064" s="1"/>
       <c r="B1064" s="1"/>
     </row>
-    <row r="1065" spans="1:2" ht="15.75">
+    <row r="1065" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1065" s="1"/>
       <c r="B1065" s="1"/>
     </row>
-    <row r="1066" spans="1:2" ht="15.75">
+    <row r="1066" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1066" s="1"/>
       <c r="B1066" s="1"/>
     </row>
-    <row r="1067" spans="1:2" ht="15.75">
+    <row r="1067" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1067" s="1"/>
       <c r="B1067" s="1"/>
     </row>
-    <row r="1068" spans="1:2" ht="15.75">
+    <row r="1068" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1068" s="1"/>
       <c r="B1068" s="1"/>
     </row>
-    <row r="1069" spans="1:2" ht="15.75">
+    <row r="1069" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1069" s="1"/>
       <c r="B1069" s="1"/>
     </row>
-    <row r="1070" spans="1:2" ht="15.75">
+    <row r="1070" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1070" s="1"/>
       <c r="B1070" s="1"/>
     </row>
-    <row r="1071" spans="1:2" ht="15.75">
+    <row r="1071" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1071" s="1"/>
       <c r="B1071" s="1"/>
     </row>
-    <row r="1072" spans="1:2" ht="15.75">
+    <row r="1072" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1072" s="1"/>
       <c r="B1072" s="1"/>
     </row>
-    <row r="1073" spans="1:2" ht="15.75">
+    <row r="1073" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1073" s="1"/>
       <c r="B1073" s="1"/>
     </row>
-    <row r="1074" spans="1:2" ht="15.75">
+    <row r="1074" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1074" s="1"/>
       <c r="B1074" s="1"/>
     </row>
-    <row r="1075" spans="1:2" ht="15.75">
+    <row r="1075" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1075" s="1"/>
       <c r="B1075" s="1"/>
     </row>
-    <row r="1076" spans="1:2" ht="15.75">
+    <row r="1076" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1076" s="1"/>
       <c r="B1076" s="1"/>
     </row>
-    <row r="1077" spans="1:2" ht="15.75">
+    <row r="1077" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1077" s="1"/>
       <c r="B1077" s="1"/>
     </row>
-    <row r="1078" spans="1:2" ht="15.75">
+    <row r="1078" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1078" s="1"/>
       <c r="B1078" s="1"/>
     </row>
-    <row r="1079" spans="1:2" ht="15.75">
+    <row r="1079" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1079" s="1"/>
       <c r="B1079" s="1"/>
     </row>
-    <row r="1080" spans="1:2" ht="15.75">
+    <row r="1080" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1080" s="1"/>
       <c r="B1080" s="1"/>
     </row>
-    <row r="1081" spans="1:2" ht="15.75">
+    <row r="1081" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1081" s="1"/>
       <c r="B1081" s="1"/>
     </row>
-    <row r="1082" spans="1:2" ht="15.75">
+    <row r="1082" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1082" s="1"/>
       <c r="B1082" s="1"/>
     </row>
-    <row r="1083" spans="1:2" ht="15.75">
+    <row r="1083" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1083" s="1"/>
       <c r="B1083" s="1"/>
     </row>
-    <row r="1084" spans="1:2" ht="15.75">
+    <row r="1084" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1084" s="1"/>
       <c r="B1084" s="1"/>
     </row>
-    <row r="1085" spans="1:2" ht="15.75">
+    <row r="1085" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1085" s="1"/>
       <c r="B1085" s="1"/>
     </row>
-    <row r="1086" spans="1:2" ht="15.75">
+    <row r="1086" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1086" s="1"/>
       <c r="B1086" s="1"/>
     </row>
-    <row r="1087" spans="1:2" ht="15.75">
+    <row r="1087" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1087" s="1"/>
       <c r="B1087" s="1"/>
     </row>
-    <row r="1088" spans="1:2" ht="15.75">
+    <row r="1088" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1088" s="1"/>
       <c r="B1088" s="1"/>
     </row>
-    <row r="1089" spans="1:2" ht="15.75">
+    <row r="1089" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1089" s="1"/>
       <c r="B1089" s="1"/>
     </row>
-    <row r="1090" spans="1:2" ht="15.75">
+    <row r="1090" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1090" s="1"/>
       <c r="B1090" s="1"/>
     </row>
-    <row r="1091" spans="1:2" ht="15.75">
+    <row r="1091" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1091" s="1"/>
       <c r="B1091" s="1"/>
     </row>
-    <row r="1092" spans="1:2" ht="15.75">
+    <row r="1092" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1092" s="1"/>
       <c r="B1092" s="1"/>
     </row>
-    <row r="1093" spans="1:2" ht="15.75">
+    <row r="1093" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1093" s="1"/>
       <c r="B1093" s="1"/>
     </row>
-    <row r="1094" spans="1:2" ht="15.75">
+    <row r="1094" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1094" s="1"/>
       <c r="B1094" s="1"/>
     </row>
-    <row r="1095" spans="1:2" ht="15.75">
+    <row r="1095" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1095" s="1"/>
       <c r="B1095" s="1"/>
     </row>
-    <row r="1096" spans="1:2" ht="15.75">
+    <row r="1096" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1096" s="1"/>
       <c r="B1096" s="1"/>
     </row>
-    <row r="1097" spans="1:2" ht="15.75">
+    <row r="1097" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1097" s="1"/>
       <c r="B1097" s="1"/>
     </row>
-    <row r="1098" spans="1:2" ht="15.75">
+    <row r="1098" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1098" s="1"/>
       <c r="B1098" s="1"/>
     </row>
-    <row r="1099" spans="1:2" ht="15.75">
+    <row r="1099" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1099" s="1"/>
       <c r="B1099" s="1"/>
     </row>
-    <row r="1100" spans="1:2" ht="15.75">
+    <row r="1100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1100" s="1"/>
       <c r="B1100" s="1"/>
     </row>
-    <row r="1101" spans="1:2" ht="15.75">
+    <row r="1101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1101" s="1"/>
       <c r="B1101" s="1"/>
     </row>
-    <row r="1102" spans="1:2" ht="15.75">
+    <row r="1102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1102" s="1"/>
       <c r="B1102" s="1"/>
     </row>
-    <row r="1103" spans="1:2" ht="15.75">
+    <row r="1103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1103" s="1"/>
       <c r="B1103" s="1"/>
     </row>
-    <row r="1104" spans="1:2" ht="15.75">
+    <row r="1104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1104" s="1"/>
       <c r="B1104" s="1"/>
     </row>
-    <row r="1105" spans="1:2" ht="15.75">
+    <row r="1105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1105" s="1"/>
       <c r="B1105" s="1"/>
     </row>
-    <row r="1106" spans="1:2" ht="15.75">
+    <row r="1106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1106" s="1"/>
       <c r="B1106" s="1"/>
     </row>
-    <row r="1107" spans="1:2" ht="15.75">
+    <row r="1107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1107" s="1"/>
       <c r="B1107" s="1"/>
     </row>
-    <row r="1108" spans="1:2" ht="15.75">
+    <row r="1108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1108" s="1"/>
       <c r="B1108" s="1"/>
     </row>
-    <row r="1109" spans="1:2" ht="15.75">
+    <row r="1109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1109" s="1"/>
       <c r="B1109" s="1"/>
     </row>
-    <row r="1110" spans="1:2" ht="15.75">
+    <row r="1110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1110" s="1"/>
       <c r="B1110" s="1"/>
     </row>
-    <row r="1111" spans="1:2" ht="15.75">
+    <row r="1111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1111" s="1"/>
       <c r="B1111" s="1"/>
     </row>
-    <row r="1112" spans="1:2" ht="15.75">
+    <row r="1112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1112" s="1"/>
       <c r="B1112" s="1"/>
     </row>
-    <row r="1113" spans="1:2" ht="15.75">
+    <row r="1113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1113" s="1"/>
       <c r="B1113" s="1"/>
     </row>
-    <row r="1114" spans="1:2" ht="15.75">
+    <row r="1114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1114" s="1"/>
       <c r="B1114" s="1"/>
     </row>
-    <row r="1115" spans="1:2" ht="15.75">
+    <row r="1115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1115" s="1"/>
       <c r="B1115" s="1"/>
     </row>
-    <row r="1116" spans="1:2" ht="15.75">
+    <row r="1116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1116" s="1"/>
       <c r="B1116" s="1"/>
     </row>
-    <row r="1117" spans="1:2" ht="15.75">
+    <row r="1117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1117" s="1"/>
       <c r="B1117" s="1"/>
     </row>
-    <row r="1118" spans="1:2" ht="15.75">
+    <row r="1118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1118" s="1"/>
       <c r="B1118" s="1"/>
     </row>
-    <row r="1119" spans="1:2" ht="15.75">
+    <row r="1119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1119" s="1"/>
       <c r="B1119" s="1"/>
     </row>
-    <row r="1120" spans="1:2" ht="15.75">
+    <row r="1120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1120" s="1"/>
       <c r="B1120" s="1"/>
     </row>
-    <row r="1121" spans="1:2" ht="15.75">
+    <row r="1121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1121" s="1"/>
       <c r="B1121" s="1"/>
     </row>
-    <row r="1122" spans="1:2" ht="15.75">
+    <row r="1122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1122" s="1"/>
       <c r="B1122" s="1"/>
     </row>
-    <row r="1123" spans="1:2" ht="15.75">
+    <row r="1123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1123" s="1"/>
       <c r="B1123" s="1"/>
     </row>
-    <row r="1124" spans="1:2" ht="15.75">
+    <row r="1124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1124" s="1"/>
       <c r="B1124" s="1"/>
     </row>
-    <row r="1125" spans="1:2" ht="15.75">
+    <row r="1125" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1125" s="1"/>
       <c r="B1125" s="1"/>
     </row>
-    <row r="1126" spans="1:2" ht="15.75">
+    <row r="1126" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1126" s="1"/>
       <c r="B1126" s="1"/>
     </row>
-    <row r="1127" spans="1:2" ht="15.75">
+    <row r="1127" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1127" s="1"/>
       <c r="B1127" s="1"/>
     </row>
-    <row r="1128" spans="1:2" ht="15.75">
+    <row r="1128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1128" s="1"/>
       <c r="B1128" s="1"/>
     </row>
-    <row r="1129" spans="1:2" ht="15.75">
+    <row r="1129" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1129" s="1"/>
       <c r="B1129" s="1"/>
     </row>
-    <row r="1130" spans="1:2" ht="15.75">
+    <row r="1130" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1130" s="1"/>
       <c r="B1130" s="1"/>
     </row>
-    <row r="1131" spans="1:2" ht="15.75">
+    <row r="1131" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1131" s="1"/>
       <c r="B1131" s="1"/>
     </row>
-    <row r="1132" spans="1:2" ht="15.75">
+    <row r="1132" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1132" s="1"/>
       <c r="B1132" s="1"/>
     </row>
-    <row r="1133" spans="1:2" ht="15.75">
+    <row r="1133" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1133" s="1"/>
       <c r="B1133" s="1"/>
     </row>
-    <row r="1134" spans="1:2" ht="15.75">
+    <row r="1134" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1134" s="1"/>
       <c r="B1134" s="1"/>
     </row>
-    <row r="1135" spans="1:2" ht="15.75">
+    <row r="1135" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1135" s="1"/>
       <c r="B1135" s="1"/>
     </row>
-    <row r="1136" spans="1:2" ht="15.75">
+    <row r="1136" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1136" s="1"/>
       <c r="B1136" s="1"/>
     </row>
-    <row r="1137" spans="1:2" ht="15.75">
+    <row r="1137" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1137" s="1"/>
       <c r="B1137" s="1"/>
     </row>
-    <row r="1138" spans="1:2" ht="15.75">
+    <row r="1138" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1138" s="1"/>
       <c r="B1138" s="1"/>
     </row>
-    <row r="1139" spans="1:2" ht="15.75">
+    <row r="1139" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1139" s="1"/>
       <c r="B1139" s="1"/>
     </row>
-    <row r="1140" spans="1:2" ht="15.75">
+    <row r="1140" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1140" s="1"/>
       <c r="B1140" s="1"/>
     </row>
-    <row r="1141" spans="1:2" ht="15.75">
+    <row r="1141" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1141" s="1"/>
       <c r="B1141" s="1"/>
     </row>
-    <row r="1142" spans="1:2" ht="15.75">
+    <row r="1142" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1142" s="1"/>
       <c r="B1142" s="1"/>
     </row>
-    <row r="1143" spans="1:2" ht="15.75">
+    <row r="1143" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1143" s="1"/>
       <c r="B1143" s="1"/>
     </row>
-    <row r="1144" spans="1:2" ht="15.75">
+    <row r="1144" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1144" s="1"/>
       <c r="B1144" s="1"/>
     </row>
-    <row r="1145" spans="1:2" ht="15.75">
+    <row r="1145" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1145" s="1"/>
       <c r="B1145" s="1"/>
     </row>
-    <row r="1146" spans="1:2" ht="15.75">
+    <row r="1146" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1146" s="1"/>
       <c r="B1146" s="1"/>
     </row>
-    <row r="1147" spans="1:2" ht="15.75">
+    <row r="1147" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1147" s="1"/>
       <c r="B1147" s="1"/>
     </row>
-    <row r="1148" spans="1:2" ht="15.75">
+    <row r="1148" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1148" s="1"/>
       <c r="B1148" s="1"/>
     </row>
-    <row r="1149" spans="1:2" ht="15.75">
+    <row r="1149" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1149" s="1"/>
       <c r="B1149" s="1"/>
     </row>
-    <row r="1150" spans="1:2" ht="15.75">
+    <row r="1150" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1150" s="1"/>
       <c r="B1150" s="1"/>
     </row>
-    <row r="1151" spans="1:2" ht="15.75">
+    <row r="1151" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1151" s="1"/>
       <c r="B1151" s="1"/>
     </row>
-    <row r="1152" spans="1:2" ht="15.75">
+    <row r="1152" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1152" s="1"/>
       <c r="B1152" s="1"/>
     </row>
-    <row r="1153" spans="1:2" ht="15.75">
+    <row r="1153" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1153" s="1"/>
       <c r="B1153" s="1"/>
     </row>
-    <row r="1154" spans="1:2" ht="15.75">
+    <row r="1154" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1154" s="1"/>
       <c r="B1154" s="1"/>
     </row>
-    <row r="1155" spans="1:2" ht="15.75">
+    <row r="1155" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1155" s="1"/>
       <c r="B1155" s="1"/>
     </row>
-    <row r="1156" spans="1:2" ht="15.75">
+    <row r="1156" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1156" s="1"/>
       <c r="B1156" s="1"/>
     </row>
-    <row r="1157" spans="1:2" ht="15.75">
+    <row r="1157" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1157" s="1"/>
       <c r="B1157" s="1"/>
     </row>
-    <row r="1158" spans="1:2" ht="15.75">
+    <row r="1158" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1158" s="1"/>
       <c r="B1158" s="1"/>
     </row>
-    <row r="1159" spans="1:2" ht="15.75">
+    <row r="1159" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1159" s="1"/>
       <c r="B1159" s="1"/>
     </row>
-    <row r="1160" spans="1:2" ht="15.75">
+    <row r="1160" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1160" s="1"/>
       <c r="B1160" s="1"/>
     </row>
-    <row r="1161" spans="1:2" ht="15.75">
+    <row r="1161" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1161" s="1"/>
       <c r="B1161" s="1"/>
     </row>
-    <row r="1162" spans="1:2" ht="15.75">
+    <row r="1162" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1162" s="1"/>
       <c r="B1162" s="1"/>
     </row>
-    <row r="1163" spans="1:2" ht="15.75">
+    <row r="1163" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1163" s="1"/>
       <c r="B1163" s="1"/>
     </row>
-    <row r="1164" spans="1:2" ht="15.75">
+    <row r="1164" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1164" s="1"/>
       <c r="B1164" s="1"/>
     </row>
-    <row r="1165" spans="1:2" ht="15.75">
+    <row r="1165" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1165" s="1"/>
       <c r="B1165" s="1"/>
     </row>
-    <row r="1166" spans="1:2" ht="15.75">
+    <row r="1166" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1166" s="1"/>
       <c r="B1166" s="1"/>
     </row>
-    <row r="1167" spans="1:2" ht="15.75">
+    <row r="1167" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1167" s="1"/>
       <c r="B1167" s="1"/>
     </row>
-    <row r="1168" spans="1:2" ht="15.75">
+    <row r="1168" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1168" s="1"/>
       <c r="B1168" s="1"/>
     </row>
-    <row r="1169" spans="1:2" ht="15.75">
+    <row r="1169" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1169" s="1"/>
       <c r="B1169" s="1"/>
     </row>
-    <row r="1170" spans="1:2" ht="15.75">
+    <row r="1170" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1170" s="1"/>
       <c r="B1170" s="1"/>
     </row>
-    <row r="1171" spans="1:2" ht="15.75">
+    <row r="1171" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1171" s="1"/>
       <c r="B1171" s="1"/>
     </row>
-    <row r="1172" spans="1:2" ht="15.75">
+    <row r="1172" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1172" s="1"/>
       <c r="B1172" s="1"/>
     </row>
-    <row r="1173" spans="1:2" ht="15.75">
+    <row r="1173" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1173" s="1"/>
       <c r="B1173" s="1"/>
     </row>
-    <row r="1174" spans="1:2" ht="15.75">
+    <row r="1174" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1174" s="1"/>
       <c r="B1174" s="1"/>
     </row>
-    <row r="1175" spans="1:2" ht="15.75">
+    <row r="1175" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1175" s="1"/>
       <c r="B1175" s="1"/>
     </row>
-    <row r="1176" spans="1:2" ht="15.75">
+    <row r="1176" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1176" s="1"/>
       <c r="B1176" s="1"/>
     </row>
-    <row r="1177" spans="1:2" ht="15.75">
+    <row r="1177" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1177" s="1"/>
       <c r="B1177" s="1"/>
     </row>
-    <row r="1178" spans="1:2" ht="15.75">
+    <row r="1178" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1178" s="1"/>
       <c r="B1178" s="1"/>
     </row>
-    <row r="1179" spans="1:2" ht="15.75">
+    <row r="1179" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1179" s="1"/>
       <c r="B1179" s="1"/>
     </row>
-    <row r="1180" spans="1:2" ht="15.75">
+    <row r="1180" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1180" s="1"/>
       <c r="B1180" s="1"/>
     </row>
-    <row r="1181" spans="1:2" ht="15.75">
+    <row r="1181" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1181" s="1"/>
       <c r="B1181" s="1"/>
     </row>
-    <row r="1182" spans="1:2" ht="15.75">
+    <row r="1182" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1182" s="1"/>
       <c r="B1182" s="1"/>
     </row>
-    <row r="1183" spans="1:2" ht="15.75">
+    <row r="1183" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1183" s="1"/>
       <c r="B1183" s="1"/>
     </row>
-    <row r="1184" spans="1:2" ht="15.75">
+    <row r="1184" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1184" s="1"/>
       <c r="B1184" s="1"/>
     </row>
-    <row r="1185" spans="1:2" ht="15.75">
+    <row r="1185" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1185" s="1"/>
       <c r="B1185" s="1"/>
     </row>
-    <row r="1186" spans="1:2" ht="15.75">
+    <row r="1186" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1186" s="1"/>
       <c r="B1186" s="1"/>
     </row>
-    <row r="1187" spans="1:2" ht="15.75">
+    <row r="1187" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1187" s="1"/>
       <c r="B1187" s="1"/>
     </row>
-    <row r="1188" spans="1:2" ht="15.75">
+    <row r="1188" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1188" s="1"/>
       <c r="B1188" s="1"/>
     </row>
-    <row r="1189" spans="1:2" ht="15.75">
+    <row r="1189" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1189" s="1"/>
       <c r="B1189" s="1"/>
     </row>
-    <row r="1190" spans="1:2" ht="15.75">
+    <row r="1190" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1190" s="1"/>
       <c r="B1190" s="1"/>
     </row>
-    <row r="1191" spans="1:2" ht="15.75">
+    <row r="1191" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1191" s="1"/>
       <c r="B1191" s="1"/>
     </row>
-    <row r="1192" spans="1:2" ht="15.75">
+    <row r="1192" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1192" s="1"/>
       <c r="B1192" s="1"/>
     </row>
-    <row r="1193" spans="1:2" ht="15.75">
+    <row r="1193" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1193" s="1"/>
       <c r="B1193" s="1"/>
     </row>
-    <row r="1194" spans="1:2" ht="15.75">
+    <row r="1194" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1194" s="1"/>
       <c r="B1194" s="1"/>
     </row>
-    <row r="1195" spans="1:2" ht="15.75">
+    <row r="1195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1195" s="1"/>
       <c r="B1195" s="1"/>
     </row>
-    <row r="1196" spans="1:2" ht="15.75">
+    <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1196" s="1"/>
       <c r="B1196" s="1"/>
     </row>
-    <row r="1197" spans="1:2" ht="15.75">
+    <row r="1197" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1197" s="1"/>
       <c r="B1197" s="1"/>
     </row>
-    <row r="1198" spans="1:2" ht="15.75">
+    <row r="1198" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1198" s="1"/>
       <c r="B1198" s="1"/>
     </row>
-    <row r="1199" spans="1:2" ht="15.75">
+    <row r="1199" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1199" s="1"/>
       <c r="B1199" s="1"/>
     </row>
-    <row r="1200" spans="1:2" ht="15.75">
+    <row r="1200" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1200" s="1"/>
       <c r="B1200" s="1"/>
     </row>
-    <row r="1201" spans="1:2" ht="15.75">
+    <row r="1201" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1201" s="1"/>
       <c r="B1201" s="1"/>
     </row>
@@ -10434,38 +10437,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA90CD46-FF53-412A-950C-99718992C948}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>382</v>
       </c>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65A379C1-DE73-44DA-BB93-F99BAFA2EA41}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01600FC2-4373-4F70-B964-0CD57C2C9BCA}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="507">
   <si>
     <t>material</t>
   </si>
@@ -294,6 +294,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(NÃO LANÇAR P/ ROTA)</t>
@@ -1570,6 +1571,9 @@
   </si>
   <si>
     <t>TINTA SPRAY AZU 250GR</t>
+  </si>
+  <si>
+    <t>CABO P/RASTR RASTR AUTOTRAC/2730</t>
   </si>
 </sst>
 </file>
@@ -1589,17 +1593,20 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1607,12 +1614,14 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF242424"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1760,7 +1769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1843,6 +1852,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2123,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1201"/>
+  <dimension ref="A1:D1202"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -6355,7 +6365,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="15">
         <v>1010053692</v>
       </c>
@@ -6366,7 +6376,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="15">
         <v>1010083992</v>
       </c>
@@ -6377,7 +6387,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="15">
         <v>1010008578</v>
       </c>
@@ -6388,7 +6398,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="15">
         <v>1010031694</v>
       </c>
@@ -6399,7 +6409,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="15">
         <v>1010051997</v>
       </c>
@@ -6410,7 +6420,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="15">
         <v>1010022601</v>
       </c>
@@ -6421,7 +6431,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="15">
         <v>1010054278</v>
       </c>
@@ -6432,7 +6442,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="15">
         <v>1010083462</v>
       </c>
@@ -6443,7 +6453,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="15">
         <v>1010027772</v>
       </c>
@@ -6454,7 +6464,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="15">
         <v>1010084144</v>
       </c>
@@ -6465,7 +6475,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="19">
         <v>214055</v>
       </c>
@@ -6475,57 +6485,58 @@
       <c r="C395" s="4" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A396" s="18">
-        <v>1010021956</v>
+      <c r="D395" s="30"/>
+    </row>
+    <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A396" s="19">
+        <v>1010084720</v>
       </c>
       <c r="B396" s="7" t="s">
-        <v>400</v>
+        <v>506</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="18">
-        <v>1010026464</v>
+        <v>1010021956</v>
       </c>
       <c r="B397" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A398" s="14">
-        <v>1010021957</v>
-      </c>
-      <c r="B398" s="5" t="s">
-        <v>402</v>
+    <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A398" s="18">
+        <v>1010026464</v>
+      </c>
+      <c r="B398" s="7" t="s">
+        <v>401</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A399" s="15">
-        <v>1010026462</v>
+    <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A399" s="14">
+        <v>1010021957</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="15">
-        <v>1010026551</v>
+        <v>1010026462</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>391</v>
@@ -6533,10 +6544,10 @@
     </row>
     <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="15">
-        <v>1010042554</v>
+        <v>1010026551</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>391</v>
@@ -6544,10 +6555,10 @@
     </row>
     <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="15">
-        <v>1010039904</v>
+        <v>1010042554</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>391</v>
@@ -6555,10 +6566,10 @@
     </row>
     <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="15">
-        <v>1010060205</v>
+        <v>1010039904</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>391</v>
@@ -6566,10 +6577,10 @@
     </row>
     <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="15">
-        <v>1010060206</v>
+        <v>1010060205</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>391</v>
@@ -6577,10 +6588,10 @@
     </row>
     <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="15">
-        <v>1010077431</v>
+        <v>1010060206</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>391</v>
@@ -6588,10 +6599,10 @@
     </row>
     <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="15">
-        <v>1010077503</v>
+        <v>1010077431</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>391</v>
@@ -6599,10 +6610,10 @@
     </row>
     <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="15">
-        <v>1010084187</v>
+        <v>1010077503</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>391</v>
@@ -6610,10 +6621,10 @@
     </row>
     <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="15">
-        <v>1010080958</v>
+        <v>1010084187</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C408" s="4" t="s">
         <v>391</v>
@@ -6621,10 +6632,10 @@
     </row>
     <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="15">
-        <v>1010026032</v>
+        <v>1010080958</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C409" s="4" t="s">
         <v>391</v>
@@ -6632,10 +6643,10 @@
     </row>
     <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="15">
-        <v>1010085384</v>
+        <v>1010026032</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>391</v>
@@ -6643,10 +6654,10 @@
     </row>
     <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="15">
-        <v>1010006347</v>
+        <v>1010085384</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C411" s="4" t="s">
         <v>391</v>
@@ -6654,10 +6665,10 @@
     </row>
     <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="15">
-        <v>1010085179</v>
+        <v>1010006347</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C412" s="4" t="s">
         <v>391</v>
@@ -6665,10 +6676,10 @@
     </row>
     <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="15">
-        <v>1010024158</v>
-      </c>
-      <c r="B413" s="8" t="s">
-        <v>417</v>
+        <v>1010085179</v>
+      </c>
+      <c r="B413" s="5" t="s">
+        <v>416</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>391</v>
@@ -6676,10 +6687,10 @@
     </row>
     <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="15">
-        <v>1010024131</v>
+        <v>1010024158</v>
       </c>
       <c r="B414" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>391</v>
@@ -6687,10 +6698,10 @@
     </row>
     <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="15">
-        <v>1010007160</v>
-      </c>
-      <c r="B415" s="5" t="s">
-        <v>419</v>
+        <v>1010024131</v>
+      </c>
+      <c r="B415" s="8" t="s">
+        <v>418</v>
       </c>
       <c r="C415" s="4" t="s">
         <v>391</v>
@@ -6698,10 +6709,10 @@
     </row>
     <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="15">
-        <v>1010023642</v>
+        <v>1010007160</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>391</v>
@@ -6709,10 +6720,10 @@
     </row>
     <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="15">
-        <v>1010007193</v>
-      </c>
-      <c r="B417" s="6" t="s">
-        <v>421</v>
+        <v>1010023642</v>
+      </c>
+      <c r="B417" s="5" t="s">
+        <v>420</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>391</v>
@@ -6720,10 +6731,10 @@
     </row>
     <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="15">
-        <v>1010042637</v>
-      </c>
-      <c r="B418" s="5" t="s">
-        <v>422</v>
+        <v>1010007193</v>
+      </c>
+      <c r="B418" s="6" t="s">
+        <v>421</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>391</v>
@@ -6731,10 +6742,10 @@
     </row>
     <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="15">
-        <v>1040075323</v>
+        <v>1010042637</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>391</v>
@@ -6742,21 +6753,21 @@
     </row>
     <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="15">
-        <v>1040075324</v>
-      </c>
-      <c r="B420" s="8" t="s">
-        <v>424</v>
+        <v>1040075323</v>
+      </c>
+      <c r="B420" s="5" t="s">
+        <v>423</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A421" s="27">
-        <v>1040074827</v>
+      <c r="A421" s="15">
+        <v>1040075324</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>391</v>
@@ -6764,10 +6775,10 @@
     </row>
     <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="27">
-        <v>1040099488</v>
+        <v>1040074827</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>391</v>
@@ -6775,10 +6786,10 @@
     </row>
     <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="27">
-        <v>1040083312</v>
+        <v>1040099488</v>
       </c>
       <c r="B423" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>391</v>
@@ -6786,10 +6797,10 @@
     </row>
     <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="27">
-        <v>1040077661</v>
+        <v>1040083312</v>
       </c>
       <c r="B424" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>391</v>
@@ -6797,21 +6808,21 @@
     </row>
     <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="27">
-        <v>1010085180</v>
-      </c>
-      <c r="B425" s="12" t="s">
-        <v>429</v>
+        <v>1040077661</v>
+      </c>
+      <c r="B425" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A426" s="14">
-        <v>1040017489</v>
-      </c>
-      <c r="B426" s="9" t="s">
-        <v>430</v>
+      <c r="A426" s="27">
+        <v>1010085180</v>
+      </c>
+      <c r="B426" s="12" t="s">
+        <v>429</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>391</v>
@@ -6819,21 +6830,21 @@
     </row>
     <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="14">
-        <v>1010085181</v>
-      </c>
-      <c r="B427" s="5" t="s">
-        <v>431</v>
+        <v>1040017489</v>
+      </c>
+      <c r="B427" s="9" t="s">
+        <v>430</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A428" s="15">
-        <v>400175</v>
+      <c r="A428" s="14">
+        <v>1010085181</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>391</v>
@@ -6841,10 +6852,10 @@
     </row>
     <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="15">
-        <v>1040017505</v>
+        <v>400175</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>391</v>
@@ -6852,10 +6863,10 @@
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="15">
-        <v>1040017503</v>
+        <v>1040017505</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>391</v>
@@ -6863,10 +6874,10 @@
     </row>
     <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="15">
-        <v>1010046445</v>
+        <v>1040017503</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>391</v>
@@ -6874,10 +6885,10 @@
     </row>
     <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="15">
-        <v>1010021033</v>
+        <v>1010046445</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C432" s="4" t="s">
         <v>391</v>
@@ -6885,10 +6896,10 @@
     </row>
     <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="15">
-        <v>1010057142</v>
+        <v>1010021033</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>391</v>
@@ -6896,10 +6907,10 @@
     </row>
     <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="15">
-        <v>1010016356</v>
+        <v>1010057142</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>391</v>
@@ -6907,10 +6918,10 @@
     </row>
     <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="15">
-        <v>1010084363</v>
+        <v>1010016356</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>391</v>
@@ -6918,10 +6929,10 @@
     </row>
     <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="15">
-        <v>1010052021</v>
+        <v>1010084363</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>391</v>
@@ -6929,10 +6940,10 @@
     </row>
     <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="15">
-        <v>1040091721</v>
+        <v>1010052021</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C437" s="4" t="s">
         <v>391</v>
@@ -6940,10 +6951,10 @@
     </row>
     <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="15">
-        <v>1010062022</v>
+        <v>1040091721</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>391</v>
@@ -6951,10 +6962,10 @@
     </row>
     <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="15">
-        <v>18336</v>
+        <v>1010062022</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>391</v>
@@ -6962,10 +6973,10 @@
     </row>
     <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="15">
-        <v>229205</v>
+        <v>18336</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>391</v>
@@ -6973,10 +6984,10 @@
     </row>
     <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="15">
-        <v>60671</v>
+        <v>229205</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>391</v>
@@ -6984,10 +6995,10 @@
     </row>
     <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="15">
-        <v>1010059726</v>
+        <v>60671</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>391</v>
@@ -6995,10 +7006,10 @@
     </row>
     <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="15">
-        <v>1010008144</v>
+        <v>1010059726</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>391</v>
@@ -7006,10 +7017,10 @@
     </row>
     <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="15">
-        <v>1010007244</v>
+        <v>1010008144</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C444" s="4" t="s">
         <v>391</v>
@@ -7017,10 +7028,10 @@
     </row>
     <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="15">
-        <v>1010006827</v>
+        <v>1010007244</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>391</v>
@@ -7028,10 +7039,10 @@
     </row>
     <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="15">
-        <v>1040075426</v>
+        <v>1010006827</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>391</v>
@@ -7039,10 +7050,10 @@
     </row>
     <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="15">
-        <v>1040075427</v>
+        <v>1040075426</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C447" s="4" t="s">
         <v>391</v>
@@ -7050,10 +7061,10 @@
     </row>
     <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="15">
-        <v>1010084313</v>
+        <v>1040075427</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C448" s="4" t="s">
         <v>391</v>
@@ -7061,10 +7072,10 @@
     </row>
     <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="15">
-        <v>403459</v>
+        <v>1010084313</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>391</v>
@@ -7072,10 +7083,10 @@
     </row>
     <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="15">
-        <v>1010044828</v>
+        <v>403459</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>391</v>
@@ -7083,10 +7094,10 @@
     </row>
     <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="15">
-        <v>1010026973</v>
+        <v>1010044828</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>391</v>
@@ -7094,32 +7105,32 @@
     </row>
     <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="15">
-        <v>1040017204</v>
+        <v>1010026973</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A453" s="24">
+      <c r="A453" s="15">
+        <v>1040017204</v>
+      </c>
+      <c r="B453" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C453" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A454" s="24">
         <v>1010022119</v>
       </c>
-      <c r="B453" s="6" t="s">
+      <c r="B454" s="6" t="s">
         <v>457</v>
-      </c>
-      <c r="C453" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="15">
-        <v>1010058709</v>
-      </c>
-      <c r="B454" s="5" t="s">
-        <v>459</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>458</v>
@@ -7127,10 +7138,10 @@
     </row>
     <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="15">
-        <v>1010025711</v>
+        <v>1010058709</v>
       </c>
       <c r="B455" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>458</v>
@@ -7138,10 +7149,10 @@
     </row>
     <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" s="15">
-        <v>1010059684</v>
+        <v>1010025711</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>458</v>
@@ -7149,10 +7160,10 @@
     </row>
     <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="15">
-        <v>427341</v>
+        <v>1010059684</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>458</v>
@@ -7160,43 +7171,43 @@
     </row>
     <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" s="15">
-        <v>1010085279</v>
+        <v>427341</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A459" s="19">
-        <v>1010022588</v>
+      <c r="A459" s="15">
+        <v>1010085279</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="15">
-        <v>1010026864</v>
-      </c>
-      <c r="B460" s="7" t="s">
-        <v>465</v>
+      <c r="A460" s="19">
+        <v>1010022588</v>
+      </c>
+      <c r="B460" s="5" t="s">
+        <v>464</v>
       </c>
       <c r="C460" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="14">
-        <v>1010030946</v>
+      <c r="A461" s="15">
+        <v>1010026864</v>
       </c>
       <c r="B461" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C461" s="4" t="s">
         <v>458</v>
@@ -7204,21 +7215,21 @@
     </row>
     <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="14">
-        <v>1010022589</v>
-      </c>
-      <c r="B462" s="5" t="s">
-        <v>467</v>
+        <v>1010030946</v>
+      </c>
+      <c r="B462" s="7" t="s">
+        <v>466</v>
       </c>
       <c r="C462" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A463" s="15">
-        <v>1040090143</v>
+      <c r="A463" s="14">
+        <v>1010022589</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C463" s="4" t="s">
         <v>458</v>
@@ -7226,10 +7237,10 @@
     </row>
     <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="15">
-        <v>1040090138</v>
+        <v>1040090143</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C464" s="4" t="s">
         <v>458</v>
@@ -7237,10 +7248,10 @@
     </row>
     <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="15">
-        <v>1030001314</v>
+        <v>1040090138</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C465" s="4" t="s">
         <v>458</v>
@@ -7248,10 +7259,10 @@
     </row>
     <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="15">
-        <v>1010052319</v>
+        <v>1030001314</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C466" s="4" t="s">
         <v>458</v>
@@ -7259,10 +7270,10 @@
     </row>
     <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" s="15">
-        <v>1010052320</v>
+        <v>1010052319</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C467" s="4" t="s">
         <v>458</v>
@@ -7270,10 +7281,10 @@
     </row>
     <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="15">
-        <v>1030000370</v>
+        <v>1010052320</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C468" s="4" t="s">
         <v>458</v>
@@ -7281,10 +7292,10 @@
     </row>
     <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="15">
-        <v>1030000366</v>
+        <v>1030000370</v>
       </c>
       <c r="B469" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C469" s="4" t="s">
         <v>458</v>
@@ -7292,10 +7303,10 @@
     </row>
     <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="15">
-        <v>1030000368</v>
+        <v>1030000366</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C470" s="4" t="s">
         <v>458</v>
@@ -7303,10 +7314,10 @@
     </row>
     <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="15">
-        <v>1030000369</v>
+        <v>1030000368</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C471" s="4" t="s">
         <v>458</v>
@@ -7314,10 +7325,10 @@
     </row>
     <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="15">
-        <v>1030000489</v>
+        <v>1030000369</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>458</v>
@@ -7325,10 +7336,10 @@
     </row>
     <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="15">
-        <v>1030000490</v>
+        <v>1030000489</v>
       </c>
       <c r="B473" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C473" s="4" t="s">
         <v>458</v>
@@ -7336,10 +7347,10 @@
     </row>
     <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="15">
-        <v>1030000821</v>
+        <v>1030000490</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C474" s="4" t="s">
         <v>458</v>
@@ -7347,21 +7358,21 @@
     </row>
     <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="15">
-        <v>1030000511</v>
-      </c>
-      <c r="B475" s="8" t="s">
-        <v>480</v>
+        <v>1030000821</v>
+      </c>
+      <c r="B475" s="5" t="s">
+        <v>479</v>
       </c>
       <c r="C475" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A476" s="16">
-        <v>1010084279</v>
+      <c r="A476" s="15">
+        <v>1030000511</v>
       </c>
       <c r="B476" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C476" s="4" t="s">
         <v>458</v>
@@ -7369,21 +7380,21 @@
     </row>
     <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="16">
-        <v>1010004281</v>
-      </c>
-      <c r="B477" s="5" t="s">
-        <v>482</v>
+        <v>1010084279</v>
+      </c>
+      <c r="B477" s="8" t="s">
+        <v>481</v>
       </c>
       <c r="C477" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="15">
-        <v>1010022118</v>
-      </c>
-      <c r="B478" s="9" t="s">
-        <v>483</v>
+      <c r="A478" s="16">
+        <v>1010004281</v>
+      </c>
+      <c r="B478" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="C478" s="4" t="s">
         <v>458</v>
@@ -7391,21 +7402,21 @@
     </row>
     <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" s="15">
+        <v>1010022118</v>
+      </c>
+      <c r="B479" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C479" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A480" s="15">
         <v>1010028657</v>
       </c>
-      <c r="B479" s="5" t="s">
+      <c r="B480" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="C479" s="4" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="18">
-        <v>1010028655</v>
-      </c>
-      <c r="B480" s="5" t="s">
-        <v>486</v>
       </c>
       <c r="C480" s="4" t="s">
         <v>485</v>
@@ -7413,43 +7424,43 @@
     </row>
     <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="18">
-        <v>145165</v>
+        <v>1010028655</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C481" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="15">
-        <v>51666</v>
+      <c r="A482" s="18">
+        <v>145165</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="18">
-        <v>1010080930</v>
+      <c r="A483" s="15">
+        <v>51666</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="15">
-        <v>161055</v>
+      <c r="A484" s="18">
+        <v>1010080930</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C484" s="4" t="s">
         <v>485</v>
@@ -7457,10 +7468,10 @@
     </row>
     <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="15">
-        <v>1010050517</v>
+        <v>161055</v>
       </c>
       <c r="B485" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>485</v>
@@ -7468,10 +7479,10 @@
     </row>
     <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="15">
-        <v>1010084190</v>
+        <v>1010050517</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>485</v>
@@ -7479,10 +7490,10 @@
     </row>
     <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="15">
-        <v>1010084195</v>
+        <v>1010084190</v>
       </c>
       <c r="B487" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>485</v>
@@ -7490,32 +7501,32 @@
     </row>
     <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="15">
-        <v>1010001400</v>
+        <v>1010084195</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A489" s="17">
-        <v>1010008416</v>
+      <c r="A489" s="15">
+        <v>1010001400</v>
       </c>
       <c r="B489" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C489" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A490" s="28">
-        <v>1010018372</v>
+      <c r="A490" s="17">
+        <v>1010008416</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C490" s="4" t="s">
         <v>485</v>
@@ -7523,32 +7534,32 @@
     </row>
     <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="28">
-        <v>1010018361</v>
-      </c>
-      <c r="B491" s="8" t="s">
-        <v>497</v>
+        <v>1010018372</v>
+      </c>
+      <c r="B491" s="5" t="s">
+        <v>496</v>
       </c>
       <c r="C491" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A492" s="16">
-        <v>1010055398</v>
-      </c>
-      <c r="B492" s="11" t="s">
-        <v>498</v>
+      <c r="A492" s="28">
+        <v>1010018361</v>
+      </c>
+      <c r="B492" s="8" t="s">
+        <v>497</v>
       </c>
       <c r="C492" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A493" s="15">
-        <v>422131</v>
-      </c>
-      <c r="B493" s="5" t="s">
-        <v>499</v>
+      <c r="A493" s="16">
+        <v>1010055398</v>
+      </c>
+      <c r="B493" s="11" t="s">
+        <v>498</v>
       </c>
       <c r="C493" s="4" t="s">
         <v>485</v>
@@ -7556,10 +7567,10 @@
     </row>
     <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="15">
-        <v>1010084370</v>
+        <v>422131</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C494" s="4" t="s">
         <v>485</v>
@@ -7567,10 +7578,10 @@
     </row>
     <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="15">
-        <v>422759</v>
+        <v>1010084370</v>
       </c>
       <c r="B495" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C495" s="4" t="s">
         <v>485</v>
@@ -7578,10 +7589,10 @@
     </row>
     <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" s="15">
-        <v>120955</v>
+        <v>422759</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C496" s="4" t="s">
         <v>485</v>
@@ -7589,21 +7600,21 @@
     </row>
     <row r="497" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" s="15">
-        <v>1010000896</v>
+        <v>120955</v>
       </c>
       <c r="B497" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="C497" s="13" t="s">
+        <v>502</v>
+      </c>
+      <c r="C497" s="4" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" s="15">
-        <v>1010084308</v>
+        <v>1010000896</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C498" s="13" t="s">
         <v>485</v>
@@ -7611,18 +7622,25 @@
     </row>
     <row r="499" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="15">
-        <v>1010084035</v>
+        <v>1010084308</v>
       </c>
       <c r="B499" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C499" s="13" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A500" s="2"/>
-      <c r="B500" s="2"/>
+      <c r="A500" s="15">
+        <v>1010084035</v>
+      </c>
+      <c r="B500" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="C500" s="13" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="501" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="2"/>
@@ -9378,7 +9396,7 @@
     </row>
     <row r="939" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A939" s="2"/>
-      <c r="B939" s="1"/>
+      <c r="B939" s="2"/>
     </row>
     <row r="940" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A940" s="2"/>
@@ -9649,7 +9667,7 @@
       <c r="B1006" s="1"/>
     </row>
     <row r="1007" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1007" s="1"/>
+      <c r="A1007" s="2"/>
       <c r="B1007" s="1"/>
     </row>
     <row r="1008" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -10427,6 +10445,10 @@
     <row r="1201" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1201" s="1"/>
       <c r="B1201" s="1"/>
+    </row>
+    <row r="1202" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1202" s="1"/>
+      <c r="B1202" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0B293A8-E3E5-4369-9A74-9A9CAA240ABB}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A68652A-162A-420A-971C-063CCEDB524B}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="511">
   <si>
     <t>material</t>
   </si>
@@ -1079,6 +1079,12 @@
   </si>
   <si>
     <t>TAMPA PROTETOR CICLISTA LIBRELATO</t>
+  </si>
+  <si>
+    <t>TERMINAL HIDRAULICO MANG 3/4 FEMEA</t>
+  </si>
+  <si>
+    <t>TERMINAL HIDRAULICO MANG 3/4 MACHO</t>
   </si>
   <si>
     <t>TECLADO AUTOTRAC</t>
@@ -1659,7 +1665,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1771,6 +1777,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1855,10 +1874,10 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2139,7 +2158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1204"/>
+  <dimension ref="A1:D1206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -5570,7 +5589,7 @@
     </row>
     <row r="312" spans="1:3" ht="15.75">
       <c r="A312" s="15">
-        <v>1040024314</v>
+        <v>1010087245</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>314</v>
@@ -5866,7 +5885,7 @@
       </c>
     </row>
     <row r="339" spans="1:3" ht="15.75">
-      <c r="A339" s="15">
+      <c r="A339" s="19">
         <v>1040040960</v>
       </c>
       <c r="B339" s="5" t="s">
@@ -5877,10 +5896,10 @@
       </c>
     </row>
     <row r="340" spans="1:3" ht="15.75">
-      <c r="A340" s="29">
-        <v>1010084767</v>
-      </c>
-      <c r="B340" s="5" t="s">
+      <c r="A340" s="15">
+        <v>1010031536</v>
+      </c>
+      <c r="B340" s="7" t="s">
         <v>342</v>
       </c>
       <c r="C340" s="4" t="s">
@@ -5889,9 +5908,9 @@
     </row>
     <row r="341" spans="1:3" ht="15.75">
       <c r="A341" s="15">
-        <v>1040077360</v>
-      </c>
-      <c r="B341" s="5" t="s">
+        <v>1010031545</v>
+      </c>
+      <c r="B341" s="7" t="s">
         <v>343</v>
       </c>
       <c r="C341" s="4" t="s">
@@ -5899,8 +5918,8 @@
       </c>
     </row>
     <row r="342" spans="1:3" ht="15.75">
-      <c r="A342" s="15">
-        <v>1010064470</v>
+      <c r="A342" s="30">
+        <v>1010084767</v>
       </c>
       <c r="B342" s="5" t="s">
         <v>344</v>
@@ -5911,7 +5930,7 @@
     </row>
     <row r="343" spans="1:3" ht="15.75">
       <c r="A343" s="15">
-        <v>1010021991</v>
+        <v>1040077360</v>
       </c>
       <c r="B343" s="5" t="s">
         <v>345</v>
@@ -5922,7 +5941,7 @@
     </row>
     <row r="344" spans="1:3" ht="15.75">
       <c r="A344" s="15">
-        <v>1010021960</v>
+        <v>1010064470</v>
       </c>
       <c r="B344" s="5" t="s">
         <v>346</v>
@@ -5933,7 +5952,7 @@
     </row>
     <row r="345" spans="1:3" ht="15.75">
       <c r="A345" s="15">
-        <v>1010031545</v>
+        <v>1010021991</v>
       </c>
       <c r="B345" s="5" t="s">
         <v>347</v>
@@ -5944,7 +5963,7 @@
     </row>
     <row r="346" spans="1:3" ht="15.75">
       <c r="A346" s="15">
-        <v>1010031690</v>
+        <v>1010021960</v>
       </c>
       <c r="B346" s="5" t="s">
         <v>348</v>
@@ -5955,7 +5974,7 @@
     </row>
     <row r="347" spans="1:3" ht="15.75">
       <c r="A347" s="15">
-        <v>1010022590</v>
+        <v>1010031545</v>
       </c>
       <c r="B347" s="5" t="s">
         <v>349</v>
@@ -5966,7 +5985,7 @@
     </row>
     <row r="348" spans="1:3" ht="15.75">
       <c r="A348" s="15">
-        <v>1040098643</v>
+        <v>1010031690</v>
       </c>
       <c r="B348" s="5" t="s">
         <v>350</v>
@@ -5977,7 +5996,7 @@
     </row>
     <row r="349" spans="1:3" ht="15.75">
       <c r="A349" s="15">
-        <v>1010086020</v>
+        <v>1010022590</v>
       </c>
       <c r="B349" s="5" t="s">
         <v>351</v>
@@ -5988,7 +6007,7 @@
     </row>
     <row r="350" spans="1:3" ht="15.75">
       <c r="A350" s="15">
-        <v>1010046550</v>
+        <v>1040098643</v>
       </c>
       <c r="B350" s="5" t="s">
         <v>352</v>
@@ -5999,7 +6018,7 @@
     </row>
     <row r="351" spans="1:3" ht="15.75">
       <c r="A351" s="15">
-        <v>1010046402</v>
+        <v>1010086020</v>
       </c>
       <c r="B351" s="5" t="s">
         <v>353</v>
@@ -6010,7 +6029,7 @@
     </row>
     <row r="352" spans="1:3" ht="15.75">
       <c r="A352" s="15">
-        <v>1010060291</v>
+        <v>1010046550</v>
       </c>
       <c r="B352" s="5" t="s">
         <v>354</v>
@@ -6021,7 +6040,7 @@
     </row>
     <row r="353" spans="1:3" ht="15.75">
       <c r="A353" s="15">
-        <v>1010050920</v>
+        <v>1010046402</v>
       </c>
       <c r="B353" s="5" t="s">
         <v>355</v>
@@ -6032,7 +6051,7 @@
     </row>
     <row r="354" spans="1:3" ht="15.75">
       <c r="A354" s="15">
-        <v>1040077412</v>
+        <v>1010060291</v>
       </c>
       <c r="B354" s="5" t="s">
         <v>356</v>
@@ -6043,7 +6062,7 @@
     </row>
     <row r="355" spans="1:3" ht="15.75">
       <c r="A355" s="15">
-        <v>1010042609</v>
+        <v>1010050920</v>
       </c>
       <c r="B355" s="5" t="s">
         <v>357</v>
@@ -6054,7 +6073,7 @@
     </row>
     <row r="356" spans="1:3" ht="15.75">
       <c r="A356" s="15">
-        <v>417701</v>
+        <v>1040077412</v>
       </c>
       <c r="B356" s="5" t="s">
         <v>358</v>
@@ -6065,7 +6084,7 @@
     </row>
     <row r="357" spans="1:3" ht="15.75">
       <c r="A357" s="15">
-        <v>399384</v>
+        <v>1010042609</v>
       </c>
       <c r="B357" s="5" t="s">
         <v>359</v>
@@ -6076,7 +6095,7 @@
     </row>
     <row r="358" spans="1:3" ht="15.75">
       <c r="A358" s="15">
-        <v>1010024086</v>
+        <v>417701</v>
       </c>
       <c r="B358" s="5" t="s">
         <v>360</v>
@@ -6087,7 +6106,7 @@
     </row>
     <row r="359" spans="1:3" ht="15.75">
       <c r="A359" s="15">
-        <v>1040077345</v>
+        <v>399384</v>
       </c>
       <c r="B359" s="5" t="s">
         <v>361</v>
@@ -6098,7 +6117,7 @@
     </row>
     <row r="360" spans="1:3" ht="15.75">
       <c r="A360" s="15">
-        <v>1010084315</v>
+        <v>1010024086</v>
       </c>
       <c r="B360" s="5" t="s">
         <v>362</v>
@@ -6109,7 +6128,7 @@
     </row>
     <row r="361" spans="1:3" ht="15.75">
       <c r="A361" s="15">
-        <v>399253</v>
+        <v>1040077345</v>
       </c>
       <c r="B361" s="5" t="s">
         <v>363</v>
@@ -6120,7 +6139,7 @@
     </row>
     <row r="362" spans="1:3" ht="15.75">
       <c r="A362" s="15">
-        <v>1010084317</v>
+        <v>1010084315</v>
       </c>
       <c r="B362" s="5" t="s">
         <v>364</v>
@@ -6130,8 +6149,8 @@
       </c>
     </row>
     <row r="363" spans="1:3" ht="15.75">
-      <c r="A363" s="25">
-        <v>1010085369</v>
+      <c r="A363" s="15">
+        <v>399253</v>
       </c>
       <c r="B363" s="5" t="s">
         <v>365</v>
@@ -6142,7 +6161,7 @@
     </row>
     <row r="364" spans="1:3" ht="15.75">
       <c r="A364" s="15">
-        <v>1010085370</v>
+        <v>1010084317</v>
       </c>
       <c r="B364" s="5" t="s">
         <v>366</v>
@@ -6152,8 +6171,8 @@
       </c>
     </row>
     <row r="365" spans="1:3" ht="15.75">
-      <c r="A365" s="15">
-        <v>1010085204</v>
+      <c r="A365" s="25">
+        <v>1010085369</v>
       </c>
       <c r="B365" s="5" t="s">
         <v>367</v>
@@ -6164,7 +6183,7 @@
     </row>
     <row r="366" spans="1:3" ht="15.75">
       <c r="A366" s="15">
-        <v>1010003966</v>
+        <v>1010085370</v>
       </c>
       <c r="B366" s="5" t="s">
         <v>368</v>
@@ -6175,7 +6194,7 @@
     </row>
     <row r="367" spans="1:3" ht="15.75">
       <c r="A367" s="15">
-        <v>1010003967</v>
+        <v>1010085204</v>
       </c>
       <c r="B367" s="5" t="s">
         <v>369</v>
@@ -6186,7 +6205,7 @@
     </row>
     <row r="368" spans="1:3" ht="15.75">
       <c r="A368" s="15">
-        <v>65219</v>
+        <v>1010003966</v>
       </c>
       <c r="B368" s="5" t="s">
         <v>370</v>
@@ -6197,7 +6216,7 @@
     </row>
     <row r="369" spans="1:3" ht="15.75">
       <c r="A369" s="15">
-        <v>10168</v>
+        <v>1010003967</v>
       </c>
       <c r="B369" s="5" t="s">
         <v>371</v>
@@ -6208,7 +6227,7 @@
     </row>
     <row r="370" spans="1:3" ht="15.75">
       <c r="A370" s="15">
-        <v>1010083792</v>
+        <v>65219</v>
       </c>
       <c r="B370" s="5" t="s">
         <v>372</v>
@@ -6219,7 +6238,7 @@
     </row>
     <row r="371" spans="1:3" ht="15.75">
       <c r="A371" s="15">
-        <v>1040077414</v>
+        <v>10168</v>
       </c>
       <c r="B371" s="5" t="s">
         <v>373</v>
@@ -6230,7 +6249,7 @@
     </row>
     <row r="372" spans="1:3" ht="15.75">
       <c r="A372" s="15">
-        <v>1010018482</v>
+        <v>1010083792</v>
       </c>
       <c r="B372" s="5" t="s">
         <v>374</v>
@@ -6241,7 +6260,7 @@
     </row>
     <row r="373" spans="1:3" ht="15.75">
       <c r="A373" s="15">
-        <v>1010084320</v>
+        <v>1040077414</v>
       </c>
       <c r="B373" s="5" t="s">
         <v>375</v>
@@ -6252,7 +6271,7 @@
     </row>
     <row r="374" spans="1:3" ht="15.75">
       <c r="A374" s="15">
-        <v>1010084532</v>
+        <v>1010018482</v>
       </c>
       <c r="B374" s="5" t="s">
         <v>376</v>
@@ -6263,7 +6282,7 @@
     </row>
     <row r="375" spans="1:3" ht="15.75">
       <c r="A375" s="15">
-        <v>1010027285</v>
+        <v>1010084320</v>
       </c>
       <c r="B375" s="5" t="s">
         <v>377</v>
@@ -6274,7 +6293,7 @@
     </row>
     <row r="376" spans="1:3" ht="15.75">
       <c r="A376" s="15">
-        <v>1040077413</v>
+        <v>1010084532</v>
       </c>
       <c r="B376" s="5" t="s">
         <v>378</v>
@@ -6285,7 +6304,7 @@
     </row>
     <row r="377" spans="1:3" ht="15.75">
       <c r="A377" s="15">
-        <v>1010085376</v>
+        <v>1010027285</v>
       </c>
       <c r="B377" s="5" t="s">
         <v>379</v>
@@ -6296,7 +6315,7 @@
     </row>
     <row r="378" spans="1:3" ht="15.75">
       <c r="A378" s="15">
-        <v>1010022819</v>
+        <v>1040077413</v>
       </c>
       <c r="B378" s="5" t="s">
         <v>380</v>
@@ -6307,7 +6326,7 @@
     </row>
     <row r="379" spans="1:3" ht="15.75">
       <c r="A379" s="15">
-        <v>1010052853</v>
+        <v>1010085376</v>
       </c>
       <c r="B379" s="5" t="s">
         <v>381</v>
@@ -6318,7 +6337,7 @@
     </row>
     <row r="380" spans="1:3" ht="15.75">
       <c r="A380" s="15">
-        <v>1010084377</v>
+        <v>1010022819</v>
       </c>
       <c r="B380" s="5" t="s">
         <v>382</v>
@@ -6328,1355 +6347,1369 @@
       </c>
     </row>
     <row r="381" spans="1:3" ht="15.75">
-      <c r="A381" s="26">
-        <v>1010062826</v>
+      <c r="A381" s="15">
+        <v>1010052853</v>
       </c>
       <c r="B381" s="5" t="s">
         <v>383</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>384</v>
+        <v>4</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="15.75">
       <c r="A382" s="15">
-        <v>1010002592</v>
+        <v>1010084377</v>
       </c>
       <c r="B382" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" ht="15.75">
+      <c r="A383" s="26">
+        <v>1010062826</v>
+      </c>
+      <c r="B383" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="C382" s="4" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="15.75">
-      <c r="A383" s="24">
-        <v>1010001155</v>
-      </c>
-      <c r="B383" s="5" t="s">
+      <c r="C383" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="C383" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="15.75">
       <c r="A384" s="15">
-        <v>1010001062</v>
+        <v>1010002592</v>
       </c>
       <c r="B384" s="5" t="s">
         <v>387</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75">
-      <c r="A385" s="15">
-        <v>1010084328</v>
+      <c r="A385" s="24">
+        <v>1010001155</v>
       </c>
       <c r="B385" s="5" t="s">
         <v>388</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75">
-      <c r="A386" s="24">
-        <v>1010044502</v>
+      <c r="A386" s="15">
+        <v>1010001062</v>
       </c>
       <c r="B386" s="5" t="s">
         <v>389</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75">
       <c r="A387" s="15">
-        <v>1010053692</v>
+        <v>1010084328</v>
       </c>
       <c r="B387" s="5" t="s">
         <v>390</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75">
-      <c r="A388" s="15">
-        <v>1010083992</v>
+      <c r="A388" s="24">
+        <v>1010044502</v>
       </c>
       <c r="B388" s="5" t="s">
         <v>391</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75">
       <c r="A389" s="15">
-        <v>1010008578</v>
+        <v>1010053692</v>
       </c>
       <c r="B389" s="5" t="s">
         <v>392</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75">
       <c r="A390" s="15">
-        <v>1010031694</v>
+        <v>1010083992</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75">
       <c r="A391" s="15">
-        <v>1010051997</v>
+        <v>1010008578</v>
       </c>
       <c r="B391" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C391" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="C391" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75">
       <c r="A392" s="15">
-        <v>1010022601</v>
+        <v>1010031694</v>
       </c>
       <c r="B392" s="5" t="s">
         <v>396</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75">
       <c r="A393" s="15">
-        <v>1010054278</v>
+        <v>1010051997</v>
       </c>
       <c r="B393" s="5" t="s">
         <v>397</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75">
       <c r="A394" s="15">
-        <v>1010083462</v>
+        <v>1010022601</v>
       </c>
       <c r="B394" s="5" t="s">
         <v>398</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75">
       <c r="A395" s="15">
-        <v>1010027772</v>
+        <v>1010054278</v>
       </c>
       <c r="B395" s="5" t="s">
         <v>399</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75">
       <c r="A396" s="15">
-        <v>1010084144</v>
+        <v>1010083462</v>
       </c>
       <c r="B396" s="5" t="s">
         <v>400</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75">
-      <c r="A397" s="19">
+      <c r="A397" s="15">
+        <v>1010027772</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" ht="15.75">
+      <c r="A398" s="15">
+        <v>1010084144</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C398" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" ht="15.75">
+      <c r="A399" s="19">
         <v>214055</v>
-      </c>
-      <c r="B397" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="C397" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="D397" s="30"/>
-    </row>
-    <row r="398" spans="1:4" ht="15.75">
-      <c r="A398" s="19">
-        <v>1010084720</v>
-      </c>
-      <c r="B398" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="C398" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4" ht="15.75">
-      <c r="A399" s="18">
-        <v>1010021956</v>
       </c>
       <c r="B399" s="7" t="s">
         <v>403</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>393</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="D399" s="29"/>
     </row>
     <row r="400" spans="1:4" ht="15.75">
-      <c r="A400" s="18">
-        <v>1010026464</v>
+      <c r="A400" s="19">
+        <v>1010084720</v>
       </c>
       <c r="B400" s="7" t="s">
         <v>404</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="15.75">
-      <c r="A401" s="14">
+      <c r="A401" s="18">
+        <v>1010021956</v>
+      </c>
+      <c r="B401" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" ht="15.75">
+      <c r="A402" s="18">
+        <v>1010026464</v>
+      </c>
+      <c r="B402" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" ht="15.75">
+      <c r="A403" s="14">
         <v>1010021957</v>
-      </c>
-      <c r="B401" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="C401" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" ht="15.75">
-      <c r="A402" s="15">
-        <v>1010026462</v>
-      </c>
-      <c r="B402" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="C402" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" ht="15.75">
-      <c r="A403" s="15">
-        <v>1010026551</v>
       </c>
       <c r="B403" s="5" t="s">
         <v>407</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="15.75">
       <c r="A404" s="15">
-        <v>1010042554</v>
+        <v>1010026462</v>
       </c>
       <c r="B404" s="5" t="s">
         <v>408</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="15.75">
       <c r="A405" s="15">
-        <v>1010039904</v>
+        <v>1010026551</v>
       </c>
       <c r="B405" s="5" t="s">
         <v>409</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="15.75">
       <c r="A406" s="15">
-        <v>1010060205</v>
+        <v>1010042554</v>
       </c>
       <c r="B406" s="5" t="s">
         <v>410</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="15.75">
       <c r="A407" s="15">
-        <v>1010060206</v>
+        <v>1010039904</v>
       </c>
       <c r="B407" s="5" t="s">
         <v>411</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="15.75">
       <c r="A408" s="15">
-        <v>1010077431</v>
+        <v>1010060205</v>
       </c>
       <c r="B408" s="5" t="s">
         <v>412</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="15.75">
       <c r="A409" s="15">
-        <v>1010077503</v>
+        <v>1010060206</v>
       </c>
       <c r="B409" s="5" t="s">
         <v>413</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="15.75">
       <c r="A410" s="15">
-        <v>1010084187</v>
+        <v>1010077431</v>
       </c>
       <c r="B410" s="5" t="s">
         <v>414</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="15.75">
       <c r="A411" s="15">
-        <v>1010080958</v>
+        <v>1010077503</v>
       </c>
       <c r="B411" s="5" t="s">
         <v>415</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="15.75">
       <c r="A412" s="15">
-        <v>1010026032</v>
+        <v>1010084187</v>
       </c>
       <c r="B412" s="5" t="s">
         <v>416</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="15.75">
       <c r="A413" s="15">
-        <v>1010085384</v>
+        <v>1010080958</v>
       </c>
       <c r="B413" s="5" t="s">
         <v>417</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="15.75">
       <c r="A414" s="15">
-        <v>1010006347</v>
+        <v>1010026032</v>
       </c>
       <c r="B414" s="5" t="s">
         <v>418</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="15.75">
       <c r="A415" s="15">
-        <v>1010085179</v>
+        <v>1010085384</v>
       </c>
       <c r="B415" s="5" t="s">
         <v>419</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="15.75">
       <c r="A416" s="15">
-        <v>1010024158</v>
-      </c>
-      <c r="B416" s="8" t="s">
+        <v>1010006347</v>
+      </c>
+      <c r="B416" s="5" t="s">
         <v>420</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15.75">
       <c r="A417" s="15">
-        <v>1010024131</v>
-      </c>
-      <c r="B417" s="8" t="s">
+        <v>1010085179</v>
+      </c>
+      <c r="B417" s="5" t="s">
         <v>421</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15.75">
       <c r="A418" s="15">
-        <v>1010007160</v>
-      </c>
-      <c r="B418" s="5" t="s">
+        <v>1010024158</v>
+      </c>
+      <c r="B418" s="8" t="s">
         <v>422</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75">
       <c r="A419" s="15">
-        <v>1010023642</v>
-      </c>
-      <c r="B419" s="5" t="s">
+        <v>1010024131</v>
+      </c>
+      <c r="B419" s="8" t="s">
         <v>423</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15.75">
       <c r="A420" s="15">
-        <v>1010007193</v>
-      </c>
-      <c r="B420" s="6" t="s">
+        <v>1010007160</v>
+      </c>
+      <c r="B420" s="5" t="s">
         <v>424</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75">
       <c r="A421" s="15">
-        <v>1010042637</v>
+        <v>1010023642</v>
       </c>
       <c r="B421" s="5" t="s">
         <v>425</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75">
       <c r="A422" s="15">
-        <v>1040075323</v>
-      </c>
-      <c r="B422" s="5" t="s">
+        <v>1010007193</v>
+      </c>
+      <c r="B422" s="6" t="s">
         <v>426</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15.75">
       <c r="A423" s="15">
+        <v>1010042637</v>
+      </c>
+      <c r="B423" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="15.75">
+      <c r="A424" s="15">
+        <v>1040075323</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" ht="15.75">
+      <c r="A425" s="15">
         <v>1040075324</v>
-      </c>
-      <c r="B423" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="C423" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" ht="15.75">
-      <c r="A424" s="27">
-        <v>1040074827</v>
-      </c>
-      <c r="B424" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="C424" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="15.75">
-      <c r="A425" s="27">
-        <v>1040099488</v>
       </c>
       <c r="B425" s="8" t="s">
         <v>429</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75">
       <c r="A426" s="27">
-        <v>1040083312</v>
+        <v>1040074827</v>
       </c>
       <c r="B426" s="8" t="s">
         <v>430</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="15.75">
       <c r="A427" s="27">
-        <v>1040077661</v>
+        <v>1040099488</v>
       </c>
       <c r="B427" s="8" t="s">
         <v>431</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="15.75">
       <c r="A428" s="27">
+        <v>1040083312</v>
+      </c>
+      <c r="B428" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" ht="15.75">
+      <c r="A429" s="27">
+        <v>1040077661</v>
+      </c>
+      <c r="B429" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="15.75">
+      <c r="A430" s="27">
         <v>1010085180</v>
       </c>
-      <c r="B428" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="C428" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="15.75">
-      <c r="A429" s="14">
+      <c r="B430" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="C430" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="15.75">
+      <c r="A431" s="14">
         <v>1040017489</v>
       </c>
-      <c r="B429" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="C429" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="15.75">
-      <c r="A430" s="14">
+      <c r="B431" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="15.75">
+      <c r="A432" s="14">
         <v>1010085181</v>
-      </c>
-      <c r="B430" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="C430" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15.75">
-      <c r="A431" s="15">
-        <v>400175</v>
-      </c>
-      <c r="B431" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C431" s="4" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75">
-      <c r="A432" s="15">
-        <v>1040017505</v>
       </c>
       <c r="B432" s="5" t="s">
         <v>436</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="15.75">
       <c r="A433" s="15">
-        <v>1040017503</v>
+        <v>400175</v>
       </c>
       <c r="B433" s="5" t="s">
         <v>437</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="15.75">
       <c r="A434" s="15">
-        <v>1010046445</v>
+        <v>1040017505</v>
       </c>
       <c r="B434" s="5" t="s">
         <v>438</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="15.75">
       <c r="A435" s="15">
-        <v>1010021033</v>
+        <v>1040017503</v>
       </c>
       <c r="B435" s="5" t="s">
         <v>439</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="15.75">
       <c r="A436" s="15">
-        <v>1010057142</v>
+        <v>1010046445</v>
       </c>
       <c r="B436" s="5" t="s">
         <v>440</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="15.75">
       <c r="A437" s="15">
-        <v>1010016356</v>
+        <v>1010021033</v>
       </c>
       <c r="B437" s="5" t="s">
         <v>441</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="15.75">
       <c r="A438" s="15">
-        <v>1010084363</v>
+        <v>1010057142</v>
       </c>
       <c r="B438" s="5" t="s">
         <v>442</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="15.75">
       <c r="A439" s="15">
-        <v>1010052021</v>
+        <v>1010016356</v>
       </c>
       <c r="B439" s="5" t="s">
         <v>443</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="15.75">
       <c r="A440" s="15">
-        <v>1040091721</v>
+        <v>1010084363</v>
       </c>
       <c r="B440" s="5" t="s">
         <v>444</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="15.75">
       <c r="A441" s="15">
-        <v>1010062022</v>
+        <v>1010052021</v>
       </c>
       <c r="B441" s="5" t="s">
         <v>445</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="15.75">
       <c r="A442" s="15">
-        <v>18336</v>
+        <v>1040091721</v>
       </c>
       <c r="B442" s="5" t="s">
         <v>446</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="15.75">
       <c r="A443" s="15">
-        <v>229205</v>
+        <v>1010062022</v>
       </c>
       <c r="B443" s="5" t="s">
         <v>447</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="15.75">
       <c r="A444" s="15">
-        <v>60671</v>
+        <v>18336</v>
       </c>
       <c r="B444" s="5" t="s">
         <v>448</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="15.75">
       <c r="A445" s="15">
-        <v>1010059726</v>
+        <v>229205</v>
       </c>
       <c r="B445" s="5" t="s">
         <v>449</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="15.75">
       <c r="A446" s="15">
-        <v>1010008144</v>
+        <v>60671</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>450</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="15.75">
       <c r="A447" s="15">
-        <v>1010007244</v>
+        <v>1010059726</v>
       </c>
       <c r="B447" s="5" t="s">
         <v>451</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="15.75">
       <c r="A448" s="15">
-        <v>1010006827</v>
+        <v>1010008144</v>
       </c>
       <c r="B448" s="5" t="s">
         <v>452</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="15.75">
       <c r="A449" s="15">
-        <v>1040075426</v>
+        <v>1010007244</v>
       </c>
       <c r="B449" s="5" t="s">
         <v>453</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="15.75">
       <c r="A450" s="15">
-        <v>1040075427</v>
+        <v>1010006827</v>
       </c>
       <c r="B450" s="5" t="s">
         <v>454</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="15.75">
       <c r="A451" s="15">
-        <v>1010084313</v>
+        <v>1040075426</v>
       </c>
       <c r="B451" s="5" t="s">
         <v>455</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="15.75">
       <c r="A452" s="15">
-        <v>403459</v>
+        <v>1040075427</v>
       </c>
       <c r="B452" s="5" t="s">
         <v>456</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="15.75">
       <c r="A453" s="15">
-        <v>1010044828</v>
+        <v>1010084313</v>
       </c>
       <c r="B453" s="5" t="s">
         <v>457</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="15.75">
       <c r="A454" s="15">
-        <v>1010026973</v>
+        <v>403459</v>
       </c>
       <c r="B454" s="5" t="s">
         <v>458</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="15.75">
       <c r="A455" s="15">
-        <v>1040017204</v>
+        <v>1010044828</v>
       </c>
       <c r="B455" s="5" t="s">
         <v>459</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="15.75">
-      <c r="A456" s="24">
-        <v>1010022119</v>
-      </c>
-      <c r="B456" s="6" t="s">
+      <c r="A456" s="15">
+        <v>1010026973</v>
+      </c>
+      <c r="B456" s="5" t="s">
         <v>460</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>461</v>
+        <v>395</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75">
       <c r="A457" s="15">
-        <v>1010058709</v>
+        <v>1040017204</v>
       </c>
       <c r="B457" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C457" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="15.75">
+      <c r="A458" s="24">
+        <v>1010022119</v>
+      </c>
+      <c r="B458" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="C457" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="15.75">
-      <c r="A458" s="15">
-        <v>1010025711</v>
-      </c>
-      <c r="B458" s="5" t="s">
+      <c r="C458" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="C458" s="4" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="15.75">
       <c r="A459" s="15">
-        <v>1010059684</v>
+        <v>1010058709</v>
       </c>
       <c r="B459" s="5" t="s">
         <v>464</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75">
       <c r="A460" s="15">
-        <v>427341</v>
+        <v>1010025711</v>
       </c>
       <c r="B460" s="5" t="s">
         <v>465</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="15.75">
       <c r="A461" s="15">
-        <v>1010085279</v>
+        <v>1010059684</v>
       </c>
       <c r="B461" s="5" t="s">
         <v>466</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="15.75">
-      <c r="A462" s="19">
-        <v>1010022588</v>
+      <c r="A462" s="15">
+        <v>427341</v>
       </c>
       <c r="B462" s="5" t="s">
         <v>467</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="15.75">
       <c r="A463" s="15">
+        <v>1010085279</v>
+      </c>
+      <c r="B463" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="C463" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" ht="15.75">
+      <c r="A464" s="19">
+        <v>1010022588</v>
+      </c>
+      <c r="B464" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="C464" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="15.75">
+      <c r="A465" s="15">
         <v>1010026864</v>
       </c>
-      <c r="B463" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="C463" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" ht="15.75">
-      <c r="A464" s="14">
+      <c r="B465" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="C465" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="15.75">
+      <c r="A466" s="14">
         <v>1010030946</v>
       </c>
-      <c r="B464" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="C464" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" ht="15.75">
-      <c r="A465" s="14">
+      <c r="B466" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="15.75">
+      <c r="A467" s="14">
         <v>1010022589</v>
-      </c>
-      <c r="B465" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C465" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" ht="15.75">
-      <c r="A466" s="15">
-        <v>1040090143</v>
-      </c>
-      <c r="B466" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="C466" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="15.75">
-      <c r="A467" s="15">
-        <v>1040090138</v>
       </c>
       <c r="B467" s="5" t="s">
         <v>472</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="15.75">
       <c r="A468" s="15">
-        <v>1030001314</v>
+        <v>1040090143</v>
       </c>
       <c r="B468" s="5" t="s">
         <v>473</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="15.75">
       <c r="A469" s="15">
-        <v>1010052319</v>
+        <v>1040090138</v>
       </c>
       <c r="B469" s="5" t="s">
         <v>474</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="15.75">
       <c r="A470" s="15">
-        <v>1010052320</v>
+        <v>1030001314</v>
       </c>
       <c r="B470" s="5" t="s">
         <v>475</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="15.75">
       <c r="A471" s="15">
-        <v>1030000370</v>
+        <v>1010052319</v>
       </c>
       <c r="B471" s="5" t="s">
         <v>476</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="15.75">
       <c r="A472" s="15">
-        <v>1030000366</v>
+        <v>1010052320</v>
       </c>
       <c r="B472" s="5" t="s">
         <v>477</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="15.75">
       <c r="A473" s="15">
-        <v>1030000368</v>
+        <v>1030000370</v>
       </c>
       <c r="B473" s="5" t="s">
         <v>478</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="15.75">
       <c r="A474" s="15">
-        <v>1030000369</v>
+        <v>1030000366</v>
       </c>
       <c r="B474" s="5" t="s">
         <v>479</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="15.75">
       <c r="A475" s="15">
-        <v>1030000489</v>
+        <v>1030000368</v>
       </c>
       <c r="B475" s="5" t="s">
         <v>480</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15.75">
       <c r="A476" s="15">
-        <v>1030000490</v>
+        <v>1030000369</v>
       </c>
       <c r="B476" s="5" t="s">
         <v>481</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="15.75">
       <c r="A477" s="15">
-        <v>1030000821</v>
+        <v>1030000489</v>
       </c>
       <c r="B477" s="5" t="s">
         <v>482</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75">
       <c r="A478" s="15">
+        <v>1030000490</v>
+      </c>
+      <c r="B478" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C478" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="15.75">
+      <c r="A479" s="15">
+        <v>1030000821</v>
+      </c>
+      <c r="B479" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C479" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="15.75">
+      <c r="A480" s="15">
         <v>1030000511</v>
       </c>
-      <c r="B478" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C478" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="15.75">
-      <c r="A479" s="16">
+      <c r="B480" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="C480" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" ht="15.75">
+      <c r="A481" s="16">
         <v>1010084279</v>
       </c>
-      <c r="B479" s="8" t="s">
-        <v>484</v>
-      </c>
-      <c r="C479" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="15.75">
-      <c r="A480" s="16">
+      <c r="B481" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C481" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" ht="15.75">
+      <c r="A482" s="16">
         <v>1010004281</v>
-      </c>
-      <c r="B480" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C480" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" ht="15.75">
-      <c r="A481" s="15">
-        <v>1010022118</v>
-      </c>
-      <c r="B481" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="C481" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" ht="15.75">
-      <c r="A482" s="15">
-        <v>1010028657</v>
       </c>
       <c r="B482" s="5" t="s">
         <v>487</v>
       </c>
       <c r="C482" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" ht="15.75">
+      <c r="A483" s="15">
+        <v>1010022118</v>
+      </c>
+      <c r="B483" s="9" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.75">
-      <c r="A483" s="18">
+      <c r="C483" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" ht="15.75">
+      <c r="A484" s="15">
+        <v>1010028657</v>
+      </c>
+      <c r="B484" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="C484" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" ht="15.75">
+      <c r="A485" s="18">
         <v>1010028655</v>
-      </c>
-      <c r="B483" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C483" s="4" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" ht="15.75">
-      <c r="A484" s="18">
-        <v>145165</v>
-      </c>
-      <c r="B484" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" ht="15.75">
-      <c r="A485" s="15">
-        <v>51666</v>
       </c>
       <c r="B485" s="5" t="s">
         <v>491</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="15.75">
       <c r="A486" s="18">
-        <v>1010080930</v>
+        <v>145165</v>
       </c>
       <c r="B486" s="5" t="s">
         <v>492</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="15.75">
       <c r="A487" s="15">
-        <v>161055</v>
+        <v>51666</v>
       </c>
       <c r="B487" s="5" t="s">
         <v>493</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="15.75">
-      <c r="A488" s="15">
-        <v>1010050517</v>
+      <c r="A488" s="18">
+        <v>1010080930</v>
       </c>
       <c r="B488" s="5" t="s">
         <v>494</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="15.75">
       <c r="A489" s="15">
-        <v>1010084190</v>
+        <v>161055</v>
       </c>
       <c r="B489" s="5" t="s">
         <v>495</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="15.75">
       <c r="A490" s="15">
-        <v>1010084195</v>
+        <v>1010050517</v>
       </c>
       <c r="B490" s="5" t="s">
         <v>496</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="15.75">
       <c r="A491" s="15">
-        <v>1010001400</v>
+        <v>1010084190</v>
       </c>
       <c r="B491" s="5" t="s">
         <v>497</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="15.75">
-      <c r="A492" s="17">
-        <v>1010008416</v>
+      <c r="A492" s="15">
+        <v>1010084195</v>
       </c>
       <c r="B492" s="5" t="s">
         <v>498</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="15.75">
-      <c r="A493" s="28">
-        <v>1010018372</v>
+      <c r="A493" s="15">
+        <v>1010001400</v>
       </c>
       <c r="B493" s="5" t="s">
         <v>499</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="15.75">
-      <c r="A494" s="28">
+      <c r="A494" s="17">
+        <v>1010008416</v>
+      </c>
+      <c r="B494" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C494" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" ht="15.75">
+      <c r="A495" s="28">
+        <v>1010018372</v>
+      </c>
+      <c r="B495" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="C495" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" ht="15.75">
+      <c r="A496" s="28">
         <v>1010018361</v>
       </c>
-      <c r="B494" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="C494" s="4" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" ht="15.75">
-      <c r="A495" s="16">
+      <c r="B496" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="C496" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" ht="15.75">
+      <c r="A497" s="16">
         <v>1010055398</v>
       </c>
-      <c r="B495" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="C495" s="4" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" ht="15.75">
-      <c r="A496" s="15">
-        <v>422131</v>
-      </c>
-      <c r="B496" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="C496" s="4" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" ht="15.75">
-      <c r="A497" s="15">
-        <v>1010084370</v>
-      </c>
-      <c r="B497" s="5" t="s">
+      <c r="B497" s="11" t="s">
         <v>503</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="15.75">
       <c r="A498" s="15">
-        <v>422759</v>
+        <v>422131</v>
       </c>
       <c r="B498" s="5" t="s">
         <v>504</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="15.75">
       <c r="A499" s="15">
-        <v>120955</v>
+        <v>1010084370</v>
       </c>
       <c r="B499" s="5" t="s">
         <v>505</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="15.75">
       <c r="A500" s="15">
-        <v>1010000896</v>
+        <v>422759</v>
       </c>
       <c r="B500" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="C500" s="13" t="s">
-        <v>488</v>
+      <c r="C500" s="4" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="15.75">
       <c r="A501" s="15">
-        <v>1010084308</v>
+        <v>120955</v>
       </c>
       <c r="B501" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="C501" s="13" t="s">
-        <v>488</v>
+      <c r="C501" s="4" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="15.75">
       <c r="A502" s="15">
-        <v>1010084035</v>
+        <v>1010000896</v>
       </c>
       <c r="B502" s="5" t="s">
         <v>508</v>
       </c>
       <c r="C502" s="13" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="15.75">
-      <c r="A503" s="2"/>
-      <c r="B503" s="2"/>
+      <c r="A503" s="15">
+        <v>1010084308</v>
+      </c>
+      <c r="B503" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="C503" s="13" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="504" spans="1:3" ht="15.75">
-      <c r="A504" s="2"/>
-      <c r="B504" s="2"/>
+      <c r="A504" s="15">
+        <v>1010084035</v>
+      </c>
+      <c r="B504" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C504" s="13" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="505" spans="1:3" ht="15.75">
       <c r="A505" s="2"/>
@@ -9428,11 +9461,11 @@
     </row>
     <row r="942" spans="1:2" ht="15.75">
       <c r="A942" s="2"/>
-      <c r="B942" s="1"/>
+      <c r="B942" s="2"/>
     </row>
     <row r="943" spans="1:2" ht="15.75">
       <c r="A943" s="2"/>
-      <c r="B943" s="1"/>
+      <c r="B943" s="2"/>
     </row>
     <row r="944" spans="1:2" ht="15.75">
       <c r="A944" s="2"/>
@@ -9699,11 +9732,11 @@
       <c r="B1009" s="1"/>
     </row>
     <row r="1010" spans="1:2" ht="15.75">
-      <c r="A1010" s="1"/>
+      <c r="A1010" s="2"/>
       <c r="B1010" s="1"/>
     </row>
     <row r="1011" spans="1:2" ht="15.75">
-      <c r="A1011" s="1"/>
+      <c r="A1011" s="2"/>
       <c r="B1011" s="1"/>
     </row>
     <row r="1012" spans="1:2" ht="15.75">
@@ -10477,6 +10510,14 @@
     <row r="1204" spans="1:2" ht="15.75">
       <c r="A1204" s="1"/>
       <c r="B1204" s="1"/>
+    </row>
+    <row r="1205" spans="1:2" ht="15.75">
+      <c r="A1205" s="1"/>
+      <c r="B1205" s="1"/>
+    </row>
+    <row r="1206" spans="1:2" ht="15.75">
+      <c r="A1206" s="1"/>
+      <c r="B1206" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10505,22 +10546,22 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A68652A-162A-420A-971C-063CCEDB524B}"/>
+  <xr:revisionPtr revIDLastSave="240" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{252F1683-31E9-46D6-B8E9-91300310265C}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="509">
   <si>
     <t>material</t>
   </si>
@@ -817,9 +817,6 @@
     <t>PONTEIRA ENGATE ESFÉRICO</t>
   </si>
   <si>
-    <t>PONTEIRA MANGUEIRA 3/4 (TERMINAL FEMEA)</t>
-  </si>
-  <si>
     <t>PONTEIRA MANGUEIRA 1POL (TERMINAL FEMEA)</t>
   </si>
   <si>
@@ -1100,9 +1097,6 @@
   </si>
   <si>
     <t>TERMINAL DIREÇÃO (L/E)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TERMINAL FEMEA </t>
   </si>
   <si>
     <t>TERMINAL ISOL AUTOTRAC (CONECTOR PARA RELE 24V)</t>
@@ -1592,7 +1586,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2158,15 +2152,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1206"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D1204"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2177,7 +2171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>1040019909</v>
       </c>
@@ -2188,7 +2182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>1040023837</v>
       </c>
@@ -2199,7 +2193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>1040023836</v>
       </c>
@@ -2210,7 +2204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>1010000216</v>
       </c>
@@ -2221,7 +2215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>423651</v>
       </c>
@@ -2232,7 +2226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>1040077347</v>
       </c>
@@ -2243,7 +2237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>1040077348</v>
       </c>
@@ -2254,7 +2248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>417715</v>
       </c>
@@ -2265,7 +2259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>1010062075</v>
       </c>
@@ -2276,7 +2270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>1040083308</v>
       </c>
@@ -2287,7 +2281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>1040077346</v>
       </c>
@@ -2298,7 +2292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>1010049326</v>
       </c>
@@ -2309,7 +2303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>1040017265</v>
       </c>
@@ -2320,7 +2314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>1010060188</v>
       </c>
@@ -2331,7 +2325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>1040019851</v>
       </c>
@@ -2342,7 +2336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>1010077433</v>
       </c>
@@ -2353,7 +2347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>1010042610</v>
       </c>
@@ -2364,7 +2358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>1040077352</v>
       </c>
@@ -2375,7 +2369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>1040083258</v>
       </c>
@@ -2386,7 +2380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>68686</v>
       </c>
@@ -2397,7 +2391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>1010084124</v>
       </c>
@@ -2408,7 +2402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>102286</v>
       </c>
@@ -2419,7 +2413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>1040097671</v>
       </c>
@@ -2430,7 +2424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>1010003651</v>
       </c>
@@ -2441,7 +2435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>1010062027</v>
       </c>
@@ -2452,7 +2446,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>1010021550</v>
       </c>
@@ -2463,7 +2457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>1040077350</v>
       </c>
@@ -2474,7 +2468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>1040077349</v>
       </c>
@@ -2485,7 +2479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>154897</v>
       </c>
@@ -2496,7 +2490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>13781</v>
       </c>
@@ -2507,7 +2501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>1010058682</v>
       </c>
@@ -2518,7 +2512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>1010059706</v>
       </c>
@@ -2529,7 +2523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>1010077386</v>
       </c>
@@ -2540,7 +2534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>1010058325</v>
       </c>
@@ -2551,7 +2545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>1010061986</v>
       </c>
@@ -2562,7 +2556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>1010004299</v>
       </c>
@@ -2573,7 +2567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>1010004301</v>
       </c>
@@ -2584,7 +2578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>1010004289</v>
       </c>
@@ -2595,7 +2589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>1010004292</v>
       </c>
@@ -2606,7 +2600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="14">
         <v>1040077354</v>
       </c>
@@ -2617,7 +2611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>1010050496</v>
       </c>
@@ -2628,7 +2622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="14">
         <v>1010050536</v>
       </c>
@@ -2639,7 +2633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="14">
         <v>1010061810</v>
       </c>
@@ -2650,7 +2644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="14">
         <v>1040092580</v>
       </c>
@@ -2661,7 +2655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
         <v>1010041375</v>
       </c>
@@ -2672,7 +2666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="14">
         <v>1040098335</v>
       </c>
@@ -2683,7 +2677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="14">
         <v>1010023362</v>
       </c>
@@ -2694,7 +2688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="14">
         <v>1010052336</v>
       </c>
@@ -2705,7 +2699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="14">
         <v>1040077355</v>
       </c>
@@ -2716,7 +2710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="14">
         <v>230110</v>
       </c>
@@ -2727,7 +2721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
         <v>1040077357</v>
       </c>
@@ -2738,7 +2732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
         <v>1040077356</v>
       </c>
@@ -2749,7 +2743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="15">
         <v>1040075251</v>
       </c>
@@ -2760,7 +2754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
         <v>1040090022</v>
       </c>
@@ -2771,7 +2765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
         <v>1010023336</v>
       </c>
@@ -2782,7 +2776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
         <v>1010021328</v>
       </c>
@@ -2793,7 +2787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
         <v>1010059706</v>
       </c>
@@ -2804,7 +2798,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>1010062152</v>
       </c>
@@ -2815,7 +2809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
         <v>1040077358</v>
       </c>
@@ -2826,7 +2820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
         <v>1010045227</v>
       </c>
@@ -2837,7 +2831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
         <v>1010085124</v>
       </c>
@@ -2848,7 +2842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
         <v>1010046495</v>
       </c>
@@ -2859,7 +2853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
         <v>1010032356</v>
       </c>
@@ -2870,7 +2864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
         <v>1010050244</v>
       </c>
@@ -2881,7 +2875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="14">
         <v>1010050243</v>
       </c>
@@ -2892,7 +2886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="14">
         <v>428995</v>
       </c>
@@ -2903,7 +2897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
         <v>428998</v>
       </c>
@@ -2914,7 +2908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="14">
         <v>1010031607</v>
       </c>
@@ -2925,7 +2919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
         <v>1010031630</v>
       </c>
@@ -2936,7 +2930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="14">
         <v>1010045647</v>
       </c>
@@ -2947,7 +2941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="14">
         <v>1010031567</v>
       </c>
@@ -2958,7 +2952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="14">
         <v>1040077361</v>
       </c>
@@ -2969,7 +2963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="14">
         <v>1010050445</v>
       </c>
@@ -2980,7 +2974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75">
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="14">
         <v>1010050461</v>
       </c>
@@ -2991,7 +2985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75">
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="14">
         <v>1010053885</v>
       </c>
@@ -3002,7 +2996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75">
+    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="15">
         <v>1040097102</v>
       </c>
@@ -3013,7 +3007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75">
+    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="15">
         <v>1010020838</v>
       </c>
@@ -3024,7 +3018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.75">
+    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="16">
         <v>341430</v>
       </c>
@@ -3035,7 +3029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75">
+    <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="15">
         <v>1010042643</v>
       </c>
@@ -3046,7 +3040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.75">
+    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="15">
         <v>425554</v>
       </c>
@@ -3057,7 +3051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75">
+    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
         <v>1010084162</v>
       </c>
@@ -3068,7 +3062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75">
+    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="15">
         <v>1010084157</v>
       </c>
@@ -3079,7 +3073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75">
+    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>1010084158</v>
       </c>
@@ -3090,7 +3084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75">
+    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>1010084159</v>
       </c>
@@ -3101,7 +3095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75">
+    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>1010084160</v>
       </c>
@@ -3112,7 +3106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75">
+    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>1010084161</v>
       </c>
@@ -3123,7 +3117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75">
+    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>224382</v>
       </c>
@@ -3134,7 +3128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75">
+    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>94314</v>
       </c>
@@ -3145,7 +3139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.75">
+    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="17">
         <v>1010003982</v>
       </c>
@@ -3156,7 +3150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.75">
+    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="15">
         <v>1010000182</v>
       </c>
@@ -3167,7 +3161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75">
+    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="15">
         <v>1010021079</v>
       </c>
@@ -3178,7 +3172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.75">
+    <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="15">
         <v>1010002463</v>
       </c>
@@ -3189,7 +3183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75">
+    <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="15">
         <v>1010062982</v>
       </c>
@@ -3200,7 +3194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.75">
+    <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="15">
         <v>1010063209</v>
       </c>
@@ -3211,7 +3205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.75">
+    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="15">
         <v>1040076302</v>
       </c>
@@ -3222,7 +3216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.75">
+    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="15">
         <v>1040077362</v>
       </c>
@@ -3233,7 +3227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.75">
+    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="15">
         <v>1040077363</v>
       </c>
@@ -3244,7 +3238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.75">
+    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="15">
         <v>1040074483</v>
       </c>
@@ -3255,7 +3249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.75">
+    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="15">
         <v>1040077364</v>
       </c>
@@ -3266,7 +3260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.75">
+    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="15">
         <v>1040048463</v>
       </c>
@@ -3277,7 +3271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75">
+    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="15">
         <v>1040096343</v>
       </c>
@@ -3288,7 +3282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.75">
+    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="15">
         <v>409640</v>
       </c>
@@ -3299,7 +3293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75">
+    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="15">
         <v>1010032753</v>
       </c>
@@ -3310,7 +3304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.75">
+    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="15">
         <v>1040098597</v>
       </c>
@@ -3321,7 +3315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.75">
+    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="15">
         <v>1040084464</v>
       </c>
@@ -3332,7 +3326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.75">
+    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="15">
         <v>1040017773</v>
       </c>
@@ -3343,7 +3337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.75">
+    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="15">
         <v>1010007405</v>
       </c>
@@ -3354,7 +3348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.75">
+    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="17">
         <v>1040077365</v>
       </c>
@@ -3365,7 +3359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.75">
+    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="15">
         <v>1010027794</v>
       </c>
@@ -3376,7 +3370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.75">
+    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="15">
         <v>1040077366</v>
       </c>
@@ -3387,7 +3381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.75">
+    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="15">
         <v>1040077367</v>
       </c>
@@ -3398,7 +3392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.75">
+    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="15">
         <v>1010021561</v>
       </c>
@@ -3409,7 +3403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.75">
+    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="15">
         <v>1010021562</v>
       </c>
@@ -3420,7 +3414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.75">
+    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="15">
         <v>1010027792</v>
       </c>
@@ -3431,7 +3425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.75">
+    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="15">
         <v>1010084930</v>
       </c>
@@ -3442,7 +3436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.75">
+    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="15">
         <v>341430</v>
       </c>
@@ -3453,7 +3447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.75">
+    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="15">
         <v>1010029366</v>
       </c>
@@ -3464,7 +3458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.75">
+    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="18">
         <v>1010031723</v>
       </c>
@@ -3475,7 +3469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75">
+    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="18">
         <v>1010049216</v>
       </c>
@@ -3486,7 +3480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.75">
+    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="15">
         <v>405558</v>
       </c>
@@ -3497,7 +3491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.75">
+    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="15">
         <v>1010023038</v>
       </c>
@@ -3508,7 +3502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75">
+    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="15">
         <v>1010084109</v>
       </c>
@@ -3519,7 +3513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75">
+    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="15">
         <v>1010021582</v>
       </c>
@@ -3530,7 +3524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.75">
+    <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="15">
         <v>1010021544</v>
       </c>
@@ -3541,7 +3535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.75">
+    <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="15">
         <v>1010021564</v>
       </c>
@@ -3552,7 +3546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.75">
+    <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="15">
         <v>1010023019</v>
       </c>
@@ -3563,7 +3557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.75">
+    <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="15">
         <v>1010048541</v>
       </c>
@@ -3574,7 +3568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.75">
+    <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="15">
         <v>1010059334</v>
       </c>
@@ -3585,7 +3579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.75">
+    <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="15">
         <v>1010000277</v>
       </c>
@@ -3596,7 +3590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.75">
+    <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="19">
         <v>1010085344</v>
       </c>
@@ -3607,7 +3601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.75">
+    <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="19">
         <v>1010085383</v>
       </c>
@@ -3618,7 +3612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.75">
+    <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="15">
         <v>1010001389</v>
       </c>
@@ -3629,7 +3623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.75">
+    <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="15">
         <v>1010017703</v>
       </c>
@@ -3640,7 +3634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.75">
+    <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="15">
         <v>1010052036</v>
       </c>
@@ -3651,7 +3645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.75">
+    <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="15">
         <v>1040097133</v>
       </c>
@@ -3662,7 +3656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.75">
+    <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="15">
         <v>1040019325</v>
       </c>
@@ -3673,7 +3667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.75">
+    <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="15">
         <v>64262</v>
       </c>
@@ -3684,7 +3678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.75">
+    <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="14">
         <v>1010047089</v>
       </c>
@@ -3695,7 +3689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.75">
+    <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="14">
         <v>1040050168</v>
       </c>
@@ -3706,7 +3700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.75">
+    <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="14">
         <v>1040077370</v>
       </c>
@@ -3717,7 +3711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.75">
+    <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="14">
         <v>1040099247</v>
       </c>
@@ -3728,7 +3722,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.75">
+    <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="15">
         <v>1040077371</v>
       </c>
@@ -3739,7 +3733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.75">
+    <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="15">
         <v>1040077399</v>
       </c>
@@ -3750,7 +3744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.75">
+    <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="15">
         <v>1040077374</v>
       </c>
@@ -3761,7 +3755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.75">
+    <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="15">
         <v>1040077399</v>
       </c>
@@ -3772,7 +3766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.75">
+    <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="15">
         <v>357623</v>
       </c>
@@ -3783,7 +3777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.75">
+    <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="15">
         <v>1010020504</v>
       </c>
@@ -3794,7 +3788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.75">
+    <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="15">
         <v>409250</v>
       </c>
@@ -3805,7 +3799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.75">
+    <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="15">
         <v>1010020541</v>
       </c>
@@ -3816,7 +3810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.75">
+    <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="15">
         <v>1010020879</v>
       </c>
@@ -3827,7 +3821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.75">
+    <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="15">
         <v>1040077380</v>
       </c>
@@ -3838,7 +3832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15.75">
+    <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="15">
         <v>1010021520</v>
       </c>
@@ -3849,7 +3843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.75">
+    <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="15">
         <v>1040098861</v>
       </c>
@@ -3860,7 +3854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.75">
+    <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="15">
         <v>1010077261</v>
       </c>
@@ -3871,7 +3865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.75">
+    <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="15">
         <v>1010027664</v>
       </c>
@@ -3882,7 +3876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.75">
+    <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="15">
         <v>1010083731</v>
       </c>
@@ -3893,7 +3887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.75">
+    <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="15">
         <v>1010083885</v>
       </c>
@@ -3904,7 +3898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.75">
+    <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="15">
         <v>1010014834</v>
       </c>
@@ -3915,7 +3909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.75">
+    <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="15">
         <v>1010083908</v>
       </c>
@@ -3926,7 +3920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.75">
+    <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="15">
         <v>1040077377</v>
       </c>
@@ -3937,7 +3931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.75">
+    <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="15">
         <v>1010061942</v>
       </c>
@@ -3948,7 +3942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.75">
+    <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="15">
         <v>1040097070</v>
       </c>
@@ -3959,7 +3953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.75">
+    <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="15">
         <v>1040097068</v>
       </c>
@@ -3970,7 +3964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.75">
+    <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="15">
         <v>22004</v>
       </c>
@@ -3981,7 +3975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.75">
+    <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="15">
         <v>1010058554</v>
       </c>
@@ -3992,7 +3986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.75">
+    <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="15">
         <v>1010027308</v>
       </c>
@@ -4003,7 +3997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15.75">
+    <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="19">
         <v>1040077383</v>
       </c>
@@ -4014,7 +4008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.75">
+    <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="19">
         <v>1010025482</v>
       </c>
@@ -4025,7 +4019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.75">
+    <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="19">
         <v>1010025509</v>
       </c>
@@ -4036,7 +4030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.75">
+    <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="15">
         <v>1010027789</v>
       </c>
@@ -4047,7 +4041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.75">
+    <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="15">
         <v>1010027790</v>
       </c>
@@ -4058,7 +4052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.75">
+    <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="15">
         <v>1010018301</v>
       </c>
@@ -4069,7 +4063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15.75">
+    <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="15">
         <v>1010031616</v>
       </c>
@@ -4080,7 +4074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.75">
+    <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="15">
         <v>1010053728</v>
       </c>
@@ -4091,7 +4085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.75">
+    <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="15">
         <v>1010020758</v>
       </c>
@@ -4102,7 +4096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.75">
+    <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="15">
         <v>1010020781</v>
       </c>
@@ -4113,7 +4107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.75">
+    <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="14">
         <v>1010058426</v>
       </c>
@@ -4124,7 +4118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.75">
+    <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="14">
         <v>1010059332</v>
       </c>
@@ -4135,7 +4129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.75">
+    <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="14">
         <v>1040077389</v>
       </c>
@@ -4146,7 +4140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.75">
+    <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="15">
         <v>1010021364</v>
       </c>
@@ -4157,7 +4151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.75">
+    <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="20">
         <v>1010021541</v>
       </c>
@@ -4168,7 +4162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75">
+    <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="14">
         <v>1010021955</v>
       </c>
@@ -4179,7 +4173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75">
+    <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="15">
         <v>1040077388</v>
       </c>
@@ -4190,7 +4184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75">
+    <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="15">
         <v>1010058100</v>
       </c>
@@ -4201,7 +4195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75">
+    <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="15">
         <v>1010020524</v>
       </c>
@@ -4212,7 +4206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75">
+    <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="15">
         <v>1010021958</v>
       </c>
@@ -4223,7 +4217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75">
+    <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="15">
         <v>1010019756</v>
       </c>
@@ -4234,7 +4228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75">
+    <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="15">
         <v>1010019752</v>
       </c>
@@ -4245,7 +4239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.75">
+    <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="15">
         <v>409639</v>
       </c>
@@ -4256,7 +4250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75">
+    <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="15">
         <v>1010047089</v>
       </c>
@@ -4267,7 +4261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.75">
+    <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="15">
         <v>1040084107</v>
       </c>
@@ -4278,7 +4272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75">
+    <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="15">
         <v>1010085203</v>
       </c>
@@ -4289,7 +4283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75">
+    <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="15">
         <v>424298</v>
       </c>
@@ -4300,7 +4294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75">
+    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="15">
         <v>421847</v>
       </c>
@@ -4311,7 +4305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75">
+    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="15">
         <v>431573</v>
       </c>
@@ -4322,7 +4316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75">
+    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="15">
         <v>1010021581</v>
       </c>
@@ -4333,7 +4327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75">
+    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="21">
         <v>412413</v>
       </c>
@@ -4344,7 +4338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75">
+    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="22">
         <v>1010022606</v>
       </c>
@@ -4355,7 +4349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75">
+    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <v>1010003527</v>
       </c>
@@ -4366,7 +4360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75">
+    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="23">
         <v>1010055707</v>
       </c>
@@ -4377,7 +4371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75">
+    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="18">
         <v>422027</v>
       </c>
@@ -4388,7 +4382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75">
+    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="14">
         <v>1010011313</v>
       </c>
@@ -4399,7 +4393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75">
+    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="15">
         <v>27051</v>
       </c>
@@ -4410,7 +4404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75">
+    <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="15">
         <v>1010011304</v>
       </c>
@@ -4421,7 +4415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75">
+    <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="15">
         <v>35659</v>
       </c>
@@ -4432,7 +4426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75">
+    <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="15">
         <v>1040077390</v>
       </c>
@@ -4443,7 +4437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75">
+    <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="15">
         <v>1010021542</v>
       </c>
@@ -4454,7 +4448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.75">
+    <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="15">
         <v>1010021733</v>
       </c>
@@ -4465,7 +4459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75">
+    <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="15">
         <v>1010011379</v>
       </c>
@@ -4476,7 +4470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75">
+    <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="15">
         <v>1010003279</v>
       </c>
@@ -4487,7 +4481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.75">
+    <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="15">
         <v>1010011380</v>
       </c>
@@ -4498,7 +4492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75">
+    <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="15">
         <v>351197</v>
       </c>
@@ -4509,7 +4503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75">
+    <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="15">
         <v>1010011286</v>
       </c>
@@ -4520,7 +4514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75">
+    <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="15">
         <v>2479</v>
       </c>
@@ -4531,7 +4525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75">
+    <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="15">
         <v>1010011382</v>
       </c>
@@ -4542,7 +4536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.75">
+    <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="16">
         <v>1010055703</v>
       </c>
@@ -4553,7 +4547,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75">
+    <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="16">
         <v>4165</v>
       </c>
@@ -4564,7 +4558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75">
+    <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="15">
         <v>301626</v>
       </c>
@@ -4575,7 +4569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75">
+    <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="15">
         <v>429495</v>
       </c>
@@ -4586,7 +4580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75">
+    <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="15">
         <v>162998</v>
       </c>
@@ -4597,7 +4591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.75">
+    <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="15">
         <v>432657</v>
       </c>
@@ -4608,7 +4602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.75">
+    <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="15">
         <v>1010021929</v>
       </c>
@@ -4619,7 +4613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75">
+    <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="15">
         <v>428065</v>
       </c>
@@ -4630,7 +4624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.75">
+    <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="15">
         <v>1010003404</v>
       </c>
@@ -4641,7 +4635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.75">
+    <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="15">
         <v>1010003322</v>
       </c>
@@ -4652,7 +4646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.75">
+    <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="15">
         <v>17738</v>
       </c>
@@ -4663,7 +4657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.75">
+    <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="15">
         <v>1010085360</v>
       </c>
@@ -4674,7 +4668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.75">
+    <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="15">
         <v>1040077391</v>
       </c>
@@ -4685,7 +4679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15.75">
+    <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="15">
         <v>1010058624</v>
       </c>
@@ -4696,7 +4690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.75">
+    <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="15">
         <v>1010024661</v>
       </c>
@@ -4707,7 +4701,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.75">
+    <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="15">
         <v>1040019315</v>
       </c>
@@ -4718,7 +4712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15.75">
+    <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="15">
         <v>1010021089</v>
       </c>
@@ -4729,7 +4723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.75">
+    <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="15">
         <v>1040017264</v>
       </c>
@@ -4740,7 +4734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.75">
+    <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="15">
         <v>1010051765</v>
       </c>
@@ -4751,7 +4745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.75">
+    <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="15">
         <v>1010035272</v>
       </c>
@@ -4762,7 +4756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.75">
+    <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="15">
         <v>1040077392</v>
       </c>
@@ -4773,7 +4767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15.75">
+    <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="15">
         <v>1040077393</v>
       </c>
@@ -4784,7 +4778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15.75">
+    <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="15">
         <v>1040077395</v>
       </c>
@@ -4795,7 +4789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15.75">
+    <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="15">
         <v>1040077401</v>
       </c>
@@ -4806,7 +4800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.75">
+    <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="15">
         <v>27572</v>
       </c>
@@ -4817,7 +4811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.75">
+    <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="15">
         <v>18745</v>
       </c>
@@ -4828,7 +4822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15.75">
+    <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="15">
         <v>1040077396</v>
       </c>
@@ -4839,7 +4833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15.75">
+    <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="15">
         <v>1010036546</v>
       </c>
@@ -4850,7 +4844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15.75">
+    <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="15">
         <v>1010014049</v>
       </c>
@@ -4861,7 +4855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15.75">
+    <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="15">
         <v>1010025148</v>
       </c>
@@ -4872,7 +4866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15.75">
+    <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="15">
         <v>1040077394</v>
       </c>
@@ -4883,7 +4877,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15.75">
+    <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="15">
         <v>1040077400</v>
       </c>
@@ -4894,7 +4888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15.75">
+    <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="15">
         <v>1040079329</v>
       </c>
@@ -4905,7 +4899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="15.75">
+    <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="15">
         <v>1040040957</v>
       </c>
@@ -4916,7 +4910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="15.75">
+    <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="15">
         <v>1040077398</v>
       </c>
@@ -4927,9 +4921,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="15.75">
+    <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="15">
-        <v>1010031545</v>
+        <v>1010053128</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>254</v>
@@ -4938,9 +4932,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="15.75">
+    <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="15">
-        <v>1010053128</v>
+        <v>1010010599</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>255</v>
@@ -4949,9 +4943,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="15.75">
+    <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="15">
-        <v>1010010599</v>
+        <v>1010056064</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>256</v>
@@ -4960,9 +4954,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="15.75">
+    <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="15">
-        <v>1010056064</v>
+        <v>5389</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>257</v>
@@ -4971,9 +4965,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="15.75">
+    <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="15">
-        <v>5389</v>
+        <v>1010055969</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>258</v>
@@ -4982,9 +4976,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="15.75">
+    <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="15">
-        <v>1010055969</v>
+        <v>1010055970</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>259</v>
@@ -4993,9 +4987,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="15.75">
+    <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="15">
-        <v>1010055970</v>
+        <v>181395</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>260</v>
@@ -5004,9 +4998,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="15.75">
-      <c r="A259" s="15">
-        <v>181395</v>
+    <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A259" s="17">
+        <v>1010055962</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>261</v>
@@ -5015,9 +5009,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="15.75">
-      <c r="A260" s="17">
-        <v>1010055962</v>
+    <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A260" s="15">
+        <v>1010003578</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>262</v>
@@ -5026,9 +5020,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="15.75">
+    <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="15">
-        <v>1010003578</v>
+        <v>332891</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>263</v>
@@ -5037,9 +5031,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="15.75">
+    <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="15">
-        <v>332891</v>
+        <v>17727</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>264</v>
@@ -5048,9 +5042,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15.75">
+    <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="15">
-        <v>17727</v>
+        <v>17918</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>265</v>
@@ -5059,9 +5053,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="15.75">
+    <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="15">
-        <v>17918</v>
+        <v>1010020554</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>266</v>
@@ -5070,9 +5064,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="15.75">
+    <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="15">
-        <v>1010020554</v>
+        <v>1040085949</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>267</v>
@@ -5081,9 +5075,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15.75">
+    <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="15">
-        <v>1040085949</v>
+        <v>1010062938</v>
       </c>
       <c r="B266" s="5" t="s">
         <v>268</v>
@@ -5092,9 +5086,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="15.75">
+    <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="15">
-        <v>1010062938</v>
+        <v>1010062086</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>269</v>
@@ -5103,9 +5097,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="15.75">
+    <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="15">
-        <v>1010062086</v>
+        <v>1010062087</v>
       </c>
       <c r="B268" s="5" t="s">
         <v>270</v>
@@ -5114,9 +5108,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="15.75">
+    <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="15">
-        <v>1010062087</v>
+        <v>1040077373</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>271</v>
@@ -5125,20 +5119,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="15.75">
-      <c r="A270" s="15">
-        <v>1040077373</v>
-      </c>
-      <c r="B270" s="5" t="s">
+    <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A270" s="24">
+        <v>1040077372</v>
+      </c>
+      <c r="B270" s="6" t="s">
         <v>272</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="15.75">
+    <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="24">
-        <v>1040077372</v>
+        <v>1040097154</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>273</v>
@@ -5147,9 +5141,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="15.75">
+    <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="24">
-        <v>1040097154</v>
+        <v>1010042579</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>274</v>
@@ -5158,20 +5152,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="15.75">
-      <c r="A273" s="24">
-        <v>1010042579</v>
-      </c>
-      <c r="B273" s="6" t="s">
+    <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A273" s="15">
+        <v>1010029427</v>
+      </c>
+      <c r="B273" s="5" t="s">
         <v>275</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="15.75">
+    <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="15">
-        <v>1010029427</v>
+        <v>133108</v>
       </c>
       <c r="B274" s="5" t="s">
         <v>276</v>
@@ -5180,9 +5174,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="15.75">
+    <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="15">
-        <v>133108</v>
+        <v>269427</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>277</v>
@@ -5191,9 +5185,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="15.75">
+    <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="15">
-        <v>269427</v>
+        <v>298227</v>
       </c>
       <c r="B276" s="5" t="s">
         <v>278</v>
@@ -5202,9 +5196,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="15.75">
+    <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="15">
-        <v>298227</v>
+        <v>1010062285</v>
       </c>
       <c r="B277" s="5" t="s">
         <v>279</v>
@@ -5213,9 +5207,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="15.75">
+    <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="15">
-        <v>1010062285</v>
+        <v>1010058052</v>
       </c>
       <c r="B278" s="5" t="s">
         <v>280</v>
@@ -5224,9 +5218,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="15.75">
+    <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="15">
-        <v>1010058052</v>
+        <v>1010050033</v>
       </c>
       <c r="B279" s="5" t="s">
         <v>281</v>
@@ -5235,9 +5229,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="15.75">
-      <c r="A280" s="15">
-        <v>1010050033</v>
+    <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A280" s="20">
+        <v>1040098869</v>
       </c>
       <c r="B280" s="5" t="s">
         <v>282</v>
@@ -5246,9 +5240,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="15.75">
+    <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="20">
-        <v>1040098869</v>
+        <v>1010056523</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>283</v>
@@ -5257,9 +5251,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="15.75">
+    <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="20">
-        <v>1010056523</v>
+        <v>1010062045</v>
       </c>
       <c r="B282" s="5" t="s">
         <v>284</v>
@@ -5268,9 +5262,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="15.75">
-      <c r="A283" s="20">
-        <v>1010062045</v>
+    <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A283" s="15">
+        <v>1040097575</v>
       </c>
       <c r="B283" s="5" t="s">
         <v>285</v>
@@ -5279,9 +5273,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="15.75">
-      <c r="A284" s="15">
-        <v>1040097575</v>
+    <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A284" s="5">
+        <v>1040100107</v>
       </c>
       <c r="B284" s="5" t="s">
         <v>286</v>
@@ -5290,9 +5284,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="15.75">
-      <c r="A285" s="5">
-        <v>1040100107</v>
+    <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A285" s="15">
+        <v>1010040346</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>287</v>
@@ -5301,9 +5295,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="15.75">
+    <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="15">
-        <v>1010040346</v>
+        <v>1010021543</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>288</v>
@@ -5312,9 +5306,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="15.75">
+    <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="15">
-        <v>1010021543</v>
+        <v>1040077397</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>289</v>
@@ -5323,9 +5317,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="15.75">
+    <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="15">
-        <v>1040077397</v>
+        <v>1040094213</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>290</v>
@@ -5334,9 +5328,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="15.75">
+    <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="15">
-        <v>1040094213</v>
+        <v>1010085326</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>291</v>
@@ -5345,9 +5339,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="15.75">
+    <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="15">
-        <v>1010085326</v>
+        <v>1010042564</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>292</v>
@@ -5356,9 +5350,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="15.75">
+    <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="15">
-        <v>1010042564</v>
+        <v>1010042688</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>293</v>
@@ -5367,9 +5361,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="15.75">
+    <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="15">
-        <v>1010042688</v>
+        <v>1010040133</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>294</v>
@@ -5378,9 +5372,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="15.75">
+    <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="15">
-        <v>1010040133</v>
+        <v>1010039879</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>295</v>
@@ -5389,9 +5383,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="15.75">
+    <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="15">
-        <v>1010039879</v>
+        <v>62608</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>296</v>
@@ -5400,9 +5394,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="15.75">
+    <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="15">
-        <v>62608</v>
+        <v>1040098603</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>297</v>
@@ -5411,9 +5405,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="15.75">
+    <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="15">
-        <v>1040098603</v>
+        <v>1040017266</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>298</v>
@@ -5422,9 +5416,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="15.75">
+    <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" s="15">
-        <v>1040017266</v>
+        <v>1010063326</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>299</v>
@@ -5433,9 +5427,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="15.75">
+    <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="15">
-        <v>1010063326</v>
+        <v>1010050574</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>300</v>
@@ -5444,9 +5438,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="15.75">
-      <c r="A299" s="15">
-        <v>1010050574</v>
+    <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A299" s="20">
+        <v>1010086126</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>301</v>
@@ -5455,9 +5449,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="15.75">
-      <c r="A300" s="20">
-        <v>1010086126</v>
+    <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A300" s="15">
+        <v>1040019838</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>302</v>
@@ -5466,9 +5460,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="15.75">
+    <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="15">
-        <v>1040019838</v>
+        <v>1010042882</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>303</v>
@@ -5477,9 +5471,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="15.75">
+    <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="15">
-        <v>1010042882</v>
+        <v>1010042873</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>304</v>
@@ -5488,9 +5482,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="15.75">
+    <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="15">
-        <v>1010042873</v>
+        <v>1010026842</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>305</v>
@@ -5499,9 +5493,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="15.75">
+    <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="15">
-        <v>1010026842</v>
+        <v>1010026841</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>306</v>
@@ -5510,9 +5504,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="15.75">
+    <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="15">
-        <v>1010026841</v>
+        <v>1010059549</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>307</v>
@@ -5521,9 +5515,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="15.75">
+    <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="15">
-        <v>1010059549</v>
+        <v>1010020552</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>308</v>
@@ -5532,9 +5526,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="15.75">
+    <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="15">
-        <v>1010020552</v>
+        <v>1040078895</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>309</v>
@@ -5543,9 +5537,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="15.75">
+    <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="15">
-        <v>1040078895</v>
+        <v>1040024309</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>310</v>
@@ -5554,9 +5548,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="15.75">
+    <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="15">
-        <v>1040024309</v>
+        <v>1040024323</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>311</v>
@@ -5565,9 +5559,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="15.75">
+    <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="15">
-        <v>1040024323</v>
+        <v>1040024322</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>312</v>
@@ -5576,9 +5570,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="15.75">
+    <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="15">
-        <v>1040024322</v>
+        <v>1010087245</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>313</v>
@@ -5587,9 +5581,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="15.75">
+    <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="15">
-        <v>1010087245</v>
+        <v>1010059685</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>314</v>
@@ -5598,9 +5592,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="15.75">
+    <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="15">
-        <v>1010059685</v>
+        <v>1010059687</v>
       </c>
       <c r="B313" s="5" t="s">
         <v>315</v>
@@ -5609,9 +5603,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="15.75">
+    <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="15">
-        <v>1010059687</v>
+        <v>1010077469</v>
       </c>
       <c r="B314" s="5" t="s">
         <v>316</v>
@@ -5620,9 +5614,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.75">
-      <c r="A315" s="15">
-        <v>1010077469</v>
+    <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A315" s="19">
+        <v>1010077470</v>
       </c>
       <c r="B315" s="5" t="s">
         <v>317</v>
@@ -5631,31 +5625,31 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="15.75">
-      <c r="A316" s="19">
-        <v>1010077470</v>
-      </c>
-      <c r="B316" s="5" t="s">
+    <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A316" s="15">
+        <v>1010084519</v>
+      </c>
+      <c r="B316" s="7" t="s">
         <v>318</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="15.75">
-      <c r="A317" s="15">
-        <v>1010084519</v>
-      </c>
-      <c r="B317" s="7" t="s">
+    <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A317" s="14">
+        <v>1010084108</v>
+      </c>
+      <c r="B317" s="5" t="s">
         <v>319</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.75">
+    <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="14">
-        <v>1010084108</v>
+        <v>1010042884</v>
       </c>
       <c r="B318" s="5" t="s">
         <v>320</v>
@@ -5664,9 +5658,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="15.75">
-      <c r="A319" s="14">
-        <v>1010042884</v>
+    <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A319" s="15">
+        <v>1040043537</v>
       </c>
       <c r="B319" s="5" t="s">
         <v>321</v>
@@ -5675,9 +5669,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="15.75">
+    <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="15">
-        <v>1040043537</v>
+        <v>1010046401</v>
       </c>
       <c r="B320" s="5" t="s">
         <v>322</v>
@@ -5686,9 +5680,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="15.75">
+    <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="15">
-        <v>1010046401</v>
+        <v>1010062007</v>
       </c>
       <c r="B321" s="5" t="s">
         <v>323</v>
@@ -5697,9 +5691,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="15.75">
+    <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="15">
-        <v>1010062007</v>
+        <v>1010051284</v>
       </c>
       <c r="B322" s="5" t="s">
         <v>324</v>
@@ -5708,9 +5702,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="15.75">
+    <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="15">
-        <v>1010051284</v>
+        <v>1010027788</v>
       </c>
       <c r="B323" s="5" t="s">
         <v>325</v>
@@ -5719,9 +5713,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="15.75">
+    <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="15">
-        <v>1010027788</v>
+        <v>1010027786</v>
       </c>
       <c r="B324" s="5" t="s">
         <v>326</v>
@@ -5730,9 +5724,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="15.75">
+    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="15">
-        <v>1010027786</v>
+        <v>1010026889</v>
       </c>
       <c r="B325" s="5" t="s">
         <v>327</v>
@@ -5741,9 +5735,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15.75">
-      <c r="A326" s="15">
-        <v>1010026889</v>
+    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A326" s="24">
+        <v>1010042358</v>
       </c>
       <c r="B326" s="5" t="s">
         <v>328</v>
@@ -5752,9 +5746,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15.75">
-      <c r="A327" s="24">
-        <v>1010042358</v>
+    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A327" s="15">
+        <v>1040023848</v>
       </c>
       <c r="B327" s="5" t="s">
         <v>329</v>
@@ -5763,9 +5757,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="15.75">
+    <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="15">
-        <v>1040023848</v>
+        <v>1010042341</v>
       </c>
       <c r="B328" s="5" t="s">
         <v>330</v>
@@ -5774,9 +5768,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="15.75">
+    <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="15">
-        <v>1010042341</v>
+        <v>1040023858</v>
       </c>
       <c r="B329" s="5" t="s">
         <v>331</v>
@@ -5785,9 +5779,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="15.75">
+    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="15">
-        <v>1040023858</v>
+        <v>1040098396</v>
       </c>
       <c r="B330" s="5" t="s">
         <v>332</v>
@@ -5796,9 +5790,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="15.75">
+    <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="15">
-        <v>1040098396</v>
+        <v>1010087281</v>
       </c>
       <c r="B331" s="5" t="s">
         <v>333</v>
@@ -5807,9 +5801,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="15.75">
+    <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="15">
-        <v>1010087281</v>
+        <v>1040041006</v>
       </c>
       <c r="B332" s="5" t="s">
         <v>334</v>
@@ -5818,9 +5812,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="15.75">
+    <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="15">
-        <v>1040041006</v>
+        <v>1040101931</v>
       </c>
       <c r="B333" s="5" t="s">
         <v>335</v>
@@ -5829,9 +5823,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="15.75">
+    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="15">
-        <v>1040101931</v>
+        <v>1040023843</v>
       </c>
       <c r="B334" s="5" t="s">
         <v>336</v>
@@ -5840,9 +5834,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="15.75">
+    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="15">
-        <v>1040023843</v>
+        <v>1040077411</v>
       </c>
       <c r="B335" s="5" t="s">
         <v>337</v>
@@ -5851,9 +5845,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.75">
+    <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="15">
-        <v>1040077411</v>
+        <v>1040077410</v>
       </c>
       <c r="B336" s="5" t="s">
         <v>338</v>
@@ -5862,9 +5856,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="15.75">
+    <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="15">
-        <v>1040077410</v>
+        <v>1010062008</v>
       </c>
       <c r="B337" s="5" t="s">
         <v>339</v>
@@ -5873,9 +5867,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="15.75">
-      <c r="A338" s="15">
-        <v>1010062008</v>
+    <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A338" s="19">
+        <v>1040040960</v>
       </c>
       <c r="B338" s="5" t="s">
         <v>340</v>
@@ -5884,20 +5878,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="15.75">
-      <c r="A339" s="19">
-        <v>1040040960</v>
-      </c>
-      <c r="B339" s="5" t="s">
+    <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A339" s="15">
+        <v>1010031536</v>
+      </c>
+      <c r="B339" s="7" t="s">
         <v>341</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="15.75">
+    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="15">
-        <v>1010031536</v>
+        <v>1010031545</v>
       </c>
       <c r="B340" s="7" t="s">
         <v>342</v>
@@ -5906,20 +5900,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="15.75">
-      <c r="A341" s="15">
-        <v>1010031545</v>
-      </c>
-      <c r="B341" s="7" t="s">
+    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A341" s="30">
+        <v>1010084767</v>
+      </c>
+      <c r="B341" s="5" t="s">
         <v>343</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="15.75">
-      <c r="A342" s="30">
-        <v>1010084767</v>
+    <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A342" s="15">
+        <v>1040077360</v>
       </c>
       <c r="B342" s="5" t="s">
         <v>344</v>
@@ -5928,9 +5922,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="15.75">
+    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="15">
-        <v>1040077360</v>
+        <v>1010064470</v>
       </c>
       <c r="B343" s="5" t="s">
         <v>345</v>
@@ -5939,9 +5933,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="15.75">
+    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="15">
-        <v>1010064470</v>
+        <v>1010021991</v>
       </c>
       <c r="B344" s="5" t="s">
         <v>346</v>
@@ -5950,9 +5944,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="15.75">
+    <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="15">
-        <v>1010021991</v>
+        <v>1010021960</v>
       </c>
       <c r="B345" s="5" t="s">
         <v>347</v>
@@ -5961,9 +5955,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="15.75">
+    <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="15">
-        <v>1010021960</v>
+        <v>1010031690</v>
       </c>
       <c r="B346" s="5" t="s">
         <v>348</v>
@@ -5972,9 +5966,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="15.75">
+    <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="15">
-        <v>1010031545</v>
+        <v>1010022590</v>
       </c>
       <c r="B347" s="5" t="s">
         <v>349</v>
@@ -5983,9 +5977,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="15.75">
+    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="15">
-        <v>1010031690</v>
+        <v>1040098643</v>
       </c>
       <c r="B348" s="5" t="s">
         <v>350</v>
@@ -5994,9 +5988,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="15.75">
+    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="15">
-        <v>1010022590</v>
+        <v>1010086020</v>
       </c>
       <c r="B349" s="5" t="s">
         <v>351</v>
@@ -6005,9 +5999,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="15.75">
+    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="15">
-        <v>1040098643</v>
+        <v>1010046550</v>
       </c>
       <c r="B350" s="5" t="s">
         <v>352</v>
@@ -6016,9 +6010,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="15.75">
+    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="15">
-        <v>1010086020</v>
+        <v>1010046402</v>
       </c>
       <c r="B351" s="5" t="s">
         <v>353</v>
@@ -6027,9 +6021,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="15.75">
+    <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="15">
-        <v>1010046550</v>
+        <v>1010060291</v>
       </c>
       <c r="B352" s="5" t="s">
         <v>354</v>
@@ -6038,9 +6032,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.75">
+    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="15">
-        <v>1010046402</v>
+        <v>1010050920</v>
       </c>
       <c r="B353" s="5" t="s">
         <v>355</v>
@@ -6049,9 +6043,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.75">
+    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="15">
-        <v>1010060291</v>
+        <v>1040077412</v>
       </c>
       <c r="B354" s="5" t="s">
         <v>356</v>
@@ -6060,9 +6054,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="15.75">
+    <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="15">
-        <v>1010050920</v>
+        <v>1010042609</v>
       </c>
       <c r="B355" s="5" t="s">
         <v>357</v>
@@ -6071,9 +6065,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="15.75">
+    <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="15">
-        <v>1040077412</v>
+        <v>417701</v>
       </c>
       <c r="B356" s="5" t="s">
         <v>358</v>
@@ -6082,9 +6076,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75">
+    <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="15">
-        <v>1010042609</v>
+        <v>399384</v>
       </c>
       <c r="B357" s="5" t="s">
         <v>359</v>
@@ -6093,9 +6087,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="15.75">
+    <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="15">
-        <v>417701</v>
+        <v>1010024086</v>
       </c>
       <c r="B358" s="5" t="s">
         <v>360</v>
@@ -6104,9 +6098,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="15.75">
+    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="15">
-        <v>399384</v>
+        <v>1040077345</v>
       </c>
       <c r="B359" s="5" t="s">
         <v>361</v>
@@ -6115,9 +6109,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="15.75">
+    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="15">
-        <v>1010024086</v>
+        <v>1010084315</v>
       </c>
       <c r="B360" s="5" t="s">
         <v>362</v>
@@ -6126,9 +6120,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="15.75">
+    <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="15">
-        <v>1040077345</v>
+        <v>399253</v>
       </c>
       <c r="B361" s="5" t="s">
         <v>363</v>
@@ -6137,9 +6131,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="15.75">
+    <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="15">
-        <v>1010084315</v>
+        <v>1010084317</v>
       </c>
       <c r="B362" s="5" t="s">
         <v>364</v>
@@ -6148,9 +6142,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="15.75">
-      <c r="A363" s="15">
-        <v>399253</v>
+    <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A363" s="25">
+        <v>1010085369</v>
       </c>
       <c r="B363" s="5" t="s">
         <v>365</v>
@@ -6159,9 +6153,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="15.75">
+    <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="15">
-        <v>1010084317</v>
+        <v>1010085370</v>
       </c>
       <c r="B364" s="5" t="s">
         <v>366</v>
@@ -6170,9 +6164,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="15.75">
-      <c r="A365" s="25">
-        <v>1010085369</v>
+    <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A365" s="15">
+        <v>1010085204</v>
       </c>
       <c r="B365" s="5" t="s">
         <v>367</v>
@@ -6181,9 +6175,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="15.75">
+    <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="15">
-        <v>1010085370</v>
+        <v>1010003966</v>
       </c>
       <c r="B366" s="5" t="s">
         <v>368</v>
@@ -6192,9 +6186,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="15.75">
+    <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="15">
-        <v>1010085204</v>
+        <v>1010003967</v>
       </c>
       <c r="B367" s="5" t="s">
         <v>369</v>
@@ -6203,9 +6197,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="15.75">
+    <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="15">
-        <v>1010003966</v>
+        <v>65219</v>
       </c>
       <c r="B368" s="5" t="s">
         <v>370</v>
@@ -6214,9 +6208,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="15.75">
+    <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="15">
-        <v>1010003967</v>
+        <v>10168</v>
       </c>
       <c r="B369" s="5" t="s">
         <v>371</v>
@@ -6225,9 +6219,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="15.75">
+    <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="15">
-        <v>65219</v>
+        <v>1010083792</v>
       </c>
       <c r="B370" s="5" t="s">
         <v>372</v>
@@ -6236,9 +6230,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="15.75">
+    <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="15">
-        <v>10168</v>
+        <v>1040077414</v>
       </c>
       <c r="B371" s="5" t="s">
         <v>373</v>
@@ -6247,9 +6241,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="15.75">
+    <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="15">
-        <v>1010083792</v>
+        <v>1010018482</v>
       </c>
       <c r="B372" s="5" t="s">
         <v>374</v>
@@ -6258,9 +6252,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="15.75">
+    <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="15">
-        <v>1040077414</v>
+        <v>1010084320</v>
       </c>
       <c r="B373" s="5" t="s">
         <v>375</v>
@@ -6269,9 +6263,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="15.75">
+    <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="15">
-        <v>1010018482</v>
+        <v>1010084532</v>
       </c>
       <c r="B374" s="5" t="s">
         <v>376</v>
@@ -6280,9 +6274,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="15.75">
+    <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="15">
-        <v>1010084320</v>
+        <v>1010027285</v>
       </c>
       <c r="B375" s="5" t="s">
         <v>377</v>
@@ -6291,9 +6285,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="15.75">
+    <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" s="15">
-        <v>1010084532</v>
+        <v>1040077413</v>
       </c>
       <c r="B376" s="5" t="s">
         <v>378</v>
@@ -6302,9 +6296,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="15.75">
+    <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="15">
-        <v>1010027285</v>
+        <v>1010085376</v>
       </c>
       <c r="B377" s="5" t="s">
         <v>379</v>
@@ -6313,9 +6307,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="15.75">
+    <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="15">
-        <v>1040077413</v>
+        <v>1010022819</v>
       </c>
       <c r="B378" s="5" t="s">
         <v>380</v>
@@ -6324,9 +6318,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="15.75">
+    <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="15">
-        <v>1010085376</v>
+        <v>1010052853</v>
       </c>
       <c r="B379" s="5" t="s">
         <v>381</v>
@@ -6335,9 +6329,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="15.75">
+    <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="15">
-        <v>1010022819</v>
+        <v>1010084377</v>
       </c>
       <c r="B380" s="5" t="s">
         <v>382</v>
@@ -6346,4178 +6340,4156 @@
         <v>4</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="15.75">
-      <c r="A381" s="15">
-        <v>1010052853</v>
+    <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A381" s="26">
+        <v>1010062826</v>
       </c>
       <c r="B381" s="5" t="s">
         <v>383</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" ht="15.75">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="15">
-        <v>1010084377</v>
+        <v>1010002592</v>
       </c>
       <c r="B382" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C382" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="C382" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="15.75">
-      <c r="A383" s="26">
-        <v>1010062826</v>
+    </row>
+    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A383" s="24">
+        <v>1010001155</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" ht="15.75">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="15">
-        <v>1010002592</v>
+        <v>1010001062</v>
       </c>
       <c r="B384" s="5" t="s">
         <v>387</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4" ht="15.75">
-      <c r="A385" s="24">
-        <v>1010001155</v>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A385" s="15">
+        <v>1010084328</v>
       </c>
       <c r="B385" s="5" t="s">
         <v>388</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" ht="15.75">
-      <c r="A386" s="15">
-        <v>1010001062</v>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A386" s="24">
+        <v>1010044502</v>
       </c>
       <c r="B386" s="5" t="s">
         <v>389</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" ht="15.75">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="15">
-        <v>1010084328</v>
+        <v>1010053692</v>
       </c>
       <c r="B387" s="5" t="s">
         <v>390</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="388" spans="1:4" ht="15.75">
-      <c r="A388" s="24">
-        <v>1010044502</v>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A388" s="15">
+        <v>1010083992</v>
       </c>
       <c r="B388" s="5" t="s">
         <v>391</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" ht="15.75">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="15">
-        <v>1010053692</v>
+        <v>1010008578</v>
       </c>
       <c r="B389" s="5" t="s">
         <v>392</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="15">
-        <v>1010083992</v>
+        <v>1010031694</v>
       </c>
       <c r="B390" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C390" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C390" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4" ht="15.75">
+    </row>
+    <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="15">
-        <v>1010008578</v>
+        <v>1010051997</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="15">
-        <v>1010031694</v>
+        <v>1010022601</v>
       </c>
       <c r="B392" s="5" t="s">
         <v>396</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="393" spans="1:4" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="15">
-        <v>1010051997</v>
+        <v>1010054278</v>
       </c>
       <c r="B393" s="5" t="s">
         <v>397</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="394" spans="1:4" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="15">
-        <v>1010022601</v>
+        <v>1010083462</v>
       </c>
       <c r="B394" s="5" t="s">
         <v>398</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="395" spans="1:4" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="15">
-        <v>1010054278</v>
+        <v>1010027772</v>
       </c>
       <c r="B395" s="5" t="s">
         <v>399</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="396" spans="1:4" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="15">
-        <v>1010083462</v>
+        <v>1010084144</v>
       </c>
       <c r="B396" s="5" t="s">
         <v>400</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="397" spans="1:4" ht="15.75">
-      <c r="A397" s="15">
-        <v>1010027772</v>
-      </c>
-      <c r="B397" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A397" s="19">
+        <v>214055</v>
+      </c>
+      <c r="B397" s="7" t="s">
         <v>401</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="398" spans="1:4" ht="15.75">
-      <c r="A398" s="15">
-        <v>1010084144</v>
-      </c>
-      <c r="B398" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A398" s="19">
+        <v>1010084720</v>
+      </c>
+      <c r="B398" s="7" t="s">
         <v>402</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4" ht="15.75">
-      <c r="A399" s="19">
-        <v>214055</v>
+        <v>393</v>
+      </c>
+      <c r="D398" s="29"/>
+    </row>
+    <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A399" s="18">
+        <v>1010021956</v>
       </c>
       <c r="B399" s="7" t="s">
         <v>403</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="D399" s="29"/>
-    </row>
-    <row r="400" spans="1:4" ht="15.75">
-      <c r="A400" s="19">
-        <v>1010084720</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A400" s="18">
+        <v>1010026464</v>
       </c>
       <c r="B400" s="7" t="s">
         <v>404</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" ht="15.75">
-      <c r="A401" s="18">
-        <v>1010021956</v>
-      </c>
-      <c r="B401" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A401" s="14">
+        <v>1010021957</v>
+      </c>
+      <c r="B401" s="5" t="s">
         <v>405</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" ht="15.75">
-      <c r="A402" s="18">
-        <v>1010026464</v>
-      </c>
-      <c r="B402" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A402" s="15">
+        <v>1010026462</v>
+      </c>
+      <c r="B402" s="5" t="s">
         <v>406</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" ht="15.75">
-      <c r="A403" s="14">
-        <v>1010021957</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A403" s="15">
+        <v>1010026551</v>
       </c>
       <c r="B403" s="5" t="s">
         <v>407</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="15">
-        <v>1010026462</v>
+        <v>1010042554</v>
       </c>
       <c r="B404" s="5" t="s">
         <v>408</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="15">
-        <v>1010026551</v>
+        <v>1010039904</v>
       </c>
       <c r="B405" s="5" t="s">
         <v>409</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="15">
-        <v>1010042554</v>
+        <v>1010060205</v>
       </c>
       <c r="B406" s="5" t="s">
         <v>410</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="15">
-        <v>1010039904</v>
+        <v>1010060206</v>
       </c>
       <c r="B407" s="5" t="s">
         <v>411</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="15">
-        <v>1010060205</v>
+        <v>1010077431</v>
       </c>
       <c r="B408" s="5" t="s">
         <v>412</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="15">
-        <v>1010060206</v>
+        <v>1010077503</v>
       </c>
       <c r="B409" s="5" t="s">
         <v>413</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="15">
-        <v>1010077431</v>
+        <v>1010084187</v>
       </c>
       <c r="B410" s="5" t="s">
         <v>414</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="15">
-        <v>1010077503</v>
+        <v>1010080958</v>
       </c>
       <c r="B411" s="5" t="s">
         <v>415</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="15">
-        <v>1010084187</v>
+        <v>1010026032</v>
       </c>
       <c r="B412" s="5" t="s">
         <v>416</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="15">
-        <v>1010080958</v>
+        <v>1010085384</v>
       </c>
       <c r="B413" s="5" t="s">
         <v>417</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="15">
-        <v>1010026032</v>
+        <v>1010006347</v>
       </c>
       <c r="B414" s="5" t="s">
         <v>418</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="15">
-        <v>1010085384</v>
+        <v>1010085179</v>
       </c>
       <c r="B415" s="5" t="s">
         <v>419</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="15">
-        <v>1010006347</v>
-      </c>
-      <c r="B416" s="5" t="s">
+        <v>1010024158</v>
+      </c>
+      <c r="B416" s="8" t="s">
         <v>420</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="15">
-        <v>1010085179</v>
-      </c>
-      <c r="B417" s="5" t="s">
+        <v>1010024131</v>
+      </c>
+      <c r="B417" s="8" t="s">
         <v>421</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="15">
-        <v>1010024158</v>
-      </c>
-      <c r="B418" s="8" t="s">
+        <v>1010007160</v>
+      </c>
+      <c r="B418" s="5" t="s">
         <v>422</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="15">
-        <v>1010024131</v>
-      </c>
-      <c r="B419" s="8" t="s">
+        <v>1010023642</v>
+      </c>
+      <c r="B419" s="5" t="s">
         <v>423</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="15">
-        <v>1010007160</v>
-      </c>
-      <c r="B420" s="5" t="s">
+        <v>1010007193</v>
+      </c>
+      <c r="B420" s="6" t="s">
         <v>424</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="15">
-        <v>1010023642</v>
+        <v>1010042637</v>
       </c>
       <c r="B421" s="5" t="s">
         <v>425</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="15">
-        <v>1010007193</v>
-      </c>
-      <c r="B422" s="6" t="s">
+        <v>1040075323</v>
+      </c>
+      <c r="B422" s="5" t="s">
         <v>426</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="15">
-        <v>1010042637</v>
-      </c>
-      <c r="B423" s="5" t="s">
+        <v>1040075324</v>
+      </c>
+      <c r="B423" s="8" t="s">
         <v>427</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" ht="15.75">
-      <c r="A424" s="15">
-        <v>1040075323</v>
-      </c>
-      <c r="B424" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A424" s="27">
+        <v>1040074827</v>
+      </c>
+      <c r="B424" s="8" t="s">
         <v>428</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="15.75">
-      <c r="A425" s="15">
-        <v>1040075324</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A425" s="27">
+        <v>1040099488</v>
       </c>
       <c r="B425" s="8" t="s">
         <v>429</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="27">
-        <v>1040074827</v>
+        <v>1040083312</v>
       </c>
       <c r="B426" s="8" t="s">
         <v>430</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="27">
-        <v>1040099488</v>
+        <v>1040077661</v>
       </c>
       <c r="B427" s="8" t="s">
         <v>431</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="27">
-        <v>1040083312</v>
-      </c>
-      <c r="B428" s="8" t="s">
+        <v>1010085180</v>
+      </c>
+      <c r="B428" s="12" t="s">
         <v>432</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="15.75">
-      <c r="A429" s="27">
-        <v>1040077661</v>
-      </c>
-      <c r="B429" s="8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A429" s="14">
+        <v>1040017489</v>
+      </c>
+      <c r="B429" s="9" t="s">
         <v>433</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="15.75">
-      <c r="A430" s="27">
-        <v>1010085180</v>
-      </c>
-      <c r="B430" s="12" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A430" s="14">
+        <v>1010085181</v>
+      </c>
+      <c r="B430" s="5" t="s">
         <v>434</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15.75">
-      <c r="A431" s="14">
-        <v>1040017489</v>
-      </c>
-      <c r="B431" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A431" s="15">
+        <v>400175</v>
+      </c>
+      <c r="B431" s="5" t="s">
         <v>435</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75">
-      <c r="A432" s="14">
-        <v>1010085181</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A432" s="15">
+        <v>1040017505</v>
       </c>
       <c r="B432" s="5" t="s">
         <v>436</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="15">
-        <v>400175</v>
+        <v>1040017503</v>
       </c>
       <c r="B433" s="5" t="s">
         <v>437</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="15">
-        <v>1040017505</v>
+        <v>1010046445</v>
       </c>
       <c r="B434" s="5" t="s">
         <v>438</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="15">
-        <v>1040017503</v>
+        <v>1010021033</v>
       </c>
       <c r="B435" s="5" t="s">
         <v>439</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="15">
-        <v>1010046445</v>
+        <v>1010057142</v>
       </c>
       <c r="B436" s="5" t="s">
         <v>440</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="15">
-        <v>1010021033</v>
+        <v>1010016356</v>
       </c>
       <c r="B437" s="5" t="s">
         <v>441</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="15">
-        <v>1010057142</v>
+        <v>1010084363</v>
       </c>
       <c r="B438" s="5" t="s">
         <v>442</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="15">
-        <v>1010016356</v>
+        <v>1010052021</v>
       </c>
       <c r="B439" s="5" t="s">
         <v>443</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="15">
-        <v>1010084363</v>
+        <v>1040091721</v>
       </c>
       <c r="B440" s="5" t="s">
         <v>444</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="15">
-        <v>1010052021</v>
+        <v>1010062022</v>
       </c>
       <c r="B441" s="5" t="s">
         <v>445</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="15">
-        <v>1040091721</v>
+        <v>18336</v>
       </c>
       <c r="B442" s="5" t="s">
         <v>446</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="15">
-        <v>1010062022</v>
+        <v>229205</v>
       </c>
       <c r="B443" s="5" t="s">
         <v>447</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="15">
-        <v>18336</v>
+        <v>60671</v>
       </c>
       <c r="B444" s="5" t="s">
         <v>448</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="15">
-        <v>229205</v>
+        <v>1010059726</v>
       </c>
       <c r="B445" s="5" t="s">
         <v>449</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="15">
-        <v>60671</v>
+        <v>1010008144</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>450</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="15">
-        <v>1010059726</v>
+        <v>1010007244</v>
       </c>
       <c r="B447" s="5" t="s">
         <v>451</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="15">
-        <v>1010008144</v>
+        <v>1010006827</v>
       </c>
       <c r="B448" s="5" t="s">
         <v>452</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="15">
-        <v>1010007244</v>
+        <v>1040075426</v>
       </c>
       <c r="B449" s="5" t="s">
         <v>453</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="15">
-        <v>1010006827</v>
+        <v>1040075427</v>
       </c>
       <c r="B450" s="5" t="s">
         <v>454</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="15">
-        <v>1040075426</v>
+        <v>1010084313</v>
       </c>
       <c r="B451" s="5" t="s">
         <v>455</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="15">
-        <v>1040075427</v>
+        <v>403459</v>
       </c>
       <c r="B452" s="5" t="s">
         <v>456</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="15">
-        <v>1010084313</v>
+        <v>1010044828</v>
       </c>
       <c r="B453" s="5" t="s">
         <v>457</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" s="15">
-        <v>403459</v>
+        <v>1010026973</v>
       </c>
       <c r="B454" s="5" t="s">
         <v>458</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" ht="15.75">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="15">
-        <v>1010044828</v>
+        <v>1040017204</v>
       </c>
       <c r="B455" s="5" t="s">
         <v>459</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" ht="15.75">
-      <c r="A456" s="15">
-        <v>1010026973</v>
-      </c>
-      <c r="B456" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A456" s="24">
+        <v>1010022119</v>
+      </c>
+      <c r="B456" s="6" t="s">
         <v>460</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="15">
-        <v>1040017204</v>
+        <v>1010058709</v>
       </c>
       <c r="B457" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C457" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="C457" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="15.75">
-      <c r="A458" s="24">
-        <v>1010022119</v>
-      </c>
-      <c r="B458" s="6" t="s">
-        <v>462</v>
+    </row>
+    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A458" s="15">
+        <v>1010025711</v>
+      </c>
+      <c r="B458" s="5" t="s">
+        <v>463</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="15">
-        <v>1010058709</v>
+        <v>1010059684</v>
       </c>
       <c r="B459" s="5" t="s">
         <v>464</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" s="15">
-        <v>1010025711</v>
+        <v>427341</v>
       </c>
       <c r="B460" s="5" t="s">
         <v>465</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" s="15">
-        <v>1010059684</v>
+        <v>1010085279</v>
       </c>
       <c r="B461" s="5" t="s">
         <v>466</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" ht="15.75">
-      <c r="A462" s="15">
-        <v>427341</v>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A462" s="19">
+        <v>1010022588</v>
       </c>
       <c r="B462" s="5" t="s">
         <v>467</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="15">
-        <v>1010085279</v>
-      </c>
-      <c r="B463" s="5" t="s">
+        <v>1010026864</v>
+      </c>
+      <c r="B463" s="7" t="s">
         <v>468</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" ht="15.75">
-      <c r="A464" s="19">
-        <v>1010022588</v>
-      </c>
-      <c r="B464" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A464" s="14">
+        <v>1010030946</v>
+      </c>
+      <c r="B464" s="7" t="s">
         <v>469</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" ht="15.75">
-      <c r="A465" s="15">
-        <v>1010026864</v>
-      </c>
-      <c r="B465" s="7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A465" s="14">
+        <v>1010022589</v>
+      </c>
+      <c r="B465" s="5" t="s">
         <v>470</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" ht="15.75">
-      <c r="A466" s="14">
-        <v>1010030946</v>
-      </c>
-      <c r="B466" s="7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A466" s="15">
+        <v>1040090143</v>
+      </c>
+      <c r="B466" s="5" t="s">
         <v>471</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="15.75">
-      <c r="A467" s="14">
-        <v>1010022589</v>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A467" s="15">
+        <v>1040090138</v>
       </c>
       <c r="B467" s="5" t="s">
         <v>472</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="15">
-        <v>1040090143</v>
+        <v>1030001314</v>
       </c>
       <c r="B468" s="5" t="s">
         <v>473</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="15">
-        <v>1040090138</v>
+        <v>1010052319</v>
       </c>
       <c r="B469" s="5" t="s">
         <v>474</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="15">
-        <v>1030001314</v>
+        <v>1010052320</v>
       </c>
       <c r="B470" s="5" t="s">
         <v>475</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="15">
-        <v>1010052319</v>
+        <v>1030000370</v>
       </c>
       <c r="B471" s="5" t="s">
         <v>476</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="15">
-        <v>1010052320</v>
+        <v>1030000366</v>
       </c>
       <c r="B472" s="5" t="s">
         <v>477</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="15">
-        <v>1030000370</v>
+        <v>1030000368</v>
       </c>
       <c r="B473" s="5" t="s">
         <v>478</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="15">
-        <v>1030000366</v>
+        <v>1030000369</v>
       </c>
       <c r="B474" s="5" t="s">
         <v>479</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="15">
-        <v>1030000368</v>
+        <v>1030000489</v>
       </c>
       <c r="B475" s="5" t="s">
         <v>480</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="15">
-        <v>1030000369</v>
+        <v>1030000490</v>
       </c>
       <c r="B476" s="5" t="s">
         <v>481</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="15">
-        <v>1030000489</v>
+        <v>1030000821</v>
       </c>
       <c r="B477" s="5" t="s">
         <v>482</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" ht="15.75">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" s="15">
-        <v>1030000490</v>
-      </c>
-      <c r="B478" s="5" t="s">
+        <v>1030000511</v>
+      </c>
+      <c r="B478" s="8" t="s">
         <v>483</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="15.75">
-      <c r="A479" s="15">
-        <v>1030000821</v>
-      </c>
-      <c r="B479" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A479" s="16">
+        <v>1010084279</v>
+      </c>
+      <c r="B479" s="8" t="s">
         <v>484</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="15.75">
-      <c r="A480" s="15">
-        <v>1030000511</v>
-      </c>
-      <c r="B480" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A480" s="16">
+        <v>1010004281</v>
+      </c>
+      <c r="B480" s="5" t="s">
         <v>485</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" ht="15.75">
-      <c r="A481" s="16">
-        <v>1010084279</v>
-      </c>
-      <c r="B481" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A481" s="15">
+        <v>1010022118</v>
+      </c>
+      <c r="B481" s="9" t="s">
         <v>486</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" ht="15.75">
-      <c r="A482" s="16">
-        <v>1010004281</v>
+        <v>461</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A482" s="15">
+        <v>1010028657</v>
       </c>
       <c r="B482" s="5" t="s">
         <v>487</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.75">
-      <c r="A483" s="15">
-        <v>1010022118</v>
-      </c>
-      <c r="B483" s="9" t="s">
         <v>488</v>
       </c>
+    </row>
+    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A483" s="18">
+        <v>1010028655</v>
+      </c>
+      <c r="B483" s="5" t="s">
+        <v>489</v>
+      </c>
       <c r="C483" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" ht="15.75">
-      <c r="A484" s="15">
-        <v>1010028657</v>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A484" s="18">
+        <v>145165</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" ht="15.75">
-      <c r="A485" s="18">
-        <v>1010028655</v>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A485" s="15">
+        <v>51666</v>
       </c>
       <c r="B485" s="5" t="s">
         <v>491</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="18">
-        <v>145165</v>
+        <v>1010080930</v>
       </c>
       <c r="B486" s="5" t="s">
         <v>492</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="15">
-        <v>51666</v>
+        <v>161055</v>
       </c>
       <c r="B487" s="5" t="s">
         <v>493</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" ht="15.75">
-      <c r="A488" s="18">
-        <v>1010080930</v>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A488" s="15">
+        <v>1010050517</v>
       </c>
       <c r="B488" s="5" t="s">
         <v>494</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="15">
-        <v>161055</v>
+        <v>1010084190</v>
       </c>
       <c r="B489" s="5" t="s">
         <v>495</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="15">
-        <v>1010050517</v>
+        <v>1010084195</v>
       </c>
       <c r="B490" s="5" t="s">
         <v>496</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="15">
-        <v>1010084190</v>
+        <v>1010001400</v>
       </c>
       <c r="B491" s="5" t="s">
         <v>497</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" ht="15.75">
-      <c r="A492" s="15">
-        <v>1010084195</v>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A492" s="17">
+        <v>1010008416</v>
       </c>
       <c r="B492" s="5" t="s">
         <v>498</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" ht="15.75">
-      <c r="A493" s="15">
-        <v>1010001400</v>
+        <v>488</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A493" s="28">
+        <v>1010018372</v>
       </c>
       <c r="B493" s="5" t="s">
         <v>499</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" ht="15.75">
-      <c r="A494" s="17">
-        <v>1010008416</v>
-      </c>
-      <c r="B494" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A494" s="28">
+        <v>1010018361</v>
+      </c>
+      <c r="B494" s="8" t="s">
         <v>500</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" ht="15.75">
-      <c r="A495" s="28">
-        <v>1010018372</v>
-      </c>
-      <c r="B495" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A495" s="16">
+        <v>1010055398</v>
+      </c>
+      <c r="B495" s="11" t="s">
         <v>501</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" ht="15.75">
-      <c r="A496" s="28">
-        <v>1010018361</v>
-      </c>
-      <c r="B496" s="8" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A496" s="15">
+        <v>422131</v>
+      </c>
+      <c r="B496" s="5" t="s">
         <v>502</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" ht="15.75">
-      <c r="A497" s="16">
-        <v>1010055398</v>
-      </c>
-      <c r="B497" s="11" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A497" s="15">
+        <v>1010084370</v>
+      </c>
+      <c r="B497" s="5" t="s">
         <v>503</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" s="15">
-        <v>422131</v>
+        <v>422759</v>
       </c>
       <c r="B498" s="5" t="s">
         <v>504</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="15">
-        <v>1010084370</v>
+        <v>120955</v>
       </c>
       <c r="B499" s="5" t="s">
         <v>505</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" s="15">
-        <v>422759</v>
+        <v>1010000896</v>
       </c>
       <c r="B500" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="C500" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" ht="15.75">
+      <c r="C500" s="13" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="15">
-        <v>120955</v>
+        <v>1010084308</v>
       </c>
       <c r="B501" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="C501" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" ht="15.75">
+      <c r="C501" s="13" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" s="15">
-        <v>1010000896</v>
+        <v>1010084035</v>
       </c>
       <c r="B502" s="5" t="s">
         <v>508</v>
       </c>
       <c r="C502" s="13" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" ht="15.75">
-      <c r="A503" s="15">
-        <v>1010084308</v>
-      </c>
-      <c r="B503" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C503" s="13" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" ht="15.75">
-      <c r="A504" s="15">
-        <v>1010084035</v>
-      </c>
-      <c r="B504" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="C504" s="13" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" ht="15.75">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A503" s="2"/>
+      <c r="B503" s="2"/>
+    </row>
+    <row r="504" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A504" s="2"/>
+      <c r="B504" s="2"/>
+    </row>
+    <row r="505" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
     </row>
-    <row r="506" spans="1:3" ht="15.75">
+    <row r="506" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
     </row>
-    <row r="507" spans="1:3" ht="15.75">
+    <row r="507" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
     </row>
-    <row r="508" spans="1:3" ht="15.75">
+    <row r="508" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
     </row>
-    <row r="509" spans="1:3" ht="15.75">
+    <row r="509" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
     </row>
-    <row r="510" spans="1:3" ht="15.75">
+    <row r="510" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
     </row>
-    <row r="511" spans="1:3" ht="15.75">
+    <row r="511" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
     </row>
-    <row r="512" spans="1:3" ht="15.75">
+    <row r="512" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
     </row>
-    <row r="513" spans="1:2" ht="15.75">
+    <row r="513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
     </row>
-    <row r="514" spans="1:2" ht="15.75">
+    <row r="514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
     </row>
-    <row r="515" spans="1:2" ht="15.75">
+    <row r="515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
     </row>
-    <row r="516" spans="1:2" ht="15.75">
+    <row r="516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
     </row>
-    <row r="517" spans="1:2" ht="15.75">
+    <row r="517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
     </row>
-    <row r="518" spans="1:2" ht="15.75">
+    <row r="518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
     </row>
-    <row r="519" spans="1:2" ht="15.75">
+    <row r="519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
     </row>
-    <row r="520" spans="1:2" ht="15.75">
+    <row r="520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
     </row>
-    <row r="521" spans="1:2" ht="15.75">
+    <row r="521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
     </row>
-    <row r="522" spans="1:2" ht="15.75">
+    <row r="522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="1:2" ht="15.75">
+    <row r="523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
     </row>
-    <row r="524" spans="1:2" ht="15.75">
+    <row r="524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
     </row>
-    <row r="525" spans="1:2" ht="15.75">
+    <row r="525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
     </row>
-    <row r="526" spans="1:2" ht="15.75">
+    <row r="526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
     </row>
-    <row r="527" spans="1:2" ht="15.75">
+    <row r="527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
     </row>
-    <row r="528" spans="1:2" ht="15.75">
+    <row r="528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
     </row>
-    <row r="529" spans="1:2" ht="15.75">
+    <row r="529" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
     </row>
-    <row r="530" spans="1:2" ht="15.75">
+    <row r="530" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
     </row>
-    <row r="531" spans="1:2" ht="15.75">
+    <row r="531" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
     </row>
-    <row r="532" spans="1:2" ht="15.75">
+    <row r="532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
     </row>
-    <row r="533" spans="1:2" ht="15.75">
+    <row r="533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
     </row>
-    <row r="534" spans="1:2" ht="15.75">
+    <row r="534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
     </row>
-    <row r="535" spans="1:2" ht="15.75">
+    <row r="535" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
     </row>
-    <row r="536" spans="1:2" ht="15.75">
+    <row r="536" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
     </row>
-    <row r="537" spans="1:2" ht="15.75">
+    <row r="537" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
     </row>
-    <row r="538" spans="1:2" ht="15.75">
+    <row r="538" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
     </row>
-    <row r="539" spans="1:2" ht="15.75">
+    <row r="539" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
     </row>
-    <row r="540" spans="1:2" ht="15.75">
+    <row r="540" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
     </row>
-    <row r="541" spans="1:2" ht="15.75">
+    <row r="541" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
     </row>
-    <row r="542" spans="1:2" ht="15.75">
+    <row r="542" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
     </row>
-    <row r="543" spans="1:2" ht="15.75">
+    <row r="543" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
     </row>
-    <row r="544" spans="1:2" ht="15.75">
+    <row r="544" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
     </row>
-    <row r="545" spans="1:2" ht="15.75">
+    <row r="545" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
     </row>
-    <row r="546" spans="1:2" ht="15.75">
+    <row r="546" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
     </row>
-    <row r="547" spans="1:2" ht="15.75">
+    <row r="547" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
     </row>
-    <row r="548" spans="1:2" ht="15.75">
+    <row r="548" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
     </row>
-    <row r="549" spans="1:2" ht="15.75">
+    <row r="549" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
     </row>
-    <row r="550" spans="1:2" ht="15.75">
+    <row r="550" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
     </row>
-    <row r="551" spans="1:2" ht="15.75">
+    <row r="551" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
     </row>
-    <row r="552" spans="1:2" ht="15.75">
+    <row r="552" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
     </row>
-    <row r="553" spans="1:2" ht="15.75">
+    <row r="553" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
     </row>
-    <row r="554" spans="1:2" ht="15.75">
+    <row r="554" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
     </row>
-    <row r="555" spans="1:2" ht="15.75">
+    <row r="555" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
     </row>
-    <row r="556" spans="1:2" ht="15.75">
+    <row r="556" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
     </row>
-    <row r="557" spans="1:2" ht="15.75">
+    <row r="557" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
     </row>
-    <row r="558" spans="1:2" ht="15.75">
+    <row r="558" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
     </row>
-    <row r="559" spans="1:2" ht="15.75">
+    <row r="559" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
     </row>
-    <row r="560" spans="1:2" ht="15.75">
+    <row r="560" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
     </row>
-    <row r="561" spans="1:2" ht="15.75">
+    <row r="561" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
     </row>
-    <row r="562" spans="1:2" ht="15.75">
+    <row r="562" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
     </row>
-    <row r="563" spans="1:2" ht="15.75">
+    <row r="563" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
     </row>
-    <row r="564" spans="1:2" ht="15.75">
+    <row r="564" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
     </row>
-    <row r="565" spans="1:2" ht="15.75">
+    <row r="565" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
     </row>
-    <row r="566" spans="1:2" ht="15.75">
+    <row r="566" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
     </row>
-    <row r="567" spans="1:2" ht="15.75">
+    <row r="567" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
     </row>
-    <row r="568" spans="1:2" ht="15.75">
+    <row r="568" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
     </row>
-    <row r="569" spans="1:2" ht="15.75">
+    <row r="569" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
     </row>
-    <row r="570" spans="1:2" ht="15.75">
+    <row r="570" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
     </row>
-    <row r="571" spans="1:2" ht="15.75">
+    <row r="571" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
     </row>
-    <row r="572" spans="1:2" ht="15.75">
+    <row r="572" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
     </row>
-    <row r="573" spans="1:2" ht="15.75">
+    <row r="573" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
     </row>
-    <row r="574" spans="1:2" ht="15.75">
+    <row r="574" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
     </row>
-    <row r="575" spans="1:2" ht="15.75">
+    <row r="575" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
     </row>
-    <row r="576" spans="1:2" ht="15.75">
+    <row r="576" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
     </row>
-    <row r="577" spans="1:2" ht="15.75">
+    <row r="577" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
     </row>
-    <row r="578" spans="1:2" ht="15.75">
+    <row r="578" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
     </row>
-    <row r="579" spans="1:2" ht="15.75">
+    <row r="579" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
     </row>
-    <row r="580" spans="1:2" ht="15.75">
+    <row r="580" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
     </row>
-    <row r="581" spans="1:2" ht="15.75">
+    <row r="581" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
     </row>
-    <row r="582" spans="1:2" ht="15.75">
+    <row r="582" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
     </row>
-    <row r="583" spans="1:2" ht="15.75">
+    <row r="583" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
     </row>
-    <row r="584" spans="1:2" ht="15.75">
+    <row r="584" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
     </row>
-    <row r="585" spans="1:2" ht="15.75">
+    <row r="585" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
     </row>
-    <row r="586" spans="1:2" ht="15.75">
+    <row r="586" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
     </row>
-    <row r="587" spans="1:2" ht="15.75">
+    <row r="587" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
     </row>
-    <row r="588" spans="1:2" ht="15.75">
+    <row r="588" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
     </row>
-    <row r="589" spans="1:2" ht="15.75">
+    <row r="589" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
     </row>
-    <row r="590" spans="1:2" ht="15.75">
+    <row r="590" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
     </row>
-    <row r="591" spans="1:2" ht="15.75">
+    <row r="591" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
     </row>
-    <row r="592" spans="1:2" ht="15.75">
+    <row r="592" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
     </row>
-    <row r="593" spans="1:2" ht="15.75">
+    <row r="593" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
     </row>
-    <row r="594" spans="1:2" ht="15.75">
+    <row r="594" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
     </row>
-    <row r="595" spans="1:2" ht="15.75">
+    <row r="595" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
     </row>
-    <row r="596" spans="1:2" ht="15.75">
+    <row r="596" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
     </row>
-    <row r="597" spans="1:2" ht="15.75">
+    <row r="597" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
     </row>
-    <row r="598" spans="1:2" ht="15.75">
+    <row r="598" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
     </row>
-    <row r="599" spans="1:2" ht="15.75">
+    <row r="599" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
     </row>
-    <row r="600" spans="1:2" ht="15.75">
+    <row r="600" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
     </row>
-    <row r="601" spans="1:2" ht="15.75">
+    <row r="601" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
     </row>
-    <row r="602" spans="1:2" ht="15.75">
+    <row r="602" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
     </row>
-    <row r="603" spans="1:2" ht="15.75">
+    <row r="603" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
     </row>
-    <row r="604" spans="1:2" ht="15.75">
+    <row r="604" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
     </row>
-    <row r="605" spans="1:2" ht="15.75">
+    <row r="605" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
     </row>
-    <row r="606" spans="1:2" ht="15.75">
+    <row r="606" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
     </row>
-    <row r="607" spans="1:2" ht="15.75">
+    <row r="607" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
     </row>
-    <row r="608" spans="1:2" ht="15.75">
+    <row r="608" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
     </row>
-    <row r="609" spans="1:2" ht="15.75">
+    <row r="609" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
     </row>
-    <row r="610" spans="1:2" ht="15.75">
+    <row r="610" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
     </row>
-    <row r="611" spans="1:2" ht="15.75">
+    <row r="611" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
     </row>
-    <row r="612" spans="1:2" ht="15.75">
+    <row r="612" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
     </row>
-    <row r="613" spans="1:2" ht="15.75">
+    <row r="613" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
     </row>
-    <row r="614" spans="1:2" ht="15.75">
+    <row r="614" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
     </row>
-    <row r="615" spans="1:2" ht="15.75">
+    <row r="615" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
     </row>
-    <row r="616" spans="1:2" ht="15.75">
+    <row r="616" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
     </row>
-    <row r="617" spans="1:2" ht="15.75">
+    <row r="617" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
     </row>
-    <row r="618" spans="1:2" ht="15.75">
+    <row r="618" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
     </row>
-    <row r="619" spans="1:2" ht="15.75">
+    <row r="619" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
     </row>
-    <row r="620" spans="1:2" ht="15.75">
+    <row r="620" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
     </row>
-    <row r="621" spans="1:2" ht="15.75">
+    <row r="621" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
     </row>
-    <row r="622" spans="1:2" ht="15.75">
+    <row r="622" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
     </row>
-    <row r="623" spans="1:2" ht="15.75">
+    <row r="623" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
     </row>
-    <row r="624" spans="1:2" ht="15.75">
+    <row r="624" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
     </row>
-    <row r="625" spans="1:2" ht="15.75">
+    <row r="625" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
     </row>
-    <row r="626" spans="1:2" ht="15.75">
+    <row r="626" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
     </row>
-    <row r="627" spans="1:2" ht="15.75">
+    <row r="627" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="1:2" ht="15.75">
+    <row r="628" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
     </row>
-    <row r="629" spans="1:2" ht="15.75">
+    <row r="629" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
     </row>
-    <row r="630" spans="1:2" ht="15.75">
+    <row r="630" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
     </row>
-    <row r="631" spans="1:2" ht="15.75">
+    <row r="631" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
     </row>
-    <row r="632" spans="1:2" ht="15.75">
+    <row r="632" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
     </row>
-    <row r="633" spans="1:2" ht="15.75">
+    <row r="633" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
     </row>
-    <row r="634" spans="1:2" ht="15.75">
+    <row r="634" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
     </row>
-    <row r="635" spans="1:2" ht="15.75">
+    <row r="635" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
     </row>
-    <row r="636" spans="1:2" ht="15.75">
+    <row r="636" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
     </row>
-    <row r="637" spans="1:2" ht="15.75">
+    <row r="637" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
     </row>
-    <row r="638" spans="1:2" ht="15.75">
+    <row r="638" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
     </row>
-    <row r="639" spans="1:2" ht="15.75">
+    <row r="639" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
     </row>
-    <row r="640" spans="1:2" ht="15.75">
+    <row r="640" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
     </row>
-    <row r="641" spans="1:2" ht="15.75">
+    <row r="641" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
     </row>
-    <row r="642" spans="1:2" ht="15.75">
+    <row r="642" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
     </row>
-    <row r="643" spans="1:2" ht="15.75">
+    <row r="643" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
     </row>
-    <row r="644" spans="1:2" ht="15.75">
+    <row r="644" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
     </row>
-    <row r="645" spans="1:2" ht="15.75">
+    <row r="645" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
     </row>
-    <row r="646" spans="1:2" ht="15.75">
+    <row r="646" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
     </row>
-    <row r="647" spans="1:2" ht="15.75">
+    <row r="647" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
     </row>
-    <row r="648" spans="1:2" ht="15.75">
+    <row r="648" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
     </row>
-    <row r="649" spans="1:2" ht="15.75">
+    <row r="649" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
     </row>
-    <row r="650" spans="1:2" ht="15.75">
+    <row r="650" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
     </row>
-    <row r="651" spans="1:2" ht="15.75">
+    <row r="651" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
     </row>
-    <row r="652" spans="1:2" ht="15.75">
+    <row r="652" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
     </row>
-    <row r="653" spans="1:2" ht="15.75">
+    <row r="653" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
     </row>
-    <row r="654" spans="1:2" ht="15.75">
+    <row r="654" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
     </row>
-    <row r="655" spans="1:2" ht="15.75">
+    <row r="655" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
     </row>
-    <row r="656" spans="1:2" ht="15.75">
+    <row r="656" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
     </row>
-    <row r="657" spans="1:2" ht="15.75">
+    <row r="657" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
     </row>
-    <row r="658" spans="1:2" ht="15.75">
+    <row r="658" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
     </row>
-    <row r="659" spans="1:2" ht="15.75">
+    <row r="659" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
     </row>
-    <row r="660" spans="1:2" ht="15.75">
+    <row r="660" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
     </row>
-    <row r="661" spans="1:2" ht="15.75">
+    <row r="661" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
     </row>
-    <row r="662" spans="1:2" ht="15.75">
+    <row r="662" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
     </row>
-    <row r="663" spans="1:2" ht="15.75">
+    <row r="663" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
     </row>
-    <row r="664" spans="1:2" ht="15.75">
+    <row r="664" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
     </row>
-    <row r="665" spans="1:2" ht="15.75">
+    <row r="665" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
     </row>
-    <row r="666" spans="1:2" ht="15.75">
+    <row r="666" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
     </row>
-    <row r="667" spans="1:2" ht="15.75">
+    <row r="667" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
     </row>
-    <row r="668" spans="1:2" ht="15.75">
+    <row r="668" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
     </row>
-    <row r="669" spans="1:2" ht="15.75">
+    <row r="669" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
     </row>
-    <row r="670" spans="1:2" ht="15.75">
+    <row r="670" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
     </row>
-    <row r="671" spans="1:2" ht="15.75">
+    <row r="671" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
     </row>
-    <row r="672" spans="1:2" ht="15.75">
+    <row r="672" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
     </row>
-    <row r="673" spans="1:2" ht="15.75">
+    <row r="673" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
     </row>
-    <row r="674" spans="1:2" ht="15.75">
+    <row r="674" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
     </row>
-    <row r="675" spans="1:2" ht="15.75">
+    <row r="675" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
     </row>
-    <row r="676" spans="1:2" ht="15.75">
+    <row r="676" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
     </row>
-    <row r="677" spans="1:2" ht="15.75">
+    <row r="677" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
     </row>
-    <row r="678" spans="1:2" ht="15.75">
+    <row r="678" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
     </row>
-    <row r="679" spans="1:2" ht="15.75">
+    <row r="679" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
     </row>
-    <row r="680" spans="1:2" ht="15.75">
+    <row r="680" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
     </row>
-    <row r="681" spans="1:2" ht="15.75">
+    <row r="681" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
     </row>
-    <row r="682" spans="1:2" ht="15.75">
+    <row r="682" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
     </row>
-    <row r="683" spans="1:2" ht="15.75">
+    <row r="683" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
     </row>
-    <row r="684" spans="1:2" ht="15.75">
+    <row r="684" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
     </row>
-    <row r="685" spans="1:2" ht="15.75">
+    <row r="685" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
     </row>
-    <row r="686" spans="1:2" ht="15.75">
+    <row r="686" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
     </row>
-    <row r="687" spans="1:2" ht="15.75">
+    <row r="687" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
     </row>
-    <row r="688" spans="1:2" ht="15.75">
+    <row r="688" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
     </row>
-    <row r="689" spans="1:2" ht="15.75">
+    <row r="689" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
     </row>
-    <row r="690" spans="1:2" ht="15.75">
+    <row r="690" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
     </row>
-    <row r="691" spans="1:2" ht="15.75">
+    <row r="691" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
     </row>
-    <row r="692" spans="1:2" ht="15.75">
+    <row r="692" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
     </row>
-    <row r="693" spans="1:2" ht="15.75">
+    <row r="693" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
     </row>
-    <row r="694" spans="1:2" ht="15.75">
+    <row r="694" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
     </row>
-    <row r="695" spans="1:2" ht="15.75">
+    <row r="695" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
     </row>
-    <row r="696" spans="1:2" ht="15.75">
+    <row r="696" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
     </row>
-    <row r="697" spans="1:2" ht="15.75">
+    <row r="697" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
     </row>
-    <row r="698" spans="1:2" ht="15.75">
+    <row r="698" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
     </row>
-    <row r="699" spans="1:2" ht="15.75">
+    <row r="699" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
     </row>
-    <row r="700" spans="1:2" ht="15.75">
+    <row r="700" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
     </row>
-    <row r="701" spans="1:2" ht="15.75">
+    <row r="701" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
     </row>
-    <row r="702" spans="1:2" ht="15.75">
+    <row r="702" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
     </row>
-    <row r="703" spans="1:2" ht="15.75">
+    <row r="703" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
     </row>
-    <row r="704" spans="1:2" ht="15.75">
+    <row r="704" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
     </row>
-    <row r="705" spans="1:2" ht="15.75">
+    <row r="705" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
     </row>
-    <row r="706" spans="1:2" ht="15.75">
+    <row r="706" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
     </row>
-    <row r="707" spans="1:2" ht="15.75">
+    <row r="707" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
     </row>
-    <row r="708" spans="1:2" ht="15.75">
+    <row r="708" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
     </row>
-    <row r="709" spans="1:2" ht="15.75">
+    <row r="709" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
     </row>
-    <row r="710" spans="1:2" ht="15.75">
+    <row r="710" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
     </row>
-    <row r="711" spans="1:2" ht="15.75">
+    <row r="711" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
     </row>
-    <row r="712" spans="1:2" ht="15.75">
+    <row r="712" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
     </row>
-    <row r="713" spans="1:2" ht="15.75">
+    <row r="713" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
     </row>
-    <row r="714" spans="1:2" ht="15.75">
+    <row r="714" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
     </row>
-    <row r="715" spans="1:2" ht="15.75">
+    <row r="715" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
     </row>
-    <row r="716" spans="1:2" ht="15.75">
+    <row r="716" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
     </row>
-    <row r="717" spans="1:2" ht="15.75">
+    <row r="717" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
     </row>
-    <row r="718" spans="1:2" ht="15.75">
+    <row r="718" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
     </row>
-    <row r="719" spans="1:2" ht="15.75">
+    <row r="719" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
     </row>
-    <row r="720" spans="1:2" ht="15.75">
+    <row r="720" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
     </row>
-    <row r="721" spans="1:2" ht="15.75">
+    <row r="721" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
     </row>
-    <row r="722" spans="1:2" ht="15.75">
+    <row r="722" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
     </row>
-    <row r="723" spans="1:2" ht="15.75">
+    <row r="723" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
     </row>
-    <row r="724" spans="1:2" ht="15.75">
+    <row r="724" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
     </row>
-    <row r="725" spans="1:2" ht="15.75">
+    <row r="725" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
     </row>
-    <row r="726" spans="1:2" ht="15.75">
+    <row r="726" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
     </row>
-    <row r="727" spans="1:2" ht="15.75">
+    <row r="727" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
     </row>
-    <row r="728" spans="1:2" ht="15.75">
+    <row r="728" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
     </row>
-    <row r="729" spans="1:2" ht="15.75">
+    <row r="729" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
     </row>
-    <row r="730" spans="1:2" ht="15.75">
+    <row r="730" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
     </row>
-    <row r="731" spans="1:2" ht="15.75">
+    <row r="731" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
     </row>
-    <row r="732" spans="1:2" ht="15.75">
+    <row r="732" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
     </row>
-    <row r="733" spans="1:2" ht="15.75">
+    <row r="733" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
     </row>
-    <row r="734" spans="1:2" ht="15.75">
+    <row r="734" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
     </row>
-    <row r="735" spans="1:2" ht="15.75">
+    <row r="735" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
     </row>
-    <row r="736" spans="1:2" ht="15.75">
+    <row r="736" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
     </row>
-    <row r="737" spans="1:2" ht="15.75">
+    <row r="737" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
     </row>
-    <row r="738" spans="1:2" ht="15.75">
+    <row r="738" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
     </row>
-    <row r="739" spans="1:2" ht="15.75">
+    <row r="739" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
     </row>
-    <row r="740" spans="1:2" ht="15.75">
+    <row r="740" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
     </row>
-    <row r="741" spans="1:2" ht="15.75">
+    <row r="741" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
     </row>
-    <row r="742" spans="1:2" ht="15.75">
+    <row r="742" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
     </row>
-    <row r="743" spans="1:2" ht="15.75">
+    <row r="743" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
     </row>
-    <row r="744" spans="1:2" ht="15.75">
+    <row r="744" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
     </row>
-    <row r="745" spans="1:2" ht="15.75">
+    <row r="745" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
     </row>
-    <row r="746" spans="1:2" ht="15.75">
+    <row r="746" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
     </row>
-    <row r="747" spans="1:2" ht="15.75">
+    <row r="747" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
     </row>
-    <row r="748" spans="1:2" ht="15.75">
+    <row r="748" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
     </row>
-    <row r="749" spans="1:2" ht="15.75">
+    <row r="749" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
     </row>
-    <row r="750" spans="1:2" ht="15.75">
+    <row r="750" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
     </row>
-    <row r="751" spans="1:2" ht="15.75">
+    <row r="751" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
     </row>
-    <row r="752" spans="1:2" ht="15.75">
+    <row r="752" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
     </row>
-    <row r="753" spans="1:2" ht="15.75">
+    <row r="753" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
     </row>
-    <row r="754" spans="1:2" ht="15.75">
+    <row r="754" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
     </row>
-    <row r="755" spans="1:2" ht="15.75">
+    <row r="755" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
     </row>
-    <row r="756" spans="1:2" ht="15.75">
+    <row r="756" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
     </row>
-    <row r="757" spans="1:2" ht="15.75">
+    <row r="757" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
     </row>
-    <row r="758" spans="1:2" ht="15.75">
+    <row r="758" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
     </row>
-    <row r="759" spans="1:2" ht="15.75">
+    <row r="759" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
     </row>
-    <row r="760" spans="1:2" ht="15.75">
+    <row r="760" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
     </row>
-    <row r="761" spans="1:2" ht="15.75">
+    <row r="761" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
     </row>
-    <row r="762" spans="1:2" ht="15.75">
+    <row r="762" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
     </row>
-    <row r="763" spans="1:2" ht="15.75">
+    <row r="763" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
     </row>
-    <row r="764" spans="1:2" ht="15.75">
+    <row r="764" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
     </row>
-    <row r="765" spans="1:2" ht="15.75">
+    <row r="765" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
     </row>
-    <row r="766" spans="1:2" ht="15.75">
+    <row r="766" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
     </row>
-    <row r="767" spans="1:2" ht="15.75">
+    <row r="767" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
     </row>
-    <row r="768" spans="1:2" ht="15.75">
+    <row r="768" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
     </row>
-    <row r="769" spans="1:2" ht="15.75">
+    <row r="769" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
     </row>
-    <row r="770" spans="1:2" ht="15.75">
+    <row r="770" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
     </row>
-    <row r="771" spans="1:2" ht="15.75">
+    <row r="771" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
     </row>
-    <row r="772" spans="1:2" ht="15.75">
+    <row r="772" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
     </row>
-    <row r="773" spans="1:2" ht="15.75">
+    <row r="773" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
     </row>
-    <row r="774" spans="1:2" ht="15.75">
+    <row r="774" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
     </row>
-    <row r="775" spans="1:2" ht="15.75">
+    <row r="775" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
     </row>
-    <row r="776" spans="1:2" ht="15.75">
+    <row r="776" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
     </row>
-    <row r="777" spans="1:2" ht="15.75">
+    <row r="777" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
     </row>
-    <row r="778" spans="1:2" ht="15.75">
+    <row r="778" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
     </row>
-    <row r="779" spans="1:2" ht="15.75">
+    <row r="779" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
     </row>
-    <row r="780" spans="1:2" ht="15.75">
+    <row r="780" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
     </row>
-    <row r="781" spans="1:2" ht="15.75">
+    <row r="781" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
     </row>
-    <row r="782" spans="1:2" ht="15.75">
+    <row r="782" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
     </row>
-    <row r="783" spans="1:2" ht="15.75">
+    <row r="783" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
     </row>
-    <row r="784" spans="1:2" ht="15.75">
+    <row r="784" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
     </row>
-    <row r="785" spans="1:2" ht="15.75">
+    <row r="785" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
     </row>
-    <row r="786" spans="1:2" ht="15.75">
+    <row r="786" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
     </row>
-    <row r="787" spans="1:2" ht="15.75">
+    <row r="787" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
     </row>
-    <row r="788" spans="1:2" ht="15.75">
+    <row r="788" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
     </row>
-    <row r="789" spans="1:2" ht="15.75">
+    <row r="789" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
     </row>
-    <row r="790" spans="1:2" ht="15.75">
+    <row r="790" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
     </row>
-    <row r="791" spans="1:2" ht="15.75">
+    <row r="791" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
     </row>
-    <row r="792" spans="1:2" ht="15.75">
+    <row r="792" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
     </row>
-    <row r="793" spans="1:2" ht="15.75">
+    <row r="793" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
     </row>
-    <row r="794" spans="1:2" ht="15.75">
+    <row r="794" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
     </row>
-    <row r="795" spans="1:2" ht="15.75">
+    <row r="795" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
     </row>
-    <row r="796" spans="1:2" ht="15.75">
+    <row r="796" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
     </row>
-    <row r="797" spans="1:2" ht="15.75">
+    <row r="797" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
     </row>
-    <row r="798" spans="1:2" ht="15.75">
+    <row r="798" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
     </row>
-    <row r="799" spans="1:2" ht="15.75">
+    <row r="799" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
     </row>
-    <row r="800" spans="1:2" ht="15.75">
+    <row r="800" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
     </row>
-    <row r="801" spans="1:2" ht="15.75">
+    <row r="801" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
     </row>
-    <row r="802" spans="1:2" ht="15.75">
+    <row r="802" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
     </row>
-    <row r="803" spans="1:2" ht="15.75">
+    <row r="803" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
     </row>
-    <row r="804" spans="1:2" ht="15.75">
+    <row r="804" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
     </row>
-    <row r="805" spans="1:2" ht="15.75">
+    <row r="805" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
     </row>
-    <row r="806" spans="1:2" ht="15.75">
+    <row r="806" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
     </row>
-    <row r="807" spans="1:2" ht="15.75">
+    <row r="807" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
     </row>
-    <row r="808" spans="1:2" ht="15.75">
+    <row r="808" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
     </row>
-    <row r="809" spans="1:2" ht="15.75">
+    <row r="809" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
     </row>
-    <row r="810" spans="1:2" ht="15.75">
+    <row r="810" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
     </row>
-    <row r="811" spans="1:2" ht="15.75">
+    <row r="811" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
     </row>
-    <row r="812" spans="1:2" ht="15.75">
+    <row r="812" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
     </row>
-    <row r="813" spans="1:2" ht="15.75">
+    <row r="813" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
     </row>
-    <row r="814" spans="1:2" ht="15.75">
+    <row r="814" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
     </row>
-    <row r="815" spans="1:2" ht="15.75">
+    <row r="815" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
     </row>
-    <row r="816" spans="1:2" ht="15.75">
+    <row r="816" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
     </row>
-    <row r="817" spans="1:2" ht="15.75">
+    <row r="817" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
     </row>
-    <row r="818" spans="1:2" ht="15.75">
+    <row r="818" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
     </row>
-    <row r="819" spans="1:2" ht="15.75">
+    <row r="819" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
     </row>
-    <row r="820" spans="1:2" ht="15.75">
+    <row r="820" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
     </row>
-    <row r="821" spans="1:2" ht="15.75">
+    <row r="821" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
     </row>
-    <row r="822" spans="1:2" ht="15.75">
+    <row r="822" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
     </row>
-    <row r="823" spans="1:2" ht="15.75">
+    <row r="823" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
     </row>
-    <row r="824" spans="1:2" ht="15.75">
+    <row r="824" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
     </row>
-    <row r="825" spans="1:2" ht="15.75">
+    <row r="825" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
     </row>
-    <row r="826" spans="1:2" ht="15.75">
+    <row r="826" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
     </row>
-    <row r="827" spans="1:2" ht="15.75">
+    <row r="827" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
     </row>
-    <row r="828" spans="1:2" ht="15.75">
+    <row r="828" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
     </row>
-    <row r="829" spans="1:2" ht="15.75">
+    <row r="829" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
     </row>
-    <row r="830" spans="1:2" ht="15.75">
+    <row r="830" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
     </row>
-    <row r="831" spans="1:2" ht="15.75">
+    <row r="831" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
     </row>
-    <row r="832" spans="1:2" ht="15.75">
+    <row r="832" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
     </row>
-    <row r="833" spans="1:2" ht="15.75">
+    <row r="833" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
     </row>
-    <row r="834" spans="1:2" ht="15.75">
+    <row r="834" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
     </row>
-    <row r="835" spans="1:2" ht="15.75">
+    <row r="835" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
     </row>
-    <row r="836" spans="1:2" ht="15.75">
+    <row r="836" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
     </row>
-    <row r="837" spans="1:2" ht="15.75">
+    <row r="837" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
     </row>
-    <row r="838" spans="1:2" ht="15.75">
+    <row r="838" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
     </row>
-    <row r="839" spans="1:2" ht="15.75">
+    <row r="839" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
     </row>
-    <row r="840" spans="1:2" ht="15.75">
+    <row r="840" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
     </row>
-    <row r="841" spans="1:2" ht="15.75">
+    <row r="841" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
     </row>
-    <row r="842" spans="1:2" ht="15.75">
+    <row r="842" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
     </row>
-    <row r="843" spans="1:2" ht="15.75">
+    <row r="843" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
     </row>
-    <row r="844" spans="1:2" ht="15.75">
+    <row r="844" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
     </row>
-    <row r="845" spans="1:2" ht="15.75">
+    <row r="845" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
     </row>
-    <row r="846" spans="1:2" ht="15.75">
+    <row r="846" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
     </row>
-    <row r="847" spans="1:2" ht="15.75">
+    <row r="847" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
     </row>
-    <row r="848" spans="1:2" ht="15.75">
+    <row r="848" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
     </row>
-    <row r="849" spans="1:2" ht="15.75">
+    <row r="849" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
     </row>
-    <row r="850" spans="1:2" ht="15.75">
+    <row r="850" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
     </row>
-    <row r="851" spans="1:2" ht="15.75">
+    <row r="851" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
     </row>
-    <row r="852" spans="1:2" ht="15.75">
+    <row r="852" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
     </row>
-    <row r="853" spans="1:2" ht="15.75">
+    <row r="853" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
     </row>
-    <row r="854" spans="1:2" ht="15.75">
+    <row r="854" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
     </row>
-    <row r="855" spans="1:2" ht="15.75">
+    <row r="855" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
     </row>
-    <row r="856" spans="1:2" ht="15.75">
+    <row r="856" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
     </row>
-    <row r="857" spans="1:2" ht="15.75">
+    <row r="857" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
     </row>
-    <row r="858" spans="1:2" ht="15.75">
+    <row r="858" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
     </row>
-    <row r="859" spans="1:2" ht="15.75">
+    <row r="859" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
     </row>
-    <row r="860" spans="1:2" ht="15.75">
+    <row r="860" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
     </row>
-    <row r="861" spans="1:2" ht="15.75">
+    <row r="861" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
     </row>
-    <row r="862" spans="1:2" ht="15.75">
+    <row r="862" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
     </row>
-    <row r="863" spans="1:2" ht="15.75">
+    <row r="863" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
     </row>
-    <row r="864" spans="1:2" ht="15.75">
+    <row r="864" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
     </row>
-    <row r="865" spans="1:2" ht="15.75">
+    <row r="865" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
     </row>
-    <row r="866" spans="1:2" ht="15.75">
+    <row r="866" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
     </row>
-    <row r="867" spans="1:2" ht="15.75">
+    <row r="867" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
     </row>
-    <row r="868" spans="1:2" ht="15.75">
+    <row r="868" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
     </row>
-    <row r="869" spans="1:2" ht="15.75">
+    <row r="869" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
     </row>
-    <row r="870" spans="1:2" ht="15.75">
+    <row r="870" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
     </row>
-    <row r="871" spans="1:2" ht="15.75">
+    <row r="871" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
     </row>
-    <row r="872" spans="1:2" ht="15.75">
+    <row r="872" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
     </row>
-    <row r="873" spans="1:2" ht="15.75">
+    <row r="873" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
     </row>
-    <row r="874" spans="1:2" ht="15.75">
+    <row r="874" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
     </row>
-    <row r="875" spans="1:2" ht="15.75">
+    <row r="875" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
     </row>
-    <row r="876" spans="1:2" ht="15.75">
+    <row r="876" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
     </row>
-    <row r="877" spans="1:2" ht="15.75">
+    <row r="877" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
     </row>
-    <row r="878" spans="1:2" ht="15.75">
+    <row r="878" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
     </row>
-    <row r="879" spans="1:2" ht="15.75">
+    <row r="879" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
     </row>
-    <row r="880" spans="1:2" ht="15.75">
+    <row r="880" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
     </row>
-    <row r="881" spans="1:2" ht="15.75">
+    <row r="881" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
     </row>
-    <row r="882" spans="1:2" ht="15.75">
+    <row r="882" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
     </row>
-    <row r="883" spans="1:2" ht="15.75">
+    <row r="883" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
     </row>
-    <row r="884" spans="1:2" ht="15.75">
+    <row r="884" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
     </row>
-    <row r="885" spans="1:2" ht="15.75">
+    <row r="885" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
     </row>
-    <row r="886" spans="1:2" ht="15.75">
+    <row r="886" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
     </row>
-    <row r="887" spans="1:2" ht="15.75">
+    <row r="887" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
     </row>
-    <row r="888" spans="1:2" ht="15.75">
+    <row r="888" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
     </row>
-    <row r="889" spans="1:2" ht="15.75">
+    <row r="889" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
     </row>
-    <row r="890" spans="1:2" ht="15.75">
+    <row r="890" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
     </row>
-    <row r="891" spans="1:2" ht="15.75">
+    <row r="891" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
     </row>
-    <row r="892" spans="1:2" ht="15.75">
+    <row r="892" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
     </row>
-    <row r="893" spans="1:2" ht="15.75">
+    <row r="893" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
     </row>
-    <row r="894" spans="1:2" ht="15.75">
+    <row r="894" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
     </row>
-    <row r="895" spans="1:2" ht="15.75">
+    <row r="895" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
     </row>
-    <row r="896" spans="1:2" ht="15.75">
+    <row r="896" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
     </row>
-    <row r="897" spans="1:2" ht="15.75">
+    <row r="897" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
     </row>
-    <row r="898" spans="1:2" ht="15.75">
+    <row r="898" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
     </row>
-    <row r="899" spans="1:2" ht="15.75">
+    <row r="899" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
     </row>
-    <row r="900" spans="1:2" ht="15.75">
+    <row r="900" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
     </row>
-    <row r="901" spans="1:2" ht="15.75">
+    <row r="901" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
     </row>
-    <row r="902" spans="1:2" ht="15.75">
+    <row r="902" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
     </row>
-    <row r="903" spans="1:2" ht="15.75">
+    <row r="903" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
     </row>
-    <row r="904" spans="1:2" ht="15.75">
+    <row r="904" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
     </row>
-    <row r="905" spans="1:2" ht="15.75">
+    <row r="905" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
     </row>
-    <row r="906" spans="1:2" ht="15.75">
+    <row r="906" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
     </row>
-    <row r="907" spans="1:2" ht="15.75">
+    <row r="907" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
     </row>
-    <row r="908" spans="1:2" ht="15.75">
+    <row r="908" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
     </row>
-    <row r="909" spans="1:2" ht="15.75">
+    <row r="909" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
     </row>
-    <row r="910" spans="1:2" ht="15.75">
+    <row r="910" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
     </row>
-    <row r="911" spans="1:2" ht="15.75">
+    <row r="911" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
     </row>
-    <row r="912" spans="1:2" ht="15.75">
+    <row r="912" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
     </row>
-    <row r="913" spans="1:2" ht="15.75">
+    <row r="913" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
     </row>
-    <row r="914" spans="1:2" ht="15.75">
+    <row r="914" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
     </row>
-    <row r="915" spans="1:2" ht="15.75">
+    <row r="915" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
     </row>
-    <row r="916" spans="1:2" ht="15.75">
+    <row r="916" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
     </row>
-    <row r="917" spans="1:2" ht="15.75">
+    <row r="917" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
     </row>
-    <row r="918" spans="1:2" ht="15.75">
+    <row r="918" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
     </row>
-    <row r="919" spans="1:2" ht="15.75">
+    <row r="919" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
     </row>
-    <row r="920" spans="1:2" ht="15.75">
+    <row r="920" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
     </row>
-    <row r="921" spans="1:2" ht="15.75">
+    <row r="921" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
     </row>
-    <row r="922" spans="1:2" ht="15.75">
+    <row r="922" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
     </row>
-    <row r="923" spans="1:2" ht="15.75">
+    <row r="923" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
     </row>
-    <row r="924" spans="1:2" ht="15.75">
+    <row r="924" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
     </row>
-    <row r="925" spans="1:2" ht="15.75">
+    <row r="925" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
     </row>
-    <row r="926" spans="1:2" ht="15.75">
+    <row r="926" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
     </row>
-    <row r="927" spans="1:2" ht="15.75">
+    <row r="927" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
     </row>
-    <row r="928" spans="1:2" ht="15.75">
+    <row r="928" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
     </row>
-    <row r="929" spans="1:2" ht="15.75">
+    <row r="929" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
     </row>
-    <row r="930" spans="1:2" ht="15.75">
+    <row r="930" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
     </row>
-    <row r="931" spans="1:2" ht="15.75">
+    <row r="931" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
     </row>
-    <row r="932" spans="1:2" ht="15.75">
+    <row r="932" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
     </row>
-    <row r="933" spans="1:2" ht="15.75">
+    <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
     </row>
-    <row r="934" spans="1:2" ht="15.75">
+    <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
     </row>
-    <row r="935" spans="1:2" ht="15.75">
+    <row r="935" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
     </row>
-    <row r="936" spans="1:2" ht="15.75">
+    <row r="936" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
     </row>
-    <row r="937" spans="1:2" ht="15.75">
+    <row r="937" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
     </row>
-    <row r="938" spans="1:2" ht="15.75">
+    <row r="938" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
     </row>
-    <row r="939" spans="1:2" ht="15.75">
+    <row r="939" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
     </row>
-    <row r="940" spans="1:2" ht="15.75">
+    <row r="940" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
     </row>
-    <row r="941" spans="1:2" ht="15.75">
+    <row r="941" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
     </row>
-    <row r="942" spans="1:2" ht="15.75">
+    <row r="942" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A942" s="2"/>
-      <c r="B942" s="2"/>
-    </row>
-    <row r="943" spans="1:2" ht="15.75">
+      <c r="B942" s="1"/>
+    </row>
+    <row r="943" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A943" s="2"/>
-      <c r="B943" s="2"/>
-    </row>
-    <row r="944" spans="1:2" ht="15.75">
+      <c r="B943" s="1"/>
+    </row>
+    <row r="944" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A944" s="2"/>
       <c r="B944" s="1"/>
     </row>
-    <row r="945" spans="1:2" ht="15.75">
+    <row r="945" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A945" s="2"/>
       <c r="B945" s="1"/>
     </row>
-    <row r="946" spans="1:2" ht="15.75">
+    <row r="946" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A946" s="2"/>
       <c r="B946" s="1"/>
     </row>
-    <row r="947" spans="1:2" ht="15.75">
+    <row r="947" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A947" s="2"/>
       <c r="B947" s="1"/>
     </row>
-    <row r="948" spans="1:2" ht="15.75">
+    <row r="948" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A948" s="2"/>
       <c r="B948" s="1"/>
     </row>
-    <row r="949" spans="1:2" ht="15.75">
+    <row r="949" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A949" s="2"/>
       <c r="B949" s="1"/>
     </row>
-    <row r="950" spans="1:2" ht="15.75">
+    <row r="950" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A950" s="2"/>
       <c r="B950" s="1"/>
     </row>
-    <row r="951" spans="1:2" ht="15.75">
+    <row r="951" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A951" s="2"/>
       <c r="B951" s="1"/>
     </row>
-    <row r="952" spans="1:2" ht="15.75">
+    <row r="952" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A952" s="2"/>
       <c r="B952" s="1"/>
     </row>
-    <row r="953" spans="1:2" ht="15.75">
+    <row r="953" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A953" s="2"/>
       <c r="B953" s="1"/>
     </row>
-    <row r="954" spans="1:2" ht="15.75">
+    <row r="954" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A954" s="2"/>
       <c r="B954" s="1"/>
     </row>
-    <row r="955" spans="1:2" ht="15.75">
+    <row r="955" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A955" s="2"/>
       <c r="B955" s="1"/>
     </row>
-    <row r="956" spans="1:2" ht="15.75">
+    <row r="956" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A956" s="2"/>
       <c r="B956" s="1"/>
     </row>
-    <row r="957" spans="1:2" ht="15.75">
+    <row r="957" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A957" s="2"/>
       <c r="B957" s="1"/>
     </row>
-    <row r="958" spans="1:2" ht="15.75">
+    <row r="958" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A958" s="2"/>
       <c r="B958" s="1"/>
     </row>
-    <row r="959" spans="1:2" ht="15.75">
+    <row r="959" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A959" s="2"/>
       <c r="B959" s="1"/>
     </row>
-    <row r="960" spans="1:2" ht="15.75">
+    <row r="960" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A960" s="2"/>
       <c r="B960" s="1"/>
     </row>
-    <row r="961" spans="1:2" ht="15.75">
+    <row r="961" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A961" s="2"/>
       <c r="B961" s="1"/>
     </row>
-    <row r="962" spans="1:2" ht="15.75">
+    <row r="962" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A962" s="2"/>
       <c r="B962" s="1"/>
     </row>
-    <row r="963" spans="1:2" ht="15.75">
+    <row r="963" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A963" s="2"/>
       <c r="B963" s="1"/>
     </row>
-    <row r="964" spans="1:2" ht="15.75">
+    <row r="964" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A964" s="2"/>
       <c r="B964" s="1"/>
     </row>
-    <row r="965" spans="1:2" ht="15.75">
+    <row r="965" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A965" s="2"/>
       <c r="B965" s="1"/>
     </row>
-    <row r="966" spans="1:2" ht="15.75">
+    <row r="966" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A966" s="2"/>
       <c r="B966" s="1"/>
     </row>
-    <row r="967" spans="1:2" ht="15.75">
+    <row r="967" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A967" s="2"/>
       <c r="B967" s="1"/>
     </row>
-    <row r="968" spans="1:2" ht="15.75">
+    <row r="968" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A968" s="2"/>
       <c r="B968" s="1"/>
     </row>
-    <row r="969" spans="1:2" ht="15.75">
+    <row r="969" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A969" s="2"/>
       <c r="B969" s="1"/>
     </row>
-    <row r="970" spans="1:2" ht="15.75">
+    <row r="970" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A970" s="2"/>
       <c r="B970" s="1"/>
     </row>
-    <row r="971" spans="1:2" ht="15.75">
+    <row r="971" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A971" s="2"/>
       <c r="B971" s="1"/>
     </row>
-    <row r="972" spans="1:2" ht="15.75">
+    <row r="972" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A972" s="2"/>
       <c r="B972" s="1"/>
     </row>
-    <row r="973" spans="1:2" ht="15.75">
+    <row r="973" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A973" s="2"/>
       <c r="B973" s="1"/>
     </row>
-    <row r="974" spans="1:2" ht="15.75">
+    <row r="974" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A974" s="2"/>
       <c r="B974" s="1"/>
     </row>
-    <row r="975" spans="1:2" ht="15.75">
+    <row r="975" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A975" s="2"/>
       <c r="B975" s="1"/>
     </row>
-    <row r="976" spans="1:2" ht="15.75">
+    <row r="976" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A976" s="2"/>
       <c r="B976" s="1"/>
     </row>
-    <row r="977" spans="1:2" ht="15.75">
+    <row r="977" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A977" s="2"/>
       <c r="B977" s="1"/>
     </row>
-    <row r="978" spans="1:2" ht="15.75">
+    <row r="978" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A978" s="2"/>
       <c r="B978" s="1"/>
     </row>
-    <row r="979" spans="1:2" ht="15.75">
+    <row r="979" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A979" s="2"/>
       <c r="B979" s="1"/>
     </row>
-    <row r="980" spans="1:2" ht="15.75">
+    <row r="980" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A980" s="2"/>
       <c r="B980" s="1"/>
     </row>
-    <row r="981" spans="1:2" ht="15.75">
+    <row r="981" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A981" s="2"/>
       <c r="B981" s="1"/>
     </row>
-    <row r="982" spans="1:2" ht="15.75">
+    <row r="982" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A982" s="2"/>
       <c r="B982" s="1"/>
     </row>
-    <row r="983" spans="1:2" ht="15.75">
+    <row r="983" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A983" s="2"/>
       <c r="B983" s="1"/>
     </row>
-    <row r="984" spans="1:2" ht="15.75">
+    <row r="984" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A984" s="2"/>
       <c r="B984" s="1"/>
     </row>
-    <row r="985" spans="1:2" ht="15.75">
+    <row r="985" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A985" s="2"/>
       <c r="B985" s="1"/>
     </row>
-    <row r="986" spans="1:2" ht="15.75">
+    <row r="986" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A986" s="2"/>
       <c r="B986" s="1"/>
     </row>
-    <row r="987" spans="1:2" ht="15.75">
+    <row r="987" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A987" s="2"/>
       <c r="B987" s="1"/>
     </row>
-    <row r="988" spans="1:2" ht="15.75">
+    <row r="988" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A988" s="2"/>
       <c r="B988" s="1"/>
     </row>
-    <row r="989" spans="1:2" ht="15.75">
+    <row r="989" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A989" s="2"/>
       <c r="B989" s="1"/>
     </row>
-    <row r="990" spans="1:2" ht="15.75">
+    <row r="990" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A990" s="2"/>
       <c r="B990" s="1"/>
     </row>
-    <row r="991" spans="1:2" ht="15.75">
+    <row r="991" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A991" s="2"/>
       <c r="B991" s="1"/>
     </row>
-    <row r="992" spans="1:2" ht="15.75">
+    <row r="992" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A992" s="2"/>
       <c r="B992" s="1"/>
     </row>
-    <row r="993" spans="1:2" ht="15.75">
+    <row r="993" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A993" s="2"/>
       <c r="B993" s="1"/>
     </row>
-    <row r="994" spans="1:2" ht="15.75">
+    <row r="994" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A994" s="2"/>
       <c r="B994" s="1"/>
     </row>
-    <row r="995" spans="1:2" ht="15.75">
+    <row r="995" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A995" s="2"/>
       <c r="B995" s="1"/>
     </row>
-    <row r="996" spans="1:2" ht="15.75">
+    <row r="996" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A996" s="2"/>
       <c r="B996" s="1"/>
     </row>
-    <row r="997" spans="1:2" ht="15.75">
+    <row r="997" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A997" s="2"/>
       <c r="B997" s="1"/>
     </row>
-    <row r="998" spans="1:2" ht="15.75">
+    <row r="998" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A998" s="2"/>
       <c r="B998" s="1"/>
     </row>
-    <row r="999" spans="1:2" ht="15.75">
+    <row r="999" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A999" s="2"/>
       <c r="B999" s="1"/>
     </row>
-    <row r="1000" spans="1:2" ht="15.75">
+    <row r="1000" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1000" s="2"/>
       <c r="B1000" s="1"/>
     </row>
-    <row r="1001" spans="1:2" ht="15.75">
+    <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1001" s="2"/>
       <c r="B1001" s="1"/>
     </row>
-    <row r="1002" spans="1:2" ht="15.75">
+    <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1002" s="2"/>
       <c r="B1002" s="1"/>
     </row>
-    <row r="1003" spans="1:2" ht="15.75">
+    <row r="1003" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1003" s="2"/>
       <c r="B1003" s="1"/>
     </row>
-    <row r="1004" spans="1:2" ht="15.75">
+    <row r="1004" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1004" s="2"/>
       <c r="B1004" s="1"/>
     </row>
-    <row r="1005" spans="1:2" ht="15.75">
+    <row r="1005" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1005" s="2"/>
       <c r="B1005" s="1"/>
     </row>
-    <row r="1006" spans="1:2" ht="15.75">
+    <row r="1006" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1006" s="2"/>
       <c r="B1006" s="1"/>
     </row>
-    <row r="1007" spans="1:2" ht="15.75">
+    <row r="1007" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1007" s="2"/>
       <c r="B1007" s="1"/>
     </row>
-    <row r="1008" spans="1:2" ht="15.75">
+    <row r="1008" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1008" s="2"/>
       <c r="B1008" s="1"/>
     </row>
-    <row r="1009" spans="1:2" ht="15.75">
+    <row r="1009" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1009" s="2"/>
       <c r="B1009" s="1"/>
     </row>
-    <row r="1010" spans="1:2" ht="15.75">
-      <c r="A1010" s="2"/>
+    <row r="1010" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1010" s="1"/>
       <c r="B1010" s="1"/>
     </row>
-    <row r="1011" spans="1:2" ht="15.75">
-      <c r="A1011" s="2"/>
+    <row r="1011" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1011" s="1"/>
       <c r="B1011" s="1"/>
     </row>
-    <row r="1012" spans="1:2" ht="15.75">
+    <row r="1012" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1012" s="1"/>
       <c r="B1012" s="1"/>
     </row>
-    <row r="1013" spans="1:2" ht="15.75">
+    <row r="1013" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1013" s="1"/>
       <c r="B1013" s="1"/>
     </row>
-    <row r="1014" spans="1:2" ht="15.75">
+    <row r="1014" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1014" s="1"/>
       <c r="B1014" s="1"/>
     </row>
-    <row r="1015" spans="1:2" ht="15.75">
+    <row r="1015" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1015" s="1"/>
       <c r="B1015" s="1"/>
     </row>
-    <row r="1016" spans="1:2" ht="15.75">
+    <row r="1016" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1016" s="1"/>
       <c r="B1016" s="1"/>
     </row>
-    <row r="1017" spans="1:2" ht="15.75">
+    <row r="1017" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1017" s="1"/>
       <c r="B1017" s="1"/>
     </row>
-    <row r="1018" spans="1:2" ht="15.75">
+    <row r="1018" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1018" s="1"/>
       <c r="B1018" s="1"/>
     </row>
-    <row r="1019" spans="1:2" ht="15.75">
+    <row r="1019" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1019" s="1"/>
       <c r="B1019" s="1"/>
     </row>
-    <row r="1020" spans="1:2" ht="15.75">
+    <row r="1020" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1020" s="1"/>
       <c r="B1020" s="1"/>
     </row>
-    <row r="1021" spans="1:2" ht="15.75">
+    <row r="1021" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1021" s="1"/>
       <c r="B1021" s="1"/>
     </row>
-    <row r="1022" spans="1:2" ht="15.75">
+    <row r="1022" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1022" s="1"/>
       <c r="B1022" s="1"/>
     </row>
-    <row r="1023" spans="1:2" ht="15.75">
+    <row r="1023" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1023" s="1"/>
       <c r="B1023" s="1"/>
     </row>
-    <row r="1024" spans="1:2" ht="15.75">
+    <row r="1024" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1024" s="1"/>
       <c r="B1024" s="1"/>
     </row>
-    <row r="1025" spans="1:2" ht="15.75">
+    <row r="1025" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1025" s="1"/>
       <c r="B1025" s="1"/>
     </row>
-    <row r="1026" spans="1:2" ht="15.75">
+    <row r="1026" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1026" s="1"/>
       <c r="B1026" s="1"/>
     </row>
-    <row r="1027" spans="1:2" ht="15.75">
+    <row r="1027" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1027" s="1"/>
       <c r="B1027" s="1"/>
     </row>
-    <row r="1028" spans="1:2" ht="15.75">
+    <row r="1028" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1028" s="1"/>
       <c r="B1028" s="1"/>
     </row>
-    <row r="1029" spans="1:2" ht="15.75">
+    <row r="1029" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1029" s="1"/>
       <c r="B1029" s="1"/>
     </row>
-    <row r="1030" spans="1:2" ht="15.75">
+    <row r="1030" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1030" s="1"/>
       <c r="B1030" s="1"/>
     </row>
-    <row r="1031" spans="1:2" ht="15.75">
+    <row r="1031" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1031" s="1"/>
       <c r="B1031" s="1"/>
     </row>
-    <row r="1032" spans="1:2" ht="15.75">
+    <row r="1032" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1032" s="1"/>
       <c r="B1032" s="1"/>
     </row>
-    <row r="1033" spans="1:2" ht="15.75">
+    <row r="1033" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1033" s="1"/>
       <c r="B1033" s="1"/>
     </row>
-    <row r="1034" spans="1:2" ht="15.75">
+    <row r="1034" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1034" s="1"/>
       <c r="B1034" s="1"/>
     </row>
-    <row r="1035" spans="1:2" ht="15.75">
+    <row r="1035" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1035" s="1"/>
       <c r="B1035" s="1"/>
     </row>
-    <row r="1036" spans="1:2" ht="15.75">
+    <row r="1036" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1036" s="1"/>
       <c r="B1036" s="1"/>
     </row>
-    <row r="1037" spans="1:2" ht="15.75">
+    <row r="1037" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1037" s="1"/>
       <c r="B1037" s="1"/>
     </row>
-    <row r="1038" spans="1:2" ht="15.75">
+    <row r="1038" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1038" s="1"/>
       <c r="B1038" s="1"/>
     </row>
-    <row r="1039" spans="1:2" ht="15.75">
+    <row r="1039" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1039" s="1"/>
       <c r="B1039" s="1"/>
     </row>
-    <row r="1040" spans="1:2" ht="15.75">
+    <row r="1040" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1040" s="1"/>
       <c r="B1040" s="1"/>
     </row>
-    <row r="1041" spans="1:2" ht="15.75">
+    <row r="1041" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1041" s="1"/>
       <c r="B1041" s="1"/>
     </row>
-    <row r="1042" spans="1:2" ht="15.75">
+    <row r="1042" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1042" s="1"/>
       <c r="B1042" s="1"/>
     </row>
-    <row r="1043" spans="1:2" ht="15.75">
+    <row r="1043" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1043" s="1"/>
       <c r="B1043" s="1"/>
     </row>
-    <row r="1044" spans="1:2" ht="15.75">
+    <row r="1044" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1044" s="1"/>
       <c r="B1044" s="1"/>
     </row>
-    <row r="1045" spans="1:2" ht="15.75">
+    <row r="1045" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1045" s="1"/>
       <c r="B1045" s="1"/>
     </row>
-    <row r="1046" spans="1:2" ht="15.75">
+    <row r="1046" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1046" s="1"/>
       <c r="B1046" s="1"/>
     </row>
-    <row r="1047" spans="1:2" ht="15.75">
+    <row r="1047" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1047" s="1"/>
       <c r="B1047" s="1"/>
     </row>
-    <row r="1048" spans="1:2" ht="15.75">
+    <row r="1048" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1048" s="1"/>
       <c r="B1048" s="1"/>
     </row>
-    <row r="1049" spans="1:2" ht="15.75">
+    <row r="1049" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1049" s="1"/>
       <c r="B1049" s="1"/>
     </row>
-    <row r="1050" spans="1:2" ht="15.75">
+    <row r="1050" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1050" s="1"/>
       <c r="B1050" s="1"/>
     </row>
-    <row r="1051" spans="1:2" ht="15.75">
+    <row r="1051" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1051" s="1"/>
       <c r="B1051" s="1"/>
     </row>
-    <row r="1052" spans="1:2" ht="15.75">
+    <row r="1052" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1052" s="1"/>
       <c r="B1052" s="1"/>
     </row>
-    <row r="1053" spans="1:2" ht="15.75">
+    <row r="1053" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1053" s="1"/>
       <c r="B1053" s="1"/>
     </row>
-    <row r="1054" spans="1:2" ht="15.75">
+    <row r="1054" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1054" s="1"/>
       <c r="B1054" s="1"/>
     </row>
-    <row r="1055" spans="1:2" ht="15.75">
+    <row r="1055" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1055" s="1"/>
       <c r="B1055" s="1"/>
     </row>
-    <row r="1056" spans="1:2" ht="15.75">
+    <row r="1056" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1056" s="1"/>
       <c r="B1056" s="1"/>
     </row>
-    <row r="1057" spans="1:2" ht="15.75">
+    <row r="1057" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1057" s="1"/>
       <c r="B1057" s="1"/>
     </row>
-    <row r="1058" spans="1:2" ht="15.75">
+    <row r="1058" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1058" s="1"/>
       <c r="B1058" s="1"/>
     </row>
-    <row r="1059" spans="1:2" ht="15.75">
+    <row r="1059" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1059" s="1"/>
       <c r="B1059" s="1"/>
     </row>
-    <row r="1060" spans="1:2" ht="15.75">
+    <row r="1060" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1060" s="1"/>
       <c r="B1060" s="1"/>
     </row>
-    <row r="1061" spans="1:2" ht="15.75">
+    <row r="1061" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1061" s="1"/>
       <c r="B1061" s="1"/>
     </row>
-    <row r="1062" spans="1:2" ht="15.75">
+    <row r="1062" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1062" s="1"/>
       <c r="B1062" s="1"/>
     </row>
-    <row r="1063" spans="1:2" ht="15.75">
+    <row r="1063" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1063" s="1"/>
       <c r="B1063" s="1"/>
     </row>
-    <row r="1064" spans="1:2" ht="15.75">
+    <row r="1064" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1064" s="1"/>
       <c r="B1064" s="1"/>
     </row>
-    <row r="1065" spans="1:2" ht="15.75">
+    <row r="1065" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1065" s="1"/>
       <c r="B1065" s="1"/>
     </row>
-    <row r="1066" spans="1:2" ht="15.75">
+    <row r="1066" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1066" s="1"/>
       <c r="B1066" s="1"/>
     </row>
-    <row r="1067" spans="1:2" ht="15.75">
+    <row r="1067" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1067" s="1"/>
       <c r="B1067" s="1"/>
     </row>
-    <row r="1068" spans="1:2" ht="15.75">
+    <row r="1068" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1068" s="1"/>
       <c r="B1068" s="1"/>
     </row>
-    <row r="1069" spans="1:2" ht="15.75">
+    <row r="1069" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1069" s="1"/>
       <c r="B1069" s="1"/>
     </row>
-    <row r="1070" spans="1:2" ht="15.75">
+    <row r="1070" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1070" s="1"/>
       <c r="B1070" s="1"/>
     </row>
-    <row r="1071" spans="1:2" ht="15.75">
+    <row r="1071" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1071" s="1"/>
       <c r="B1071" s="1"/>
     </row>
-    <row r="1072" spans="1:2" ht="15.75">
+    <row r="1072" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1072" s="1"/>
       <c r="B1072" s="1"/>
     </row>
-    <row r="1073" spans="1:2" ht="15.75">
+    <row r="1073" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1073" s="1"/>
       <c r="B1073" s="1"/>
     </row>
-    <row r="1074" spans="1:2" ht="15.75">
+    <row r="1074" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1074" s="1"/>
       <c r="B1074" s="1"/>
     </row>
-    <row r="1075" spans="1:2" ht="15.75">
+    <row r="1075" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1075" s="1"/>
       <c r="B1075" s="1"/>
     </row>
-    <row r="1076" spans="1:2" ht="15.75">
+    <row r="1076" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1076" s="1"/>
       <c r="B1076" s="1"/>
     </row>
-    <row r="1077" spans="1:2" ht="15.75">
+    <row r="1077" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1077" s="1"/>
       <c r="B1077" s="1"/>
     </row>
-    <row r="1078" spans="1:2" ht="15.75">
+    <row r="1078" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1078" s="1"/>
       <c r="B1078" s="1"/>
     </row>
-    <row r="1079" spans="1:2" ht="15.75">
+    <row r="1079" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1079" s="1"/>
       <c r="B1079" s="1"/>
     </row>
-    <row r="1080" spans="1:2" ht="15.75">
+    <row r="1080" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1080" s="1"/>
       <c r="B1080" s="1"/>
     </row>
-    <row r="1081" spans="1:2" ht="15.75">
+    <row r="1081" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1081" s="1"/>
       <c r="B1081" s="1"/>
     </row>
-    <row r="1082" spans="1:2" ht="15.75">
+    <row r="1082" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1082" s="1"/>
       <c r="B1082" s="1"/>
     </row>
-    <row r="1083" spans="1:2" ht="15.75">
+    <row r="1083" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1083" s="1"/>
       <c r="B1083" s="1"/>
     </row>
-    <row r="1084" spans="1:2" ht="15.75">
+    <row r="1084" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1084" s="1"/>
       <c r="B1084" s="1"/>
     </row>
-    <row r="1085" spans="1:2" ht="15.75">
+    <row r="1085" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1085" s="1"/>
       <c r="B1085" s="1"/>
     </row>
-    <row r="1086" spans="1:2" ht="15.75">
+    <row r="1086" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1086" s="1"/>
       <c r="B1086" s="1"/>
     </row>
-    <row r="1087" spans="1:2" ht="15.75">
+    <row r="1087" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1087" s="1"/>
       <c r="B1087" s="1"/>
     </row>
-    <row r="1088" spans="1:2" ht="15.75">
+    <row r="1088" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1088" s="1"/>
       <c r="B1088" s="1"/>
     </row>
-    <row r="1089" spans="1:2" ht="15.75">
+    <row r="1089" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1089" s="1"/>
       <c r="B1089" s="1"/>
     </row>
-    <row r="1090" spans="1:2" ht="15.75">
+    <row r="1090" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1090" s="1"/>
       <c r="B1090" s="1"/>
     </row>
-    <row r="1091" spans="1:2" ht="15.75">
+    <row r="1091" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1091" s="1"/>
       <c r="B1091" s="1"/>
     </row>
-    <row r="1092" spans="1:2" ht="15.75">
+    <row r="1092" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1092" s="1"/>
       <c r="B1092" s="1"/>
     </row>
-    <row r="1093" spans="1:2" ht="15.75">
+    <row r="1093" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1093" s="1"/>
       <c r="B1093" s="1"/>
     </row>
-    <row r="1094" spans="1:2" ht="15.75">
+    <row r="1094" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1094" s="1"/>
       <c r="B1094" s="1"/>
     </row>
-    <row r="1095" spans="1:2" ht="15.75">
+    <row r="1095" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1095" s="1"/>
       <c r="B1095" s="1"/>
     </row>
-    <row r="1096" spans="1:2" ht="15.75">
+    <row r="1096" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1096" s="1"/>
       <c r="B1096" s="1"/>
     </row>
-    <row r="1097" spans="1:2" ht="15.75">
+    <row r="1097" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1097" s="1"/>
       <c r="B1097" s="1"/>
     </row>
-    <row r="1098" spans="1:2" ht="15.75">
+    <row r="1098" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1098" s="1"/>
       <c r="B1098" s="1"/>
     </row>
-    <row r="1099" spans="1:2" ht="15.75">
+    <row r="1099" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1099" s="1"/>
       <c r="B1099" s="1"/>
     </row>
-    <row r="1100" spans="1:2" ht="15.75">
+    <row r="1100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1100" s="1"/>
       <c r="B1100" s="1"/>
     </row>
-    <row r="1101" spans="1:2" ht="15.75">
+    <row r="1101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1101" s="1"/>
       <c r="B1101" s="1"/>
     </row>
-    <row r="1102" spans="1:2" ht="15.75">
+    <row r="1102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1102" s="1"/>
       <c r="B1102" s="1"/>
     </row>
-    <row r="1103" spans="1:2" ht="15.75">
+    <row r="1103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1103" s="1"/>
       <c r="B1103" s="1"/>
     </row>
-    <row r="1104" spans="1:2" ht="15.75">
+    <row r="1104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1104" s="1"/>
       <c r="B1104" s="1"/>
     </row>
-    <row r="1105" spans="1:2" ht="15.75">
+    <row r="1105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1105" s="1"/>
       <c r="B1105" s="1"/>
     </row>
-    <row r="1106" spans="1:2" ht="15.75">
+    <row r="1106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1106" s="1"/>
       <c r="B1106" s="1"/>
     </row>
-    <row r="1107" spans="1:2" ht="15.75">
+    <row r="1107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1107" s="1"/>
       <c r="B1107" s="1"/>
     </row>
-    <row r="1108" spans="1:2" ht="15.75">
+    <row r="1108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1108" s="1"/>
       <c r="B1108" s="1"/>
     </row>
-    <row r="1109" spans="1:2" ht="15.75">
+    <row r="1109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1109" s="1"/>
       <c r="B1109" s="1"/>
     </row>
-    <row r="1110" spans="1:2" ht="15.75">
+    <row r="1110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1110" s="1"/>
       <c r="B1110" s="1"/>
     </row>
-    <row r="1111" spans="1:2" ht="15.75">
+    <row r="1111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1111" s="1"/>
       <c r="B1111" s="1"/>
     </row>
-    <row r="1112" spans="1:2" ht="15.75">
+    <row r="1112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1112" s="1"/>
       <c r="B1112" s="1"/>
     </row>
-    <row r="1113" spans="1:2" ht="15.75">
+    <row r="1113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1113" s="1"/>
       <c r="B1113" s="1"/>
     </row>
-    <row r="1114" spans="1:2" ht="15.75">
+    <row r="1114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1114" s="1"/>
       <c r="B1114" s="1"/>
     </row>
-    <row r="1115" spans="1:2" ht="15.75">
+    <row r="1115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1115" s="1"/>
       <c r="B1115" s="1"/>
     </row>
-    <row r="1116" spans="1:2" ht="15.75">
+    <row r="1116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1116" s="1"/>
       <c r="B1116" s="1"/>
     </row>
-    <row r="1117" spans="1:2" ht="15.75">
+    <row r="1117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1117" s="1"/>
       <c r="B1117" s="1"/>
     </row>
-    <row r="1118" spans="1:2" ht="15.75">
+    <row r="1118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1118" s="1"/>
       <c r="B1118" s="1"/>
     </row>
-    <row r="1119" spans="1:2" ht="15.75">
+    <row r="1119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1119" s="1"/>
       <c r="B1119" s="1"/>
     </row>
-    <row r="1120" spans="1:2" ht="15.75">
+    <row r="1120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1120" s="1"/>
       <c r="B1120" s="1"/>
     </row>
-    <row r="1121" spans="1:2" ht="15.75">
+    <row r="1121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1121" s="1"/>
       <c r="B1121" s="1"/>
     </row>
-    <row r="1122" spans="1:2" ht="15.75">
+    <row r="1122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1122" s="1"/>
       <c r="B1122" s="1"/>
     </row>
-    <row r="1123" spans="1:2" ht="15.75">
+    <row r="1123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1123" s="1"/>
       <c r="B1123" s="1"/>
     </row>
-    <row r="1124" spans="1:2" ht="15.75">
+    <row r="1124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1124" s="1"/>
       <c r="B1124" s="1"/>
     </row>
-    <row r="1125" spans="1:2" ht="15.75">
+    <row r="1125" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1125" s="1"/>
       <c r="B1125" s="1"/>
     </row>
-    <row r="1126" spans="1:2" ht="15.75">
+    <row r="1126" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1126" s="1"/>
       <c r="B1126" s="1"/>
     </row>
-    <row r="1127" spans="1:2" ht="15.75">
+    <row r="1127" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1127" s="1"/>
       <c r="B1127" s="1"/>
     </row>
-    <row r="1128" spans="1:2" ht="15.75">
+    <row r="1128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1128" s="1"/>
       <c r="B1128" s="1"/>
     </row>
-    <row r="1129" spans="1:2" ht="15.75">
+    <row r="1129" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1129" s="1"/>
       <c r="B1129" s="1"/>
     </row>
-    <row r="1130" spans="1:2" ht="15.75">
+    <row r="1130" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1130" s="1"/>
       <c r="B1130" s="1"/>
     </row>
-    <row r="1131" spans="1:2" ht="15.75">
+    <row r="1131" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1131" s="1"/>
       <c r="B1131" s="1"/>
     </row>
-    <row r="1132" spans="1:2" ht="15.75">
+    <row r="1132" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1132" s="1"/>
       <c r="B1132" s="1"/>
     </row>
-    <row r="1133" spans="1:2" ht="15.75">
+    <row r="1133" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1133" s="1"/>
       <c r="B1133" s="1"/>
     </row>
-    <row r="1134" spans="1:2" ht="15.75">
+    <row r="1134" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1134" s="1"/>
       <c r="B1134" s="1"/>
     </row>
-    <row r="1135" spans="1:2" ht="15.75">
+    <row r="1135" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1135" s="1"/>
       <c r="B1135" s="1"/>
     </row>
-    <row r="1136" spans="1:2" ht="15.75">
+    <row r="1136" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1136" s="1"/>
       <c r="B1136" s="1"/>
     </row>
-    <row r="1137" spans="1:2" ht="15.75">
+    <row r="1137" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1137" s="1"/>
       <c r="B1137" s="1"/>
     </row>
-    <row r="1138" spans="1:2" ht="15.75">
+    <row r="1138" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1138" s="1"/>
       <c r="B1138" s="1"/>
     </row>
-    <row r="1139" spans="1:2" ht="15.75">
+    <row r="1139" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1139" s="1"/>
       <c r="B1139" s="1"/>
     </row>
-    <row r="1140" spans="1:2" ht="15.75">
+    <row r="1140" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1140" s="1"/>
       <c r="B1140" s="1"/>
     </row>
-    <row r="1141" spans="1:2" ht="15.75">
+    <row r="1141" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1141" s="1"/>
       <c r="B1141" s="1"/>
     </row>
-    <row r="1142" spans="1:2" ht="15.75">
+    <row r="1142" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1142" s="1"/>
       <c r="B1142" s="1"/>
     </row>
-    <row r="1143" spans="1:2" ht="15.75">
+    <row r="1143" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1143" s="1"/>
       <c r="B1143" s="1"/>
     </row>
-    <row r="1144" spans="1:2" ht="15.75">
+    <row r="1144" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1144" s="1"/>
       <c r="B1144" s="1"/>
     </row>
-    <row r="1145" spans="1:2" ht="15.75">
+    <row r="1145" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1145" s="1"/>
       <c r="B1145" s="1"/>
     </row>
-    <row r="1146" spans="1:2" ht="15.75">
+    <row r="1146" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1146" s="1"/>
       <c r="B1146" s="1"/>
     </row>
-    <row r="1147" spans="1:2" ht="15.75">
+    <row r="1147" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1147" s="1"/>
       <c r="B1147" s="1"/>
     </row>
-    <row r="1148" spans="1:2" ht="15.75">
+    <row r="1148" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1148" s="1"/>
       <c r="B1148" s="1"/>
     </row>
-    <row r="1149" spans="1:2" ht="15.75">
+    <row r="1149" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1149" s="1"/>
       <c r="B1149" s="1"/>
     </row>
-    <row r="1150" spans="1:2" ht="15.75">
+    <row r="1150" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1150" s="1"/>
       <c r="B1150" s="1"/>
     </row>
-    <row r="1151" spans="1:2" ht="15.75">
+    <row r="1151" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1151" s="1"/>
       <c r="B1151" s="1"/>
     </row>
-    <row r="1152" spans="1:2" ht="15.75">
+    <row r="1152" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1152" s="1"/>
       <c r="B1152" s="1"/>
     </row>
-    <row r="1153" spans="1:2" ht="15.75">
+    <row r="1153" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1153" s="1"/>
       <c r="B1153" s="1"/>
     </row>
-    <row r="1154" spans="1:2" ht="15.75">
+    <row r="1154" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1154" s="1"/>
       <c r="B1154" s="1"/>
     </row>
-    <row r="1155" spans="1:2" ht="15.75">
+    <row r="1155" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1155" s="1"/>
       <c r="B1155" s="1"/>
     </row>
-    <row r="1156" spans="1:2" ht="15.75">
+    <row r="1156" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1156" s="1"/>
       <c r="B1156" s="1"/>
     </row>
-    <row r="1157" spans="1:2" ht="15.75">
+    <row r="1157" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1157" s="1"/>
       <c r="B1157" s="1"/>
     </row>
-    <row r="1158" spans="1:2" ht="15.75">
+    <row r="1158" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1158" s="1"/>
       <c r="B1158" s="1"/>
     </row>
-    <row r="1159" spans="1:2" ht="15.75">
+    <row r="1159" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1159" s="1"/>
       <c r="B1159" s="1"/>
     </row>
-    <row r="1160" spans="1:2" ht="15.75">
+    <row r="1160" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1160" s="1"/>
       <c r="B1160" s="1"/>
     </row>
-    <row r="1161" spans="1:2" ht="15.75">
+    <row r="1161" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1161" s="1"/>
       <c r="B1161" s="1"/>
     </row>
-    <row r="1162" spans="1:2" ht="15.75">
+    <row r="1162" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1162" s="1"/>
       <c r="B1162" s="1"/>
     </row>
-    <row r="1163" spans="1:2" ht="15.75">
+    <row r="1163" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1163" s="1"/>
       <c r="B1163" s="1"/>
     </row>
-    <row r="1164" spans="1:2" ht="15.75">
+    <row r="1164" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1164" s="1"/>
       <c r="B1164" s="1"/>
     </row>
-    <row r="1165" spans="1:2" ht="15.75">
+    <row r="1165" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1165" s="1"/>
       <c r="B1165" s="1"/>
     </row>
-    <row r="1166" spans="1:2" ht="15.75">
+    <row r="1166" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1166" s="1"/>
       <c r="B1166" s="1"/>
     </row>
-    <row r="1167" spans="1:2" ht="15.75">
+    <row r="1167" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1167" s="1"/>
       <c r="B1167" s="1"/>
     </row>
-    <row r="1168" spans="1:2" ht="15.75">
+    <row r="1168" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1168" s="1"/>
       <c r="B1168" s="1"/>
     </row>
-    <row r="1169" spans="1:2" ht="15.75">
+    <row r="1169" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1169" s="1"/>
       <c r="B1169" s="1"/>
     </row>
-    <row r="1170" spans="1:2" ht="15.75">
+    <row r="1170" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1170" s="1"/>
       <c r="B1170" s="1"/>
     </row>
-    <row r="1171" spans="1:2" ht="15.75">
+    <row r="1171" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1171" s="1"/>
       <c r="B1171" s="1"/>
     </row>
-    <row r="1172" spans="1:2" ht="15.75">
+    <row r="1172" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1172" s="1"/>
       <c r="B1172" s="1"/>
     </row>
-    <row r="1173" spans="1:2" ht="15.75">
+    <row r="1173" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1173" s="1"/>
       <c r="B1173" s="1"/>
     </row>
-    <row r="1174" spans="1:2" ht="15.75">
+    <row r="1174" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1174" s="1"/>
       <c r="B1174" s="1"/>
     </row>
-    <row r="1175" spans="1:2" ht="15.75">
+    <row r="1175" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1175" s="1"/>
       <c r="B1175" s="1"/>
     </row>
-    <row r="1176" spans="1:2" ht="15.75">
+    <row r="1176" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1176" s="1"/>
       <c r="B1176" s="1"/>
     </row>
-    <row r="1177" spans="1:2" ht="15.75">
+    <row r="1177" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1177" s="1"/>
       <c r="B1177" s="1"/>
     </row>
-    <row r="1178" spans="1:2" ht="15.75">
+    <row r="1178" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1178" s="1"/>
       <c r="B1178" s="1"/>
     </row>
-    <row r="1179" spans="1:2" ht="15.75">
+    <row r="1179" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1179" s="1"/>
       <c r="B1179" s="1"/>
     </row>
-    <row r="1180" spans="1:2" ht="15.75">
+    <row r="1180" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1180" s="1"/>
       <c r="B1180" s="1"/>
     </row>
-    <row r="1181" spans="1:2" ht="15.75">
+    <row r="1181" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1181" s="1"/>
       <c r="B1181" s="1"/>
     </row>
-    <row r="1182" spans="1:2" ht="15.75">
+    <row r="1182" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1182" s="1"/>
       <c r="B1182" s="1"/>
     </row>
-    <row r="1183" spans="1:2" ht="15.75">
+    <row r="1183" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1183" s="1"/>
       <c r="B1183" s="1"/>
     </row>
-    <row r="1184" spans="1:2" ht="15.75">
+    <row r="1184" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1184" s="1"/>
       <c r="B1184" s="1"/>
     </row>
-    <row r="1185" spans="1:2" ht="15.75">
+    <row r="1185" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1185" s="1"/>
       <c r="B1185" s="1"/>
     </row>
-    <row r="1186" spans="1:2" ht="15.75">
+    <row r="1186" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1186" s="1"/>
       <c r="B1186" s="1"/>
     </row>
-    <row r="1187" spans="1:2" ht="15.75">
+    <row r="1187" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1187" s="1"/>
       <c r="B1187" s="1"/>
     </row>
-    <row r="1188" spans="1:2" ht="15.75">
+    <row r="1188" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1188" s="1"/>
       <c r="B1188" s="1"/>
     </row>
-    <row r="1189" spans="1:2" ht="15.75">
+    <row r="1189" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1189" s="1"/>
       <c r="B1189" s="1"/>
     </row>
-    <row r="1190" spans="1:2" ht="15.75">
+    <row r="1190" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1190" s="1"/>
       <c r="B1190" s="1"/>
     </row>
-    <row r="1191" spans="1:2" ht="15.75">
+    <row r="1191" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1191" s="1"/>
       <c r="B1191" s="1"/>
     </row>
-    <row r="1192" spans="1:2" ht="15.75">
+    <row r="1192" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1192" s="1"/>
       <c r="B1192" s="1"/>
     </row>
-    <row r="1193" spans="1:2" ht="15.75">
+    <row r="1193" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1193" s="1"/>
       <c r="B1193" s="1"/>
     </row>
-    <row r="1194" spans="1:2" ht="15.75">
+    <row r="1194" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1194" s="1"/>
       <c r="B1194" s="1"/>
     </row>
-    <row r="1195" spans="1:2" ht="15.75">
+    <row r="1195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1195" s="1"/>
       <c r="B1195" s="1"/>
     </row>
-    <row r="1196" spans="1:2" ht="15.75">
+    <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1196" s="1"/>
       <c r="B1196" s="1"/>
     </row>
-    <row r="1197" spans="1:2" ht="15.75">
+    <row r="1197" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1197" s="1"/>
       <c r="B1197" s="1"/>
     </row>
-    <row r="1198" spans="1:2" ht="15.75">
+    <row r="1198" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1198" s="1"/>
       <c r="B1198" s="1"/>
     </row>
-    <row r="1199" spans="1:2" ht="15.75">
+    <row r="1199" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1199" s="1"/>
       <c r="B1199" s="1"/>
     </row>
-    <row r="1200" spans="1:2" ht="15.75">
+    <row r="1200" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1200" s="1"/>
       <c r="B1200" s="1"/>
     </row>
-    <row r="1201" spans="1:2" ht="15.75">
+    <row r="1201" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1201" s="1"/>
       <c r="B1201" s="1"/>
     </row>
-    <row r="1202" spans="1:2" ht="15.75">
+    <row r="1202" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1202" s="1"/>
       <c r="B1202" s="1"/>
     </row>
-    <row r="1203" spans="1:2" ht="15.75">
+    <row r="1203" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1203" s="1"/>
       <c r="B1203" s="1"/>
     </row>
-    <row r="1204" spans="1:2" ht="15.75">
+    <row r="1204" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1204" s="1"/>
       <c r="B1204" s="1"/>
-    </row>
-    <row r="1205" spans="1:2" ht="15.75">
-      <c r="A1205" s="1"/>
-      <c r="B1205" s="1"/>
-    </row>
-    <row r="1206" spans="1:2" ht="15.75">
-      <c r="A1206" s="1"/>
-      <c r="B1206" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10528,40 +10500,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA90CD46-FF53-412A-950C-99718992C948}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{252F1683-31E9-46D6-B8E9-91300310265C}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAE79998-B747-4041-95CF-2F89056D2D63}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="15">
-        <v>1040077371</v>
+        <v>1040100560</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>145</v>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0004796B-CDA4-4C58-83F2-433A24F639E6}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C007812D-C761-4AF8-B92C-B8C8C6FD394F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="515">
   <si>
     <t>material</t>
   </si>
@@ -280,6 +280,12 @@
   </si>
   <si>
     <t>CATRACA FREIO CAVALO DIANT (L/E)</t>
+  </si>
+  <si>
+    <t>CINTA BUJÃO DE AR DOLLY</t>
+  </si>
+  <si>
+    <t>CINTA DO BUJÃO DE AR CARRETA</t>
   </si>
   <si>
     <t>CINTA BUJÃO DE AR P</t>
@@ -2164,7 +2170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1208"/>
+  <dimension ref="A1:D1210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3021,7 +3027,7 @@
     </row>
     <row r="78" spans="1:3" ht="15.75">
       <c r="A78" s="14">
-        <v>1010053885</v>
+        <v>1010087609</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>80</v>
@@ -3031,8 +3037,8 @@
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75">
-      <c r="A79" s="15">
-        <v>1040097102</v>
+      <c r="A79" s="14">
+        <v>1010087738</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>81</v>
@@ -3042,10 +3048,10 @@
       </c>
     </row>
     <row r="80" spans="1:3" ht="15.75">
-      <c r="A80" s="15">
-        <v>1010020838</v>
-      </c>
-      <c r="B80" s="8" t="s">
+      <c r="A80" s="14">
+        <v>1010053885</v>
+      </c>
+      <c r="B80" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -3053,10 +3059,10 @@
       </c>
     </row>
     <row r="81" spans="1:3" ht="15.75">
-      <c r="A81" s="16">
-        <v>341430</v>
-      </c>
-      <c r="B81" s="10" t="s">
+      <c r="A81" s="15">
+        <v>1040097102</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C81" s="4" t="s">
@@ -3065,9 +3071,9 @@
     </row>
     <row r="82" spans="1:3" ht="15.75">
       <c r="A82" s="15">
-        <v>1010042643</v>
-      </c>
-      <c r="B82" s="9" t="s">
+        <v>1010020838</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>84</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -3075,10 +3081,10 @@
       </c>
     </row>
     <row r="83" spans="1:3" ht="15.75">
-      <c r="A83" s="15">
-        <v>425554</v>
-      </c>
-      <c r="B83" s="5" t="s">
+      <c r="A83" s="16">
+        <v>341430</v>
+      </c>
+      <c r="B83" s="10" t="s">
         <v>85</v>
       </c>
       <c r="C83" s="4" t="s">
@@ -3087,9 +3093,9 @@
     </row>
     <row r="84" spans="1:3" ht="15.75">
       <c r="A84" s="15">
-        <v>1010084162</v>
-      </c>
-      <c r="B84" s="5" t="s">
+        <v>1010042643</v>
+      </c>
+      <c r="B84" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C84" s="4" t="s">
@@ -3098,7 +3104,7 @@
     </row>
     <row r="85" spans="1:3" ht="15.75">
       <c r="A85" s="15">
-        <v>1010084157</v>
+        <v>425554</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>87</v>
@@ -3109,7 +3115,7 @@
     </row>
     <row r="86" spans="1:3" ht="15.75">
       <c r="A86" s="15">
-        <v>1010084158</v>
+        <v>1010084162</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>88</v>
@@ -3120,7 +3126,7 @@
     </row>
     <row r="87" spans="1:3" ht="15.75">
       <c r="A87" s="15">
-        <v>1010084159</v>
+        <v>1010084157</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>89</v>
@@ -3131,7 +3137,7 @@
     </row>
     <row r="88" spans="1:3" ht="15.75">
       <c r="A88" s="15">
-        <v>1010084160</v>
+        <v>1010084158</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>90</v>
@@ -3142,7 +3148,7 @@
     </row>
     <row r="89" spans="1:3" ht="15.75">
       <c r="A89" s="15">
-        <v>1010084161</v>
+        <v>1010084159</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>91</v>
@@ -3153,7 +3159,7 @@
     </row>
     <row r="90" spans="1:3" ht="15.75">
       <c r="A90" s="15">
-        <v>224382</v>
+        <v>1010084160</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>92</v>
@@ -3164,7 +3170,7 @@
     </row>
     <row r="91" spans="1:3" ht="15.75">
       <c r="A91" s="15">
-        <v>94314</v>
+        <v>1010084161</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>93</v>
@@ -3174,8 +3180,8 @@
       </c>
     </row>
     <row r="92" spans="1:3" ht="15.75">
-      <c r="A92" s="17">
-        <v>1010003982</v>
+      <c r="A92" s="15">
+        <v>224382</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>94</v>
@@ -3186,7 +3192,7 @@
     </row>
     <row r="93" spans="1:3" ht="15.75">
       <c r="A93" s="15">
-        <v>1010000182</v>
+        <v>94314</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>95</v>
@@ -3196,8 +3202,8 @@
       </c>
     </row>
     <row r="94" spans="1:3" ht="15.75">
-      <c r="A94" s="15">
-        <v>1010021079</v>
+      <c r="A94" s="17">
+        <v>1010003982</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>96</v>
@@ -3208,7 +3214,7 @@
     </row>
     <row r="95" spans="1:3" ht="15.75">
       <c r="A95" s="15">
-        <v>1010002463</v>
+        <v>1010000182</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>97</v>
@@ -3219,7 +3225,7 @@
     </row>
     <row r="96" spans="1:3" ht="15.75">
       <c r="A96" s="15">
-        <v>1010062982</v>
+        <v>1010021079</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>98</v>
@@ -3230,7 +3236,7 @@
     </row>
     <row r="97" spans="1:3" ht="15.75">
       <c r="A97" s="15">
-        <v>1010063209</v>
+        <v>1010002463</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>99</v>
@@ -3241,7 +3247,7 @@
     </row>
     <row r="98" spans="1:3" ht="15.75">
       <c r="A98" s="15">
-        <v>1040076302</v>
+        <v>1010062982</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>100</v>
@@ -3252,7 +3258,7 @@
     </row>
     <row r="99" spans="1:3" ht="15.75">
       <c r="A99" s="15">
-        <v>1040077362</v>
+        <v>1010063209</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>101</v>
@@ -3263,7 +3269,7 @@
     </row>
     <row r="100" spans="1:3" ht="15.75">
       <c r="A100" s="15">
-        <v>1040077363</v>
+        <v>1040076302</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>102</v>
@@ -3274,7 +3280,7 @@
     </row>
     <row r="101" spans="1:3" ht="15.75">
       <c r="A101" s="15">
-        <v>1040074483</v>
+        <v>1040077362</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>103</v>
@@ -3285,7 +3291,7 @@
     </row>
     <row r="102" spans="1:3" ht="15.75">
       <c r="A102" s="15">
-        <v>1040077364</v>
+        <v>1040077363</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>104</v>
@@ -3296,7 +3302,7 @@
     </row>
     <row r="103" spans="1:3" ht="15.75">
       <c r="A103" s="15">
-        <v>1040048463</v>
+        <v>1040074483</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>105</v>
@@ -3307,7 +3313,7 @@
     </row>
     <row r="104" spans="1:3" ht="15.75">
       <c r="A104" s="15">
-        <v>1040096343</v>
+        <v>1040077364</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>106</v>
@@ -3318,7 +3324,7 @@
     </row>
     <row r="105" spans="1:3" ht="15.75">
       <c r="A105" s="15">
-        <v>409640</v>
+        <v>1040048463</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>107</v>
@@ -3329,7 +3335,7 @@
     </row>
     <row r="106" spans="1:3" ht="15.75">
       <c r="A106" s="15">
-        <v>1010032753</v>
+        <v>1040096343</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>108</v>
@@ -3340,7 +3346,7 @@
     </row>
     <row r="107" spans="1:3" ht="15.75">
       <c r="A107" s="15">
-        <v>1040098597</v>
+        <v>409640</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>109</v>
@@ -3351,7 +3357,7 @@
     </row>
     <row r="108" spans="1:3" ht="15.75">
       <c r="A108" s="15">
-        <v>1040084464</v>
+        <v>1010032753</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>110</v>
@@ -3362,7 +3368,7 @@
     </row>
     <row r="109" spans="1:3" ht="15.75">
       <c r="A109" s="15">
-        <v>1040017773</v>
+        <v>1040098597</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>111</v>
@@ -3373,7 +3379,7 @@
     </row>
     <row r="110" spans="1:3" ht="15.75">
       <c r="A110" s="15">
-        <v>1010007405</v>
+        <v>1040084464</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>112</v>
@@ -3383,8 +3389,8 @@
       </c>
     </row>
     <row r="111" spans="1:3" ht="15.75">
-      <c r="A111" s="17">
-        <v>1040077365</v>
+      <c r="A111" s="15">
+        <v>1040017773</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>113</v>
@@ -3395,7 +3401,7 @@
     </row>
     <row r="112" spans="1:3" ht="15.75">
       <c r="A112" s="15">
-        <v>1010027794</v>
+        <v>1010007405</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>114</v>
@@ -3405,8 +3411,8 @@
       </c>
     </row>
     <row r="113" spans="1:3" ht="15.75">
-      <c r="A113" s="15">
-        <v>1040077366</v>
+      <c r="A113" s="17">
+        <v>1040077365</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>115</v>
@@ -3417,7 +3423,7 @@
     </row>
     <row r="114" spans="1:3" ht="15.75">
       <c r="A114" s="15">
-        <v>1040077367</v>
+        <v>1010027794</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>116</v>
@@ -3428,7 +3434,7 @@
     </row>
     <row r="115" spans="1:3" ht="15.75">
       <c r="A115" s="15">
-        <v>1010021561</v>
+        <v>1040077366</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>117</v>
@@ -3439,7 +3445,7 @@
     </row>
     <row r="116" spans="1:3" ht="15.75">
       <c r="A116" s="15">
-        <v>1010021562</v>
+        <v>1040077367</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>118</v>
@@ -3450,7 +3456,7 @@
     </row>
     <row r="117" spans="1:3" ht="15.75">
       <c r="A117" s="15">
-        <v>1010027792</v>
+        <v>1010021561</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>119</v>
@@ -3461,7 +3467,7 @@
     </row>
     <row r="118" spans="1:3" ht="15.75">
       <c r="A118" s="15">
-        <v>1010084930</v>
+        <v>1010021562</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>120</v>
@@ -3472,7 +3478,7 @@
     </row>
     <row r="119" spans="1:3" ht="15.75">
       <c r="A119" s="15">
-        <v>341430</v>
+        <v>1010027792</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>121</v>
@@ -3483,7 +3489,7 @@
     </row>
     <row r="120" spans="1:3" ht="15.75">
       <c r="A120" s="15">
-        <v>1010029366</v>
+        <v>1010084930</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>122</v>
@@ -3493,8 +3499,8 @@
       </c>
     </row>
     <row r="121" spans="1:3" ht="15.75">
-      <c r="A121" s="18">
-        <v>1010031723</v>
+      <c r="A121" s="15">
+        <v>341430</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>123</v>
@@ -3504,8 +3510,8 @@
       </c>
     </row>
     <row r="122" spans="1:3" ht="15.75">
-      <c r="A122" s="18">
-        <v>1010049216</v>
+      <c r="A122" s="15">
+        <v>1010029366</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>124</v>
@@ -3515,8 +3521,8 @@
       </c>
     </row>
     <row r="123" spans="1:3" ht="15.75">
-      <c r="A123" s="15">
-        <v>405558</v>
+      <c r="A123" s="18">
+        <v>1010031723</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>125</v>
@@ -3526,8 +3532,8 @@
       </c>
     </row>
     <row r="124" spans="1:3" ht="15.75">
-      <c r="A124" s="15">
-        <v>1010023038</v>
+      <c r="A124" s="18">
+        <v>1010049216</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>126</v>
@@ -3538,7 +3544,7 @@
     </row>
     <row r="125" spans="1:3" ht="15.75">
       <c r="A125" s="15">
-        <v>1010084109</v>
+        <v>405558</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>127</v>
@@ -3549,7 +3555,7 @@
     </row>
     <row r="126" spans="1:3" ht="15.75">
       <c r="A126" s="15">
-        <v>1010021582</v>
+        <v>1010023038</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>128</v>
@@ -3560,7 +3566,7 @@
     </row>
     <row r="127" spans="1:3" ht="15.75">
       <c r="A127" s="15">
-        <v>1010021544</v>
+        <v>1010084109</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>129</v>
@@ -3571,7 +3577,7 @@
     </row>
     <row r="128" spans="1:3" ht="15.75">
       <c r="A128" s="15">
-        <v>1010021564</v>
+        <v>1010021582</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>130</v>
@@ -3582,7 +3588,7 @@
     </row>
     <row r="129" spans="1:3" ht="15.75">
       <c r="A129" s="15">
-        <v>1010023019</v>
+        <v>1010021544</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>131</v>
@@ -3593,7 +3599,7 @@
     </row>
     <row r="130" spans="1:3" ht="15.75">
       <c r="A130" s="15">
-        <v>1010048541</v>
+        <v>1010021564</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>132</v>
@@ -3604,7 +3610,7 @@
     </row>
     <row r="131" spans="1:3" ht="15.75">
       <c r="A131" s="15">
-        <v>1010059334</v>
+        <v>1010023019</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>133</v>
@@ -3615,7 +3621,7 @@
     </row>
     <row r="132" spans="1:3" ht="15.75">
       <c r="A132" s="15">
-        <v>1010000277</v>
+        <v>1010048541</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>134</v>
@@ -3625,43 +3631,43 @@
       </c>
     </row>
     <row r="133" spans="1:3" ht="15.75">
-      <c r="A133" s="19">
+      <c r="A133" s="15">
+        <v>1010059334</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="15.75">
+      <c r="A134" s="15">
+        <v>1010000277</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="15.75">
+      <c r="A135" s="19">
         <v>1010085344</v>
       </c>
-      <c r="B133" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="15.75">
-      <c r="A134" s="19">
+      <c r="B135" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="15.75">
+      <c r="A136" s="19">
         <v>1010085383</v>
       </c>
-      <c r="B134" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="15.75">
-      <c r="A135" s="15">
-        <v>1010001389</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="15.75">
-      <c r="A136" s="15">
-        <v>1010017703</v>
-      </c>
-      <c r="B136" s="5" t="s">
+      <c r="B136" s="8" t="s">
         <v>138</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -3670,7 +3676,7 @@
     </row>
     <row r="137" spans="1:3" ht="15.75">
       <c r="A137" s="15">
-        <v>1010052036</v>
+        <v>1010001389</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>139</v>
@@ -3681,7 +3687,7 @@
     </row>
     <row r="138" spans="1:3" ht="15.75">
       <c r="A138" s="15">
-        <v>1040097133</v>
+        <v>1010017703</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>140</v>
@@ -3692,9 +3698,9 @@
     </row>
     <row r="139" spans="1:3" ht="15.75">
       <c r="A139" s="15">
-        <v>1040019325</v>
-      </c>
-      <c r="B139" s="9" t="s">
+        <v>1010052036</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>141</v>
       </c>
       <c r="C139" s="4" t="s">
@@ -3703,9 +3709,9 @@
     </row>
     <row r="140" spans="1:3" ht="15.75">
       <c r="A140" s="15">
-        <v>64262</v>
-      </c>
-      <c r="B140" s="9" t="s">
+        <v>1040097133</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>142</v>
       </c>
       <c r="C140" s="4" t="s">
@@ -3713,8 +3719,8 @@
       </c>
     </row>
     <row r="141" spans="1:3" ht="15.75">
-      <c r="A141" s="14">
-        <v>1010047089</v>
+      <c r="A141" s="15">
+        <v>1040019325</v>
       </c>
       <c r="B141" s="9" t="s">
         <v>143</v>
@@ -3724,8 +3730,8 @@
       </c>
     </row>
     <row r="142" spans="1:3" ht="15.75">
-      <c r="A142" s="14">
-        <v>1040050168</v>
+      <c r="A142" s="15">
+        <v>64262</v>
       </c>
       <c r="B142" s="9" t="s">
         <v>144</v>
@@ -3736,7 +3742,7 @@
     </row>
     <row r="143" spans="1:3" ht="15.75">
       <c r="A143" s="14">
-        <v>1040077370</v>
+        <v>1010047089</v>
       </c>
       <c r="B143" s="9" t="s">
         <v>145</v>
@@ -3747,7 +3753,7 @@
     </row>
     <row r="144" spans="1:3" ht="15.75">
       <c r="A144" s="14">
-        <v>1040099247</v>
+        <v>1040050168</v>
       </c>
       <c r="B144" s="9" t="s">
         <v>146</v>
@@ -3757,10 +3763,10 @@
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75">
-      <c r="A145" s="15">
-        <v>1040100560</v>
-      </c>
-      <c r="B145" s="5" t="s">
+      <c r="A145" s="14">
+        <v>1040077370</v>
+      </c>
+      <c r="B145" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C145" s="4" t="s">
@@ -3768,10 +3774,10 @@
       </c>
     </row>
     <row r="146" spans="1:3" ht="15.75">
-      <c r="A146" s="15">
-        <v>1040077399</v>
-      </c>
-      <c r="B146" s="5" t="s">
+      <c r="A146" s="14">
+        <v>1040099247</v>
+      </c>
+      <c r="B146" s="9" t="s">
         <v>148</v>
       </c>
       <c r="C146" s="4" t="s">
@@ -3780,7 +3786,7 @@
     </row>
     <row r="147" spans="1:3" ht="15.75">
       <c r="A147" s="15">
-        <v>1040077374</v>
+        <v>1040100560</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>149</v>
@@ -3802,7 +3808,7 @@
     </row>
     <row r="149" spans="1:3" ht="15.75">
       <c r="A149" s="15">
-        <v>357623</v>
+        <v>1040077374</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>151</v>
@@ -3813,7 +3819,7 @@
     </row>
     <row r="150" spans="1:3" ht="15.75">
       <c r="A150" s="15">
-        <v>1010020504</v>
+        <v>1040077399</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>152</v>
@@ -3824,7 +3830,7 @@
     </row>
     <row r="151" spans="1:3" ht="15.75">
       <c r="A151" s="15">
-        <v>409250</v>
+        <v>357623</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>153</v>
@@ -3835,7 +3841,7 @@
     </row>
     <row r="152" spans="1:3" ht="15.75">
       <c r="A152" s="15">
-        <v>1010020541</v>
+        <v>1010020504</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>154</v>
@@ -3846,7 +3852,7 @@
     </row>
     <row r="153" spans="1:3" ht="15.75">
       <c r="A153" s="15">
-        <v>1010020879</v>
+        <v>409250</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>155</v>
@@ -3857,7 +3863,7 @@
     </row>
     <row r="154" spans="1:3" ht="15.75">
       <c r="A154" s="15">
-        <v>1040077380</v>
+        <v>1010020541</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>156</v>
@@ -3868,7 +3874,7 @@
     </row>
     <row r="155" spans="1:3" ht="15.75">
       <c r="A155" s="15">
-        <v>1010021520</v>
+        <v>1010020879</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>157</v>
@@ -3879,7 +3885,7 @@
     </row>
     <row r="156" spans="1:3" ht="15.75">
       <c r="A156" s="15">
-        <v>1040098861</v>
+        <v>1040077380</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>158</v>
@@ -3890,7 +3896,7 @@
     </row>
     <row r="157" spans="1:3" ht="15.75">
       <c r="A157" s="15">
-        <v>1010077261</v>
+        <v>1010021520</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>159</v>
@@ -3901,7 +3907,7 @@
     </row>
     <row r="158" spans="1:3" ht="15.75">
       <c r="A158" s="15">
-        <v>1010027664</v>
+        <v>1040098861</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>160</v>
@@ -3912,7 +3918,7 @@
     </row>
     <row r="159" spans="1:3" ht="15.75">
       <c r="A159" s="15">
-        <v>1010083731</v>
+        <v>1010077261</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>161</v>
@@ -3923,7 +3929,7 @@
     </row>
     <row r="160" spans="1:3" ht="15.75">
       <c r="A160" s="15">
-        <v>1010083885</v>
+        <v>1010027664</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>162</v>
@@ -3934,7 +3940,7 @@
     </row>
     <row r="161" spans="1:3" ht="15.75">
       <c r="A161" s="15">
-        <v>1010014834</v>
+        <v>1010083731</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>163</v>
@@ -3945,7 +3951,7 @@
     </row>
     <row r="162" spans="1:3" ht="15.75">
       <c r="A162" s="15">
-        <v>1010083908</v>
+        <v>1010083885</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>164</v>
@@ -3956,7 +3962,7 @@
     </row>
     <row r="163" spans="1:3" ht="15.75">
       <c r="A163" s="15">
-        <v>1010024047</v>
+        <v>1010014834</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>165</v>
@@ -3967,7 +3973,7 @@
     </row>
     <row r="164" spans="1:3" ht="15.75">
       <c r="A164" s="15">
-        <v>1040077377</v>
+        <v>1010083908</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>166</v>
@@ -3978,7 +3984,7 @@
     </row>
     <row r="165" spans="1:3" ht="15.75">
       <c r="A165" s="15">
-        <v>1010061942</v>
+        <v>1010024047</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>167</v>
@@ -3989,7 +3995,7 @@
     </row>
     <row r="166" spans="1:3" ht="15.75">
       <c r="A166" s="15">
-        <v>1040097070</v>
+        <v>1040077377</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>168</v>
@@ -4000,7 +4006,7 @@
     </row>
     <row r="167" spans="1:3" ht="15.75">
       <c r="A167" s="15">
-        <v>1040097068</v>
+        <v>1010061942</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>169</v>
@@ -4011,7 +4017,7 @@
     </row>
     <row r="168" spans="1:3" ht="15.75">
       <c r="A168" s="15">
-        <v>22004</v>
+        <v>1040097070</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>170</v>
@@ -4022,7 +4028,7 @@
     </row>
     <row r="169" spans="1:3" ht="15.75">
       <c r="A169" s="15">
-        <v>1010058554</v>
+        <v>1040097068</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>171</v>
@@ -4033,7 +4039,7 @@
     </row>
     <row r="170" spans="1:3" ht="15.75">
       <c r="A170" s="15">
-        <v>1010027308</v>
+        <v>22004</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>172</v>
@@ -4043,10 +4049,10 @@
       </c>
     </row>
     <row r="171" spans="1:3" ht="15.75">
-      <c r="A171" s="19">
-        <v>1040077383</v>
-      </c>
-      <c r="B171" s="8" t="s">
+      <c r="A171" s="15">
+        <v>1010058554</v>
+      </c>
+      <c r="B171" s="5" t="s">
         <v>173</v>
       </c>
       <c r="C171" s="4" t="s">
@@ -4054,10 +4060,10 @@
       </c>
     </row>
     <row r="172" spans="1:3" ht="15.75">
-      <c r="A172" s="19">
-        <v>1010025482</v>
-      </c>
-      <c r="B172" s="8" t="s">
+      <c r="A172" s="15">
+        <v>1010027308</v>
+      </c>
+      <c r="B172" s="5" t="s">
         <v>174</v>
       </c>
       <c r="C172" s="4" t="s">
@@ -4066,7 +4072,7 @@
     </row>
     <row r="173" spans="1:3" ht="15.75">
       <c r="A173" s="19">
-        <v>1010025509</v>
+        <v>1040077383</v>
       </c>
       <c r="B173" s="8" t="s">
         <v>175</v>
@@ -4076,10 +4082,10 @@
       </c>
     </row>
     <row r="174" spans="1:3" ht="15.75">
-      <c r="A174" s="15">
-        <v>1010027789</v>
-      </c>
-      <c r="B174" s="5" t="s">
+      <c r="A174" s="19">
+        <v>1010025482</v>
+      </c>
+      <c r="B174" s="8" t="s">
         <v>176</v>
       </c>
       <c r="C174" s="4" t="s">
@@ -4087,10 +4093,10 @@
       </c>
     </row>
     <row r="175" spans="1:3" ht="15.75">
-      <c r="A175" s="15">
-        <v>1010027790</v>
-      </c>
-      <c r="B175" s="5" t="s">
+      <c r="A175" s="19">
+        <v>1010025509</v>
+      </c>
+      <c r="B175" s="8" t="s">
         <v>177</v>
       </c>
       <c r="C175" s="4" t="s">
@@ -4099,7 +4105,7 @@
     </row>
     <row r="176" spans="1:3" ht="15.75">
       <c r="A176" s="15">
-        <v>1010018301</v>
+        <v>1010027789</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>178</v>
@@ -4110,7 +4116,7 @@
     </row>
     <row r="177" spans="1:3" ht="15.75">
       <c r="A177" s="15">
-        <v>1010031616</v>
+        <v>1010027790</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>179</v>
@@ -4121,7 +4127,7 @@
     </row>
     <row r="178" spans="1:3" ht="15.75">
       <c r="A178" s="15">
-        <v>1010053728</v>
+        <v>1010018301</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>180</v>
@@ -4132,7 +4138,7 @@
     </row>
     <row r="179" spans="1:3" ht="15.75">
       <c r="A179" s="15">
-        <v>1010020758</v>
+        <v>1010031616</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>181</v>
@@ -4143,7 +4149,7 @@
     </row>
     <row r="180" spans="1:3" ht="15.75">
       <c r="A180" s="15">
-        <v>1010020781</v>
+        <v>1010053728</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>182</v>
@@ -4153,10 +4159,10 @@
       </c>
     </row>
     <row r="181" spans="1:3" ht="15.75">
-      <c r="A181" s="14">
-        <v>1010058426</v>
-      </c>
-      <c r="B181" s="9" t="s">
+      <c r="A181" s="15">
+        <v>1010020758</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>183</v>
       </c>
       <c r="C181" s="4" t="s">
@@ -4164,10 +4170,10 @@
       </c>
     </row>
     <row r="182" spans="1:3" ht="15.75">
-      <c r="A182" s="14">
-        <v>1010059332</v>
-      </c>
-      <c r="B182" s="9" t="s">
+      <c r="A182" s="15">
+        <v>1010020781</v>
+      </c>
+      <c r="B182" s="5" t="s">
         <v>184</v>
       </c>
       <c r="C182" s="4" t="s">
@@ -4176,7 +4182,7 @@
     </row>
     <row r="183" spans="1:3" ht="15.75">
       <c r="A183" s="14">
-        <v>1040077389</v>
+        <v>1010058426</v>
       </c>
       <c r="B183" s="9" t="s">
         <v>185</v>
@@ -4186,41 +4192,41 @@
       </c>
     </row>
     <row r="184" spans="1:3" ht="15.75">
-      <c r="A184" s="15">
+      <c r="A184" s="14">
+        <v>1010059332</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="15.75">
+      <c r="A185" s="14">
+        <v>1040077389</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="15.75">
+      <c r="A186" s="15">
         <v>1010021364</v>
       </c>
-      <c r="B184" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" ht="15.75">
-      <c r="A185" s="20">
+      <c r="B186" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="15.75">
+      <c r="A187" s="20">
         <v>1010021541</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="15.75">
-      <c r="A186" s="14">
-        <v>1010021955</v>
-      </c>
-      <c r="B186" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="15.75">
-      <c r="A187" s="15">
-        <v>1040077388</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>189</v>
@@ -4230,10 +4236,10 @@
       </c>
     </row>
     <row r="188" spans="1:3" ht="15.75">
-      <c r="A188" s="15">
-        <v>1010058100</v>
-      </c>
-      <c r="B188" s="5" t="s">
+      <c r="A188" s="14">
+        <v>1010021955</v>
+      </c>
+      <c r="B188" s="9" t="s">
         <v>190</v>
       </c>
       <c r="C188" s="4" t="s">
@@ -4242,7 +4248,7 @@
     </row>
     <row r="189" spans="1:3" ht="15.75">
       <c r="A189" s="15">
-        <v>1010020524</v>
+        <v>1040077388</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>191</v>
@@ -4253,7 +4259,7 @@
     </row>
     <row r="190" spans="1:3" ht="15.75">
       <c r="A190" s="15">
-        <v>1010021958</v>
+        <v>1010058100</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>192</v>
@@ -4264,7 +4270,7 @@
     </row>
     <row r="191" spans="1:3" ht="15.75">
       <c r="A191" s="15">
-        <v>1010019756</v>
+        <v>1010020524</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>193</v>
@@ -4275,7 +4281,7 @@
     </row>
     <row r="192" spans="1:3" ht="15.75">
       <c r="A192" s="15">
-        <v>1010019752</v>
+        <v>1010021958</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>194</v>
@@ -4286,7 +4292,7 @@
     </row>
     <row r="193" spans="1:3" ht="15.75">
       <c r="A193" s="15">
-        <v>409639</v>
+        <v>1010019756</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>195</v>
@@ -4297,7 +4303,7 @@
     </row>
     <row r="194" spans="1:3" ht="15.75">
       <c r="A194" s="15">
-        <v>1010047089</v>
+        <v>1010019752</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>196</v>
@@ -4308,7 +4314,7 @@
     </row>
     <row r="195" spans="1:3" ht="15.75">
       <c r="A195" s="15">
-        <v>1040084107</v>
+        <v>409639</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>197</v>
@@ -4319,7 +4325,7 @@
     </row>
     <row r="196" spans="1:3" ht="15.75">
       <c r="A196" s="15">
-        <v>1010085203</v>
+        <v>1010047089</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>198</v>
@@ -4330,7 +4336,7 @@
     </row>
     <row r="197" spans="1:3" ht="15.75">
       <c r="A197" s="15">
-        <v>424298</v>
+        <v>1040084107</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>199</v>
@@ -4341,7 +4347,7 @@
     </row>
     <row r="198" spans="1:3" ht="15.75">
       <c r="A198" s="15">
-        <v>421847</v>
+        <v>1010085203</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>200</v>
@@ -4352,7 +4358,7 @@
     </row>
     <row r="199" spans="1:3" ht="15.75">
       <c r="A199" s="15">
-        <v>431573</v>
+        <v>424298</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>201</v>
@@ -4363,7 +4369,7 @@
     </row>
     <row r="200" spans="1:3" ht="15.75">
       <c r="A200" s="15">
-        <v>1010021581</v>
+        <v>421847</v>
       </c>
       <c r="B200" s="5" t="s">
         <v>202</v>
@@ -4373,10 +4379,10 @@
       </c>
     </row>
     <row r="201" spans="1:3" ht="15.75">
-      <c r="A201" s="21">
-        <v>412413</v>
-      </c>
-      <c r="B201" s="7" t="s">
+      <c r="A201" s="15">
+        <v>431573</v>
+      </c>
+      <c r="B201" s="5" t="s">
         <v>203</v>
       </c>
       <c r="C201" s="4" t="s">
@@ -4384,8 +4390,8 @@
       </c>
     </row>
     <row r="202" spans="1:3" ht="15.75">
-      <c r="A202" s="22">
-        <v>1010022606</v>
+      <c r="A202" s="15">
+        <v>1010021581</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>204</v>
@@ -4395,8 +4401,8 @@
       </c>
     </row>
     <row r="203" spans="1:3" ht="15.75">
-      <c r="A203" s="23">
-        <v>1010003527</v>
+      <c r="A203" s="21">
+        <v>412413</v>
       </c>
       <c r="B203" s="7" t="s">
         <v>205</v>
@@ -4406,10 +4412,10 @@
       </c>
     </row>
     <row r="204" spans="1:3" ht="15.75">
-      <c r="A204" s="23">
-        <v>1010055707</v>
-      </c>
-      <c r="B204" s="7" t="s">
+      <c r="A204" s="22">
+        <v>1010022606</v>
+      </c>
+      <c r="B204" s="5" t="s">
         <v>206</v>
       </c>
       <c r="C204" s="4" t="s">
@@ -4417,8 +4423,8 @@
       </c>
     </row>
     <row r="205" spans="1:3" ht="15.75">
-      <c r="A205" s="18">
-        <v>422027</v>
+      <c r="A205" s="23">
+        <v>1010003527</v>
       </c>
       <c r="B205" s="7" t="s">
         <v>207</v>
@@ -4428,30 +4434,30 @@
       </c>
     </row>
     <row r="206" spans="1:3" ht="15.75">
-      <c r="A206" s="14">
+      <c r="A206" s="23">
+        <v>1010055707</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="15.75">
+      <c r="A207" s="18">
+        <v>422027</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="15.75">
+      <c r="A208" s="14">
         <v>1010011313</v>
-      </c>
-      <c r="B206" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="15.75">
-      <c r="A207" s="15">
-        <v>27051</v>
-      </c>
-      <c r="B207" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" ht="15.75">
-      <c r="A208" s="15">
-        <v>1010011304</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>210</v>
@@ -4462,7 +4468,7 @@
     </row>
     <row r="209" spans="1:3" ht="15.75">
       <c r="A209" s="15">
-        <v>35659</v>
+        <v>27051</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>211</v>
@@ -4473,7 +4479,7 @@
     </row>
     <row r="210" spans="1:3" ht="15.75">
       <c r="A210" s="15">
-        <v>1040077390</v>
+        <v>1010011304</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>212</v>
@@ -4484,7 +4490,7 @@
     </row>
     <row r="211" spans="1:3" ht="15.75">
       <c r="A211" s="15">
-        <v>1010021542</v>
+        <v>35659</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>213</v>
@@ -4495,7 +4501,7 @@
     </row>
     <row r="212" spans="1:3" ht="15.75">
       <c r="A212" s="15">
-        <v>1010021733</v>
+        <v>1040077390</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>214</v>
@@ -4506,7 +4512,7 @@
     </row>
     <row r="213" spans="1:3" ht="15.75">
       <c r="A213" s="15">
-        <v>1010011379</v>
+        <v>1010021542</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>215</v>
@@ -4517,7 +4523,7 @@
     </row>
     <row r="214" spans="1:3" ht="15.75">
       <c r="A214" s="15">
-        <v>1010003279</v>
+        <v>1010021733</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>216</v>
@@ -4528,7 +4534,7 @@
     </row>
     <row r="215" spans="1:3" ht="15.75">
       <c r="A215" s="15">
-        <v>1010011380</v>
+        <v>1010011379</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>217</v>
@@ -4539,7 +4545,7 @@
     </row>
     <row r="216" spans="1:3" ht="15.75">
       <c r="A216" s="15">
-        <v>351197</v>
+        <v>1010003279</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>218</v>
@@ -4550,7 +4556,7 @@
     </row>
     <row r="217" spans="1:3" ht="15.75">
       <c r="A217" s="15">
-        <v>1010011286</v>
+        <v>1010011380</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>219</v>
@@ -4561,7 +4567,7 @@
     </row>
     <row r="218" spans="1:3" ht="15.75">
       <c r="A218" s="15">
-        <v>2479</v>
+        <v>351197</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>220</v>
@@ -4572,7 +4578,7 @@
     </row>
     <row r="219" spans="1:3" ht="15.75">
       <c r="A219" s="15">
-        <v>1010011382</v>
+        <v>1010011286</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>221</v>
@@ -4582,10 +4588,10 @@
       </c>
     </row>
     <row r="220" spans="1:3" ht="15.75">
-      <c r="A220" s="16">
-        <v>1010055703</v>
-      </c>
-      <c r="B220" s="8" t="s">
+      <c r="A220" s="15">
+        <v>2479</v>
+      </c>
+      <c r="B220" s="5" t="s">
         <v>222</v>
       </c>
       <c r="C220" s="4" t="s">
@@ -4593,8 +4599,8 @@
       </c>
     </row>
     <row r="221" spans="1:3" ht="15.75">
-      <c r="A221" s="16">
-        <v>4165</v>
+      <c r="A221" s="15">
+        <v>1010011382</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>223</v>
@@ -4604,10 +4610,10 @@
       </c>
     </row>
     <row r="222" spans="1:3" ht="15.75">
-      <c r="A222" s="15">
-        <v>301626</v>
-      </c>
-      <c r="B222" s="9" t="s">
+      <c r="A222" s="16">
+        <v>1010055703</v>
+      </c>
+      <c r="B222" s="8" t="s">
         <v>224</v>
       </c>
       <c r="C222" s="4" t="s">
@@ -4615,8 +4621,8 @@
       </c>
     </row>
     <row r="223" spans="1:3" ht="15.75">
-      <c r="A223" s="15">
-        <v>429495</v>
+      <c r="A223" s="16">
+        <v>4165</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>225</v>
@@ -4627,9 +4633,9 @@
     </row>
     <row r="224" spans="1:3" ht="15.75">
       <c r="A224" s="15">
-        <v>162998</v>
-      </c>
-      <c r="B224" s="5" t="s">
+        <v>301626</v>
+      </c>
+      <c r="B224" s="9" t="s">
         <v>226</v>
       </c>
       <c r="C224" s="4" t="s">
@@ -4638,7 +4644,7 @@
     </row>
     <row r="225" spans="1:3" ht="15.75">
       <c r="A225" s="15">
-        <v>432657</v>
+        <v>429495</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>227</v>
@@ -4649,7 +4655,7 @@
     </row>
     <row r="226" spans="1:3" ht="15.75">
       <c r="A226" s="15">
-        <v>1010021929</v>
+        <v>162998</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>228</v>
@@ -4660,7 +4666,7 @@
     </row>
     <row r="227" spans="1:3" ht="15.75">
       <c r="A227" s="15">
-        <v>428065</v>
+        <v>432657</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>229</v>
@@ -4671,7 +4677,7 @@
     </row>
     <row r="228" spans="1:3" ht="15.75">
       <c r="A228" s="15">
-        <v>1010003404</v>
+        <v>1010021929</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>230</v>
@@ -4682,9 +4688,9 @@
     </row>
     <row r="229" spans="1:3" ht="15.75">
       <c r="A229" s="15">
-        <v>1010003322</v>
-      </c>
-      <c r="B229" s="7" t="s">
+        <v>428065</v>
+      </c>
+      <c r="B229" s="5" t="s">
         <v>231</v>
       </c>
       <c r="C229" s="4" t="s">
@@ -4693,9 +4699,9 @@
     </row>
     <row r="230" spans="1:3" ht="15.75">
       <c r="A230" s="15">
-        <v>17738</v>
-      </c>
-      <c r="B230" s="7" t="s">
+        <v>1010003404</v>
+      </c>
+      <c r="B230" s="5" t="s">
         <v>232</v>
       </c>
       <c r="C230" s="4" t="s">
@@ -4704,7 +4710,7 @@
     </row>
     <row r="231" spans="1:3" ht="15.75">
       <c r="A231" s="15">
-        <v>1010085360</v>
+        <v>1010003322</v>
       </c>
       <c r="B231" s="7" t="s">
         <v>233</v>
@@ -4715,9 +4721,9 @@
     </row>
     <row r="232" spans="1:3" ht="15.75">
       <c r="A232" s="15">
-        <v>1040077391</v>
-      </c>
-      <c r="B232" s="5" t="s">
+        <v>17738</v>
+      </c>
+      <c r="B232" s="7" t="s">
         <v>234</v>
       </c>
       <c r="C232" s="4" t="s">
@@ -4726,9 +4732,9 @@
     </row>
     <row r="233" spans="1:3" ht="15.75">
       <c r="A233" s="15">
-        <v>1010058624</v>
-      </c>
-      <c r="B233" s="5" t="s">
+        <v>1010085360</v>
+      </c>
+      <c r="B233" s="7" t="s">
         <v>235</v>
       </c>
       <c r="C233" s="4" t="s">
@@ -4737,7 +4743,7 @@
     </row>
     <row r="234" spans="1:3" ht="15.75">
       <c r="A234" s="15">
-        <v>1010024661</v>
+        <v>1040077391</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>236</v>
@@ -4748,7 +4754,7 @@
     </row>
     <row r="235" spans="1:3" ht="15.75">
       <c r="A235" s="15">
-        <v>1040019315</v>
+        <v>1010058624</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>237</v>
@@ -4759,7 +4765,7 @@
     </row>
     <row r="236" spans="1:3" ht="15.75">
       <c r="A236" s="15">
-        <v>1010021089</v>
+        <v>1010024661</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>238</v>
@@ -4770,7 +4776,7 @@
     </row>
     <row r="237" spans="1:3" ht="15.75">
       <c r="A237" s="15">
-        <v>1040017264</v>
+        <v>1040019315</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>239</v>
@@ -4781,7 +4787,7 @@
     </row>
     <row r="238" spans="1:3" ht="15.75">
       <c r="A238" s="15">
-        <v>1010051765</v>
+        <v>1010021089</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>240</v>
@@ -4792,7 +4798,7 @@
     </row>
     <row r="239" spans="1:3" ht="15.75">
       <c r="A239" s="15">
-        <v>1010035272</v>
+        <v>1040017264</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>241</v>
@@ -4803,7 +4809,7 @@
     </row>
     <row r="240" spans="1:3" ht="15.75">
       <c r="A240" s="15">
-        <v>1040077392</v>
+        <v>1010051765</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>242</v>
@@ -4814,7 +4820,7 @@
     </row>
     <row r="241" spans="1:3" ht="15.75">
       <c r="A241" s="15">
-        <v>1040077393</v>
+        <v>1010035272</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>243</v>
@@ -4825,7 +4831,7 @@
     </row>
     <row r="242" spans="1:3" ht="15.75">
       <c r="A242" s="15">
-        <v>1040077395</v>
+        <v>1040077392</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>244</v>
@@ -4836,7 +4842,7 @@
     </row>
     <row r="243" spans="1:3" ht="15.75">
       <c r="A243" s="15">
-        <v>1040077401</v>
+        <v>1040077393</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>245</v>
@@ -4847,7 +4853,7 @@
     </row>
     <row r="244" spans="1:3" ht="15.75">
       <c r="A244" s="15">
-        <v>27572</v>
+        <v>1040077395</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>246</v>
@@ -4858,7 +4864,7 @@
     </row>
     <row r="245" spans="1:3" ht="15.75">
       <c r="A245" s="15">
-        <v>18745</v>
+        <v>1040077401</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>247</v>
@@ -4869,7 +4875,7 @@
     </row>
     <row r="246" spans="1:3" ht="15.75">
       <c r="A246" s="15">
-        <v>1040077396</v>
+        <v>27572</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>248</v>
@@ -4880,7 +4886,7 @@
     </row>
     <row r="247" spans="1:3" ht="15.75">
       <c r="A247" s="15">
-        <v>1010036546</v>
+        <v>18745</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>249</v>
@@ -4891,7 +4897,7 @@
     </row>
     <row r="248" spans="1:3" ht="15.75">
       <c r="A248" s="15">
-        <v>1010014049</v>
+        <v>1040077396</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>250</v>
@@ -4902,7 +4908,7 @@
     </row>
     <row r="249" spans="1:3" ht="15.75">
       <c r="A249" s="15">
-        <v>1010025148</v>
+        <v>1010036546</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>251</v>
@@ -4913,7 +4919,7 @@
     </row>
     <row r="250" spans="1:3" ht="15.75">
       <c r="A250" s="15">
-        <v>1040077394</v>
+        <v>1010014049</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>252</v>
@@ -4924,7 +4930,7 @@
     </row>
     <row r="251" spans="1:3" ht="15.75">
       <c r="A251" s="15">
-        <v>1040077400</v>
+        <v>1010025148</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>253</v>
@@ -4935,7 +4941,7 @@
     </row>
     <row r="252" spans="1:3" ht="15.75">
       <c r="A252" s="15">
-        <v>1040079329</v>
+        <v>1040077394</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>254</v>
@@ -4946,7 +4952,7 @@
     </row>
     <row r="253" spans="1:3" ht="15.75">
       <c r="A253" s="15">
-        <v>1040040957</v>
+        <v>1040077400</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>255</v>
@@ -4957,7 +4963,7 @@
     </row>
     <row r="254" spans="1:3" ht="15.75">
       <c r="A254" s="15">
-        <v>1040077398</v>
+        <v>1040079329</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>256</v>
@@ -4968,7 +4974,7 @@
     </row>
     <row r="255" spans="1:3" ht="15.75">
       <c r="A255" s="15">
-        <v>1010053128</v>
+        <v>1040040957</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>257</v>
@@ -4979,7 +4985,7 @@
     </row>
     <row r="256" spans="1:3" ht="15.75">
       <c r="A256" s="15">
-        <v>1010010599</v>
+        <v>1040077398</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>258</v>
@@ -4990,7 +4996,7 @@
     </row>
     <row r="257" spans="1:3" ht="15.75">
       <c r="A257" s="15">
-        <v>1010056064</v>
+        <v>1010053128</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>259</v>
@@ -5001,7 +5007,7 @@
     </row>
     <row r="258" spans="1:3" ht="15.75">
       <c r="A258" s="15">
-        <v>5389</v>
+        <v>1010010599</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>260</v>
@@ -5012,7 +5018,7 @@
     </row>
     <row r="259" spans="1:3" ht="15.75">
       <c r="A259" s="15">
-        <v>1010055969</v>
+        <v>1010056064</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>261</v>
@@ -5023,7 +5029,7 @@
     </row>
     <row r="260" spans="1:3" ht="15.75">
       <c r="A260" s="15">
-        <v>1010055970</v>
+        <v>5389</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>262</v>
@@ -5034,7 +5040,7 @@
     </row>
     <row r="261" spans="1:3" ht="15.75">
       <c r="A261" s="15">
-        <v>181395</v>
+        <v>1010055969</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>263</v>
@@ -5044,8 +5050,8 @@
       </c>
     </row>
     <row r="262" spans="1:3" ht="15.75">
-      <c r="A262" s="17">
-        <v>1010055962</v>
+      <c r="A262" s="15">
+        <v>1010055970</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>264</v>
@@ -5056,7 +5062,7 @@
     </row>
     <row r="263" spans="1:3" ht="15.75">
       <c r="A263" s="15">
-        <v>1010003578</v>
+        <v>181395</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>265</v>
@@ -5066,8 +5072,8 @@
       </c>
     </row>
     <row r="264" spans="1:3" ht="15.75">
-      <c r="A264" s="15">
-        <v>332891</v>
+      <c r="A264" s="17">
+        <v>1010055962</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>266</v>
@@ -5078,7 +5084,7 @@
     </row>
     <row r="265" spans="1:3" ht="15.75">
       <c r="A265" s="15">
-        <v>17727</v>
+        <v>1010003578</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>267</v>
@@ -5089,7 +5095,7 @@
     </row>
     <row r="266" spans="1:3" ht="15.75">
       <c r="A266" s="15">
-        <v>17918</v>
+        <v>332891</v>
       </c>
       <c r="B266" s="5" t="s">
         <v>268</v>
@@ -5100,7 +5106,7 @@
     </row>
     <row r="267" spans="1:3" ht="15.75">
       <c r="A267" s="15">
-        <v>1010020554</v>
+        <v>17727</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>269</v>
@@ -5111,7 +5117,7 @@
     </row>
     <row r="268" spans="1:3" ht="15.75">
       <c r="A268" s="15">
-        <v>1040085949</v>
+        <v>17918</v>
       </c>
       <c r="B268" s="5" t="s">
         <v>270</v>
@@ -5122,7 +5128,7 @@
     </row>
     <row r="269" spans="1:3" ht="15.75">
       <c r="A269" s="15">
-        <v>1010062938</v>
+        <v>1010020554</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>271</v>
@@ -5133,7 +5139,7 @@
     </row>
     <row r="270" spans="1:3" ht="15.75">
       <c r="A270" s="15">
-        <v>1010062086</v>
+        <v>1040085949</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>272</v>
@@ -5144,7 +5150,7 @@
     </row>
     <row r="271" spans="1:3" ht="15.75">
       <c r="A271" s="15">
-        <v>1010062087</v>
+        <v>1010062938</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>273</v>
@@ -5155,7 +5161,7 @@
     </row>
     <row r="272" spans="1:3" ht="15.75">
       <c r="A272" s="15">
-        <v>1040077373</v>
+        <v>1010062086</v>
       </c>
       <c r="B272" s="5" t="s">
         <v>274</v>
@@ -5165,10 +5171,10 @@
       </c>
     </row>
     <row r="273" spans="1:3" ht="15.75">
-      <c r="A273" s="24">
-        <v>1040077372</v>
-      </c>
-      <c r="B273" s="6" t="s">
+      <c r="A273" s="15">
+        <v>1010062087</v>
+      </c>
+      <c r="B273" s="5" t="s">
         <v>275</v>
       </c>
       <c r="C273" s="4" t="s">
@@ -5176,10 +5182,10 @@
       </c>
     </row>
     <row r="274" spans="1:3" ht="15.75">
-      <c r="A274" s="24">
-        <v>1040097154</v>
-      </c>
-      <c r="B274" s="6" t="s">
+      <c r="A274" s="15">
+        <v>1040077373</v>
+      </c>
+      <c r="B274" s="5" t="s">
         <v>276</v>
       </c>
       <c r="C274" s="4" t="s">
@@ -5188,7 +5194,7 @@
     </row>
     <row r="275" spans="1:3" ht="15.75">
       <c r="A275" s="24">
-        <v>1010042579</v>
+        <v>1040077372</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>277</v>
@@ -5198,10 +5204,10 @@
       </c>
     </row>
     <row r="276" spans="1:3" ht="15.75">
-      <c r="A276" s="15">
-        <v>1010029427</v>
-      </c>
-      <c r="B276" s="5" t="s">
+      <c r="A276" s="24">
+        <v>1040097154</v>
+      </c>
+      <c r="B276" s="6" t="s">
         <v>278</v>
       </c>
       <c r="C276" s="4" t="s">
@@ -5209,10 +5215,10 @@
       </c>
     </row>
     <row r="277" spans="1:3" ht="15.75">
-      <c r="A277" s="15">
-        <v>133108</v>
-      </c>
-      <c r="B277" s="5" t="s">
+      <c r="A277" s="24">
+        <v>1010042579</v>
+      </c>
+      <c r="B277" s="6" t="s">
         <v>279</v>
       </c>
       <c r="C277" s="4" t="s">
@@ -5221,7 +5227,7 @@
     </row>
     <row r="278" spans="1:3" ht="15.75">
       <c r="A278" s="15">
-        <v>269427</v>
+        <v>1010029427</v>
       </c>
       <c r="B278" s="5" t="s">
         <v>280</v>
@@ -5232,7 +5238,7 @@
     </row>
     <row r="279" spans="1:3" ht="15.75">
       <c r="A279" s="15">
-        <v>298227</v>
+        <v>133108</v>
       </c>
       <c r="B279" s="5" t="s">
         <v>281</v>
@@ -5243,7 +5249,7 @@
     </row>
     <row r="280" spans="1:3" ht="15.75">
       <c r="A280" s="15">
-        <v>1010062285</v>
+        <v>269427</v>
       </c>
       <c r="B280" s="5" t="s">
         <v>282</v>
@@ -5254,7 +5260,7 @@
     </row>
     <row r="281" spans="1:3" ht="15.75">
       <c r="A281" s="15">
-        <v>1010058052</v>
+        <v>298227</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>283</v>
@@ -5265,7 +5271,7 @@
     </row>
     <row r="282" spans="1:3" ht="15.75">
       <c r="A282" s="15">
-        <v>1010050033</v>
+        <v>1010062285</v>
       </c>
       <c r="B282" s="5" t="s">
         <v>284</v>
@@ -5275,8 +5281,8 @@
       </c>
     </row>
     <row r="283" spans="1:3" ht="15.75">
-      <c r="A283" s="20">
-        <v>1040098869</v>
+      <c r="A283" s="15">
+        <v>1010058052</v>
       </c>
       <c r="B283" s="5" t="s">
         <v>285</v>
@@ -5286,8 +5292,8 @@
       </c>
     </row>
     <row r="284" spans="1:3" ht="15.75">
-      <c r="A284" s="20">
-        <v>1010056523</v>
+      <c r="A284" s="15">
+        <v>1010050033</v>
       </c>
       <c r="B284" s="5" t="s">
         <v>286</v>
@@ -5298,7 +5304,7 @@
     </row>
     <row r="285" spans="1:3" ht="15.75">
       <c r="A285" s="20">
-        <v>1010062045</v>
+        <v>1040098869</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>287</v>
@@ -5308,8 +5314,8 @@
       </c>
     </row>
     <row r="286" spans="1:3" ht="15.75">
-      <c r="A286" s="15">
-        <v>1040097575</v>
+      <c r="A286" s="20">
+        <v>1010056523</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>288</v>
@@ -5319,8 +5325,8 @@
       </c>
     </row>
     <row r="287" spans="1:3" ht="15.75">
-      <c r="A287" s="5">
-        <v>1040100107</v>
+      <c r="A287" s="20">
+        <v>1010062045</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>289</v>
@@ -5331,7 +5337,7 @@
     </row>
     <row r="288" spans="1:3" ht="15.75">
       <c r="A288" s="15">
-        <v>1010040346</v>
+        <v>1040097575</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>290</v>
@@ -5341,8 +5347,8 @@
       </c>
     </row>
     <row r="289" spans="1:3" ht="15.75">
-      <c r="A289" s="15">
-        <v>1010021543</v>
+      <c r="A289" s="5">
+        <v>1040100107</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>291</v>
@@ -5353,7 +5359,7 @@
     </row>
     <row r="290" spans="1:3" ht="15.75">
       <c r="A290" s="15">
-        <v>1040077397</v>
+        <v>1010040346</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>292</v>
@@ -5364,7 +5370,7 @@
     </row>
     <row r="291" spans="1:3" ht="15.75">
       <c r="A291" s="15">
-        <v>1040094213</v>
+        <v>1010021543</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>293</v>
@@ -5375,7 +5381,7 @@
     </row>
     <row r="292" spans="1:3" ht="15.75">
       <c r="A292" s="15">
-        <v>1010085326</v>
+        <v>1040077397</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>294</v>
@@ -5386,7 +5392,7 @@
     </row>
     <row r="293" spans="1:3" ht="15.75">
       <c r="A293" s="15">
-        <v>1010042564</v>
+        <v>1040094213</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>295</v>
@@ -5397,7 +5403,7 @@
     </row>
     <row r="294" spans="1:3" ht="15.75">
       <c r="A294" s="15">
-        <v>1010042688</v>
+        <v>1010085326</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>296</v>
@@ -5408,7 +5414,7 @@
     </row>
     <row r="295" spans="1:3" ht="15.75">
       <c r="A295" s="15">
-        <v>1010040133</v>
+        <v>1010042564</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>297</v>
@@ -5419,7 +5425,7 @@
     </row>
     <row r="296" spans="1:3" ht="15.75">
       <c r="A296" s="15">
-        <v>1010039879</v>
+        <v>1010042688</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>298</v>
@@ -5430,7 +5436,7 @@
     </row>
     <row r="297" spans="1:3" ht="15.75">
       <c r="A297" s="15">
-        <v>62608</v>
+        <v>1010040133</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>299</v>
@@ -5441,7 +5447,7 @@
     </row>
     <row r="298" spans="1:3" ht="15.75">
       <c r="A298" s="15">
-        <v>1040098603</v>
+        <v>1010039879</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>300</v>
@@ -5452,7 +5458,7 @@
     </row>
     <row r="299" spans="1:3" ht="15.75">
       <c r="A299" s="15">
-        <v>1040017266</v>
+        <v>62608</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>301</v>
@@ -5463,7 +5469,7 @@
     </row>
     <row r="300" spans="1:3" ht="15.75">
       <c r="A300" s="15">
-        <v>1010063326</v>
+        <v>1040098603</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>302</v>
@@ -5474,7 +5480,7 @@
     </row>
     <row r="301" spans="1:3" ht="15.75">
       <c r="A301" s="15">
-        <v>1010050574</v>
+        <v>1040017266</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>303</v>
@@ -5484,8 +5490,8 @@
       </c>
     </row>
     <row r="302" spans="1:3" ht="15.75">
-      <c r="A302" s="20">
-        <v>1010086126</v>
+      <c r="A302" s="15">
+        <v>1010063326</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>304</v>
@@ -5496,7 +5502,7 @@
     </row>
     <row r="303" spans="1:3" ht="15.75">
       <c r="A303" s="15">
-        <v>1040019838</v>
+        <v>1010050574</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>305</v>
@@ -5506,8 +5512,8 @@
       </c>
     </row>
     <row r="304" spans="1:3" ht="15.75">
-      <c r="A304" s="15">
-        <v>1010042882</v>
+      <c r="A304" s="20">
+        <v>1010086126</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>306</v>
@@ -5518,7 +5524,7 @@
     </row>
     <row r="305" spans="1:3" ht="15.75">
       <c r="A305" s="15">
-        <v>1010042873</v>
+        <v>1040019838</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>307</v>
@@ -5529,7 +5535,7 @@
     </row>
     <row r="306" spans="1:3" ht="15.75">
       <c r="A306" s="15">
-        <v>1010026842</v>
+        <v>1010042882</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>308</v>
@@ -5540,7 +5546,7 @@
     </row>
     <row r="307" spans="1:3" ht="15.75">
       <c r="A307" s="15">
-        <v>1010026841</v>
+        <v>1010042873</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>309</v>
@@ -5551,7 +5557,7 @@
     </row>
     <row r="308" spans="1:3" ht="15.75">
       <c r="A308" s="15">
-        <v>1010059549</v>
+        <v>1010026842</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>310</v>
@@ -5562,7 +5568,7 @@
     </row>
     <row r="309" spans="1:3" ht="15.75">
       <c r="A309" s="15">
-        <v>1010020552</v>
+        <v>1010026841</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>311</v>
@@ -5573,7 +5579,7 @@
     </row>
     <row r="310" spans="1:3" ht="15.75">
       <c r="A310" s="15">
-        <v>1040078895</v>
+        <v>1010059549</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>312</v>
@@ -5584,7 +5590,7 @@
     </row>
     <row r="311" spans="1:3" ht="15.75">
       <c r="A311" s="15">
-        <v>1040024309</v>
+        <v>1010020552</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>313</v>
@@ -5595,7 +5601,7 @@
     </row>
     <row r="312" spans="1:3" ht="15.75">
       <c r="A312" s="15">
-        <v>1040024323</v>
+        <v>1040078895</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>314</v>
@@ -5606,7 +5612,7 @@
     </row>
     <row r="313" spans="1:3" ht="15.75">
       <c r="A313" s="15">
-        <v>1040024322</v>
+        <v>1040024309</v>
       </c>
       <c r="B313" s="5" t="s">
         <v>315</v>
@@ -5617,7 +5623,7 @@
     </row>
     <row r="314" spans="1:3" ht="15.75">
       <c r="A314" s="15">
-        <v>1010087245</v>
+        <v>1040024323</v>
       </c>
       <c r="B314" s="5" t="s">
         <v>316</v>
@@ -5628,7 +5634,7 @@
     </row>
     <row r="315" spans="1:3" ht="15.75">
       <c r="A315" s="15">
-        <v>1010059685</v>
+        <v>1040024322</v>
       </c>
       <c r="B315" s="5" t="s">
         <v>317</v>
@@ -5639,7 +5645,7 @@
     </row>
     <row r="316" spans="1:3" ht="15.75">
       <c r="A316" s="15">
-        <v>1010059687</v>
+        <v>1010087245</v>
       </c>
       <c r="B316" s="5" t="s">
         <v>318</v>
@@ -5650,7 +5656,7 @@
     </row>
     <row r="317" spans="1:3" ht="15.75">
       <c r="A317" s="15">
-        <v>1010077469</v>
+        <v>1010059685</v>
       </c>
       <c r="B317" s="5" t="s">
         <v>319</v>
@@ -5660,8 +5666,8 @@
       </c>
     </row>
     <row r="318" spans="1:3" ht="15.75">
-      <c r="A318" s="19">
-        <v>1010077470</v>
+      <c r="A318" s="15">
+        <v>1010059687</v>
       </c>
       <c r="B318" s="5" t="s">
         <v>320</v>
@@ -5672,9 +5678,9 @@
     </row>
     <row r="319" spans="1:3" ht="15.75">
       <c r="A319" s="15">
-        <v>1010084519</v>
-      </c>
-      <c r="B319" s="7" t="s">
+        <v>1010077469</v>
+      </c>
+      <c r="B319" s="5" t="s">
         <v>321</v>
       </c>
       <c r="C319" s="4" t="s">
@@ -5682,8 +5688,8 @@
       </c>
     </row>
     <row r="320" spans="1:3" ht="15.75">
-      <c r="A320" s="14">
-        <v>1010084108</v>
+      <c r="A320" s="19">
+        <v>1010077470</v>
       </c>
       <c r="B320" s="5" t="s">
         <v>322</v>
@@ -5693,10 +5699,10 @@
       </c>
     </row>
     <row r="321" spans="1:3" ht="15.75">
-      <c r="A321" s="14">
-        <v>1010042884</v>
-      </c>
-      <c r="B321" s="5" t="s">
+      <c r="A321" s="15">
+        <v>1010084519</v>
+      </c>
+      <c r="B321" s="7" t="s">
         <v>323</v>
       </c>
       <c r="C321" s="4" t="s">
@@ -5704,8 +5710,8 @@
       </c>
     </row>
     <row r="322" spans="1:3" ht="15.75">
-      <c r="A322" s="15">
-        <v>1040043537</v>
+      <c r="A322" s="14">
+        <v>1010084108</v>
       </c>
       <c r="B322" s="5" t="s">
         <v>324</v>
@@ -5715,8 +5721,8 @@
       </c>
     </row>
     <row r="323" spans="1:3" ht="15.75">
-      <c r="A323" s="15">
-        <v>1010046401</v>
+      <c r="A323" s="14">
+        <v>1010042884</v>
       </c>
       <c r="B323" s="5" t="s">
         <v>325</v>
@@ -5727,7 +5733,7 @@
     </row>
     <row r="324" spans="1:3" ht="15.75">
       <c r="A324" s="15">
-        <v>1010062007</v>
+        <v>1040043537</v>
       </c>
       <c r="B324" s="5" t="s">
         <v>326</v>
@@ -5738,7 +5744,7 @@
     </row>
     <row r="325" spans="1:3" ht="15.75">
       <c r="A325" s="15">
-        <v>1010051284</v>
+        <v>1010046401</v>
       </c>
       <c r="B325" s="5" t="s">
         <v>327</v>
@@ -5749,7 +5755,7 @@
     </row>
     <row r="326" spans="1:3" ht="15.75">
       <c r="A326" s="15">
-        <v>1010027788</v>
+        <v>1010062007</v>
       </c>
       <c r="B326" s="5" t="s">
         <v>328</v>
@@ -5760,7 +5766,7 @@
     </row>
     <row r="327" spans="1:3" ht="15.75">
       <c r="A327" s="15">
-        <v>1010027786</v>
+        <v>1010051284</v>
       </c>
       <c r="B327" s="5" t="s">
         <v>329</v>
@@ -5771,7 +5777,7 @@
     </row>
     <row r="328" spans="1:3" ht="15.75">
       <c r="A328" s="15">
-        <v>1010026889</v>
+        <v>1010027788</v>
       </c>
       <c r="B328" s="5" t="s">
         <v>330</v>
@@ -5781,8 +5787,8 @@
       </c>
     </row>
     <row r="329" spans="1:3" ht="15.75">
-      <c r="A329" s="24">
-        <v>1010042358</v>
+      <c r="A329" s="15">
+        <v>1010027786</v>
       </c>
       <c r="B329" s="5" t="s">
         <v>331</v>
@@ -5793,7 +5799,7 @@
     </row>
     <row r="330" spans="1:3" ht="15.75">
       <c r="A330" s="15">
-        <v>1040023848</v>
+        <v>1010026889</v>
       </c>
       <c r="B330" s="5" t="s">
         <v>332</v>
@@ -5803,8 +5809,8 @@
       </c>
     </row>
     <row r="331" spans="1:3" ht="15.75">
-      <c r="A331" s="15">
-        <v>1010042341</v>
+      <c r="A331" s="24">
+        <v>1010042358</v>
       </c>
       <c r="B331" s="5" t="s">
         <v>333</v>
@@ -5815,7 +5821,7 @@
     </row>
     <row r="332" spans="1:3" ht="15.75">
       <c r="A332" s="15">
-        <v>1040023858</v>
+        <v>1040023848</v>
       </c>
       <c r="B332" s="5" t="s">
         <v>334</v>
@@ -5826,7 +5832,7 @@
     </row>
     <row r="333" spans="1:3" ht="15.75">
       <c r="A333" s="15">
-        <v>1040098396</v>
+        <v>1010042341</v>
       </c>
       <c r="B333" s="5" t="s">
         <v>335</v>
@@ -5837,7 +5843,7 @@
     </row>
     <row r="334" spans="1:3" ht="15.75">
       <c r="A334" s="15">
-        <v>1010087281</v>
+        <v>1040023858</v>
       </c>
       <c r="B334" s="5" t="s">
         <v>336</v>
@@ -5848,7 +5854,7 @@
     </row>
     <row r="335" spans="1:3" ht="15.75">
       <c r="A335" s="15">
-        <v>1040041006</v>
+        <v>1040098396</v>
       </c>
       <c r="B335" s="5" t="s">
         <v>337</v>
@@ -5859,7 +5865,7 @@
     </row>
     <row r="336" spans="1:3" ht="15.75">
       <c r="A336" s="15">
-        <v>1040101931</v>
+        <v>1010087281</v>
       </c>
       <c r="B336" s="5" t="s">
         <v>338</v>
@@ -5870,7 +5876,7 @@
     </row>
     <row r="337" spans="1:3" ht="15.75">
       <c r="A337" s="15">
-        <v>1040023843</v>
+        <v>1040041006</v>
       </c>
       <c r="B337" s="5" t="s">
         <v>339</v>
@@ -5881,7 +5887,7 @@
     </row>
     <row r="338" spans="1:3" ht="15.75">
       <c r="A338" s="15">
-        <v>1040077411</v>
+        <v>1040101931</v>
       </c>
       <c r="B338" s="5" t="s">
         <v>340</v>
@@ -5892,7 +5898,7 @@
     </row>
     <row r="339" spans="1:3" ht="15.75">
       <c r="A339" s="15">
-        <v>1040077410</v>
+        <v>1040023843</v>
       </c>
       <c r="B339" s="5" t="s">
         <v>341</v>
@@ -5903,7 +5909,7 @@
     </row>
     <row r="340" spans="1:3" ht="15.75">
       <c r="A340" s="15">
-        <v>1010062008</v>
+        <v>1040077411</v>
       </c>
       <c r="B340" s="5" t="s">
         <v>342</v>
@@ -5913,8 +5919,8 @@
       </c>
     </row>
     <row r="341" spans="1:3" ht="15.75">
-      <c r="A341" s="19">
-        <v>1040040960</v>
+      <c r="A341" s="15">
+        <v>1040077410</v>
       </c>
       <c r="B341" s="5" t="s">
         <v>343</v>
@@ -5925,31 +5931,31 @@
     </row>
     <row r="342" spans="1:3" ht="15.75">
       <c r="A342" s="15">
+        <v>1010062008</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="15.75">
+      <c r="A343" s="19">
+        <v>1040040960</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="15.75">
+      <c r="A344" s="15">
         <v>1010031536</v>
       </c>
-      <c r="B342" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="C342" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" ht="15.75">
-      <c r="A343" s="15">
-        <v>1010031545</v>
-      </c>
-      <c r="B343" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C343" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" ht="15.75">
-      <c r="A344" s="30">
-        <v>1010084767</v>
-      </c>
-      <c r="B344" s="5" t="s">
+      <c r="B344" s="7" t="s">
         <v>346</v>
       </c>
       <c r="C344" s="4" t="s">
@@ -5958,9 +5964,9 @@
     </row>
     <row r="345" spans="1:3" ht="15.75">
       <c r="A345" s="15">
-        <v>1040077360</v>
-      </c>
-      <c r="B345" s="5" t="s">
+        <v>1010031545</v>
+      </c>
+      <c r="B345" s="7" t="s">
         <v>347</v>
       </c>
       <c r="C345" s="4" t="s">
@@ -5968,8 +5974,8 @@
       </c>
     </row>
     <row r="346" spans="1:3" ht="15.75">
-      <c r="A346" s="15">
-        <v>1010064470</v>
+      <c r="A346" s="30">
+        <v>1010084767</v>
       </c>
       <c r="B346" s="5" t="s">
         <v>348</v>
@@ -5980,7 +5986,7 @@
     </row>
     <row r="347" spans="1:3" ht="15.75">
       <c r="A347" s="15">
-        <v>1010021991</v>
+        <v>1040077360</v>
       </c>
       <c r="B347" s="5" t="s">
         <v>349</v>
@@ -5991,7 +5997,7 @@
     </row>
     <row r="348" spans="1:3" ht="15.75">
       <c r="A348" s="15">
-        <v>1010021960</v>
+        <v>1010064470</v>
       </c>
       <c r="B348" s="5" t="s">
         <v>350</v>
@@ -6002,7 +6008,7 @@
     </row>
     <row r="349" spans="1:3" ht="15.75">
       <c r="A349" s="15">
-        <v>1010031690</v>
+        <v>1010021991</v>
       </c>
       <c r="B349" s="5" t="s">
         <v>351</v>
@@ -6013,7 +6019,7 @@
     </row>
     <row r="350" spans="1:3" ht="15.75">
       <c r="A350" s="15">
-        <v>1010022590</v>
+        <v>1010021960</v>
       </c>
       <c r="B350" s="5" t="s">
         <v>352</v>
@@ -6024,7 +6030,7 @@
     </row>
     <row r="351" spans="1:3" ht="15.75">
       <c r="A351" s="15">
-        <v>1040098643</v>
+        <v>1010031690</v>
       </c>
       <c r="B351" s="5" t="s">
         <v>353</v>
@@ -6035,7 +6041,7 @@
     </row>
     <row r="352" spans="1:3" ht="15.75">
       <c r="A352" s="15">
-        <v>1010086020</v>
+        <v>1010022590</v>
       </c>
       <c r="B352" s="5" t="s">
         <v>354</v>
@@ -6046,7 +6052,7 @@
     </row>
     <row r="353" spans="1:3" ht="15.75">
       <c r="A353" s="15">
-        <v>1010046550</v>
+        <v>1040098643</v>
       </c>
       <c r="B353" s="5" t="s">
         <v>355</v>
@@ -6057,7 +6063,7 @@
     </row>
     <row r="354" spans="1:3" ht="15.75">
       <c r="A354" s="15">
-        <v>1010046402</v>
+        <v>1010086020</v>
       </c>
       <c r="B354" s="5" t="s">
         <v>356</v>
@@ -6068,7 +6074,7 @@
     </row>
     <row r="355" spans="1:3" ht="15.75">
       <c r="A355" s="15">
-        <v>1010060291</v>
+        <v>1010046550</v>
       </c>
       <c r="B355" s="5" t="s">
         <v>357</v>
@@ -6079,7 +6085,7 @@
     </row>
     <row r="356" spans="1:3" ht="15.75">
       <c r="A356" s="15">
-        <v>1010050920</v>
+        <v>1010046402</v>
       </c>
       <c r="B356" s="5" t="s">
         <v>358</v>
@@ -6090,7 +6096,7 @@
     </row>
     <row r="357" spans="1:3" ht="15.75">
       <c r="A357" s="15">
-        <v>1040077412</v>
+        <v>1010060291</v>
       </c>
       <c r="B357" s="5" t="s">
         <v>359</v>
@@ -6101,7 +6107,7 @@
     </row>
     <row r="358" spans="1:3" ht="15.75">
       <c r="A358" s="15">
-        <v>1010042609</v>
+        <v>1010050920</v>
       </c>
       <c r="B358" s="5" t="s">
         <v>360</v>
@@ -6112,7 +6118,7 @@
     </row>
     <row r="359" spans="1:3" ht="15.75">
       <c r="A359" s="15">
-        <v>417701</v>
+        <v>1040077412</v>
       </c>
       <c r="B359" s="5" t="s">
         <v>361</v>
@@ -6123,7 +6129,7 @@
     </row>
     <row r="360" spans="1:3" ht="15.75">
       <c r="A360" s="15">
-        <v>399384</v>
+        <v>1010042609</v>
       </c>
       <c r="B360" s="5" t="s">
         <v>362</v>
@@ -6134,7 +6140,7 @@
     </row>
     <row r="361" spans="1:3" ht="15.75">
       <c r="A361" s="15">
-        <v>1010024086</v>
+        <v>417701</v>
       </c>
       <c r="B361" s="5" t="s">
         <v>363</v>
@@ -6145,7 +6151,7 @@
     </row>
     <row r="362" spans="1:3" ht="15.75">
       <c r="A362" s="15">
-        <v>1040077345</v>
+        <v>399384</v>
       </c>
       <c r="B362" s="5" t="s">
         <v>364</v>
@@ -6156,7 +6162,7 @@
     </row>
     <row r="363" spans="1:3" ht="15.75">
       <c r="A363" s="15">
-        <v>1010084315</v>
+        <v>1010024086</v>
       </c>
       <c r="B363" s="5" t="s">
         <v>365</v>
@@ -6167,7 +6173,7 @@
     </row>
     <row r="364" spans="1:3" ht="15.75">
       <c r="A364" s="15">
-        <v>399253</v>
+        <v>1040077345</v>
       </c>
       <c r="B364" s="5" t="s">
         <v>366</v>
@@ -6178,7 +6184,7 @@
     </row>
     <row r="365" spans="1:3" ht="15.75">
       <c r="A365" s="15">
-        <v>1010084317</v>
+        <v>1010084315</v>
       </c>
       <c r="B365" s="5" t="s">
         <v>367</v>
@@ -6188,8 +6194,8 @@
       </c>
     </row>
     <row r="366" spans="1:3" ht="15.75">
-      <c r="A366" s="25">
-        <v>1010085369</v>
+      <c r="A366" s="15">
+        <v>399253</v>
       </c>
       <c r="B366" s="5" t="s">
         <v>368</v>
@@ -6200,7 +6206,7 @@
     </row>
     <row r="367" spans="1:3" ht="15.75">
       <c r="A367" s="15">
-        <v>1010085370</v>
+        <v>1010084317</v>
       </c>
       <c r="B367" s="5" t="s">
         <v>369</v>
@@ -6210,8 +6216,8 @@
       </c>
     </row>
     <row r="368" spans="1:3" ht="15.75">
-      <c r="A368" s="15">
-        <v>1010085204</v>
+      <c r="A368" s="25">
+        <v>1010085369</v>
       </c>
       <c r="B368" s="5" t="s">
         <v>370</v>
@@ -6222,7 +6228,7 @@
     </row>
     <row r="369" spans="1:3" ht="15.75">
       <c r="A369" s="15">
-        <v>1010003966</v>
+        <v>1010085370</v>
       </c>
       <c r="B369" s="5" t="s">
         <v>371</v>
@@ -6233,7 +6239,7 @@
     </row>
     <row r="370" spans="1:3" ht="15.75">
       <c r="A370" s="15">
-        <v>1010003967</v>
+        <v>1010085204</v>
       </c>
       <c r="B370" s="5" t="s">
         <v>372</v>
@@ -6244,7 +6250,7 @@
     </row>
     <row r="371" spans="1:3" ht="15.75">
       <c r="A371" s="15">
-        <v>65219</v>
+        <v>1010003966</v>
       </c>
       <c r="B371" s="5" t="s">
         <v>373</v>
@@ -6255,7 +6261,7 @@
     </row>
     <row r="372" spans="1:3" ht="15.75">
       <c r="A372" s="15">
-        <v>10168</v>
+        <v>1010003967</v>
       </c>
       <c r="B372" s="5" t="s">
         <v>374</v>
@@ -6266,7 +6272,7 @@
     </row>
     <row r="373" spans="1:3" ht="15.75">
       <c r="A373" s="15">
-        <v>1010083792</v>
+        <v>65219</v>
       </c>
       <c r="B373" s="5" t="s">
         <v>375</v>
@@ -6277,7 +6283,7 @@
     </row>
     <row r="374" spans="1:3" ht="15.75">
       <c r="A374" s="15">
-        <v>1040077414</v>
+        <v>10168</v>
       </c>
       <c r="B374" s="5" t="s">
         <v>376</v>
@@ -6288,7 +6294,7 @@
     </row>
     <row r="375" spans="1:3" ht="15.75">
       <c r="A375" s="15">
-        <v>1010018482</v>
+        <v>1010083792</v>
       </c>
       <c r="B375" s="5" t="s">
         <v>377</v>
@@ -6299,7 +6305,7 @@
     </row>
     <row r="376" spans="1:3" ht="15.75">
       <c r="A376" s="15">
-        <v>1010084320</v>
+        <v>1040077414</v>
       </c>
       <c r="B376" s="5" t="s">
         <v>378</v>
@@ -6310,7 +6316,7 @@
     </row>
     <row r="377" spans="1:3" ht="15.75">
       <c r="A377" s="15">
-        <v>1010084532</v>
+        <v>1010018482</v>
       </c>
       <c r="B377" s="5" t="s">
         <v>379</v>
@@ -6321,7 +6327,7 @@
     </row>
     <row r="378" spans="1:3" ht="15.75">
       <c r="A378" s="15">
-        <v>1010027285</v>
+        <v>1010084320</v>
       </c>
       <c r="B378" s="5" t="s">
         <v>380</v>
@@ -6332,7 +6338,7 @@
     </row>
     <row r="379" spans="1:3" ht="15.75">
       <c r="A379" s="15">
-        <v>1040077413</v>
+        <v>1010084532</v>
       </c>
       <c r="B379" s="5" t="s">
         <v>381</v>
@@ -6343,7 +6349,7 @@
     </row>
     <row r="380" spans="1:3" ht="15.75">
       <c r="A380" s="15">
-        <v>1010085376</v>
+        <v>1010027285</v>
       </c>
       <c r="B380" s="5" t="s">
         <v>382</v>
@@ -6354,7 +6360,7 @@
     </row>
     <row r="381" spans="1:3" ht="15.75">
       <c r="A381" s="15">
-        <v>1010022819</v>
+        <v>1040077413</v>
       </c>
       <c r="B381" s="5" t="s">
         <v>383</v>
@@ -6365,7 +6371,7 @@
     </row>
     <row r="382" spans="1:3" ht="15.75">
       <c r="A382" s="15">
-        <v>1010052853</v>
+        <v>1010085376</v>
       </c>
       <c r="B382" s="5" t="s">
         <v>384</v>
@@ -6376,7 +6382,7 @@
     </row>
     <row r="383" spans="1:3" ht="15.75">
       <c r="A383" s="15">
-        <v>1010084377</v>
+        <v>1010022819</v>
       </c>
       <c r="B383" s="5" t="s">
         <v>385</v>
@@ -6386,1366 +6392,1380 @@
       </c>
     </row>
     <row r="384" spans="1:3" ht="15.75">
-      <c r="A384" s="26">
-        <v>1010062826</v>
+      <c r="A384" s="15">
+        <v>1010052853</v>
       </c>
       <c r="B384" s="5" t="s">
         <v>386</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>387</v>
+        <v>4</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="15.75">
       <c r="A385" s="15">
-        <v>1010002592</v>
+        <v>1010084377</v>
       </c>
       <c r="B385" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" ht="15.75">
+      <c r="A386" s="26">
+        <v>1010062826</v>
+      </c>
+      <c r="B386" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="C385" s="4" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" ht="15.75">
-      <c r="A386" s="24">
-        <v>1010001155</v>
-      </c>
-      <c r="B386" s="5" t="s">
+      <c r="C386" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="C386" s="4" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="15.75">
       <c r="A387" s="15">
-        <v>1010001062</v>
+        <v>1010002592</v>
       </c>
       <c r="B387" s="5" t="s">
         <v>390</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="15.75">
-      <c r="A388" s="15">
-        <v>1010084328</v>
+      <c r="A388" s="24">
+        <v>1010001155</v>
       </c>
       <c r="B388" s="5" t="s">
         <v>391</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="15.75">
-      <c r="A389" s="24">
-        <v>1010044502</v>
+      <c r="A389" s="15">
+        <v>1010001062</v>
       </c>
       <c r="B389" s="5" t="s">
         <v>392</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="15.75">
       <c r="A390" s="15">
-        <v>1010053692</v>
+        <v>1010084328</v>
       </c>
       <c r="B390" s="5" t="s">
         <v>393</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="15.75">
-      <c r="A391" s="15">
-        <v>1010083992</v>
+      <c r="A391" s="24">
+        <v>1010044502</v>
       </c>
       <c r="B391" s="5" t="s">
         <v>394</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="15.75">
       <c r="A392" s="15">
-        <v>1010008578</v>
+        <v>1010053692</v>
       </c>
       <c r="B392" s="5" t="s">
         <v>395</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="15.75">
       <c r="A393" s="15">
-        <v>1010031694</v>
+        <v>1010083992</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="15.75">
       <c r="A394" s="15">
-        <v>1010051997</v>
+        <v>1010008578</v>
       </c>
       <c r="B394" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C394" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="C394" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="15.75">
       <c r="A395" s="15">
-        <v>1010022601</v>
+        <v>1010031694</v>
       </c>
       <c r="B395" s="5" t="s">
         <v>399</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="15.75">
       <c r="A396" s="15">
-        <v>1010054278</v>
+        <v>1010051997</v>
       </c>
       <c r="B396" s="5" t="s">
         <v>400</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="15.75">
       <c r="A397" s="15">
-        <v>1010083462</v>
+        <v>1010022601</v>
       </c>
       <c r="B397" s="5" t="s">
         <v>401</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="15.75">
       <c r="A398" s="15">
-        <v>1010027772</v>
+        <v>1010054278</v>
       </c>
       <c r="B398" s="5" t="s">
         <v>402</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="15.75">
       <c r="A399" s="15">
-        <v>1010084144</v>
+        <v>1010083462</v>
       </c>
       <c r="B399" s="5" t="s">
         <v>403</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="15.75">
-      <c r="A400" s="19">
+      <c r="A400" s="15">
+        <v>1010027772</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" ht="15.75">
+      <c r="A401" s="15">
+        <v>1010084144</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="15.75">
+      <c r="A402" s="19">
         <v>1010084958</v>
-      </c>
-      <c r="B400" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="C400" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4" ht="15.75">
-      <c r="A401" s="19">
-        <v>1010084720</v>
-      </c>
-      <c r="B401" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="C401" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="D401" s="29"/>
-    </row>
-    <row r="402" spans="1:4" ht="15.75">
-      <c r="A402" s="18">
-        <v>1010021956</v>
       </c>
       <c r="B402" s="7" t="s">
         <v>406</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15.75">
-      <c r="A403" s="18">
-        <v>1010026464</v>
+      <c r="A403" s="19">
+        <v>1010084720</v>
       </c>
       <c r="B403" s="7" t="s">
         <v>407</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>396</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="D403" s="29"/>
     </row>
     <row r="404" spans="1:4" ht="15.75">
-      <c r="A404" s="14">
+      <c r="A404" s="18">
+        <v>1010021956</v>
+      </c>
+      <c r="B404" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="15.75">
+      <c r="A405" s="18">
+        <v>1010026464</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" ht="15.75">
+      <c r="A406" s="14">
         <v>1010021957</v>
-      </c>
-      <c r="B404" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="C404" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" ht="15.75">
-      <c r="A405" s="15">
-        <v>1010026462</v>
-      </c>
-      <c r="B405" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="C405" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" ht="15.75">
-      <c r="A406" s="15">
-        <v>1010026551</v>
       </c>
       <c r="B406" s="5" t="s">
         <v>410</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="15.75">
       <c r="A407" s="15">
-        <v>1010042554</v>
+        <v>1010026462</v>
       </c>
       <c r="B407" s="5" t="s">
         <v>411</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15.75">
       <c r="A408" s="15">
-        <v>1010039904</v>
+        <v>1010026551</v>
       </c>
       <c r="B408" s="5" t="s">
         <v>412</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="15.75">
       <c r="A409" s="15">
-        <v>1010060205</v>
+        <v>1010042554</v>
       </c>
       <c r="B409" s="5" t="s">
         <v>413</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75">
       <c r="A410" s="15">
-        <v>1010060206</v>
+        <v>1010039904</v>
       </c>
       <c r="B410" s="5" t="s">
         <v>414</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="15.75">
       <c r="A411" s="15">
-        <v>1010077431</v>
+        <v>1010060205</v>
       </c>
       <c r="B411" s="5" t="s">
         <v>415</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="15.75">
       <c r="A412" s="15">
-        <v>1010077503</v>
+        <v>1010060206</v>
       </c>
       <c r="B412" s="5" t="s">
         <v>416</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="15.75">
       <c r="A413" s="15">
-        <v>1010084187</v>
+        <v>1010077431</v>
       </c>
       <c r="B413" s="5" t="s">
         <v>417</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15.75">
       <c r="A414" s="15">
-        <v>1010080958</v>
+        <v>1010077503</v>
       </c>
       <c r="B414" s="5" t="s">
         <v>418</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="15.75">
       <c r="A415" s="15">
-        <v>1010026032</v>
+        <v>1010084187</v>
       </c>
       <c r="B415" s="5" t="s">
         <v>419</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="416" spans="1:4" ht="15.75">
       <c r="A416" s="15">
-        <v>1010085384</v>
+        <v>1010080958</v>
       </c>
       <c r="B416" s="5" t="s">
         <v>420</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15.75">
       <c r="A417" s="15">
-        <v>1010006347</v>
+        <v>1010026032</v>
       </c>
       <c r="B417" s="5" t="s">
         <v>421</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15.75">
       <c r="A418" s="15">
-        <v>1010085179</v>
+        <v>1010085384</v>
       </c>
       <c r="B418" s="5" t="s">
         <v>422</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75">
       <c r="A419" s="15">
-        <v>1010024158</v>
-      </c>
-      <c r="B419" s="8" t="s">
+        <v>1010006347</v>
+      </c>
+      <c r="B419" s="5" t="s">
         <v>423</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15.75">
       <c r="A420" s="15">
-        <v>1010024131</v>
-      </c>
-      <c r="B420" s="8" t="s">
+        <v>1010085179</v>
+      </c>
+      <c r="B420" s="5" t="s">
         <v>424</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75">
       <c r="A421" s="15">
-        <v>1010007160</v>
-      </c>
-      <c r="B421" s="5" t="s">
+        <v>1010024158</v>
+      </c>
+      <c r="B421" s="8" t="s">
         <v>425</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75">
       <c r="A422" s="15">
-        <v>1010023642</v>
-      </c>
-      <c r="B422" s="5" t="s">
+        <v>1010024131</v>
+      </c>
+      <c r="B422" s="8" t="s">
         <v>426</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15.75">
       <c r="A423" s="15">
-        <v>1010007193</v>
-      </c>
-      <c r="B423" s="6" t="s">
+        <v>1010007160</v>
+      </c>
+      <c r="B423" s="5" t="s">
         <v>427</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15.75">
       <c r="A424" s="15">
-        <v>1010042637</v>
+        <v>1010023642</v>
       </c>
       <c r="B424" s="5" t="s">
         <v>428</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="15.75">
       <c r="A425" s="15">
-        <v>1040075323</v>
-      </c>
-      <c r="B425" s="5" t="s">
+        <v>1010007193</v>
+      </c>
+      <c r="B425" s="6" t="s">
         <v>429</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75">
       <c r="A426" s="15">
+        <v>1010042637</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C426" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" ht="15.75">
+      <c r="A427" s="15">
+        <v>1040075323</v>
+      </c>
+      <c r="B427" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" ht="15.75">
+      <c r="A428" s="15">
         <v>1040075324</v>
-      </c>
-      <c r="B426" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="C426" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="15.75">
-      <c r="A427" s="27">
-        <v>1040074827</v>
-      </c>
-      <c r="B427" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="C427" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" ht="15.75">
-      <c r="A428" s="27">
-        <v>1040099488</v>
       </c>
       <c r="B428" s="8" t="s">
         <v>432</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="15.75">
       <c r="A429" s="27">
-        <v>1040083312</v>
+        <v>1040074827</v>
       </c>
       <c r="B429" s="8" t="s">
         <v>433</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15.75">
       <c r="A430" s="27">
-        <v>1040077661</v>
+        <v>1040099488</v>
       </c>
       <c r="B430" s="8" t="s">
         <v>434</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15.75">
       <c r="A431" s="27">
+        <v>1040083312</v>
+      </c>
+      <c r="B431" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="15.75">
+      <c r="A432" s="27">
+        <v>1040077661</v>
+      </c>
+      <c r="B432" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="15.75">
+      <c r="A433" s="27">
         <v>1010085180</v>
       </c>
-      <c r="B431" s="12" t="s">
-        <v>435</v>
-      </c>
-      <c r="C431" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75">
-      <c r="A432" s="14">
+      <c r="B433" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="15.75">
+      <c r="A434" s="14">
         <v>1040017489</v>
       </c>
-      <c r="B432" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="15.75">
-      <c r="A433" s="14">
+      <c r="B434" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="15.75">
+      <c r="A435" s="14">
         <v>1010085181</v>
-      </c>
-      <c r="B433" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C433" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="15.75">
-      <c r="A434" s="15">
-        <v>400175</v>
-      </c>
-      <c r="B434" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="15.75">
-      <c r="A435" s="15">
-        <v>1040017505</v>
       </c>
       <c r="B435" s="5" t="s">
         <v>439</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="15.75">
       <c r="A436" s="15">
-        <v>1040017503</v>
+        <v>400175</v>
       </c>
       <c r="B436" s="5" t="s">
         <v>440</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="15.75">
       <c r="A437" s="15">
-        <v>1010046445</v>
+        <v>1040017505</v>
       </c>
       <c r="B437" s="5" t="s">
         <v>441</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="15.75">
       <c r="A438" s="15">
-        <v>1010021033</v>
+        <v>1040017503</v>
       </c>
       <c r="B438" s="5" t="s">
         <v>442</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="15.75">
       <c r="A439" s="15">
-        <v>1010057142</v>
+        <v>1010046445</v>
       </c>
       <c r="B439" s="5" t="s">
         <v>443</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="15.75">
       <c r="A440" s="15">
-        <v>1010016356</v>
+        <v>1010021033</v>
       </c>
       <c r="B440" s="5" t="s">
         <v>444</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="15.75">
       <c r="A441" s="15">
-        <v>1010084363</v>
+        <v>1010057142</v>
       </c>
       <c r="B441" s="5" t="s">
         <v>445</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="15.75">
       <c r="A442" s="15">
-        <v>1010052021</v>
+        <v>1010016356</v>
       </c>
       <c r="B442" s="5" t="s">
         <v>446</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="15.75">
       <c r="A443" s="15">
-        <v>1040091721</v>
+        <v>1010084363</v>
       </c>
       <c r="B443" s="5" t="s">
         <v>447</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="15.75">
       <c r="A444" s="15">
-        <v>1010062022</v>
+        <v>1010052021</v>
       </c>
       <c r="B444" s="5" t="s">
         <v>448</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="15.75">
       <c r="A445" s="15">
-        <v>18336</v>
+        <v>1040091721</v>
       </c>
       <c r="B445" s="5" t="s">
         <v>449</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="15.75">
       <c r="A446" s="15">
-        <v>229205</v>
+        <v>1010062022</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>450</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="15.75">
       <c r="A447" s="15">
-        <v>60671</v>
+        <v>18336</v>
       </c>
       <c r="B447" s="5" t="s">
         <v>451</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="15.75">
       <c r="A448" s="15">
-        <v>1010059726</v>
+        <v>229205</v>
       </c>
       <c r="B448" s="5" t="s">
         <v>452</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="15.75">
       <c r="A449" s="15">
-        <v>1010008144</v>
+        <v>60671</v>
       </c>
       <c r="B449" s="5" t="s">
         <v>453</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="15.75">
       <c r="A450" s="15">
-        <v>1010007244</v>
+        <v>1010059726</v>
       </c>
       <c r="B450" s="5" t="s">
         <v>454</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="15.75">
       <c r="A451" s="15">
-        <v>1010006827</v>
+        <v>1010008144</v>
       </c>
       <c r="B451" s="5" t="s">
         <v>455</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="15.75">
       <c r="A452" s="15">
-        <v>1040075426</v>
+        <v>1010007244</v>
       </c>
       <c r="B452" s="5" t="s">
         <v>456</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="15.75">
       <c r="A453" s="15">
-        <v>1040075427</v>
+        <v>1010006827</v>
       </c>
       <c r="B453" s="5" t="s">
         <v>457</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="15.75">
       <c r="A454" s="15">
-        <v>1010084313</v>
+        <v>1040075426</v>
       </c>
       <c r="B454" s="5" t="s">
         <v>458</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="15.75">
       <c r="A455" s="15">
-        <v>403459</v>
+        <v>1040075427</v>
       </c>
       <c r="B455" s="5" t="s">
         <v>459</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="15.75">
       <c r="A456" s="15">
-        <v>1010044828</v>
+        <v>1010084313</v>
       </c>
       <c r="B456" s="5" t="s">
         <v>460</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="15.75">
       <c r="A457" s="15">
-        <v>1010026973</v>
+        <v>403459</v>
       </c>
       <c r="B457" s="5" t="s">
         <v>461</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="15.75">
       <c r="A458" s="15">
-        <v>1040017204</v>
+        <v>1010044828</v>
       </c>
       <c r="B458" s="5" t="s">
         <v>462</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="15.75">
-      <c r="A459" s="24">
-        <v>1010022119</v>
-      </c>
-      <c r="B459" s="6" t="s">
+      <c r="A459" s="15">
+        <v>1010026973</v>
+      </c>
+      <c r="B459" s="5" t="s">
         <v>463</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>464</v>
+        <v>398</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="15.75">
       <c r="A460" s="15">
-        <v>1010058709</v>
+        <v>1040017204</v>
       </c>
       <c r="B460" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="15.75">
+      <c r="A461" s="24">
+        <v>1010022119</v>
+      </c>
+      <c r="B461" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="C460" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" ht="15.75">
-      <c r="A461" s="15">
-        <v>1010025711</v>
-      </c>
-      <c r="B461" s="5" t="s">
+      <c r="C461" s="4" t="s">
         <v>466</v>
-      </c>
-      <c r="C461" s="4" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="15.75">
       <c r="A462" s="15">
-        <v>1010059684</v>
+        <v>1010058709</v>
       </c>
       <c r="B462" s="5" t="s">
         <v>467</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="15.75">
       <c r="A463" s="15">
-        <v>427341</v>
+        <v>1010025711</v>
       </c>
       <c r="B463" s="5" t="s">
         <v>468</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="15.75">
       <c r="A464" s="15">
-        <v>392696</v>
+        <v>1010059684</v>
       </c>
       <c r="B464" s="5" t="s">
         <v>469</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="15.75">
       <c r="A465" s="15">
-        <v>1010085279</v>
+        <v>427341</v>
       </c>
       <c r="B465" s="5" t="s">
         <v>470</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="15.75">
-      <c r="A466" s="19">
-        <v>1010022588</v>
+      <c r="A466" s="15">
+        <v>392696</v>
       </c>
       <c r="B466" s="5" t="s">
         <v>471</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="15.75">
       <c r="A467" s="15">
+        <v>1010085279</v>
+      </c>
+      <c r="B467" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C467" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="15.75">
+      <c r="A468" s="19">
+        <v>1010022588</v>
+      </c>
+      <c r="B468" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C468" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" ht="15.75">
+      <c r="A469" s="15">
         <v>1010026864</v>
       </c>
-      <c r="B467" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="C467" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="15.75">
-      <c r="A468" s="14">
+      <c r="B469" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="C469" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="15.75">
+      <c r="A470" s="14">
         <v>1010030946</v>
       </c>
-      <c r="B468" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="C468" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" ht="15.75">
-      <c r="A469" s="14">
+      <c r="B470" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="C470" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="15.75">
+      <c r="A471" s="14">
         <v>1010022589</v>
-      </c>
-      <c r="B469" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C469" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" ht="15.75">
-      <c r="A470" s="15">
-        <v>1040090143</v>
-      </c>
-      <c r="B470" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C470" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" ht="15.75">
-      <c r="A471" s="15">
-        <v>1040090138</v>
       </c>
       <c r="B471" s="5" t="s">
         <v>476</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="15.75">
       <c r="A472" s="15">
-        <v>1030001314</v>
+        <v>1040090143</v>
       </c>
       <c r="B472" s="5" t="s">
         <v>477</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="15.75">
       <c r="A473" s="15">
-        <v>1010052319</v>
+        <v>1040090138</v>
       </c>
       <c r="B473" s="5" t="s">
         <v>478</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="15.75">
       <c r="A474" s="15">
-        <v>1010052320</v>
+        <v>1030001314</v>
       </c>
       <c r="B474" s="5" t="s">
         <v>479</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="15.75">
       <c r="A475" s="15">
-        <v>1030000370</v>
+        <v>1010052319</v>
       </c>
       <c r="B475" s="5" t="s">
         <v>480</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15.75">
       <c r="A476" s="15">
-        <v>1030000366</v>
+        <v>1010052320</v>
       </c>
       <c r="B476" s="5" t="s">
         <v>481</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="15.75">
       <c r="A477" s="15">
-        <v>1030000368</v>
+        <v>1030000370</v>
       </c>
       <c r="B477" s="5" t="s">
         <v>482</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15.75">
       <c r="A478" s="15">
-        <v>1030000369</v>
+        <v>1030000366</v>
       </c>
       <c r="B478" s="5" t="s">
         <v>483</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="15.75">
       <c r="A479" s="15">
-        <v>1030000489</v>
+        <v>1030000368</v>
       </c>
       <c r="B479" s="5" t="s">
         <v>484</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15.75">
       <c r="A480" s="15">
-        <v>1030000490</v>
+        <v>1030000369</v>
       </c>
       <c r="B480" s="5" t="s">
         <v>485</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="15.75">
       <c r="A481" s="15">
-        <v>1030000821</v>
+        <v>1030000489</v>
       </c>
       <c r="B481" s="5" t="s">
         <v>486</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15.75">
       <c r="A482" s="15">
+        <v>1030000490</v>
+      </c>
+      <c r="B482" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C482" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" ht="15.75">
+      <c r="A483" s="15">
+        <v>1030000821</v>
+      </c>
+      <c r="B483" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C483" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" ht="15.75">
+      <c r="A484" s="15">
         <v>1030000511</v>
       </c>
-      <c r="B482" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="C482" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.75">
-      <c r="A483" s="16">
+      <c r="B484" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C484" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" ht="15.75">
+      <c r="A485" s="16">
         <v>1010084279</v>
       </c>
-      <c r="B483" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="C483" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" ht="15.75">
-      <c r="A484" s="16">
+      <c r="B485" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="C485" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" ht="15.75">
+      <c r="A486" s="16">
         <v>1010004281</v>
-      </c>
-      <c r="B484" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" ht="15.75">
-      <c r="A485" s="15">
-        <v>1010022118</v>
-      </c>
-      <c r="B485" s="9" t="s">
-        <v>490</v>
-      </c>
-      <c r="C485" s="4" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" ht="15.75">
-      <c r="A486" s="15">
-        <v>1010028657</v>
       </c>
       <c r="B486" s="5" t="s">
         <v>491</v>
       </c>
       <c r="C486" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" ht="15.75">
+      <c r="A487" s="15">
+        <v>1010022118</v>
+      </c>
+      <c r="B487" s="9" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="487" spans="1:3" ht="15.75">
-      <c r="A487" s="18">
+      <c r="C487" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" ht="15.75">
+      <c r="A488" s="15">
+        <v>1010028657</v>
+      </c>
+      <c r="B488" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C488" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" ht="15.75">
+      <c r="A489" s="18">
         <v>1010028655</v>
-      </c>
-      <c r="B487" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="C487" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" ht="15.75">
-      <c r="A488" s="18">
-        <v>145165</v>
-      </c>
-      <c r="B488" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="C488" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" ht="15.75">
-      <c r="A489" s="15">
-        <v>51666</v>
       </c>
       <c r="B489" s="5" t="s">
         <v>495</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="15.75">
       <c r="A490" s="18">
-        <v>1010080930</v>
+        <v>145165</v>
       </c>
       <c r="B490" s="5" t="s">
         <v>496</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="15.75">
       <c r="A491" s="15">
-        <v>161055</v>
+        <v>51666</v>
       </c>
       <c r="B491" s="5" t="s">
         <v>497</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="15.75">
-      <c r="A492" s="15">
-        <v>1010050517</v>
+      <c r="A492" s="18">
+        <v>1010080930</v>
       </c>
       <c r="B492" s="5" t="s">
         <v>498</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="15.75">
       <c r="A493" s="15">
-        <v>1010084190</v>
+        <v>161055</v>
       </c>
       <c r="B493" s="5" t="s">
         <v>499</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="15.75">
       <c r="A494" s="15">
-        <v>1010084195</v>
+        <v>1010050517</v>
       </c>
       <c r="B494" s="5" t="s">
         <v>500</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="15.75">
       <c r="A495" s="15">
-        <v>1010001400</v>
+        <v>1010084190</v>
       </c>
       <c r="B495" s="5" t="s">
         <v>501</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="15.75">
-      <c r="A496" s="17">
-        <v>1010008416</v>
+      <c r="A496" s="15">
+        <v>1010084195</v>
       </c>
       <c r="B496" s="5" t="s">
         <v>502</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="15.75">
-      <c r="A497" s="28">
-        <v>1010018372</v>
+      <c r="A497" s="15">
+        <v>1010001400</v>
       </c>
       <c r="B497" s="5" t="s">
         <v>503</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="15.75">
-      <c r="A498" s="28">
+      <c r="A498" s="17">
+        <v>1010008416</v>
+      </c>
+      <c r="B498" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C498" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" ht="15.75">
+      <c r="A499" s="28">
+        <v>1010018372</v>
+      </c>
+      <c r="B499" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="C499" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" ht="15.75">
+      <c r="A500" s="28">
         <v>1010018361</v>
       </c>
-      <c r="B498" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="C498" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" ht="15.75">
-      <c r="A499" s="16">
+      <c r="B500" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C500" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" ht="15.75">
+      <c r="A501" s="16">
         <v>1010055398</v>
       </c>
-      <c r="B499" s="11" t="s">
-        <v>505</v>
-      </c>
-      <c r="C499" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" ht="15.75">
-      <c r="A500" s="15">
-        <v>422131</v>
-      </c>
-      <c r="B500" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="C500" s="4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" ht="15.75">
-      <c r="A501" s="15">
-        <v>1010084370</v>
-      </c>
-      <c r="B501" s="5" t="s">
+      <c r="B501" s="11" t="s">
         <v>507</v>
       </c>
       <c r="C501" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="15.75">
       <c r="A502" s="15">
-        <v>422759</v>
+        <v>422131</v>
       </c>
       <c r="B502" s="5" t="s">
         <v>508</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="15.75">
       <c r="A503" s="15">
-        <v>120955</v>
+        <v>1010084370</v>
       </c>
       <c r="B503" s="5" t="s">
         <v>509</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="15.75">
       <c r="A504" s="15">
-        <v>1010000896</v>
+        <v>422759</v>
       </c>
       <c r="B504" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="C504" s="13" t="s">
-        <v>492</v>
+      <c r="C504" s="4" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="15.75">
       <c r="A505" s="15">
-        <v>1010084308</v>
+        <v>120955</v>
       </c>
       <c r="B505" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="C505" s="13" t="s">
-        <v>492</v>
+      <c r="C505" s="4" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="15.75">
       <c r="A506" s="15">
-        <v>1010084035</v>
+        <v>1010000896</v>
       </c>
       <c r="B506" s="5" t="s">
         <v>512</v>
       </c>
       <c r="C506" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="15.75">
-      <c r="A507" s="2"/>
-      <c r="B507" s="2"/>
+      <c r="A507" s="15">
+        <v>1010084308</v>
+      </c>
+      <c r="B507" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="C507" s="13" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="508" spans="1:3" ht="15.75">
-      <c r="A508" s="2"/>
-      <c r="B508" s="2"/>
+      <c r="A508" s="15">
+        <v>1010084035</v>
+      </c>
+      <c r="B508" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="C508" s="13" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="509" spans="1:3" ht="15.75">
       <c r="A509" s="2"/>
@@ -9497,11 +9517,11 @@
     </row>
     <row r="946" spans="1:2" ht="15.75">
       <c r="A946" s="2"/>
-      <c r="B946" s="1"/>
+      <c r="B946" s="2"/>
     </row>
     <row r="947" spans="1:2" ht="15.75">
       <c r="A947" s="2"/>
-      <c r="B947" s="1"/>
+      <c r="B947" s="2"/>
     </row>
     <row r="948" spans="1:2" ht="15.75">
       <c r="A948" s="2"/>
@@ -9768,11 +9788,11 @@
       <c r="B1013" s="1"/>
     </row>
     <row r="1014" spans="1:2" ht="15.75">
-      <c r="A1014" s="1"/>
+      <c r="A1014" s="2"/>
       <c r="B1014" s="1"/>
     </row>
     <row r="1015" spans="1:2" ht="15.75">
-      <c r="A1015" s="1"/>
+      <c r="A1015" s="2"/>
       <c r="B1015" s="1"/>
     </row>
     <row r="1016" spans="1:2" ht="15.75">
@@ -10546,6 +10566,14 @@
     <row r="1208" spans="1:2" ht="15.75">
       <c r="A1208" s="1"/>
       <c r="B1208" s="1"/>
+    </row>
+    <row r="1209" spans="1:2" ht="15.75">
+      <c r="A1209" s="1"/>
+      <c r="B1209" s="1"/>
+    </row>
+    <row r="1210" spans="1:2" ht="15.75">
+      <c r="A1210" s="1"/>
+      <c r="B1210" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10574,22 +10602,22 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C007812D-C761-4AF8-B92C-B8C8C6FD394F}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B142A3D4-7CD6-4772-8E1B-AA6D80766BFB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="151" spans="1:3" ht="15.75">
       <c r="A151" s="15">
-        <v>357623</v>
+        <v>1010050632</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>153</v>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B142A3D4-7CD6-4772-8E1B-AA6D80766BFB}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B53BDE8-CAB2-4A63-8770-DBF0AE12CD98}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,7 +514,7 @@
     <t>PORCA P/GRAMPO PNEUMATICO (4UND)</t>
   </si>
   <si>
-    <t>GRAXA LITIO 20KG (1 UNID)</t>
+    <t>GRAXA LITIO 20KG (LANÇAR POR KG)</t>
   </si>
   <si>
     <t>GRAXA TEXACO 170KG</t>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B53BDE8-CAB2-4A63-8770-DBF0AE12CD98}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C27745F-8FF7-41E5-88C5-E0A2A8D86011}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,9 +775,6 @@
     <t>PARALAMA VOLVO MEIO PARALAMA (PARTE DE BAIXO)</t>
   </si>
   <si>
-    <t>PARA-LAMA VOLVO 2ª PARTE (PARTE DE CIMA)</t>
-  </si>
-  <si>
     <t>PARALAMA CARRETA LIBRELATO</t>
   </si>
   <si>
@@ -1598,13 +1595,16 @@
   </si>
   <si>
     <t>TINTA SPRAY AZU 250GR</t>
+  </si>
+  <si>
+    <t>PARALAMA VOLVO 2ª PARTE (PARTE DE CIMA)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2170,15 +2170,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1210"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F1210"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>1040019909</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>1040023837</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>1040023836</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>1010000216</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>423651</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>1040077347</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>1040077348</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>417715</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>1010062075</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>1040083308</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>1040077346</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>1010049326</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>1040017265</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>1010060188</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>1040019851</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>1010077433</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>1010042610</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>1040077352</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>1040083258</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>68686</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>1010084124</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>102286</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>1040097671</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>1010003651</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>1010062027</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>1010021550</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>1040077350</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>1040077349</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>154897</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>13781</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>1010058682</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>1010059706</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>1010077386</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>1010058325</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>1010061986</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>1010004299</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>1010004301</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>1010004289</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>1010004292</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>1010012756</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>1040077354</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="14">
         <v>1010050496</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="14">
         <v>1010050536</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="14">
         <v>1010061810</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
         <v>1040092580</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="14">
         <v>1010041375</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="14">
         <v>1040098335</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="14">
         <v>1010023362</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="14">
         <v>1010052336</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="14">
         <v>1040077355</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
         <v>230110</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
         <v>1040077357</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="14">
         <v>1040077356</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="15">
         <v>1040075251</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
         <v>1040090022</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
         <v>1010023336</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
         <v>1010021328</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>1010059706</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
         <v>1010062152</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
         <v>1040077358</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
         <v>1010045227</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
         <v>1010085124</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
         <v>1010046495</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
         <v>1040101764</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="14">
         <v>1010032356</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="14">
         <v>1010050244</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="14">
         <v>1010050243</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="14">
         <v>428995</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="14">
         <v>428998</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="14">
         <v>1010031607</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="14">
         <v>1010031630</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="14">
         <v>1010045647</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="14">
         <v>1010031567</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75">
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="14">
         <v>1040077361</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75">
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="14">
         <v>1010050445</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75">
+    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="14">
         <v>1010050461</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75">
+    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="14">
         <v>1010087609</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.75">
+    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="14">
         <v>1010087738</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75">
+    <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="14">
         <v>1010053885</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.75">
+    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="15">
         <v>1040097102</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75">
+    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
         <v>1010020838</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75">
+    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="16">
         <v>341430</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75">
+    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>1010042643</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75">
+    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>425554</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75">
+    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>1010084162</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75">
+    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>1010084157</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75">
+    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>1010084158</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75">
+    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>1010084159</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.75">
+    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="15">
         <v>1010084160</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.75">
+    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="15">
         <v>1010084161</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75">
+    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="15">
         <v>224382</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.75">
+    <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="15">
         <v>94314</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75">
+    <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="17">
         <v>1010003982</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.75">
+    <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="15">
         <v>1010000182</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.75">
+    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="15">
         <v>1010021079</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.75">
+    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="15">
         <v>1010002463</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.75">
+    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="15">
         <v>1010062982</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.75">
+    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="15">
         <v>1010063209</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.75">
+    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="15">
         <v>1040076302</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.75">
+    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="15">
         <v>1040077362</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75">
+    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="15">
         <v>1040077363</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.75">
+    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="15">
         <v>1040074483</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75">
+    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="15">
         <v>1040077364</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.75">
+    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="15">
         <v>1040048463</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.75">
+    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="15">
         <v>1040096343</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.75">
+    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="15">
         <v>409640</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.75">
+    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="15">
         <v>1010032753</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.75">
+    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="15">
         <v>1040098597</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.75">
+    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="15">
         <v>1040084464</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.75">
+    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="15">
         <v>1040017773</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.75">
+    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="15">
         <v>1010007405</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.75">
+    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="17">
         <v>1040077365</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.75">
+    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="15">
         <v>1010027794</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.75">
+    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="15">
         <v>1040077366</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.75">
+    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="15">
         <v>1040077367</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.75">
+    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="15">
         <v>1010021561</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.75">
+    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="15">
         <v>1010021562</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.75">
+    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="15">
         <v>1010027792</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75">
+    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="15">
         <v>1010084930</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.75">
+    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="15">
         <v>341430</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.75">
+    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="15">
         <v>1010029366</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75">
+    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="18">
         <v>1010031723</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75">
+    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="18">
         <v>1010049216</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.75">
+    <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="15">
         <v>405558</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.75">
+    <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="15">
         <v>1010023038</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.75">
+    <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="15">
         <v>1010084109</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.75">
+    <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="15">
         <v>1010021582</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.75">
+    <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="15">
         <v>1010021544</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.75">
+    <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="15">
         <v>1010021564</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.75">
+    <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="15">
         <v>1010023019</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.75">
+    <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="15">
         <v>1010048541</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.75">
+    <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="15">
         <v>1010059334</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.75">
+    <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="15">
         <v>1010000277</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.75">
+    <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="19">
         <v>1010085344</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.75">
+    <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="19">
         <v>1010085383</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.75">
+    <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="15">
         <v>1010001389</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.75">
+    <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="15">
         <v>1010017703</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.75">
+    <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="15">
         <v>1010052036</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.75">
+    <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="15">
         <v>1040097133</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.75">
+    <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="15">
         <v>1040019325</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.75">
+    <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="15">
         <v>64262</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.75">
+    <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="14">
         <v>1010047089</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.75">
+    <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="14">
         <v>1040050168</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.75">
+    <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="14">
         <v>1040077370</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.75">
+    <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="14">
         <v>1040099247</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.75">
+    <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="15">
         <v>1040100560</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.75">
+    <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="15">
         <v>1040077399</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.75">
+    <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="15">
         <v>1040077374</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.75">
+    <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="15">
         <v>1040077399</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.75">
+    <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="15">
         <v>1010050632</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.75">
+    <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="15">
         <v>1010020504</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15.75">
+    <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="15">
         <v>409250</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.75">
+    <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="15">
         <v>1010020541</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.75">
+    <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="15">
         <v>1010020879</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.75">
+    <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="15">
         <v>1040077380</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.75">
+    <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="15">
         <v>1010021520</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.75">
+    <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="15">
         <v>1040098861</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.75">
+    <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="15">
         <v>1010077261</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.75">
+    <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="15">
         <v>1010027664</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.75">
+    <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="15">
         <v>1010083731</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.75">
+    <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="15">
         <v>1010083885</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.75">
+    <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="15">
         <v>1010014834</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.75">
+    <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="15">
         <v>1010083908</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.75">
+    <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="15">
         <v>1010024047</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.75">
+    <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="15">
         <v>1040077377</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.75">
+    <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="15">
         <v>1010061942</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15.75">
+    <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="15">
         <v>1040097070</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.75">
+    <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="15">
         <v>1040097068</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.75">
+    <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="15">
         <v>22004</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.75">
+    <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="15">
         <v>1010058554</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.75">
+    <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="15">
         <v>1010027308</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.75">
+    <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="19">
         <v>1040077383</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15.75">
+    <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="19">
         <v>1010025482</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.75">
+    <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="19">
         <v>1010025509</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.75">
+    <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="15">
         <v>1010027789</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.75">
+    <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="15">
         <v>1010027790</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.75">
+    <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="15">
         <v>1010018301</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.75">
+    <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="15">
         <v>1010031616</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.75">
+    <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="15">
         <v>1010053728</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.75">
+    <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="15">
         <v>1010020758</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.75">
+    <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="15">
         <v>1010020781</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75">
+    <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="14">
         <v>1010058426</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75">
+    <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="14">
         <v>1010059332</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75">
+    <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="14">
         <v>1040077389</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75">
+    <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="15">
         <v>1010021364</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75">
+    <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="20">
         <v>1010021541</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75">
+    <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="14">
         <v>1010021955</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75">
+    <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="15">
         <v>1040077388</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.75">
+    <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="15">
         <v>1010058100</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75">
+    <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="15">
         <v>1010020524</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.75">
+    <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="15">
         <v>1010021958</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75">
+    <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="15">
         <v>1010019756</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75">
+    <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="15">
         <v>1010019752</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75">
+    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="15">
         <v>409639</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75">
+    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="15">
         <v>1010047089</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75">
+    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="15">
         <v>1040084107</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75">
+    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="15">
         <v>1010085203</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75">
+    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="15">
         <v>424298</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75">
+    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="15">
         <v>421847</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75">
+    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="15">
         <v>431573</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75">
+    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="15">
         <v>1010021581</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75">
+    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="21">
         <v>412413</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75">
+    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="22">
         <v>1010022606</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75">
+    <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="23">
         <v>1010003527</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75">
+    <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="23">
         <v>1010055707</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75">
+    <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="18">
         <v>422027</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75">
+    <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="14">
         <v>1010011313</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.75">
+    <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="15">
         <v>27051</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75">
+    <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="15">
         <v>1010011304</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75">
+    <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="15">
         <v>35659</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.75">
+    <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="15">
         <v>1040077390</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75">
+    <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="15">
         <v>1010021542</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75">
+    <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="15">
         <v>1010021733</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75">
+    <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="15">
         <v>1010011379</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75">
+    <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="15">
         <v>1010003279</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.75">
+    <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="15">
         <v>1010011380</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75">
+    <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="15">
         <v>351197</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75">
+    <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="15">
         <v>1010011286</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75">
+    <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="15">
         <v>2479</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75">
+    <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="15">
         <v>1010011382</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.75">
+    <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="16">
         <v>1010055703</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.75">
+    <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="16">
         <v>4165</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75">
+    <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="15">
         <v>301626</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.75">
+    <row r="225" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="15">
         <v>429495</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.75">
+    <row r="226" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="15">
         <v>162998</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.75">
+    <row r="227" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="15">
         <v>432657</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.75">
+    <row r="228" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="15">
         <v>1010021929</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.75">
+    <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="15">
         <v>428065</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15.75">
+    <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="15">
         <v>1010003404</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.75">
+    <row r="231" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="15">
         <v>1010003322</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.75">
+    <row r="232" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="15">
         <v>17738</v>
       </c>
@@ -4729,8 +4729,9 @@
       <c r="C232" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" ht="15.75">
+      <c r="F232" s="29"/>
+    </row>
+    <row r="233" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="15">
         <v>1010085360</v>
       </c>
@@ -4741,7 +4742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.75">
+    <row r="234" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="15">
         <v>1040077391</v>
       </c>
@@ -4752,7 +4753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.75">
+    <row r="235" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="15">
         <v>1010058624</v>
       </c>
@@ -4763,7 +4764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.75">
+    <row r="236" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="15">
         <v>1010024661</v>
       </c>
@@ -4774,7 +4775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.75">
+    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="15">
         <v>1040019315</v>
       </c>
@@ -4785,5793 +4786,5793 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15.75">
+    <row r="238" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="15">
         <v>1010021089</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>240</v>
+        <v>514</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15.75">
+    <row r="239" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="15">
         <v>1040017264</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15.75">
+    <row r="240" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="15">
         <v>1010051765</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.75">
+    <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="15">
         <v>1010035272</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.75">
+    <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="15">
         <v>1040077392</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15.75">
+    <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="15">
         <v>1040077393</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15.75">
+    <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="15">
         <v>1040077395</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15.75">
+    <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="15">
         <v>1040077401</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15.75">
+    <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="15">
         <v>27572</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15.75">
+    <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="15">
         <v>18745</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15.75">
+    <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="15">
         <v>1040077396</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15.75">
+    <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="15">
         <v>1010036546</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="15.75">
+    <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="15">
         <v>1010014049</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="15.75">
+    <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="15">
         <v>1010025148</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="15.75">
+    <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="15">
         <v>1040077394</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="15.75">
+    <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="15">
         <v>1040077400</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="15.75">
+    <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="15">
         <v>1040079329</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="15.75">
+    <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="15">
         <v>1040040957</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="15.75">
+    <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="15">
         <v>1040077398</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="15.75">
+    <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="15">
         <v>1010053128</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="15.75">
+    <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="15">
         <v>1010010599</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="15.75">
+    <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="15">
         <v>1010056064</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="15.75">
+    <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="15">
         <v>5389</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="15.75">
+    <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="15">
         <v>1010055969</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="15.75">
+    <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="15">
         <v>1010055970</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15.75">
+    <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="15">
         <v>181395</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="15.75">
+    <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="17">
         <v>1010055962</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="15.75">
+    <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="15">
         <v>1010003578</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15.75">
+    <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="15">
         <v>332891</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="15.75">
+    <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="15">
         <v>17727</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="15.75">
+    <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="15">
         <v>17918</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="15.75">
+    <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="15">
         <v>1010020554</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="15.75">
+    <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="15">
         <v>1040085949</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="15.75">
+    <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="15">
         <v>1010062938</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="15.75">
+    <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="15">
         <v>1010062086</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="15.75">
+    <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="15">
         <v>1010062087</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="15.75">
+    <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="15">
         <v>1040077373</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="15.75">
+    <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="24">
         <v>1040077372</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="15.75">
+    <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="24">
         <v>1040097154</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="15.75">
+    <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="24">
         <v>1010042579</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="15.75">
+    <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="15">
         <v>1010029427</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="15.75">
+    <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="15">
         <v>133108</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="15.75">
+    <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" s="15">
         <v>269427</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="15.75">
+    <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="15">
         <v>298227</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C281" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="15.75">
+    <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="15">
         <v>1010062285</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="15.75">
+    <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" s="15">
         <v>1010058052</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="15.75">
+    <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="15">
         <v>1010050033</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="15.75">
+    <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="20">
         <v>1040098869</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="15.75">
+    <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="20">
         <v>1010056523</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="15.75">
+    <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="20">
         <v>1010062045</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="15.75">
+    <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="15">
         <v>1040097575</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="15.75">
+    <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="5">
         <v>1040100107</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="15.75">
+    <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="15">
         <v>1010040346</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="15.75">
+    <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="15">
         <v>1010021543</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="15.75">
+    <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="15">
         <v>1040077397</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="15.75">
+    <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="15">
         <v>1040094213</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="15.75">
+    <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="15">
         <v>1010085326</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="15.75">
+    <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="15">
         <v>1010042564</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="15.75">
+    <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="15">
         <v>1010042688</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="15.75">
+    <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" s="15">
         <v>1010040133</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="15.75">
+    <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="15">
         <v>1010039879</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="15.75">
+    <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="15">
         <v>62608</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="15.75">
+    <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="15">
         <v>1040098603</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="15.75">
+    <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="15">
         <v>1040017266</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="15.75">
+    <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="15">
         <v>1010063326</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="15.75">
+    <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="15">
         <v>1010050574</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="15.75">
+    <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="20">
         <v>1010086126</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="15.75">
+    <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="15">
         <v>1040019838</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="15.75">
+    <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="15">
         <v>1010042882</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="15.75">
+    <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="15">
         <v>1010042873</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="15.75">
+    <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="15">
         <v>1010026842</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="15.75">
+    <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="15">
         <v>1010026841</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="15.75">
+    <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="15">
         <v>1010059549</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="15.75">
+    <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="15">
         <v>1010020552</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="15.75">
+    <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="15">
         <v>1040078895</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="15.75">
+    <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="15">
         <v>1040024309</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="15.75">
+    <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="15">
         <v>1040024323</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.75">
+    <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" s="15">
         <v>1040024322</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="15.75">
+    <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" s="15">
         <v>1010087245</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="15.75">
+    <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" s="15">
         <v>1010059685</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.75">
+    <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="15">
         <v>1010059687</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="15.75">
+    <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="15">
         <v>1010077469</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="15.75">
+    <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="19">
         <v>1010077470</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="15.75">
+    <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="15">
         <v>1010084519</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="15.75">
+    <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="14">
         <v>1010084108</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="15.75">
+    <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="14">
         <v>1010042884</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="15.75">
+    <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="15">
         <v>1040043537</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="15.75">
+    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="15">
         <v>1010046401</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15.75">
+    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="15">
         <v>1010062007</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15.75">
+    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="15">
         <v>1010051284</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="15.75">
+    <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="15">
         <v>1010027788</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="15.75">
+    <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="15">
         <v>1010027786</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="15.75">
+    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="15">
         <v>1010026889</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="15.75">
+    <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="24">
         <v>1010042358</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="15.75">
+    <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="15">
         <v>1040023848</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="15.75">
+    <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="15">
         <v>1010042341</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="15.75">
+    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="15">
         <v>1040023858</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="15.75">
+    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="15">
         <v>1040098396</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.75">
+    <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="15">
         <v>1010087281</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="15.75">
+    <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="15">
         <v>1040041006</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="15.75">
+    <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="15">
         <v>1040101931</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="15.75">
+    <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="15">
         <v>1040023843</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="15.75">
+    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="15">
         <v>1040077411</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="15.75">
+    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="15">
         <v>1040077410</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="15.75">
+    <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="15">
         <v>1010062008</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="15.75">
+    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="19">
         <v>1040040960</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="15.75">
+    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="15">
         <v>1010031536</v>
       </c>
       <c r="B344" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="15.75">
+    <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="15">
         <v>1010031545</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="15.75">
+    <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="30">
         <v>1010084767</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="15.75">
+    <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="15">
         <v>1040077360</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="15.75">
+    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="15">
         <v>1010064470</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="15.75">
+    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="15">
         <v>1010021991</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="15.75">
+    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="15">
         <v>1010021960</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="15.75">
+    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="15">
         <v>1010031690</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="15.75">
+    <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="15">
         <v>1010022590</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.75">
+    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="15">
         <v>1040098643</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.75">
+    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="15">
         <v>1010086020</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="15.75">
+    <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="15">
         <v>1010046550</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="15.75">
+    <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="15">
         <v>1010046402</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75">
+    <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="15">
         <v>1010060291</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="15.75">
+    <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="15">
         <v>1010050920</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="15.75">
+    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="15">
         <v>1040077412</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="15.75">
+    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="15">
         <v>1010042609</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="15.75">
+    <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="15">
         <v>417701</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="15.75">
+    <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="15">
         <v>399384</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="15.75">
+    <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="15">
         <v>1010024086</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="15.75">
+    <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="15">
         <v>1040077345</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="15.75">
+    <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="15">
         <v>1010084315</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="15.75">
+    <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="15">
         <v>399253</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="15.75">
+    <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="15">
         <v>1010084317</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="15.75">
+    <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="25">
         <v>1010085369</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="15.75">
+    <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="15">
         <v>1010085370</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="15.75">
+    <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="15">
         <v>1010085204</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="15.75">
+    <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="15">
         <v>1010003966</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="15.75">
+    <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="15">
         <v>1010003967</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="15.75">
+    <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="15">
         <v>65219</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C373" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="15.75">
+    <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="15">
         <v>10168</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="15.75">
+    <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="15">
         <v>1010083792</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="15.75">
+    <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" s="15">
         <v>1040077414</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="15.75">
+    <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="15">
         <v>1010018482</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="15.75">
+    <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="15">
         <v>1010084320</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="15.75">
+    <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="15">
         <v>1010084532</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="15.75">
+    <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="15">
         <v>1010027285</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="15.75">
+    <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="15">
         <v>1040077413</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="15.75">
+    <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="15">
         <v>1010085376</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="15.75">
+    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" s="15">
         <v>1010022819</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C383" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="15.75">
+    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="15">
         <v>1010052853</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="15.75">
+    <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="15">
         <v>1010084377</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="15.75">
+    <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="26">
         <v>1010062826</v>
       </c>
       <c r="B386" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C386" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="C386" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" ht="15.75">
+    </row>
+    <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="15">
         <v>1010002592</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" ht="15.75">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="24">
         <v>1010001155</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" ht="15.75">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="15">
         <v>1010001062</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" ht="15.75">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="15">
         <v>1010084328</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="15.75">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="24">
         <v>1010044502</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="15.75">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="15">
         <v>1010053692</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" ht="15.75">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="15">
         <v>1010083992</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" ht="15.75">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="15">
         <v>1010008578</v>
       </c>
       <c r="B394" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="C394" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="C394" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" ht="15.75">
+    </row>
+    <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="15">
         <v>1010031694</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="15">
         <v>1010051997</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="15">
         <v>1010022601</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="15">
         <v>1010054278</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="15">
         <v>1010083462</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="15">
         <v>1010027772</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="15">
         <v>1010084144</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="19">
         <v>1010084958</v>
       </c>
       <c r="B402" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="403" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="19">
         <v>1010084720</v>
       </c>
       <c r="B403" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D403" s="29"/>
     </row>
-    <row r="404" spans="1:4" ht="15.75">
+    <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="18">
         <v>1010021956</v>
       </c>
       <c r="B404" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="18">
         <v>1010026464</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="14">
         <v>1010021957</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="15">
         <v>1010026462</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="15">
         <v>1010026551</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="15">
         <v>1010042554</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="15">
         <v>1010039904</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="15">
         <v>1010060205</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="15">
         <v>1010060206</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="15">
         <v>1010077431</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="15">
         <v>1010077503</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="415" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="15">
         <v>1010084187</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="15">
         <v>1010080958</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="15">
         <v>1010026032</v>
       </c>
       <c r="B417" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="15">
         <v>1010085384</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="15">
         <v>1010006347</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="15">
         <v>1010085179</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="15">
         <v>1010024158</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="15">
         <v>1010024131</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="15">
         <v>1010007160</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="15">
         <v>1010023642</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="15">
         <v>1010007193</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="15">
         <v>1010042637</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="15">
         <v>1040075323</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="15">
         <v>1040075324</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="27">
         <v>1040074827</v>
       </c>
       <c r="B429" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="27">
         <v>1040099488</v>
       </c>
       <c r="B430" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="27">
         <v>1040083312</v>
       </c>
       <c r="B431" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="27">
         <v>1040077661</v>
       </c>
       <c r="B432" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="27">
         <v>1010085180</v>
       </c>
       <c r="B433" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="14">
         <v>1040017489</v>
       </c>
       <c r="B434" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="14">
         <v>1010085181</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="15">
         <v>400175</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="15">
         <v>1040017505</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="15">
         <v>1040017503</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="15">
         <v>1010046445</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="15">
         <v>1010021033</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="15">
         <v>1010057142</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="15">
         <v>1010016356</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="15">
         <v>1010084363</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="15">
         <v>1010052021</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="15">
         <v>1040091721</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="15">
         <v>1010062022</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="15">
         <v>18336</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="15">
         <v>229205</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="15">
         <v>60671</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="15">
         <v>1010059726</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="15">
         <v>1010008144</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="15">
         <v>1010007244</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="15">
         <v>1010006827</v>
       </c>
       <c r="B453" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" s="15">
         <v>1040075426</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="15">
         <v>1040075427</v>
       </c>
       <c r="B455" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" s="15">
         <v>1010084313</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="15">
         <v>403459</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" s="15">
         <v>1010044828</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="15">
         <v>1010026973</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" s="15">
         <v>1040017204</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" ht="15.75">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" s="24">
         <v>1010022119</v>
       </c>
       <c r="B461" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C461" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="C461" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" ht="15.75">
+    </row>
+    <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="15">
         <v>1010058709</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="15">
         <v>1010025711</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="15">
         <v>1010059684</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="15">
         <v>427341</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="15">
         <v>392696</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" s="15">
         <v>1010085279</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="19">
         <v>1010022588</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="15">
         <v>1010026864</v>
       </c>
       <c r="B469" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="14">
         <v>1010030946</v>
       </c>
       <c r="B470" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="14">
         <v>1010022589</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="15">
         <v>1040090143</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="15">
         <v>1040090138</v>
       </c>
       <c r="B473" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="15">
         <v>1030001314</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="15">
         <v>1010052319</v>
       </c>
       <c r="B475" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="15">
         <v>1010052320</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="15">
         <v>1030000370</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" s="15">
         <v>1030000366</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" s="15">
         <v>1030000368</v>
       </c>
       <c r="B479" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" s="15">
         <v>1030000369</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="15">
         <v>1030000489</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="15">
         <v>1030000490</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" s="15">
         <v>1030000821</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" s="15">
         <v>1030000511</v>
       </c>
       <c r="B484" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="16">
         <v>1010084279</v>
       </c>
       <c r="B485" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="16">
         <v>1010004281</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="15">
         <v>1010022118</v>
       </c>
       <c r="B487" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" ht="15.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="15">
         <v>1010028657</v>
       </c>
       <c r="B488" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="C488" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="C488" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" ht="15.75">
+    </row>
+    <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="18">
         <v>1010028655</v>
       </c>
       <c r="B489" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="18">
         <v>145165</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="15">
         <v>51666</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="18">
         <v>1010080930</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" s="15">
         <v>161055</v>
       </c>
       <c r="B493" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="15">
         <v>1010050517</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="15">
         <v>1010084190</v>
       </c>
       <c r="B495" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" s="15">
         <v>1010084195</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" s="15">
         <v>1010001400</v>
       </c>
       <c r="B497" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" s="17">
         <v>1010008416</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="28">
         <v>1010018372</v>
       </c>
       <c r="B499" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" s="28">
         <v>1010018361</v>
       </c>
       <c r="B500" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="16">
         <v>1010055398</v>
       </c>
       <c r="B501" s="11" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C501" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" s="15">
         <v>422131</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" s="15">
         <v>1010084370</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" s="15">
         <v>422759</v>
       </c>
       <c r="B504" s="5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" s="15">
         <v>120955</v>
       </c>
       <c r="B505" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C505" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" s="15">
         <v>1010000896</v>
       </c>
       <c r="B506" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C506" s="13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" s="15">
         <v>1010084308</v>
       </c>
       <c r="B507" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C507" s="13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" s="15">
         <v>1010084035</v>
       </c>
       <c r="B508" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C508" s="13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" ht="15.75">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
     </row>
-    <row r="510" spans="1:3" ht="15.75">
+    <row r="510" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
     </row>
-    <row r="511" spans="1:3" ht="15.75">
+    <row r="511" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
     </row>
-    <row r="512" spans="1:3" ht="15.75">
+    <row r="512" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
     </row>
-    <row r="513" spans="1:2" ht="15.75">
+    <row r="513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
     </row>
-    <row r="514" spans="1:2" ht="15.75">
+    <row r="514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
     </row>
-    <row r="515" spans="1:2" ht="15.75">
+    <row r="515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
     </row>
-    <row r="516" spans="1:2" ht="15.75">
+    <row r="516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
     </row>
-    <row r="517" spans="1:2" ht="15.75">
+    <row r="517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
     </row>
-    <row r="518" spans="1:2" ht="15.75">
+    <row r="518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
     </row>
-    <row r="519" spans="1:2" ht="15.75">
+    <row r="519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
     </row>
-    <row r="520" spans="1:2" ht="15.75">
+    <row r="520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
     </row>
-    <row r="521" spans="1:2" ht="15.75">
+    <row r="521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
     </row>
-    <row r="522" spans="1:2" ht="15.75">
+    <row r="522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="1:2" ht="15.75">
+    <row r="523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
     </row>
-    <row r="524" spans="1:2" ht="15.75">
+    <row r="524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
     </row>
-    <row r="525" spans="1:2" ht="15.75">
+    <row r="525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
     </row>
-    <row r="526" spans="1:2" ht="15.75">
+    <row r="526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
     </row>
-    <row r="527" spans="1:2" ht="15.75">
+    <row r="527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
     </row>
-    <row r="528" spans="1:2" ht="15.75">
+    <row r="528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
     </row>
-    <row r="529" spans="1:2" ht="15.75">
+    <row r="529" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
     </row>
-    <row r="530" spans="1:2" ht="15.75">
+    <row r="530" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
     </row>
-    <row r="531" spans="1:2" ht="15.75">
+    <row r="531" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
     </row>
-    <row r="532" spans="1:2" ht="15.75">
+    <row r="532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
     </row>
-    <row r="533" spans="1:2" ht="15.75">
+    <row r="533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
     </row>
-    <row r="534" spans="1:2" ht="15.75">
+    <row r="534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
     </row>
-    <row r="535" spans="1:2" ht="15.75">
+    <row r="535" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
     </row>
-    <row r="536" spans="1:2" ht="15.75">
+    <row r="536" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
     </row>
-    <row r="537" spans="1:2" ht="15.75">
+    <row r="537" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
     </row>
-    <row r="538" spans="1:2" ht="15.75">
+    <row r="538" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
     </row>
-    <row r="539" spans="1:2" ht="15.75">
+    <row r="539" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
     </row>
-    <row r="540" spans="1:2" ht="15.75">
+    <row r="540" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
     </row>
-    <row r="541" spans="1:2" ht="15.75">
+    <row r="541" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
     </row>
-    <row r="542" spans="1:2" ht="15.75">
+    <row r="542" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
     </row>
-    <row r="543" spans="1:2" ht="15.75">
+    <row r="543" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
     </row>
-    <row r="544" spans="1:2" ht="15.75">
+    <row r="544" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
     </row>
-    <row r="545" spans="1:2" ht="15.75">
+    <row r="545" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
     </row>
-    <row r="546" spans="1:2" ht="15.75">
+    <row r="546" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
     </row>
-    <row r="547" spans="1:2" ht="15.75">
+    <row r="547" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
     </row>
-    <row r="548" spans="1:2" ht="15.75">
+    <row r="548" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
     </row>
-    <row r="549" spans="1:2" ht="15.75">
+    <row r="549" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
     </row>
-    <row r="550" spans="1:2" ht="15.75">
+    <row r="550" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
     </row>
-    <row r="551" spans="1:2" ht="15.75">
+    <row r="551" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
     </row>
-    <row r="552" spans="1:2" ht="15.75">
+    <row r="552" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
     </row>
-    <row r="553" spans="1:2" ht="15.75">
+    <row r="553" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
     </row>
-    <row r="554" spans="1:2" ht="15.75">
+    <row r="554" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
     </row>
-    <row r="555" spans="1:2" ht="15.75">
+    <row r="555" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
     </row>
-    <row r="556" spans="1:2" ht="15.75">
+    <row r="556" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
     </row>
-    <row r="557" spans="1:2" ht="15.75">
+    <row r="557" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
     </row>
-    <row r="558" spans="1:2" ht="15.75">
+    <row r="558" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
     </row>
-    <row r="559" spans="1:2" ht="15.75">
+    <row r="559" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
     </row>
-    <row r="560" spans="1:2" ht="15.75">
+    <row r="560" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
     </row>
-    <row r="561" spans="1:2" ht="15.75">
+    <row r="561" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
     </row>
-    <row r="562" spans="1:2" ht="15.75">
+    <row r="562" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
     </row>
-    <row r="563" spans="1:2" ht="15.75">
+    <row r="563" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
     </row>
-    <row r="564" spans="1:2" ht="15.75">
+    <row r="564" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
     </row>
-    <row r="565" spans="1:2" ht="15.75">
+    <row r="565" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
     </row>
-    <row r="566" spans="1:2" ht="15.75">
+    <row r="566" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
     </row>
-    <row r="567" spans="1:2" ht="15.75">
+    <row r="567" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
     </row>
-    <row r="568" spans="1:2" ht="15.75">
+    <row r="568" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
     </row>
-    <row r="569" spans="1:2" ht="15.75">
+    <row r="569" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
     </row>
-    <row r="570" spans="1:2" ht="15.75">
+    <row r="570" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
     </row>
-    <row r="571" spans="1:2" ht="15.75">
+    <row r="571" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
     </row>
-    <row r="572" spans="1:2" ht="15.75">
+    <row r="572" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
     </row>
-    <row r="573" spans="1:2" ht="15.75">
+    <row r="573" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
     </row>
-    <row r="574" spans="1:2" ht="15.75">
+    <row r="574" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
     </row>
-    <row r="575" spans="1:2" ht="15.75">
+    <row r="575" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
     </row>
-    <row r="576" spans="1:2" ht="15.75">
+    <row r="576" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
     </row>
-    <row r="577" spans="1:2" ht="15.75">
+    <row r="577" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
     </row>
-    <row r="578" spans="1:2" ht="15.75">
+    <row r="578" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
     </row>
-    <row r="579" spans="1:2" ht="15.75">
+    <row r="579" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
     </row>
-    <row r="580" spans="1:2" ht="15.75">
+    <row r="580" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
     </row>
-    <row r="581" spans="1:2" ht="15.75">
+    <row r="581" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
     </row>
-    <row r="582" spans="1:2" ht="15.75">
+    <row r="582" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
     </row>
-    <row r="583" spans="1:2" ht="15.75">
+    <row r="583" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
     </row>
-    <row r="584" spans="1:2" ht="15.75">
+    <row r="584" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
     </row>
-    <row r="585" spans="1:2" ht="15.75">
+    <row r="585" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
     </row>
-    <row r="586" spans="1:2" ht="15.75">
+    <row r="586" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
     </row>
-    <row r="587" spans="1:2" ht="15.75">
+    <row r="587" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
     </row>
-    <row r="588" spans="1:2" ht="15.75">
+    <row r="588" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
     </row>
-    <row r="589" spans="1:2" ht="15.75">
+    <row r="589" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
     </row>
-    <row r="590" spans="1:2" ht="15.75">
+    <row r="590" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
     </row>
-    <row r="591" spans="1:2" ht="15.75">
+    <row r="591" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
     </row>
-    <row r="592" spans="1:2" ht="15.75">
+    <row r="592" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
     </row>
-    <row r="593" spans="1:2" ht="15.75">
+    <row r="593" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
     </row>
-    <row r="594" spans="1:2" ht="15.75">
+    <row r="594" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
     </row>
-    <row r="595" spans="1:2" ht="15.75">
+    <row r="595" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
     </row>
-    <row r="596" spans="1:2" ht="15.75">
+    <row r="596" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
     </row>
-    <row r="597" spans="1:2" ht="15.75">
+    <row r="597" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
     </row>
-    <row r="598" spans="1:2" ht="15.75">
+    <row r="598" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
     </row>
-    <row r="599" spans="1:2" ht="15.75">
+    <row r="599" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
     </row>
-    <row r="600" spans="1:2" ht="15.75">
+    <row r="600" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
     </row>
-    <row r="601" spans="1:2" ht="15.75">
+    <row r="601" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
     </row>
-    <row r="602" spans="1:2" ht="15.75">
+    <row r="602" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
     </row>
-    <row r="603" spans="1:2" ht="15.75">
+    <row r="603" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
     </row>
-    <row r="604" spans="1:2" ht="15.75">
+    <row r="604" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
     </row>
-    <row r="605" spans="1:2" ht="15.75">
+    <row r="605" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
     </row>
-    <row r="606" spans="1:2" ht="15.75">
+    <row r="606" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
     </row>
-    <row r="607" spans="1:2" ht="15.75">
+    <row r="607" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
     </row>
-    <row r="608" spans="1:2" ht="15.75">
+    <row r="608" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
     </row>
-    <row r="609" spans="1:2" ht="15.75">
+    <row r="609" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
     </row>
-    <row r="610" spans="1:2" ht="15.75">
+    <row r="610" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
     </row>
-    <row r="611" spans="1:2" ht="15.75">
+    <row r="611" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
     </row>
-    <row r="612" spans="1:2" ht="15.75">
+    <row r="612" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
     </row>
-    <row r="613" spans="1:2" ht="15.75">
+    <row r="613" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
     </row>
-    <row r="614" spans="1:2" ht="15.75">
+    <row r="614" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
     </row>
-    <row r="615" spans="1:2" ht="15.75">
+    <row r="615" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
     </row>
-    <row r="616" spans="1:2" ht="15.75">
+    <row r="616" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
     </row>
-    <row r="617" spans="1:2" ht="15.75">
+    <row r="617" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
     </row>
-    <row r="618" spans="1:2" ht="15.75">
+    <row r="618" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
     </row>
-    <row r="619" spans="1:2" ht="15.75">
+    <row r="619" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
     </row>
-    <row r="620" spans="1:2" ht="15.75">
+    <row r="620" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
     </row>
-    <row r="621" spans="1:2" ht="15.75">
+    <row r="621" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
     </row>
-    <row r="622" spans="1:2" ht="15.75">
+    <row r="622" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
     </row>
-    <row r="623" spans="1:2" ht="15.75">
+    <row r="623" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
     </row>
-    <row r="624" spans="1:2" ht="15.75">
+    <row r="624" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
     </row>
-    <row r="625" spans="1:2" ht="15.75">
+    <row r="625" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
     </row>
-    <row r="626" spans="1:2" ht="15.75">
+    <row r="626" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
     </row>
-    <row r="627" spans="1:2" ht="15.75">
+    <row r="627" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="1:2" ht="15.75">
+    <row r="628" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
     </row>
-    <row r="629" spans="1:2" ht="15.75">
+    <row r="629" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
     </row>
-    <row r="630" spans="1:2" ht="15.75">
+    <row r="630" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
     </row>
-    <row r="631" spans="1:2" ht="15.75">
+    <row r="631" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
     </row>
-    <row r="632" spans="1:2" ht="15.75">
+    <row r="632" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
     </row>
-    <row r="633" spans="1:2" ht="15.75">
+    <row r="633" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
     </row>
-    <row r="634" spans="1:2" ht="15.75">
+    <row r="634" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
     </row>
-    <row r="635" spans="1:2" ht="15.75">
+    <row r="635" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
     </row>
-    <row r="636" spans="1:2" ht="15.75">
+    <row r="636" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
     </row>
-    <row r="637" spans="1:2" ht="15.75">
+    <row r="637" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
     </row>
-    <row r="638" spans="1:2" ht="15.75">
+    <row r="638" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
     </row>
-    <row r="639" spans="1:2" ht="15.75">
+    <row r="639" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
     </row>
-    <row r="640" spans="1:2" ht="15.75">
+    <row r="640" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
     </row>
-    <row r="641" spans="1:2" ht="15.75">
+    <row r="641" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
     </row>
-    <row r="642" spans="1:2" ht="15.75">
+    <row r="642" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
     </row>
-    <row r="643" spans="1:2" ht="15.75">
+    <row r="643" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
     </row>
-    <row r="644" spans="1:2" ht="15.75">
+    <row r="644" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
     </row>
-    <row r="645" spans="1:2" ht="15.75">
+    <row r="645" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
     </row>
-    <row r="646" spans="1:2" ht="15.75">
+    <row r="646" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
     </row>
-    <row r="647" spans="1:2" ht="15.75">
+    <row r="647" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
     </row>
-    <row r="648" spans="1:2" ht="15.75">
+    <row r="648" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
     </row>
-    <row r="649" spans="1:2" ht="15.75">
+    <row r="649" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
     </row>
-    <row r="650" spans="1:2" ht="15.75">
+    <row r="650" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
     </row>
-    <row r="651" spans="1:2" ht="15.75">
+    <row r="651" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
     </row>
-    <row r="652" spans="1:2" ht="15.75">
+    <row r="652" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
     </row>
-    <row r="653" spans="1:2" ht="15.75">
+    <row r="653" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
     </row>
-    <row r="654" spans="1:2" ht="15.75">
+    <row r="654" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
     </row>
-    <row r="655" spans="1:2" ht="15.75">
+    <row r="655" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
     </row>
-    <row r="656" spans="1:2" ht="15.75">
+    <row r="656" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
     </row>
-    <row r="657" spans="1:2" ht="15.75">
+    <row r="657" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
     </row>
-    <row r="658" spans="1:2" ht="15.75">
+    <row r="658" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
     </row>
-    <row r="659" spans="1:2" ht="15.75">
+    <row r="659" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
     </row>
-    <row r="660" spans="1:2" ht="15.75">
+    <row r="660" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
     </row>
-    <row r="661" spans="1:2" ht="15.75">
+    <row r="661" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
     </row>
-    <row r="662" spans="1:2" ht="15.75">
+    <row r="662" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
     </row>
-    <row r="663" spans="1:2" ht="15.75">
+    <row r="663" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
     </row>
-    <row r="664" spans="1:2" ht="15.75">
+    <row r="664" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
     </row>
-    <row r="665" spans="1:2" ht="15.75">
+    <row r="665" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
     </row>
-    <row r="666" spans="1:2" ht="15.75">
+    <row r="666" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
     </row>
-    <row r="667" spans="1:2" ht="15.75">
+    <row r="667" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
     </row>
-    <row r="668" spans="1:2" ht="15.75">
+    <row r="668" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
     </row>
-    <row r="669" spans="1:2" ht="15.75">
+    <row r="669" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
     </row>
-    <row r="670" spans="1:2" ht="15.75">
+    <row r="670" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
     </row>
-    <row r="671" spans="1:2" ht="15.75">
+    <row r="671" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
     </row>
-    <row r="672" spans="1:2" ht="15.75">
+    <row r="672" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
     </row>
-    <row r="673" spans="1:2" ht="15.75">
+    <row r="673" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
     </row>
-    <row r="674" spans="1:2" ht="15.75">
+    <row r="674" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
     </row>
-    <row r="675" spans="1:2" ht="15.75">
+    <row r="675" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
     </row>
-    <row r="676" spans="1:2" ht="15.75">
+    <row r="676" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
     </row>
-    <row r="677" spans="1:2" ht="15.75">
+    <row r="677" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
     </row>
-    <row r="678" spans="1:2" ht="15.75">
+    <row r="678" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
     </row>
-    <row r="679" spans="1:2" ht="15.75">
+    <row r="679" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
     </row>
-    <row r="680" spans="1:2" ht="15.75">
+    <row r="680" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
     </row>
-    <row r="681" spans="1:2" ht="15.75">
+    <row r="681" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
     </row>
-    <row r="682" spans="1:2" ht="15.75">
+    <row r="682" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
     </row>
-    <row r="683" spans="1:2" ht="15.75">
+    <row r="683" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
     </row>
-    <row r="684" spans="1:2" ht="15.75">
+    <row r="684" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
     </row>
-    <row r="685" spans="1:2" ht="15.75">
+    <row r="685" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
     </row>
-    <row r="686" spans="1:2" ht="15.75">
+    <row r="686" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
     </row>
-    <row r="687" spans="1:2" ht="15.75">
+    <row r="687" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
     </row>
-    <row r="688" spans="1:2" ht="15.75">
+    <row r="688" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
     </row>
-    <row r="689" spans="1:2" ht="15.75">
+    <row r="689" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
     </row>
-    <row r="690" spans="1:2" ht="15.75">
+    <row r="690" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
     </row>
-    <row r="691" spans="1:2" ht="15.75">
+    <row r="691" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
     </row>
-    <row r="692" spans="1:2" ht="15.75">
+    <row r="692" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
     </row>
-    <row r="693" spans="1:2" ht="15.75">
+    <row r="693" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
     </row>
-    <row r="694" spans="1:2" ht="15.75">
+    <row r="694" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
     </row>
-    <row r="695" spans="1:2" ht="15.75">
+    <row r="695" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
     </row>
-    <row r="696" spans="1:2" ht="15.75">
+    <row r="696" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
     </row>
-    <row r="697" spans="1:2" ht="15.75">
+    <row r="697" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
     </row>
-    <row r="698" spans="1:2" ht="15.75">
+    <row r="698" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
     </row>
-    <row r="699" spans="1:2" ht="15.75">
+    <row r="699" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
     </row>
-    <row r="700" spans="1:2" ht="15.75">
+    <row r="700" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
     </row>
-    <row r="701" spans="1:2" ht="15.75">
+    <row r="701" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
     </row>
-    <row r="702" spans="1:2" ht="15.75">
+    <row r="702" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
     </row>
-    <row r="703" spans="1:2" ht="15.75">
+    <row r="703" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
     </row>
-    <row r="704" spans="1:2" ht="15.75">
+    <row r="704" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
     </row>
-    <row r="705" spans="1:2" ht="15.75">
+    <row r="705" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
     </row>
-    <row r="706" spans="1:2" ht="15.75">
+    <row r="706" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
     </row>
-    <row r="707" spans="1:2" ht="15.75">
+    <row r="707" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
     </row>
-    <row r="708" spans="1:2" ht="15.75">
+    <row r="708" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
     </row>
-    <row r="709" spans="1:2" ht="15.75">
+    <row r="709" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
     </row>
-    <row r="710" spans="1:2" ht="15.75">
+    <row r="710" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
     </row>
-    <row r="711" spans="1:2" ht="15.75">
+    <row r="711" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
     </row>
-    <row r="712" spans="1:2" ht="15.75">
+    <row r="712" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
     </row>
-    <row r="713" spans="1:2" ht="15.75">
+    <row r="713" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
     </row>
-    <row r="714" spans="1:2" ht="15.75">
+    <row r="714" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
     </row>
-    <row r="715" spans="1:2" ht="15.75">
+    <row r="715" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
     </row>
-    <row r="716" spans="1:2" ht="15.75">
+    <row r="716" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
     </row>
-    <row r="717" spans="1:2" ht="15.75">
+    <row r="717" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
     </row>
-    <row r="718" spans="1:2" ht="15.75">
+    <row r="718" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
     </row>
-    <row r="719" spans="1:2" ht="15.75">
+    <row r="719" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
     </row>
-    <row r="720" spans="1:2" ht="15.75">
+    <row r="720" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
     </row>
-    <row r="721" spans="1:2" ht="15.75">
+    <row r="721" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
     </row>
-    <row r="722" spans="1:2" ht="15.75">
+    <row r="722" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
     </row>
-    <row r="723" spans="1:2" ht="15.75">
+    <row r="723" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
     </row>
-    <row r="724" spans="1:2" ht="15.75">
+    <row r="724" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
     </row>
-    <row r="725" spans="1:2" ht="15.75">
+    <row r="725" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
     </row>
-    <row r="726" spans="1:2" ht="15.75">
+    <row r="726" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
     </row>
-    <row r="727" spans="1:2" ht="15.75">
+    <row r="727" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
     </row>
-    <row r="728" spans="1:2" ht="15.75">
+    <row r="728" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
     </row>
-    <row r="729" spans="1:2" ht="15.75">
+    <row r="729" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
     </row>
-    <row r="730" spans="1:2" ht="15.75">
+    <row r="730" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
     </row>
-    <row r="731" spans="1:2" ht="15.75">
+    <row r="731" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
     </row>
-    <row r="732" spans="1:2" ht="15.75">
+    <row r="732" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
     </row>
-    <row r="733" spans="1:2" ht="15.75">
+    <row r="733" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
     </row>
-    <row r="734" spans="1:2" ht="15.75">
+    <row r="734" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
     </row>
-    <row r="735" spans="1:2" ht="15.75">
+    <row r="735" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
     </row>
-    <row r="736" spans="1:2" ht="15.75">
+    <row r="736" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
     </row>
-    <row r="737" spans="1:2" ht="15.75">
+    <row r="737" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
     </row>
-    <row r="738" spans="1:2" ht="15.75">
+    <row r="738" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
     </row>
-    <row r="739" spans="1:2" ht="15.75">
+    <row r="739" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
     </row>
-    <row r="740" spans="1:2" ht="15.75">
+    <row r="740" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
     </row>
-    <row r="741" spans="1:2" ht="15.75">
+    <row r="741" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
     </row>
-    <row r="742" spans="1:2" ht="15.75">
+    <row r="742" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
     </row>
-    <row r="743" spans="1:2" ht="15.75">
+    <row r="743" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
     </row>
-    <row r="744" spans="1:2" ht="15.75">
+    <row r="744" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
     </row>
-    <row r="745" spans="1:2" ht="15.75">
+    <row r="745" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
     </row>
-    <row r="746" spans="1:2" ht="15.75">
+    <row r="746" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
     </row>
-    <row r="747" spans="1:2" ht="15.75">
+    <row r="747" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
     </row>
-    <row r="748" spans="1:2" ht="15.75">
+    <row r="748" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
     </row>
-    <row r="749" spans="1:2" ht="15.75">
+    <row r="749" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
     </row>
-    <row r="750" spans="1:2" ht="15.75">
+    <row r="750" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
     </row>
-    <row r="751" spans="1:2" ht="15.75">
+    <row r="751" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
     </row>
-    <row r="752" spans="1:2" ht="15.75">
+    <row r="752" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
     </row>
-    <row r="753" spans="1:2" ht="15.75">
+    <row r="753" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
     </row>
-    <row r="754" spans="1:2" ht="15.75">
+    <row r="754" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
     </row>
-    <row r="755" spans="1:2" ht="15.75">
+    <row r="755" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
     </row>
-    <row r="756" spans="1:2" ht="15.75">
+    <row r="756" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
     </row>
-    <row r="757" spans="1:2" ht="15.75">
+    <row r="757" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
     </row>
-    <row r="758" spans="1:2" ht="15.75">
+    <row r="758" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
     </row>
-    <row r="759" spans="1:2" ht="15.75">
+    <row r="759" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
     </row>
-    <row r="760" spans="1:2" ht="15.75">
+    <row r="760" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
     </row>
-    <row r="761" spans="1:2" ht="15.75">
+    <row r="761" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
     </row>
-    <row r="762" spans="1:2" ht="15.75">
+    <row r="762" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
     </row>
-    <row r="763" spans="1:2" ht="15.75">
+    <row r="763" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
     </row>
-    <row r="764" spans="1:2" ht="15.75">
+    <row r="764" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
     </row>
-    <row r="765" spans="1:2" ht="15.75">
+    <row r="765" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
     </row>
-    <row r="766" spans="1:2" ht="15.75">
+    <row r="766" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
     </row>
-    <row r="767" spans="1:2" ht="15.75">
+    <row r="767" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
     </row>
-    <row r="768" spans="1:2" ht="15.75">
+    <row r="768" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
     </row>
-    <row r="769" spans="1:2" ht="15.75">
+    <row r="769" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
     </row>
-    <row r="770" spans="1:2" ht="15.75">
+    <row r="770" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
     </row>
-    <row r="771" spans="1:2" ht="15.75">
+    <row r="771" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
     </row>
-    <row r="772" spans="1:2" ht="15.75">
+    <row r="772" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
     </row>
-    <row r="773" spans="1:2" ht="15.75">
+    <row r="773" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
     </row>
-    <row r="774" spans="1:2" ht="15.75">
+    <row r="774" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
     </row>
-    <row r="775" spans="1:2" ht="15.75">
+    <row r="775" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
     </row>
-    <row r="776" spans="1:2" ht="15.75">
+    <row r="776" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
     </row>
-    <row r="777" spans="1:2" ht="15.75">
+    <row r="777" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
     </row>
-    <row r="778" spans="1:2" ht="15.75">
+    <row r="778" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
     </row>
-    <row r="779" spans="1:2" ht="15.75">
+    <row r="779" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
     </row>
-    <row r="780" spans="1:2" ht="15.75">
+    <row r="780" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
     </row>
-    <row r="781" spans="1:2" ht="15.75">
+    <row r="781" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
     </row>
-    <row r="782" spans="1:2" ht="15.75">
+    <row r="782" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
     </row>
-    <row r="783" spans="1:2" ht="15.75">
+    <row r="783" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
     </row>
-    <row r="784" spans="1:2" ht="15.75">
+    <row r="784" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
     </row>
-    <row r="785" spans="1:2" ht="15.75">
+    <row r="785" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
     </row>
-    <row r="786" spans="1:2" ht="15.75">
+    <row r="786" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
     </row>
-    <row r="787" spans="1:2" ht="15.75">
+    <row r="787" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
     </row>
-    <row r="788" spans="1:2" ht="15.75">
+    <row r="788" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
     </row>
-    <row r="789" spans="1:2" ht="15.75">
+    <row r="789" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
     </row>
-    <row r="790" spans="1:2" ht="15.75">
+    <row r="790" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
     </row>
-    <row r="791" spans="1:2" ht="15.75">
+    <row r="791" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
     </row>
-    <row r="792" spans="1:2" ht="15.75">
+    <row r="792" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
     </row>
-    <row r="793" spans="1:2" ht="15.75">
+    <row r="793" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
     </row>
-    <row r="794" spans="1:2" ht="15.75">
+    <row r="794" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
     </row>
-    <row r="795" spans="1:2" ht="15.75">
+    <row r="795" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
     </row>
-    <row r="796" spans="1:2" ht="15.75">
+    <row r="796" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
     </row>
-    <row r="797" spans="1:2" ht="15.75">
+    <row r="797" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
     </row>
-    <row r="798" spans="1:2" ht="15.75">
+    <row r="798" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
     </row>
-    <row r="799" spans="1:2" ht="15.75">
+    <row r="799" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
     </row>
-    <row r="800" spans="1:2" ht="15.75">
+    <row r="800" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
     </row>
-    <row r="801" spans="1:2" ht="15.75">
+    <row r="801" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
     </row>
-    <row r="802" spans="1:2" ht="15.75">
+    <row r="802" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
     </row>
-    <row r="803" spans="1:2" ht="15.75">
+    <row r="803" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
     </row>
-    <row r="804" spans="1:2" ht="15.75">
+    <row r="804" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
     </row>
-    <row r="805" spans="1:2" ht="15.75">
+    <row r="805" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
     </row>
-    <row r="806" spans="1:2" ht="15.75">
+    <row r="806" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
     </row>
-    <row r="807" spans="1:2" ht="15.75">
+    <row r="807" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
     </row>
-    <row r="808" spans="1:2" ht="15.75">
+    <row r="808" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
     </row>
-    <row r="809" spans="1:2" ht="15.75">
+    <row r="809" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
     </row>
-    <row r="810" spans="1:2" ht="15.75">
+    <row r="810" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
     </row>
-    <row r="811" spans="1:2" ht="15.75">
+    <row r="811" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
     </row>
-    <row r="812" spans="1:2" ht="15.75">
+    <row r="812" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
     </row>
-    <row r="813" spans="1:2" ht="15.75">
+    <row r="813" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
     </row>
-    <row r="814" spans="1:2" ht="15.75">
+    <row r="814" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
     </row>
-    <row r="815" spans="1:2" ht="15.75">
+    <row r="815" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
     </row>
-    <row r="816" spans="1:2" ht="15.75">
+    <row r="816" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
     </row>
-    <row r="817" spans="1:2" ht="15.75">
+    <row r="817" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
     </row>
-    <row r="818" spans="1:2" ht="15.75">
+    <row r="818" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
     </row>
-    <row r="819" spans="1:2" ht="15.75">
+    <row r="819" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
     </row>
-    <row r="820" spans="1:2" ht="15.75">
+    <row r="820" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
     </row>
-    <row r="821" spans="1:2" ht="15.75">
+    <row r="821" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
     </row>
-    <row r="822" spans="1:2" ht="15.75">
+    <row r="822" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
     </row>
-    <row r="823" spans="1:2" ht="15.75">
+    <row r="823" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
     </row>
-    <row r="824" spans="1:2" ht="15.75">
+    <row r="824" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
     </row>
-    <row r="825" spans="1:2" ht="15.75">
+    <row r="825" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
     </row>
-    <row r="826" spans="1:2" ht="15.75">
+    <row r="826" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
     </row>
-    <row r="827" spans="1:2" ht="15.75">
+    <row r="827" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
     </row>
-    <row r="828" spans="1:2" ht="15.75">
+    <row r="828" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
     </row>
-    <row r="829" spans="1:2" ht="15.75">
+    <row r="829" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
     </row>
-    <row r="830" spans="1:2" ht="15.75">
+    <row r="830" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
     </row>
-    <row r="831" spans="1:2" ht="15.75">
+    <row r="831" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
     </row>
-    <row r="832" spans="1:2" ht="15.75">
+    <row r="832" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
     </row>
-    <row r="833" spans="1:2" ht="15.75">
+    <row r="833" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
     </row>
-    <row r="834" spans="1:2" ht="15.75">
+    <row r="834" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
     </row>
-    <row r="835" spans="1:2" ht="15.75">
+    <row r="835" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
     </row>
-    <row r="836" spans="1:2" ht="15.75">
+    <row r="836" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
     </row>
-    <row r="837" spans="1:2" ht="15.75">
+    <row r="837" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
     </row>
-    <row r="838" spans="1:2" ht="15.75">
+    <row r="838" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
     </row>
-    <row r="839" spans="1:2" ht="15.75">
+    <row r="839" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
     </row>
-    <row r="840" spans="1:2" ht="15.75">
+    <row r="840" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
     </row>
-    <row r="841" spans="1:2" ht="15.75">
+    <row r="841" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
     </row>
-    <row r="842" spans="1:2" ht="15.75">
+    <row r="842" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
     </row>
-    <row r="843" spans="1:2" ht="15.75">
+    <row r="843" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
     </row>
-    <row r="844" spans="1:2" ht="15.75">
+    <row r="844" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
     </row>
-    <row r="845" spans="1:2" ht="15.75">
+    <row r="845" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
     </row>
-    <row r="846" spans="1:2" ht="15.75">
+    <row r="846" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
     </row>
-    <row r="847" spans="1:2" ht="15.75">
+    <row r="847" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
     </row>
-    <row r="848" spans="1:2" ht="15.75">
+    <row r="848" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
     </row>
-    <row r="849" spans="1:2" ht="15.75">
+    <row r="849" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
     </row>
-    <row r="850" spans="1:2" ht="15.75">
+    <row r="850" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
     </row>
-    <row r="851" spans="1:2" ht="15.75">
+    <row r="851" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
     </row>
-    <row r="852" spans="1:2" ht="15.75">
+    <row r="852" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
     </row>
-    <row r="853" spans="1:2" ht="15.75">
+    <row r="853" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
     </row>
-    <row r="854" spans="1:2" ht="15.75">
+    <row r="854" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
     </row>
-    <row r="855" spans="1:2" ht="15.75">
+    <row r="855" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
     </row>
-    <row r="856" spans="1:2" ht="15.75">
+    <row r="856" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
     </row>
-    <row r="857" spans="1:2" ht="15.75">
+    <row r="857" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
     </row>
-    <row r="858" spans="1:2" ht="15.75">
+    <row r="858" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
     </row>
-    <row r="859" spans="1:2" ht="15.75">
+    <row r="859" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
     </row>
-    <row r="860" spans="1:2" ht="15.75">
+    <row r="860" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
     </row>
-    <row r="861" spans="1:2" ht="15.75">
+    <row r="861" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
     </row>
-    <row r="862" spans="1:2" ht="15.75">
+    <row r="862" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
     </row>
-    <row r="863" spans="1:2" ht="15.75">
+    <row r="863" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
     </row>
-    <row r="864" spans="1:2" ht="15.75">
+    <row r="864" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
     </row>
-    <row r="865" spans="1:2" ht="15.75">
+    <row r="865" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
     </row>
-    <row r="866" spans="1:2" ht="15.75">
+    <row r="866" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
     </row>
-    <row r="867" spans="1:2" ht="15.75">
+    <row r="867" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
     </row>
-    <row r="868" spans="1:2" ht="15.75">
+    <row r="868" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
     </row>
-    <row r="869" spans="1:2" ht="15.75">
+    <row r="869" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
     </row>
-    <row r="870" spans="1:2" ht="15.75">
+    <row r="870" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
     </row>
-    <row r="871" spans="1:2" ht="15.75">
+    <row r="871" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
     </row>
-    <row r="872" spans="1:2" ht="15.75">
+    <row r="872" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
     </row>
-    <row r="873" spans="1:2" ht="15.75">
+    <row r="873" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
     </row>
-    <row r="874" spans="1:2" ht="15.75">
+    <row r="874" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
     </row>
-    <row r="875" spans="1:2" ht="15.75">
+    <row r="875" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
     </row>
-    <row r="876" spans="1:2" ht="15.75">
+    <row r="876" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
     </row>
-    <row r="877" spans="1:2" ht="15.75">
+    <row r="877" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
     </row>
-    <row r="878" spans="1:2" ht="15.75">
+    <row r="878" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
     </row>
-    <row r="879" spans="1:2" ht="15.75">
+    <row r="879" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
     </row>
-    <row r="880" spans="1:2" ht="15.75">
+    <row r="880" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
     </row>
-    <row r="881" spans="1:2" ht="15.75">
+    <row r="881" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
     </row>
-    <row r="882" spans="1:2" ht="15.75">
+    <row r="882" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
     </row>
-    <row r="883" spans="1:2" ht="15.75">
+    <row r="883" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
     </row>
-    <row r="884" spans="1:2" ht="15.75">
+    <row r="884" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
     </row>
-    <row r="885" spans="1:2" ht="15.75">
+    <row r="885" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
     </row>
-    <row r="886" spans="1:2" ht="15.75">
+    <row r="886" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
     </row>
-    <row r="887" spans="1:2" ht="15.75">
+    <row r="887" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
     </row>
-    <row r="888" spans="1:2" ht="15.75">
+    <row r="888" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
     </row>
-    <row r="889" spans="1:2" ht="15.75">
+    <row r="889" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
     </row>
-    <row r="890" spans="1:2" ht="15.75">
+    <row r="890" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
     </row>
-    <row r="891" spans="1:2" ht="15.75">
+    <row r="891" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
     </row>
-    <row r="892" spans="1:2" ht="15.75">
+    <row r="892" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
     </row>
-    <row r="893" spans="1:2" ht="15.75">
+    <row r="893" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
     </row>
-    <row r="894" spans="1:2" ht="15.75">
+    <row r="894" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
     </row>
-    <row r="895" spans="1:2" ht="15.75">
+    <row r="895" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
     </row>
-    <row r="896" spans="1:2" ht="15.75">
+    <row r="896" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
     </row>
-    <row r="897" spans="1:2" ht="15.75">
+    <row r="897" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
     </row>
-    <row r="898" spans="1:2" ht="15.75">
+    <row r="898" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
     </row>
-    <row r="899" spans="1:2" ht="15.75">
+    <row r="899" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
     </row>
-    <row r="900" spans="1:2" ht="15.75">
+    <row r="900" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
     </row>
-    <row r="901" spans="1:2" ht="15.75">
+    <row r="901" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
     </row>
-    <row r="902" spans="1:2" ht="15.75">
+    <row r="902" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
     </row>
-    <row r="903" spans="1:2" ht="15.75">
+    <row r="903" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
     </row>
-    <row r="904" spans="1:2" ht="15.75">
+    <row r="904" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
     </row>
-    <row r="905" spans="1:2" ht="15.75">
+    <row r="905" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
     </row>
-    <row r="906" spans="1:2" ht="15.75">
+    <row r="906" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
     </row>
-    <row r="907" spans="1:2" ht="15.75">
+    <row r="907" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
     </row>
-    <row r="908" spans="1:2" ht="15.75">
+    <row r="908" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
     </row>
-    <row r="909" spans="1:2" ht="15.75">
+    <row r="909" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
     </row>
-    <row r="910" spans="1:2" ht="15.75">
+    <row r="910" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
     </row>
-    <row r="911" spans="1:2" ht="15.75">
+    <row r="911" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
     </row>
-    <row r="912" spans="1:2" ht="15.75">
+    <row r="912" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
     </row>
-    <row r="913" spans="1:2" ht="15.75">
+    <row r="913" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
     </row>
-    <row r="914" spans="1:2" ht="15.75">
+    <row r="914" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
     </row>
-    <row r="915" spans="1:2" ht="15.75">
+    <row r="915" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
     </row>
-    <row r="916" spans="1:2" ht="15.75">
+    <row r="916" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
     </row>
-    <row r="917" spans="1:2" ht="15.75">
+    <row r="917" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
     </row>
-    <row r="918" spans="1:2" ht="15.75">
+    <row r="918" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
     </row>
-    <row r="919" spans="1:2" ht="15.75">
+    <row r="919" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
     </row>
-    <row r="920" spans="1:2" ht="15.75">
+    <row r="920" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
     </row>
-    <row r="921" spans="1:2" ht="15.75">
+    <row r="921" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
     </row>
-    <row r="922" spans="1:2" ht="15.75">
+    <row r="922" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
     </row>
-    <row r="923" spans="1:2" ht="15.75">
+    <row r="923" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
     </row>
-    <row r="924" spans="1:2" ht="15.75">
+    <row r="924" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
     </row>
-    <row r="925" spans="1:2" ht="15.75">
+    <row r="925" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
     </row>
-    <row r="926" spans="1:2" ht="15.75">
+    <row r="926" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
     </row>
-    <row r="927" spans="1:2" ht="15.75">
+    <row r="927" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
     </row>
-    <row r="928" spans="1:2" ht="15.75">
+    <row r="928" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
     </row>
-    <row r="929" spans="1:2" ht="15.75">
+    <row r="929" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
     </row>
-    <row r="930" spans="1:2" ht="15.75">
+    <row r="930" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
     </row>
-    <row r="931" spans="1:2" ht="15.75">
+    <row r="931" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
     </row>
-    <row r="932" spans="1:2" ht="15.75">
+    <row r="932" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
     </row>
-    <row r="933" spans="1:2" ht="15.75">
+    <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
     </row>
-    <row r="934" spans="1:2" ht="15.75">
+    <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
     </row>
-    <row r="935" spans="1:2" ht="15.75">
+    <row r="935" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
     </row>
-    <row r="936" spans="1:2" ht="15.75">
+    <row r="936" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
     </row>
-    <row r="937" spans="1:2" ht="15.75">
+    <row r="937" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
     </row>
-    <row r="938" spans="1:2" ht="15.75">
+    <row r="938" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
     </row>
-    <row r="939" spans="1:2" ht="15.75">
+    <row r="939" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
     </row>
-    <row r="940" spans="1:2" ht="15.75">
+    <row r="940" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
     </row>
-    <row r="941" spans="1:2" ht="15.75">
+    <row r="941" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
     </row>
-    <row r="942" spans="1:2" ht="15.75">
+    <row r="942" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
     </row>
-    <row r="943" spans="1:2" ht="15.75">
+    <row r="943" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
     </row>
-    <row r="944" spans="1:2" ht="15.75">
+    <row r="944" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
     </row>
-    <row r="945" spans="1:2" ht="15.75">
+    <row r="945" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
     </row>
-    <row r="946" spans="1:2" ht="15.75">
+    <row r="946" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
     </row>
-    <row r="947" spans="1:2" ht="15.75">
+    <row r="947" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
     </row>
-    <row r="948" spans="1:2" ht="15.75">
+    <row r="948" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A948" s="2"/>
       <c r="B948" s="1"/>
     </row>
-    <row r="949" spans="1:2" ht="15.75">
+    <row r="949" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A949" s="2"/>
       <c r="B949" s="1"/>
     </row>
-    <row r="950" spans="1:2" ht="15.75">
+    <row r="950" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A950" s="2"/>
       <c r="B950" s="1"/>
     </row>
-    <row r="951" spans="1:2" ht="15.75">
+    <row r="951" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A951" s="2"/>
       <c r="B951" s="1"/>
     </row>
-    <row r="952" spans="1:2" ht="15.75">
+    <row r="952" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A952" s="2"/>
       <c r="B952" s="1"/>
     </row>
-    <row r="953" spans="1:2" ht="15.75">
+    <row r="953" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A953" s="2"/>
       <c r="B953" s="1"/>
     </row>
-    <row r="954" spans="1:2" ht="15.75">
+    <row r="954" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A954" s="2"/>
       <c r="B954" s="1"/>
     </row>
-    <row r="955" spans="1:2" ht="15.75">
+    <row r="955" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A955" s="2"/>
       <c r="B955" s="1"/>
     </row>
-    <row r="956" spans="1:2" ht="15.75">
+    <row r="956" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A956" s="2"/>
       <c r="B956" s="1"/>
     </row>
-    <row r="957" spans="1:2" ht="15.75">
+    <row r="957" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A957" s="2"/>
       <c r="B957" s="1"/>
     </row>
-    <row r="958" spans="1:2" ht="15.75">
+    <row r="958" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A958" s="2"/>
       <c r="B958" s="1"/>
     </row>
-    <row r="959" spans="1:2" ht="15.75">
+    <row r="959" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A959" s="2"/>
       <c r="B959" s="1"/>
     </row>
-    <row r="960" spans="1:2" ht="15.75">
+    <row r="960" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A960" s="2"/>
       <c r="B960" s="1"/>
     </row>
-    <row r="961" spans="1:2" ht="15.75">
+    <row r="961" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A961" s="2"/>
       <c r="B961" s="1"/>
     </row>
-    <row r="962" spans="1:2" ht="15.75">
+    <row r="962" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A962" s="2"/>
       <c r="B962" s="1"/>
     </row>
-    <row r="963" spans="1:2" ht="15.75">
+    <row r="963" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A963" s="2"/>
       <c r="B963" s="1"/>
     </row>
-    <row r="964" spans="1:2" ht="15.75">
+    <row r="964" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A964" s="2"/>
       <c r="B964" s="1"/>
     </row>
-    <row r="965" spans="1:2" ht="15.75">
+    <row r="965" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A965" s="2"/>
       <c r="B965" s="1"/>
     </row>
-    <row r="966" spans="1:2" ht="15.75">
+    <row r="966" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A966" s="2"/>
       <c r="B966" s="1"/>
     </row>
-    <row r="967" spans="1:2" ht="15.75">
+    <row r="967" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A967" s="2"/>
       <c r="B967" s="1"/>
     </row>
-    <row r="968" spans="1:2" ht="15.75">
+    <row r="968" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A968" s="2"/>
       <c r="B968" s="1"/>
     </row>
-    <row r="969" spans="1:2" ht="15.75">
+    <row r="969" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A969" s="2"/>
       <c r="B969" s="1"/>
     </row>
-    <row r="970" spans="1:2" ht="15.75">
+    <row r="970" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A970" s="2"/>
       <c r="B970" s="1"/>
     </row>
-    <row r="971" spans="1:2" ht="15.75">
+    <row r="971" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A971" s="2"/>
       <c r="B971" s="1"/>
     </row>
-    <row r="972" spans="1:2" ht="15.75">
+    <row r="972" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A972" s="2"/>
       <c r="B972" s="1"/>
     </row>
-    <row r="973" spans="1:2" ht="15.75">
+    <row r="973" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A973" s="2"/>
       <c r="B973" s="1"/>
     </row>
-    <row r="974" spans="1:2" ht="15.75">
+    <row r="974" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A974" s="2"/>
       <c r="B974" s="1"/>
     </row>
-    <row r="975" spans="1:2" ht="15.75">
+    <row r="975" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A975" s="2"/>
       <c r="B975" s="1"/>
     </row>
-    <row r="976" spans="1:2" ht="15.75">
+    <row r="976" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A976" s="2"/>
       <c r="B976" s="1"/>
     </row>
-    <row r="977" spans="1:2" ht="15.75">
+    <row r="977" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A977" s="2"/>
       <c r="B977" s="1"/>
     </row>
-    <row r="978" spans="1:2" ht="15.75">
+    <row r="978" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A978" s="2"/>
       <c r="B978" s="1"/>
     </row>
-    <row r="979" spans="1:2" ht="15.75">
+    <row r="979" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A979" s="2"/>
       <c r="B979" s="1"/>
     </row>
-    <row r="980" spans="1:2" ht="15.75">
+    <row r="980" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A980" s="2"/>
       <c r="B980" s="1"/>
     </row>
-    <row r="981" spans="1:2" ht="15.75">
+    <row r="981" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A981" s="2"/>
       <c r="B981" s="1"/>
     </row>
-    <row r="982" spans="1:2" ht="15.75">
+    <row r="982" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A982" s="2"/>
       <c r="B982" s="1"/>
     </row>
-    <row r="983" spans="1:2" ht="15.75">
+    <row r="983" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A983" s="2"/>
       <c r="B983" s="1"/>
     </row>
-    <row r="984" spans="1:2" ht="15.75">
+    <row r="984" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A984" s="2"/>
       <c r="B984" s="1"/>
     </row>
-    <row r="985" spans="1:2" ht="15.75">
+    <row r="985" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A985" s="2"/>
       <c r="B985" s="1"/>
     </row>
-    <row r="986" spans="1:2" ht="15.75">
+    <row r="986" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A986" s="2"/>
       <c r="B986" s="1"/>
     </row>
-    <row r="987" spans="1:2" ht="15.75">
+    <row r="987" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A987" s="2"/>
       <c r="B987" s="1"/>
     </row>
-    <row r="988" spans="1:2" ht="15.75">
+    <row r="988" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A988" s="2"/>
       <c r="B988" s="1"/>
     </row>
-    <row r="989" spans="1:2" ht="15.75">
+    <row r="989" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A989" s="2"/>
       <c r="B989" s="1"/>
     </row>
-    <row r="990" spans="1:2" ht="15.75">
+    <row r="990" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A990" s="2"/>
       <c r="B990" s="1"/>
     </row>
-    <row r="991" spans="1:2" ht="15.75">
+    <row r="991" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A991" s="2"/>
       <c r="B991" s="1"/>
     </row>
-    <row r="992" spans="1:2" ht="15.75">
+    <row r="992" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A992" s="2"/>
       <c r="B992" s="1"/>
     </row>
-    <row r="993" spans="1:2" ht="15.75">
+    <row r="993" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A993" s="2"/>
       <c r="B993" s="1"/>
     </row>
-    <row r="994" spans="1:2" ht="15.75">
+    <row r="994" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A994" s="2"/>
       <c r="B994" s="1"/>
     </row>
-    <row r="995" spans="1:2" ht="15.75">
+    <row r="995" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A995" s="2"/>
       <c r="B995" s="1"/>
     </row>
-    <row r="996" spans="1:2" ht="15.75">
+    <row r="996" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A996" s="2"/>
       <c r="B996" s="1"/>
     </row>
-    <row r="997" spans="1:2" ht="15.75">
+    <row r="997" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A997" s="2"/>
       <c r="B997" s="1"/>
     </row>
-    <row r="998" spans="1:2" ht="15.75">
+    <row r="998" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A998" s="2"/>
       <c r="B998" s="1"/>
     </row>
-    <row r="999" spans="1:2" ht="15.75">
+    <row r="999" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A999" s="2"/>
       <c r="B999" s="1"/>
     </row>
-    <row r="1000" spans="1:2" ht="15.75">
+    <row r="1000" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1000" s="2"/>
       <c r="B1000" s="1"/>
     </row>
-    <row r="1001" spans="1:2" ht="15.75">
+    <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1001" s="2"/>
       <c r="B1001" s="1"/>
     </row>
-    <row r="1002" spans="1:2" ht="15.75">
+    <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1002" s="2"/>
       <c r="B1002" s="1"/>
     </row>
-    <row r="1003" spans="1:2" ht="15.75">
+    <row r="1003" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1003" s="2"/>
       <c r="B1003" s="1"/>
     </row>
-    <row r="1004" spans="1:2" ht="15.75">
+    <row r="1004" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1004" s="2"/>
       <c r="B1004" s="1"/>
     </row>
-    <row r="1005" spans="1:2" ht="15.75">
+    <row r="1005" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1005" s="2"/>
       <c r="B1005" s="1"/>
     </row>
-    <row r="1006" spans="1:2" ht="15.75">
+    <row r="1006" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1006" s="2"/>
       <c r="B1006" s="1"/>
     </row>
-    <row r="1007" spans="1:2" ht="15.75">
+    <row r="1007" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1007" s="2"/>
       <c r="B1007" s="1"/>
     </row>
-    <row r="1008" spans="1:2" ht="15.75">
+    <row r="1008" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1008" s="2"/>
       <c r="B1008" s="1"/>
     </row>
-    <row r="1009" spans="1:2" ht="15.75">
+    <row r="1009" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1009" s="2"/>
       <c r="B1009" s="1"/>
     </row>
-    <row r="1010" spans="1:2" ht="15.75">
+    <row r="1010" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1010" s="2"/>
       <c r="B1010" s="1"/>
     </row>
-    <row r="1011" spans="1:2" ht="15.75">
+    <row r="1011" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1011" s="2"/>
       <c r="B1011" s="1"/>
     </row>
-    <row r="1012" spans="1:2" ht="15.75">
+    <row r="1012" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1012" s="2"/>
       <c r="B1012" s="1"/>
     </row>
-    <row r="1013" spans="1:2" ht="15.75">
+    <row r="1013" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1013" s="2"/>
       <c r="B1013" s="1"/>
     </row>
-    <row r="1014" spans="1:2" ht="15.75">
+    <row r="1014" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1014" s="2"/>
       <c r="B1014" s="1"/>
     </row>
-    <row r="1015" spans="1:2" ht="15.75">
+    <row r="1015" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1015" s="2"/>
       <c r="B1015" s="1"/>
     </row>
-    <row r="1016" spans="1:2" ht="15.75">
+    <row r="1016" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1016" s="1"/>
       <c r="B1016" s="1"/>
     </row>
-    <row r="1017" spans="1:2" ht="15.75">
+    <row r="1017" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1017" s="1"/>
       <c r="B1017" s="1"/>
     </row>
-    <row r="1018" spans="1:2" ht="15.75">
+    <row r="1018" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1018" s="1"/>
       <c r="B1018" s="1"/>
     </row>
-    <row r="1019" spans="1:2" ht="15.75">
+    <row r="1019" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1019" s="1"/>
       <c r="B1019" s="1"/>
     </row>
-    <row r="1020" spans="1:2" ht="15.75">
+    <row r="1020" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1020" s="1"/>
       <c r="B1020" s="1"/>
     </row>
-    <row r="1021" spans="1:2" ht="15.75">
+    <row r="1021" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1021" s="1"/>
       <c r="B1021" s="1"/>
     </row>
-    <row r="1022" spans="1:2" ht="15.75">
+    <row r="1022" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1022" s="1"/>
       <c r="B1022" s="1"/>
     </row>
-    <row r="1023" spans="1:2" ht="15.75">
+    <row r="1023" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1023" s="1"/>
       <c r="B1023" s="1"/>
     </row>
-    <row r="1024" spans="1:2" ht="15.75">
+    <row r="1024" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1024" s="1"/>
       <c r="B1024" s="1"/>
     </row>
-    <row r="1025" spans="1:2" ht="15.75">
+    <row r="1025" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1025" s="1"/>
       <c r="B1025" s="1"/>
     </row>
-    <row r="1026" spans="1:2" ht="15.75">
+    <row r="1026" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1026" s="1"/>
       <c r="B1026" s="1"/>
     </row>
-    <row r="1027" spans="1:2" ht="15.75">
+    <row r="1027" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1027" s="1"/>
       <c r="B1027" s="1"/>
     </row>
-    <row r="1028" spans="1:2" ht="15.75">
+    <row r="1028" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1028" s="1"/>
       <c r="B1028" s="1"/>
     </row>
-    <row r="1029" spans="1:2" ht="15.75">
+    <row r="1029" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1029" s="1"/>
       <c r="B1029" s="1"/>
     </row>
-    <row r="1030" spans="1:2" ht="15.75">
+    <row r="1030" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1030" s="1"/>
       <c r="B1030" s="1"/>
     </row>
-    <row r="1031" spans="1:2" ht="15.75">
+    <row r="1031" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1031" s="1"/>
       <c r="B1031" s="1"/>
     </row>
-    <row r="1032" spans="1:2" ht="15.75">
+    <row r="1032" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1032" s="1"/>
       <c r="B1032" s="1"/>
     </row>
-    <row r="1033" spans="1:2" ht="15.75">
+    <row r="1033" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1033" s="1"/>
       <c r="B1033" s="1"/>
     </row>
-    <row r="1034" spans="1:2" ht="15.75">
+    <row r="1034" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1034" s="1"/>
       <c r="B1034" s="1"/>
     </row>
-    <row r="1035" spans="1:2" ht="15.75">
+    <row r="1035" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1035" s="1"/>
       <c r="B1035" s="1"/>
     </row>
-    <row r="1036" spans="1:2" ht="15.75">
+    <row r="1036" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1036" s="1"/>
       <c r="B1036" s="1"/>
     </row>
-    <row r="1037" spans="1:2" ht="15.75">
+    <row r="1037" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1037" s="1"/>
       <c r="B1037" s="1"/>
     </row>
-    <row r="1038" spans="1:2" ht="15.75">
+    <row r="1038" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1038" s="1"/>
       <c r="B1038" s="1"/>
     </row>
-    <row r="1039" spans="1:2" ht="15.75">
+    <row r="1039" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1039" s="1"/>
       <c r="B1039" s="1"/>
     </row>
-    <row r="1040" spans="1:2" ht="15.75">
+    <row r="1040" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1040" s="1"/>
       <c r="B1040" s="1"/>
     </row>
-    <row r="1041" spans="1:2" ht="15.75">
+    <row r="1041" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1041" s="1"/>
       <c r="B1041" s="1"/>
     </row>
-    <row r="1042" spans="1:2" ht="15.75">
+    <row r="1042" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1042" s="1"/>
       <c r="B1042" s="1"/>
     </row>
-    <row r="1043" spans="1:2" ht="15.75">
+    <row r="1043" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1043" s="1"/>
       <c r="B1043" s="1"/>
     </row>
-    <row r="1044" spans="1:2" ht="15.75">
+    <row r="1044" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1044" s="1"/>
       <c r="B1044" s="1"/>
     </row>
-    <row r="1045" spans="1:2" ht="15.75">
+    <row r="1045" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1045" s="1"/>
       <c r="B1045" s="1"/>
     </row>
-    <row r="1046" spans="1:2" ht="15.75">
+    <row r="1046" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1046" s="1"/>
       <c r="B1046" s="1"/>
     </row>
-    <row r="1047" spans="1:2" ht="15.75">
+    <row r="1047" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1047" s="1"/>
       <c r="B1047" s="1"/>
     </row>
-    <row r="1048" spans="1:2" ht="15.75">
+    <row r="1048" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1048" s="1"/>
       <c r="B1048" s="1"/>
     </row>
-    <row r="1049" spans="1:2" ht="15.75">
+    <row r="1049" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1049" s="1"/>
       <c r="B1049" s="1"/>
     </row>
-    <row r="1050" spans="1:2" ht="15.75">
+    <row r="1050" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1050" s="1"/>
       <c r="B1050" s="1"/>
     </row>
-    <row r="1051" spans="1:2" ht="15.75">
+    <row r="1051" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1051" s="1"/>
       <c r="B1051" s="1"/>
     </row>
-    <row r="1052" spans="1:2" ht="15.75">
+    <row r="1052" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1052" s="1"/>
       <c r="B1052" s="1"/>
     </row>
-    <row r="1053" spans="1:2" ht="15.75">
+    <row r="1053" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1053" s="1"/>
       <c r="B1053" s="1"/>
     </row>
-    <row r="1054" spans="1:2" ht="15.75">
+    <row r="1054" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1054" s="1"/>
       <c r="B1054" s="1"/>
     </row>
-    <row r="1055" spans="1:2" ht="15.75">
+    <row r="1055" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1055" s="1"/>
       <c r="B1055" s="1"/>
     </row>
-    <row r="1056" spans="1:2" ht="15.75">
+    <row r="1056" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1056" s="1"/>
       <c r="B1056" s="1"/>
     </row>
-    <row r="1057" spans="1:2" ht="15.75">
+    <row r="1057" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1057" s="1"/>
       <c r="B1057" s="1"/>
     </row>
-    <row r="1058" spans="1:2" ht="15.75">
+    <row r="1058" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1058" s="1"/>
       <c r="B1058" s="1"/>
     </row>
-    <row r="1059" spans="1:2" ht="15.75">
+    <row r="1059" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1059" s="1"/>
       <c r="B1059" s="1"/>
     </row>
-    <row r="1060" spans="1:2" ht="15.75">
+    <row r="1060" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1060" s="1"/>
       <c r="B1060" s="1"/>
     </row>
-    <row r="1061" spans="1:2" ht="15.75">
+    <row r="1061" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1061" s="1"/>
       <c r="B1061" s="1"/>
     </row>
-    <row r="1062" spans="1:2" ht="15.75">
+    <row r="1062" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1062" s="1"/>
       <c r="B1062" s="1"/>
     </row>
-    <row r="1063" spans="1:2" ht="15.75">
+    <row r="1063" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1063" s="1"/>
       <c r="B1063" s="1"/>
     </row>
-    <row r="1064" spans="1:2" ht="15.75">
+    <row r="1064" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1064" s="1"/>
       <c r="B1064" s="1"/>
     </row>
-    <row r="1065" spans="1:2" ht="15.75">
+    <row r="1065" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1065" s="1"/>
       <c r="B1065" s="1"/>
     </row>
-    <row r="1066" spans="1:2" ht="15.75">
+    <row r="1066" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1066" s="1"/>
       <c r="B1066" s="1"/>
     </row>
-    <row r="1067" spans="1:2" ht="15.75">
+    <row r="1067" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1067" s="1"/>
       <c r="B1067" s="1"/>
     </row>
-    <row r="1068" spans="1:2" ht="15.75">
+    <row r="1068" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1068" s="1"/>
       <c r="B1068" s="1"/>
     </row>
-    <row r="1069" spans="1:2" ht="15.75">
+    <row r="1069" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1069" s="1"/>
       <c r="B1069" s="1"/>
     </row>
-    <row r="1070" spans="1:2" ht="15.75">
+    <row r="1070" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1070" s="1"/>
       <c r="B1070" s="1"/>
     </row>
-    <row r="1071" spans="1:2" ht="15.75">
+    <row r="1071" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1071" s="1"/>
       <c r="B1071" s="1"/>
     </row>
-    <row r="1072" spans="1:2" ht="15.75">
+    <row r="1072" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1072" s="1"/>
       <c r="B1072" s="1"/>
     </row>
-    <row r="1073" spans="1:2" ht="15.75">
+    <row r="1073" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1073" s="1"/>
       <c r="B1073" s="1"/>
     </row>
-    <row r="1074" spans="1:2" ht="15.75">
+    <row r="1074" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1074" s="1"/>
       <c r="B1074" s="1"/>
     </row>
-    <row r="1075" spans="1:2" ht="15.75">
+    <row r="1075" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1075" s="1"/>
       <c r="B1075" s="1"/>
     </row>
-    <row r="1076" spans="1:2" ht="15.75">
+    <row r="1076" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1076" s="1"/>
       <c r="B1076" s="1"/>
     </row>
-    <row r="1077" spans="1:2" ht="15.75">
+    <row r="1077" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1077" s="1"/>
       <c r="B1077" s="1"/>
     </row>
-    <row r="1078" spans="1:2" ht="15.75">
+    <row r="1078" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1078" s="1"/>
       <c r="B1078" s="1"/>
     </row>
-    <row r="1079" spans="1:2" ht="15.75">
+    <row r="1079" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1079" s="1"/>
       <c r="B1079" s="1"/>
     </row>
-    <row r="1080" spans="1:2" ht="15.75">
+    <row r="1080" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1080" s="1"/>
       <c r="B1080" s="1"/>
     </row>
-    <row r="1081" spans="1:2" ht="15.75">
+    <row r="1081" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1081" s="1"/>
       <c r="B1081" s="1"/>
     </row>
-    <row r="1082" spans="1:2" ht="15.75">
+    <row r="1082" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1082" s="1"/>
       <c r="B1082" s="1"/>
     </row>
-    <row r="1083" spans="1:2" ht="15.75">
+    <row r="1083" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1083" s="1"/>
       <c r="B1083" s="1"/>
     </row>
-    <row r="1084" spans="1:2" ht="15.75">
+    <row r="1084" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1084" s="1"/>
       <c r="B1084" s="1"/>
     </row>
-    <row r="1085" spans="1:2" ht="15.75">
+    <row r="1085" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1085" s="1"/>
       <c r="B1085" s="1"/>
     </row>
-    <row r="1086" spans="1:2" ht="15.75">
+    <row r="1086" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1086" s="1"/>
       <c r="B1086" s="1"/>
     </row>
-    <row r="1087" spans="1:2" ht="15.75">
+    <row r="1087" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1087" s="1"/>
       <c r="B1087" s="1"/>
     </row>
-    <row r="1088" spans="1:2" ht="15.75">
+    <row r="1088" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1088" s="1"/>
       <c r="B1088" s="1"/>
     </row>
-    <row r="1089" spans="1:2" ht="15.75">
+    <row r="1089" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1089" s="1"/>
       <c r="B1089" s="1"/>
     </row>
-    <row r="1090" spans="1:2" ht="15.75">
+    <row r="1090" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1090" s="1"/>
       <c r="B1090" s="1"/>
     </row>
-    <row r="1091" spans="1:2" ht="15.75">
+    <row r="1091" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1091" s="1"/>
       <c r="B1091" s="1"/>
     </row>
-    <row r="1092" spans="1:2" ht="15.75">
+    <row r="1092" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1092" s="1"/>
       <c r="B1092" s="1"/>
     </row>
-    <row r="1093" spans="1:2" ht="15.75">
+    <row r="1093" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1093" s="1"/>
       <c r="B1093" s="1"/>
     </row>
-    <row r="1094" spans="1:2" ht="15.75">
+    <row r="1094" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1094" s="1"/>
       <c r="B1094" s="1"/>
     </row>
-    <row r="1095" spans="1:2" ht="15.75">
+    <row r="1095" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1095" s="1"/>
       <c r="B1095" s="1"/>
     </row>
-    <row r="1096" spans="1:2" ht="15.75">
+    <row r="1096" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1096" s="1"/>
       <c r="B1096" s="1"/>
     </row>
-    <row r="1097" spans="1:2" ht="15.75">
+    <row r="1097" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1097" s="1"/>
       <c r="B1097" s="1"/>
     </row>
-    <row r="1098" spans="1:2" ht="15.75">
+    <row r="1098" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1098" s="1"/>
       <c r="B1098" s="1"/>
     </row>
-    <row r="1099" spans="1:2" ht="15.75">
+    <row r="1099" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1099" s="1"/>
       <c r="B1099" s="1"/>
     </row>
-    <row r="1100" spans="1:2" ht="15.75">
+    <row r="1100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1100" s="1"/>
       <c r="B1100" s="1"/>
     </row>
-    <row r="1101" spans="1:2" ht="15.75">
+    <row r="1101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1101" s="1"/>
       <c r="B1101" s="1"/>
     </row>
-    <row r="1102" spans="1:2" ht="15.75">
+    <row r="1102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1102" s="1"/>
       <c r="B1102" s="1"/>
     </row>
-    <row r="1103" spans="1:2" ht="15.75">
+    <row r="1103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1103" s="1"/>
       <c r="B1103" s="1"/>
     </row>
-    <row r="1104" spans="1:2" ht="15.75">
+    <row r="1104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1104" s="1"/>
       <c r="B1104" s="1"/>
     </row>
-    <row r="1105" spans="1:2" ht="15.75">
+    <row r="1105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1105" s="1"/>
       <c r="B1105" s="1"/>
     </row>
-    <row r="1106" spans="1:2" ht="15.75">
+    <row r="1106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1106" s="1"/>
       <c r="B1106" s="1"/>
     </row>
-    <row r="1107" spans="1:2" ht="15.75">
+    <row r="1107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1107" s="1"/>
       <c r="B1107" s="1"/>
     </row>
-    <row r="1108" spans="1:2" ht="15.75">
+    <row r="1108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1108" s="1"/>
       <c r="B1108" s="1"/>
     </row>
-    <row r="1109" spans="1:2" ht="15.75">
+    <row r="1109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1109" s="1"/>
       <c r="B1109" s="1"/>
     </row>
-    <row r="1110" spans="1:2" ht="15.75">
+    <row r="1110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1110" s="1"/>
       <c r="B1110" s="1"/>
     </row>
-    <row r="1111" spans="1:2" ht="15.75">
+    <row r="1111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1111" s="1"/>
       <c r="B1111" s="1"/>
     </row>
-    <row r="1112" spans="1:2" ht="15.75">
+    <row r="1112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1112" s="1"/>
       <c r="B1112" s="1"/>
     </row>
-    <row r="1113" spans="1:2" ht="15.75">
+    <row r="1113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1113" s="1"/>
       <c r="B1113" s="1"/>
     </row>
-    <row r="1114" spans="1:2" ht="15.75">
+    <row r="1114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1114" s="1"/>
       <c r="B1114" s="1"/>
     </row>
-    <row r="1115" spans="1:2" ht="15.75">
+    <row r="1115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1115" s="1"/>
       <c r="B1115" s="1"/>
     </row>
-    <row r="1116" spans="1:2" ht="15.75">
+    <row r="1116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1116" s="1"/>
       <c r="B1116" s="1"/>
     </row>
-    <row r="1117" spans="1:2" ht="15.75">
+    <row r="1117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1117" s="1"/>
       <c r="B1117" s="1"/>
     </row>
-    <row r="1118" spans="1:2" ht="15.75">
+    <row r="1118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1118" s="1"/>
       <c r="B1118" s="1"/>
     </row>
-    <row r="1119" spans="1:2" ht="15.75">
+    <row r="1119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1119" s="1"/>
       <c r="B1119" s="1"/>
     </row>
-    <row r="1120" spans="1:2" ht="15.75">
+    <row r="1120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1120" s="1"/>
       <c r="B1120" s="1"/>
     </row>
-    <row r="1121" spans="1:2" ht="15.75">
+    <row r="1121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1121" s="1"/>
       <c r="B1121" s="1"/>
     </row>
-    <row r="1122" spans="1:2" ht="15.75">
+    <row r="1122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1122" s="1"/>
       <c r="B1122" s="1"/>
     </row>
-    <row r="1123" spans="1:2" ht="15.75">
+    <row r="1123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1123" s="1"/>
       <c r="B1123" s="1"/>
     </row>
-    <row r="1124" spans="1:2" ht="15.75">
+    <row r="1124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1124" s="1"/>
       <c r="B1124" s="1"/>
     </row>
-    <row r="1125" spans="1:2" ht="15.75">
+    <row r="1125" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1125" s="1"/>
       <c r="B1125" s="1"/>
     </row>
-    <row r="1126" spans="1:2" ht="15.75">
+    <row r="1126" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1126" s="1"/>
       <c r="B1126" s="1"/>
     </row>
-    <row r="1127" spans="1:2" ht="15.75">
+    <row r="1127" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1127" s="1"/>
       <c r="B1127" s="1"/>
     </row>
-    <row r="1128" spans="1:2" ht="15.75">
+    <row r="1128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1128" s="1"/>
       <c r="B1128" s="1"/>
     </row>
-    <row r="1129" spans="1:2" ht="15.75">
+    <row r="1129" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1129" s="1"/>
       <c r="B1129" s="1"/>
     </row>
-    <row r="1130" spans="1:2" ht="15.75">
+    <row r="1130" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1130" s="1"/>
       <c r="B1130" s="1"/>
     </row>
-    <row r="1131" spans="1:2" ht="15.75">
+    <row r="1131" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1131" s="1"/>
       <c r="B1131" s="1"/>
     </row>
-    <row r="1132" spans="1:2" ht="15.75">
+    <row r="1132" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1132" s="1"/>
       <c r="B1132" s="1"/>
     </row>
-    <row r="1133" spans="1:2" ht="15.75">
+    <row r="1133" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1133" s="1"/>
       <c r="B1133" s="1"/>
     </row>
-    <row r="1134" spans="1:2" ht="15.75">
+    <row r="1134" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1134" s="1"/>
       <c r="B1134" s="1"/>
     </row>
-    <row r="1135" spans="1:2" ht="15.75">
+    <row r="1135" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1135" s="1"/>
       <c r="B1135" s="1"/>
     </row>
-    <row r="1136" spans="1:2" ht="15.75">
+    <row r="1136" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1136" s="1"/>
       <c r="B1136" s="1"/>
     </row>
-    <row r="1137" spans="1:2" ht="15.75">
+    <row r="1137" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1137" s="1"/>
       <c r="B1137" s="1"/>
     </row>
-    <row r="1138" spans="1:2" ht="15.75">
+    <row r="1138" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1138" s="1"/>
       <c r="B1138" s="1"/>
     </row>
-    <row r="1139" spans="1:2" ht="15.75">
+    <row r="1139" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1139" s="1"/>
       <c r="B1139" s="1"/>
     </row>
-    <row r="1140" spans="1:2" ht="15.75">
+    <row r="1140" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1140" s="1"/>
       <c r="B1140" s="1"/>
     </row>
-    <row r="1141" spans="1:2" ht="15.75">
+    <row r="1141" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1141" s="1"/>
       <c r="B1141" s="1"/>
     </row>
-    <row r="1142" spans="1:2" ht="15.75">
+    <row r="1142" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1142" s="1"/>
       <c r="B1142" s="1"/>
     </row>
-    <row r="1143" spans="1:2" ht="15.75">
+    <row r="1143" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1143" s="1"/>
       <c r="B1143" s="1"/>
     </row>
-    <row r="1144" spans="1:2" ht="15.75">
+    <row r="1144" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1144" s="1"/>
       <c r="B1144" s="1"/>
     </row>
-    <row r="1145" spans="1:2" ht="15.75">
+    <row r="1145" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1145" s="1"/>
       <c r="B1145" s="1"/>
     </row>
-    <row r="1146" spans="1:2" ht="15.75">
+    <row r="1146" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1146" s="1"/>
       <c r="B1146" s="1"/>
     </row>
-    <row r="1147" spans="1:2" ht="15.75">
+    <row r="1147" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1147" s="1"/>
       <c r="B1147" s="1"/>
     </row>
-    <row r="1148" spans="1:2" ht="15.75">
+    <row r="1148" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1148" s="1"/>
       <c r="B1148" s="1"/>
     </row>
-    <row r="1149" spans="1:2" ht="15.75">
+    <row r="1149" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1149" s="1"/>
       <c r="B1149" s="1"/>
     </row>
-    <row r="1150" spans="1:2" ht="15.75">
+    <row r="1150" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1150" s="1"/>
       <c r="B1150" s="1"/>
     </row>
-    <row r="1151" spans="1:2" ht="15.75">
+    <row r="1151" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1151" s="1"/>
       <c r="B1151" s="1"/>
     </row>
-    <row r="1152" spans="1:2" ht="15.75">
+    <row r="1152" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1152" s="1"/>
       <c r="B1152" s="1"/>
     </row>
-    <row r="1153" spans="1:2" ht="15.75">
+    <row r="1153" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1153" s="1"/>
       <c r="B1153" s="1"/>
     </row>
-    <row r="1154" spans="1:2" ht="15.75">
+    <row r="1154" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1154" s="1"/>
       <c r="B1154" s="1"/>
     </row>
-    <row r="1155" spans="1:2" ht="15.75">
+    <row r="1155" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1155" s="1"/>
       <c r="B1155" s="1"/>
     </row>
-    <row r="1156" spans="1:2" ht="15.75">
+    <row r="1156" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1156" s="1"/>
       <c r="B1156" s="1"/>
     </row>
-    <row r="1157" spans="1:2" ht="15.75">
+    <row r="1157" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1157" s="1"/>
       <c r="B1157" s="1"/>
     </row>
-    <row r="1158" spans="1:2" ht="15.75">
+    <row r="1158" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1158" s="1"/>
       <c r="B1158" s="1"/>
     </row>
-    <row r="1159" spans="1:2" ht="15.75">
+    <row r="1159" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1159" s="1"/>
       <c r="B1159" s="1"/>
     </row>
-    <row r="1160" spans="1:2" ht="15.75">
+    <row r="1160" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1160" s="1"/>
       <c r="B1160" s="1"/>
     </row>
-    <row r="1161" spans="1:2" ht="15.75">
+    <row r="1161" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1161" s="1"/>
       <c r="B1161" s="1"/>
     </row>
-    <row r="1162" spans="1:2" ht="15.75">
+    <row r="1162" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1162" s="1"/>
       <c r="B1162" s="1"/>
     </row>
-    <row r="1163" spans="1:2" ht="15.75">
+    <row r="1163" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1163" s="1"/>
       <c r="B1163" s="1"/>
     </row>
-    <row r="1164" spans="1:2" ht="15.75">
+    <row r="1164" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1164" s="1"/>
       <c r="B1164" s="1"/>
     </row>
-    <row r="1165" spans="1:2" ht="15.75">
+    <row r="1165" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1165" s="1"/>
       <c r="B1165" s="1"/>
     </row>
-    <row r="1166" spans="1:2" ht="15.75">
+    <row r="1166" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1166" s="1"/>
       <c r="B1166" s="1"/>
     </row>
-    <row r="1167" spans="1:2" ht="15.75">
+    <row r="1167" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1167" s="1"/>
       <c r="B1167" s="1"/>
     </row>
-    <row r="1168" spans="1:2" ht="15.75">
+    <row r="1168" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1168" s="1"/>
       <c r="B1168" s="1"/>
     </row>
-    <row r="1169" spans="1:2" ht="15.75">
+    <row r="1169" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1169" s="1"/>
       <c r="B1169" s="1"/>
     </row>
-    <row r="1170" spans="1:2" ht="15.75">
+    <row r="1170" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1170" s="1"/>
       <c r="B1170" s="1"/>
     </row>
-    <row r="1171" spans="1:2" ht="15.75">
+    <row r="1171" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1171" s="1"/>
       <c r="B1171" s="1"/>
     </row>
-    <row r="1172" spans="1:2" ht="15.75">
+    <row r="1172" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1172" s="1"/>
       <c r="B1172" s="1"/>
     </row>
-    <row r="1173" spans="1:2" ht="15.75">
+    <row r="1173" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1173" s="1"/>
       <c r="B1173" s="1"/>
     </row>
-    <row r="1174" spans="1:2" ht="15.75">
+    <row r="1174" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1174" s="1"/>
       <c r="B1174" s="1"/>
     </row>
-    <row r="1175" spans="1:2" ht="15.75">
+    <row r="1175" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1175" s="1"/>
       <c r="B1175" s="1"/>
     </row>
-    <row r="1176" spans="1:2" ht="15.75">
+    <row r="1176" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1176" s="1"/>
       <c r="B1176" s="1"/>
     </row>
-    <row r="1177" spans="1:2" ht="15.75">
+    <row r="1177" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1177" s="1"/>
       <c r="B1177" s="1"/>
     </row>
-    <row r="1178" spans="1:2" ht="15.75">
+    <row r="1178" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1178" s="1"/>
       <c r="B1178" s="1"/>
     </row>
-    <row r="1179" spans="1:2" ht="15.75">
+    <row r="1179" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1179" s="1"/>
       <c r="B1179" s="1"/>
     </row>
-    <row r="1180" spans="1:2" ht="15.75">
+    <row r="1180" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1180" s="1"/>
       <c r="B1180" s="1"/>
     </row>
-    <row r="1181" spans="1:2" ht="15.75">
+    <row r="1181" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1181" s="1"/>
       <c r="B1181" s="1"/>
     </row>
-    <row r="1182" spans="1:2" ht="15.75">
+    <row r="1182" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1182" s="1"/>
       <c r="B1182" s="1"/>
     </row>
-    <row r="1183" spans="1:2" ht="15.75">
+    <row r="1183" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1183" s="1"/>
       <c r="B1183" s="1"/>
     </row>
-    <row r="1184" spans="1:2" ht="15.75">
+    <row r="1184" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1184" s="1"/>
       <c r="B1184" s="1"/>
     </row>
-    <row r="1185" spans="1:2" ht="15.75">
+    <row r="1185" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1185" s="1"/>
       <c r="B1185" s="1"/>
     </row>
-    <row r="1186" spans="1:2" ht="15.75">
+    <row r="1186" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1186" s="1"/>
       <c r="B1186" s="1"/>
     </row>
-    <row r="1187" spans="1:2" ht="15.75">
+    <row r="1187" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1187" s="1"/>
       <c r="B1187" s="1"/>
     </row>
-    <row r="1188" spans="1:2" ht="15.75">
+    <row r="1188" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1188" s="1"/>
       <c r="B1188" s="1"/>
     </row>
-    <row r="1189" spans="1:2" ht="15.75">
+    <row r="1189" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1189" s="1"/>
       <c r="B1189" s="1"/>
     </row>
-    <row r="1190" spans="1:2" ht="15.75">
+    <row r="1190" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1190" s="1"/>
       <c r="B1190" s="1"/>
     </row>
-    <row r="1191" spans="1:2" ht="15.75">
+    <row r="1191" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1191" s="1"/>
       <c r="B1191" s="1"/>
     </row>
-    <row r="1192" spans="1:2" ht="15.75">
+    <row r="1192" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1192" s="1"/>
       <c r="B1192" s="1"/>
     </row>
-    <row r="1193" spans="1:2" ht="15.75">
+    <row r="1193" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1193" s="1"/>
       <c r="B1193" s="1"/>
     </row>
-    <row r="1194" spans="1:2" ht="15.75">
+    <row r="1194" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1194" s="1"/>
       <c r="B1194" s="1"/>
     </row>
-    <row r="1195" spans="1:2" ht="15.75">
+    <row r="1195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1195" s="1"/>
       <c r="B1195" s="1"/>
     </row>
-    <row r="1196" spans="1:2" ht="15.75">
+    <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1196" s="1"/>
       <c r="B1196" s="1"/>
     </row>
-    <row r="1197" spans="1:2" ht="15.75">
+    <row r="1197" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1197" s="1"/>
       <c r="B1197" s="1"/>
     </row>
-    <row r="1198" spans="1:2" ht="15.75">
+    <row r="1198" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1198" s="1"/>
       <c r="B1198" s="1"/>
     </row>
-    <row r="1199" spans="1:2" ht="15.75">
+    <row r="1199" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1199" s="1"/>
       <c r="B1199" s="1"/>
     </row>
-    <row r="1200" spans="1:2" ht="15.75">
+    <row r="1200" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1200" s="1"/>
       <c r="B1200" s="1"/>
     </row>
-    <row r="1201" spans="1:2" ht="15.75">
+    <row r="1201" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1201" s="1"/>
       <c r="B1201" s="1"/>
     </row>
-    <row r="1202" spans="1:2" ht="15.75">
+    <row r="1202" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1202" s="1"/>
       <c r="B1202" s="1"/>
     </row>
-    <row r="1203" spans="1:2" ht="15.75">
+    <row r="1203" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1203" s="1"/>
       <c r="B1203" s="1"/>
     </row>
-    <row r="1204" spans="1:2" ht="15.75">
+    <row r="1204" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1204" s="1"/>
       <c r="B1204" s="1"/>
     </row>
-    <row r="1205" spans="1:2" ht="15.75">
+    <row r="1205" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1205" s="1"/>
       <c r="B1205" s="1"/>
     </row>
-    <row r="1206" spans="1:2" ht="15.75">
+    <row r="1206" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1206" s="1"/>
       <c r="B1206" s="1"/>
     </row>
-    <row r="1207" spans="1:2" ht="15.75">
+    <row r="1207" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1207" s="1"/>
       <c r="B1207" s="1"/>
     </row>
-    <row r="1208" spans="1:2" ht="15.75">
+    <row r="1208" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1208" s="1"/>
       <c r="B1208" s="1"/>
     </row>
-    <row r="1209" spans="1:2" ht="15.75">
+    <row r="1209" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1209" s="1"/>
       <c r="B1209" s="1"/>
     </row>
-    <row r="1210" spans="1:2" ht="15.75">
+    <row r="1210" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1210" s="1"/>
       <c r="B1210" s="1"/>
     </row>
@@ -10584,40 +10585,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA90CD46-FF53-412A-950C-99718992C948}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="277" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C27745F-8FF7-41E5-88C5-E0A2A8D86011}"/>
+  <xr:revisionPtr revIDLastSave="281" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A9B5BF8-C0C0-434C-98D5-ADE6A0E6428C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,6 +775,9 @@
     <t>PARALAMA VOLVO MEIO PARALAMA (PARTE DE BAIXO)</t>
   </si>
   <si>
+    <t>PARALAMA VOLVO 2ª PARTE (PARTE DE CIMA)</t>
+  </si>
+  <si>
     <t>PARALAMA CARRETA LIBRELATO</t>
   </si>
   <si>
@@ -892,7 +895,7 @@
     <t>REDUCAO MACH/FEM 22X16MM</t>
   </si>
   <si>
-    <t>REBITE FERRO</t>
+    <t>REBITE ALUMINIO</t>
   </si>
   <si>
     <t>REPARO CENTRAL DA CUICA CARRETA</t>
@@ -1595,16 +1598,13 @@
   </si>
   <si>
     <t>TINTA SPRAY AZU 250GR</t>
-  </si>
-  <si>
-    <t>PARALAMA VOLVO 2ª PARTE (PARTE DE CIMA)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2171,14 +2171,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F1210"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.75">
       <c r="A2" s="14">
         <v>1040019909</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.75">
       <c r="A3" s="14">
         <v>1040023837</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15.75">
       <c r="A4" s="14">
         <v>1040023836</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15.75">
       <c r="A5" s="14">
         <v>1010000216</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15.75">
       <c r="A6" s="14">
         <v>423651</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.75">
       <c r="A7" s="14">
         <v>1040077347</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15.75">
       <c r="A8" s="14">
         <v>1040077348</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15.75">
       <c r="A9" s="14">
         <v>417715</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15.75">
       <c r="A10" s="14">
         <v>1010062075</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="15.75">
       <c r="A11" s="14">
         <v>1040083308</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15.75">
       <c r="A12" s="14">
         <v>1040077346</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15.75">
       <c r="A13" s="14">
         <v>1010049326</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="15.75">
       <c r="A14" s="14">
         <v>1040017265</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15.75">
       <c r="A15" s="14">
         <v>1010060188</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="15.75">
       <c r="A16" s="14">
         <v>1040019851</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15.75">
       <c r="A17" s="14">
         <v>1010077433</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15.75">
       <c r="A18" s="14">
         <v>1010042610</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="15.75">
       <c r="A19" s="14">
         <v>1040077352</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="15.75">
       <c r="A20" s="14">
         <v>1040083258</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="15.75">
       <c r="A21" s="14">
         <v>68686</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15.75">
       <c r="A22" s="14">
         <v>1010084124</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="15.75">
       <c r="A23" s="14">
         <v>102286</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="15.75">
       <c r="A24" s="15">
         <v>1040097671</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="15.75">
       <c r="A25" s="14">
         <v>1010003651</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="15.75">
       <c r="A26" s="14">
         <v>1010062027</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="15.75">
       <c r="A27" s="14">
         <v>1010021550</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="15.75">
       <c r="A28" s="14">
         <v>1040077350</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="15.75">
       <c r="A29" s="14">
         <v>1040077349</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="15.75">
       <c r="A30" s="14">
         <v>154897</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="15.75">
       <c r="A31" s="14">
         <v>13781</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="15.75">
       <c r="A32" s="14">
         <v>1010058682</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="15.75">
       <c r="A33" s="14">
         <v>1010059706</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="15.75">
       <c r="A34" s="14">
         <v>1010077386</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="15.75">
       <c r="A35" s="14">
         <v>1010058325</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="15.75">
       <c r="A36" s="14">
         <v>1010061986</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="15.75">
       <c r="A37" s="9">
         <v>1010004299</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="15.75">
       <c r="A38" s="9">
         <v>1010004301</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="15.75">
       <c r="A39" s="9">
         <v>1010004289</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="15.75">
       <c r="A40" s="9">
         <v>1010004292</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="15.75">
       <c r="A41" s="9">
         <v>1010012756</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="15.75">
       <c r="A42" s="14">
         <v>1040077354</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="15.75">
       <c r="A43" s="14">
         <v>1010050496</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="15.75">
       <c r="A44" s="14">
         <v>1010050536</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="15.75">
       <c r="A45" s="14">
         <v>1010061810</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="15.75">
       <c r="A46" s="14">
         <v>1040092580</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="15.75">
       <c r="A47" s="14">
         <v>1010041375</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="15.75">
       <c r="A48" s="14">
         <v>1040098335</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="15.75">
       <c r="A49" s="14">
         <v>1010023362</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="15.75">
       <c r="A50" s="14">
         <v>1010052336</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="15.75">
       <c r="A51" s="14">
         <v>1040077355</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="15.75">
       <c r="A52" s="14">
         <v>230110</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="15.75">
       <c r="A53" s="14">
         <v>1040077357</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="15.75">
       <c r="A54" s="14">
         <v>1040077356</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="15.75">
       <c r="A55" s="15">
         <v>1040075251</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="15.75">
       <c r="A56" s="14">
         <v>1040090022</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="15.75">
       <c r="A57" s="14">
         <v>1010023336</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="15.75">
       <c r="A58" s="14">
         <v>1010021328</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="15.75">
       <c r="A59" s="14">
         <v>1010059706</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="15.75">
       <c r="A60" s="14">
         <v>1010062152</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="15.75">
       <c r="A61" s="14">
         <v>1040077358</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="15.75">
       <c r="A62" s="14">
         <v>1010045227</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="15.75">
       <c r="A63" s="14">
         <v>1010085124</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="15.75">
       <c r="A64" s="14">
         <v>1010046495</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="15.75">
       <c r="A65" s="14">
         <v>1040101764</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="15.75">
       <c r="A66" s="14">
         <v>1010032356</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="15.75">
       <c r="A67" s="14">
         <v>1010050244</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="15.75">
       <c r="A68" s="14">
         <v>1010050243</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="15.75">
       <c r="A69" s="14">
         <v>428995</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="15.75">
       <c r="A70" s="14">
         <v>428998</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="15.75">
       <c r="A71" s="14">
         <v>1010031607</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="15.75">
       <c r="A72" s="14">
         <v>1010031630</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="15.75">
       <c r="A73" s="14">
         <v>1010045647</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="15.75">
       <c r="A74" s="14">
         <v>1010031567</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="15.75">
       <c r="A75" s="14">
         <v>1040077361</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="15.75">
       <c r="A76" s="14">
         <v>1010050445</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="15.75">
       <c r="A77" s="14">
         <v>1010050461</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="15.75">
       <c r="A78" s="14">
         <v>1010087609</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="15.75">
       <c r="A79" s="14">
         <v>1010087738</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="15.75">
       <c r="A80" s="14">
         <v>1010053885</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="15.75">
       <c r="A81" s="15">
         <v>1040097102</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="15.75">
       <c r="A82" s="15">
         <v>1010020838</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="15.75">
       <c r="A83" s="16">
         <v>341430</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="15.75">
       <c r="A84" s="15">
         <v>1010042643</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="15.75">
       <c r="A85" s="15">
         <v>425554</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="15.75">
       <c r="A86" s="15">
         <v>1010084162</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="15.75">
       <c r="A87" s="15">
         <v>1010084157</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="15.75">
       <c r="A88" s="15">
         <v>1010084158</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="15.75">
       <c r="A89" s="15">
         <v>1010084159</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="15.75">
       <c r="A90" s="15">
         <v>1010084160</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="15.75">
       <c r="A91" s="15">
         <v>1010084161</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="15.75">
       <c r="A92" s="15">
         <v>224382</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="15.75">
       <c r="A93" s="15">
         <v>94314</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="15.75">
       <c r="A94" s="17">
         <v>1010003982</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="15.75">
       <c r="A95" s="15">
         <v>1010000182</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="15.75">
       <c r="A96" s="15">
         <v>1010021079</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="15.75">
       <c r="A97" s="15">
         <v>1010002463</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="15.75">
       <c r="A98" s="15">
         <v>1010062982</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="15.75">
       <c r="A99" s="15">
         <v>1010063209</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="15.75">
       <c r="A100" s="15">
         <v>1040076302</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="15.75">
       <c r="A101" s="15">
         <v>1040077362</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="15.75">
       <c r="A102" s="15">
         <v>1040077363</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="15.75">
       <c r="A103" s="15">
         <v>1040074483</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="15.75">
       <c r="A104" s="15">
         <v>1040077364</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="15.75">
       <c r="A105" s="15">
         <v>1040048463</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="15.75">
       <c r="A106" s="15">
         <v>1040096343</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="15.75">
       <c r="A107" s="15">
         <v>409640</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="15.75">
       <c r="A108" s="15">
         <v>1010032753</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="15.75">
       <c r="A109" s="15">
         <v>1040098597</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="15.75">
       <c r="A110" s="15">
         <v>1040084464</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="15.75">
       <c r="A111" s="15">
         <v>1040017773</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="15.75">
       <c r="A112" s="15">
         <v>1010007405</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="15.75">
       <c r="A113" s="17">
         <v>1040077365</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="15.75">
       <c r="A114" s="15">
         <v>1010027794</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="15.75">
       <c r="A115" s="15">
         <v>1040077366</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="15.75">
       <c r="A116" s="15">
         <v>1040077367</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="15.75">
       <c r="A117" s="15">
         <v>1010021561</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="15.75">
       <c r="A118" s="15">
         <v>1010021562</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="15.75">
       <c r="A119" s="15">
         <v>1010027792</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="15.75">
       <c r="A120" s="15">
         <v>1010084930</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="15.75">
       <c r="A121" s="15">
         <v>341430</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="15.75">
       <c r="A122" s="15">
         <v>1010029366</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="15.75">
       <c r="A123" s="18">
         <v>1010031723</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="15.75">
       <c r="A124" s="18">
         <v>1010049216</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="15.75">
       <c r="A125" s="15">
         <v>405558</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="15.75">
       <c r="A126" s="15">
         <v>1010023038</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="15.75">
       <c r="A127" s="15">
         <v>1010084109</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="15.75">
       <c r="A128" s="15">
         <v>1010021582</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" ht="15.75">
       <c r="A129" s="15">
         <v>1010021544</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" ht="15.75">
       <c r="A130" s="15">
         <v>1010021564</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" ht="15.75">
       <c r="A131" s="15">
         <v>1010023019</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="15.75">
       <c r="A132" s="15">
         <v>1010048541</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="15.75">
       <c r="A133" s="15">
         <v>1010059334</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="15.75">
       <c r="A134" s="15">
         <v>1010000277</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="15.75">
       <c r="A135" s="19">
         <v>1010085344</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" ht="15.75">
       <c r="A136" s="19">
         <v>1010085383</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="15.75">
       <c r="A137" s="15">
         <v>1010001389</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="15.75">
       <c r="A138" s="15">
         <v>1010017703</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="15.75">
       <c r="A139" s="15">
         <v>1010052036</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="15.75">
       <c r="A140" s="15">
         <v>1040097133</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="15.75">
       <c r="A141" s="15">
         <v>1040019325</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="15.75">
       <c r="A142" s="15">
         <v>64262</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="15.75">
       <c r="A143" s="14">
         <v>1010047089</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="15.75">
       <c r="A144" s="14">
         <v>1040050168</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" ht="15.75">
       <c r="A145" s="14">
         <v>1040077370</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="15.75">
       <c r="A146" s="14">
         <v>1040099247</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="15.75">
       <c r="A147" s="15">
         <v>1040100560</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="15.75">
       <c r="A148" s="15">
         <v>1040077399</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="15.75">
       <c r="A149" s="15">
         <v>1040077374</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="15.75">
       <c r="A150" s="15">
         <v>1040077399</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="15.75">
       <c r="A151" s="15">
         <v>1010050632</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="15.75">
       <c r="A152" s="15">
         <v>1010020504</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="15.75">
       <c r="A153" s="15">
         <v>409250</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="15.75">
       <c r="A154" s="15">
         <v>1010020541</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="15.75">
       <c r="A155" s="15">
         <v>1010020879</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="15.75">
       <c r="A156" s="15">
         <v>1040077380</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="15.75">
       <c r="A157" s="15">
         <v>1010021520</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="15.75">
       <c r="A158" s="15">
         <v>1040098861</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="15.75">
       <c r="A159" s="15">
         <v>1010077261</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="15.75">
       <c r="A160" s="15">
         <v>1010027664</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="15.75">
       <c r="A161" s="15">
         <v>1010083731</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" ht="15.75">
       <c r="A162" s="15">
         <v>1010083885</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="15.75">
       <c r="A163" s="15">
         <v>1010014834</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="15.75">
       <c r="A164" s="15">
         <v>1010083908</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="15.75">
       <c r="A165" s="15">
         <v>1010024047</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="15.75">
       <c r="A166" s="15">
         <v>1040077377</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="15.75">
       <c r="A167" s="15">
         <v>1010061942</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="15.75">
       <c r="A168" s="15">
         <v>1040097070</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="15.75">
       <c r="A169" s="15">
         <v>1040097068</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="15.75">
       <c r="A170" s="15">
         <v>22004</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="15.75">
       <c r="A171" s="15">
         <v>1010058554</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="15.75">
       <c r="A172" s="15">
         <v>1010027308</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="15.75">
       <c r="A173" s="19">
         <v>1040077383</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="15.75">
       <c r="A174" s="19">
         <v>1010025482</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="15.75">
       <c r="A175" s="19">
         <v>1010025509</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="15.75">
       <c r="A176" s="15">
         <v>1010027789</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="15.75">
       <c r="A177" s="15">
         <v>1010027790</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="15.75">
       <c r="A178" s="15">
         <v>1010018301</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="15.75">
       <c r="A179" s="15">
         <v>1010031616</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="15.75">
       <c r="A180" s="15">
         <v>1010053728</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="15.75">
       <c r="A181" s="15">
         <v>1010020758</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="15.75">
       <c r="A182" s="15">
         <v>1010020781</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="15.75">
       <c r="A183" s="14">
         <v>1010058426</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="15.75">
       <c r="A184" s="14">
         <v>1010059332</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="15.75">
       <c r="A185" s="14">
         <v>1040077389</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="15.75">
       <c r="A186" s="15">
         <v>1010021364</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="15.75">
       <c r="A187" s="20">
         <v>1010021541</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="15.75">
       <c r="A188" s="14">
         <v>1010021955</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="15.75">
       <c r="A189" s="15">
         <v>1040077388</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="15.75">
       <c r="A190" s="15">
         <v>1010058100</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="15.75">
       <c r="A191" s="15">
         <v>1010020524</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="15.75">
       <c r="A192" s="15">
         <v>1010021958</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="15.75">
       <c r="A193" s="15">
         <v>1010019756</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="15.75">
       <c r="A194" s="15">
         <v>1010019752</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="15.75">
       <c r="A195" s="15">
         <v>409639</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="15.75">
       <c r="A196" s="15">
         <v>1010047089</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="15.75">
       <c r="A197" s="15">
         <v>1040084107</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="15.75">
       <c r="A198" s="15">
         <v>1010085203</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="15.75">
       <c r="A199" s="15">
         <v>424298</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" ht="15.75">
       <c r="A200" s="15">
         <v>421847</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="15.75">
       <c r="A201" s="15">
         <v>431573</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="15.75">
       <c r="A202" s="15">
         <v>1010021581</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="15.75">
       <c r="A203" s="21">
         <v>412413</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" ht="15.75">
       <c r="A204" s="22">
         <v>1010022606</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" ht="15.75">
       <c r="A205" s="23">
         <v>1010003527</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" ht="15.75">
       <c r="A206" s="23">
         <v>1010055707</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" ht="15.75">
       <c r="A207" s="18">
         <v>422027</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="15.75">
       <c r="A208" s="14">
         <v>1010011313</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" ht="15.75">
       <c r="A209" s="15">
         <v>27051</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" ht="15.75">
       <c r="A210" s="15">
         <v>1010011304</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="15.75">
       <c r="A211" s="15">
         <v>35659</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="15.75">
       <c r="A212" s="15">
         <v>1040077390</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="15.75">
       <c r="A213" s="15">
         <v>1010021542</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="15.75">
       <c r="A214" s="15">
         <v>1010021733</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="15.75">
       <c r="A215" s="15">
         <v>1010011379</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" ht="15.75">
       <c r="A216" s="15">
         <v>1010003279</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" ht="15.75">
       <c r="A217" s="15">
         <v>1010011380</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" ht="15.75">
       <c r="A218" s="15">
         <v>351197</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" ht="15.75">
       <c r="A219" s="15">
         <v>1010011286</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" ht="15.75">
       <c r="A220" s="15">
         <v>2479</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" ht="15.75">
       <c r="A221" s="15">
         <v>1010011382</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" ht="15.75">
       <c r="A222" s="16">
         <v>1010055703</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" ht="15.75">
       <c r="A223" s="16">
         <v>4165</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" ht="15.75">
       <c r="A224" s="15">
         <v>301626</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" ht="15.75">
       <c r="A225" s="15">
         <v>429495</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" ht="15.75">
       <c r="A226" s="15">
         <v>162998</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" ht="15.75">
       <c r="A227" s="15">
         <v>432657</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" ht="15.75">
       <c r="A228" s="15">
         <v>1010021929</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" ht="15.75">
       <c r="A229" s="15">
         <v>428065</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="15.75">
       <c r="A230" s="15">
         <v>1010003404</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" ht="15.75">
       <c r="A231" s="15">
         <v>1010003322</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" ht="15.75">
       <c r="A232" s="15">
         <v>17738</v>
       </c>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="F232" s="29"/>
     </row>
-    <row r="233" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" ht="15.75">
       <c r="A233" s="15">
         <v>1010085360</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" ht="15.75">
       <c r="A234" s="15">
         <v>1040077391</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" ht="15.75">
       <c r="A235" s="15">
         <v>1010058624</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" ht="15.75">
       <c r="A236" s="15">
         <v>1010024661</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" ht="15.75">
       <c r="A237" s="15">
         <v>1040019315</v>
       </c>
@@ -4786,5793 +4786,5793 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" ht="15.75">
       <c r="A238" s="15">
         <v>1010021089</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>514</v>
+        <v>240</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" ht="15.75">
       <c r="A239" s="15">
         <v>1040017264</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" ht="15.75">
       <c r="A240" s="15">
         <v>1010051765</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" ht="15.75">
       <c r="A241" s="15">
         <v>1010035272</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" ht="15.75">
       <c r="A242" s="15">
         <v>1040077392</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" ht="15.75">
       <c r="A243" s="15">
         <v>1040077393</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" ht="15.75">
       <c r="A244" s="15">
         <v>1040077395</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" ht="15.75">
       <c r="A245" s="15">
         <v>1040077401</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" ht="15.75">
       <c r="A246" s="15">
         <v>27572</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" ht="15.75">
       <c r="A247" s="15">
         <v>18745</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" ht="15.75">
       <c r="A248" s="15">
         <v>1040077396</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" ht="15.75">
       <c r="A249" s="15">
         <v>1010036546</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" ht="15.75">
       <c r="A250" s="15">
         <v>1010014049</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" ht="15.75">
       <c r="A251" s="15">
         <v>1010025148</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" ht="15.75">
       <c r="A252" s="15">
         <v>1040077394</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" ht="15.75">
       <c r="A253" s="15">
         <v>1040077400</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" ht="15.75">
       <c r="A254" s="15">
         <v>1040079329</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" ht="15.75">
       <c r="A255" s="15">
         <v>1040040957</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" ht="15.75">
       <c r="A256" s="15">
         <v>1040077398</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" ht="15.75">
       <c r="A257" s="15">
         <v>1010053128</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" ht="15.75">
       <c r="A258" s="15">
         <v>1010010599</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" ht="15.75">
       <c r="A259" s="15">
         <v>1010056064</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" ht="15.75">
       <c r="A260" s="15">
         <v>5389</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" ht="15.75">
       <c r="A261" s="15">
         <v>1010055969</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" ht="15.75">
       <c r="A262" s="15">
         <v>1010055970</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" ht="15.75">
       <c r="A263" s="15">
         <v>181395</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" ht="15.75">
       <c r="A264" s="17">
         <v>1010055962</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" ht="15.75">
       <c r="A265" s="15">
         <v>1010003578</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" ht="15.75">
       <c r="A266" s="15">
         <v>332891</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" ht="15.75">
       <c r="A267" s="15">
         <v>17727</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" ht="15.75">
       <c r="A268" s="15">
         <v>17918</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" ht="15.75">
       <c r="A269" s="15">
         <v>1010020554</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" ht="15.75">
       <c r="A270" s="15">
         <v>1040085949</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" ht="15.75">
       <c r="A271" s="15">
         <v>1010062938</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" ht="15.75">
       <c r="A272" s="15">
         <v>1010062086</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" ht="15.75">
       <c r="A273" s="15">
         <v>1010062087</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" ht="15.75">
       <c r="A274" s="15">
         <v>1040077373</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" ht="15.75">
       <c r="A275" s="24">
         <v>1040077372</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" ht="15.75">
       <c r="A276" s="24">
         <v>1040097154</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" ht="15.75">
       <c r="A277" s="24">
         <v>1010042579</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" ht="15.75">
       <c r="A278" s="15">
-        <v>1010029427</v>
+        <v>1010081353</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" ht="15.75">
       <c r="A279" s="15">
         <v>133108</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" ht="15.75">
       <c r="A280" s="15">
         <v>269427</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" ht="15.75">
       <c r="A281" s="15">
         <v>298227</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C281" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" ht="15.75">
       <c r="A282" s="15">
         <v>1010062285</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" ht="15.75">
       <c r="A283" s="15">
         <v>1010058052</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" ht="15.75">
       <c r="A284" s="15">
         <v>1010050033</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" ht="15.75">
       <c r="A285" s="20">
         <v>1040098869</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" ht="15.75">
       <c r="A286" s="20">
         <v>1010056523</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" ht="15.75">
       <c r="A287" s="20">
         <v>1010062045</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" ht="15.75">
       <c r="A288" s="15">
         <v>1040097575</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" ht="15.75">
       <c r="A289" s="5">
         <v>1040100107</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" ht="15.75">
       <c r="A290" s="15">
         <v>1010040346</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" ht="15.75">
       <c r="A291" s="15">
         <v>1010021543</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" ht="15.75">
       <c r="A292" s="15">
         <v>1040077397</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" ht="15.75">
       <c r="A293" s="15">
         <v>1040094213</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" ht="15.75">
       <c r="A294" s="15">
         <v>1010085326</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" ht="15.75">
       <c r="A295" s="15">
         <v>1010042564</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" ht="15.75">
       <c r="A296" s="15">
         <v>1010042688</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" ht="15.75">
       <c r="A297" s="15">
         <v>1010040133</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C297" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" ht="15.75">
       <c r="A298" s="15">
         <v>1010039879</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" ht="15.75">
       <c r="A299" s="15">
         <v>62608</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" ht="15.75">
       <c r="A300" s="15">
         <v>1040098603</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" ht="15.75">
       <c r="A301" s="15">
         <v>1040017266</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" ht="15.75">
       <c r="A302" s="15">
         <v>1010063326</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" ht="15.75">
       <c r="A303" s="15">
         <v>1010050574</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" ht="15.75">
       <c r="A304" s="20">
         <v>1010086126</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" ht="15.75">
       <c r="A305" s="15">
         <v>1040019838</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" ht="15.75">
       <c r="A306" s="15">
         <v>1010042882</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" ht="15.75">
       <c r="A307" s="15">
         <v>1010042873</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" ht="15.75">
       <c r="A308" s="15">
         <v>1010026842</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" ht="15.75">
       <c r="A309" s="15">
         <v>1010026841</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" ht="15.75">
       <c r="A310" s="15">
         <v>1010059549</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" ht="15.75">
       <c r="A311" s="15">
         <v>1010020552</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" ht="15.75">
       <c r="A312" s="15">
         <v>1040078895</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" ht="15.75">
       <c r="A313" s="15">
         <v>1040024309</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" ht="15.75">
       <c r="A314" s="15">
         <v>1040024323</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" ht="15.75">
       <c r="A315" s="15">
         <v>1040024322</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" ht="15.75">
       <c r="A316" s="15">
         <v>1010087245</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" ht="15.75">
       <c r="A317" s="15">
         <v>1010059685</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" ht="15.75">
       <c r="A318" s="15">
         <v>1010059687</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" ht="15.75">
       <c r="A319" s="15">
         <v>1010077469</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" ht="15.75">
       <c r="A320" s="19">
         <v>1010077470</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" ht="15.75">
       <c r="A321" s="15">
         <v>1010084519</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" ht="15.75">
       <c r="A322" s="14">
         <v>1010084108</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C322" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" ht="15.75">
       <c r="A323" s="14">
         <v>1010042884</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" ht="15.75">
       <c r="A324" s="15">
         <v>1040043537</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" ht="15.75">
       <c r="A325" s="15">
         <v>1010046401</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" ht="15.75">
       <c r="A326" s="15">
         <v>1010062007</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" ht="15.75">
       <c r="A327" s="15">
         <v>1010051284</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" ht="15.75">
       <c r="A328" s="15">
         <v>1010027788</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" ht="15.75">
       <c r="A329" s="15">
         <v>1010027786</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" ht="15.75">
       <c r="A330" s="15">
         <v>1010026889</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" ht="15.75">
       <c r="A331" s="24">
         <v>1010042358</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" ht="15.75">
       <c r="A332" s="15">
         <v>1040023848</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" ht="15.75">
       <c r="A333" s="15">
         <v>1010042341</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" ht="15.75">
       <c r="A334" s="15">
         <v>1040023858</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" ht="15.75">
       <c r="A335" s="15">
         <v>1040098396</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" ht="15.75">
       <c r="A336" s="15">
         <v>1010087281</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" ht="15.75">
       <c r="A337" s="15">
         <v>1040041006</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" ht="15.75">
       <c r="A338" s="15">
         <v>1040101931</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" ht="15.75">
       <c r="A339" s="15">
         <v>1040023843</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C339" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" ht="15.75">
       <c r="A340" s="15">
         <v>1040077411</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" ht="15.75">
       <c r="A341" s="15">
         <v>1040077410</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C341" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" ht="15.75">
       <c r="A342" s="15">
         <v>1010062008</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" ht="15.75">
       <c r="A343" s="19">
         <v>1040040960</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" ht="15.75">
       <c r="A344" s="15">
         <v>1010031536</v>
       </c>
       <c r="B344" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" ht="15.75">
       <c r="A345" s="15">
         <v>1010031545</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" ht="15.75">
       <c r="A346" s="30">
         <v>1010084767</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" ht="15.75">
       <c r="A347" s="15">
         <v>1040077360</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" ht="15.75">
       <c r="A348" s="15">
         <v>1010064470</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" ht="15.75">
       <c r="A349" s="15">
         <v>1010021991</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" ht="15.75">
       <c r="A350" s="15">
         <v>1010021960</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" ht="15.75">
       <c r="A351" s="15">
         <v>1010031690</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" ht="15.75">
       <c r="A352" s="15">
         <v>1010022590</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" ht="15.75">
       <c r="A353" s="15">
         <v>1040098643</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" ht="15.75">
       <c r="A354" s="15">
         <v>1010086020</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" ht="15.75">
       <c r="A355" s="15">
         <v>1010046550</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" ht="15.75">
       <c r="A356" s="15">
         <v>1010046402</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" ht="15.75">
       <c r="A357" s="15">
         <v>1010060291</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" ht="15.75">
       <c r="A358" s="15">
         <v>1010050920</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" ht="15.75">
       <c r="A359" s="15">
         <v>1040077412</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" ht="15.75">
       <c r="A360" s="15">
         <v>1010042609</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" ht="15.75">
       <c r="A361" s="15">
         <v>417701</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" ht="15.75">
       <c r="A362" s="15">
         <v>399384</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" ht="15.75">
       <c r="A363" s="15">
         <v>1010024086</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" ht="15.75">
       <c r="A364" s="15">
         <v>1040077345</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" ht="15.75">
       <c r="A365" s="15">
         <v>1010084315</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" ht="15.75">
       <c r="A366" s="15">
         <v>399253</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" ht="15.75">
       <c r="A367" s="15">
         <v>1010084317</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" ht="15.75">
       <c r="A368" s="25">
         <v>1010085369</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" ht="15.75">
       <c r="A369" s="15">
         <v>1010085370</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" ht="15.75">
       <c r="A370" s="15">
         <v>1010085204</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" ht="15.75">
       <c r="A371" s="15">
         <v>1010003966</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" ht="15.75">
       <c r="A372" s="15">
         <v>1010003967</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" ht="15.75">
       <c r="A373" s="15">
         <v>65219</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C373" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" ht="15.75">
       <c r="A374" s="15">
         <v>10168</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" ht="15.75">
       <c r="A375" s="15">
         <v>1010083792</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" ht="15.75">
       <c r="A376" s="15">
         <v>1040077414</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" ht="15.75">
       <c r="A377" s="15">
         <v>1010018482</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" ht="15.75">
       <c r="A378" s="15">
         <v>1010084320</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" ht="15.75">
       <c r="A379" s="15">
         <v>1010084532</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" ht="15.75">
       <c r="A380" s="15">
         <v>1010027285</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" ht="15.75">
       <c r="A381" s="15">
         <v>1040077413</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" ht="15.75">
       <c r="A382" s="15">
         <v>1010085376</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" ht="15.75">
       <c r="A383" s="15">
         <v>1010022819</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C383" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" ht="15.75">
       <c r="A384" s="15">
         <v>1010052853</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" ht="15.75">
       <c r="A385" s="15">
         <v>1010084377</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" ht="15.75">
       <c r="A386" s="26">
         <v>1010062826</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" ht="15.75">
       <c r="A387" s="15">
         <v>1010002592</v>
       </c>
       <c r="B387" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C387" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="C387" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="1:3" ht="15.75">
       <c r="A388" s="24">
         <v>1010001155</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="15.75">
       <c r="A389" s="15">
         <v>1010001062</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" ht="15.75">
       <c r="A390" s="15">
         <v>1010084328</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" ht="15.75">
       <c r="A391" s="24">
         <v>1010044502</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" ht="15.75">
       <c r="A392" s="15">
         <v>1010053692</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" ht="15.75">
       <c r="A393" s="15">
         <v>1010083992</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" ht="15.75">
       <c r="A394" s="15">
         <v>1010008578</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" ht="15.75">
       <c r="A395" s="15">
         <v>1010031694</v>
       </c>
       <c r="B395" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C395" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="C395" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="1:3" ht="15.75">
       <c r="A396" s="15">
         <v>1010051997</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" ht="15.75">
       <c r="A397" s="15">
         <v>1010022601</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" ht="15.75">
       <c r="A398" s="15">
         <v>1010054278</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" ht="15.75">
       <c r="A399" s="15">
         <v>1010083462</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" ht="15.75">
       <c r="A400" s="15">
         <v>1010027772</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" ht="15.75">
       <c r="A401" s="15">
         <v>1010084144</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="15.75">
       <c r="A402" s="19">
         <v>1010084958</v>
       </c>
       <c r="B402" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" ht="15.75">
       <c r="A403" s="19">
         <v>1010084720</v>
       </c>
       <c r="B403" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D403" s="29"/>
     </row>
-    <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" ht="15.75">
       <c r="A404" s="18">
         <v>1010021956</v>
       </c>
       <c r="B404" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="15.75">
       <c r="A405" s="18">
         <v>1010026464</v>
       </c>
       <c r="B405" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" ht="15.75">
       <c r="A406" s="14">
         <v>1010021957</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" ht="15.75">
       <c r="A407" s="15">
         <v>1010026462</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" ht="15.75">
       <c r="A408" s="15">
         <v>1010026551</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" ht="15.75">
       <c r="A409" s="15">
         <v>1010042554</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" ht="15.75">
       <c r="A410" s="15">
         <v>1010039904</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="15.75">
       <c r="A411" s="15">
         <v>1010060205</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" ht="15.75">
       <c r="A412" s="15">
         <v>1010060206</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" ht="15.75">
       <c r="A413" s="15">
         <v>1010077431</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" ht="15.75">
       <c r="A414" s="15">
         <v>1010077503</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" ht="15.75">
       <c r="A415" s="15">
         <v>1010084187</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="15.75">
       <c r="A416" s="15">
         <v>1010080958</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="15.75">
       <c r="A417" s="15">
         <v>1010026032</v>
       </c>
       <c r="B417" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="15.75">
       <c r="A418" s="15">
         <v>1010085384</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="15.75">
       <c r="A419" s="15">
         <v>1010006347</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="15.75">
       <c r="A420" s="15">
         <v>1010085179</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="15.75">
       <c r="A421" s="15">
         <v>1010024158</v>
       </c>
       <c r="B421" s="8" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" ht="15.75">
       <c r="A422" s="15">
         <v>1010024131</v>
       </c>
       <c r="B422" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="15.75">
       <c r="A423" s="15">
         <v>1010007160</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="15.75">
       <c r="A424" s="15">
         <v>1010023642</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" ht="15.75">
       <c r="A425" s="15">
         <v>1010007193</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="15.75">
       <c r="A426" s="15">
         <v>1010042637</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" ht="15.75">
       <c r="A427" s="15">
         <v>1040075323</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3" ht="15.75">
       <c r="A428" s="15">
         <v>1040075324</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" ht="15.75">
       <c r="A429" s="27">
         <v>1040074827</v>
       </c>
       <c r="B429" s="8" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="15.75">
       <c r="A430" s="27">
         <v>1040099488</v>
       </c>
       <c r="B430" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="15.75">
       <c r="A431" s="27">
         <v>1040083312</v>
       </c>
       <c r="B431" s="8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" ht="15.75">
       <c r="A432" s="27">
         <v>1040077661</v>
       </c>
       <c r="B432" s="8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" ht="15.75">
       <c r="A433" s="27">
         <v>1010085180</v>
       </c>
       <c r="B433" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" ht="15.75">
       <c r="A434" s="14">
         <v>1040017489</v>
       </c>
       <c r="B434" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" ht="15.75">
       <c r="A435" s="14">
         <v>1010085181</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" ht="15.75">
       <c r="A436" s="15">
         <v>400175</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" ht="15.75">
       <c r="A437" s="15">
         <v>1040017505</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" ht="15.75">
       <c r="A438" s="15">
         <v>1040017503</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" ht="15.75">
       <c r="A439" s="15">
         <v>1010046445</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" ht="15.75">
       <c r="A440" s="15">
         <v>1010021033</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" ht="15.75">
       <c r="A441" s="15">
         <v>1010057142</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" ht="15.75">
       <c r="A442" s="15">
         <v>1010016356</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" ht="15.75">
       <c r="A443" s="15">
         <v>1010084363</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" ht="15.75">
       <c r="A444" s="15">
         <v>1010052021</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" ht="15.75">
       <c r="A445" s="15">
         <v>1040091721</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" ht="15.75">
       <c r="A446" s="15">
         <v>1010062022</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" ht="15.75">
       <c r="A447" s="15">
         <v>18336</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" ht="15.75">
       <c r="A448" s="15">
         <v>229205</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" ht="15.75">
       <c r="A449" s="15">
         <v>60671</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" ht="15.75">
       <c r="A450" s="15">
         <v>1010059726</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" ht="15.75">
       <c r="A451" s="15">
         <v>1010008144</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" ht="15.75">
       <c r="A452" s="15">
         <v>1010007244</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" ht="15.75">
       <c r="A453" s="15">
         <v>1010006827</v>
       </c>
       <c r="B453" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" ht="15.75">
       <c r="A454" s="15">
         <v>1040075426</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" ht="15.75">
       <c r="A455" s="15">
         <v>1040075427</v>
       </c>
       <c r="B455" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" ht="15.75">
       <c r="A456" s="15">
         <v>1010084313</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" ht="15.75">
       <c r="A457" s="15">
         <v>403459</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" ht="15.75">
       <c r="A458" s="15">
         <v>1010044828</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" ht="15.75">
       <c r="A459" s="15">
         <v>1010026973</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" ht="15.75">
       <c r="A460" s="15">
         <v>1040017204</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" ht="15.75">
       <c r="A461" s="24">
         <v>1010022119</v>
       </c>
       <c r="B461" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" ht="15.75">
       <c r="A462" s="15">
         <v>1010058709</v>
       </c>
       <c r="B462" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C462" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="C462" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="463" spans="1:3" ht="15.75">
       <c r="A463" s="15">
         <v>1010025711</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" ht="15.75">
       <c r="A464" s="15">
         <v>1010059684</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" ht="15.75">
       <c r="A465" s="15">
         <v>427341</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" ht="15.75">
       <c r="A466" s="15">
         <v>392696</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" ht="15.75">
       <c r="A467" s="15">
         <v>1010085279</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" ht="15.75">
       <c r="A468" s="19">
         <v>1010022588</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" ht="15.75">
       <c r="A469" s="15">
         <v>1010026864</v>
       </c>
       <c r="B469" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" ht="15.75">
       <c r="A470" s="14">
         <v>1010030946</v>
       </c>
       <c r="B470" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" ht="15.75">
       <c r="A471" s="14">
         <v>1010022589</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" ht="15.75">
       <c r="A472" s="15">
         <v>1040090143</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="15.75">
       <c r="A473" s="15">
         <v>1040090138</v>
       </c>
       <c r="B473" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="15.75">
       <c r="A474" s="15">
         <v>1030001314</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" ht="15.75">
       <c r="A475" s="15">
         <v>1010052319</v>
       </c>
       <c r="B475" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" ht="15.75">
       <c r="A476" s="15">
         <v>1010052320</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" ht="15.75">
       <c r="A477" s="15">
         <v>1030000370</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" ht="15.75">
       <c r="A478" s="15">
         <v>1030000366</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="15.75">
       <c r="A479" s="15">
         <v>1030000368</v>
       </c>
       <c r="B479" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="15.75">
       <c r="A480" s="15">
         <v>1030000369</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" ht="15.75">
       <c r="A481" s="15">
         <v>1030000489</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" ht="15.75">
       <c r="A482" s="15">
         <v>1030000490</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" ht="15.75">
       <c r="A483" s="15">
         <v>1030000821</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" ht="15.75">
       <c r="A484" s="15">
         <v>1030000511</v>
       </c>
       <c r="B484" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" ht="15.75">
       <c r="A485" s="16">
         <v>1010084279</v>
       </c>
       <c r="B485" s="8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" ht="15.75">
       <c r="A486" s="16">
         <v>1010004281</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" ht="15.75">
       <c r="A487" s="15">
         <v>1010022118</v>
       </c>
       <c r="B487" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" ht="15.75">
       <c r="A488" s="15">
         <v>1010028657</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" ht="15.75">
       <c r="A489" s="18">
         <v>1010028655</v>
       </c>
       <c r="B489" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C489" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="C489" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:3" ht="15.75">
       <c r="A490" s="18">
         <v>145165</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" ht="15.75">
       <c r="A491" s="15">
         <v>51666</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" ht="15.75">
       <c r="A492" s="18">
         <v>1010080930</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" ht="15.75">
       <c r="A493" s="15">
         <v>161055</v>
       </c>
       <c r="B493" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" ht="15.75">
       <c r="A494" s="15">
         <v>1010050517</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" ht="15.75">
       <c r="A495" s="15">
         <v>1010084190</v>
       </c>
       <c r="B495" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" ht="15.75">
       <c r="A496" s="15">
         <v>1010084195</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" ht="15.75">
       <c r="A497" s="15">
         <v>1010001400</v>
       </c>
       <c r="B497" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" ht="15.75">
       <c r="A498" s="17">
         <v>1010008416</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" ht="15.75">
       <c r="A499" s="28">
         <v>1010018372</v>
       </c>
       <c r="B499" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" ht="15.75">
       <c r="A500" s="28">
         <v>1010018361</v>
       </c>
       <c r="B500" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" ht="15.75">
       <c r="A501" s="16">
         <v>1010055398</v>
       </c>
       <c r="B501" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C501" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" ht="15.75">
       <c r="A502" s="15">
         <v>422131</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" ht="15.75">
       <c r="A503" s="15">
         <v>1010084370</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" ht="15.75">
       <c r="A504" s="15">
         <v>422759</v>
       </c>
       <c r="B504" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" ht="15.75">
       <c r="A505" s="15">
         <v>120955</v>
       </c>
       <c r="B505" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C505" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" ht="15.75">
       <c r="A506" s="15">
         <v>1010000896</v>
       </c>
       <c r="B506" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C506" s="13" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" ht="15.75">
       <c r="A507" s="15">
         <v>1010084308</v>
       </c>
       <c r="B507" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C507" s="13" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" ht="15.75">
       <c r="A508" s="15">
         <v>1010084035</v>
       </c>
       <c r="B508" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C508" s="13" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" ht="15.75">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
     </row>
-    <row r="510" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" ht="15.75">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
     </row>
-    <row r="511" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" ht="15.75">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
     </row>
-    <row r="512" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" ht="15.75">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
     </row>
-    <row r="513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" ht="15.75">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
     </row>
-    <row r="514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" ht="15.75">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
     </row>
-    <row r="515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" ht="15.75">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
     </row>
-    <row r="516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" ht="15.75">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
     </row>
-    <row r="517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" ht="15.75">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
     </row>
-    <row r="518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" ht="15.75">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
     </row>
-    <row r="519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" ht="15.75">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
     </row>
-    <row r="520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" ht="15.75">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
     </row>
-    <row r="521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" ht="15.75">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
     </row>
-    <row r="522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" ht="15.75">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" ht="15.75">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
     </row>
-    <row r="524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" ht="15.75">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
     </row>
-    <row r="525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" ht="15.75">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
     </row>
-    <row r="526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" ht="15.75">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
     </row>
-    <row r="527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" ht="15.75">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
     </row>
-    <row r="528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" ht="15.75">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
     </row>
-    <row r="529" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:2" ht="15.75">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
     </row>
-    <row r="530" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:2" ht="15.75">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
     </row>
-    <row r="531" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:2" ht="15.75">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
     </row>
-    <row r="532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:2" ht="15.75">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
     </row>
-    <row r="533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:2" ht="15.75">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
     </row>
-    <row r="534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:2" ht="15.75">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
     </row>
-    <row r="535" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:2" ht="15.75">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
     </row>
-    <row r="536" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:2" ht="15.75">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
     </row>
-    <row r="537" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:2" ht="15.75">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
     </row>
-    <row r="538" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:2" ht="15.75">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
     </row>
-    <row r="539" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:2" ht="15.75">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
     </row>
-    <row r="540" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:2" ht="15.75">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
     </row>
-    <row r="541" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:2" ht="15.75">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
     </row>
-    <row r="542" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:2" ht="15.75">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
     </row>
-    <row r="543" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:2" ht="15.75">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
     </row>
-    <row r="544" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:2" ht="15.75">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
     </row>
-    <row r="545" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:2" ht="15.75">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
     </row>
-    <row r="546" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:2" ht="15.75">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
     </row>
-    <row r="547" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:2" ht="15.75">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
     </row>
-    <row r="548" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:2" ht="15.75">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
     </row>
-    <row r="549" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:2" ht="15.75">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
     </row>
-    <row r="550" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:2" ht="15.75">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
     </row>
-    <row r="551" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:2" ht="15.75">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
     </row>
-    <row r="552" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:2" ht="15.75">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
     </row>
-    <row r="553" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:2" ht="15.75">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
     </row>
-    <row r="554" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:2" ht="15.75">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
     </row>
-    <row r="555" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:2" ht="15.75">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
     </row>
-    <row r="556" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:2" ht="15.75">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
     </row>
-    <row r="557" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:2" ht="15.75">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
     </row>
-    <row r="558" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:2" ht="15.75">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
     </row>
-    <row r="559" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:2" ht="15.75">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
     </row>
-    <row r="560" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:2" ht="15.75">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
     </row>
-    <row r="561" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:2" ht="15.75">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
     </row>
-    <row r="562" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:2" ht="15.75">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
     </row>
-    <row r="563" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:2" ht="15.75">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
     </row>
-    <row r="564" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:2" ht="15.75">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
     </row>
-    <row r="565" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:2" ht="15.75">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
     </row>
-    <row r="566" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:2" ht="15.75">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
     </row>
-    <row r="567" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:2" ht="15.75">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
     </row>
-    <row r="568" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:2" ht="15.75">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
     </row>
-    <row r="569" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:2" ht="15.75">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
     </row>
-    <row r="570" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:2" ht="15.75">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
     </row>
-    <row r="571" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:2" ht="15.75">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
     </row>
-    <row r="572" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:2" ht="15.75">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
     </row>
-    <row r="573" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:2" ht="15.75">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
     </row>
-    <row r="574" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:2" ht="15.75">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
     </row>
-    <row r="575" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:2" ht="15.75">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
     </row>
-    <row r="576" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:2" ht="15.75">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
     </row>
-    <row r="577" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:2" ht="15.75">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
     </row>
-    <row r="578" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:2" ht="15.75">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
     </row>
-    <row r="579" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:2" ht="15.75">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
     </row>
-    <row r="580" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:2" ht="15.75">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
     </row>
-    <row r="581" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:2" ht="15.75">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
     </row>
-    <row r="582" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:2" ht="15.75">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
     </row>
-    <row r="583" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:2" ht="15.75">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
     </row>
-    <row r="584" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:2" ht="15.75">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
     </row>
-    <row r="585" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:2" ht="15.75">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
     </row>
-    <row r="586" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:2" ht="15.75">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
     </row>
-    <row r="587" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:2" ht="15.75">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
     </row>
-    <row r="588" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:2" ht="15.75">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
     </row>
-    <row r="589" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:2" ht="15.75">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
     </row>
-    <row r="590" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:2" ht="15.75">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
     </row>
-    <row r="591" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:2" ht="15.75">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
     </row>
-    <row r="592" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:2" ht="15.75">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
     </row>
-    <row r="593" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:2" ht="15.75">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
     </row>
-    <row r="594" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:2" ht="15.75">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
     </row>
-    <row r="595" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:2" ht="15.75">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
     </row>
-    <row r="596" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:2" ht="15.75">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
     </row>
-    <row r="597" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:2" ht="15.75">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
     </row>
-    <row r="598" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:2" ht="15.75">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
     </row>
-    <row r="599" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:2" ht="15.75">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
     </row>
-    <row r="600" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:2" ht="15.75">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
     </row>
-    <row r="601" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:2" ht="15.75">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
     </row>
-    <row r="602" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:2" ht="15.75">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
     </row>
-    <row r="603" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:2" ht="15.75">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
     </row>
-    <row r="604" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:2" ht="15.75">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
     </row>
-    <row r="605" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:2" ht="15.75">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
     </row>
-    <row r="606" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:2" ht="15.75">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
     </row>
-    <row r="607" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:2" ht="15.75">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
     </row>
-    <row r="608" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:2" ht="15.75">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
     </row>
-    <row r="609" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:2" ht="15.75">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
     </row>
-    <row r="610" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:2" ht="15.75">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
     </row>
-    <row r="611" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:2" ht="15.75">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
     </row>
-    <row r="612" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:2" ht="15.75">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
     </row>
-    <row r="613" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:2" ht="15.75">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
     </row>
-    <row r="614" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:2" ht="15.75">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
     </row>
-    <row r="615" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:2" ht="15.75">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
     </row>
-    <row r="616" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:2" ht="15.75">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
     </row>
-    <row r="617" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:2" ht="15.75">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
     </row>
-    <row r="618" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:2" ht="15.75">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
     </row>
-    <row r="619" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:2" ht="15.75">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
     </row>
-    <row r="620" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:2" ht="15.75">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
     </row>
-    <row r="621" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:2" ht="15.75">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
     </row>
-    <row r="622" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:2" ht="15.75">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
     </row>
-    <row r="623" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:2" ht="15.75">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
     </row>
-    <row r="624" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:2" ht="15.75">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
     </row>
-    <row r="625" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:2" ht="15.75">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
     </row>
-    <row r="626" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:2" ht="15.75">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
     </row>
-    <row r="627" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:2" ht="15.75">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:2" ht="15.75">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
     </row>
-    <row r="629" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:2" ht="15.75">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
     </row>
-    <row r="630" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:2" ht="15.75">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
     </row>
-    <row r="631" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:2" ht="15.75">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
     </row>
-    <row r="632" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:2" ht="15.75">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
     </row>
-    <row r="633" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:2" ht="15.75">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
     </row>
-    <row r="634" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:2" ht="15.75">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
     </row>
-    <row r="635" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:2" ht="15.75">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
     </row>
-    <row r="636" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:2" ht="15.75">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
     </row>
-    <row r="637" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:2" ht="15.75">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
     </row>
-    <row r="638" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:2" ht="15.75">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
     </row>
-    <row r="639" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:2" ht="15.75">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
     </row>
-    <row r="640" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:2" ht="15.75">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
     </row>
-    <row r="641" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:2" ht="15.75">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
     </row>
-    <row r="642" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:2" ht="15.75">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
     </row>
-    <row r="643" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:2" ht="15.75">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
     </row>
-    <row r="644" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:2" ht="15.75">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
     </row>
-    <row r="645" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:2" ht="15.75">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
     </row>
-    <row r="646" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:2" ht="15.75">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
     </row>
-    <row r="647" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:2" ht="15.75">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
     </row>
-    <row r="648" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:2" ht="15.75">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
     </row>
-    <row r="649" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:2" ht="15.75">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
     </row>
-    <row r="650" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:2" ht="15.75">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
     </row>
-    <row r="651" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:2" ht="15.75">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
     </row>
-    <row r="652" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:2" ht="15.75">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
     </row>
-    <row r="653" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:2" ht="15.75">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
     </row>
-    <row r="654" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:2" ht="15.75">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
     </row>
-    <row r="655" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:2" ht="15.75">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
     </row>
-    <row r="656" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:2" ht="15.75">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
     </row>
-    <row r="657" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:2" ht="15.75">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
     </row>
-    <row r="658" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:2" ht="15.75">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
     </row>
-    <row r="659" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:2" ht="15.75">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
     </row>
-    <row r="660" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:2" ht="15.75">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
     </row>
-    <row r="661" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:2" ht="15.75">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
     </row>
-    <row r="662" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:2" ht="15.75">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
     </row>
-    <row r="663" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:2" ht="15.75">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
     </row>
-    <row r="664" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:2" ht="15.75">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
     </row>
-    <row r="665" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:2" ht="15.75">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
     </row>
-    <row r="666" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:2" ht="15.75">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
     </row>
-    <row r="667" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:2" ht="15.75">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
     </row>
-    <row r="668" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:2" ht="15.75">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
     </row>
-    <row r="669" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:2" ht="15.75">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
     </row>
-    <row r="670" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:2" ht="15.75">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
     </row>
-    <row r="671" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:2" ht="15.75">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
     </row>
-    <row r="672" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:2" ht="15.75">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
     </row>
-    <row r="673" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:2" ht="15.75">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
     </row>
-    <row r="674" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:2" ht="15.75">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
     </row>
-    <row r="675" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:2" ht="15.75">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
     </row>
-    <row r="676" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:2" ht="15.75">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
     </row>
-    <row r="677" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:2" ht="15.75">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
     </row>
-    <row r="678" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:2" ht="15.75">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
     </row>
-    <row r="679" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:2" ht="15.75">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
     </row>
-    <row r="680" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:2" ht="15.75">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
     </row>
-    <row r="681" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:2" ht="15.75">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
     </row>
-    <row r="682" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:2" ht="15.75">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
     </row>
-    <row r="683" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:2" ht="15.75">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
     </row>
-    <row r="684" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:2" ht="15.75">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
     </row>
-    <row r="685" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:2" ht="15.75">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
     </row>
-    <row r="686" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:2" ht="15.75">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
     </row>
-    <row r="687" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:2" ht="15.75">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
     </row>
-    <row r="688" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:2" ht="15.75">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
     </row>
-    <row r="689" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:2" ht="15.75">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
     </row>
-    <row r="690" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:2" ht="15.75">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
     </row>
-    <row r="691" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:2" ht="15.75">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
     </row>
-    <row r="692" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:2" ht="15.75">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
     </row>
-    <row r="693" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:2" ht="15.75">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
     </row>
-    <row r="694" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:2" ht="15.75">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
     </row>
-    <row r="695" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:2" ht="15.75">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
     </row>
-    <row r="696" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:2" ht="15.75">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
     </row>
-    <row r="697" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:2" ht="15.75">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
     </row>
-    <row r="698" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:2" ht="15.75">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
     </row>
-    <row r="699" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:2" ht="15.75">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
     </row>
-    <row r="700" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:2" ht="15.75">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
     </row>
-    <row r="701" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:2" ht="15.75">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
     </row>
-    <row r="702" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:2" ht="15.75">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
     </row>
-    <row r="703" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:2" ht="15.75">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
     </row>
-    <row r="704" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:2" ht="15.75">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
     </row>
-    <row r="705" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:2" ht="15.75">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
     </row>
-    <row r="706" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:2" ht="15.75">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
     </row>
-    <row r="707" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:2" ht="15.75">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
     </row>
-    <row r="708" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:2" ht="15.75">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
     </row>
-    <row r="709" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:2" ht="15.75">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
     </row>
-    <row r="710" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:2" ht="15.75">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
     </row>
-    <row r="711" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:2" ht="15.75">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
     </row>
-    <row r="712" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:2" ht="15.75">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
     </row>
-    <row r="713" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:2" ht="15.75">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
     </row>
-    <row r="714" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:2" ht="15.75">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
     </row>
-    <row r="715" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:2" ht="15.75">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
     </row>
-    <row r="716" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:2" ht="15.75">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
     </row>
-    <row r="717" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:2" ht="15.75">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
     </row>
-    <row r="718" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:2" ht="15.75">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
     </row>
-    <row r="719" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:2" ht="15.75">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
     </row>
-    <row r="720" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:2" ht="15.75">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
     </row>
-    <row r="721" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:2" ht="15.75">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
     </row>
-    <row r="722" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:2" ht="15.75">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
     </row>
-    <row r="723" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:2" ht="15.75">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
     </row>
-    <row r="724" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:2" ht="15.75">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
     </row>
-    <row r="725" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:2" ht="15.75">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
     </row>
-    <row r="726" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:2" ht="15.75">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
     </row>
-    <row r="727" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:2" ht="15.75">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
     </row>
-    <row r="728" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:2" ht="15.75">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
     </row>
-    <row r="729" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:2" ht="15.75">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
     </row>
-    <row r="730" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:2" ht="15.75">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
     </row>
-    <row r="731" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:2" ht="15.75">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
     </row>
-    <row r="732" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:2" ht="15.75">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
     </row>
-    <row r="733" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:2" ht="15.75">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
     </row>
-    <row r="734" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:2" ht="15.75">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
     </row>
-    <row r="735" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:2" ht="15.75">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
     </row>
-    <row r="736" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:2" ht="15.75">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
     </row>
-    <row r="737" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:2" ht="15.75">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
     </row>
-    <row r="738" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:2" ht="15.75">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
     </row>
-    <row r="739" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:2" ht="15.75">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
     </row>
-    <row r="740" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:2" ht="15.75">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
     </row>
-    <row r="741" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:2" ht="15.75">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
     </row>
-    <row r="742" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:2" ht="15.75">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
     </row>
-    <row r="743" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:2" ht="15.75">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
     </row>
-    <row r="744" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:2" ht="15.75">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
     </row>
-    <row r="745" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:2" ht="15.75">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
     </row>
-    <row r="746" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:2" ht="15.75">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
     </row>
-    <row r="747" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:2" ht="15.75">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
     </row>
-    <row r="748" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:2" ht="15.75">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
     </row>
-    <row r="749" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:2" ht="15.75">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
     </row>
-    <row r="750" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:2" ht="15.75">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
     </row>
-    <row r="751" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:2" ht="15.75">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
     </row>
-    <row r="752" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:2" ht="15.75">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
     </row>
-    <row r="753" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:2" ht="15.75">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
     </row>
-    <row r="754" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:2" ht="15.75">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
     </row>
-    <row r="755" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:2" ht="15.75">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
     </row>
-    <row r="756" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:2" ht="15.75">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
     </row>
-    <row r="757" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:2" ht="15.75">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
     </row>
-    <row r="758" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:2" ht="15.75">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
     </row>
-    <row r="759" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:2" ht="15.75">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
     </row>
-    <row r="760" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:2" ht="15.75">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
     </row>
-    <row r="761" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:2" ht="15.75">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
     </row>
-    <row r="762" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:2" ht="15.75">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
     </row>
-    <row r="763" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:2" ht="15.75">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
     </row>
-    <row r="764" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:2" ht="15.75">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
     </row>
-    <row r="765" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:2" ht="15.75">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
     </row>
-    <row r="766" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:2" ht="15.75">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
     </row>
-    <row r="767" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:2" ht="15.75">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
     </row>
-    <row r="768" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:2" ht="15.75">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
     </row>
-    <row r="769" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:2" ht="15.75">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
     </row>
-    <row r="770" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:2" ht="15.75">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
     </row>
-    <row r="771" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:2" ht="15.75">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
     </row>
-    <row r="772" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:2" ht="15.75">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
     </row>
-    <row r="773" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:2" ht="15.75">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
     </row>
-    <row r="774" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:2" ht="15.75">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
     </row>
-    <row r="775" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:2" ht="15.75">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
     </row>
-    <row r="776" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:2" ht="15.75">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
     </row>
-    <row r="777" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:2" ht="15.75">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
     </row>
-    <row r="778" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:2" ht="15.75">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
     </row>
-    <row r="779" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:2" ht="15.75">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
     </row>
-    <row r="780" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:2" ht="15.75">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
     </row>
-    <row r="781" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:2" ht="15.75">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
     </row>
-    <row r="782" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:2" ht="15.75">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
     </row>
-    <row r="783" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:2" ht="15.75">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
     </row>
-    <row r="784" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:2" ht="15.75">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
     </row>
-    <row r="785" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:2" ht="15.75">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
     </row>
-    <row r="786" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:2" ht="15.75">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
     </row>
-    <row r="787" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:2" ht="15.75">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
     </row>
-    <row r="788" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:2" ht="15.75">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
     </row>
-    <row r="789" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:2" ht="15.75">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
     </row>
-    <row r="790" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:2" ht="15.75">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
     </row>
-    <row r="791" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:2" ht="15.75">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
     </row>
-    <row r="792" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:2" ht="15.75">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
     </row>
-    <row r="793" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:2" ht="15.75">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
     </row>
-    <row r="794" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:2" ht="15.75">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
     </row>
-    <row r="795" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:2" ht="15.75">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
     </row>
-    <row r="796" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:2" ht="15.75">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
     </row>
-    <row r="797" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:2" ht="15.75">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
     </row>
-    <row r="798" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:2" ht="15.75">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
     </row>
-    <row r="799" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:2" ht="15.75">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
     </row>
-    <row r="800" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:2" ht="15.75">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
     </row>
-    <row r="801" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:2" ht="15.75">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
     </row>
-    <row r="802" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:2" ht="15.75">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
     </row>
-    <row r="803" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:2" ht="15.75">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
     </row>
-    <row r="804" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:2" ht="15.75">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
     </row>
-    <row r="805" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:2" ht="15.75">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
     </row>
-    <row r="806" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:2" ht="15.75">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
     </row>
-    <row r="807" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:2" ht="15.75">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
     </row>
-    <row r="808" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:2" ht="15.75">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
     </row>
-    <row r="809" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:2" ht="15.75">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
     </row>
-    <row r="810" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:2" ht="15.75">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
     </row>
-    <row r="811" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:2" ht="15.75">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
     </row>
-    <row r="812" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:2" ht="15.75">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
     </row>
-    <row r="813" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:2" ht="15.75">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
     </row>
-    <row r="814" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:2" ht="15.75">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
     </row>
-    <row r="815" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:2" ht="15.75">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
     </row>
-    <row r="816" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:2" ht="15.75">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
     </row>
-    <row r="817" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:2" ht="15.75">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
     </row>
-    <row r="818" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:2" ht="15.75">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
     </row>
-    <row r="819" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:2" ht="15.75">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
     </row>
-    <row r="820" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:2" ht="15.75">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
     </row>
-    <row r="821" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:2" ht="15.75">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
     </row>
-    <row r="822" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:2" ht="15.75">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
     </row>
-    <row r="823" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:2" ht="15.75">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
     </row>
-    <row r="824" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:2" ht="15.75">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
     </row>
-    <row r="825" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:2" ht="15.75">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
     </row>
-    <row r="826" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:2" ht="15.75">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
     </row>
-    <row r="827" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:2" ht="15.75">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
     </row>
-    <row r="828" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:2" ht="15.75">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
     </row>
-    <row r="829" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:2" ht="15.75">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
     </row>
-    <row r="830" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:2" ht="15.75">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
     </row>
-    <row r="831" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:2" ht="15.75">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
     </row>
-    <row r="832" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:2" ht="15.75">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
     </row>
-    <row r="833" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:2" ht="15.75">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
     </row>
-    <row r="834" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:2" ht="15.75">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
     </row>
-    <row r="835" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:2" ht="15.75">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
     </row>
-    <row r="836" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:2" ht="15.75">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
     </row>
-    <row r="837" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:2" ht="15.75">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
     </row>
-    <row r="838" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:2" ht="15.75">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
     </row>
-    <row r="839" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:2" ht="15.75">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
     </row>
-    <row r="840" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:2" ht="15.75">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
     </row>
-    <row r="841" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:2" ht="15.75">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
     </row>
-    <row r="842" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:2" ht="15.75">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
     </row>
-    <row r="843" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:2" ht="15.75">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
     </row>
-    <row r="844" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:2" ht="15.75">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
     </row>
-    <row r="845" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:2" ht="15.75">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
     </row>
-    <row r="846" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:2" ht="15.75">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
     </row>
-    <row r="847" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:2" ht="15.75">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
     </row>
-    <row r="848" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:2" ht="15.75">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
     </row>
-    <row r="849" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:2" ht="15.75">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
     </row>
-    <row r="850" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:2" ht="15.75">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
     </row>
-    <row r="851" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:2" ht="15.75">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
     </row>
-    <row r="852" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:2" ht="15.75">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
     </row>
-    <row r="853" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:2" ht="15.75">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
     </row>
-    <row r="854" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:2" ht="15.75">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
     </row>
-    <row r="855" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:2" ht="15.75">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
     </row>
-    <row r="856" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:2" ht="15.75">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
     </row>
-    <row r="857" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:2" ht="15.75">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
     </row>
-    <row r="858" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:2" ht="15.75">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
     </row>
-    <row r="859" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:2" ht="15.75">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
     </row>
-    <row r="860" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:2" ht="15.75">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
     </row>
-    <row r="861" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:2" ht="15.75">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
     </row>
-    <row r="862" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:2" ht="15.75">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
     </row>
-    <row r="863" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:2" ht="15.75">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
     </row>
-    <row r="864" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:2" ht="15.75">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
     </row>
-    <row r="865" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:2" ht="15.75">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
     </row>
-    <row r="866" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:2" ht="15.75">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
     </row>
-    <row r="867" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:2" ht="15.75">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
     </row>
-    <row r="868" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:2" ht="15.75">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
     </row>
-    <row r="869" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:2" ht="15.75">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
     </row>
-    <row r="870" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:2" ht="15.75">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
     </row>
-    <row r="871" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:2" ht="15.75">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
     </row>
-    <row r="872" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:2" ht="15.75">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
     </row>
-    <row r="873" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:2" ht="15.75">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
     </row>
-    <row r="874" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:2" ht="15.75">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
     </row>
-    <row r="875" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:2" ht="15.75">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
     </row>
-    <row r="876" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:2" ht="15.75">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
     </row>
-    <row r="877" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:2" ht="15.75">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
     </row>
-    <row r="878" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:2" ht="15.75">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
     </row>
-    <row r="879" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:2" ht="15.75">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
     </row>
-    <row r="880" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:2" ht="15.75">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
     </row>
-    <row r="881" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:2" ht="15.75">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
     </row>
-    <row r="882" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:2" ht="15.75">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
     </row>
-    <row r="883" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:2" ht="15.75">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
     </row>
-    <row r="884" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:2" ht="15.75">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
     </row>
-    <row r="885" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:2" ht="15.75">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
     </row>
-    <row r="886" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:2" ht="15.75">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
     </row>
-    <row r="887" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:2" ht="15.75">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
     </row>
-    <row r="888" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:2" ht="15.75">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
     </row>
-    <row r="889" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:2" ht="15.75">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
     </row>
-    <row r="890" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:2" ht="15.75">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
     </row>
-    <row r="891" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:2" ht="15.75">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
     </row>
-    <row r="892" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:2" ht="15.75">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
     </row>
-    <row r="893" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:2" ht="15.75">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
     </row>
-    <row r="894" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:2" ht="15.75">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
     </row>
-    <row r="895" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:2" ht="15.75">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
     </row>
-    <row r="896" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:2" ht="15.75">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
     </row>
-    <row r="897" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:2" ht="15.75">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
     </row>
-    <row r="898" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:2" ht="15.75">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
     </row>
-    <row r="899" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:2" ht="15.75">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
     </row>
-    <row r="900" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:2" ht="15.75">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
     </row>
-    <row r="901" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:2" ht="15.75">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
     </row>
-    <row r="902" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:2" ht="15.75">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
     </row>
-    <row r="903" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:2" ht="15.75">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
     </row>
-    <row r="904" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:2" ht="15.75">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
     </row>
-    <row r="905" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:2" ht="15.75">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
     </row>
-    <row r="906" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:2" ht="15.75">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
     </row>
-    <row r="907" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:2" ht="15.75">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
     </row>
-    <row r="908" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:2" ht="15.75">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
     </row>
-    <row r="909" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:2" ht="15.75">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
     </row>
-    <row r="910" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:2" ht="15.75">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
     </row>
-    <row r="911" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:2" ht="15.75">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
     </row>
-    <row r="912" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:2" ht="15.75">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
     </row>
-    <row r="913" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:2" ht="15.75">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
     </row>
-    <row r="914" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:2" ht="15.75">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
     </row>
-    <row r="915" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:2" ht="15.75">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
     </row>
-    <row r="916" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:2" ht="15.75">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
     </row>
-    <row r="917" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:2" ht="15.75">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
     </row>
-    <row r="918" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:2" ht="15.75">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
     </row>
-    <row r="919" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:2" ht="15.75">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
     </row>
-    <row r="920" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:2" ht="15.75">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
     </row>
-    <row r="921" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:2" ht="15.75">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
     </row>
-    <row r="922" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:2" ht="15.75">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
     </row>
-    <row r="923" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:2" ht="15.75">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
     </row>
-    <row r="924" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:2" ht="15.75">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
     </row>
-    <row r="925" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:2" ht="15.75">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
     </row>
-    <row r="926" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:2" ht="15.75">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
     </row>
-    <row r="927" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:2" ht="15.75">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
     </row>
-    <row r="928" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:2" ht="15.75">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
     </row>
-    <row r="929" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:2" ht="15.75">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
     </row>
-    <row r="930" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:2" ht="15.75">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
     </row>
-    <row r="931" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:2" ht="15.75">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
     </row>
-    <row r="932" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:2" ht="15.75">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
     </row>
-    <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:2" ht="15.75">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
     </row>
-    <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:2" ht="15.75">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
     </row>
-    <row r="935" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:2" ht="15.75">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
     </row>
-    <row r="936" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:2" ht="15.75">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
     </row>
-    <row r="937" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:2" ht="15.75">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
     </row>
-    <row r="938" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:2" ht="15.75">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
     </row>
-    <row r="939" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:2" ht="15.75">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
     </row>
-    <row r="940" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:2" ht="15.75">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
     </row>
-    <row r="941" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:2" ht="15.75">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
     </row>
-    <row r="942" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:2" ht="15.75">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
     </row>
-    <row r="943" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:2" ht="15.75">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
     </row>
-    <row r="944" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:2" ht="15.75">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
     </row>
-    <row r="945" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:2" ht="15.75">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
     </row>
-    <row r="946" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:2" ht="15.75">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
     </row>
-    <row r="947" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:2" ht="15.75">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
     </row>
-    <row r="948" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:2" ht="15.75">
       <c r="A948" s="2"/>
       <c r="B948" s="1"/>
     </row>
-    <row r="949" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:2" ht="15.75">
       <c r="A949" s="2"/>
       <c r="B949" s="1"/>
     </row>
-    <row r="950" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:2" ht="15.75">
       <c r="A950" s="2"/>
       <c r="B950" s="1"/>
     </row>
-    <row r="951" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:2" ht="15.75">
       <c r="A951" s="2"/>
       <c r="B951" s="1"/>
     </row>
-    <row r="952" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:2" ht="15.75">
       <c r="A952" s="2"/>
       <c r="B952" s="1"/>
     </row>
-    <row r="953" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:2" ht="15.75">
       <c r="A953" s="2"/>
       <c r="B953" s="1"/>
     </row>
-    <row r="954" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:2" ht="15.75">
       <c r="A954" s="2"/>
       <c r="B954" s="1"/>
     </row>
-    <row r="955" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:2" ht="15.75">
       <c r="A955" s="2"/>
       <c r="B955" s="1"/>
     </row>
-    <row r="956" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:2" ht="15.75">
       <c r="A956" s="2"/>
       <c r="B956" s="1"/>
     </row>
-    <row r="957" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:2" ht="15.75">
       <c r="A957" s="2"/>
       <c r="B957" s="1"/>
     </row>
-    <row r="958" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:2" ht="15.75">
       <c r="A958" s="2"/>
       <c r="B958" s="1"/>
     </row>
-    <row r="959" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:2" ht="15.75">
       <c r="A959" s="2"/>
       <c r="B959" s="1"/>
     </row>
-    <row r="960" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:2" ht="15.75">
       <c r="A960" s="2"/>
       <c r="B960" s="1"/>
     </row>
-    <row r="961" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:2" ht="15.75">
       <c r="A961" s="2"/>
       <c r="B961" s="1"/>
     </row>
-    <row r="962" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:2" ht="15.75">
       <c r="A962" s="2"/>
       <c r="B962" s="1"/>
     </row>
-    <row r="963" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:2" ht="15.75">
       <c r="A963" s="2"/>
       <c r="B963" s="1"/>
     </row>
-    <row r="964" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:2" ht="15.75">
       <c r="A964" s="2"/>
       <c r="B964" s="1"/>
     </row>
-    <row r="965" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:2" ht="15.75">
       <c r="A965" s="2"/>
       <c r="B965" s="1"/>
     </row>
-    <row r="966" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:2" ht="15.75">
       <c r="A966" s="2"/>
       <c r="B966" s="1"/>
     </row>
-    <row r="967" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:2" ht="15.75">
       <c r="A967" s="2"/>
       <c r="B967" s="1"/>
     </row>
-    <row r="968" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:2" ht="15.75">
       <c r="A968" s="2"/>
       <c r="B968" s="1"/>
     </row>
-    <row r="969" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:2" ht="15.75">
       <c r="A969" s="2"/>
       <c r="B969" s="1"/>
     </row>
-    <row r="970" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:2" ht="15.75">
       <c r="A970" s="2"/>
       <c r="B970" s="1"/>
     </row>
-    <row r="971" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:2" ht="15.75">
       <c r="A971" s="2"/>
       <c r="B971" s="1"/>
     </row>
-    <row r="972" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:2" ht="15.75">
       <c r="A972" s="2"/>
       <c r="B972" s="1"/>
     </row>
-    <row r="973" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:2" ht="15.75">
       <c r="A973" s="2"/>
       <c r="B973" s="1"/>
     </row>
-    <row r="974" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:2" ht="15.75">
       <c r="A974" s="2"/>
       <c r="B974" s="1"/>
     </row>
-    <row r="975" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:2" ht="15.75">
       <c r="A975" s="2"/>
       <c r="B975" s="1"/>
     </row>
-    <row r="976" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:2" ht="15.75">
       <c r="A976" s="2"/>
       <c r="B976" s="1"/>
     </row>
-    <row r="977" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:2" ht="15.75">
       <c r="A977" s="2"/>
       <c r="B977" s="1"/>
     </row>
-    <row r="978" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:2" ht="15.75">
       <c r="A978" s="2"/>
       <c r="B978" s="1"/>
     </row>
-    <row r="979" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:2" ht="15.75">
       <c r="A979" s="2"/>
       <c r="B979" s="1"/>
     </row>
-    <row r="980" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:2" ht="15.75">
       <c r="A980" s="2"/>
       <c r="B980" s="1"/>
     </row>
-    <row r="981" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:2" ht="15.75">
       <c r="A981" s="2"/>
       <c r="B981" s="1"/>
     </row>
-    <row r="982" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:2" ht="15.75">
       <c r="A982" s="2"/>
       <c r="B982" s="1"/>
     </row>
-    <row r="983" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:2" ht="15.75">
       <c r="A983" s="2"/>
       <c r="B983" s="1"/>
     </row>
-    <row r="984" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:2" ht="15.75">
       <c r="A984" s="2"/>
       <c r="B984" s="1"/>
     </row>
-    <row r="985" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:2" ht="15.75">
       <c r="A985" s="2"/>
       <c r="B985" s="1"/>
     </row>
-    <row r="986" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:2" ht="15.75">
       <c r="A986" s="2"/>
       <c r="B986" s="1"/>
     </row>
-    <row r="987" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:2" ht="15.75">
       <c r="A987" s="2"/>
       <c r="B987" s="1"/>
     </row>
-    <row r="988" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:2" ht="15.75">
       <c r="A988" s="2"/>
       <c r="B988" s="1"/>
     </row>
-    <row r="989" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:2" ht="15.75">
       <c r="A989" s="2"/>
       <c r="B989" s="1"/>
     </row>
-    <row r="990" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:2" ht="15.75">
       <c r="A990" s="2"/>
       <c r="B990" s="1"/>
     </row>
-    <row r="991" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:2" ht="15.75">
       <c r="A991" s="2"/>
       <c r="B991" s="1"/>
     </row>
-    <row r="992" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:2" ht="15.75">
       <c r="A992" s="2"/>
       <c r="B992" s="1"/>
     </row>
-    <row r="993" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:2" ht="15.75">
       <c r="A993" s="2"/>
       <c r="B993" s="1"/>
     </row>
-    <row r="994" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:2" ht="15.75">
       <c r="A994" s="2"/>
       <c r="B994" s="1"/>
     </row>
-    <row r="995" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:2" ht="15.75">
       <c r="A995" s="2"/>
       <c r="B995" s="1"/>
     </row>
-    <row r="996" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:2" ht="15.75">
       <c r="A996" s="2"/>
       <c r="B996" s="1"/>
     </row>
-    <row r="997" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:2" ht="15.75">
       <c r="A997" s="2"/>
       <c r="B997" s="1"/>
     </row>
-    <row r="998" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:2" ht="15.75">
       <c r="A998" s="2"/>
       <c r="B998" s="1"/>
     </row>
-    <row r="999" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:2" ht="15.75">
       <c r="A999" s="2"/>
       <c r="B999" s="1"/>
     </row>
-    <row r="1000" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:2" ht="15.75">
       <c r="A1000" s="2"/>
       <c r="B1000" s="1"/>
     </row>
-    <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:2" ht="15.75">
       <c r="A1001" s="2"/>
       <c r="B1001" s="1"/>
     </row>
-    <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:2" ht="15.75">
       <c r="A1002" s="2"/>
       <c r="B1002" s="1"/>
     </row>
-    <row r="1003" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:2" ht="15.75">
       <c r="A1003" s="2"/>
       <c r="B1003" s="1"/>
     </row>
-    <row r="1004" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:2" ht="15.75">
       <c r="A1004" s="2"/>
       <c r="B1004" s="1"/>
     </row>
-    <row r="1005" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:2" ht="15.75">
       <c r="A1005" s="2"/>
       <c r="B1005" s="1"/>
     </row>
-    <row r="1006" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:2" ht="15.75">
       <c r="A1006" s="2"/>
       <c r="B1006" s="1"/>
     </row>
-    <row r="1007" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:2" ht="15.75">
       <c r="A1007" s="2"/>
       <c r="B1007" s="1"/>
     </row>
-    <row r="1008" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:2" ht="15.75">
       <c r="A1008" s="2"/>
       <c r="B1008" s="1"/>
     </row>
-    <row r="1009" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:2" ht="15.75">
       <c r="A1009" s="2"/>
       <c r="B1009" s="1"/>
     </row>
-    <row r="1010" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:2" ht="15.75">
       <c r="A1010" s="2"/>
       <c r="B1010" s="1"/>
     </row>
-    <row r="1011" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:2" ht="15.75">
       <c r="A1011" s="2"/>
       <c r="B1011" s="1"/>
     </row>
-    <row r="1012" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:2" ht="15.75">
       <c r="A1012" s="2"/>
       <c r="B1012" s="1"/>
     </row>
-    <row r="1013" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:2" ht="15.75">
       <c r="A1013" s="2"/>
       <c r="B1013" s="1"/>
     </row>
-    <row r="1014" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:2" ht="15.75">
       <c r="A1014" s="2"/>
       <c r="B1014" s="1"/>
     </row>
-    <row r="1015" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:2" ht="15.75">
       <c r="A1015" s="2"/>
       <c r="B1015" s="1"/>
     </row>
-    <row r="1016" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:2" ht="15.75">
       <c r="A1016" s="1"/>
       <c r="B1016" s="1"/>
     </row>
-    <row r="1017" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:2" ht="15.75">
       <c r="A1017" s="1"/>
       <c r="B1017" s="1"/>
     </row>
-    <row r="1018" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:2" ht="15.75">
       <c r="A1018" s="1"/>
       <c r="B1018" s="1"/>
     </row>
-    <row r="1019" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:2" ht="15.75">
       <c r="A1019" s="1"/>
       <c r="B1019" s="1"/>
     </row>
-    <row r="1020" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:2" ht="15.75">
       <c r="A1020" s="1"/>
       <c r="B1020" s="1"/>
     </row>
-    <row r="1021" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:2" ht="15.75">
       <c r="A1021" s="1"/>
       <c r="B1021" s="1"/>
     </row>
-    <row r="1022" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:2" ht="15.75">
       <c r="A1022" s="1"/>
       <c r="B1022" s="1"/>
     </row>
-    <row r="1023" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:2" ht="15.75">
       <c r="A1023" s="1"/>
       <c r="B1023" s="1"/>
     </row>
-    <row r="1024" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:2" ht="15.75">
       <c r="A1024" s="1"/>
       <c r="B1024" s="1"/>
     </row>
-    <row r="1025" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:2" ht="15.75">
       <c r="A1025" s="1"/>
       <c r="B1025" s="1"/>
     </row>
-    <row r="1026" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:2" ht="15.75">
       <c r="A1026" s="1"/>
       <c r="B1026" s="1"/>
     </row>
-    <row r="1027" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:2" ht="15.75">
       <c r="A1027" s="1"/>
       <c r="B1027" s="1"/>
     </row>
-    <row r="1028" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:2" ht="15.75">
       <c r="A1028" s="1"/>
       <c r="B1028" s="1"/>
     </row>
-    <row r="1029" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:2" ht="15.75">
       <c r="A1029" s="1"/>
       <c r="B1029" s="1"/>
     </row>
-    <row r="1030" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:2" ht="15.75">
       <c r="A1030" s="1"/>
       <c r="B1030" s="1"/>
     </row>
-    <row r="1031" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:2" ht="15.75">
       <c r="A1031" s="1"/>
       <c r="B1031" s="1"/>
     </row>
-    <row r="1032" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:2" ht="15.75">
       <c r="A1032" s="1"/>
       <c r="B1032" s="1"/>
     </row>
-    <row r="1033" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:2" ht="15.75">
       <c r="A1033" s="1"/>
       <c r="B1033" s="1"/>
     </row>
-    <row r="1034" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:2" ht="15.75">
       <c r="A1034" s="1"/>
       <c r="B1034" s="1"/>
     </row>
-    <row r="1035" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:2" ht="15.75">
       <c r="A1035" s="1"/>
       <c r="B1035" s="1"/>
     </row>
-    <row r="1036" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:2" ht="15.75">
       <c r="A1036" s="1"/>
       <c r="B1036" s="1"/>
     </row>
-    <row r="1037" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:2" ht="15.75">
       <c r="A1037" s="1"/>
       <c r="B1037" s="1"/>
     </row>
-    <row r="1038" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:2" ht="15.75">
       <c r="A1038" s="1"/>
       <c r="B1038" s="1"/>
     </row>
-    <row r="1039" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:2" ht="15.75">
       <c r="A1039" s="1"/>
       <c r="B1039" s="1"/>
     </row>
-    <row r="1040" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:2" ht="15.75">
       <c r="A1040" s="1"/>
       <c r="B1040" s="1"/>
     </row>
-    <row r="1041" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:2" ht="15.75">
       <c r="A1041" s="1"/>
       <c r="B1041" s="1"/>
     </row>
-    <row r="1042" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:2" ht="15.75">
       <c r="A1042" s="1"/>
       <c r="B1042" s="1"/>
     </row>
-    <row r="1043" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:2" ht="15.75">
       <c r="A1043" s="1"/>
       <c r="B1043" s="1"/>
     </row>
-    <row r="1044" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:2" ht="15.75">
       <c r="A1044" s="1"/>
       <c r="B1044" s="1"/>
     </row>
-    <row r="1045" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:2" ht="15.75">
       <c r="A1045" s="1"/>
       <c r="B1045" s="1"/>
     </row>
-    <row r="1046" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:2" ht="15.75">
       <c r="A1046" s="1"/>
       <c r="B1046" s="1"/>
     </row>
-    <row r="1047" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:2" ht="15.75">
       <c r="A1047" s="1"/>
       <c r="B1047" s="1"/>
     </row>
-    <row r="1048" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:2" ht="15.75">
       <c r="A1048" s="1"/>
       <c r="B1048" s="1"/>
     </row>
-    <row r="1049" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:2" ht="15.75">
       <c r="A1049" s="1"/>
       <c r="B1049" s="1"/>
     </row>
-    <row r="1050" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:2" ht="15.75">
       <c r="A1050" s="1"/>
       <c r="B1050" s="1"/>
     </row>
-    <row r="1051" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:2" ht="15.75">
       <c r="A1051" s="1"/>
       <c r="B1051" s="1"/>
     </row>
-    <row r="1052" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:2" ht="15.75">
       <c r="A1052" s="1"/>
       <c r="B1052" s="1"/>
     </row>
-    <row r="1053" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:2" ht="15.75">
       <c r="A1053" s="1"/>
       <c r="B1053" s="1"/>
     </row>
-    <row r="1054" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:2" ht="15.75">
       <c r="A1054" s="1"/>
       <c r="B1054" s="1"/>
     </row>
-    <row r="1055" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:2" ht="15.75">
       <c r="A1055" s="1"/>
       <c r="B1055" s="1"/>
     </row>
-    <row r="1056" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:2" ht="15.75">
       <c r="A1056" s="1"/>
       <c r="B1056" s="1"/>
     </row>
-    <row r="1057" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:2" ht="15.75">
       <c r="A1057" s="1"/>
       <c r="B1057" s="1"/>
     </row>
-    <row r="1058" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:2" ht="15.75">
       <c r="A1058" s="1"/>
       <c r="B1058" s="1"/>
     </row>
-    <row r="1059" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:2" ht="15.75">
       <c r="A1059" s="1"/>
       <c r="B1059" s="1"/>
     </row>
-    <row r="1060" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:2" ht="15.75">
       <c r="A1060" s="1"/>
       <c r="B1060" s="1"/>
     </row>
-    <row r="1061" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:2" ht="15.75">
       <c r="A1061" s="1"/>
       <c r="B1061" s="1"/>
     </row>
-    <row r="1062" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:2" ht="15.75">
       <c r="A1062" s="1"/>
       <c r="B1062" s="1"/>
     </row>
-    <row r="1063" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:2" ht="15.75">
       <c r="A1063" s="1"/>
       <c r="B1063" s="1"/>
     </row>
-    <row r="1064" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:2" ht="15.75">
       <c r="A1064" s="1"/>
       <c r="B1064" s="1"/>
     </row>
-    <row r="1065" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:2" ht="15.75">
       <c r="A1065" s="1"/>
       <c r="B1065" s="1"/>
     </row>
-    <row r="1066" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:2" ht="15.75">
       <c r="A1066" s="1"/>
       <c r="B1066" s="1"/>
     </row>
-    <row r="1067" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1067" spans="1:2" ht="15.75">
       <c r="A1067" s="1"/>
       <c r="B1067" s="1"/>
     </row>
-    <row r="1068" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1068" spans="1:2" ht="15.75">
       <c r="A1068" s="1"/>
       <c r="B1068" s="1"/>
     </row>
-    <row r="1069" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1069" spans="1:2" ht="15.75">
       <c r="A1069" s="1"/>
       <c r="B1069" s="1"/>
     </row>
-    <row r="1070" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1070" spans="1:2" ht="15.75">
       <c r="A1070" s="1"/>
       <c r="B1070" s="1"/>
     </row>
-    <row r="1071" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1071" spans="1:2" ht="15.75">
       <c r="A1071" s="1"/>
       <c r="B1071" s="1"/>
     </row>
-    <row r="1072" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1072" spans="1:2" ht="15.75">
       <c r="A1072" s="1"/>
       <c r="B1072" s="1"/>
     </row>
-    <row r="1073" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:2" ht="15.75">
       <c r="A1073" s="1"/>
       <c r="B1073" s="1"/>
     </row>
-    <row r="1074" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:2" ht="15.75">
       <c r="A1074" s="1"/>
       <c r="B1074" s="1"/>
     </row>
-    <row r="1075" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:2" ht="15.75">
       <c r="A1075" s="1"/>
       <c r="B1075" s="1"/>
     </row>
-    <row r="1076" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:2" ht="15.75">
       <c r="A1076" s="1"/>
       <c r="B1076" s="1"/>
     </row>
-    <row r="1077" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:2" ht="15.75">
       <c r="A1077" s="1"/>
       <c r="B1077" s="1"/>
     </row>
-    <row r="1078" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:2" ht="15.75">
       <c r="A1078" s="1"/>
       <c r="B1078" s="1"/>
     </row>
-    <row r="1079" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:2" ht="15.75">
       <c r="A1079" s="1"/>
       <c r="B1079" s="1"/>
     </row>
-    <row r="1080" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:2" ht="15.75">
       <c r="A1080" s="1"/>
       <c r="B1080" s="1"/>
     </row>
-    <row r="1081" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:2" ht="15.75">
       <c r="A1081" s="1"/>
       <c r="B1081" s="1"/>
     </row>
-    <row r="1082" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1082" spans="1:2" ht="15.75">
       <c r="A1082" s="1"/>
       <c r="B1082" s="1"/>
     </row>
-    <row r="1083" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1083" spans="1:2" ht="15.75">
       <c r="A1083" s="1"/>
       <c r="B1083" s="1"/>
     </row>
-    <row r="1084" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1084" spans="1:2" ht="15.75">
       <c r="A1084" s="1"/>
       <c r="B1084" s="1"/>
     </row>
-    <row r="1085" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1085" spans="1:2" ht="15.75">
       <c r="A1085" s="1"/>
       <c r="B1085" s="1"/>
     </row>
-    <row r="1086" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:2" ht="15.75">
       <c r="A1086" s="1"/>
       <c r="B1086" s="1"/>
     </row>
-    <row r="1087" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:2" ht="15.75">
       <c r="A1087" s="1"/>
       <c r="B1087" s="1"/>
     </row>
-    <row r="1088" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1088" spans="1:2" ht="15.75">
       <c r="A1088" s="1"/>
       <c r="B1088" s="1"/>
     </row>
-    <row r="1089" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1089" spans="1:2" ht="15.75">
       <c r="A1089" s="1"/>
       <c r="B1089" s="1"/>
     </row>
-    <row r="1090" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1090" spans="1:2" ht="15.75">
       <c r="A1090" s="1"/>
       <c r="B1090" s="1"/>
     </row>
-    <row r="1091" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:2" ht="15.75">
       <c r="A1091" s="1"/>
       <c r="B1091" s="1"/>
     </row>
-    <row r="1092" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:2" ht="15.75">
       <c r="A1092" s="1"/>
       <c r="B1092" s="1"/>
     </row>
-    <row r="1093" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:2" ht="15.75">
       <c r="A1093" s="1"/>
       <c r="B1093" s="1"/>
     </row>
-    <row r="1094" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1094" spans="1:2" ht="15.75">
       <c r="A1094" s="1"/>
       <c r="B1094" s="1"/>
     </row>
-    <row r="1095" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:2" ht="15.75">
       <c r="A1095" s="1"/>
       <c r="B1095" s="1"/>
     </row>
-    <row r="1096" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:2" ht="15.75">
       <c r="A1096" s="1"/>
       <c r="B1096" s="1"/>
     </row>
-    <row r="1097" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1097" spans="1:2" ht="15.75">
       <c r="A1097" s="1"/>
       <c r="B1097" s="1"/>
     </row>
-    <row r="1098" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1098" spans="1:2" ht="15.75">
       <c r="A1098" s="1"/>
       <c r="B1098" s="1"/>
     </row>
-    <row r="1099" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:2" ht="15.75">
       <c r="A1099" s="1"/>
       <c r="B1099" s="1"/>
     </row>
-    <row r="1100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:2" ht="15.75">
       <c r="A1100" s="1"/>
       <c r="B1100" s="1"/>
     </row>
-    <row r="1101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:2" ht="15.75">
       <c r="A1101" s="1"/>
       <c r="B1101" s="1"/>
     </row>
-    <row r="1102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1102" spans="1:2" ht="15.75">
       <c r="A1102" s="1"/>
       <c r="B1102" s="1"/>
     </row>
-    <row r="1103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:2" ht="15.75">
       <c r="A1103" s="1"/>
       <c r="B1103" s="1"/>
     </row>
-    <row r="1104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1104" spans="1:2" ht="15.75">
       <c r="A1104" s="1"/>
       <c r="B1104" s="1"/>
     </row>
-    <row r="1105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1105" spans="1:2" ht="15.75">
       <c r="A1105" s="1"/>
       <c r="B1105" s="1"/>
     </row>
-    <row r="1106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1106" spans="1:2" ht="15.75">
       <c r="A1106" s="1"/>
       <c r="B1106" s="1"/>
     </row>
-    <row r="1107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1107" spans="1:2" ht="15.75">
       <c r="A1107" s="1"/>
       <c r="B1107" s="1"/>
     </row>
-    <row r="1108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1108" spans="1:2" ht="15.75">
       <c r="A1108" s="1"/>
       <c r="B1108" s="1"/>
     </row>
-    <row r="1109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1109" spans="1:2" ht="15.75">
       <c r="A1109" s="1"/>
       <c r="B1109" s="1"/>
     </row>
-    <row r="1110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1110" spans="1:2" ht="15.75">
       <c r="A1110" s="1"/>
       <c r="B1110" s="1"/>
     </row>
-    <row r="1111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:2" ht="15.75">
       <c r="A1111" s="1"/>
       <c r="B1111" s="1"/>
     </row>
-    <row r="1112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1112" spans="1:2" ht="15.75">
       <c r="A1112" s="1"/>
       <c r="B1112" s="1"/>
     </row>
-    <row r="1113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1113" spans="1:2" ht="15.75">
       <c r="A1113" s="1"/>
       <c r="B1113" s="1"/>
     </row>
-    <row r="1114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1114" spans="1:2" ht="15.75">
       <c r="A1114" s="1"/>
       <c r="B1114" s="1"/>
     </row>
-    <row r="1115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1115" spans="1:2" ht="15.75">
       <c r="A1115" s="1"/>
       <c r="B1115" s="1"/>
     </row>
-    <row r="1116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:2" ht="15.75">
       <c r="A1116" s="1"/>
       <c r="B1116" s="1"/>
     </row>
-    <row r="1117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1117" spans="1:2" ht="15.75">
       <c r="A1117" s="1"/>
       <c r="B1117" s="1"/>
     </row>
-    <row r="1118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1118" spans="1:2" ht="15.75">
       <c r="A1118" s="1"/>
       <c r="B1118" s="1"/>
     </row>
-    <row r="1119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1119" spans="1:2" ht="15.75">
       <c r="A1119" s="1"/>
       <c r="B1119" s="1"/>
     </row>
-    <row r="1120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1120" spans="1:2" ht="15.75">
       <c r="A1120" s="1"/>
       <c r="B1120" s="1"/>
     </row>
-    <row r="1121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1121" spans="1:2" ht="15.75">
       <c r="A1121" s="1"/>
       <c r="B1121" s="1"/>
     </row>
-    <row r="1122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1122" spans="1:2" ht="15.75">
       <c r="A1122" s="1"/>
       <c r="B1122" s="1"/>
     </row>
-    <row r="1123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1123" spans="1:2" ht="15.75">
       <c r="A1123" s="1"/>
       <c r="B1123" s="1"/>
     </row>
-    <row r="1124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1124" spans="1:2" ht="15.75">
       <c r="A1124" s="1"/>
       <c r="B1124" s="1"/>
     </row>
-    <row r="1125" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1125" spans="1:2" ht="15.75">
       <c r="A1125" s="1"/>
       <c r="B1125" s="1"/>
     </row>
-    <row r="1126" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1126" spans="1:2" ht="15.75">
       <c r="A1126" s="1"/>
       <c r="B1126" s="1"/>
     </row>
-    <row r="1127" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1127" spans="1:2" ht="15.75">
       <c r="A1127" s="1"/>
       <c r="B1127" s="1"/>
     </row>
-    <row r="1128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1128" spans="1:2" ht="15.75">
       <c r="A1128" s="1"/>
       <c r="B1128" s="1"/>
     </row>
-    <row r="1129" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1129" spans="1:2" ht="15.75">
       <c r="A1129" s="1"/>
       <c r="B1129" s="1"/>
     </row>
-    <row r="1130" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1130" spans="1:2" ht="15.75">
       <c r="A1130" s="1"/>
       <c r="B1130" s="1"/>
     </row>
-    <row r="1131" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1131" spans="1:2" ht="15.75">
       <c r="A1131" s="1"/>
       <c r="B1131" s="1"/>
     </row>
-    <row r="1132" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1132" spans="1:2" ht="15.75">
       <c r="A1132" s="1"/>
       <c r="B1132" s="1"/>
     </row>
-    <row r="1133" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1133" spans="1:2" ht="15.75">
       <c r="A1133" s="1"/>
       <c r="B1133" s="1"/>
     </row>
-    <row r="1134" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1134" spans="1:2" ht="15.75">
       <c r="A1134" s="1"/>
       <c r="B1134" s="1"/>
     </row>
-    <row r="1135" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1135" spans="1:2" ht="15.75">
       <c r="A1135" s="1"/>
       <c r="B1135" s="1"/>
     </row>
-    <row r="1136" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1136" spans="1:2" ht="15.75">
       <c r="A1136" s="1"/>
       <c r="B1136" s="1"/>
     </row>
-    <row r="1137" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1137" spans="1:2" ht="15.75">
       <c r="A1137" s="1"/>
       <c r="B1137" s="1"/>
     </row>
-    <row r="1138" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1138" spans="1:2" ht="15.75">
       <c r="A1138" s="1"/>
       <c r="B1138" s="1"/>
     </row>
-    <row r="1139" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1139" spans="1:2" ht="15.75">
       <c r="A1139" s="1"/>
       <c r="B1139" s="1"/>
     </row>
-    <row r="1140" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1140" spans="1:2" ht="15.75">
       <c r="A1140" s="1"/>
       <c r="B1140" s="1"/>
     </row>
-    <row r="1141" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1141" spans="1:2" ht="15.75">
       <c r="A1141" s="1"/>
       <c r="B1141" s="1"/>
     </row>
-    <row r="1142" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1142" spans="1:2" ht="15.75">
       <c r="A1142" s="1"/>
       <c r="B1142" s="1"/>
     </row>
-    <row r="1143" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1143" spans="1:2" ht="15.75">
       <c r="A1143" s="1"/>
       <c r="B1143" s="1"/>
     </row>
-    <row r="1144" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1144" spans="1:2" ht="15.75">
       <c r="A1144" s="1"/>
       <c r="B1144" s="1"/>
     </row>
-    <row r="1145" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1145" spans="1:2" ht="15.75">
       <c r="A1145" s="1"/>
       <c r="B1145" s="1"/>
     </row>
-    <row r="1146" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1146" spans="1:2" ht="15.75">
       <c r="A1146" s="1"/>
       <c r="B1146" s="1"/>
     </row>
-    <row r="1147" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1147" spans="1:2" ht="15.75">
       <c r="A1147" s="1"/>
       <c r="B1147" s="1"/>
     </row>
-    <row r="1148" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1148" spans="1:2" ht="15.75">
       <c r="A1148" s="1"/>
       <c r="B1148" s="1"/>
     </row>
-    <row r="1149" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1149" spans="1:2" ht="15.75">
       <c r="A1149" s="1"/>
       <c r="B1149" s="1"/>
     </row>
-    <row r="1150" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1150" spans="1:2" ht="15.75">
       <c r="A1150" s="1"/>
       <c r="B1150" s="1"/>
     </row>
-    <row r="1151" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1151" spans="1:2" ht="15.75">
       <c r="A1151" s="1"/>
       <c r="B1151" s="1"/>
     </row>
-    <row r="1152" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1152" spans="1:2" ht="15.75">
       <c r="A1152" s="1"/>
       <c r="B1152" s="1"/>
     </row>
-    <row r="1153" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1153" spans="1:2" ht="15.75">
       <c r="A1153" s="1"/>
       <c r="B1153" s="1"/>
     </row>
-    <row r="1154" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1154" spans="1:2" ht="15.75">
       <c r="A1154" s="1"/>
       <c r="B1154" s="1"/>
     </row>
-    <row r="1155" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1155" spans="1:2" ht="15.75">
       <c r="A1155" s="1"/>
       <c r="B1155" s="1"/>
     </row>
-    <row r="1156" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1156" spans="1:2" ht="15.75">
       <c r="A1156" s="1"/>
       <c r="B1156" s="1"/>
     </row>
-    <row r="1157" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1157" spans="1:2" ht="15.75">
       <c r="A1157" s="1"/>
       <c r="B1157" s="1"/>
     </row>
-    <row r="1158" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1158" spans="1:2" ht="15.75">
       <c r="A1158" s="1"/>
       <c r="B1158" s="1"/>
     </row>
-    <row r="1159" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1159" spans="1:2" ht="15.75">
       <c r="A1159" s="1"/>
       <c r="B1159" s="1"/>
     </row>
-    <row r="1160" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1160" spans="1:2" ht="15.75">
       <c r="A1160" s="1"/>
       <c r="B1160" s="1"/>
     </row>
-    <row r="1161" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1161" spans="1:2" ht="15.75">
       <c r="A1161" s="1"/>
       <c r="B1161" s="1"/>
     </row>
-    <row r="1162" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1162" spans="1:2" ht="15.75">
       <c r="A1162" s="1"/>
       <c r="B1162" s="1"/>
     </row>
-    <row r="1163" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1163" spans="1:2" ht="15.75">
       <c r="A1163" s="1"/>
       <c r="B1163" s="1"/>
     </row>
-    <row r="1164" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1164" spans="1:2" ht="15.75">
       <c r="A1164" s="1"/>
       <c r="B1164" s="1"/>
     </row>
-    <row r="1165" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1165" spans="1:2" ht="15.75">
       <c r="A1165" s="1"/>
       <c r="B1165" s="1"/>
     </row>
-    <row r="1166" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1166" spans="1:2" ht="15.75">
       <c r="A1166" s="1"/>
       <c r="B1166" s="1"/>
     </row>
-    <row r="1167" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1167" spans="1:2" ht="15.75">
       <c r="A1167" s="1"/>
       <c r="B1167" s="1"/>
     </row>
-    <row r="1168" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1168" spans="1:2" ht="15.75">
       <c r="A1168" s="1"/>
       <c r="B1168" s="1"/>
     </row>
-    <row r="1169" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1169" spans="1:2" ht="15.75">
       <c r="A1169" s="1"/>
       <c r="B1169" s="1"/>
     </row>
-    <row r="1170" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1170" spans="1:2" ht="15.75">
       <c r="A1170" s="1"/>
       <c r="B1170" s="1"/>
     </row>
-    <row r="1171" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1171" spans="1:2" ht="15.75">
       <c r="A1171" s="1"/>
       <c r="B1171" s="1"/>
     </row>
-    <row r="1172" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1172" spans="1:2" ht="15.75">
       <c r="A1172" s="1"/>
       <c r="B1172" s="1"/>
     </row>
-    <row r="1173" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1173" spans="1:2" ht="15.75">
       <c r="A1173" s="1"/>
       <c r="B1173" s="1"/>
     </row>
-    <row r="1174" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1174" spans="1:2" ht="15.75">
       <c r="A1174" s="1"/>
       <c r="B1174" s="1"/>
     </row>
-    <row r="1175" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1175" spans="1:2" ht="15.75">
       <c r="A1175" s="1"/>
       <c r="B1175" s="1"/>
     </row>
-    <row r="1176" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1176" spans="1:2" ht="15.75">
       <c r="A1176" s="1"/>
       <c r="B1176" s="1"/>
     </row>
-    <row r="1177" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1177" spans="1:2" ht="15.75">
       <c r="A1177" s="1"/>
       <c r="B1177" s="1"/>
     </row>
-    <row r="1178" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1178" spans="1:2" ht="15.75">
       <c r="A1178" s="1"/>
       <c r="B1178" s="1"/>
     </row>
-    <row r="1179" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1179" spans="1:2" ht="15.75">
       <c r="A1179" s="1"/>
       <c r="B1179" s="1"/>
     </row>
-    <row r="1180" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1180" spans="1:2" ht="15.75">
       <c r="A1180" s="1"/>
       <c r="B1180" s="1"/>
     </row>
-    <row r="1181" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1181" spans="1:2" ht="15.75">
       <c r="A1181" s="1"/>
       <c r="B1181" s="1"/>
     </row>
-    <row r="1182" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1182" spans="1:2" ht="15.75">
       <c r="A1182" s="1"/>
       <c r="B1182" s="1"/>
     </row>
-    <row r="1183" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1183" spans="1:2" ht="15.75">
       <c r="A1183" s="1"/>
       <c r="B1183" s="1"/>
     </row>
-    <row r="1184" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1184" spans="1:2" ht="15.75">
       <c r="A1184" s="1"/>
       <c r="B1184" s="1"/>
     </row>
-    <row r="1185" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1185" spans="1:2" ht="15.75">
       <c r="A1185" s="1"/>
       <c r="B1185" s="1"/>
     </row>
-    <row r="1186" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1186" spans="1:2" ht="15.75">
       <c r="A1186" s="1"/>
       <c r="B1186" s="1"/>
     </row>
-    <row r="1187" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1187" spans="1:2" ht="15.75">
       <c r="A1187" s="1"/>
       <c r="B1187" s="1"/>
     </row>
-    <row r="1188" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1188" spans="1:2" ht="15.75">
       <c r="A1188" s="1"/>
       <c r="B1188" s="1"/>
     </row>
-    <row r="1189" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1189" spans="1:2" ht="15.75">
       <c r="A1189" s="1"/>
       <c r="B1189" s="1"/>
     </row>
-    <row r="1190" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1190" spans="1:2" ht="15.75">
       <c r="A1190" s="1"/>
       <c r="B1190" s="1"/>
     </row>
-    <row r="1191" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1191" spans="1:2" ht="15.75">
       <c r="A1191" s="1"/>
       <c r="B1191" s="1"/>
     </row>
-    <row r="1192" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1192" spans="1:2" ht="15.75">
       <c r="A1192" s="1"/>
       <c r="B1192" s="1"/>
     </row>
-    <row r="1193" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1193" spans="1:2" ht="15.75">
       <c r="A1193" s="1"/>
       <c r="B1193" s="1"/>
     </row>
-    <row r="1194" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1194" spans="1:2" ht="15.75">
       <c r="A1194" s="1"/>
       <c r="B1194" s="1"/>
     </row>
-    <row r="1195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1195" spans="1:2" ht="15.75">
       <c r="A1195" s="1"/>
       <c r="B1195" s="1"/>
     </row>
-    <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1196" spans="1:2" ht="15.75">
       <c r="A1196" s="1"/>
       <c r="B1196" s="1"/>
     </row>
-    <row r="1197" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1197" spans="1:2" ht="15.75">
       <c r="A1197" s="1"/>
       <c r="B1197" s="1"/>
     </row>
-    <row r="1198" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1198" spans="1:2" ht="15.75">
       <c r="A1198" s="1"/>
       <c r="B1198" s="1"/>
     </row>
-    <row r="1199" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1199" spans="1:2" ht="15.75">
       <c r="A1199" s="1"/>
       <c r="B1199" s="1"/>
     </row>
-    <row r="1200" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1200" spans="1:2" ht="15.75">
       <c r="A1200" s="1"/>
       <c r="B1200" s="1"/>
     </row>
-    <row r="1201" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1201" spans="1:2" ht="15.75">
       <c r="A1201" s="1"/>
       <c r="B1201" s="1"/>
     </row>
-    <row r="1202" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1202" spans="1:2" ht="15.75">
       <c r="A1202" s="1"/>
       <c r="B1202" s="1"/>
     </row>
-    <row r="1203" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1203" spans="1:2" ht="15.75">
       <c r="A1203" s="1"/>
       <c r="B1203" s="1"/>
     </row>
-    <row r="1204" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1204" spans="1:2" ht="15.75">
       <c r="A1204" s="1"/>
       <c r="B1204" s="1"/>
     </row>
-    <row r="1205" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1205" spans="1:2" ht="15.75">
       <c r="A1205" s="1"/>
       <c r="B1205" s="1"/>
     </row>
-    <row r="1206" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1206" spans="1:2" ht="15.75">
       <c r="A1206" s="1"/>
       <c r="B1206" s="1"/>
     </row>
-    <row r="1207" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1207" spans="1:2" ht="15.75">
       <c r="A1207" s="1"/>
       <c r="B1207" s="1"/>
     </row>
-    <row r="1208" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1208" spans="1:2" ht="15.75">
       <c r="A1208" s="1"/>
       <c r="B1208" s="1"/>
     </row>
-    <row r="1209" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1209" spans="1:2" ht="15.75">
       <c r="A1209" s="1"/>
       <c r="B1209" s="1"/>
     </row>
-    <row r="1210" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1210" spans="1:2" ht="15.75">
       <c r="A1210" s="1"/>
       <c r="B1210" s="1"/>
     </row>
@@ -10585,40 +10585,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA90CD46-FF53-412A-950C-99718992C948}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="4"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="4" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="4" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/dados-catalago-pcm-interno/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-interno/nomes_usuais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados-catalago-pcm-interno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="281" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A9B5BF8-C0C0-434C-98D5-ADE6A0E6428C}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E12C3ED9-BCF8-44EA-9114-C7489D24A71A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="365" spans="1:3" ht="15.75">
       <c r="A365" s="15">
-        <v>1010084315</v>
+        <v>1040077368</v>
       </c>
       <c r="B365" s="5" t="s">
         <v>367</v>
